--- a/bet_log.xlsx
+++ b/bet_log.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -687,7 +687,7 @@
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>22</v>
@@ -828,16 +828,16 @@
         </is>
       </c>
       <c r="G6" s="8" t="n">
-        <v>-146</v>
+        <v>-144</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>0.666</v>
+        <v>0.648</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.5935</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.0725</v>
+        <v>0.0578</v>
       </c>
       <c r="K6" s="11" t="n">
         <v>4.714</v>
@@ -846,7 +846,7 @@
         <v>0.5</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="N6" s="8" t="inlineStr"/>
       <c r="O6" s="12" t="inlineStr"/>
@@ -858,17 +858,17 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Andre Pallante</t>
+          <t>Aaron Civale</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>OAK</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
@@ -880,25 +880,25 @@
         </is>
       </c>
       <c r="G7" s="8" t="n">
-        <v>126</v>
+        <v>-146</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.523</v>
+        <v>0.666</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>0.4425</v>
+        <v>0.5935</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.0805</v>
+        <v>0.0725</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>3.876</v>
+        <v>4.714</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
       <c r="N7" s="8" t="inlineStr"/>
       <c r="O7" s="12" t="inlineStr"/>
@@ -910,47 +910,47 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Max Scherzer</t>
+          <t>José Soriano</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G8" s="8" t="n">
-        <v>-130</v>
+        <v>-110</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>0.652</v>
+        <v>0.676</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>0.5652</v>
+        <v>0.5238</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.0868</v>
+        <v>0.1522</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>4.757</v>
+        <v>5.918</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="N8" s="8" t="inlineStr"/>
       <c r="O8" s="12" t="inlineStr"/>
@@ -962,17 +962,17 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Erick Fedde</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
@@ -984,25 +984,25 @@
         </is>
       </c>
       <c r="G9" s="8" t="n">
-        <v>134</v>
+        <v>-108</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.527</v>
+        <v>0.655</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>0.4274</v>
+        <v>0.5192</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.1358</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>3.852</v>
+        <v>4.719</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.44</v>
+        <v>0.71</v>
       </c>
       <c r="N9" s="8" t="inlineStr"/>
       <c r="O9" s="12" t="inlineStr"/>
@@ -1066,17 +1066,17 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Erick Fedde</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
@@ -1088,25 +1088,25 @@
         </is>
       </c>
       <c r="G11" s="8" t="n">
-        <v>-108</v>
+        <v>134</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.655</v>
+        <v>0.527</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>0.5192</v>
+        <v>0.4274</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.1358</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>4.719</v>
+        <v>3.852</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.71</v>
+        <v>0.44</v>
       </c>
       <c r="N11" s="8" t="inlineStr"/>
       <c r="O11" s="12" t="inlineStr"/>
@@ -1118,493 +1118,445 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>José Soriano</t>
+          <t>Max Scherzer</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G12" s="8" t="n">
-        <v>-110</v>
+        <v>-130</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>0.676</v>
+        <v>0.652</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>0.5238</v>
+        <v>0.5652</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.1522</v>
+        <v>0.0868</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>5.918</v>
+        <v>4.757</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="N12" s="8" t="inlineStr"/>
       <c r="O12" s="12" t="inlineStr"/>
       <c r="P12" s="13" t="inlineStr"/>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="14" t="n">
+      <c r="A13" s="6" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Andre Pallante</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>126</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>0.0805</v>
+      </c>
+      <c r="K13" s="11" t="n">
+        <v>3.876</v>
+      </c>
+      <c r="L13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="11" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="N13" s="8" t="inlineStr"/>
+      <c r="O13" s="12" t="inlineStr"/>
+      <c r="P13" s="13" t="inlineStr"/>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Ryan Feltner</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="K14" s="11" t="n">
+        <v>4.719</v>
+      </c>
+      <c r="L14" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" s="11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N14" s="8" t="inlineStr"/>
+      <c r="O14" s="12" t="inlineStr"/>
+      <c r="P14" s="13" t="inlineStr"/>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="6" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>José Soriano</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>-108</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>0.1528</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>5.918</v>
+      </c>
+      <c r="L15" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" s="11" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="N15" s="8" t="inlineStr"/>
+      <c r="O15" s="12" t="inlineStr"/>
+      <c r="P15" s="13" t="inlineStr"/>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="6" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Max Scherzer</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>-120</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>0.5455</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>0.1145</v>
+      </c>
+      <c r="K16" s="11" t="n">
+        <v>4.757</v>
+      </c>
+      <c r="L16" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M16" s="11" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N16" s="8" t="inlineStr"/>
+      <c r="O16" s="12" t="inlineStr"/>
+      <c r="P16" s="13" t="inlineStr"/>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="6" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Erick Fedde</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>124</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>0.0786</v>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>3.852</v>
+      </c>
+      <c r="L17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="11" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N17" s="8" t="inlineStr"/>
+      <c r="O17" s="12" t="inlineStr"/>
+      <c r="P17" s="13" t="inlineStr"/>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="6" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Andre Pallante</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="K18" s="11" t="n">
+        <v>3.876</v>
+      </c>
+      <c r="L18" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M18" s="11" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N18" s="8" t="inlineStr"/>
+      <c r="O18" s="12" t="inlineStr"/>
+      <c r="P18" s="13" t="inlineStr"/>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="14" t="n">
         <v>46111</v>
       </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>Simeon Woods Richardson</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Jacob Lopez</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>OAK</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G13" s="16" t="n">
-        <v>-112</v>
-      </c>
-      <c r="H13" s="18" t="n">
-        <v>0.783</v>
-      </c>
-      <c r="I13" s="18" t="n">
-        <v>0.5283</v>
-      </c>
-      <c r="J13" s="18" t="n">
-        <v>0.2547</v>
-      </c>
-      <c r="K13" s="19" t="n">
-        <v>5.562</v>
-      </c>
-      <c r="L13" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" s="19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="N13" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="O13" s="20" t="inlineStr">
+      <c r="G19" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="H19" s="18" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="I19" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J19" s="18" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="K19" s="19" t="n">
+        <v>6.418</v>
+      </c>
+      <c r="L19" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="19" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="20" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P13" s="21" t="n">
+      <c r="P19" s="21" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="22" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>Davis Martin</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="E14" s="25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F14" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G14" s="24" t="n">
-        <v>-114</v>
-      </c>
-      <c r="H14" s="26" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="I14" s="26" t="n">
-        <v>0.5327</v>
-      </c>
-      <c r="J14" s="26" t="n">
-        <v>0.0513</v>
-      </c>
-      <c r="K14" s="27" t="n">
-        <v>4.252</v>
-      </c>
-      <c r="L14" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M14" s="27" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="N14" s="24" t="n">
-        <v>6</v>
-      </c>
-      <c r="O14" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P14" s="29" t="n">
-        <v>0.8772</v>
-      </c>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="14" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>Kyle Harrison</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="n">
-        <v>114</v>
-      </c>
-      <c r="H15" s="18" t="n">
-        <v>0.521</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>0.4673</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <v>0.0537</v>
-      </c>
-      <c r="K15" s="19" t="n">
-        <v>4.628</v>
-      </c>
-      <c r="L15" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M15" s="19" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N15" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="O15" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P15" s="21" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="14" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="n">
-        <v>-174</v>
-      </c>
-      <c r="H16" s="18" t="n">
-        <v>0.6889999999999999</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="J16" s="18" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="K16" s="19" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="L16" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M16" s="19" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="N16" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="O16" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P16" s="21" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="14" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>Jacob Lopez</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>OAK</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="n">
-        <v>100</v>
-      </c>
-      <c r="H17" s="18" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J17" s="18" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="K17" s="19" t="n">
-        <v>6.418</v>
-      </c>
-      <c r="L17" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" s="19" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="N17" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P17" s="21" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="22" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>Jack Leiter</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F18" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G18" s="24" t="n">
-        <v>-144</v>
-      </c>
-      <c r="H18" s="26" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="I18" s="26" t="n">
-        <v>0.5901999999999999</v>
-      </c>
-      <c r="J18" s="26" t="n">
-        <v>0.0888</v>
-      </c>
-      <c r="K18" s="27" t="n">
-        <v>6.017</v>
-      </c>
-      <c r="L18" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" s="27" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="N18" s="24" t="n">
-        <v>8</v>
-      </c>
-      <c r="O18" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P18" s="29" t="n">
-        <v>0.6944</v>
-      </c>
-    </row>
-    <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="22" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>Edward Cabrera</t>
-        </is>
-      </c>
-      <c r="C19" s="24" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="E19" s="25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F19" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G19" s="24" t="n">
-        <v>116</v>
-      </c>
-      <c r="H19" s="26" t="n">
-        <v>0.6889999999999999</v>
-      </c>
-      <c r="I19" s="26" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J19" s="26" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="K19" s="27" t="n">
-        <v>5.286</v>
-      </c>
-      <c r="L19" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" s="27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N19" s="24" t="n">
-        <v>5</v>
-      </c>
-      <c r="O19" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P19" s="29" t="n">
-        <v>1.16</v>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="22" t="n">
-        <v>46109</v>
+        <v>46111</v>
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E20" s="25" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
@@ -1612,28 +1564,28 @@
         </is>
       </c>
       <c r="G20" s="24" t="n">
-        <v>140</v>
+        <v>-114</v>
       </c>
       <c r="H20" s="26" t="n">
-        <v>0.476</v>
+        <v>0.584</v>
       </c>
       <c r="I20" s="26" t="n">
-        <v>0.4167</v>
+        <v>0.5327</v>
       </c>
       <c r="J20" s="26" t="n">
-        <v>0.0593</v>
+        <v>0.0513</v>
       </c>
       <c r="K20" s="27" t="n">
-        <v>4.645</v>
+        <v>4.252</v>
       </c>
       <c r="L20" s="25" t="n">
         <v>0.5</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="N20" s="24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O20" s="28" t="inlineStr">
         <is>
@@ -1641,26 +1593,26 @@
         </is>
       </c>
       <c r="P20" s="29" t="n">
-        <v>1.4</v>
+        <v>0.8772</v>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="14" t="n">
-        <v>46109</v>
+        <v>46111</v>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Will Warren</t>
+          <t>Kyle Harrison</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E21" s="17" t="n">
@@ -1668,32 +1620,32 @@
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G21" s="16" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H21" s="18" t="n">
-        <v>0.573</v>
+        <v>0.521</v>
       </c>
       <c r="I21" s="18" t="n">
-        <v>0.4762</v>
+        <v>0.4673</v>
       </c>
       <c r="J21" s="18" t="n">
-        <v>0.0968</v>
+        <v>0.0537</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>5.339</v>
+        <v>4.628</v>
       </c>
       <c r="L21" s="17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>0.46</v>
+        <v>0.25</v>
       </c>
       <c r="N21" s="16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O21" s="20" t="inlineStr">
         <is>
@@ -1706,21 +1658,21 @@
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="14" t="n">
-        <v>46109</v>
+        <v>46111</v>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Jeffrey Springs</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>OAK</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E22" s="17" t="n">
@@ -1732,28 +1684,28 @@
         </is>
       </c>
       <c r="G22" s="16" t="n">
-        <v>102</v>
+        <v>-174</v>
       </c>
       <c r="H22" s="18" t="n">
-        <v>0.599</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="I22" s="18" t="n">
-        <v>0.495</v>
+        <v>0.635</v>
       </c>
       <c r="J22" s="18" t="n">
-        <v>0.104</v>
+        <v>0.054</v>
       </c>
       <c r="K22" s="19" t="n">
-        <v>4.389</v>
+        <v>4.97</v>
       </c>
       <c r="L22" s="17" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M22" s="19" t="n">
-        <v>0.51</v>
+        <v>0.37</v>
       </c>
       <c r="N22" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O22" s="20" t="inlineStr">
         <is>
@@ -1765,82 +1717,82 @@
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="14" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>Eury Pérez</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="n">
-        <v>-154</v>
-      </c>
-      <c r="H23" s="18" t="n">
-        <v>0.713</v>
-      </c>
-      <c r="I23" s="18" t="n">
-        <v>0.6063</v>
-      </c>
-      <c r="J23" s="18" t="n">
-        <v>0.1067</v>
-      </c>
-      <c r="K23" s="19" t="n">
-        <v>5.311</v>
-      </c>
-      <c r="L23" s="17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M23" s="19" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="N23" s="16" t="n">
+      <c r="A23" s="22" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>Jack Leiter</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="n">
+        <v>-144</v>
+      </c>
+      <c r="H23" s="26" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="I23" s="26" t="n">
+        <v>0.5901999999999999</v>
+      </c>
+      <c r="J23" s="26" t="n">
+        <v>0.0888</v>
+      </c>
+      <c r="K23" s="27" t="n">
+        <v>6.017</v>
+      </c>
+      <c r="L23" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="27" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N23" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="O23" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P23" s="21" t="n">
-        <v>-1</v>
+      <c r="O23" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P23" s="29" t="n">
+        <v>0.6944</v>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="14" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Simeon Woods Richardson</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E24" s="17" t="n">
@@ -1852,25 +1804,25 @@
         </is>
       </c>
       <c r="G24" s="16" t="n">
-        <v>-158</v>
+        <v>-112</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>0.677</v>
+        <v>0.783</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.5283</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>0.0646</v>
+        <v>0.2547</v>
       </c>
       <c r="K24" s="19" t="n">
-        <v>4.869</v>
+        <v>5.562</v>
       </c>
       <c r="L24" s="17" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="M24" s="19" t="n">
-        <v>0.42</v>
+        <v>1.35</v>
       </c>
       <c r="N24" s="16" t="n">
         <v>2</v>
@@ -1886,25 +1838,25 @@
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="22" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>Robbie Ray</t>
+          <t>Edward Cabrera</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E25" s="25" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
@@ -1915,25 +1867,25 @@
         <v>116</v>
       </c>
       <c r="H25" s="26" t="n">
-        <v>0.532</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="I25" s="26" t="n">
         <v>0.463</v>
       </c>
       <c r="J25" s="26" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.226</v>
       </c>
       <c r="K25" s="27" t="n">
-        <v>5.578</v>
+        <v>5.286</v>
       </c>
       <c r="L25" s="25" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>0.32</v>
+        <v>1.05</v>
       </c>
       <c r="N25" s="24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O25" s="28" t="inlineStr">
         <is>
@@ -1946,21 +1898,21 @@
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="22" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E26" s="25" t="n">
@@ -1972,299 +1924,299 @@
         </is>
       </c>
       <c r="G26" s="24" t="n">
-        <v>-128</v>
+        <v>140</v>
       </c>
       <c r="H26" s="26" t="n">
-        <v>0.659</v>
+        <v>0.476</v>
       </c>
       <c r="I26" s="26" t="n">
-        <v>0.5614</v>
+        <v>0.4167</v>
       </c>
       <c r="J26" s="26" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.0593</v>
       </c>
       <c r="K26" s="27" t="n">
-        <v>5.818</v>
+        <v>4.645</v>
       </c>
       <c r="L26" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N26" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="O26" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P26" s="29" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="14" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Will Warren</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G27" s="16" t="n">
+        <v>110</v>
+      </c>
+      <c r="H27" s="18" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="I27" s="18" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="J27" s="18" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="K27" s="19" t="n">
+        <v>5.339</v>
+      </c>
+      <c r="L27" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="M26" s="27" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="N26" s="24" t="n">
+      <c r="M27" s="19" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N27" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O27" s="20" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P27" s="21" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="14" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>Jeffrey Springs</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>OAK</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G28" s="16" t="n">
+        <v>102</v>
+      </c>
+      <c r="H28" s="18" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="I28" s="18" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="J28" s="18" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="K28" s="19" t="n">
+        <v>4.389</v>
+      </c>
+      <c r="L28" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M28" s="19" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N28" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O28" s="20" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P28" s="21" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="14" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>Eury Pérez</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G29" s="16" t="n">
+        <v>-154</v>
+      </c>
+      <c r="H29" s="18" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="I29" s="18" t="n">
+        <v>0.6063</v>
+      </c>
+      <c r="J29" s="18" t="n">
+        <v>0.1067</v>
+      </c>
+      <c r="K29" s="19" t="n">
+        <v>5.311</v>
+      </c>
+      <c r="L29" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M29" s="19" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="N29" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="O26" s="28" t="inlineStr">
+      <c r="O29" s="20" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P29" s="21" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="22" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>Robbie Ray</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E30" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="n">
+        <v>116</v>
+      </c>
+      <c r="H30" s="26" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="I30" s="26" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J30" s="26" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="K30" s="27" t="n">
+        <v>5.578</v>
+      </c>
+      <c r="L30" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M30" s="27" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N30" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="O30" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P26" s="29" t="n">
-        <v>0.7812</v>
-      </c>
-    </row>
-    <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="22" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B27" s="23" t="inlineStr">
-        <is>
-          <t>Tarik Skubal</t>
-        </is>
-      </c>
-      <c r="C27" s="24" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="D27" s="24" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E27" s="25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F27" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G27" s="24" t="n">
-        <v>-172</v>
-      </c>
-      <c r="H27" s="26" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="I27" s="26" t="n">
-        <v>0.6324</v>
-      </c>
-      <c r="J27" s="26" t="n">
-        <v>0.1346</v>
-      </c>
-      <c r="K27" s="27" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="L27" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M27" s="27" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="N27" s="24" t="n">
-        <v>6</v>
-      </c>
-      <c r="O27" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P27" s="29" t="n">
-        <v>0.5814</v>
-      </c>
-    </row>
-    <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="22" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B28" s="23" t="inlineStr">
-        <is>
-          <t>Andrew Abbott</t>
-        </is>
-      </c>
-      <c r="C28" s="24" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="D28" s="24" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="E28" s="25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F28" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G28" s="24" t="n">
-        <v>120</v>
-      </c>
-      <c r="H28" s="26" t="n">
-        <v>0.509</v>
-      </c>
-      <c r="I28" s="26" t="n">
-        <v>0.4545</v>
-      </c>
-      <c r="J28" s="26" t="n">
-        <v>0.0545</v>
-      </c>
-      <c r="K28" s="27" t="n">
-        <v>4.814</v>
-      </c>
-      <c r="L28" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M28" s="27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N28" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="O28" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P28" s="29" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="22" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B29" s="23" t="inlineStr">
-        <is>
-          <t>Nick Pivetta</t>
-        </is>
-      </c>
-      <c r="C29" s="24" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="D29" s="24" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="E29" s="25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F29" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G29" s="24" t="n">
-        <v>110</v>
-      </c>
-      <c r="H29" s="26" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I29" s="26" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="J29" s="26" t="n">
-        <v>0.0638</v>
-      </c>
-      <c r="K29" s="27" t="n">
-        <v>5.548</v>
-      </c>
-      <c r="L29" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M29" s="27" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N29" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="O29" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P29" s="29" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="14" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>Jacob Misiorowski</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="n">
-        <v>124</v>
-      </c>
-      <c r="H30" s="18" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I30" s="18" t="n">
-        <v>0.4464</v>
-      </c>
-      <c r="J30" s="18" t="n">
-        <v>0.0736</v>
-      </c>
-      <c r="K30" s="19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L30" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M30" s="19" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="N30" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="O30" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P30" s="21" t="n">
-        <v>-1</v>
+      <c r="P30" s="29" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="14" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Shane Smith</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
@@ -2272,25 +2224,25 @@
         </is>
       </c>
       <c r="G31" s="16" t="n">
-        <v>-114</v>
+        <v>-158</v>
       </c>
       <c r="H31" s="18" t="n">
-        <v>0.607</v>
+        <v>0.677</v>
       </c>
       <c r="I31" s="18" t="n">
-        <v>0.5327</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J31" s="18" t="n">
-        <v>0.0743</v>
+        <v>0.0646</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>5.338</v>
+        <v>4.869</v>
       </c>
       <c r="L31" s="17" t="n">
         <v>0.5</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="N31" s="16" t="n">
         <v>2</v>
@@ -2306,21 +2258,21 @@
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="22" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>José Soriano</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E32" s="25" t="n">
@@ -2332,28 +2284,28 @@
         </is>
       </c>
       <c r="G32" s="24" t="n">
-        <v>108</v>
+        <v>-128</v>
       </c>
       <c r="H32" s="26" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.659</v>
       </c>
       <c r="I32" s="26" t="n">
-        <v>0.4808</v>
+        <v>0.5614</v>
       </c>
       <c r="J32" s="26" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="K32" s="27" t="n">
-        <v>5.163</v>
+        <v>5.818</v>
       </c>
       <c r="L32" s="25" t="n">
         <v>1</v>
       </c>
       <c r="M32" s="27" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N32" s="24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O32" s="28" t="inlineStr">
         <is>
@@ -2361,7 +2313,7 @@
         </is>
       </c>
       <c r="P32" s="29" t="n">
-        <v>1.08</v>
+        <v>0.7812</v>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
@@ -2370,50 +2322,50 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Shane Smith</t>
         </is>
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G33" s="16" t="n">
-        <v>114</v>
+        <v>-114</v>
       </c>
       <c r="H33" s="18" t="n">
-        <v>0.587</v>
+        <v>0.607</v>
       </c>
       <c r="I33" s="18" t="n">
-        <v>0.4673</v>
+        <v>0.5327</v>
       </c>
       <c r="J33" s="18" t="n">
-        <v>0.1197</v>
+        <v>0.0743</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>6.417</v>
+        <v>5.338</v>
       </c>
       <c r="L33" s="17" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="N33" s="16" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O33" s="20" t="inlineStr">
         <is>
@@ -2430,57 +2382,417 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
+          <t>Hunter Brown</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G34" s="16" t="n">
+        <v>114</v>
+      </c>
+      <c r="H34" s="18" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="I34" s="18" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="J34" s="18" t="n">
+        <v>0.1197</v>
+      </c>
+      <c r="K34" s="19" t="n">
+        <v>6.417</v>
+      </c>
+      <c r="L34" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M34" s="19" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="N34" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="O34" s="20" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P34" s="21" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="22" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>José Soriano</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E35" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="n">
+        <v>108</v>
+      </c>
+      <c r="H35" s="26" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I35" s="26" t="n">
+        <v>0.4808</v>
+      </c>
+      <c r="J35" s="26" t="n">
+        <v>0.07920000000000001</v>
+      </c>
+      <c r="K35" s="27" t="n">
+        <v>5.163</v>
+      </c>
+      <c r="L35" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="27" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N35" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="O35" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P35" s="29" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="22" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>Tarik Skubal</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E36" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="n">
+        <v>-172</v>
+      </c>
+      <c r="H36" s="26" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="I36" s="26" t="n">
+        <v>0.6324</v>
+      </c>
+      <c r="J36" s="26" t="n">
+        <v>0.1346</v>
+      </c>
+      <c r="K36" s="27" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="L36" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M36" s="27" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="N36" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="O36" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P36" s="29" t="n">
+        <v>0.5814</v>
+      </c>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="14" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G37" s="16" t="n">
+        <v>124</v>
+      </c>
+      <c r="H37" s="18" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I37" s="18" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="J37" s="18" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="K37" s="19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L37" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M37" s="19" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N37" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="O37" s="20" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P37" s="21" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="22" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>Nick Pivetta</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="E38" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="n">
+        <v>110</v>
+      </c>
+      <c r="H38" s="26" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I38" s="26" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="J38" s="26" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="K38" s="27" t="n">
+        <v>5.548</v>
+      </c>
+      <c r="L38" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M38" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N38" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="O38" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P38" s="29" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="22" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>Andrew Abbott</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="E39" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G39" s="24" t="n">
+        <v>120</v>
+      </c>
+      <c r="H39" s="26" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="I39" s="26" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="J39" s="26" t="n">
+        <v>0.0545</v>
+      </c>
+      <c r="K39" s="27" t="n">
+        <v>4.814</v>
+      </c>
+      <c r="L39" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M39" s="27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N39" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="O39" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P39" s="29" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="14" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
           <t>Matthew Boyd</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C40" s="16" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E34" s="17" t="n">
+      <c r="E40" s="17" t="n">
         <v>4.5</v>
       </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="F40" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G34" s="16" t="n">
+      <c r="G40" s="16" t="n">
         <v>132</v>
       </c>
-      <c r="H34" s="18" t="n">
+      <c r="H40" s="18" t="n">
         <v>0.59</v>
       </c>
-      <c r="I34" s="18" t="n">
+      <c r="I40" s="18" t="n">
         <v>0.431</v>
       </c>
-      <c r="J34" s="18" t="n">
+      <c r="J40" s="18" t="n">
         <v>0.159</v>
       </c>
-      <c r="K34" s="19" t="n">
+      <c r="K40" s="19" t="n">
         <v>4.258</v>
       </c>
-      <c r="L34" s="17" t="n">
+      <c r="L40" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="M34" s="19" t="n">
+      <c r="M40" s="19" t="n">
         <v>0.7</v>
       </c>
-      <c r="N34" s="16" t="n">
+      <c r="N40" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="O34" s="20" t="inlineStr">
+      <c r="O40" s="20" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P34" s="21" t="n">
+      <c r="P40" s="21" t="n">
         <v>-1</v>
       </c>
     </row>

--- a/bet_log.xlsx
+++ b/bet_log.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -687,7 +687,7 @@
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>22</v>
@@ -828,16 +828,16 @@
         </is>
       </c>
       <c r="G6" s="8" t="n">
-        <v>-144</v>
+        <v>-146</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>0.648</v>
+        <v>0.666</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.5935</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.0578</v>
+        <v>0.0725</v>
       </c>
       <c r="K6" s="11" t="n">
         <v>4.714</v>
@@ -846,7 +846,7 @@
         <v>0.5</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="N6" s="8" t="inlineStr"/>
       <c r="O6" s="12" t="inlineStr"/>
@@ -858,17 +858,17 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Aaron Civale</t>
+          <t>Andre Pallante</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>OAK</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
@@ -880,25 +880,25 @@
         </is>
       </c>
       <c r="G7" s="8" t="n">
-        <v>-146</v>
+        <v>126</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.666</v>
+        <v>0.523</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>0.5935</v>
+        <v>0.4425</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.0725</v>
+        <v>0.0805</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>4.714</v>
+        <v>3.876</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.45</v>
+        <v>0.36</v>
       </c>
       <c r="N7" s="8" t="inlineStr"/>
       <c r="O7" s="12" t="inlineStr"/>
@@ -910,47 +910,47 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>José Soriano</t>
+          <t>Max Scherzer</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G8" s="8" t="n">
-        <v>-110</v>
+        <v>-130</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>0.676</v>
+        <v>0.652</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>0.5238</v>
+        <v>0.5652</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.1522</v>
+        <v>0.0868</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>5.918</v>
+        <v>4.757</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="N8" s="8" t="inlineStr"/>
       <c r="O8" s="12" t="inlineStr"/>
@@ -962,17 +962,17 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Erick Fedde</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
@@ -984,25 +984,25 @@
         </is>
       </c>
       <c r="G9" s="8" t="n">
-        <v>-108</v>
+        <v>134</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.655</v>
+        <v>0.527</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>0.5192</v>
+        <v>0.4274</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.1358</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>4.719</v>
+        <v>3.852</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.71</v>
+        <v>0.44</v>
       </c>
       <c r="N9" s="8" t="inlineStr"/>
       <c r="O9" s="12" t="inlineStr"/>
@@ -1066,17 +1066,17 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Erick Fedde</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
@@ -1088,25 +1088,25 @@
         </is>
       </c>
       <c r="G11" s="8" t="n">
-        <v>134</v>
+        <v>-108</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.527</v>
+        <v>0.655</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>0.4274</v>
+        <v>0.5192</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.1358</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>3.852</v>
+        <v>4.719</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.44</v>
+        <v>0.71</v>
       </c>
       <c r="N11" s="8" t="inlineStr"/>
       <c r="O11" s="12" t="inlineStr"/>
@@ -1118,445 +1118,493 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Max Scherzer</t>
+          <t>José Soriano</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G12" s="8" t="n">
-        <v>-130</v>
+        <v>-110</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>0.652</v>
+        <v>0.676</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>0.5652</v>
+        <v>0.5238</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.0868</v>
+        <v>0.1522</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>4.757</v>
+        <v>5.918</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="N12" s="8" t="inlineStr"/>
       <c r="O12" s="12" t="inlineStr"/>
       <c r="P12" s="13" t="inlineStr"/>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Andre Pallante</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>NYM</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="n">
+      <c r="A13" s="14" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Simeon Woods Richardson</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="n">
         <v>3.5</v>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G13" s="8" t="n">
-        <v>126</v>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>0.523</v>
-      </c>
-      <c r="I13" s="10" t="n">
-        <v>0.4425</v>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>0.0805</v>
-      </c>
-      <c r="K13" s="11" t="n">
-        <v>3.876</v>
-      </c>
-      <c r="L13" s="9" t="n">
+      <c r="G13" s="16" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H13" s="18" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="I13" s="18" t="n">
+        <v>0.5283</v>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>0.2547</v>
+      </c>
+      <c r="K13" s="19" t="n">
+        <v>5.562</v>
+      </c>
+      <c r="L13" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" s="19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="N13" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" s="20" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P13" s="21" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="22" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>Davis Martin</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H14" s="26" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="I14" s="26" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="J14" s="26" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="K14" s="27" t="n">
+        <v>4.252</v>
+      </c>
+      <c r="L14" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="N14" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="O14" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P14" s="29" t="n">
+        <v>0.8772</v>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="14" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Kyle Harrison</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>114</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="K15" s="19" t="n">
+        <v>4.628</v>
+      </c>
+      <c r="L15" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M15" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N15" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="O15" s="20" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P15" s="21" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="14" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="n">
+        <v>-174</v>
+      </c>
+      <c r="H16" s="18" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="J16" s="18" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="K16" s="19" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="L16" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M16" s="19" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="N16" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" s="20" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P16" s="21" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="14" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Jacob Lopez</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>OAK</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="H17" s="18" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J17" s="18" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="K17" s="19" t="n">
+        <v>6.418</v>
+      </c>
+      <c r="L17" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="M13" s="11" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="N13" s="8" t="inlineStr"/>
-      <c r="O13" s="12" t="inlineStr"/>
-      <c r="P13" s="13" t="inlineStr"/>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="6" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Ryan Feltner</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="M17" s="19" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N17" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="20" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P17" s="21" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="22" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>Jack Leiter</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G14" s="8" t="n">
-        <v>-102</v>
-      </c>
-      <c r="H14" s="10" t="n">
-        <v>0.6830000000000001</v>
-      </c>
-      <c r="I14" s="10" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="J14" s="10" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="K14" s="11" t="n">
-        <v>4.719</v>
-      </c>
-      <c r="L14" s="9" t="n">
+      <c r="G18" s="24" t="n">
+        <v>-144</v>
+      </c>
+      <c r="H18" s="26" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="I18" s="26" t="n">
+        <v>0.5901999999999999</v>
+      </c>
+      <c r="J18" s="26" t="n">
+        <v>0.0888</v>
+      </c>
+      <c r="K18" s="27" t="n">
+        <v>6.017</v>
+      </c>
+      <c r="L18" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N18" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="O18" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P18" s="29" t="n">
+        <v>0.6944</v>
+      </c>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="22" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>Edward Cabrera</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E19" s="25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="n">
+        <v>116</v>
+      </c>
+      <c r="H19" s="26" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="I19" s="26" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J19" s="26" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="K19" s="27" t="n">
+        <v>5.286</v>
+      </c>
+      <c r="L19" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M14" s="11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N14" s="8" t="inlineStr"/>
-      <c r="O14" s="12" t="inlineStr"/>
-      <c r="P14" s="13" t="inlineStr"/>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="6" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>José Soriano</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>-108</v>
-      </c>
-      <c r="H15" s="10" t="n">
-        <v>0.672</v>
-      </c>
-      <c r="I15" s="10" t="n">
-        <v>0.5192</v>
-      </c>
-      <c r="J15" s="10" t="n">
-        <v>0.1528</v>
-      </c>
-      <c r="K15" s="11" t="n">
-        <v>5.918</v>
-      </c>
-      <c r="L15" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" s="11" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="N15" s="8" t="inlineStr"/>
-      <c r="O15" s="12" t="inlineStr"/>
-      <c r="P15" s="13" t="inlineStr"/>
-    </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="6" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Max Scherzer</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>-120</v>
-      </c>
-      <c r="H16" s="10" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="I16" s="10" t="n">
-        <v>0.5455</v>
-      </c>
-      <c r="J16" s="10" t="n">
-        <v>0.1145</v>
-      </c>
-      <c r="K16" s="11" t="n">
-        <v>4.757</v>
-      </c>
-      <c r="L16" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M16" s="11" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="N16" s="8" t="inlineStr"/>
-      <c r="O16" s="12" t="inlineStr"/>
-      <c r="P16" s="13" t="inlineStr"/>
-    </row>
-    <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="6" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Erick Fedde</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>124</v>
-      </c>
-      <c r="H17" s="10" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="I17" s="10" t="n">
-        <v>0.4464</v>
-      </c>
-      <c r="J17" s="10" t="n">
-        <v>0.0786</v>
-      </c>
-      <c r="K17" s="11" t="n">
-        <v>3.852</v>
-      </c>
-      <c r="L17" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" s="11" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="N17" s="8" t="inlineStr"/>
-      <c r="O17" s="12" t="inlineStr"/>
-      <c r="P17" s="13" t="inlineStr"/>
-    </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="6" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Andre Pallante</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>NYM</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="H18" s="10" t="n">
-        <v>0.517</v>
-      </c>
-      <c r="I18" s="10" t="n">
-        <v>0.4545</v>
-      </c>
-      <c r="J18" s="10" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="K18" s="11" t="n">
-        <v>3.876</v>
-      </c>
-      <c r="L18" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M18" s="11" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="N18" s="8" t="inlineStr"/>
-      <c r="O18" s="12" t="inlineStr"/>
-      <c r="P18" s="13" t="inlineStr"/>
-    </row>
-    <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="14" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>Jacob Lopez</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>OAK</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="n">
-        <v>100</v>
-      </c>
-      <c r="H19" s="18" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="I19" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J19" s="18" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="K19" s="19" t="n">
-        <v>6.418</v>
-      </c>
-      <c r="L19" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" s="19" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="N19" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P19" s="21" t="n">
-        <v>-1</v>
+      <c r="M19" s="27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N19" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="O19" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P19" s="29" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="22" t="n">
-        <v>46111</v>
+        <v>46109</v>
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E20" s="25" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
@@ -1564,28 +1612,28 @@
         </is>
       </c>
       <c r="G20" s="24" t="n">
-        <v>-114</v>
+        <v>140</v>
       </c>
       <c r="H20" s="26" t="n">
-        <v>0.584</v>
+        <v>0.476</v>
       </c>
       <c r="I20" s="26" t="n">
-        <v>0.5327</v>
+        <v>0.4167</v>
       </c>
       <c r="J20" s="26" t="n">
-        <v>0.0513</v>
+        <v>0.0593</v>
       </c>
       <c r="K20" s="27" t="n">
-        <v>4.252</v>
+        <v>4.645</v>
       </c>
       <c r="L20" s="25" t="n">
         <v>0.5</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="N20" s="24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O20" s="28" t="inlineStr">
         <is>
@@ -1593,26 +1641,26 @@
         </is>
       </c>
       <c r="P20" s="29" t="n">
-        <v>0.8772</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="14" t="n">
-        <v>46111</v>
+        <v>46109</v>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Kyle Harrison</t>
+          <t>Will Warren</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E21" s="17" t="n">
@@ -1620,32 +1668,32 @@
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G21" s="16" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H21" s="18" t="n">
-        <v>0.521</v>
+        <v>0.573</v>
       </c>
       <c r="I21" s="18" t="n">
-        <v>0.4673</v>
+        <v>0.4762</v>
       </c>
       <c r="J21" s="18" t="n">
-        <v>0.0537</v>
+        <v>0.0968</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>4.628</v>
+        <v>5.339</v>
       </c>
       <c r="L21" s="17" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="N21" s="16" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O21" s="20" t="inlineStr">
         <is>
@@ -1658,21 +1706,21 @@
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="14" t="n">
-        <v>46111</v>
+        <v>46109</v>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Jeffrey Springs</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>OAK</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E22" s="17" t="n">
@@ -1684,28 +1732,28 @@
         </is>
       </c>
       <c r="G22" s="16" t="n">
-        <v>-174</v>
+        <v>102</v>
       </c>
       <c r="H22" s="18" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.599</v>
       </c>
       <c r="I22" s="18" t="n">
-        <v>0.635</v>
+        <v>0.495</v>
       </c>
       <c r="J22" s="18" t="n">
-        <v>0.054</v>
+        <v>0.104</v>
       </c>
       <c r="K22" s="19" t="n">
-        <v>4.97</v>
+        <v>4.389</v>
       </c>
       <c r="L22" s="17" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M22" s="19" t="n">
-        <v>0.37</v>
+        <v>0.51</v>
       </c>
       <c r="N22" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O22" s="20" t="inlineStr">
         <is>
@@ -1717,82 +1765,82 @@
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="22" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B23" s="23" t="inlineStr">
-        <is>
-          <t>Jack Leiter</t>
-        </is>
-      </c>
-      <c r="C23" s="24" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
-      <c r="D23" s="24" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="E23" s="25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F23" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G23" s="24" t="n">
-        <v>-144</v>
-      </c>
-      <c r="H23" s="26" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="I23" s="26" t="n">
-        <v>0.5901999999999999</v>
-      </c>
-      <c r="J23" s="26" t="n">
-        <v>0.0888</v>
-      </c>
-      <c r="K23" s="27" t="n">
-        <v>6.017</v>
-      </c>
-      <c r="L23" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" s="27" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="N23" s="24" t="n">
+      <c r="A23" s="14" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>Eury Pérez</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G23" s="16" t="n">
+        <v>-154</v>
+      </c>
+      <c r="H23" s="18" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="I23" s="18" t="n">
+        <v>0.6063</v>
+      </c>
+      <c r="J23" s="18" t="n">
+        <v>0.1067</v>
+      </c>
+      <c r="K23" s="19" t="n">
+        <v>5.311</v>
+      </c>
+      <c r="L23" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M23" s="19" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="N23" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="O23" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P23" s="29" t="n">
-        <v>0.6944</v>
+      <c r="O23" s="20" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P23" s="21" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="14" t="n">
-        <v>46111</v>
+        <v>46108</v>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Simeon Woods Richardson</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E24" s="17" t="n">
@@ -1804,25 +1852,25 @@
         </is>
       </c>
       <c r="G24" s="16" t="n">
-        <v>-112</v>
+        <v>-158</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>0.783</v>
+        <v>0.677</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>0.5283</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>0.2547</v>
+        <v>0.0646</v>
       </c>
       <c r="K24" s="19" t="n">
-        <v>5.562</v>
+        <v>4.869</v>
       </c>
       <c r="L24" s="17" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="M24" s="19" t="n">
-        <v>1.35</v>
+        <v>0.42</v>
       </c>
       <c r="N24" s="16" t="n">
         <v>2</v>
@@ -1838,25 +1886,25 @@
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="22" t="n">
-        <v>46111</v>
+        <v>46108</v>
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>Edward Cabrera</t>
+          <t>Robbie Ray</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E25" s="25" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
@@ -1867,25 +1915,25 @@
         <v>116</v>
       </c>
       <c r="H25" s="26" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.532</v>
       </c>
       <c r="I25" s="26" t="n">
         <v>0.463</v>
       </c>
       <c r="J25" s="26" t="n">
-        <v>0.226</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K25" s="27" t="n">
-        <v>5.286</v>
+        <v>5.578</v>
       </c>
       <c r="L25" s="25" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>1.05</v>
+        <v>0.32</v>
       </c>
       <c r="N25" s="24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O25" s="28" t="inlineStr">
         <is>
@@ -1898,21 +1946,21 @@
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="22" t="n">
-        <v>46109</v>
+        <v>46108</v>
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E26" s="25" t="n">
@@ -1924,299 +1972,299 @@
         </is>
       </c>
       <c r="G26" s="24" t="n">
-        <v>140</v>
+        <v>-128</v>
       </c>
       <c r="H26" s="26" t="n">
-        <v>0.476</v>
+        <v>0.659</v>
       </c>
       <c r="I26" s="26" t="n">
-        <v>0.4167</v>
+        <v>0.5614</v>
       </c>
       <c r="J26" s="26" t="n">
-        <v>0.0593</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="K26" s="27" t="n">
-        <v>4.645</v>
+        <v>5.818</v>
       </c>
       <c r="L26" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="N26" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="O26" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P26" s="29" t="n">
+        <v>0.7812</v>
+      </c>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="22" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>Tarik Skubal</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="n">
+        <v>-172</v>
+      </c>
+      <c r="H27" s="26" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="I27" s="26" t="n">
+        <v>0.6324</v>
+      </c>
+      <c r="J27" s="26" t="n">
+        <v>0.1346</v>
+      </c>
+      <c r="K27" s="27" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="L27" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M27" s="27" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="N27" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="O27" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P27" s="29" t="n">
+        <v>0.5814</v>
+      </c>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="22" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>Andrew Abbott</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="n">
+        <v>120</v>
+      </c>
+      <c r="H28" s="26" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="I28" s="26" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="J28" s="26" t="n">
+        <v>0.0545</v>
+      </c>
+      <c r="K28" s="27" t="n">
+        <v>4.814</v>
+      </c>
+      <c r="L28" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M26" s="27" t="n">
+      <c r="M28" s="27" t="n">
         <v>0.25</v>
       </c>
-      <c r="N26" s="24" t="n">
-        <v>7</v>
-      </c>
-      <c r="O26" s="28" t="inlineStr">
+      <c r="N28" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="O28" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P26" s="29" t="n">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="14" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>Will Warren</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="n">
+      <c r="P28" s="29" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="22" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>Nick Pivetta</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="E29" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="n">
         <v>110</v>
       </c>
-      <c r="H27" s="18" t="n">
-        <v>0.573</v>
-      </c>
-      <c r="I27" s="18" t="n">
+      <c r="H29" s="26" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I29" s="26" t="n">
         <v>0.4762</v>
       </c>
-      <c r="J27" s="18" t="n">
-        <v>0.0968</v>
-      </c>
-      <c r="K27" s="19" t="n">
-        <v>5.339</v>
-      </c>
-      <c r="L27" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" s="19" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="N27" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="O27" s="20" t="inlineStr">
+      <c r="J29" s="26" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="K29" s="27" t="n">
+        <v>5.548</v>
+      </c>
+      <c r="L29" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M29" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N29" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="O29" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P29" s="29" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="14" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G30" s="16" t="n">
+        <v>124</v>
+      </c>
+      <c r="H30" s="18" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I30" s="18" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="J30" s="18" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="K30" s="19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L30" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M30" s="19" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N30" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="O30" s="20" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P27" s="21" t="n">
+      <c r="P30" s="21" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="14" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>Jeffrey Springs</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>OAK</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="n">
-        <v>102</v>
-      </c>
-      <c r="H28" s="18" t="n">
-        <v>0.599</v>
-      </c>
-      <c r="I28" s="18" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="J28" s="18" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="K28" s="19" t="n">
-        <v>4.389</v>
-      </c>
-      <c r="L28" s="17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M28" s="19" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="N28" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="O28" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P28" s="21" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="14" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>Eury Pérez</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="n">
-        <v>-154</v>
-      </c>
-      <c r="H29" s="18" t="n">
-        <v>0.713</v>
-      </c>
-      <c r="I29" s="18" t="n">
-        <v>0.6063</v>
-      </c>
-      <c r="J29" s="18" t="n">
-        <v>0.1067</v>
-      </c>
-      <c r="K29" s="19" t="n">
-        <v>5.311</v>
-      </c>
-      <c r="L29" s="17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M29" s="19" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="N29" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="O29" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P29" s="21" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="22" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B30" s="23" t="inlineStr">
-        <is>
-          <t>Robbie Ray</t>
-        </is>
-      </c>
-      <c r="C30" s="24" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="D30" s="24" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="E30" s="25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F30" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G30" s="24" t="n">
-        <v>116</v>
-      </c>
-      <c r="H30" s="26" t="n">
-        <v>0.532</v>
-      </c>
-      <c r="I30" s="26" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J30" s="26" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="K30" s="27" t="n">
-        <v>5.578</v>
-      </c>
-      <c r="L30" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M30" s="27" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="N30" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="O30" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P30" s="29" t="n">
-        <v>1.16</v>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="14" t="n">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Shane Smith</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
@@ -2224,25 +2272,25 @@
         </is>
       </c>
       <c r="G31" s="16" t="n">
-        <v>-158</v>
+        <v>-114</v>
       </c>
       <c r="H31" s="18" t="n">
-        <v>0.677</v>
+        <v>0.607</v>
       </c>
       <c r="I31" s="18" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.5327</v>
       </c>
       <c r="J31" s="18" t="n">
-        <v>0.0646</v>
+        <v>0.0743</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>4.869</v>
+        <v>5.338</v>
       </c>
       <c r="L31" s="17" t="n">
         <v>0.5</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="N31" s="16" t="n">
         <v>2</v>
@@ -2258,21 +2306,21 @@
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="22" t="n">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>José Soriano</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E32" s="25" t="n">
@@ -2284,28 +2332,28 @@
         </is>
       </c>
       <c r="G32" s="24" t="n">
-        <v>-128</v>
+        <v>108</v>
       </c>
       <c r="H32" s="26" t="n">
-        <v>0.659</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I32" s="26" t="n">
-        <v>0.5614</v>
+        <v>0.4808</v>
       </c>
       <c r="J32" s="26" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="K32" s="27" t="n">
-        <v>5.818</v>
+        <v>5.163</v>
       </c>
       <c r="L32" s="25" t="n">
         <v>1</v>
       </c>
       <c r="M32" s="27" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="N32" s="24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O32" s="28" t="inlineStr">
         <is>
@@ -2313,7 +2361,7 @@
         </is>
       </c>
       <c r="P32" s="29" t="n">
-        <v>0.7812</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
@@ -2322,50 +2370,50 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>Shane Smith</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G33" s="16" t="n">
-        <v>-114</v>
+        <v>114</v>
       </c>
       <c r="H33" s="18" t="n">
-        <v>0.607</v>
+        <v>0.587</v>
       </c>
       <c r="I33" s="18" t="n">
-        <v>0.5327</v>
+        <v>0.4673</v>
       </c>
       <c r="J33" s="18" t="n">
-        <v>0.0743</v>
+        <v>0.1197</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>5.338</v>
+        <v>6.417</v>
       </c>
       <c r="L33" s="17" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N33" s="16" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O33" s="20" t="inlineStr">
         <is>
@@ -2382,21 +2430,21 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Matthew Boyd</t>
         </is>
       </c>
       <c r="C34" s="16" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E34" s="17" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="F34" s="16" t="inlineStr">
         <is>
@@ -2404,28 +2452,28 @@
         </is>
       </c>
       <c r="G34" s="16" t="n">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="H34" s="18" t="n">
-        <v>0.587</v>
+        <v>0.59</v>
       </c>
       <c r="I34" s="18" t="n">
-        <v>0.4673</v>
+        <v>0.431</v>
       </c>
       <c r="J34" s="18" t="n">
-        <v>0.1197</v>
+        <v>0.159</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>6.417</v>
+        <v>4.258</v>
       </c>
       <c r="L34" s="17" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="N34" s="16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O34" s="20" t="inlineStr">
         <is>
@@ -2433,366 +2481,6 @@
         </is>
       </c>
       <c r="P34" s="21" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="22" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B35" s="23" t="inlineStr">
-        <is>
-          <t>José Soriano</t>
-        </is>
-      </c>
-      <c r="C35" s="24" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="D35" s="24" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="E35" s="25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F35" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G35" s="24" t="n">
-        <v>108</v>
-      </c>
-      <c r="H35" s="26" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I35" s="26" t="n">
-        <v>0.4808</v>
-      </c>
-      <c r="J35" s="26" t="n">
-        <v>0.07920000000000001</v>
-      </c>
-      <c r="K35" s="27" t="n">
-        <v>5.163</v>
-      </c>
-      <c r="L35" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M35" s="27" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="N35" s="24" t="n">
-        <v>7</v>
-      </c>
-      <c r="O35" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P35" s="29" t="n">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="22" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B36" s="23" t="inlineStr">
-        <is>
-          <t>Tarik Skubal</t>
-        </is>
-      </c>
-      <c r="C36" s="24" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="D36" s="24" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E36" s="25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F36" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G36" s="24" t="n">
-        <v>-172</v>
-      </c>
-      <c r="H36" s="26" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="I36" s="26" t="n">
-        <v>0.6324</v>
-      </c>
-      <c r="J36" s="26" t="n">
-        <v>0.1346</v>
-      </c>
-      <c r="K36" s="27" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="L36" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M36" s="27" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="N36" s="24" t="n">
-        <v>6</v>
-      </c>
-      <c r="O36" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P36" s="29" t="n">
-        <v>0.5814</v>
-      </c>
-    </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="14" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B37" s="15" t="inlineStr">
-        <is>
-          <t>Jacob Misiorowski</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D37" s="16" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F37" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G37" s="16" t="n">
-        <v>124</v>
-      </c>
-      <c r="H37" s="18" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I37" s="18" t="n">
-        <v>0.4464</v>
-      </c>
-      <c r="J37" s="18" t="n">
-        <v>0.0736</v>
-      </c>
-      <c r="K37" s="19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L37" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M37" s="19" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="N37" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="O37" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P37" s="21" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="22" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B38" s="23" t="inlineStr">
-        <is>
-          <t>Nick Pivetta</t>
-        </is>
-      </c>
-      <c r="C38" s="24" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="D38" s="24" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="E38" s="25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F38" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G38" s="24" t="n">
-        <v>110</v>
-      </c>
-      <c r="H38" s="26" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I38" s="26" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="J38" s="26" t="n">
-        <v>0.0638</v>
-      </c>
-      <c r="K38" s="27" t="n">
-        <v>5.548</v>
-      </c>
-      <c r="L38" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M38" s="27" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N38" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="O38" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P38" s="29" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="22" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B39" s="23" t="inlineStr">
-        <is>
-          <t>Andrew Abbott</t>
-        </is>
-      </c>
-      <c r="C39" s="24" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="D39" s="24" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="E39" s="25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F39" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G39" s="24" t="n">
-        <v>120</v>
-      </c>
-      <c r="H39" s="26" t="n">
-        <v>0.509</v>
-      </c>
-      <c r="I39" s="26" t="n">
-        <v>0.4545</v>
-      </c>
-      <c r="J39" s="26" t="n">
-        <v>0.0545</v>
-      </c>
-      <c r="K39" s="27" t="n">
-        <v>4.814</v>
-      </c>
-      <c r="L39" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M39" s="27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N39" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="O39" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P39" s="29" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="14" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B40" s="15" t="inlineStr">
-        <is>
-          <t>Matthew Boyd</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="D40" s="16" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F40" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G40" s="16" t="n">
-        <v>132</v>
-      </c>
-      <c r="H40" s="18" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="I40" s="18" t="n">
-        <v>0.431</v>
-      </c>
-      <c r="J40" s="18" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="K40" s="19" t="n">
-        <v>4.258</v>
-      </c>
-      <c r="L40" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M40" s="19" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N40" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="O40" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P40" s="21" t="n">
         <v>-1</v>
       </c>
     </row>

--- a/bet_log.xlsx
+++ b/bet_log.xlsx
@@ -75,6 +75,18 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="002D6A4F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001A7431"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00A4262C"/>
       <sz val="10"/>
     </font>
@@ -82,18 +94,6 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C0392B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="002D6A4F"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001A7431"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -126,12 +126,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAD7D7"/>
+        <fgColor rgb="00D6EFD8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6EFD8"/>
+        <fgColor rgb="00FAD7D7"/>
       </patternFill>
     </fill>
   </fills>
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -687,33 +687,33 @@
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="B3" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>22</v>
-      </c>
       <c r="C3" s="3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>-1.966 u</t>
+          <t>-0.771 u</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>-4.384 u</t>
+          <t>-2.646 u</t>
         </is>
       </c>
     </row>
@@ -802,51 +802,51 @@
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="6" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Aaron Civale</t>
+          <t>Yusei Kikuchi</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>OAK</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G6" s="8" t="n">
-        <v>-146</v>
+        <v>104</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>0.666</v>
+        <v>0.556</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.5935</v>
+        <v>0.4902</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.0725</v>
+        <v>0.0658</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>4.714</v>
+        <v>4.364</v>
       </c>
       <c r="L6" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>0.45</v>
+        <v>0.32</v>
       </c>
       <c r="N6" s="8" t="inlineStr"/>
       <c r="O6" s="12" t="inlineStr"/>
@@ -854,51 +854,51 @@
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Andre Pallante</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G7" s="8" t="n">
-        <v>126</v>
+        <v>-132</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.523</v>
+        <v>0.696</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>0.4425</v>
+        <v>0.569</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.0805</v>
+        <v>0.127</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>3.876</v>
+        <v>6.191</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.36</v>
+        <v>0.74</v>
       </c>
       <c r="N7" s="8" t="inlineStr"/>
       <c r="O7" s="12" t="inlineStr"/>
@@ -906,21 +906,21 @@
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="6" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Max Scherzer</t>
+          <t>Zac Gallen</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
@@ -932,25 +932,25 @@
         </is>
       </c>
       <c r="G8" s="8" t="n">
-        <v>-130</v>
+        <v>116</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>0.652</v>
+        <v>0.707</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>0.5652</v>
+        <v>0.463</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.0868</v>
+        <v>0.244</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>4.757</v>
+        <v>4.34</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.5</v>
+        <v>1.14</v>
       </c>
       <c r="N8" s="8" t="inlineStr"/>
       <c r="O8" s="12" t="inlineStr"/>
@@ -958,51 +958,51 @@
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Erick Fedde</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G9" s="8" t="n">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.527</v>
+        <v>0.644</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>0.4274</v>
+        <v>0.463</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.181</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>3.852</v>
+        <v>5.865</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.44</v>
+        <v>0.84</v>
       </c>
       <c r="N9" s="8" t="inlineStr"/>
       <c r="O9" s="12" t="inlineStr"/>
@@ -1010,51 +1010,51 @@
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="6" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Jameson Taillon</t>
+          <t>Adrian Houser</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G10" s="8" t="n">
-        <v>116</v>
+        <v>-125</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>0.569</v>
+        <v>0.724</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>0.463</v>
+        <v>0.5556</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.106</v>
+        <v>0.1684</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>4.313</v>
+        <v>5.063</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.49</v>
+        <v>0.95</v>
       </c>
       <c r="N10" s="8" t="inlineStr"/>
       <c r="O10" s="12" t="inlineStr"/>
@@ -1062,25 +1062,25 @@
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Cade Cavalli</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
@@ -1088,25 +1088,25 @@
         </is>
       </c>
       <c r="G11" s="8" t="n">
-        <v>-108</v>
+        <v>-102</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.655</v>
+        <v>0.668</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>0.5192</v>
+        <v>0.505</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.1358</v>
+        <v>0.163</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>4.719</v>
+        <v>5.697</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="N11" s="8" t="inlineStr"/>
       <c r="O11" s="12" t="inlineStr"/>
@@ -1114,21 +1114,21 @@
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="6" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>José Soriano</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
@@ -1136,835 +1136,747 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G12" s="8" t="n">
-        <v>-110</v>
+        <v>-136</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>0.5238</v>
+        <v>0.5763</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.1522</v>
+        <v>0.1557</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>5.918</v>
+        <v>3.414</v>
       </c>
       <c r="L12" s="9" t="n">
         <v>2</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="N12" s="8" t="inlineStr"/>
       <c r="O12" s="12" t="inlineStr"/>
       <c r="P12" s="13" t="inlineStr"/>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="14" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>Simeon Woods Richardson</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="A13" s="6" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Andrew Abbott</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>0.5283</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>0.1487</v>
+      </c>
+      <c r="K13" s="11" t="n">
+        <v>4.469</v>
+      </c>
+      <c r="L13" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M13" s="11" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="N13" s="8" t="inlineStr"/>
+      <c r="O13" s="12" t="inlineStr"/>
+      <c r="P13" s="13" t="inlineStr"/>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Cam Schlittler</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>-146</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>0.5935</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>0.1415</v>
+      </c>
+      <c r="K14" s="11" t="n">
+        <v>7.561</v>
+      </c>
+      <c r="L14" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M14" s="11" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="N14" s="8" t="inlineStr"/>
+      <c r="O14" s="12" t="inlineStr"/>
+      <c r="P14" s="13" t="inlineStr"/>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="6" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>106</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>0.4854</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>0.1386</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>7.784</v>
+      </c>
+      <c r="L15" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M15" s="11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N15" s="8" t="inlineStr"/>
+      <c r="O15" s="12" t="inlineStr"/>
+      <c r="P15" s="13" t="inlineStr"/>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="6" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Nathan Eovaldi</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>-172</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>0.6324</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>0.1106</v>
+      </c>
+      <c r="K16" s="11" t="n">
+        <v>7.699</v>
+      </c>
+      <c r="L16" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M16" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N16" s="8" t="inlineStr"/>
+      <c r="O16" s="12" t="inlineStr"/>
+      <c r="P16" s="13" t="inlineStr"/>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="6" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Mike Burrows</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>0.5283</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>0.1077</v>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>4.943</v>
+      </c>
+      <c r="L17" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M17" s="11" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N17" s="8" t="inlineStr"/>
+      <c r="O17" s="12" t="inlineStr"/>
+      <c r="P17" s="13" t="inlineStr"/>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="6" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>George Kirby</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>-178</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>0.6403</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="K18" s="11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N18" s="8" t="inlineStr"/>
+      <c r="O18" s="12" t="inlineStr"/>
+      <c r="P18" s="13" t="inlineStr"/>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="6" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Noah Cameron</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="n">
+      <c r="E19" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="I19" s="10" t="n">
+        <v>0.4902</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>0.0708</v>
+      </c>
+      <c r="K19" s="11" t="n">
+        <v>5.047</v>
+      </c>
+      <c r="L19" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M19" s="11" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N19" s="8" t="inlineStr"/>
+      <c r="O19" s="12" t="inlineStr"/>
+      <c r="P19" s="13" t="inlineStr"/>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="6" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Kyle Freeland</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G13" s="16" t="n">
-        <v>-112</v>
-      </c>
-      <c r="H13" s="18" t="n">
-        <v>0.783</v>
-      </c>
-      <c r="I13" s="18" t="n">
-        <v>0.5283</v>
-      </c>
-      <c r="J13" s="18" t="n">
-        <v>0.2547</v>
-      </c>
-      <c r="K13" s="19" t="n">
-        <v>5.562</v>
-      </c>
-      <c r="L13" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" s="19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="N13" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="O13" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P13" s="21" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="22" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>Davis Martin</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="E14" s="25" t="n">
+      <c r="G20" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I20" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K20" s="11" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="L20" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M20" s="11" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N20" s="8" t="inlineStr"/>
+      <c r="O20" s="12" t="inlineStr"/>
+      <c r="P20" s="13" t="inlineStr"/>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="6" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Nick Pivetta</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>108</v>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I21" s="10" t="n">
+        <v>0.4808</v>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>0.0692</v>
+      </c>
+      <c r="K21" s="11" t="n">
+        <v>5.551</v>
+      </c>
+      <c r="L21" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M21" s="11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N21" s="8" t="inlineStr"/>
+      <c r="O21" s="12" t="inlineStr"/>
+      <c r="P21" s="13" t="inlineStr"/>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="6" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Matthew Liberatore</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="F14" s="24" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="I22" s="10" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>0.0663</v>
+      </c>
+      <c r="K22" s="11" t="n">
+        <v>3.583</v>
+      </c>
+      <c r="L22" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M22" s="11" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N22" s="8" t="inlineStr"/>
+      <c r="O22" s="12" t="inlineStr"/>
+      <c r="P22" s="13" t="inlineStr"/>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="6" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Kevin Gausman</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G14" s="24" t="n">
-        <v>-114</v>
-      </c>
-      <c r="H14" s="26" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="I14" s="26" t="n">
-        <v>0.5327</v>
-      </c>
-      <c r="J14" s="26" t="n">
-        <v>0.0513</v>
-      </c>
-      <c r="K14" s="27" t="n">
-        <v>4.252</v>
-      </c>
-      <c r="L14" s="25" t="n">
+      <c r="G23" s="8" t="n">
+        <v>116</v>
+      </c>
+      <c r="H23" s="10" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="I23" s="10" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="K23" s="11" t="n">
+        <v>7.914</v>
+      </c>
+      <c r="L23" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="M14" s="27" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="N14" s="24" t="n">
-        <v>6</v>
-      </c>
-      <c r="O14" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P14" s="29" t="n">
-        <v>0.8772</v>
-      </c>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="14" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>Kyle Harrison</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="n">
-        <v>114</v>
-      </c>
-      <c r="H15" s="18" t="n">
-        <v>0.521</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>0.4673</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <v>0.0537</v>
-      </c>
-      <c r="K15" s="19" t="n">
-        <v>4.628</v>
-      </c>
-      <c r="L15" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M15" s="19" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N15" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="O15" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P15" s="21" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="14" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="n">
-        <v>-174</v>
-      </c>
-      <c r="H16" s="18" t="n">
-        <v>0.6889999999999999</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="J16" s="18" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="K16" s="19" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="L16" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M16" s="19" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="N16" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="O16" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P16" s="21" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="14" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>Jacob Lopez</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>OAK</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="n">
-        <v>100</v>
-      </c>
-      <c r="H17" s="18" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J17" s="18" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="K17" s="19" t="n">
-        <v>6.418</v>
-      </c>
-      <c r="L17" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" s="19" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="N17" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P17" s="21" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="22" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>Jack Leiter</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F18" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G18" s="24" t="n">
-        <v>-144</v>
-      </c>
-      <c r="H18" s="26" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="I18" s="26" t="n">
-        <v>0.5901999999999999</v>
-      </c>
-      <c r="J18" s="26" t="n">
-        <v>0.0888</v>
-      </c>
-      <c r="K18" s="27" t="n">
-        <v>6.017</v>
-      </c>
-      <c r="L18" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" s="27" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="N18" s="24" t="n">
-        <v>8</v>
-      </c>
-      <c r="O18" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P18" s="29" t="n">
-        <v>0.6944</v>
-      </c>
-    </row>
-    <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="22" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>Edward Cabrera</t>
-        </is>
-      </c>
-      <c r="C19" s="24" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="E19" s="25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F19" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G19" s="24" t="n">
-        <v>116</v>
-      </c>
-      <c r="H19" s="26" t="n">
-        <v>0.6889999999999999</v>
-      </c>
-      <c r="I19" s="26" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J19" s="26" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="K19" s="27" t="n">
-        <v>5.286</v>
-      </c>
-      <c r="L19" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" s="27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N19" s="24" t="n">
-        <v>5</v>
-      </c>
-      <c r="O19" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P19" s="29" t="n">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="22" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>Michael Wacha</t>
-        </is>
-      </c>
-      <c r="C20" s="24" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F20" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G20" s="24" t="n">
-        <v>140</v>
-      </c>
-      <c r="H20" s="26" t="n">
-        <v>0.476</v>
-      </c>
-      <c r="I20" s="26" t="n">
-        <v>0.4167</v>
-      </c>
-      <c r="J20" s="26" t="n">
-        <v>0.0593</v>
-      </c>
-      <c r="K20" s="27" t="n">
-        <v>4.645</v>
-      </c>
-      <c r="L20" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M20" s="27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N20" s="24" t="n">
-        <v>7</v>
-      </c>
-      <c r="O20" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P20" s="29" t="n">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="14" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>Will Warren</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="n">
-        <v>110</v>
-      </c>
-      <c r="H21" s="18" t="n">
-        <v>0.573</v>
-      </c>
-      <c r="I21" s="18" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="J21" s="18" t="n">
-        <v>0.0968</v>
-      </c>
-      <c r="K21" s="19" t="n">
-        <v>5.339</v>
-      </c>
-      <c r="L21" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" s="19" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="N21" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="O21" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P21" s="21" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="14" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>Jeffrey Springs</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>OAK</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="n">
-        <v>102</v>
-      </c>
-      <c r="H22" s="18" t="n">
-        <v>0.599</v>
-      </c>
-      <c r="I22" s="18" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="J22" s="18" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="K22" s="19" t="n">
-        <v>4.389</v>
-      </c>
-      <c r="L22" s="17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M22" s="19" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="N22" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="O22" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P22" s="21" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="14" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>Eury Pérez</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="n">
-        <v>-154</v>
-      </c>
-      <c r="H23" s="18" t="n">
-        <v>0.713</v>
-      </c>
-      <c r="I23" s="18" t="n">
-        <v>0.6063</v>
-      </c>
-      <c r="J23" s="18" t="n">
-        <v>0.1067</v>
-      </c>
-      <c r="K23" s="19" t="n">
-        <v>5.311</v>
-      </c>
-      <c r="L23" s="17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M23" s="19" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="N23" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="O23" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P23" s="21" t="n">
-        <v>-1</v>
-      </c>
+      <c r="M23" s="11" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N23" s="8" t="inlineStr"/>
+      <c r="O23" s="12" t="inlineStr"/>
+      <c r="P23" s="13" t="inlineStr"/>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="14" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Jameson Taillon</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E24" s="17" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F24" s="16" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G24" s="16" t="n">
-        <v>-158</v>
+        <v>116</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>0.677</v>
+        <v>0.569</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.463</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>0.0646</v>
+        <v>0.106</v>
       </c>
       <c r="K24" s="19" t="n">
-        <v>4.869</v>
+        <v>4.313</v>
       </c>
       <c r="L24" s="17" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M24" s="19" t="n">
-        <v>0.42</v>
+        <v>0.49</v>
       </c>
       <c r="N24" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O24" s="20" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>win</t>
         </is>
       </c>
       <c r="P24" s="21" t="n">
-        <v>-1</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="22" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>Robbie Ray</t>
+          <t>Aaron Civale</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>OAK</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E25" s="25" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G25" s="24" t="n">
-        <v>116</v>
+        <v>-146</v>
       </c>
       <c r="H25" s="26" t="n">
-        <v>0.532</v>
+        <v>0.666</v>
       </c>
       <c r="I25" s="26" t="n">
-        <v>0.463</v>
+        <v>0.5935</v>
       </c>
       <c r="J25" s="26" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0725</v>
       </c>
       <c r="K25" s="27" t="n">
-        <v>5.578</v>
+        <v>4.714</v>
       </c>
       <c r="L25" s="25" t="n">
         <v>0.5</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>0.32</v>
+        <v>0.45</v>
       </c>
       <c r="N25" s="24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O25" s="28" t="inlineStr">
         <is>
-          <t>win</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="P25" s="29" t="n">
-        <v>1.16</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="22" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Andre Pallante</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E26" s="25" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
@@ -1972,285 +1884,285 @@
         </is>
       </c>
       <c r="G26" s="24" t="n">
-        <v>-128</v>
+        <v>126</v>
       </c>
       <c r="H26" s="26" t="n">
-        <v>0.659</v>
+        <v>0.523</v>
       </c>
       <c r="I26" s="26" t="n">
-        <v>0.5614</v>
+        <v>0.4425</v>
       </c>
       <c r="J26" s="26" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.0805</v>
       </c>
       <c r="K26" s="27" t="n">
-        <v>5.818</v>
+        <v>3.876</v>
       </c>
       <c r="L26" s="25" t="n">
         <v>1</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="N26" s="24" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O26" s="28" t="inlineStr">
         <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P26" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="14" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Max Scherzer</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G27" s="16" t="n">
+        <v>-130</v>
+      </c>
+      <c r="H27" s="18" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="I27" s="18" t="n">
+        <v>0.5652</v>
+      </c>
+      <c r="J27" s="18" t="n">
+        <v>0.0868</v>
+      </c>
+      <c r="K27" s="19" t="n">
+        <v>4.757</v>
+      </c>
+      <c r="L27" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N27" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O27" s="20" t="inlineStr">
+        <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P26" s="29" t="n">
-        <v>0.7812</v>
-      </c>
-    </row>
-    <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="22" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B27" s="23" t="inlineStr">
-        <is>
-          <t>Tarik Skubal</t>
-        </is>
-      </c>
-      <c r="C27" s="24" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="D27" s="24" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E27" s="25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F27" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G27" s="24" t="n">
-        <v>-172</v>
-      </c>
-      <c r="H27" s="26" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="I27" s="26" t="n">
-        <v>0.6324</v>
-      </c>
-      <c r="J27" s="26" t="n">
-        <v>0.1346</v>
-      </c>
-      <c r="K27" s="27" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="L27" s="25" t="n">
+      <c r="P27" s="21" t="n">
+        <v>0.7692</v>
+      </c>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="14" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>Erick Fedde</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G28" s="16" t="n">
+        <v>134</v>
+      </c>
+      <c r="H28" s="18" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="I28" s="18" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="J28" s="18" t="n">
+        <v>0.09959999999999999</v>
+      </c>
+      <c r="K28" s="19" t="n">
+        <v>3.852</v>
+      </c>
+      <c r="L28" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" s="19" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="N28" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O28" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P28" s="21" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="14" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>Ryan Feltner</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G29" s="16" t="n">
+        <v>-108</v>
+      </c>
+      <c r="H29" s="18" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="I29" s="18" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="J29" s="18" t="n">
+        <v>0.1358</v>
+      </c>
+      <c r="K29" s="19" t="n">
+        <v>4.719</v>
+      </c>
+      <c r="L29" s="17" t="n">
         <v>1.5</v>
       </c>
-      <c r="M27" s="27" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="N27" s="24" t="n">
-        <v>6</v>
-      </c>
-      <c r="O27" s="28" t="inlineStr">
+      <c r="M29" s="19" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="N29" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O29" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P27" s="29" t="n">
-        <v>0.5814</v>
-      </c>
-    </row>
-    <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="22" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B28" s="23" t="inlineStr">
-        <is>
-          <t>Andrew Abbott</t>
-        </is>
-      </c>
-      <c r="C28" s="24" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="D28" s="24" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="E28" s="25" t="n">
+      <c r="P29" s="21" t="n">
+        <v>0.9258999999999999</v>
+      </c>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="22" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>José Soriano</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="E30" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F28" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G28" s="24" t="n">
-        <v>120</v>
-      </c>
-      <c r="H28" s="26" t="n">
-        <v>0.509</v>
-      </c>
-      <c r="I28" s="26" t="n">
-        <v>0.4545</v>
-      </c>
-      <c r="J28" s="26" t="n">
-        <v>0.0545</v>
-      </c>
-      <c r="K28" s="27" t="n">
-        <v>4.814</v>
-      </c>
-      <c r="L28" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M28" s="27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N28" s="24" t="n">
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H30" s="26" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="I30" s="26" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="J30" s="26" t="n">
+        <v>0.1522</v>
+      </c>
+      <c r="K30" s="27" t="n">
+        <v>5.918</v>
+      </c>
+      <c r="L30" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M30" s="27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N30" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="O28" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P28" s="29" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="22" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B29" s="23" t="inlineStr">
-        <is>
-          <t>Nick Pivetta</t>
-        </is>
-      </c>
-      <c r="C29" s="24" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="D29" s="24" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="E29" s="25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F29" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G29" s="24" t="n">
-        <v>110</v>
-      </c>
-      <c r="H29" s="26" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I29" s="26" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="J29" s="26" t="n">
-        <v>0.0638</v>
-      </c>
-      <c r="K29" s="27" t="n">
-        <v>5.548</v>
-      </c>
-      <c r="L29" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M29" s="27" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N29" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="O29" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P29" s="29" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="14" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>Jacob Misiorowski</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="n">
-        <v>124</v>
-      </c>
-      <c r="H30" s="18" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I30" s="18" t="n">
-        <v>0.4464</v>
-      </c>
-      <c r="J30" s="18" t="n">
-        <v>0.0736</v>
-      </c>
-      <c r="K30" s="19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L30" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M30" s="19" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="N30" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="O30" s="20" t="inlineStr">
+      <c r="O30" s="28" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P30" s="21" t="n">
+      <c r="P30" s="29" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="14" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Shane Smith</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2260,11 +2172,11 @@
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
@@ -2275,52 +2187,52 @@
         <v>-114</v>
       </c>
       <c r="H31" s="18" t="n">
-        <v>0.607</v>
+        <v>0.584</v>
       </c>
       <c r="I31" s="18" t="n">
         <v>0.5327</v>
       </c>
       <c r="J31" s="18" t="n">
-        <v>0.0743</v>
+        <v>0.0513</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>5.338</v>
+        <v>4.252</v>
       </c>
       <c r="L31" s="17" t="n">
         <v>0.5</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>0.4</v>
+        <v>0.27</v>
       </c>
       <c r="N31" s="16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O31" s="20" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>win</t>
         </is>
       </c>
       <c r="P31" s="21" t="n">
-        <v>-1</v>
+        <v>0.8772</v>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="22" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>José Soriano</t>
+          <t>Kyle Harrison</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E32" s="25" t="n">
@@ -2328,159 +2240,1239 @@
       </c>
       <c r="F32" s="24" t="inlineStr">
         <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="n">
+        <v>114</v>
+      </c>
+      <c r="H32" s="26" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="I32" s="26" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="J32" s="26" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="K32" s="27" t="n">
+        <v>4.628</v>
+      </c>
+      <c r="L32" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M32" s="27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N32" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="O32" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P32" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="22" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G32" s="24" t="n">
+      <c r="G33" s="24" t="n">
+        <v>-174</v>
+      </c>
+      <c r="H33" s="26" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="I33" s="26" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="J33" s="26" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="K33" s="27" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="L33" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M33" s="27" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="N33" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O33" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P33" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="22" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>Jacob Lopez</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>OAK</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E34" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="n">
+        <v>100</v>
+      </c>
+      <c r="H34" s="26" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="I34" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J34" s="26" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="K34" s="27" t="n">
+        <v>6.418</v>
+      </c>
+      <c r="L34" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="27" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N34" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P34" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="14" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>Jack Leiter</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G35" s="16" t="n">
+        <v>-144</v>
+      </c>
+      <c r="H35" s="18" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="I35" s="18" t="n">
+        <v>0.5901999999999999</v>
+      </c>
+      <c r="J35" s="18" t="n">
+        <v>0.0888</v>
+      </c>
+      <c r="K35" s="19" t="n">
+        <v>6.017</v>
+      </c>
+      <c r="L35" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="19" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N35" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="O35" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P35" s="21" t="n">
+        <v>0.6944</v>
+      </c>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="14" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>Edward Cabrera</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G36" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="H36" s="18" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="I36" s="18" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J36" s="18" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="K36" s="19" t="n">
+        <v>5.286</v>
+      </c>
+      <c r="L36" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M36" s="19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N36" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="O36" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P36" s="21" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="22" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>Simeon Woods Richardson</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="E37" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G37" s="24" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H37" s="26" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="I37" s="26" t="n">
+        <v>0.5283</v>
+      </c>
+      <c r="J37" s="26" t="n">
+        <v>0.2547</v>
+      </c>
+      <c r="K37" s="27" t="n">
+        <v>5.562</v>
+      </c>
+      <c r="L37" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M37" s="27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="N37" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O37" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P37" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="22" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>Jeffrey Springs</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>OAK</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E38" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="n">
+        <v>102</v>
+      </c>
+      <c r="H38" s="26" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="I38" s="26" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="J38" s="26" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="K38" s="27" t="n">
+        <v>4.389</v>
+      </c>
+      <c r="L38" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M38" s="27" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N38" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O38" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P38" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="22" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>Eury Pérez</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E39" s="25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G39" s="24" t="n">
+        <v>-154</v>
+      </c>
+      <c r="H39" s="26" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="I39" s="26" t="n">
+        <v>0.6063</v>
+      </c>
+      <c r="J39" s="26" t="n">
+        <v>0.1067</v>
+      </c>
+      <c r="K39" s="27" t="n">
+        <v>5.311</v>
+      </c>
+      <c r="L39" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M39" s="27" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="N39" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="O39" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P39" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="14" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>Michael Wacha</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G40" s="16" t="n">
+        <v>140</v>
+      </c>
+      <c r="H40" s="18" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="I40" s="18" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="J40" s="18" t="n">
+        <v>0.0593</v>
+      </c>
+      <c r="K40" s="19" t="n">
+        <v>4.645</v>
+      </c>
+      <c r="L40" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M40" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N40" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O40" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P40" s="21" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="22" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>Will Warren</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="E41" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F41" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G41" s="24" t="n">
+        <v>110</v>
+      </c>
+      <c r="H41" s="26" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="I41" s="26" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="J41" s="26" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="K41" s="27" t="n">
+        <v>5.339</v>
+      </c>
+      <c r="L41" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" s="27" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N41" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O41" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P41" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="22" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Kyle Freeland</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E42" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F42" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G42" s="24" t="n">
+        <v>-158</v>
+      </c>
+      <c r="H42" s="26" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="I42" s="26" t="n">
+        <v>0.6124000000000001</v>
+      </c>
+      <c r="J42" s="26" t="n">
+        <v>0.0646</v>
+      </c>
+      <c r="K42" s="27" t="n">
+        <v>4.869</v>
+      </c>
+      <c r="L42" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M42" s="27" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="N42" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O42" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P42" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="14" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>Robbie Ray</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G43" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="H43" s="18" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="I43" s="18" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J43" s="18" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="K43" s="19" t="n">
+        <v>5.578</v>
+      </c>
+      <c r="L43" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M43" s="19" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N43" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O43" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P43" s="21" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="14" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>Cam Schlittler</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G44" s="16" t="n">
+        <v>-128</v>
+      </c>
+      <c r="H44" s="18" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="I44" s="18" t="n">
+        <v>0.5614</v>
+      </c>
+      <c r="J44" s="18" t="n">
+        <v>0.09760000000000001</v>
+      </c>
+      <c r="K44" s="19" t="n">
+        <v>5.818</v>
+      </c>
+      <c r="L44" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" s="19" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="N44" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="O44" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P44" s="21" t="n">
+        <v>0.7812</v>
+      </c>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="22" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t>Shane Smith</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E45" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F45" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G45" s="24" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H45" s="26" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="I45" s="26" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="J45" s="26" t="n">
+        <v>0.0743</v>
+      </c>
+      <c r="K45" s="27" t="n">
+        <v>5.338</v>
+      </c>
+      <c r="L45" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M45" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N45" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O45" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P45" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="22" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>Hunter Brown</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E46" s="25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F46" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G46" s="24" t="n">
+        <v>114</v>
+      </c>
+      <c r="H46" s="26" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="I46" s="26" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="J46" s="26" t="n">
+        <v>0.1197</v>
+      </c>
+      <c r="K46" s="27" t="n">
+        <v>6.417</v>
+      </c>
+      <c r="L46" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M46" s="27" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="N46" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="O46" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P46" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="14" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>José Soriano</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G47" s="16" t="n">
         <v>108</v>
       </c>
-      <c r="H32" s="26" t="n">
+      <c r="H47" s="18" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="I32" s="26" t="n">
+      <c r="I47" s="18" t="n">
         <v>0.4808</v>
       </c>
-      <c r="J32" s="26" t="n">
+      <c r="J47" s="18" t="n">
         <v>0.07920000000000001</v>
       </c>
-      <c r="K32" s="27" t="n">
+      <c r="K47" s="19" t="n">
         <v>5.163</v>
       </c>
-      <c r="L32" s="25" t="n">
+      <c r="L47" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="M32" s="27" t="n">
+      <c r="M47" s="19" t="n">
         <v>0.38</v>
       </c>
-      <c r="N32" s="24" t="n">
+      <c r="N47" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="O32" s="28" t="inlineStr">
+      <c r="O47" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P32" s="29" t="n">
+      <c r="P47" s="21" t="n">
         <v>1.08</v>
       </c>
     </row>
-    <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="14" t="n">
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="14" t="n">
         <v>46107</v>
       </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>Hunter Brown</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>Tarik Skubal</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F48" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G33" s="16" t="n">
-        <v>114</v>
-      </c>
-      <c r="H33" s="18" t="n">
-        <v>0.587</v>
-      </c>
-      <c r="I33" s="18" t="n">
-        <v>0.4673</v>
-      </c>
-      <c r="J33" s="18" t="n">
-        <v>0.1197</v>
-      </c>
-      <c r="K33" s="19" t="n">
-        <v>6.417</v>
-      </c>
-      <c r="L33" s="17" t="n">
+      <c r="G48" s="16" t="n">
+        <v>-172</v>
+      </c>
+      <c r="H48" s="18" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="I48" s="18" t="n">
+        <v>0.6324</v>
+      </c>
+      <c r="J48" s="18" t="n">
+        <v>0.1346</v>
+      </c>
+      <c r="K48" s="19" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="L48" s="17" t="n">
         <v>1.5</v>
       </c>
-      <c r="M33" s="19" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="N33" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="O33" s="20" t="inlineStr">
+      <c r="M48" s="19" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="N48" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O48" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P48" s="21" t="n">
+        <v>0.5814</v>
+      </c>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="22" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E49" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G49" s="24" t="n">
+        <v>124</v>
+      </c>
+      <c r="H49" s="26" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I49" s="26" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="J49" s="26" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="K49" s="27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L49" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M49" s="27" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N49" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="O49" s="28" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P33" s="21" t="n">
+      <c r="P49" s="29" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="14" t="n">
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="14" t="n">
         <v>46107</v>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>Nick Pivetta</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D50" s="16" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F50" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G50" s="16" t="n">
+        <v>110</v>
+      </c>
+      <c r="H50" s="18" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I50" s="18" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="J50" s="18" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="K50" s="19" t="n">
+        <v>5.548</v>
+      </c>
+      <c r="L50" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M50" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N50" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O50" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P50" s="21" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="14" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>Andrew Abbott</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="D51" s="16" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F51" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G51" s="16" t="n">
+        <v>120</v>
+      </c>
+      <c r="H51" s="18" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="I51" s="18" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="J51" s="18" t="n">
+        <v>0.0545</v>
+      </c>
+      <c r="K51" s="19" t="n">
+        <v>4.814</v>
+      </c>
+      <c r="L51" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M51" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N51" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O51" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P51" s="21" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="22" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B52" s="23" t="inlineStr">
         <is>
           <t>Matthew Boyd</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C52" s="24" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D52" s="24" t="inlineStr">
         <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E34" s="17" t="n">
+      <c r="E52" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="F52" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G34" s="16" t="n">
+      <c r="G52" s="24" t="n">
         <v>132</v>
       </c>
-      <c r="H34" s="18" t="n">
+      <c r="H52" s="26" t="n">
         <v>0.59</v>
       </c>
-      <c r="I34" s="18" t="n">
+      <c r="I52" s="26" t="n">
         <v>0.431</v>
       </c>
-      <c r="J34" s="18" t="n">
+      <c r="J52" s="26" t="n">
         <v>0.159</v>
       </c>
-      <c r="K34" s="19" t="n">
+      <c r="K52" s="27" t="n">
         <v>4.258</v>
       </c>
-      <c r="L34" s="17" t="n">
+      <c r="L52" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M34" s="19" t="n">
+      <c r="M52" s="27" t="n">
         <v>0.7</v>
       </c>
-      <c r="N34" s="16" t="n">
+      <c r="N52" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="O34" s="20" t="inlineStr">
+      <c r="O52" s="28" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P34" s="21" t="n">
+      <c r="P52" s="29" t="n">
         <v>-1</v>
       </c>
     </row>

--- a/bet_log.xlsx
+++ b/bet_log.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P52"/>
+  <dimension ref="A1:P54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -687,7 +687,7 @@
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>29</v>
@@ -806,47 +806,47 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Yusei Kikuchi</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G6" s="8" t="n">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>0.556</v>
+        <v>0.515</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.4902</v>
+        <v>0.463</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.0658</v>
+        <v>0.052</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>4.364</v>
+        <v>6.789</v>
       </c>
       <c r="L6" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="N6" s="8" t="inlineStr"/>
       <c r="O6" s="12" t="inlineStr"/>
@@ -858,47 +858,47 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Nathan Eovaldi</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G7" s="8" t="n">
-        <v>-132</v>
+        <v>-172</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.696</v>
+        <v>0.743</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>0.569</v>
+        <v>0.6324</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.127</v>
+        <v>0.1106</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>6.191</v>
+        <v>7.699</v>
       </c>
       <c r="L7" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="N7" s="8" t="inlineStr"/>
       <c r="O7" s="12" t="inlineStr"/>
@@ -1326,47 +1326,47 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Nathan Eovaldi</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G16" s="8" t="n">
-        <v>-172</v>
+        <v>-132</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>0.743</v>
+        <v>0.696</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>0.6324</v>
+        <v>0.569</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.1106</v>
+        <v>0.127</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>7.699</v>
+        <v>6.191</v>
       </c>
       <c r="L16" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="N16" s="8" t="inlineStr"/>
       <c r="O16" s="12" t="inlineStr"/>
@@ -1737,303 +1737,287 @@
       <c r="P23" s="13" t="inlineStr"/>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="6" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Yusei Kikuchi</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="I24" s="10" t="n">
+        <v>0.4902</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>0.0658</v>
+      </c>
+      <c r="K24" s="11" t="n">
+        <v>4.364</v>
+      </c>
+      <c r="L24" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M24" s="11" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N24" s="8" t="inlineStr"/>
+      <c r="O24" s="12" t="inlineStr"/>
+      <c r="P24" s="13" t="inlineStr"/>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="6" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Shane Smith</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="I25" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="K25" s="11" t="n">
+        <v>5.393</v>
+      </c>
+      <c r="L25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="11" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N25" s="8" t="inlineStr"/>
+      <c r="O25" s="12" t="inlineStr"/>
+      <c r="P25" s="13" t="inlineStr"/>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="14" t="n">
         <v>46112</v>
       </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>Jameson Taillon</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="n">
-        <v>116</v>
-      </c>
-      <c r="H24" s="18" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="I24" s="18" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J24" s="18" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="K24" s="19" t="n">
-        <v>4.313</v>
-      </c>
-      <c r="L24" s="17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M24" s="19" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="N24" s="16" t="n">
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>Erick Fedde</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G26" s="16" t="n">
+        <v>134</v>
+      </c>
+      <c r="H26" s="18" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="I26" s="18" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="J26" s="18" t="n">
+        <v>0.09959999999999999</v>
+      </c>
+      <c r="K26" s="19" t="n">
+        <v>3.852</v>
+      </c>
+      <c r="L26" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="19" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="N26" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O26" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P26" s="21" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="22" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>Aaron Civale</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>OAK</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="n">
+        <v>-146</v>
+      </c>
+      <c r="H27" s="26" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="I27" s="26" t="n">
+        <v>0.5935</v>
+      </c>
+      <c r="J27" s="26" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="K27" s="27" t="n">
+        <v>4.714</v>
+      </c>
+      <c r="L27" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M27" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N27" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="O24" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P24" s="21" t="n">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="22" t="n">
+      <c r="O27" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P27" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="22" t="n">
         <v>46112</v>
       </c>
-      <c r="B25" s="23" t="inlineStr">
-        <is>
-          <t>Aaron Civale</t>
-        </is>
-      </c>
-      <c r="C25" s="24" t="inlineStr">
-        <is>
-          <t>OAK</t>
-        </is>
-      </c>
-      <c r="D25" s="24" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="E25" s="25" t="n">
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>Andre Pallante</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="n">
         <v>3.5</v>
       </c>
-      <c r="F25" s="24" t="inlineStr">
+      <c r="F28" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G25" s="24" t="n">
-        <v>-146</v>
-      </c>
-      <c r="H25" s="26" t="n">
-        <v>0.666</v>
-      </c>
-      <c r="I25" s="26" t="n">
-        <v>0.5935</v>
-      </c>
-      <c r="J25" s="26" t="n">
-        <v>0.0725</v>
-      </c>
-      <c r="K25" s="27" t="n">
-        <v>4.714</v>
-      </c>
-      <c r="L25" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M25" s="27" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="N25" s="24" t="n">
+      <c r="G28" s="24" t="n">
+        <v>126</v>
+      </c>
+      <c r="H28" s="26" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="I28" s="26" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="J28" s="26" t="n">
+        <v>0.0805</v>
+      </c>
+      <c r="K28" s="27" t="n">
+        <v>3.876</v>
+      </c>
+      <c r="L28" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" s="27" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="N28" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="O25" s="28" t="inlineStr">
+      <c r="O28" s="28" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P25" s="29" t="n">
+      <c r="P28" s="29" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="22" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B26" s="23" t="inlineStr">
-        <is>
-          <t>Andre Pallante</t>
-        </is>
-      </c>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="D26" s="24" t="inlineStr">
-        <is>
-          <t>NYM</t>
-        </is>
-      </c>
-      <c r="E26" s="25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F26" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G26" s="24" t="n">
-        <v>126</v>
-      </c>
-      <c r="H26" s="26" t="n">
-        <v>0.523</v>
-      </c>
-      <c r="I26" s="26" t="n">
-        <v>0.4425</v>
-      </c>
-      <c r="J26" s="26" t="n">
-        <v>0.0805</v>
-      </c>
-      <c r="K26" s="27" t="n">
-        <v>3.876</v>
-      </c>
-      <c r="L26" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" s="27" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="N26" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="O26" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P26" s="29" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="14" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>Max Scherzer</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="n">
-        <v>-130</v>
-      </c>
-      <c r="H27" s="18" t="n">
-        <v>0.652</v>
-      </c>
-      <c r="I27" s="18" t="n">
-        <v>0.5652</v>
-      </c>
-      <c r="J27" s="18" t="n">
-        <v>0.0868</v>
-      </c>
-      <c r="K27" s="19" t="n">
-        <v>4.757</v>
-      </c>
-      <c r="L27" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" s="19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N27" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="O27" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P27" s="21" t="n">
-        <v>0.7692</v>
-      </c>
-    </row>
-    <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="14" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>Erick Fedde</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="n">
-        <v>134</v>
-      </c>
-      <c r="H28" s="18" t="n">
-        <v>0.527</v>
-      </c>
-      <c r="I28" s="18" t="n">
-        <v>0.4274</v>
-      </c>
-      <c r="J28" s="18" t="n">
-        <v>0.09959999999999999</v>
-      </c>
-      <c r="K28" s="19" t="n">
-        <v>3.852</v>
-      </c>
-      <c r="L28" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" s="19" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="N28" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="O28" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P28" s="21" t="n">
-        <v>1.34</v>
       </c>
     </row>
     <row r="29" ht="17" customHeight="1">
@@ -2042,47 +2026,47 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Max Scherzer</t>
         </is>
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
       <c r="E29" s="17" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G29" s="16" t="n">
-        <v>-108</v>
+        <v>-130</v>
       </c>
       <c r="H29" s="18" t="n">
-        <v>0.655</v>
+        <v>0.652</v>
       </c>
       <c r="I29" s="18" t="n">
-        <v>0.5192</v>
+        <v>0.5652</v>
       </c>
       <c r="J29" s="18" t="n">
-        <v>0.1358</v>
+        <v>0.0868</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>4.719</v>
+        <v>4.757</v>
       </c>
       <c r="L29" s="17" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>0.71</v>
+        <v>0.5</v>
       </c>
       <c r="N29" s="16" t="n">
         <v>4</v>
@@ -2093,187 +2077,187 @@
         </is>
       </c>
       <c r="P29" s="21" t="n">
+        <v>0.7692</v>
+      </c>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="14" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Jameson Taillon</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G30" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="H30" s="18" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="I30" s="18" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J30" s="18" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="K30" s="19" t="n">
+        <v>4.313</v>
+      </c>
+      <c r="L30" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M30" s="19" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="N30" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O30" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P30" s="21" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="22" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>José Soriano</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="E31" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H31" s="26" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="I31" s="26" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="J31" s="26" t="n">
+        <v>0.1522</v>
+      </c>
+      <c r="K31" s="27" t="n">
+        <v>5.918</v>
+      </c>
+      <c r="L31" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M31" s="27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N31" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="O31" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P31" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="14" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>Ryan Feltner</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G32" s="16" t="n">
+        <v>-108</v>
+      </c>
+      <c r="H32" s="18" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="I32" s="18" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="J32" s="18" t="n">
+        <v>0.1358</v>
+      </c>
+      <c r="K32" s="19" t="n">
+        <v>4.719</v>
+      </c>
+      <c r="L32" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M32" s="19" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="N32" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O32" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P32" s="21" t="n">
         <v>0.9258999999999999</v>
-      </c>
-    </row>
-    <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="22" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B30" s="23" t="inlineStr">
-        <is>
-          <t>José Soriano</t>
-        </is>
-      </c>
-      <c r="C30" s="24" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="D30" s="24" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="E30" s="25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F30" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G30" s="24" t="n">
-        <v>-110</v>
-      </c>
-      <c r="H30" s="26" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="I30" s="26" t="n">
-        <v>0.5238</v>
-      </c>
-      <c r="J30" s="26" t="n">
-        <v>0.1522</v>
-      </c>
-      <c r="K30" s="27" t="n">
-        <v>5.918</v>
-      </c>
-      <c r="L30" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M30" s="27" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N30" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="O30" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P30" s="29" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="14" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>Davis Martin</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="n">
-        <v>-114</v>
-      </c>
-      <c r="H31" s="18" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="I31" s="18" t="n">
-        <v>0.5327</v>
-      </c>
-      <c r="J31" s="18" t="n">
-        <v>0.0513</v>
-      </c>
-      <c r="K31" s="19" t="n">
-        <v>4.252</v>
-      </c>
-      <c r="L31" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M31" s="19" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="N31" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="O31" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P31" s="21" t="n">
-        <v>0.8772</v>
-      </c>
-    </row>
-    <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="22" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B32" s="23" t="inlineStr">
-        <is>
-          <t>Kyle Harrison</t>
-        </is>
-      </c>
-      <c r="C32" s="24" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D32" s="24" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="E32" s="25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F32" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G32" s="24" t="n">
-        <v>114</v>
-      </c>
-      <c r="H32" s="26" t="n">
-        <v>0.521</v>
-      </c>
-      <c r="I32" s="26" t="n">
-        <v>0.4673</v>
-      </c>
-      <c r="J32" s="26" t="n">
-        <v>0.0537</v>
-      </c>
-      <c r="K32" s="27" t="n">
-        <v>4.628</v>
-      </c>
-      <c r="L32" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M32" s="27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N32" s="24" t="n">
-        <v>8</v>
-      </c>
-      <c r="O32" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P32" s="29" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
@@ -2282,17 +2266,17 @@
       </c>
       <c r="B33" s="23" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Simeon Woods Richardson</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D33" s="24" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E33" s="25" t="n">
@@ -2304,28 +2288,28 @@
         </is>
       </c>
       <c r="G33" s="24" t="n">
-        <v>-174</v>
+        <v>-112</v>
       </c>
       <c r="H33" s="26" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.783</v>
       </c>
       <c r="I33" s="26" t="n">
-        <v>0.635</v>
+        <v>0.5283</v>
       </c>
       <c r="J33" s="26" t="n">
-        <v>0.054</v>
+        <v>0.2547</v>
       </c>
       <c r="K33" s="27" t="n">
-        <v>4.97</v>
+        <v>5.562</v>
       </c>
       <c r="L33" s="25" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="M33" s="27" t="n">
-        <v>0.37</v>
+        <v>1.35</v>
       </c>
       <c r="N33" s="24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O33" s="28" t="inlineStr">
         <is>
@@ -2337,183 +2321,183 @@
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="22" t="n">
+      <c r="A34" s="14" t="n">
         <v>46111</v>
       </c>
-      <c r="B34" s="23" t="inlineStr">
-        <is>
-          <t>Jacob Lopez</t>
-        </is>
-      </c>
-      <c r="C34" s="24" t="inlineStr">
-        <is>
-          <t>OAK</t>
-        </is>
-      </c>
-      <c r="D34" s="24" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="E34" s="25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F34" s="24" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>Davis Martin</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F34" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G34" s="24" t="n">
-        <v>100</v>
-      </c>
-      <c r="H34" s="26" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="I34" s="26" t="n">
+      <c r="G34" s="16" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H34" s="18" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="I34" s="18" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="J34" s="18" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="K34" s="19" t="n">
+        <v>4.252</v>
+      </c>
+      <c r="L34" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="J34" s="26" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="K34" s="27" t="n">
-        <v>6.418</v>
-      </c>
-      <c r="L34" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" s="27" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="N34" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="28" t="inlineStr">
+      <c r="M34" s="19" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="N34" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O34" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P34" s="21" t="n">
+        <v>0.8772</v>
+      </c>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="22" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>Kyle Harrison</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E35" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="n">
+        <v>114</v>
+      </c>
+      <c r="H35" s="26" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="I35" s="26" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="J35" s="26" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="K35" s="27" t="n">
+        <v>4.628</v>
+      </c>
+      <c r="L35" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M35" s="27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N35" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="O35" s="28" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P34" s="29" t="n">
+      <c r="P35" s="29" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="14" t="n">
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="22" t="n">
         <v>46111</v>
       </c>
-      <c r="B35" s="15" t="inlineStr">
-        <is>
-          <t>Jack Leiter</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
-      <c r="D35" s="16" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="E35" s="17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F35" s="16" t="inlineStr">
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E36" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G35" s="16" t="n">
-        <v>-144</v>
-      </c>
-      <c r="H35" s="18" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="I35" s="18" t="n">
-        <v>0.5901999999999999</v>
-      </c>
-      <c r="J35" s="18" t="n">
-        <v>0.0888</v>
-      </c>
-      <c r="K35" s="19" t="n">
-        <v>6.017</v>
-      </c>
-      <c r="L35" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M35" s="19" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="N35" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="O35" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P35" s="21" t="n">
-        <v>0.6944</v>
-      </c>
-    </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="14" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B36" s="15" t="inlineStr">
-        <is>
-          <t>Edward Cabrera</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="E36" s="17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F36" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G36" s="16" t="n">
-        <v>116</v>
-      </c>
-      <c r="H36" s="18" t="n">
+      <c r="G36" s="24" t="n">
+        <v>-174</v>
+      </c>
+      <c r="H36" s="26" t="n">
         <v>0.6889999999999999</v>
       </c>
-      <c r="I36" s="18" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J36" s="18" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="K36" s="19" t="n">
-        <v>5.286</v>
-      </c>
-      <c r="L36" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M36" s="19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N36" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="O36" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P36" s="21" t="n">
-        <v>1.16</v>
+      <c r="I36" s="26" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="J36" s="26" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="K36" s="27" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="L36" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M36" s="27" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="N36" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O36" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P36" s="29" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
@@ -2522,21 +2506,21 @@
       </c>
       <c r="B37" s="23" t="inlineStr">
         <is>
-          <t>Simeon Woods Richardson</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OAK</t>
         </is>
       </c>
       <c r="D37" s="24" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E37" s="25" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="F37" s="24" t="inlineStr">
         <is>
@@ -2544,28 +2528,28 @@
         </is>
       </c>
       <c r="G37" s="24" t="n">
-        <v>-112</v>
+        <v>100</v>
       </c>
       <c r="H37" s="26" t="n">
-        <v>0.783</v>
+        <v>0.586</v>
       </c>
       <c r="I37" s="26" t="n">
-        <v>0.5283</v>
+        <v>0.5</v>
       </c>
       <c r="J37" s="26" t="n">
-        <v>0.2547</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="K37" s="27" t="n">
-        <v>5.562</v>
+        <v>6.418</v>
       </c>
       <c r="L37" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M37" s="27" t="n">
-        <v>1.35</v>
+        <v>0.43</v>
       </c>
       <c r="N37" s="24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O37" s="28" t="inlineStr">
         <is>
@@ -2577,183 +2561,183 @@
       </c>
     </row>
     <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="22" t="n">
+      <c r="A38" s="14" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>Jack Leiter</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G38" s="16" t="n">
+        <v>-144</v>
+      </c>
+      <c r="H38" s="18" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="I38" s="18" t="n">
+        <v>0.5901999999999999</v>
+      </c>
+      <c r="J38" s="18" t="n">
+        <v>0.0888</v>
+      </c>
+      <c r="K38" s="19" t="n">
+        <v>6.017</v>
+      </c>
+      <c r="L38" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" s="19" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N38" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="O38" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P38" s="21" t="n">
+        <v>0.6944</v>
+      </c>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="14" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>Edward Cabrera</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G39" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="H39" s="18" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="I39" s="18" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J39" s="18" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="K39" s="19" t="n">
+        <v>5.286</v>
+      </c>
+      <c r="L39" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M39" s="19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N39" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="O39" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P39" s="21" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="22" t="n">
         <v>46109</v>
       </c>
-      <c r="B38" s="23" t="inlineStr">
-        <is>
-          <t>Jeffrey Springs</t>
-        </is>
-      </c>
-      <c r="C38" s="24" t="inlineStr">
-        <is>
-          <t>OAK</t>
-        </is>
-      </c>
-      <c r="D38" s="24" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="E38" s="25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F38" s="24" t="inlineStr">
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>Will Warren</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="E40" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F40" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G38" s="24" t="n">
-        <v>102</v>
-      </c>
-      <c r="H38" s="26" t="n">
-        <v>0.599</v>
-      </c>
-      <c r="I38" s="26" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="J38" s="26" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="K38" s="27" t="n">
-        <v>4.389</v>
-      </c>
-      <c r="L38" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M38" s="27" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="N38" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="O38" s="28" t="inlineStr">
+      <c r="G40" s="24" t="n">
+        <v>110</v>
+      </c>
+      <c r="H40" s="26" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="I40" s="26" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="J40" s="26" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="K40" s="27" t="n">
+        <v>5.339</v>
+      </c>
+      <c r="L40" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" s="27" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N40" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O40" s="28" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P38" s="29" t="n">
+      <c r="P40" s="29" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="22" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B39" s="23" t="inlineStr">
-        <is>
-          <t>Eury Pérez</t>
-        </is>
-      </c>
-      <c r="C39" s="24" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="D39" s="24" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="E39" s="25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F39" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G39" s="24" t="n">
-        <v>-154</v>
-      </c>
-      <c r="H39" s="26" t="n">
-        <v>0.713</v>
-      </c>
-      <c r="I39" s="26" t="n">
-        <v>0.6063</v>
-      </c>
-      <c r="J39" s="26" t="n">
-        <v>0.1067</v>
-      </c>
-      <c r="K39" s="27" t="n">
-        <v>5.311</v>
-      </c>
-      <c r="L39" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M39" s="27" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="N39" s="24" t="n">
-        <v>8</v>
-      </c>
-      <c r="O39" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P39" s="29" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="14" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B40" s="15" t="inlineStr">
-        <is>
-          <t>Michael Wacha</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="D40" s="16" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F40" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G40" s="16" t="n">
-        <v>140</v>
-      </c>
-      <c r="H40" s="18" t="n">
-        <v>0.476</v>
-      </c>
-      <c r="I40" s="18" t="n">
-        <v>0.4167</v>
-      </c>
-      <c r="J40" s="18" t="n">
-        <v>0.0593</v>
-      </c>
-      <c r="K40" s="19" t="n">
-        <v>4.645</v>
-      </c>
-      <c r="L40" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M40" s="19" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N40" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="O40" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P40" s="21" t="n">
-        <v>1.4</v>
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
@@ -2762,50 +2746,50 @@
       </c>
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>Will Warren</t>
+          <t>Eury Pérez</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D41" s="24" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E41" s="25" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="F41" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G41" s="24" t="n">
-        <v>110</v>
+        <v>-154</v>
       </c>
       <c r="H41" s="26" t="n">
-        <v>0.573</v>
+        <v>0.713</v>
       </c>
       <c r="I41" s="26" t="n">
-        <v>0.4762</v>
+        <v>0.6063</v>
       </c>
       <c r="J41" s="26" t="n">
-        <v>0.0968</v>
+        <v>0.1067</v>
       </c>
       <c r="K41" s="27" t="n">
-        <v>5.339</v>
+        <v>5.311</v>
       </c>
       <c r="L41" s="25" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M41" s="27" t="n">
-        <v>0.46</v>
+        <v>0.68</v>
       </c>
       <c r="N41" s="24" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O41" s="28" t="inlineStr">
         <is>
@@ -2818,21 +2802,21 @@
     </row>
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="22" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B42" s="23" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Jeffrey Springs</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>OAK</t>
         </is>
       </c>
       <c r="D42" s="24" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E42" s="25" t="n">
@@ -2844,25 +2828,25 @@
         </is>
       </c>
       <c r="G42" s="24" t="n">
-        <v>-158</v>
+        <v>102</v>
       </c>
       <c r="H42" s="26" t="n">
-        <v>0.677</v>
+        <v>0.599</v>
       </c>
       <c r="I42" s="26" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.495</v>
       </c>
       <c r="J42" s="26" t="n">
-        <v>0.0646</v>
+        <v>0.104</v>
       </c>
       <c r="K42" s="27" t="n">
-        <v>4.869</v>
+        <v>4.389</v>
       </c>
       <c r="L42" s="25" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M42" s="27" t="n">
-        <v>0.42</v>
+        <v>0.51</v>
       </c>
       <c r="N42" s="24" t="n">
         <v>2</v>
@@ -2878,422 +2862,422 @@
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="14" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>Robbie Ray</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="C43" s="16" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G43" s="16" t="n">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>0.532</v>
+        <v>0.476</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>0.463</v>
+        <v>0.4167</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0593</v>
       </c>
       <c r="K43" s="19" t="n">
-        <v>5.578</v>
+        <v>4.645</v>
       </c>
       <c r="L43" s="17" t="n">
         <v>0.5</v>
       </c>
       <c r="M43" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N43" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O43" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P43" s="21" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="22" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Kyle Freeland</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D44" s="24" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E44" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F44" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G44" s="24" t="n">
+        <v>-158</v>
+      </c>
+      <c r="H44" s="26" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="I44" s="26" t="n">
+        <v>0.6124000000000001</v>
+      </c>
+      <c r="J44" s="26" t="n">
+        <v>0.0646</v>
+      </c>
+      <c r="K44" s="27" t="n">
+        <v>4.869</v>
+      </c>
+      <c r="L44" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M44" s="27" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="N44" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O44" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P44" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="14" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>Robbie Ray</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F45" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G45" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="H45" s="18" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="I45" s="18" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J45" s="18" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="K45" s="19" t="n">
+        <v>5.578</v>
+      </c>
+      <c r="L45" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M45" s="19" t="n">
         <v>0.32</v>
       </c>
-      <c r="N43" s="16" t="n">
+      <c r="N45" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="O43" s="20" t="inlineStr">
+      <c r="O45" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P43" s="21" t="n">
+      <c r="P45" s="21" t="n">
         <v>1.16</v>
       </c>
     </row>
-    <row r="44" ht="17" customHeight="1">
-      <c r="A44" s="14" t="n">
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="14" t="n">
         <v>46108</v>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>Cam Schlittler</t>
         </is>
       </c>
-      <c r="C44" s="16" t="inlineStr">
+      <c r="C46" s="16" t="inlineStr">
         <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="D44" s="16" t="inlineStr">
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="E44" s="17" t="n">
+      <c r="E46" s="17" t="n">
         <v>4.5</v>
       </c>
-      <c r="F44" s="16" t="inlineStr">
+      <c r="F46" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G44" s="16" t="n">
+      <c r="G46" s="16" t="n">
         <v>-128</v>
       </c>
-      <c r="H44" s="18" t="n">
+      <c r="H46" s="18" t="n">
         <v>0.659</v>
       </c>
-      <c r="I44" s="18" t="n">
+      <c r="I46" s="18" t="n">
         <v>0.5614</v>
       </c>
-      <c r="J44" s="18" t="n">
+      <c r="J46" s="18" t="n">
         <v>0.09760000000000001</v>
       </c>
-      <c r="K44" s="19" t="n">
+      <c r="K46" s="19" t="n">
         <v>5.818</v>
       </c>
-      <c r="L44" s="17" t="n">
+      <c r="L46" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="M44" s="19" t="n">
+      <c r="M46" s="19" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="N44" s="16" t="n">
+      <c r="N46" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="O44" s="20" t="inlineStr">
+      <c r="O46" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P44" s="21" t="n">
+      <c r="P46" s="21" t="n">
         <v>0.7812</v>
       </c>
     </row>
-    <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="22" t="n">
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="22" t="n">
         <v>46107</v>
       </c>
-      <c r="B45" s="23" t="inlineStr">
+      <c r="B47" s="23" t="inlineStr">
         <is>
           <t>Shane Smith</t>
         </is>
       </c>
-      <c r="C45" s="24" t="inlineStr">
+      <c r="C47" s="24" t="inlineStr">
         <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="D45" s="24" t="inlineStr">
+      <c r="D47" s="24" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E45" s="25" t="n">
+      <c r="E47" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F45" s="24" t="inlineStr">
+      <c r="F47" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G45" s="24" t="n">
+      <c r="G47" s="24" t="n">
         <v>-114</v>
       </c>
-      <c r="H45" s="26" t="n">
+      <c r="H47" s="26" t="n">
         <v>0.607</v>
       </c>
-      <c r="I45" s="26" t="n">
+      <c r="I47" s="26" t="n">
         <v>0.5327</v>
       </c>
-      <c r="J45" s="26" t="n">
+      <c r="J47" s="26" t="n">
         <v>0.0743</v>
       </c>
-      <c r="K45" s="27" t="n">
+      <c r="K47" s="27" t="n">
         <v>5.338</v>
       </c>
-      <c r="L45" s="25" t="n">
+      <c r="L47" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M45" s="27" t="n">
+      <c r="M47" s="27" t="n">
         <v>0.4</v>
       </c>
-      <c r="N45" s="24" t="n">
+      <c r="N47" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="O45" s="28" t="inlineStr">
+      <c r="O47" s="28" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P45" s="29" t="n">
+      <c r="P47" s="29" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="22" t="n">
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="22" t="n">
         <v>46107</v>
       </c>
-      <c r="B46" s="23" t="inlineStr">
+      <c r="B48" s="23" t="inlineStr">
         <is>
           <t>Hunter Brown</t>
         </is>
       </c>
-      <c r="C46" s="24" t="inlineStr">
+      <c r="C48" s="24" t="inlineStr">
         <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="D46" s="24" t="inlineStr">
+      <c r="D48" s="24" t="inlineStr">
         <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="E46" s="25" t="n">
+      <c r="E48" s="25" t="n">
         <v>6.5</v>
       </c>
-      <c r="F46" s="24" t="inlineStr">
+      <c r="F48" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G46" s="24" t="n">
+      <c r="G48" s="24" t="n">
         <v>114</v>
       </c>
-      <c r="H46" s="26" t="n">
+      <c r="H48" s="26" t="n">
         <v>0.587</v>
       </c>
-      <c r="I46" s="26" t="n">
+      <c r="I48" s="26" t="n">
         <v>0.4673</v>
       </c>
-      <c r="J46" s="26" t="n">
+      <c r="J48" s="26" t="n">
         <v>0.1197</v>
       </c>
-      <c r="K46" s="27" t="n">
+      <c r="K48" s="27" t="n">
         <v>6.417</v>
       </c>
-      <c r="L46" s="25" t="n">
+      <c r="L48" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="M46" s="27" t="n">
+      <c r="M48" s="27" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="N46" s="24" t="n">
+      <c r="N48" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="O46" s="28" t="inlineStr">
+      <c r="O48" s="28" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P46" s="29" t="n">
+      <c r="P48" s="29" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="14" t="n">
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="14" t="n">
         <v>46107</v>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>José Soriano</t>
         </is>
       </c>
-      <c r="C47" s="16" t="inlineStr">
+      <c r="C49" s="16" t="inlineStr">
         <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="D47" s="16" t="inlineStr">
+      <c r="D49" s="16" t="inlineStr">
         <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E47" s="17" t="n">
+      <c r="E49" s="17" t="n">
         <v>4.5</v>
       </c>
-      <c r="F47" s="16" t="inlineStr">
+      <c r="F49" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G47" s="16" t="n">
+      <c r="G49" s="16" t="n">
         <v>108</v>
       </c>
-      <c r="H47" s="18" t="n">
+      <c r="H49" s="18" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="I47" s="18" t="n">
+      <c r="I49" s="18" t="n">
         <v>0.4808</v>
       </c>
-      <c r="J47" s="18" t="n">
+      <c r="J49" s="18" t="n">
         <v>0.07920000000000001</v>
       </c>
-      <c r="K47" s="19" t="n">
+      <c r="K49" s="19" t="n">
         <v>5.163</v>
       </c>
-      <c r="L47" s="17" t="n">
+      <c r="L49" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="M47" s="19" t="n">
+      <c r="M49" s="19" t="n">
         <v>0.38</v>
       </c>
-      <c r="N47" s="16" t="n">
+      <c r="N49" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="O47" s="20" t="inlineStr">
+      <c r="O49" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P47" s="21" t="n">
+      <c r="P49" s="21" t="n">
         <v>1.08</v>
-      </c>
-    </row>
-    <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="14" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>Tarik Skubal</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="D48" s="16" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E48" s="17" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F48" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G48" s="16" t="n">
-        <v>-172</v>
-      </c>
-      <c r="H48" s="18" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="I48" s="18" t="n">
-        <v>0.6324</v>
-      </c>
-      <c r="J48" s="18" t="n">
-        <v>0.1346</v>
-      </c>
-      <c r="K48" s="19" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="L48" s="17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M48" s="19" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="N48" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="O48" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P48" s="21" t="n">
-        <v>0.5814</v>
-      </c>
-    </row>
-    <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="22" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B49" s="23" t="inlineStr">
-        <is>
-          <t>Jacob Misiorowski</t>
-        </is>
-      </c>
-      <c r="C49" s="24" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D49" s="24" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="E49" s="25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F49" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G49" s="24" t="n">
-        <v>124</v>
-      </c>
-      <c r="H49" s="26" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I49" s="26" t="n">
-        <v>0.4464</v>
-      </c>
-      <c r="J49" s="26" t="n">
-        <v>0.0736</v>
-      </c>
-      <c r="K49" s="27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L49" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M49" s="27" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="N49" s="24" t="n">
-        <v>11</v>
-      </c>
-      <c r="O49" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P49" s="29" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="50" ht="17" customHeight="1">
@@ -3302,177 +3286,297 @@
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
+          <t>Tarik Skubal</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="D50" s="16" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F50" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G50" s="16" t="n">
+        <v>-172</v>
+      </c>
+      <c r="H50" s="18" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="I50" s="18" t="n">
+        <v>0.6324</v>
+      </c>
+      <c r="J50" s="18" t="n">
+        <v>0.1346</v>
+      </c>
+      <c r="K50" s="19" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="L50" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M50" s="19" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="N50" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O50" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P50" s="21" t="n">
+        <v>0.5814</v>
+      </c>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="22" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B51" s="23" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E51" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G51" s="24" t="n">
+        <v>124</v>
+      </c>
+      <c r="H51" s="26" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I51" s="26" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="J51" s="26" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="K51" s="27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L51" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M51" s="27" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N51" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="O51" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P51" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="14" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
           <t>Nick Pivetta</t>
         </is>
       </c>
-      <c r="C50" s="16" t="inlineStr">
+      <c r="C52" s="16" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="D50" s="16" t="inlineStr">
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="E50" s="17" t="n">
+      <c r="E52" s="17" t="n">
         <v>5.5</v>
       </c>
-      <c r="F50" s="16" t="inlineStr">
+      <c r="F52" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G50" s="16" t="n">
+      <c r="G52" s="16" t="n">
         <v>110</v>
       </c>
-      <c r="H50" s="18" t="n">
+      <c r="H52" s="18" t="n">
         <v>0.54</v>
       </c>
-      <c r="I50" s="18" t="n">
+      <c r="I52" s="18" t="n">
         <v>0.4762</v>
       </c>
-      <c r="J50" s="18" t="n">
+      <c r="J52" s="18" t="n">
         <v>0.0638</v>
       </c>
-      <c r="K50" s="19" t="n">
+      <c r="K52" s="19" t="n">
         <v>5.548</v>
       </c>
-      <c r="L50" s="17" t="n">
+      <c r="L52" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="M50" s="19" t="n">
+      <c r="M52" s="19" t="n">
         <v>0.3</v>
       </c>
-      <c r="N50" s="16" t="n">
+      <c r="N52" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="O50" s="20" t="inlineStr">
+      <c r="O52" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P50" s="21" t="n">
+      <c r="P52" s="21" t="n">
         <v>1.1</v>
       </c>
     </row>
-    <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="14" t="n">
+    <row r="53" ht="17" customHeight="1">
+      <c r="A53" s="14" t="n">
         <v>46107</v>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B53" s="15" t="inlineStr">
         <is>
           <t>Andrew Abbott</t>
         </is>
       </c>
-      <c r="C51" s="16" t="inlineStr">
+      <c r="C53" s="16" t="inlineStr">
         <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="D51" s="16" t="inlineStr">
+      <c r="D53" s="16" t="inlineStr">
         <is>
           <t>BOS</t>
         </is>
       </c>
-      <c r="E51" s="17" t="n">
+      <c r="E53" s="17" t="n">
         <v>4.5</v>
       </c>
-      <c r="F51" s="16" t="inlineStr">
+      <c r="F53" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G51" s="16" t="n">
+      <c r="G53" s="16" t="n">
         <v>120</v>
       </c>
-      <c r="H51" s="18" t="n">
+      <c r="H53" s="18" t="n">
         <v>0.509</v>
       </c>
-      <c r="I51" s="18" t="n">
+      <c r="I53" s="18" t="n">
         <v>0.4545</v>
       </c>
-      <c r="J51" s="18" t="n">
+      <c r="J53" s="18" t="n">
         <v>0.0545</v>
       </c>
-      <c r="K51" s="19" t="n">
+      <c r="K53" s="19" t="n">
         <v>4.814</v>
       </c>
-      <c r="L51" s="17" t="n">
+      <c r="L53" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="M51" s="19" t="n">
+      <c r="M53" s="19" t="n">
         <v>0.25</v>
       </c>
-      <c r="N51" s="16" t="n">
+      <c r="N53" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="O51" s="20" t="inlineStr">
+      <c r="O53" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P51" s="21" t="n">
+      <c r="P53" s="21" t="n">
         <v>1.2</v>
       </c>
     </row>
-    <row r="52" ht="17" customHeight="1">
-      <c r="A52" s="22" t="n">
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="22" t="n">
         <v>46107</v>
       </c>
-      <c r="B52" s="23" t="inlineStr">
+      <c r="B54" s="23" t="inlineStr">
         <is>
           <t>Matthew Boyd</t>
         </is>
       </c>
-      <c r="C52" s="24" t="inlineStr">
+      <c r="C54" s="24" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="D52" s="24" t="inlineStr">
+      <c r="D54" s="24" t="inlineStr">
         <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E52" s="25" t="n">
+      <c r="E54" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F52" s="24" t="inlineStr">
+      <c r="F54" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G52" s="24" t="n">
+      <c r="G54" s="24" t="n">
         <v>132</v>
       </c>
-      <c r="H52" s="26" t="n">
+      <c r="H54" s="26" t="n">
         <v>0.59</v>
       </c>
-      <c r="I52" s="26" t="n">
+      <c r="I54" s="26" t="n">
         <v>0.431</v>
       </c>
-      <c r="J52" s="26" t="n">
+      <c r="J54" s="26" t="n">
         <v>0.159</v>
       </c>
-      <c r="K52" s="27" t="n">
+      <c r="K54" s="27" t="n">
         <v>4.258</v>
       </c>
-      <c r="L52" s="25" t="n">
+      <c r="L54" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M52" s="27" t="n">
+      <c r="M54" s="27" t="n">
         <v>0.7</v>
       </c>
-      <c r="N52" s="24" t="n">
+      <c r="N54" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="O52" s="28" t="inlineStr">
+      <c r="O54" s="28" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P52" s="29" t="n">
+      <c r="P54" s="29" t="n">
         <v>-1</v>
       </c>
     </row>

--- a/bet_log.xlsx
+++ b/bet_log.xlsx
@@ -858,17 +858,17 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Nathan Eovaldi</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
@@ -876,29 +876,29 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G7" s="8" t="n">
-        <v>-172</v>
+        <v>128</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.743</v>
+        <v>0.55</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>0.6324</v>
+        <v>0.4386</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.1106</v>
+        <v>0.1114</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>7.699</v>
+        <v>5.551</v>
       </c>
       <c r="L7" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="N7" s="8" t="inlineStr"/>
       <c r="O7" s="12" t="inlineStr"/>
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="G8" s="8" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H8" s="10" t="n">
         <v>0.707</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>0.463</v>
+        <v>0.4717</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.244</v>
+        <v>0.2353</v>
       </c>
       <c r="K8" s="11" t="n">
         <v>4.34</v>
@@ -950,7 +950,7 @@
         <v>2</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="N8" s="8" t="inlineStr"/>
       <c r="O8" s="12" t="inlineStr"/>
@@ -962,47 +962,47 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Adrian Houser</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G9" s="8" t="n">
-        <v>116</v>
+        <v>-125</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.644</v>
+        <v>0.724</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>0.463</v>
+        <v>0.5556</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.181</v>
+        <v>0.1684</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>5.865</v>
+        <v>5.063</v>
       </c>
       <c r="L9" s="9" t="n">
         <v>2</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="N9" s="8" t="inlineStr"/>
       <c r="O9" s="12" t="inlineStr"/>
@@ -1014,47 +1014,47 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Adrian Houser</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G10" s="8" t="n">
-        <v>-125</v>
+        <v>108</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>0.724</v>
+        <v>0.644</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>0.5556</v>
+        <v>0.4808</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.1684</v>
+        <v>0.1632</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>5.063</v>
+        <v>5.865</v>
       </c>
       <c r="L10" s="9" t="n">
         <v>2</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.95</v>
+        <v>0.79</v>
       </c>
       <c r="N10" s="8" t="inlineStr"/>
       <c r="O10" s="12" t="inlineStr"/>
@@ -1192,16 +1192,16 @@
         </is>
       </c>
       <c r="G13" s="8" t="n">
-        <v>-112</v>
+        <v>-114</v>
       </c>
       <c r="H13" s="10" t="n">
         <v>0.677</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>0.5283</v>
+        <v>0.5327</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.1487</v>
+        <v>0.1443</v>
       </c>
       <c r="K13" s="11" t="n">
         <v>4.469</v>
@@ -1210,7 +1210,7 @@
         <v>1.5</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="N13" s="8" t="inlineStr"/>
       <c r="O13" s="12" t="inlineStr"/>
@@ -1274,47 +1274,47 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G15" s="8" t="n">
-        <v>106</v>
+        <v>-132</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.624</v>
+        <v>0.696</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>0.4854</v>
+        <v>0.569</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.1386</v>
+        <v>0.127</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>7.784</v>
+        <v>6.191</v>
       </c>
       <c r="L15" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="N15" s="8" t="inlineStr"/>
       <c r="O15" s="12" t="inlineStr"/>
@@ -1326,47 +1326,47 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G16" s="8" t="n">
-        <v>-132</v>
+        <v>100</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>0.696</v>
+        <v>0.624</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>0.569</v>
+        <v>0.5</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.127</v>
+        <v>0.124</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>6.191</v>
+        <v>7.784</v>
       </c>
       <c r="L16" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.74</v>
+        <v>0.62</v>
       </c>
       <c r="N16" s="8" t="inlineStr"/>
       <c r="O16" s="12" t="inlineStr"/>
@@ -1378,17 +1378,17 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Mike Burrows</t>
+          <t>Nathan Eovaldi</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
@@ -1396,29 +1396,29 @@
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G17" s="8" t="n">
-        <v>-112</v>
+        <v>-172</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>0.636</v>
+        <v>0.743</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>0.5283</v>
+        <v>0.6324</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.1077</v>
+        <v>0.1106</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>4.943</v>
+        <v>7.699</v>
       </c>
       <c r="L17" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="N17" s="8" t="inlineStr"/>
       <c r="O17" s="12" t="inlineStr"/>
@@ -1430,21 +1430,21 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>George Kirby</t>
+          <t>Mike Burrows</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
@@ -1452,25 +1452,25 @@
         </is>
       </c>
       <c r="G18" s="8" t="n">
-        <v>-178</v>
+        <v>-114</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>0.726</v>
+        <v>0.636</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>0.6403</v>
+        <v>0.5327</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.0857</v>
+        <v>0.1033</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>5.8</v>
+        <v>4.943</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="N18" s="8" t="inlineStr"/>
       <c r="O18" s="12" t="inlineStr"/>
@@ -1482,47 +1482,47 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>George Kirby</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G19" s="8" t="n">
-        <v>104</v>
+        <v>-178</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.726</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>0.4902</v>
+        <v>0.6403</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.0708</v>
+        <v>0.0857</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>5.047</v>
+        <v>5.8</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="N19" s="8" t="inlineStr"/>
       <c r="O19" s="12" t="inlineStr"/>
@@ -1534,47 +1534,47 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Yusei Kikuchi</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G20" s="8" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>0.57</v>
+        <v>0.556</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>0.5</v>
+        <v>0.4762</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0798</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>4.038</v>
+        <v>4.364</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="N20" s="8" t="inlineStr"/>
       <c r="O20" s="12" t="inlineStr"/>
@@ -1586,47 +1586,47 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Shane Smith</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G21" s="8" t="n">
-        <v>108</v>
+        <v>-102</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>0.55</v>
+        <v>0.576</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>0.4808</v>
+        <v>0.505</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.0692</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>5.551</v>
+        <v>5.393</v>
       </c>
       <c r="L21" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="N21" s="8" t="inlineStr"/>
       <c r="O21" s="12" t="inlineStr"/>
@@ -1638,47 +1638,47 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Matthew Liberatore</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G22" s="8" t="n">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>0.525</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>0.4587</v>
+        <v>0.4902</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.0663</v>
+        <v>0.0708</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>3.583</v>
+        <v>5.047</v>
       </c>
       <c r="L22" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="N22" s="8" t="inlineStr"/>
       <c r="O22" s="12" t="inlineStr"/>
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="G23" s="8" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H23" s="10" t="n">
         <v>0.529</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>0.463</v>
+        <v>0.4587</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.066</v>
+        <v>0.0703</v>
       </c>
       <c r="K23" s="11" t="n">
         <v>7.914</v>
@@ -1730,7 +1730,7 @@
         <v>0.5</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="N23" s="8" t="inlineStr"/>
       <c r="O23" s="12" t="inlineStr"/>
@@ -1742,47 +1742,47 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Yusei Kikuchi</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G24" s="8" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>0.556</v>
+        <v>0.57</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>0.4902</v>
+        <v>0.5</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.0658</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>4.364</v>
+        <v>4.038</v>
       </c>
       <c r="L24" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="N24" s="8" t="inlineStr"/>
       <c r="O24" s="12" t="inlineStr"/>
@@ -1794,47 +1794,47 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Shane Smith</t>
+          <t>Matthew Liberatore</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G25" s="8" t="n">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>0.576</v>
+        <v>0.525</v>
       </c>
       <c r="I25" s="10" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="K25" s="11" t="n">
+        <v>3.583</v>
+      </c>
+      <c r="L25" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="J25" s="10" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="K25" s="11" t="n">
-        <v>5.393</v>
-      </c>
-      <c r="L25" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="M25" s="11" t="n">
-        <v>0.38</v>
+        <v>0.29</v>
       </c>
       <c r="N25" s="8" t="inlineStr"/>
       <c r="O25" s="12" t="inlineStr"/>

--- a/bet_log.xlsx
+++ b/bet_log.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P54"/>
+  <dimension ref="A1:P52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -687,7 +687,7 @@
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>29</v>
@@ -858,17 +858,17 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Nathan Eovaldi</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
@@ -876,29 +876,29 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G7" s="8" t="n">
-        <v>128</v>
+        <v>-168</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.55</v>
+        <v>0.743</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>0.4386</v>
+        <v>0.6269</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.1114</v>
+        <v>0.1161</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>5.551</v>
+        <v>7.699</v>
       </c>
       <c r="L7" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="N7" s="8" t="inlineStr"/>
       <c r="O7" s="12" t="inlineStr"/>
@@ -962,47 +962,47 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Adrian Houser</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G9" s="8" t="n">
-        <v>-125</v>
+        <v>-118</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.724</v>
+        <v>0.732</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>0.5556</v>
+        <v>0.5413</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.1684</v>
+        <v>0.1907</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>5.063</v>
+        <v>3.414</v>
       </c>
       <c r="L9" s="9" t="n">
         <v>2</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.95</v>
+        <v>1.04</v>
       </c>
       <c r="N9" s="8" t="inlineStr"/>
       <c r="O9" s="12" t="inlineStr"/>
@@ -1014,47 +1014,47 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Adrian Houser</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G10" s="8" t="n">
-        <v>108</v>
+        <v>-125</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>0.644</v>
+        <v>0.724</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>0.4808</v>
+        <v>0.5556</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.1632</v>
+        <v>0.1684</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>5.865</v>
+        <v>5.063</v>
       </c>
       <c r="L10" s="9" t="n">
         <v>2</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="N10" s="8" t="inlineStr"/>
       <c r="O10" s="12" t="inlineStr"/>
@@ -1066,47 +1066,47 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Cade Cavalli</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G11" s="8" t="n">
-        <v>-102</v>
+        <v>108</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.668</v>
+        <v>0.644</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>0.505</v>
+        <v>0.4808</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.163</v>
+        <v>0.1632</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>5.697</v>
+        <v>5.865</v>
       </c>
       <c r="L11" s="9" t="n">
         <v>2</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="N11" s="8" t="inlineStr"/>
       <c r="O11" s="12" t="inlineStr"/>
@@ -1118,17 +1118,17 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Cade Cavalli</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
@@ -1136,29 +1136,29 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G12" s="8" t="n">
-        <v>-136</v>
+        <v>-102</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>0.732</v>
+        <v>0.668</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>0.5763</v>
+        <v>0.505</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.1557</v>
+        <v>0.163</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>3.414</v>
+        <v>5.697</v>
       </c>
       <c r="L12" s="9" t="n">
         <v>2</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.92</v>
+        <v>0.82</v>
       </c>
       <c r="N12" s="8" t="inlineStr"/>
       <c r="O12" s="12" t="inlineStr"/>
@@ -1192,25 +1192,25 @@
         </is>
       </c>
       <c r="G13" s="8" t="n">
-        <v>-114</v>
+        <v>-110</v>
       </c>
       <c r="H13" s="10" t="n">
         <v>0.677</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>0.5327</v>
+        <v>0.5238</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.1443</v>
+        <v>0.1532</v>
       </c>
       <c r="K13" s="11" t="n">
         <v>4.469</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="N13" s="8" t="inlineStr"/>
       <c r="O13" s="12" t="inlineStr"/>
@@ -1222,47 +1222,47 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G14" s="8" t="n">
-        <v>-146</v>
+        <v>-132</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>0.735</v>
+        <v>0.696</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>0.5935</v>
+        <v>0.569</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.1415</v>
+        <v>0.127</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>7.561</v>
+        <v>6.191</v>
       </c>
       <c r="L14" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.87</v>
+        <v>0.74</v>
       </c>
       <c r="N14" s="8" t="inlineStr"/>
       <c r="O14" s="12" t="inlineStr"/>
@@ -1274,47 +1274,47 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G15" s="8" t="n">
-        <v>-132</v>
+        <v>100</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.696</v>
+        <v>0.624</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>0.569</v>
+        <v>0.5</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.127</v>
+        <v>0.124</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>6.191</v>
+        <v>7.784</v>
       </c>
       <c r="L15" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.74</v>
+        <v>0.62</v>
       </c>
       <c r="N15" s="8" t="inlineStr"/>
       <c r="O15" s="12" t="inlineStr"/>
@@ -1326,47 +1326,47 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G16" s="8" t="n">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>0.624</v>
+        <v>0.55</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>0.5</v>
+        <v>0.4386</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.124</v>
+        <v>0.1114</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>7.784</v>
+        <v>5.551</v>
       </c>
       <c r="L16" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
       <c r="N16" s="8" t="inlineStr"/>
       <c r="O16" s="12" t="inlineStr"/>
@@ -1378,17 +1378,17 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Nathan Eovaldi</t>
+          <t>Mike Burrows</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
@@ -1396,29 +1396,29 @@
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G17" s="8" t="n">
-        <v>-172</v>
+        <v>-114</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>0.743</v>
+        <v>0.636</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>0.6324</v>
+        <v>0.5327</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.1106</v>
+        <v>0.1033</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>7.699</v>
+        <v>4.943</v>
       </c>
       <c r="L17" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.75</v>
+        <v>0.55</v>
       </c>
       <c r="N17" s="8" t="inlineStr"/>
       <c r="O17" s="12" t="inlineStr"/>
@@ -1430,47 +1430,47 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Mike Burrows</t>
+          <t>Shane Smith</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G18" s="8" t="n">
-        <v>-114</v>
+        <v>100</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>0.636</v>
+        <v>0.576</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>0.5327</v>
+        <v>0.5</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.1033</v>
+        <v>0.076</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>4.943</v>
+        <v>5.393</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.55</v>
+        <v>0.38</v>
       </c>
       <c r="N18" s="8" t="inlineStr"/>
       <c r="O18" s="12" t="inlineStr"/>
@@ -1482,47 +1482,47 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>George Kirby</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G19" s="8" t="n">
-        <v>-178</v>
+        <v>104</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>0.726</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>0.6403</v>
+        <v>0.4902</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.0857</v>
+        <v>0.0708</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>5.8</v>
+        <v>5.047</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="N19" s="8" t="inlineStr"/>
       <c r="O19" s="12" t="inlineStr"/>
@@ -1534,47 +1534,47 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Yusei Kikuchi</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G20" s="8" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>0.556</v>
+        <v>0.57</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>0.4762</v>
+        <v>0.5</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.0798</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>4.364</v>
+        <v>4.038</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="N20" s="8" t="inlineStr"/>
       <c r="O20" s="12" t="inlineStr"/>
@@ -1586,47 +1586,47 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Shane Smith</t>
+          <t>Matthew Liberatore</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G21" s="8" t="n">
-        <v>-102</v>
+        <v>118</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>0.576</v>
+        <v>0.525</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>0.505</v>
+        <v>0.4587</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0663</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>5.393</v>
+        <v>3.583</v>
       </c>
       <c r="L21" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="N21" s="8" t="inlineStr"/>
       <c r="O21" s="12" t="inlineStr"/>
@@ -1638,21 +1638,21 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Kevin Gausman</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
@@ -1660,25 +1660,25 @@
         </is>
       </c>
       <c r="G22" s="8" t="n">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.529</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>0.4902</v>
+        <v>0.463</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.0708</v>
+        <v>0.066</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>5.047</v>
+        <v>7.914</v>
       </c>
       <c r="L22" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="N22" s="8" t="inlineStr"/>
       <c r="O22" s="12" t="inlineStr"/>
@@ -1690,334 +1690,350 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Kevin Gausman</t>
+          <t>Yusei Kikuchi</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G23" s="8" t="n">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>0.529</v>
+        <v>0.556</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>0.4587</v>
+        <v>0.495</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.0703</v>
+        <v>0.061</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>7.914</v>
+        <v>4.364</v>
       </c>
       <c r="L23" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="N23" s="8" t="inlineStr"/>
       <c r="O23" s="12" t="inlineStr"/>
       <c r="P23" s="13" t="inlineStr"/>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="6" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Kyle Freeland</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="A24" s="14" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Jameson Taillon</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G24" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="H24" s="18" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="I24" s="18" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J24" s="18" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="K24" s="19" t="n">
+        <v>4.313</v>
+      </c>
+      <c r="L24" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M24" s="19" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="N24" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O24" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P24" s="21" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="22" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>Aaron Civale</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>OAK</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E25" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="n">
+        <v>-146</v>
+      </c>
+      <c r="H25" s="26" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="I25" s="26" t="n">
+        <v>0.5935</v>
+      </c>
+      <c r="J25" s="26" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="K25" s="27" t="n">
+        <v>4.714</v>
+      </c>
+      <c r="L25" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M25" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N25" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O25" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P25" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="22" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>Andre Pallante</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="n">
+        <v>126</v>
+      </c>
+      <c r="H26" s="26" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="I26" s="26" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="J26" s="26" t="n">
+        <v>0.0805</v>
+      </c>
+      <c r="K26" s="27" t="n">
+        <v>3.876</v>
+      </c>
+      <c r="L26" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="N26" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O26" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P26" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="14" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Max Scherzer</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="n">
+      <c r="E27" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G27" s="16" t="n">
+        <v>-130</v>
+      </c>
+      <c r="H27" s="18" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="I27" s="18" t="n">
+        <v>0.5652</v>
+      </c>
+      <c r="J27" s="18" t="n">
+        <v>0.0868</v>
+      </c>
+      <c r="K27" s="19" t="n">
+        <v>4.757</v>
+      </c>
+      <c r="L27" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N27" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O27" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P27" s="21" t="n">
+        <v>0.7692</v>
+      </c>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="14" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>Erick Fedde</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="n">
         <v>3.5</v>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F28" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G24" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="H24" s="10" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="I24" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J24" s="10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K24" s="11" t="n">
-        <v>4.038</v>
-      </c>
-      <c r="L24" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M24" s="11" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="N24" s="8" t="inlineStr"/>
-      <c r="O24" s="12" t="inlineStr"/>
-      <c r="P24" s="13" t="inlineStr"/>
-    </row>
-    <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="6" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Matthew Liberatore</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>NYM</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="n">
-        <v>116</v>
-      </c>
-      <c r="H25" s="10" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="I25" s="10" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J25" s="10" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="K25" s="11" t="n">
-        <v>3.583</v>
-      </c>
-      <c r="L25" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M25" s="11" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="N25" s="8" t="inlineStr"/>
-      <c r="O25" s="12" t="inlineStr"/>
-      <c r="P25" s="13" t="inlineStr"/>
-    </row>
-    <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="14" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>Erick Fedde</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="n">
+      <c r="G28" s="16" t="n">
         <v>134</v>
       </c>
-      <c r="H26" s="18" t="n">
+      <c r="H28" s="18" t="n">
         <v>0.527</v>
       </c>
-      <c r="I26" s="18" t="n">
+      <c r="I28" s="18" t="n">
         <v>0.4274</v>
       </c>
-      <c r="J26" s="18" t="n">
+      <c r="J28" s="18" t="n">
         <v>0.09959999999999999</v>
       </c>
-      <c r="K26" s="19" t="n">
+      <c r="K28" s="19" t="n">
         <v>3.852</v>
       </c>
-      <c r="L26" s="17" t="n">
+      <c r="L28" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="M26" s="19" t="n">
+      <c r="M28" s="19" t="n">
         <v>0.44</v>
       </c>
-      <c r="N26" s="16" t="n">
+      <c r="N28" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="O26" s="20" t="inlineStr">
+      <c r="O28" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P26" s="21" t="n">
+      <c r="P28" s="21" t="n">
         <v>1.34</v>
-      </c>
-    </row>
-    <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="22" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B27" s="23" t="inlineStr">
-        <is>
-          <t>Aaron Civale</t>
-        </is>
-      </c>
-      <c r="C27" s="24" t="inlineStr">
-        <is>
-          <t>OAK</t>
-        </is>
-      </c>
-      <c r="D27" s="24" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="E27" s="25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F27" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G27" s="24" t="n">
-        <v>-146</v>
-      </c>
-      <c r="H27" s="26" t="n">
-        <v>0.666</v>
-      </c>
-      <c r="I27" s="26" t="n">
-        <v>0.5935</v>
-      </c>
-      <c r="J27" s="26" t="n">
-        <v>0.0725</v>
-      </c>
-      <c r="K27" s="27" t="n">
-        <v>4.714</v>
-      </c>
-      <c r="L27" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M27" s="27" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="N27" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="O27" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P27" s="29" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="22" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B28" s="23" t="inlineStr">
-        <is>
-          <t>Andre Pallante</t>
-        </is>
-      </c>
-      <c r="C28" s="24" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="D28" s="24" t="inlineStr">
-        <is>
-          <t>NYM</t>
-        </is>
-      </c>
-      <c r="E28" s="25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F28" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G28" s="24" t="n">
-        <v>126</v>
-      </c>
-      <c r="H28" s="26" t="n">
-        <v>0.523</v>
-      </c>
-      <c r="I28" s="26" t="n">
-        <v>0.4425</v>
-      </c>
-      <c r="J28" s="26" t="n">
-        <v>0.0805</v>
-      </c>
-      <c r="K28" s="27" t="n">
-        <v>3.876</v>
-      </c>
-      <c r="L28" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" s="27" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="N28" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="O28" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P28" s="29" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="29" ht="17" customHeight="1">
@@ -2026,47 +2042,47 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Max Scherzer</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
       <c r="E29" s="17" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G29" s="16" t="n">
-        <v>-130</v>
+        <v>-108</v>
       </c>
       <c r="H29" s="18" t="n">
-        <v>0.652</v>
+        <v>0.655</v>
       </c>
       <c r="I29" s="18" t="n">
-        <v>0.5652</v>
+        <v>0.5192</v>
       </c>
       <c r="J29" s="18" t="n">
-        <v>0.0868</v>
+        <v>0.1358</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>4.757</v>
+        <v>4.719</v>
       </c>
       <c r="L29" s="17" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="N29" s="16" t="n">
         <v>4</v>
@@ -2077,187 +2093,187 @@
         </is>
       </c>
       <c r="P29" s="21" t="n">
-        <v>0.7692</v>
+        <v>0.9258999999999999</v>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="22" t="n">
         <v>46112</v>
       </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>Jameson Taillon</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>José Soriano</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="n">
+      <c r="E30" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H30" s="26" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="I30" s="26" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="J30" s="26" t="n">
+        <v>0.1522</v>
+      </c>
+      <c r="K30" s="27" t="n">
+        <v>5.918</v>
+      </c>
+      <c r="L30" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M30" s="27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N30" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="O30" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P30" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="14" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>Davis Martin</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G31" s="16" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H31" s="18" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="I31" s="18" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="J31" s="18" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="K31" s="19" t="n">
+        <v>4.252</v>
+      </c>
+      <c r="L31" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M31" s="19" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="N31" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O31" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P31" s="21" t="n">
+        <v>0.8772</v>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="22" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>Kyle Harrison</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E32" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G30" s="16" t="n">
-        <v>116</v>
-      </c>
-      <c r="H30" s="18" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="I30" s="18" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J30" s="18" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="K30" s="19" t="n">
-        <v>4.313</v>
-      </c>
-      <c r="L30" s="17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M30" s="19" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="N30" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="O30" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P30" s="21" t="n">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="22" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B31" s="23" t="inlineStr">
-        <is>
-          <t>José Soriano</t>
-        </is>
-      </c>
-      <c r="C31" s="24" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="D31" s="24" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="E31" s="25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F31" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G31" s="24" t="n">
-        <v>-110</v>
-      </c>
-      <c r="H31" s="26" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="I31" s="26" t="n">
-        <v>0.5238</v>
-      </c>
-      <c r="J31" s="26" t="n">
-        <v>0.1522</v>
-      </c>
-      <c r="K31" s="27" t="n">
-        <v>5.918</v>
-      </c>
-      <c r="L31" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M31" s="27" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N31" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="O31" s="28" t="inlineStr">
+      <c r="G32" s="24" t="n">
+        <v>114</v>
+      </c>
+      <c r="H32" s="26" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="I32" s="26" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="J32" s="26" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="K32" s="27" t="n">
+        <v>4.628</v>
+      </c>
+      <c r="L32" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M32" s="27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N32" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="O32" s="28" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P31" s="29" t="n">
+      <c r="P32" s="29" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="14" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>Ryan Feltner</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F32" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="n">
-        <v>-108</v>
-      </c>
-      <c r="H32" s="18" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="I32" s="18" t="n">
-        <v>0.5192</v>
-      </c>
-      <c r="J32" s="18" t="n">
-        <v>0.1358</v>
-      </c>
-      <c r="K32" s="19" t="n">
-        <v>4.719</v>
-      </c>
-      <c r="L32" s="17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M32" s="19" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="N32" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="O32" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P32" s="21" t="n">
-        <v>0.9258999999999999</v>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
@@ -2266,17 +2282,17 @@
       </c>
       <c r="B33" s="23" t="inlineStr">
         <is>
-          <t>Simeon Woods Richardson</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="D33" s="24" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E33" s="25" t="n">
@@ -2288,28 +2304,28 @@
         </is>
       </c>
       <c r="G33" s="24" t="n">
-        <v>-112</v>
+        <v>-174</v>
       </c>
       <c r="H33" s="26" t="n">
-        <v>0.783</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="I33" s="26" t="n">
-        <v>0.5283</v>
+        <v>0.635</v>
       </c>
       <c r="J33" s="26" t="n">
-        <v>0.2547</v>
+        <v>0.054</v>
       </c>
       <c r="K33" s="27" t="n">
-        <v>5.562</v>
+        <v>4.97</v>
       </c>
       <c r="L33" s="25" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="M33" s="27" t="n">
-        <v>1.35</v>
+        <v>0.37</v>
       </c>
       <c r="N33" s="24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O33" s="28" t="inlineStr">
         <is>
@@ -2321,183 +2337,183 @@
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="22" t="n">
         <v>46111</v>
       </c>
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>Davis Martin</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>Jacob Lopez</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>OAK</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E34" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G34" s="16" t="n">
-        <v>-114</v>
-      </c>
-      <c r="H34" s="18" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="I34" s="18" t="n">
-        <v>0.5327</v>
-      </c>
-      <c r="J34" s="18" t="n">
-        <v>0.0513</v>
-      </c>
-      <c r="K34" s="19" t="n">
-        <v>4.252</v>
-      </c>
-      <c r="L34" s="17" t="n">
+      <c r="G34" s="24" t="n">
+        <v>100</v>
+      </c>
+      <c r="H34" s="26" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="I34" s="26" t="n">
         <v>0.5</v>
       </c>
-      <c r="M34" s="19" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="N34" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="O34" s="20" t="inlineStr">
+      <c r="J34" s="26" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="K34" s="27" t="n">
+        <v>6.418</v>
+      </c>
+      <c r="L34" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="27" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N34" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P34" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="14" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>Jack Leiter</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G35" s="16" t="n">
+        <v>-144</v>
+      </c>
+      <c r="H35" s="18" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="I35" s="18" t="n">
+        <v>0.5901999999999999</v>
+      </c>
+      <c r="J35" s="18" t="n">
+        <v>0.0888</v>
+      </c>
+      <c r="K35" s="19" t="n">
+        <v>6.017</v>
+      </c>
+      <c r="L35" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="19" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N35" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="O35" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P34" s="21" t="n">
-        <v>0.8772</v>
-      </c>
-    </row>
-    <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="22" t="n">
+      <c r="P35" s="21" t="n">
+        <v>0.6944</v>
+      </c>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="14" t="n">
         <v>46111</v>
       </c>
-      <c r="B35" s="23" t="inlineStr">
-        <is>
-          <t>Kyle Harrison</t>
-        </is>
-      </c>
-      <c r="C35" s="24" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D35" s="24" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="E35" s="25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F35" s="24" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>Edward Cabrera</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F36" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G35" s="24" t="n">
-        <v>114</v>
-      </c>
-      <c r="H35" s="26" t="n">
-        <v>0.521</v>
-      </c>
-      <c r="I35" s="26" t="n">
-        <v>0.4673</v>
-      </c>
-      <c r="J35" s="26" t="n">
-        <v>0.0537</v>
-      </c>
-      <c r="K35" s="27" t="n">
-        <v>4.628</v>
-      </c>
-      <c r="L35" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M35" s="27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N35" s="24" t="n">
-        <v>8</v>
-      </c>
-      <c r="O35" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P35" s="29" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="22" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B36" s="23" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="C36" s="24" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="D36" s="24" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="E36" s="25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F36" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G36" s="24" t="n">
-        <v>-174</v>
-      </c>
-      <c r="H36" s="26" t="n">
+      <c r="G36" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="H36" s="18" t="n">
         <v>0.6889999999999999</v>
       </c>
-      <c r="I36" s="26" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="J36" s="26" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="K36" s="27" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="L36" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M36" s="27" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="N36" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="O36" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P36" s="29" t="n">
-        <v>-1</v>
+      <c r="I36" s="18" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J36" s="18" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="K36" s="19" t="n">
+        <v>5.286</v>
+      </c>
+      <c r="L36" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M36" s="19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N36" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="O36" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P36" s="21" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
@@ -2506,21 +2522,21 @@
       </c>
       <c r="B37" s="23" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Simeon Woods Richardson</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>OAK</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D37" s="24" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E37" s="25" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F37" s="24" t="inlineStr">
         <is>
@@ -2528,28 +2544,28 @@
         </is>
       </c>
       <c r="G37" s="24" t="n">
-        <v>100</v>
+        <v>-112</v>
       </c>
       <c r="H37" s="26" t="n">
-        <v>0.586</v>
+        <v>0.783</v>
       </c>
       <c r="I37" s="26" t="n">
-        <v>0.5</v>
+        <v>0.5283</v>
       </c>
       <c r="J37" s="26" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.2547</v>
       </c>
       <c r="K37" s="27" t="n">
-        <v>6.418</v>
+        <v>5.562</v>
       </c>
       <c r="L37" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M37" s="27" t="n">
-        <v>0.43</v>
+        <v>1.35</v>
       </c>
       <c r="N37" s="24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O37" s="28" t="inlineStr">
         <is>
@@ -2561,183 +2577,183 @@
       </c>
     </row>
     <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="14" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B38" s="15" t="inlineStr">
-        <is>
-          <t>Jack Leiter</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
-      <c r="D38" s="16" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="E38" s="17" t="n">
+      <c r="A38" s="22" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>Jeffrey Springs</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>OAK</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E38" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="n">
+        <v>102</v>
+      </c>
+      <c r="H38" s="26" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="I38" s="26" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="J38" s="26" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="K38" s="27" t="n">
+        <v>4.389</v>
+      </c>
+      <c r="L38" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M38" s="27" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N38" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O38" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P38" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="22" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>Eury Pérez</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E39" s="25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G39" s="24" t="n">
+        <v>-154</v>
+      </c>
+      <c r="H39" s="26" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="I39" s="26" t="n">
+        <v>0.6063</v>
+      </c>
+      <c r="J39" s="26" t="n">
+        <v>0.1067</v>
+      </c>
+      <c r="K39" s="27" t="n">
+        <v>5.311</v>
+      </c>
+      <c r="L39" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M39" s="27" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="N39" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="O39" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P39" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="14" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>Michael Wacha</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="n">
         <v>4.5</v>
       </c>
-      <c r="F38" s="16" t="inlineStr">
+      <c r="F40" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G38" s="16" t="n">
-        <v>-144</v>
-      </c>
-      <c r="H38" s="18" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="I38" s="18" t="n">
-        <v>0.5901999999999999</v>
-      </c>
-      <c r="J38" s="18" t="n">
-        <v>0.0888</v>
-      </c>
-      <c r="K38" s="19" t="n">
-        <v>6.017</v>
-      </c>
-      <c r="L38" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M38" s="19" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="N38" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="O38" s="20" t="inlineStr">
+      <c r="G40" s="16" t="n">
+        <v>140</v>
+      </c>
+      <c r="H40" s="18" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="I40" s="18" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="J40" s="18" t="n">
+        <v>0.0593</v>
+      </c>
+      <c r="K40" s="19" t="n">
+        <v>4.645</v>
+      </c>
+      <c r="L40" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M40" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N40" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O40" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P38" s="21" t="n">
-        <v>0.6944</v>
-      </c>
-    </row>
-    <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="14" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B39" s="15" t="inlineStr">
-        <is>
-          <t>Edward Cabrera</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="D39" s="16" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="E39" s="17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F39" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G39" s="16" t="n">
-        <v>116</v>
-      </c>
-      <c r="H39" s="18" t="n">
-        <v>0.6889999999999999</v>
-      </c>
-      <c r="I39" s="18" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J39" s="18" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="K39" s="19" t="n">
-        <v>5.286</v>
-      </c>
-      <c r="L39" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M39" s="19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N39" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="O39" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P39" s="21" t="n">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="22" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B40" s="23" t="inlineStr">
-        <is>
-          <t>Will Warren</t>
-        </is>
-      </c>
-      <c r="C40" s="24" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="D40" s="24" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="E40" s="25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F40" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G40" s="24" t="n">
-        <v>110</v>
-      </c>
-      <c r="H40" s="26" t="n">
-        <v>0.573</v>
-      </c>
-      <c r="I40" s="26" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="J40" s="26" t="n">
-        <v>0.0968</v>
-      </c>
-      <c r="K40" s="27" t="n">
-        <v>5.339</v>
-      </c>
-      <c r="L40" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M40" s="27" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="N40" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="O40" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P40" s="29" t="n">
-        <v>-1</v>
+      <c r="P40" s="21" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
@@ -2746,50 +2762,50 @@
       </c>
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>Eury Pérez</t>
+          <t>Will Warren</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="D41" s="24" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E41" s="25" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="F41" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G41" s="24" t="n">
-        <v>-154</v>
+        <v>110</v>
       </c>
       <c r="H41" s="26" t="n">
-        <v>0.713</v>
+        <v>0.573</v>
       </c>
       <c r="I41" s="26" t="n">
-        <v>0.6063</v>
+        <v>0.4762</v>
       </c>
       <c r="J41" s="26" t="n">
-        <v>0.1067</v>
+        <v>0.0968</v>
       </c>
       <c r="K41" s="27" t="n">
-        <v>5.311</v>
+        <v>5.339</v>
       </c>
       <c r="L41" s="25" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M41" s="27" t="n">
-        <v>0.68</v>
+        <v>0.46</v>
       </c>
       <c r="N41" s="24" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O41" s="28" t="inlineStr">
         <is>
@@ -2802,21 +2818,21 @@
     </row>
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="22" t="n">
-        <v>46109</v>
+        <v>46108</v>
       </c>
       <c r="B42" s="23" t="inlineStr">
         <is>
-          <t>Jeffrey Springs</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>OAK</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D42" s="24" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E42" s="25" t="n">
@@ -2828,25 +2844,25 @@
         </is>
       </c>
       <c r="G42" s="24" t="n">
-        <v>102</v>
+        <v>-158</v>
       </c>
       <c r="H42" s="26" t="n">
-        <v>0.599</v>
+        <v>0.677</v>
       </c>
       <c r="I42" s="26" t="n">
-        <v>0.495</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J42" s="26" t="n">
-        <v>0.104</v>
+        <v>0.0646</v>
       </c>
       <c r="K42" s="27" t="n">
-        <v>4.389</v>
+        <v>4.869</v>
       </c>
       <c r="L42" s="25" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M42" s="27" t="n">
-        <v>0.51</v>
+        <v>0.42</v>
       </c>
       <c r="N42" s="24" t="n">
         <v>2</v>
@@ -2862,422 +2878,422 @@
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="14" t="n">
-        <v>46109</v>
+        <v>46108</v>
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Robbie Ray</t>
         </is>
       </c>
       <c r="C43" s="16" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G43" s="16" t="n">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>0.476</v>
+        <v>0.532</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>0.4167</v>
+        <v>0.463</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>0.0593</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K43" s="19" t="n">
-        <v>4.645</v>
+        <v>5.578</v>
       </c>
       <c r="L43" s="17" t="n">
         <v>0.5</v>
       </c>
       <c r="M43" s="19" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="N43" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O43" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P43" s="21" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="14" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>Cam Schlittler</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G44" s="16" t="n">
+        <v>-128</v>
+      </c>
+      <c r="H44" s="18" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="I44" s="18" t="n">
+        <v>0.5614</v>
+      </c>
+      <c r="J44" s="18" t="n">
+        <v>0.09760000000000001</v>
+      </c>
+      <c r="K44" s="19" t="n">
+        <v>5.818</v>
+      </c>
+      <c r="L44" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" s="19" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="N44" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="O44" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P44" s="21" t="n">
+        <v>0.7812</v>
+      </c>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="22" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t>Shane Smith</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E45" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F45" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G45" s="24" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H45" s="26" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="I45" s="26" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="J45" s="26" t="n">
+        <v>0.0743</v>
+      </c>
+      <c r="K45" s="27" t="n">
+        <v>5.338</v>
+      </c>
+      <c r="L45" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M45" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N45" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O45" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P45" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="22" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>Hunter Brown</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E46" s="25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F46" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G46" s="24" t="n">
+        <v>114</v>
+      </c>
+      <c r="H46" s="26" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="I46" s="26" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="J46" s="26" t="n">
+        <v>0.1197</v>
+      </c>
+      <c r="K46" s="27" t="n">
+        <v>6.417</v>
+      </c>
+      <c r="L46" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M46" s="27" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="N46" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="O46" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P46" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="14" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>José Soriano</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G47" s="16" t="n">
+        <v>108</v>
+      </c>
+      <c r="H47" s="18" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I47" s="18" t="n">
+        <v>0.4808</v>
+      </c>
+      <c r="J47" s="18" t="n">
+        <v>0.07920000000000001</v>
+      </c>
+      <c r="K47" s="19" t="n">
+        <v>5.163</v>
+      </c>
+      <c r="L47" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" s="19" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N47" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="O43" s="20" t="inlineStr">
+      <c r="O47" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P43" s="21" t="n">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="44" ht="17" customHeight="1">
-      <c r="A44" s="22" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B44" s="23" t="inlineStr">
-        <is>
-          <t>Kyle Freeland</t>
-        </is>
-      </c>
-      <c r="C44" s="24" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="D44" s="24" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="E44" s="25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F44" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G44" s="24" t="n">
-        <v>-158</v>
-      </c>
-      <c r="H44" s="26" t="n">
-        <v>0.677</v>
-      </c>
-      <c r="I44" s="26" t="n">
-        <v>0.6124000000000001</v>
-      </c>
-      <c r="J44" s="26" t="n">
-        <v>0.0646</v>
-      </c>
-      <c r="K44" s="27" t="n">
-        <v>4.869</v>
-      </c>
-      <c r="L44" s="25" t="n">
+      <c r="P47" s="21" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="14" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>Tarik Skubal</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F48" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G48" s="16" t="n">
+        <v>-172</v>
+      </c>
+      <c r="H48" s="18" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="I48" s="18" t="n">
+        <v>0.6324</v>
+      </c>
+      <c r="J48" s="18" t="n">
+        <v>0.1346</v>
+      </c>
+      <c r="K48" s="19" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="L48" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M48" s="19" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="N48" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O48" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P48" s="21" t="n">
+        <v>0.5814</v>
+      </c>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="22" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E49" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G49" s="24" t="n">
+        <v>124</v>
+      </c>
+      <c r="H49" s="26" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I49" s="26" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="J49" s="26" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="K49" s="27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L49" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M44" s="27" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="N44" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="O44" s="28" t="inlineStr">
+      <c r="M49" s="27" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N49" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="O49" s="28" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P44" s="29" t="n">
+      <c r="P49" s="29" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="14" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B45" s="15" t="inlineStr">
-        <is>
-          <t>Robbie Ray</t>
-        </is>
-      </c>
-      <c r="C45" s="16" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="D45" s="16" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="E45" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F45" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G45" s="16" t="n">
-        <v>116</v>
-      </c>
-      <c r="H45" s="18" t="n">
-        <v>0.532</v>
-      </c>
-      <c r="I45" s="18" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J45" s="18" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="K45" s="19" t="n">
-        <v>5.578</v>
-      </c>
-      <c r="L45" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M45" s="19" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="N45" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="O45" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P45" s="21" t="n">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="14" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B46" s="15" t="inlineStr">
-        <is>
-          <t>Cam Schlittler</t>
-        </is>
-      </c>
-      <c r="C46" s="16" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="D46" s="16" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="E46" s="17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F46" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G46" s="16" t="n">
-        <v>-128</v>
-      </c>
-      <c r="H46" s="18" t="n">
-        <v>0.659</v>
-      </c>
-      <c r="I46" s="18" t="n">
-        <v>0.5614</v>
-      </c>
-      <c r="J46" s="18" t="n">
-        <v>0.09760000000000001</v>
-      </c>
-      <c r="K46" s="19" t="n">
-        <v>5.818</v>
-      </c>
-      <c r="L46" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M46" s="19" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="N46" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="O46" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P46" s="21" t="n">
-        <v>0.7812</v>
-      </c>
-    </row>
-    <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="22" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B47" s="23" t="inlineStr">
-        <is>
-          <t>Shane Smith</t>
-        </is>
-      </c>
-      <c r="C47" s="24" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="D47" s="24" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="E47" s="25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F47" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G47" s="24" t="n">
-        <v>-114</v>
-      </c>
-      <c r="H47" s="26" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="I47" s="26" t="n">
-        <v>0.5327</v>
-      </c>
-      <c r="J47" s="26" t="n">
-        <v>0.0743</v>
-      </c>
-      <c r="K47" s="27" t="n">
-        <v>5.338</v>
-      </c>
-      <c r="L47" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M47" s="27" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N47" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="O47" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P47" s="29" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="22" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B48" s="23" t="inlineStr">
-        <is>
-          <t>Hunter Brown</t>
-        </is>
-      </c>
-      <c r="C48" s="24" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="D48" s="24" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="E48" s="25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F48" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G48" s="24" t="n">
-        <v>114</v>
-      </c>
-      <c r="H48" s="26" t="n">
-        <v>0.587</v>
-      </c>
-      <c r="I48" s="26" t="n">
-        <v>0.4673</v>
-      </c>
-      <c r="J48" s="26" t="n">
-        <v>0.1197</v>
-      </c>
-      <c r="K48" s="27" t="n">
-        <v>6.417</v>
-      </c>
-      <c r="L48" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M48" s="27" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="N48" s="24" t="n">
-        <v>9</v>
-      </c>
-      <c r="O48" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P48" s="29" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="14" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>José Soriano</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="D49" s="16" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="E49" s="17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F49" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G49" s="16" t="n">
-        <v>108</v>
-      </c>
-      <c r="H49" s="18" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I49" s="18" t="n">
-        <v>0.4808</v>
-      </c>
-      <c r="J49" s="18" t="n">
-        <v>0.07920000000000001</v>
-      </c>
-      <c r="K49" s="19" t="n">
-        <v>5.163</v>
-      </c>
-      <c r="L49" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M49" s="19" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="N49" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="O49" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P49" s="21" t="n">
-        <v>1.08</v>
       </c>
     </row>
     <row r="50" ht="17" customHeight="1">
@@ -3286,21 +3302,21 @@
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="C50" s="16" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D50" s="16" t="inlineStr">
+        <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="D50" s="16" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="E50" s="17" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="F50" s="16" t="inlineStr">
         <is>
@@ -3308,28 +3324,28 @@
         </is>
       </c>
       <c r="G50" s="16" t="n">
-        <v>-172</v>
+        <v>110</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>0.767</v>
+        <v>0.54</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>0.6324</v>
+        <v>0.4762</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>0.1346</v>
+        <v>0.0638</v>
       </c>
       <c r="K50" s="19" t="n">
-        <v>5.68</v>
+        <v>5.548</v>
       </c>
       <c r="L50" s="17" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M50" s="19" t="n">
-        <v>0.92</v>
+        <v>0.3</v>
       </c>
       <c r="N50" s="16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O50" s="20" t="inlineStr">
         <is>
@@ -3337,246 +3353,126 @@
         </is>
       </c>
       <c r="P50" s="21" t="n">
-        <v>0.5814</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="22" t="n">
+      <c r="A51" s="14" t="n">
         <v>46107</v>
       </c>
-      <c r="B51" s="23" t="inlineStr">
-        <is>
-          <t>Jacob Misiorowski</t>
-        </is>
-      </c>
-      <c r="C51" s="24" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D51" s="24" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="E51" s="25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F51" s="24" t="inlineStr">
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>Andrew Abbott</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="D51" s="16" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F51" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G51" s="24" t="n">
-        <v>124</v>
-      </c>
-      <c r="H51" s="26" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I51" s="26" t="n">
-        <v>0.4464</v>
-      </c>
-      <c r="J51" s="26" t="n">
-        <v>0.0736</v>
-      </c>
-      <c r="K51" s="27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L51" s="25" t="n">
+      <c r="G51" s="16" t="n">
+        <v>120</v>
+      </c>
+      <c r="H51" s="18" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="I51" s="18" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="J51" s="18" t="n">
+        <v>0.0545</v>
+      </c>
+      <c r="K51" s="19" t="n">
+        <v>4.814</v>
+      </c>
+      <c r="L51" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="M51" s="27" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="N51" s="24" t="n">
-        <v>11</v>
-      </c>
-      <c r="O51" s="28" t="inlineStr">
+      <c r="M51" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N51" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O51" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P51" s="21" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="22" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t>Matthew Boyd</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="D52" s="24" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="E52" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F52" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G52" s="24" t="n">
+        <v>132</v>
+      </c>
+      <c r="H52" s="26" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="I52" s="26" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="J52" s="26" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="K52" s="27" t="n">
+        <v>4.258</v>
+      </c>
+      <c r="L52" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M52" s="27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N52" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="O52" s="28" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P51" s="29" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="52" ht="17" customHeight="1">
-      <c r="A52" s="14" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B52" s="15" t="inlineStr">
-        <is>
-          <t>Nick Pivetta</t>
-        </is>
-      </c>
-      <c r="C52" s="16" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="D52" s="16" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="E52" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F52" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G52" s="16" t="n">
-        <v>110</v>
-      </c>
-      <c r="H52" s="18" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I52" s="18" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="J52" s="18" t="n">
-        <v>0.0638</v>
-      </c>
-      <c r="K52" s="19" t="n">
-        <v>5.548</v>
-      </c>
-      <c r="L52" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M52" s="19" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N52" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="O52" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P52" s="21" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="53" ht="17" customHeight="1">
-      <c r="A53" s="14" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B53" s="15" t="inlineStr">
-        <is>
-          <t>Andrew Abbott</t>
-        </is>
-      </c>
-      <c r="C53" s="16" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="D53" s="16" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="E53" s="17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F53" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G53" s="16" t="n">
-        <v>120</v>
-      </c>
-      <c r="H53" s="18" t="n">
-        <v>0.509</v>
-      </c>
-      <c r="I53" s="18" t="n">
-        <v>0.4545</v>
-      </c>
-      <c r="J53" s="18" t="n">
-        <v>0.0545</v>
-      </c>
-      <c r="K53" s="19" t="n">
-        <v>4.814</v>
-      </c>
-      <c r="L53" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M53" s="19" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N53" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="O53" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P53" s="21" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="54" ht="17" customHeight="1">
-      <c r="A54" s="22" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B54" s="23" t="inlineStr">
-        <is>
-          <t>Matthew Boyd</t>
-        </is>
-      </c>
-      <c r="C54" s="24" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="D54" s="24" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
-      <c r="E54" s="25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F54" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G54" s="24" t="n">
-        <v>132</v>
-      </c>
-      <c r="H54" s="26" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="I54" s="26" t="n">
-        <v>0.431</v>
-      </c>
-      <c r="J54" s="26" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="K54" s="27" t="n">
-        <v>4.258</v>
-      </c>
-      <c r="L54" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M54" s="27" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N54" s="24" t="n">
-        <v>7</v>
-      </c>
-      <c r="O54" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P54" s="29" t="n">
+      <c r="P52" s="29" t="n">
         <v>-1</v>
       </c>
     </row>

--- a/bet_log.xlsx
+++ b/bet_log.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P52"/>
+  <dimension ref="A1:P53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -687,7 +687,7 @@
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>29</v>
@@ -1192,25 +1192,25 @@
         </is>
       </c>
       <c r="G13" s="8" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="H13" s="10" t="n">
         <v>0.677</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>0.5238</v>
+        <v>0.5283</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.1532</v>
+        <v>0.1487</v>
       </c>
       <c r="K13" s="11" t="n">
         <v>4.469</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="N13" s="8" t="inlineStr"/>
       <c r="O13" s="12" t="inlineStr"/>
@@ -1222,47 +1222,47 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G14" s="8" t="n">
-        <v>-132</v>
+        <v>-144</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>0.696</v>
+        <v>0.735</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>0.569</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.127</v>
+        <v>0.1448</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>6.191</v>
+        <v>7.561</v>
       </c>
       <c r="L14" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.74</v>
+        <v>0.88</v>
       </c>
       <c r="N14" s="8" t="inlineStr"/>
       <c r="O14" s="12" t="inlineStr"/>
@@ -1274,47 +1274,47 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G15" s="8" t="n">
-        <v>100</v>
+        <v>-132</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.624</v>
+        <v>0.696</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>0.5</v>
+        <v>0.569</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.124</v>
+        <v>0.127</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>7.784</v>
+        <v>6.191</v>
       </c>
       <c r="L15" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.62</v>
+        <v>0.74</v>
       </c>
       <c r="N15" s="8" t="inlineStr"/>
       <c r="O15" s="12" t="inlineStr"/>
@@ -1326,47 +1326,47 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G16" s="8" t="n">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>0.55</v>
+        <v>0.624</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>0.4386</v>
+        <v>0.5</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.1114</v>
+        <v>0.124</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>5.551</v>
+        <v>7.784</v>
       </c>
       <c r="L16" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="N16" s="8" t="inlineStr"/>
       <c r="O16" s="12" t="inlineStr"/>
@@ -1378,17 +1378,17 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Mike Burrows</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
@@ -1400,25 +1400,25 @@
         </is>
       </c>
       <c r="G17" s="8" t="n">
-        <v>-114</v>
+        <v>128</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>0.636</v>
+        <v>0.55</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>0.5327</v>
+        <v>0.4386</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.1033</v>
+        <v>0.1114</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>4.943</v>
+        <v>5.551</v>
       </c>
       <c r="L17" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="N17" s="8" t="inlineStr"/>
       <c r="O17" s="12" t="inlineStr"/>
@@ -1430,47 +1430,47 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Shane Smith</t>
+          <t>Mike Burrows</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G18" s="8" t="n">
-        <v>100</v>
+        <v>-114</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>0.576</v>
+        <v>0.636</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>0.5</v>
+        <v>0.5327</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.076</v>
+        <v>0.1033</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>5.393</v>
+        <v>4.943</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.38</v>
+        <v>0.55</v>
       </c>
       <c r="N18" s="8" t="inlineStr"/>
       <c r="O18" s="12" t="inlineStr"/>
@@ -1482,47 +1482,47 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>George Kirby</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G19" s="8" t="n">
-        <v>104</v>
+        <v>-178</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.726</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>0.4902</v>
+        <v>0.6403</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.0708</v>
+        <v>0.0857</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>5.047</v>
+        <v>5.8</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="N19" s="8" t="inlineStr"/>
       <c r="O19" s="12" t="inlineStr"/>
@@ -1534,21 +1534,21 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Shane Smith</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
@@ -1559,22 +1559,22 @@
         <v>100</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>0.57</v>
+        <v>0.576</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>4.038</v>
+        <v>5.393</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="N20" s="8" t="inlineStr"/>
       <c r="O20" s="12" t="inlineStr"/>
@@ -1586,17 +1586,17 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Matthew Liberatore</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
@@ -1604,29 +1604,29 @@
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G21" s="8" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>0.525</v>
+        <v>0.57</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>0.4587</v>
+        <v>0.5</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.0663</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>3.583</v>
+        <v>4.038</v>
       </c>
       <c r="L21" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="N21" s="8" t="inlineStr"/>
       <c r="O21" s="12" t="inlineStr"/>
@@ -1638,41 +1638,41 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Kevin Gausman</t>
+          <t>Matthew Liberatore</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G22" s="8" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>0.529</v>
+        <v>0.525</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>0.463</v>
+        <v>0.4587</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.066</v>
+        <v>0.0663</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>7.914</v>
+        <v>3.583</v>
       </c>
       <c r="L22" s="9" t="n">
         <v>0.5</v>
@@ -1690,170 +1690,162 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Yusei Kikuchi</t>
+          <t>Kevin Gausman</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G23" s="8" t="n">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>0.556</v>
+        <v>0.529</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>0.495</v>
+        <v>0.463</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.061</v>
+        <v>0.066</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>4.364</v>
+        <v>7.914</v>
       </c>
       <c r="L23" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="N23" s="8" t="inlineStr"/>
       <c r="O23" s="12" t="inlineStr"/>
       <c r="P23" s="13" t="inlineStr"/>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="6" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Yusei Kikuchi</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>102</v>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="I24" s="10" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="K24" s="11" t="n">
+        <v>4.364</v>
+      </c>
+      <c r="L24" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M24" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N24" s="8" t="inlineStr"/>
+      <c r="O24" s="12" t="inlineStr"/>
+      <c r="P24" s="13" t="inlineStr"/>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="14" t="n">
         <v>46112</v>
       </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>Jameson Taillon</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="n">
-        <v>116</v>
-      </c>
-      <c r="H24" s="18" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="I24" s="18" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J24" s="18" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="K24" s="19" t="n">
-        <v>4.313</v>
-      </c>
-      <c r="L24" s="17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M24" s="19" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="N24" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="O24" s="20" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>Erick Fedde</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G25" s="16" t="n">
+        <v>134</v>
+      </c>
+      <c r="H25" s="18" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="I25" s="18" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="J25" s="18" t="n">
+        <v>0.09959999999999999</v>
+      </c>
+      <c r="K25" s="19" t="n">
+        <v>3.852</v>
+      </c>
+      <c r="L25" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="19" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="N25" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O25" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P24" s="21" t="n">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="22" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B25" s="23" t="inlineStr">
-        <is>
-          <t>Aaron Civale</t>
-        </is>
-      </c>
-      <c r="C25" s="24" t="inlineStr">
-        <is>
-          <t>OAK</t>
-        </is>
-      </c>
-      <c r="D25" s="24" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="E25" s="25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F25" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G25" s="24" t="n">
-        <v>-146</v>
-      </c>
-      <c r="H25" s="26" t="n">
-        <v>0.666</v>
-      </c>
-      <c r="I25" s="26" t="n">
-        <v>0.5935</v>
-      </c>
-      <c r="J25" s="26" t="n">
-        <v>0.0725</v>
-      </c>
-      <c r="K25" s="27" t="n">
-        <v>4.714</v>
-      </c>
-      <c r="L25" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M25" s="27" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="N25" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="O25" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P25" s="29" t="n">
-        <v>-1</v>
+      <c r="P25" s="21" t="n">
+        <v>1.34</v>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
@@ -1862,17 +1854,17 @@
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>Andre Pallante</t>
+          <t>Aaron Civale</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>OAK</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E26" s="25" t="n">
@@ -1884,25 +1876,25 @@
         </is>
       </c>
       <c r="G26" s="24" t="n">
-        <v>126</v>
+        <v>-146</v>
       </c>
       <c r="H26" s="26" t="n">
-        <v>0.523</v>
+        <v>0.666</v>
       </c>
       <c r="I26" s="26" t="n">
-        <v>0.4425</v>
+        <v>0.5935</v>
       </c>
       <c r="J26" s="26" t="n">
-        <v>0.0805</v>
+        <v>0.0725</v>
       </c>
       <c r="K26" s="27" t="n">
-        <v>3.876</v>
+        <v>4.714</v>
       </c>
       <c r="L26" s="25" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
       <c r="N26" s="24" t="n">
         <v>3</v>
@@ -1917,63 +1909,63 @@
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="22" t="n">
         <v>46112</v>
       </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>Max Scherzer</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="n">
-        <v>-130</v>
-      </c>
-      <c r="H27" s="18" t="n">
-        <v>0.652</v>
-      </c>
-      <c r="I27" s="18" t="n">
-        <v>0.5652</v>
-      </c>
-      <c r="J27" s="18" t="n">
-        <v>0.0868</v>
-      </c>
-      <c r="K27" s="19" t="n">
-        <v>4.757</v>
-      </c>
-      <c r="L27" s="17" t="n">
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>Andre Pallante</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="n">
+        <v>126</v>
+      </c>
+      <c r="H27" s="26" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="I27" s="26" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="J27" s="26" t="n">
+        <v>0.0805</v>
+      </c>
+      <c r="K27" s="27" t="n">
+        <v>3.876</v>
+      </c>
+      <c r="L27" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="M27" s="19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N27" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="O27" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P27" s="21" t="n">
-        <v>0.7692</v>
+      <c r="M27" s="27" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="N27" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O27" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P27" s="29" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
@@ -1982,47 +1974,47 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Erick Fedde</t>
+          <t>Max Scherzer</t>
         </is>
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E28" s="17" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="F28" s="16" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G28" s="16" t="n">
-        <v>134</v>
+        <v>-130</v>
       </c>
       <c r="H28" s="18" t="n">
-        <v>0.527</v>
+        <v>0.652</v>
       </c>
       <c r="I28" s="18" t="n">
-        <v>0.4274</v>
+        <v>0.5652</v>
       </c>
       <c r="J28" s="18" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.0868</v>
       </c>
       <c r="K28" s="19" t="n">
-        <v>3.852</v>
+        <v>4.757</v>
       </c>
       <c r="L28" s="17" t="n">
         <v>1</v>
       </c>
       <c r="M28" s="19" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="N28" s="16" t="n">
         <v>4</v>
@@ -2033,7 +2025,7 @@
         </is>
       </c>
       <c r="P28" s="21" t="n">
-        <v>1.34</v>
+        <v>0.7692</v>
       </c>
     </row>
     <row r="29" ht="17" customHeight="1">
@@ -2042,50 +2034,50 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Jameson Taillon</t>
         </is>
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E29" s="17" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G29" s="16" t="n">
-        <v>-108</v>
+        <v>116</v>
       </c>
       <c r="H29" s="18" t="n">
-        <v>0.655</v>
+        <v>0.569</v>
       </c>
       <c r="I29" s="18" t="n">
-        <v>0.5192</v>
+        <v>0.463</v>
       </c>
       <c r="J29" s="18" t="n">
-        <v>0.1358</v>
+        <v>0.106</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>4.719</v>
+        <v>4.313</v>
       </c>
       <c r="L29" s="17" t="n">
         <v>1.5</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>0.71</v>
+        <v>0.49</v>
       </c>
       <c r="N29" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O29" s="20" t="inlineStr">
         <is>
@@ -2093,7 +2085,7 @@
         </is>
       </c>
       <c r="P29" s="21" t="n">
-        <v>0.9258999999999999</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1">
@@ -2158,21 +2150,21 @@
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="14" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E31" s="17" t="n">
@@ -2184,28 +2176,28 @@
         </is>
       </c>
       <c r="G31" s="16" t="n">
-        <v>-114</v>
+        <v>-108</v>
       </c>
       <c r="H31" s="18" t="n">
-        <v>0.584</v>
+        <v>0.655</v>
       </c>
       <c r="I31" s="18" t="n">
-        <v>0.5327</v>
+        <v>0.5192</v>
       </c>
       <c r="J31" s="18" t="n">
-        <v>0.0513</v>
+        <v>0.1358</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>4.252</v>
+        <v>4.719</v>
       </c>
       <c r="L31" s="17" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>0.27</v>
+        <v>0.71</v>
       </c>
       <c r="N31" s="16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O31" s="20" t="inlineStr">
         <is>
@@ -2213,7 +2205,7 @@
         </is>
       </c>
       <c r="P31" s="21" t="n">
-        <v>0.8772</v>
+        <v>0.9258999999999999</v>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
@@ -2222,50 +2214,50 @@
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>Kyle Harrison</t>
+          <t>Simeon Woods Richardson</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E32" s="25" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F32" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G32" s="24" t="n">
-        <v>114</v>
+        <v>-112</v>
       </c>
       <c r="H32" s="26" t="n">
-        <v>0.521</v>
+        <v>0.783</v>
       </c>
       <c r="I32" s="26" t="n">
-        <v>0.4673</v>
+        <v>0.5283</v>
       </c>
       <c r="J32" s="26" t="n">
-        <v>0.0537</v>
+        <v>0.2547</v>
       </c>
       <c r="K32" s="27" t="n">
-        <v>4.628</v>
+        <v>5.562</v>
       </c>
       <c r="L32" s="25" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="M32" s="27" t="n">
-        <v>0.25</v>
+        <v>1.35</v>
       </c>
       <c r="N32" s="24" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O32" s="28" t="inlineStr">
         <is>
@@ -2277,63 +2269,63 @@
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="22" t="n">
+      <c r="A33" s="14" t="n">
         <v>46111</v>
       </c>
-      <c r="B33" s="23" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="C33" s="24" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="D33" s="24" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="E33" s="25" t="n">
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>Davis Martin</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="n">
         <v>3.5</v>
       </c>
-      <c r="F33" s="24" t="inlineStr">
+      <c r="F33" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G33" s="24" t="n">
-        <v>-174</v>
-      </c>
-      <c r="H33" s="26" t="n">
-        <v>0.6889999999999999</v>
-      </c>
-      <c r="I33" s="26" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="J33" s="26" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="K33" s="27" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="L33" s="25" t="n">
+      <c r="G33" s="16" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H33" s="18" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="I33" s="18" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="J33" s="18" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="K33" s="19" t="n">
+        <v>4.252</v>
+      </c>
+      <c r="L33" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="M33" s="27" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="N33" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="O33" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P33" s="29" t="n">
-        <v>-1</v>
+      <c r="M33" s="19" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="N33" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O33" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P33" s="21" t="n">
+        <v>0.8772</v>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
@@ -2342,50 +2334,50 @@
       </c>
       <c r="B34" s="23" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Kyle Harrison</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>OAK</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E34" s="25" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F34" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G34" s="24" t="n">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="H34" s="26" t="n">
-        <v>0.586</v>
+        <v>0.521</v>
       </c>
       <c r="I34" s="26" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="J34" s="26" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="K34" s="27" t="n">
+        <v>4.628</v>
+      </c>
+      <c r="L34" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="J34" s="26" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="K34" s="27" t="n">
-        <v>6.418</v>
-      </c>
-      <c r="L34" s="25" t="n">
-        <v>1</v>
-      </c>
       <c r="M34" s="27" t="n">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="N34" s="24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O34" s="28" t="inlineStr">
         <is>
@@ -2397,243 +2389,243 @@
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="14" t="n">
+      <c r="A35" s="22" t="n">
         <v>46111</v>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E35" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="n">
+        <v>-174</v>
+      </c>
+      <c r="H35" s="26" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="I35" s="26" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="J35" s="26" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="K35" s="27" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="L35" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M35" s="27" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="N35" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O35" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P35" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="22" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>Jacob Lopez</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>OAK</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E36" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="n">
+        <v>100</v>
+      </c>
+      <c r="H36" s="26" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="I36" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J36" s="26" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="K36" s="27" t="n">
+        <v>6.418</v>
+      </c>
+      <c r="L36" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" s="27" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N36" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P36" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="14" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>Jack Leiter</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C37" s="16" t="inlineStr">
         <is>
           <t>TEX</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>BAL</t>
         </is>
       </c>
-      <c r="E35" s="17" t="n">
+      <c r="E37" s="17" t="n">
         <v>4.5</v>
       </c>
-      <c r="F35" s="16" t="inlineStr">
+      <c r="F37" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G35" s="16" t="n">
+      <c r="G37" s="16" t="n">
         <v>-144</v>
       </c>
-      <c r="H35" s="18" t="n">
+      <c r="H37" s="18" t="n">
         <v>0.679</v>
       </c>
-      <c r="I35" s="18" t="n">
+      <c r="I37" s="18" t="n">
         <v>0.5901999999999999</v>
       </c>
-      <c r="J35" s="18" t="n">
+      <c r="J37" s="18" t="n">
         <v>0.0888</v>
       </c>
-      <c r="K35" s="19" t="n">
+      <c r="K37" s="19" t="n">
         <v>6.017</v>
       </c>
-      <c r="L35" s="17" t="n">
+      <c r="L37" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="M35" s="19" t="n">
+      <c r="M37" s="19" t="n">
         <v>0.54</v>
       </c>
-      <c r="N35" s="16" t="n">
+      <c r="N37" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="O35" s="20" t="inlineStr">
+      <c r="O37" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P35" s="21" t="n">
+      <c r="P37" s="21" t="n">
         <v>0.6944</v>
       </c>
     </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="14" t="n">
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="14" t="n">
         <v>46111</v>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>Edward Cabrera</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="C38" s="16" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="E36" s="17" t="n">
+      <c r="E38" s="17" t="n">
         <v>6.5</v>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="F38" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G36" s="16" t="n">
+      <c r="G38" s="16" t="n">
         <v>116</v>
       </c>
-      <c r="H36" s="18" t="n">
+      <c r="H38" s="18" t="n">
         <v>0.6889999999999999</v>
       </c>
-      <c r="I36" s="18" t="n">
+      <c r="I38" s="18" t="n">
         <v>0.463</v>
       </c>
-      <c r="J36" s="18" t="n">
+      <c r="J38" s="18" t="n">
         <v>0.226</v>
       </c>
-      <c r="K36" s="19" t="n">
+      <c r="K38" s="19" t="n">
         <v>5.286</v>
       </c>
-      <c r="L36" s="17" t="n">
+      <c r="L38" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="M36" s="19" t="n">
+      <c r="M38" s="19" t="n">
         <v>1.05</v>
       </c>
-      <c r="N36" s="16" t="n">
+      <c r="N38" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="O36" s="20" t="inlineStr">
+      <c r="O38" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P36" s="21" t="n">
+      <c r="P38" s="21" t="n">
         <v>1.16</v>
-      </c>
-    </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="22" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B37" s="23" t="inlineStr">
-        <is>
-          <t>Simeon Woods Richardson</t>
-        </is>
-      </c>
-      <c r="C37" s="24" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="D37" s="24" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="E37" s="25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F37" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G37" s="24" t="n">
-        <v>-112</v>
-      </c>
-      <c r="H37" s="26" t="n">
-        <v>0.783</v>
-      </c>
-      <c r="I37" s="26" t="n">
-        <v>0.5283</v>
-      </c>
-      <c r="J37" s="26" t="n">
-        <v>0.2547</v>
-      </c>
-      <c r="K37" s="27" t="n">
-        <v>5.562</v>
-      </c>
-      <c r="L37" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M37" s="27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="N37" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="O37" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P37" s="29" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="22" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B38" s="23" t="inlineStr">
-        <is>
-          <t>Jeffrey Springs</t>
-        </is>
-      </c>
-      <c r="C38" s="24" t="inlineStr">
-        <is>
-          <t>OAK</t>
-        </is>
-      </c>
-      <c r="D38" s="24" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="E38" s="25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F38" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G38" s="24" t="n">
-        <v>102</v>
-      </c>
-      <c r="H38" s="26" t="n">
-        <v>0.599</v>
-      </c>
-      <c r="I38" s="26" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="J38" s="26" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="K38" s="27" t="n">
-        <v>4.389</v>
-      </c>
-      <c r="L38" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M38" s="27" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="N38" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="O38" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P38" s="29" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="39" ht="17" customHeight="1">
@@ -2642,50 +2634,50 @@
       </c>
       <c r="B39" s="23" t="inlineStr">
         <is>
-          <t>Eury Pérez</t>
+          <t>Will Warren</t>
         </is>
       </c>
       <c r="C39" s="24" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="D39" s="24" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E39" s="25" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="F39" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G39" s="24" t="n">
-        <v>-154</v>
+        <v>110</v>
       </c>
       <c r="H39" s="26" t="n">
-        <v>0.713</v>
+        <v>0.573</v>
       </c>
       <c r="I39" s="26" t="n">
-        <v>0.6063</v>
+        <v>0.4762</v>
       </c>
       <c r="J39" s="26" t="n">
-        <v>0.1067</v>
+        <v>0.0968</v>
       </c>
       <c r="K39" s="27" t="n">
-        <v>5.311</v>
+        <v>5.339</v>
       </c>
       <c r="L39" s="25" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M39" s="27" t="n">
-        <v>0.68</v>
+        <v>0.46</v>
       </c>
       <c r="N39" s="24" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O39" s="28" t="inlineStr">
         <is>
@@ -2697,63 +2689,63 @@
       </c>
     </row>
     <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="14" t="n">
+      <c r="A40" s="22" t="n">
         <v>46109</v>
       </c>
-      <c r="B40" s="15" t="inlineStr">
-        <is>
-          <t>Michael Wacha</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="D40" s="16" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F40" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G40" s="16" t="n">
-        <v>140</v>
-      </c>
-      <c r="H40" s="18" t="n">
-        <v>0.476</v>
-      </c>
-      <c r="I40" s="18" t="n">
-        <v>0.4167</v>
-      </c>
-      <c r="J40" s="18" t="n">
-        <v>0.0593</v>
-      </c>
-      <c r="K40" s="19" t="n">
-        <v>4.645</v>
-      </c>
-      <c r="L40" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M40" s="19" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N40" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="O40" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P40" s="21" t="n">
-        <v>1.4</v>
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>Eury Pérez</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E40" s="25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F40" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G40" s="24" t="n">
+        <v>-154</v>
+      </c>
+      <c r="H40" s="26" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="I40" s="26" t="n">
+        <v>0.6063</v>
+      </c>
+      <c r="J40" s="26" t="n">
+        <v>0.1067</v>
+      </c>
+      <c r="K40" s="27" t="n">
+        <v>5.311</v>
+      </c>
+      <c r="L40" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M40" s="27" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="N40" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="O40" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P40" s="29" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
@@ -2762,21 +2754,21 @@
       </c>
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>Will Warren</t>
+          <t>Jeffrey Springs</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>OAK</t>
         </is>
       </c>
       <c r="D41" s="24" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E41" s="25" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F41" s="24" t="inlineStr">
         <is>
@@ -2784,28 +2776,28 @@
         </is>
       </c>
       <c r="G41" s="24" t="n">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H41" s="26" t="n">
-        <v>0.573</v>
+        <v>0.599</v>
       </c>
       <c r="I41" s="26" t="n">
-        <v>0.4762</v>
+        <v>0.495</v>
       </c>
       <c r="J41" s="26" t="n">
-        <v>0.0968</v>
+        <v>0.104</v>
       </c>
       <c r="K41" s="27" t="n">
-        <v>5.339</v>
+        <v>4.389</v>
       </c>
       <c r="L41" s="25" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M41" s="27" t="n">
-        <v>0.46</v>
+        <v>0.51</v>
       </c>
       <c r="N41" s="24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O41" s="28" t="inlineStr">
         <is>
@@ -2817,123 +2809,123 @@
       </c>
     </row>
     <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="22" t="n">
+      <c r="A42" s="14" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>Michael Wacha</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G42" s="16" t="n">
+        <v>140</v>
+      </c>
+      <c r="H42" s="18" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="I42" s="18" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="J42" s="18" t="n">
+        <v>0.0593</v>
+      </c>
+      <c r="K42" s="19" t="n">
+        <v>4.645</v>
+      </c>
+      <c r="L42" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M42" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N42" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O42" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P42" s="21" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="22" t="n">
         <v>46108</v>
       </c>
-      <c r="B42" s="23" t="inlineStr">
+      <c r="B43" s="23" t="inlineStr">
         <is>
           <t>Kyle Freeland</t>
         </is>
       </c>
-      <c r="C42" s="24" t="inlineStr">
+      <c r="C43" s="24" t="inlineStr">
         <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="D42" s="24" t="inlineStr">
+      <c r="D43" s="24" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="E42" s="25" t="n">
+      <c r="E43" s="25" t="n">
         <v>3.5</v>
       </c>
-      <c r="F42" s="24" t="inlineStr">
+      <c r="F43" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G42" s="24" t="n">
+      <c r="G43" s="24" t="n">
         <v>-158</v>
       </c>
-      <c r="H42" s="26" t="n">
+      <c r="H43" s="26" t="n">
         <v>0.677</v>
       </c>
-      <c r="I42" s="26" t="n">
+      <c r="I43" s="26" t="n">
         <v>0.6124000000000001</v>
       </c>
-      <c r="J42" s="26" t="n">
+      <c r="J43" s="26" t="n">
         <v>0.0646</v>
       </c>
-      <c r="K42" s="27" t="n">
+      <c r="K43" s="27" t="n">
         <v>4.869</v>
       </c>
-      <c r="L42" s="25" t="n">
+      <c r="L43" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M42" s="27" t="n">
+      <c r="M43" s="27" t="n">
         <v>0.42</v>
       </c>
-      <c r="N42" s="24" t="n">
+      <c r="N43" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="O42" s="28" t="inlineStr">
+      <c r="O43" s="28" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P42" s="29" t="n">
+      <c r="P43" s="29" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="14" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B43" s="15" t="inlineStr">
-        <is>
-          <t>Robbie Ray</t>
-        </is>
-      </c>
-      <c r="C43" s="16" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="D43" s="16" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="E43" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F43" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G43" s="16" t="n">
-        <v>116</v>
-      </c>
-      <c r="H43" s="18" t="n">
-        <v>0.532</v>
-      </c>
-      <c r="I43" s="18" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J43" s="18" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="K43" s="19" t="n">
-        <v>5.578</v>
-      </c>
-      <c r="L43" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M43" s="19" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="N43" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="O43" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P43" s="21" t="n">
-        <v>1.16</v>
       </c>
     </row>
     <row r="44" ht="17" customHeight="1">
@@ -2942,118 +2934,118 @@
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
+          <t>Robbie Ray</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G44" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="H44" s="18" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="I44" s="18" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J44" s="18" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="K44" s="19" t="n">
+        <v>5.578</v>
+      </c>
+      <c r="L44" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M44" s="19" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N44" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O44" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P44" s="21" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="14" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
           <t>Cam Schlittler</t>
         </is>
       </c>
-      <c r="C44" s="16" t="inlineStr">
+      <c r="C45" s="16" t="inlineStr">
         <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="D44" s="16" t="inlineStr">
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="E44" s="17" t="n">
+      <c r="E45" s="17" t="n">
         <v>4.5</v>
       </c>
-      <c r="F44" s="16" t="inlineStr">
+      <c r="F45" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G44" s="16" t="n">
+      <c r="G45" s="16" t="n">
         <v>-128</v>
       </c>
-      <c r="H44" s="18" t="n">
+      <c r="H45" s="18" t="n">
         <v>0.659</v>
       </c>
-      <c r="I44" s="18" t="n">
+      <c r="I45" s="18" t="n">
         <v>0.5614</v>
       </c>
-      <c r="J44" s="18" t="n">
+      <c r="J45" s="18" t="n">
         <v>0.09760000000000001</v>
       </c>
-      <c r="K44" s="19" t="n">
+      <c r="K45" s="19" t="n">
         <v>5.818</v>
       </c>
-      <c r="L44" s="17" t="n">
+      <c r="L45" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="M44" s="19" t="n">
+      <c r="M45" s="19" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="N44" s="16" t="n">
+      <c r="N45" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="O44" s="20" t="inlineStr">
+      <c r="O45" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P44" s="21" t="n">
+      <c r="P45" s="21" t="n">
         <v>0.7812</v>
-      </c>
-    </row>
-    <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="22" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B45" s="23" t="inlineStr">
-        <is>
-          <t>Shane Smith</t>
-        </is>
-      </c>
-      <c r="C45" s="24" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="D45" s="24" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="E45" s="25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F45" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G45" s="24" t="n">
-        <v>-114</v>
-      </c>
-      <c r="H45" s="26" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="I45" s="26" t="n">
-        <v>0.5327</v>
-      </c>
-      <c r="J45" s="26" t="n">
-        <v>0.0743</v>
-      </c>
-      <c r="K45" s="27" t="n">
-        <v>5.338</v>
-      </c>
-      <c r="L45" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M45" s="27" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N45" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="O45" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P45" s="29" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="46" ht="17" customHeight="1">
@@ -3062,50 +3054,50 @@
       </c>
       <c r="B46" s="23" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Shane Smith</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="D46" s="24" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E46" s="25" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="F46" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G46" s="24" t="n">
-        <v>114</v>
+        <v>-114</v>
       </c>
       <c r="H46" s="26" t="n">
-        <v>0.587</v>
+        <v>0.607</v>
       </c>
       <c r="I46" s="26" t="n">
-        <v>0.4673</v>
+        <v>0.5327</v>
       </c>
       <c r="J46" s="26" t="n">
-        <v>0.1197</v>
+        <v>0.0743</v>
       </c>
       <c r="K46" s="27" t="n">
-        <v>6.417</v>
+        <v>5.338</v>
       </c>
       <c r="L46" s="25" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M46" s="27" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="N46" s="24" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O46" s="28" t="inlineStr">
         <is>
@@ -3117,63 +3109,63 @@
       </c>
     </row>
     <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="14" t="n">
+      <c r="A47" s="22" t="n">
         <v>46107</v>
       </c>
-      <c r="B47" s="15" t="inlineStr">
-        <is>
-          <t>José Soriano</t>
-        </is>
-      </c>
-      <c r="C47" s="16" t="inlineStr">
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t>Hunter Brown</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="inlineStr">
         <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="D47" s="16" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="E47" s="17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F47" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G47" s="16" t="n">
-        <v>108</v>
-      </c>
-      <c r="H47" s="18" t="n">
+      <c r="E47" s="25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F47" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G47" s="24" t="n">
+        <v>114</v>
+      </c>
+      <c r="H47" s="26" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="I47" s="26" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="J47" s="26" t="n">
+        <v>0.1197</v>
+      </c>
+      <c r="K47" s="27" t="n">
+        <v>6.417</v>
+      </c>
+      <c r="L47" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M47" s="27" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="I47" s="18" t="n">
-        <v>0.4808</v>
-      </c>
-      <c r="J47" s="18" t="n">
-        <v>0.07920000000000001</v>
-      </c>
-      <c r="K47" s="19" t="n">
-        <v>5.163</v>
-      </c>
-      <c r="L47" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M47" s="19" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="N47" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="O47" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P47" s="21" t="n">
-        <v>1.08</v>
+      <c r="N47" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="O47" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P47" s="29" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="48" ht="17" customHeight="1">
@@ -3182,178 +3174,178 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
+          <t>José Soriano</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F48" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G48" s="16" t="n">
+        <v>108</v>
+      </c>
+      <c r="H48" s="18" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I48" s="18" t="n">
+        <v>0.4808</v>
+      </c>
+      <c r="J48" s="18" t="n">
+        <v>0.07920000000000001</v>
+      </c>
+      <c r="K48" s="19" t="n">
+        <v>5.163</v>
+      </c>
+      <c r="L48" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" s="19" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N48" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O48" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P48" s="21" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="14" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
           <t>Tarik Skubal</t>
         </is>
       </c>
-      <c r="C48" s="16" t="inlineStr">
+      <c r="C49" s="16" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="D48" s="16" t="inlineStr">
+      <c r="D49" s="16" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E48" s="17" t="n">
+      <c r="E49" s="17" t="n">
         <v>7.5</v>
       </c>
-      <c r="F48" s="16" t="inlineStr">
+      <c r="F49" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G48" s="16" t="n">
+      <c r="G49" s="16" t="n">
         <v>-172</v>
       </c>
-      <c r="H48" s="18" t="n">
+      <c r="H49" s="18" t="n">
         <v>0.767</v>
       </c>
-      <c r="I48" s="18" t="n">
+      <c r="I49" s="18" t="n">
         <v>0.6324</v>
       </c>
-      <c r="J48" s="18" t="n">
+      <c r="J49" s="18" t="n">
         <v>0.1346</v>
       </c>
-      <c r="K48" s="19" t="n">
+      <c r="K49" s="19" t="n">
         <v>5.68</v>
       </c>
-      <c r="L48" s="17" t="n">
+      <c r="L49" s="17" t="n">
         <v>1.5</v>
       </c>
-      <c r="M48" s="19" t="n">
+      <c r="M49" s="19" t="n">
         <v>0.92</v>
       </c>
-      <c r="N48" s="16" t="n">
+      <c r="N49" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="O48" s="20" t="inlineStr">
+      <c r="O49" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P48" s="21" t="n">
+      <c r="P49" s="21" t="n">
         <v>0.5814</v>
       </c>
     </row>
-    <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="22" t="n">
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="22" t="n">
         <v>46107</v>
       </c>
-      <c r="B49" s="23" t="inlineStr">
+      <c r="B50" s="23" t="inlineStr">
         <is>
           <t>Jacob Misiorowski</t>
         </is>
       </c>
-      <c r="C49" s="24" t="inlineStr">
+      <c r="C50" s="24" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="D49" s="24" t="inlineStr">
+      <c r="D50" s="24" t="inlineStr">
         <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E49" s="25" t="n">
+      <c r="E50" s="25" t="n">
         <v>5.5</v>
       </c>
-      <c r="F49" s="24" t="inlineStr">
+      <c r="F50" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G49" s="24" t="n">
+      <c r="G50" s="24" t="n">
         <v>124</v>
       </c>
-      <c r="H49" s="26" t="n">
+      <c r="H50" s="26" t="n">
         <v>0.52</v>
       </c>
-      <c r="I49" s="26" t="n">
+      <c r="I50" s="26" t="n">
         <v>0.4464</v>
       </c>
-      <c r="J49" s="26" t="n">
+      <c r="J50" s="26" t="n">
         <v>0.0736</v>
       </c>
-      <c r="K49" s="27" t="n">
+      <c r="K50" s="27" t="n">
         <v>5.5</v>
       </c>
-      <c r="L49" s="25" t="n">
+      <c r="L50" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M49" s="27" t="n">
+      <c r="M50" s="27" t="n">
         <v>0.33</v>
       </c>
-      <c r="N49" s="24" t="n">
+      <c r="N50" s="24" t="n">
         <v>11</v>
       </c>
-      <c r="O49" s="28" t="inlineStr">
+      <c r="O50" s="28" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P49" s="29" t="n">
+      <c r="P50" s="29" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="14" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t>Nick Pivetta</t>
-        </is>
-      </c>
-      <c r="C50" s="16" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="D50" s="16" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="E50" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F50" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G50" s="16" t="n">
-        <v>110</v>
-      </c>
-      <c r="H50" s="18" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I50" s="18" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="J50" s="18" t="n">
-        <v>0.0638</v>
-      </c>
-      <c r="K50" s="19" t="n">
-        <v>5.548</v>
-      </c>
-      <c r="L50" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M50" s="19" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N50" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="O50" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P50" s="21" t="n">
-        <v>1.1</v>
       </c>
     </row>
     <row r="51" ht="17" customHeight="1">
@@ -3362,21 +3354,21 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>Andrew Abbott</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="C51" s="16" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E51" s="17" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F51" s="16" t="inlineStr">
         <is>
@@ -3384,25 +3376,25 @@
         </is>
       </c>
       <c r="G51" s="16" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>0.509</v>
+        <v>0.54</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>0.4545</v>
+        <v>0.4762</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>0.0545</v>
+        <v>0.0638</v>
       </c>
       <c r="K51" s="19" t="n">
-        <v>4.814</v>
+        <v>5.548</v>
       </c>
       <c r="L51" s="17" t="n">
         <v>0.5</v>
       </c>
       <c r="M51" s="19" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="N51" s="16" t="n">
         <v>4</v>
@@ -3413,66 +3405,126 @@
         </is>
       </c>
       <c r="P51" s="21" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="14" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>Andrew Abbott</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="D52" s="16" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F52" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G52" s="16" t="n">
+        <v>120</v>
+      </c>
+      <c r="H52" s="18" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="I52" s="18" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="J52" s="18" t="n">
+        <v>0.0545</v>
+      </c>
+      <c r="K52" s="19" t="n">
+        <v>4.814</v>
+      </c>
+      <c r="L52" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M52" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N52" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O52" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P52" s="21" t="n">
         <v>1.2</v>
       </c>
     </row>
-    <row r="52" ht="17" customHeight="1">
-      <c r="A52" s="22" t="n">
+    <row r="53" ht="17" customHeight="1">
+      <c r="A53" s="22" t="n">
         <v>46107</v>
       </c>
-      <c r="B52" s="23" t="inlineStr">
+      <c r="B53" s="23" t="inlineStr">
         <is>
           <t>Matthew Boyd</t>
         </is>
       </c>
-      <c r="C52" s="24" t="inlineStr">
+      <c r="C53" s="24" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="D52" s="24" t="inlineStr">
+      <c r="D53" s="24" t="inlineStr">
         <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E52" s="25" t="n">
+      <c r="E53" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F52" s="24" t="inlineStr">
+      <c r="F53" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G52" s="24" t="n">
+      <c r="G53" s="24" t="n">
         <v>132</v>
       </c>
-      <c r="H52" s="26" t="n">
+      <c r="H53" s="26" t="n">
         <v>0.59</v>
       </c>
-      <c r="I52" s="26" t="n">
+      <c r="I53" s="26" t="n">
         <v>0.431</v>
       </c>
-      <c r="J52" s="26" t="n">
+      <c r="J53" s="26" t="n">
         <v>0.159</v>
       </c>
-      <c r="K52" s="27" t="n">
+      <c r="K53" s="27" t="n">
         <v>4.258</v>
       </c>
-      <c r="L52" s="25" t="n">
+      <c r="L53" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M52" s="27" t="n">
+      <c r="M53" s="27" t="n">
         <v>0.7</v>
       </c>
-      <c r="N52" s="24" t="n">
+      <c r="N53" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="O52" s="28" t="inlineStr">
+      <c r="O53" s="28" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P52" s="29" t="n">
+      <c r="P53" s="29" t="n">
         <v>-1</v>
       </c>
     </row>

--- a/bet_log.xlsx
+++ b/bet_log.xlsx
@@ -52,7 +52,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00C0392B"/>
+      <color rgb="001A7431"/>
       <sz val="11"/>
     </font>
     <font>
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P53"/>
+  <dimension ref="A1:P55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -687,33 +687,33 @@
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B3" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>29</v>
-      </c>
       <c r="C3" s="3" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>-0.771 u</t>
+          <t>+3.636 u</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>-2.646 u</t>
+          <t>+1.184 u</t>
         </is>
       </c>
     </row>
@@ -802,21 +802,21 @@
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="6" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Cole Ragans</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
@@ -824,29 +824,29 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G6" s="8" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>0.515</v>
+        <v>0.722</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.463</v>
+        <v>0.4587</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.052</v>
+        <v>0.2633</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>6.789</v>
+        <v>5.263</v>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>0.24</v>
+        <v>1.22</v>
       </c>
       <c r="N6" s="8" t="inlineStr"/>
       <c r="O6" s="12" t="inlineStr"/>
@@ -854,25 +854,25 @@
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Nathan Eovaldi</t>
+          <t>Taj Bradley</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
@@ -880,1272 +880,1408 @@
         </is>
       </c>
       <c r="G7" s="8" t="n">
-        <v>-168</v>
+        <v>118</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.743</v>
+        <v>0.868</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>0.6269</v>
+        <v>0.4587</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.1161</v>
+        <v>0.4093</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>7.699</v>
+        <v>7.999</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.78</v>
+        <v>1.89</v>
       </c>
       <c r="N7" s="8" t="inlineStr"/>
       <c r="O7" s="12" t="inlineStr"/>
       <c r="P7" s="13" t="inlineStr"/>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="6" t="n">
+      <c r="A8" s="14" t="n">
         <v>46113</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="K8" s="19" t="n">
+        <v>7.784</v>
+      </c>
+      <c r="L8" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M8" s="19" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="N8" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O8" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P8" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="14" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Zac Gallen</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E9" s="17" t="n">
         <v>5.5</v>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G9" s="16" t="n">
         <v>112</v>
       </c>
-      <c r="H8" s="10" t="n">
+      <c r="H9" s="18" t="n">
         <v>0.707</v>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="I9" s="18" t="n">
         <v>0.4717</v>
       </c>
-      <c r="J8" s="10" t="n">
+      <c r="J9" s="18" t="n">
         <v>0.2353</v>
       </c>
-      <c r="K8" s="11" t="n">
+      <c r="K9" s="19" t="n">
         <v>4.34</v>
       </c>
-      <c r="L8" s="9" t="n">
+      <c r="L9" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="M8" s="11" t="n">
+      <c r="M9" s="19" t="n">
         <v>1.11</v>
       </c>
-      <c r="N8" s="8" t="inlineStr"/>
-      <c r="O8" s="12" t="inlineStr"/>
-      <c r="P8" s="13" t="inlineStr"/>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="6" t="n">
+      <c r="N9" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P9" s="21" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="22" t="n">
         <v>46113</v>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>Drew Rasmussen</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E10" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G9" s="8" t="n">
+      <c r="G10" s="24" t="n">
         <v>-118</v>
       </c>
-      <c r="H9" s="10" t="n">
+      <c r="H10" s="26" t="n">
         <v>0.732</v>
       </c>
-      <c r="I9" s="10" t="n">
+      <c r="I10" s="26" t="n">
         <v>0.5413</v>
       </c>
-      <c r="J9" s="10" t="n">
+      <c r="J10" s="26" t="n">
         <v>0.1907</v>
       </c>
-      <c r="K9" s="11" t="n">
+      <c r="K10" s="27" t="n">
         <v>3.414</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="L10" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M9" s="11" t="n">
+      <c r="M10" s="27" t="n">
         <v>1.04</v>
       </c>
-      <c r="N9" s="8" t="inlineStr"/>
-      <c r="O9" s="12" t="inlineStr"/>
-      <c r="P9" s="13" t="inlineStr"/>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="6" t="n">
+      <c r="N10" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="O10" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P10" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="14" t="n">
         <v>46113</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Adrian Houser</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E11" s="17" t="n">
         <v>3.5</v>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="G11" s="16" t="n">
         <v>-125</v>
       </c>
-      <c r="H10" s="10" t="n">
+      <c r="H11" s="18" t="n">
         <v>0.724</v>
       </c>
-      <c r="I10" s="10" t="n">
+      <c r="I11" s="18" t="n">
         <v>0.5556</v>
       </c>
-      <c r="J10" s="10" t="n">
+      <c r="J11" s="18" t="n">
         <v>0.1684</v>
       </c>
-      <c r="K10" s="11" t="n">
+      <c r="K11" s="19" t="n">
         <v>5.063</v>
       </c>
-      <c r="L10" s="9" t="n">
+      <c r="L11" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="M10" s="11" t="n">
+      <c r="M11" s="19" t="n">
         <v>0.95</v>
       </c>
-      <c r="N10" s="8" t="inlineStr"/>
-      <c r="O10" s="12" t="inlineStr"/>
-      <c r="P10" s="13" t="inlineStr"/>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="6" t="n">
+      <c r="N11" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P11" s="21" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="14" t="n">
         <v>46113</v>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Tarik Skubal</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E12" s="17" t="n">
         <v>6.5</v>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G11" s="8" t="n">
+      <c r="G12" s="16" t="n">
         <v>108</v>
       </c>
-      <c r="H11" s="10" t="n">
+      <c r="H12" s="18" t="n">
         <v>0.644</v>
       </c>
-      <c r="I11" s="10" t="n">
+      <c r="I12" s="18" t="n">
         <v>0.4808</v>
       </c>
-      <c r="J11" s="10" t="n">
+      <c r="J12" s="18" t="n">
         <v>0.1632</v>
       </c>
-      <c r="K11" s="11" t="n">
+      <c r="K12" s="19" t="n">
         <v>5.865</v>
       </c>
-      <c r="L11" s="9" t="n">
+      <c r="L12" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="M11" s="11" t="n">
+      <c r="M12" s="19" t="n">
         <v>0.79</v>
       </c>
-      <c r="N11" s="8" t="inlineStr"/>
-      <c r="O11" s="12" t="inlineStr"/>
-      <c r="P11" s="13" t="inlineStr"/>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="6" t="n">
+      <c r="N12" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P12" s="21" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="22" t="n">
         <v>46113</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>Cade Cavalli</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D13" s="24" t="inlineStr">
         <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E13" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F13" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G12" s="8" t="n">
+      <c r="G13" s="24" t="n">
         <v>-102</v>
       </c>
-      <c r="H12" s="10" t="n">
+      <c r="H13" s="26" t="n">
         <v>0.668</v>
       </c>
-      <c r="I12" s="10" t="n">
+      <c r="I13" s="26" t="n">
         <v>0.505</v>
       </c>
-      <c r="J12" s="10" t="n">
+      <c r="J13" s="26" t="n">
         <v>0.163</v>
       </c>
-      <c r="K12" s="11" t="n">
+      <c r="K13" s="27" t="n">
         <v>5.697</v>
       </c>
-      <c r="L12" s="9" t="n">
+      <c r="L13" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M12" s="11" t="n">
+      <c r="M13" s="27" t="n">
         <v>0.82</v>
       </c>
-      <c r="N12" s="8" t="inlineStr"/>
-      <c r="O12" s="12" t="inlineStr"/>
-      <c r="P12" s="13" t="inlineStr"/>
-    </row>
-    <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="6" t="n">
+      <c r="N13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P13" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="14" t="n">
         <v>46113</v>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>Andrew Abbott</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E14" s="17" t="n">
         <v>5.5</v>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G13" s="8" t="n">
+      <c r="G14" s="16" t="n">
         <v>-112</v>
       </c>
-      <c r="H13" s="10" t="n">
+      <c r="H14" s="18" t="n">
         <v>0.677</v>
       </c>
-      <c r="I13" s="10" t="n">
+      <c r="I14" s="18" t="n">
         <v>0.5283</v>
       </c>
-      <c r="J13" s="10" t="n">
+      <c r="J14" s="18" t="n">
         <v>0.1487</v>
       </c>
-      <c r="K13" s="11" t="n">
+      <c r="K14" s="19" t="n">
         <v>4.469</v>
       </c>
-      <c r="L13" s="9" t="n">
+      <c r="L14" s="17" t="n">
         <v>1.5</v>
       </c>
-      <c r="M13" s="11" t="n">
+      <c r="M14" s="19" t="n">
         <v>0.79</v>
       </c>
-      <c r="N13" s="8" t="inlineStr"/>
-      <c r="O13" s="12" t="inlineStr"/>
-      <c r="P13" s="13" t="inlineStr"/>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="6" t="n">
+      <c r="N14" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="O14" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P14" s="21" t="n">
+        <v>0.8929</v>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="14" t="n">
         <v>46113</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>Cam Schlittler</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E15" s="17" t="n">
         <v>5.5</v>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G14" s="8" t="n">
+      <c r="G15" s="16" t="n">
         <v>-144</v>
       </c>
-      <c r="H14" s="10" t="n">
+      <c r="H15" s="18" t="n">
         <v>0.735</v>
       </c>
-      <c r="I14" s="10" t="n">
+      <c r="I15" s="18" t="n">
         <v>0.5901999999999999</v>
       </c>
-      <c r="J14" s="10" t="n">
+      <c r="J15" s="18" t="n">
         <v>0.1448</v>
       </c>
-      <c r="K14" s="11" t="n">
+      <c r="K15" s="19" t="n">
         <v>7.561</v>
       </c>
-      <c r="L14" s="9" t="n">
+      <c r="L15" s="17" t="n">
         <v>1.5</v>
       </c>
-      <c r="M14" s="11" t="n">
+      <c r="M15" s="19" t="n">
         <v>0.88</v>
       </c>
-      <c r="N14" s="8" t="inlineStr"/>
-      <c r="O14" s="12" t="inlineStr"/>
-      <c r="P14" s="13" t="inlineStr"/>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="6" t="n">
+      <c r="N15" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O15" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P15" s="21" t="n">
+        <v>0.6944</v>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="14" t="n">
         <v>46113</v>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>Paul Skenes</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E16" s="17" t="n">
         <v>7.5</v>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G15" s="8" t="n">
+      <c r="G16" s="16" t="n">
         <v>-132</v>
       </c>
-      <c r="H15" s="10" t="n">
+      <c r="H16" s="18" t="n">
         <v>0.696</v>
       </c>
-      <c r="I15" s="10" t="n">
+      <c r="I16" s="18" t="n">
         <v>0.569</v>
       </c>
-      <c r="J15" s="10" t="n">
+      <c r="J16" s="18" t="n">
         <v>0.127</v>
       </c>
-      <c r="K15" s="11" t="n">
+      <c r="K16" s="19" t="n">
         <v>6.191</v>
       </c>
-      <c r="L15" s="9" t="n">
+      <c r="L16" s="17" t="n">
         <v>1.5</v>
       </c>
-      <c r="M15" s="11" t="n">
+      <c r="M16" s="19" t="n">
         <v>0.74</v>
       </c>
-      <c r="N15" s="8" t="inlineStr"/>
-      <c r="O15" s="12" t="inlineStr"/>
-      <c r="P15" s="13" t="inlineStr"/>
-    </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="6" t="n">
+      <c r="N16" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="O16" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P16" s="21" t="n">
+        <v>0.7576000000000001</v>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="22" t="n">
         <v>46113</v>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Jacob Misiorowski</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="n">
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Nathan Eovaldi</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="n">
+        <v>-168</v>
+      </c>
+      <c r="H17" s="26" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="I17" s="26" t="n">
+        <v>0.6269</v>
+      </c>
+      <c r="J17" s="26" t="n">
+        <v>0.1161</v>
+      </c>
+      <c r="K17" s="27" t="n">
+        <v>7.699</v>
+      </c>
+      <c r="L17" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M17" s="27" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="N17" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="O17" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P17" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="22" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>Nick Pivetta</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="n">
+        <v>128</v>
+      </c>
+      <c r="H18" s="26" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I18" s="26" t="n">
+        <v>0.4386</v>
+      </c>
+      <c r="J18" s="26" t="n">
+        <v>0.1114</v>
+      </c>
+      <c r="K18" s="27" t="n">
+        <v>5.551</v>
+      </c>
+      <c r="L18" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N18" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="O18" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P18" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="22" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>Mike Burrows</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="E19" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H19" s="26" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="I19" s="26" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="J19" s="26" t="n">
+        <v>0.1033</v>
+      </c>
+      <c r="K19" s="27" t="n">
+        <v>4.943</v>
+      </c>
+      <c r="L19" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M19" s="27" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N19" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="O19" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P19" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="14" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>George Kirby</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G20" s="16" t="n">
+        <v>-178</v>
+      </c>
+      <c r="H20" s="18" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="I20" s="18" t="n">
+        <v>0.6403</v>
+      </c>
+      <c r="J20" s="18" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="K20" s="19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L20" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N20" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O20" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P20" s="21" t="n">
+        <v>0.5618</v>
+      </c>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="22" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>Shane Smith</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E21" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="n">
+        <v>100</v>
+      </c>
+      <c r="H21" s="26" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="I21" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J21" s="26" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="K21" s="27" t="n">
+        <v>5.393</v>
+      </c>
+      <c r="L21" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P21" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="14" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Kyle Freeland</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G22" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="H22" s="18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I22" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J22" s="18" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K22" s="19" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="L22" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M22" s="19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N22" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O22" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P22" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="14" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>Matthew Liberatore</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G23" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="H23" s="18" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="I23" s="18" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="J23" s="18" t="n">
+        <v>0.0663</v>
+      </c>
+      <c r="K23" s="19" t="n">
+        <v>3.583</v>
+      </c>
+      <c r="L23" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M23" s="19" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N23" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P23" s="21" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="14" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Kevin Gausman</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G24" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="H24" s="18" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="I24" s="18" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J24" s="18" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="K24" s="19" t="n">
+        <v>7.914</v>
+      </c>
+      <c r="L24" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M24" s="19" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N24" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="O24" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P24" s="21" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="22" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>Yusei Kikuchi</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="E25" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="n">
+        <v>102</v>
+      </c>
+      <c r="H25" s="26" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="I25" s="26" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="J25" s="26" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="K25" s="27" t="n">
+        <v>4.364</v>
+      </c>
+      <c r="L25" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M25" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N25" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="O25" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P25" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="14" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="n">
         <v>6.5</v>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G16" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="H16" s="10" t="n">
-        <v>0.624</v>
-      </c>
-      <c r="I16" s="10" t="n">
+      <c r="G26" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="H26" s="18" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="I26" s="18" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J26" s="18" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="K26" s="19" t="n">
+        <v>6.789</v>
+      </c>
+      <c r="L26" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="J16" s="10" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="K16" s="11" t="n">
-        <v>7.784</v>
-      </c>
-      <c r="L16" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M16" s="11" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="N16" s="8" t="inlineStr"/>
-      <c r="O16" s="12" t="inlineStr"/>
-      <c r="P16" s="13" t="inlineStr"/>
-    </row>
-    <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="6" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Nick Pivetta</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="n">
+      <c r="M26" s="19" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N26" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O26" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P26" s="21" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="14" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Max Scherzer</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="n">
         <v>5.5</v>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F27" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G17" s="8" t="n">
-        <v>128</v>
-      </c>
-      <c r="H17" s="10" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I17" s="10" t="n">
-        <v>0.4386</v>
-      </c>
-      <c r="J17" s="10" t="n">
-        <v>0.1114</v>
-      </c>
-      <c r="K17" s="11" t="n">
-        <v>5.551</v>
-      </c>
-      <c r="L17" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M17" s="11" t="n">
+      <c r="G27" s="16" t="n">
+        <v>-130</v>
+      </c>
+      <c r="H27" s="18" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="I27" s="18" t="n">
+        <v>0.5652</v>
+      </c>
+      <c r="J27" s="18" t="n">
+        <v>0.0868</v>
+      </c>
+      <c r="K27" s="19" t="n">
+        <v>4.757</v>
+      </c>
+      <c r="L27" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="N17" s="8" t="inlineStr"/>
-      <c r="O17" s="12" t="inlineStr"/>
-      <c r="P17" s="13" t="inlineStr"/>
-    </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="6" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Mike Burrows</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>-114</v>
-      </c>
-      <c r="H18" s="10" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="I18" s="10" t="n">
-        <v>0.5327</v>
-      </c>
-      <c r="J18" s="10" t="n">
-        <v>0.1033</v>
-      </c>
-      <c r="K18" s="11" t="n">
-        <v>4.943</v>
-      </c>
-      <c r="L18" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M18" s="11" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="N18" s="8" t="inlineStr"/>
-      <c r="O18" s="12" t="inlineStr"/>
-      <c r="P18" s="13" t="inlineStr"/>
-    </row>
-    <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="6" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>George Kirby</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>-178</v>
-      </c>
-      <c r="H19" s="10" t="n">
-        <v>0.726</v>
-      </c>
-      <c r="I19" s="10" t="n">
-        <v>0.6403</v>
-      </c>
-      <c r="J19" s="10" t="n">
-        <v>0.0857</v>
-      </c>
-      <c r="K19" s="11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L19" s="9" t="n">
+      <c r="N27" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O27" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P27" s="21" t="n">
+        <v>0.7692</v>
+      </c>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="22" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>Aaron Civale</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>OAK</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="n">
+        <v>-146</v>
+      </c>
+      <c r="H28" s="26" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="I28" s="26" t="n">
+        <v>0.5935</v>
+      </c>
+      <c r="J28" s="26" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="K28" s="27" t="n">
+        <v>4.714</v>
+      </c>
+      <c r="L28" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M28" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N28" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O28" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P28" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="22" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>Andre Pallante</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="E29" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="n">
+        <v>126</v>
+      </c>
+      <c r="H29" s="26" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="I29" s="26" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="J29" s="26" t="n">
+        <v>0.0805</v>
+      </c>
+      <c r="K29" s="27" t="n">
+        <v>3.876</v>
+      </c>
+      <c r="L29" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="M19" s="11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N19" s="8" t="inlineStr"/>
-      <c r="O19" s="12" t="inlineStr"/>
-      <c r="P19" s="13" t="inlineStr"/>
-    </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="6" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Shane Smith</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="M29" s="27" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="N29" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O29" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P29" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="14" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Erick Fedde</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="E20" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="E30" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G20" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="H20" s="10" t="n">
-        <v>0.576</v>
-      </c>
-      <c r="I20" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J20" s="10" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="K20" s="11" t="n">
-        <v>5.393</v>
-      </c>
-      <c r="L20" s="9" t="n">
+      <c r="G30" s="16" t="n">
+        <v>134</v>
+      </c>
+      <c r="H30" s="18" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="I30" s="18" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="J30" s="18" t="n">
+        <v>0.09959999999999999</v>
+      </c>
+      <c r="K30" s="19" t="n">
+        <v>3.852</v>
+      </c>
+      <c r="L30" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="M20" s="11" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="N20" s="8" t="inlineStr"/>
-      <c r="O20" s="12" t="inlineStr"/>
-      <c r="P20" s="13" t="inlineStr"/>
-    </row>
-    <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="6" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Kyle Freeland</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="H21" s="10" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="I21" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J21" s="10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K21" s="11" t="n">
-        <v>4.038</v>
-      </c>
-      <c r="L21" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M21" s="11" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="N21" s="8" t="inlineStr"/>
-      <c r="O21" s="12" t="inlineStr"/>
-      <c r="P21" s="13" t="inlineStr"/>
-    </row>
-    <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="6" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Matthew Liberatore</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>NYM</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>118</v>
-      </c>
-      <c r="H22" s="10" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="I22" s="10" t="n">
-        <v>0.4587</v>
-      </c>
-      <c r="J22" s="10" t="n">
-        <v>0.0663</v>
-      </c>
-      <c r="K22" s="11" t="n">
-        <v>3.583</v>
-      </c>
-      <c r="L22" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M22" s="11" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="N22" s="8" t="inlineStr"/>
-      <c r="O22" s="12" t="inlineStr"/>
-      <c r="P22" s="13" t="inlineStr"/>
-    </row>
-    <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="6" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Kevin Gausman</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="n">
-        <v>116</v>
-      </c>
-      <c r="H23" s="10" t="n">
-        <v>0.529</v>
-      </c>
-      <c r="I23" s="10" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J23" s="10" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="K23" s="11" t="n">
-        <v>7.914</v>
-      </c>
-      <c r="L23" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M23" s="11" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="N23" s="8" t="inlineStr"/>
-      <c r="O23" s="12" t="inlineStr"/>
-      <c r="P23" s="13" t="inlineStr"/>
-    </row>
-    <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="6" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Yusei Kikuchi</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="n">
-        <v>102</v>
-      </c>
-      <c r="H24" s="10" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="I24" s="10" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="J24" s="10" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="K24" s="11" t="n">
-        <v>4.364</v>
-      </c>
-      <c r="L24" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M24" s="11" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N24" s="8" t="inlineStr"/>
-      <c r="O24" s="12" t="inlineStr"/>
-      <c r="P24" s="13" t="inlineStr"/>
-    </row>
-    <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="14" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>Erick Fedde</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="n">
-        <v>134</v>
-      </c>
-      <c r="H25" s="18" t="n">
-        <v>0.527</v>
-      </c>
-      <c r="I25" s="18" t="n">
-        <v>0.4274</v>
-      </c>
-      <c r="J25" s="18" t="n">
-        <v>0.09959999999999999</v>
-      </c>
-      <c r="K25" s="19" t="n">
-        <v>3.852</v>
-      </c>
-      <c r="L25" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" s="19" t="n">
+      <c r="M30" s="19" t="n">
         <v>0.44</v>
       </c>
-      <c r="N25" s="16" t="n">
+      <c r="N30" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="O25" s="20" t="inlineStr">
+      <c r="O30" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P25" s="21" t="n">
+      <c r="P30" s="21" t="n">
         <v>1.34</v>
-      </c>
-    </row>
-    <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="22" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B26" s="23" t="inlineStr">
-        <is>
-          <t>Aaron Civale</t>
-        </is>
-      </c>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>OAK</t>
-        </is>
-      </c>
-      <c r="D26" s="24" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="E26" s="25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F26" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G26" s="24" t="n">
-        <v>-146</v>
-      </c>
-      <c r="H26" s="26" t="n">
-        <v>0.666</v>
-      </c>
-      <c r="I26" s="26" t="n">
-        <v>0.5935</v>
-      </c>
-      <c r="J26" s="26" t="n">
-        <v>0.0725</v>
-      </c>
-      <c r="K26" s="27" t="n">
-        <v>4.714</v>
-      </c>
-      <c r="L26" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M26" s="27" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="N26" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="O26" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P26" s="29" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="22" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B27" s="23" t="inlineStr">
-        <is>
-          <t>Andre Pallante</t>
-        </is>
-      </c>
-      <c r="C27" s="24" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="D27" s="24" t="inlineStr">
-        <is>
-          <t>NYM</t>
-        </is>
-      </c>
-      <c r="E27" s="25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F27" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G27" s="24" t="n">
-        <v>126</v>
-      </c>
-      <c r="H27" s="26" t="n">
-        <v>0.523</v>
-      </c>
-      <c r="I27" s="26" t="n">
-        <v>0.4425</v>
-      </c>
-      <c r="J27" s="26" t="n">
-        <v>0.0805</v>
-      </c>
-      <c r="K27" s="27" t="n">
-        <v>3.876</v>
-      </c>
-      <c r="L27" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" s="27" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="N27" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="O27" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P27" s="29" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="14" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>Max Scherzer</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="n">
-        <v>-130</v>
-      </c>
-      <c r="H28" s="18" t="n">
-        <v>0.652</v>
-      </c>
-      <c r="I28" s="18" t="n">
-        <v>0.5652</v>
-      </c>
-      <c r="J28" s="18" t="n">
-        <v>0.0868</v>
-      </c>
-      <c r="K28" s="19" t="n">
-        <v>4.757</v>
-      </c>
-      <c r="L28" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" s="19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N28" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="O28" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P28" s="21" t="n">
-        <v>0.7692</v>
-      </c>
-    </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="14" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>Jameson Taillon</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="n">
-        <v>116</v>
-      </c>
-      <c r="H29" s="18" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="I29" s="18" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J29" s="18" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="K29" s="19" t="n">
-        <v>4.313</v>
-      </c>
-      <c r="L29" s="17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M29" s="19" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="N29" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="O29" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P29" s="21" t="n">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="22" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B30" s="23" t="inlineStr">
-        <is>
-          <t>José Soriano</t>
-        </is>
-      </c>
-      <c r="C30" s="24" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="D30" s="24" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="E30" s="25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F30" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G30" s="24" t="n">
-        <v>-110</v>
-      </c>
-      <c r="H30" s="26" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="I30" s="26" t="n">
-        <v>0.5238</v>
-      </c>
-      <c r="J30" s="26" t="n">
-        <v>0.1522</v>
-      </c>
-      <c r="K30" s="27" t="n">
-        <v>5.918</v>
-      </c>
-      <c r="L30" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M30" s="27" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N30" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="O30" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P30" s="29" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
@@ -2154,178 +2290,178 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Jameson Taillon</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G31" s="16" t="n">
-        <v>-108</v>
+        <v>116</v>
       </c>
       <c r="H31" s="18" t="n">
-        <v>0.655</v>
+        <v>0.569</v>
       </c>
       <c r="I31" s="18" t="n">
-        <v>0.5192</v>
+        <v>0.463</v>
       </c>
       <c r="J31" s="18" t="n">
-        <v>0.1358</v>
+        <v>0.106</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>4.719</v>
+        <v>4.313</v>
       </c>
       <c r="L31" s="17" t="n">
         <v>1.5</v>
       </c>
       <c r="M31" s="19" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="N31" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O31" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P31" s="21" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="14" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>Ryan Feltner</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G32" s="16" t="n">
+        <v>-108</v>
+      </c>
+      <c r="H32" s="18" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="I32" s="18" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="J32" s="18" t="n">
+        <v>0.1358</v>
+      </c>
+      <c r="K32" s="19" t="n">
+        <v>4.719</v>
+      </c>
+      <c r="L32" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M32" s="19" t="n">
         <v>0.71</v>
       </c>
-      <c r="N31" s="16" t="n">
+      <c r="N32" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="O31" s="20" t="inlineStr">
+      <c r="O32" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P31" s="21" t="n">
+      <c r="P32" s="21" t="n">
         <v>0.9258999999999999</v>
       </c>
     </row>
-    <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="22" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B32" s="23" t="inlineStr">
-        <is>
-          <t>Simeon Woods Richardson</t>
-        </is>
-      </c>
-      <c r="C32" s="24" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="D32" s="24" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="E32" s="25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F32" s="24" t="inlineStr">
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="22" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>José Soriano</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G32" s="24" t="n">
-        <v>-112</v>
-      </c>
-      <c r="H32" s="26" t="n">
-        <v>0.783</v>
-      </c>
-      <c r="I32" s="26" t="n">
-        <v>0.5283</v>
-      </c>
-      <c r="J32" s="26" t="n">
-        <v>0.2547</v>
-      </c>
-      <c r="K32" s="27" t="n">
-        <v>5.562</v>
-      </c>
-      <c r="L32" s="25" t="n">
+      <c r="G33" s="24" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H33" s="26" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="I33" s="26" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="J33" s="26" t="n">
+        <v>0.1522</v>
+      </c>
+      <c r="K33" s="27" t="n">
+        <v>5.918</v>
+      </c>
+      <c r="L33" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M32" s="27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="N32" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="O32" s="28" t="inlineStr">
+      <c r="M33" s="27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N33" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="O33" s="28" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P32" s="29" t="n">
+      <c r="P33" s="29" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="14" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>Davis Martin</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G33" s="16" t="n">
-        <v>-114</v>
-      </c>
-      <c r="H33" s="18" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="I33" s="18" t="n">
-        <v>0.5327</v>
-      </c>
-      <c r="J33" s="18" t="n">
-        <v>0.0513</v>
-      </c>
-      <c r="K33" s="19" t="n">
-        <v>4.252</v>
-      </c>
-      <c r="L33" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M33" s="19" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="N33" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="O33" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P33" s="21" t="n">
-        <v>0.8772</v>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
@@ -2334,50 +2470,50 @@
       </c>
       <c r="B34" s="23" t="inlineStr">
         <is>
-          <t>Kyle Harrison</t>
+          <t>Simeon Woods Richardson</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E34" s="25" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F34" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G34" s="24" t="n">
-        <v>114</v>
+        <v>-112</v>
       </c>
       <c r="H34" s="26" t="n">
-        <v>0.521</v>
+        <v>0.783</v>
       </c>
       <c r="I34" s="26" t="n">
-        <v>0.4673</v>
+        <v>0.5283</v>
       </c>
       <c r="J34" s="26" t="n">
-        <v>0.0537</v>
+        <v>0.2547</v>
       </c>
       <c r="K34" s="27" t="n">
-        <v>4.628</v>
+        <v>5.562</v>
       </c>
       <c r="L34" s="25" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="M34" s="27" t="n">
-        <v>0.25</v>
+        <v>1.35</v>
       </c>
       <c r="N34" s="24" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O34" s="28" t="inlineStr">
         <is>
@@ -2389,63 +2525,63 @@
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="22" t="n">
+      <c r="A35" s="14" t="n">
         <v>46111</v>
       </c>
-      <c r="B35" s="23" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="C35" s="24" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="D35" s="24" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="E35" s="25" t="n">
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>Davis Martin</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="n">
         <v>3.5</v>
       </c>
-      <c r="F35" s="24" t="inlineStr">
+      <c r="F35" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G35" s="24" t="n">
-        <v>-174</v>
-      </c>
-      <c r="H35" s="26" t="n">
-        <v>0.6889999999999999</v>
-      </c>
-      <c r="I35" s="26" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="J35" s="26" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="K35" s="27" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="L35" s="25" t="n">
+      <c r="G35" s="16" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H35" s="18" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="I35" s="18" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="J35" s="18" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="K35" s="19" t="n">
+        <v>4.252</v>
+      </c>
+      <c r="L35" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="M35" s="27" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="N35" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="O35" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P35" s="29" t="n">
-        <v>-1</v>
+      <c r="M35" s="19" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="N35" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O35" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P35" s="21" t="n">
+        <v>0.8772</v>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
@@ -2454,50 +2590,50 @@
       </c>
       <c r="B36" s="23" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Kyle Harrison</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>OAK</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D36" s="24" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E36" s="25" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F36" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G36" s="24" t="n">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="H36" s="26" t="n">
-        <v>0.586</v>
+        <v>0.521</v>
       </c>
       <c r="I36" s="26" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="J36" s="26" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="K36" s="27" t="n">
+        <v>4.628</v>
+      </c>
+      <c r="L36" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="J36" s="26" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="K36" s="27" t="n">
-        <v>6.418</v>
-      </c>
-      <c r="L36" s="25" t="n">
-        <v>1</v>
-      </c>
       <c r="M36" s="27" t="n">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="N36" s="24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O36" s="28" t="inlineStr">
         <is>
@@ -2509,243 +2645,243 @@
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="14" t="n">
+      <c r="A37" s="22" t="n">
         <v>46111</v>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E37" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G37" s="24" t="n">
+        <v>-174</v>
+      </c>
+      <c r="H37" s="26" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="I37" s="26" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="J37" s="26" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="K37" s="27" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="L37" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M37" s="27" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="N37" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O37" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P37" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="22" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>Jacob Lopez</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>OAK</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E38" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="n">
+        <v>100</v>
+      </c>
+      <c r="H38" s="26" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="I38" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J38" s="26" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="K38" s="27" t="n">
+        <v>6.418</v>
+      </c>
+      <c r="L38" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" s="27" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N38" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P38" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="14" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
         <is>
           <t>Jack Leiter</t>
         </is>
       </c>
-      <c r="C37" s="16" t="inlineStr">
+      <c r="C39" s="16" t="inlineStr">
         <is>
           <t>TEX</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>BAL</t>
         </is>
       </c>
-      <c r="E37" s="17" t="n">
+      <c r="E39" s="17" t="n">
         <v>4.5</v>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="F39" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G37" s="16" t="n">
+      <c r="G39" s="16" t="n">
         <v>-144</v>
       </c>
-      <c r="H37" s="18" t="n">
+      <c r="H39" s="18" t="n">
         <v>0.679</v>
       </c>
-      <c r="I37" s="18" t="n">
+      <c r="I39" s="18" t="n">
         <v>0.5901999999999999</v>
       </c>
-      <c r="J37" s="18" t="n">
+      <c r="J39" s="18" t="n">
         <v>0.0888</v>
       </c>
-      <c r="K37" s="19" t="n">
+      <c r="K39" s="19" t="n">
         <v>6.017</v>
       </c>
-      <c r="L37" s="17" t="n">
+      <c r="L39" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="M37" s="19" t="n">
+      <c r="M39" s="19" t="n">
         <v>0.54</v>
       </c>
-      <c r="N37" s="16" t="n">
+      <c r="N39" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="O37" s="20" t="inlineStr">
+      <c r="O39" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P37" s="21" t="n">
+      <c r="P39" s="21" t="n">
         <v>0.6944</v>
       </c>
     </row>
-    <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="14" t="n">
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="14" t="n">
         <v>46111</v>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>Edward Cabrera</t>
         </is>
       </c>
-      <c r="C38" s="16" t="inlineStr">
+      <c r="C40" s="16" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="E38" s="17" t="n">
+      <c r="E40" s="17" t="n">
         <v>6.5</v>
       </c>
-      <c r="F38" s="16" t="inlineStr">
+      <c r="F40" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G38" s="16" t="n">
+      <c r="G40" s="16" t="n">
         <v>116</v>
       </c>
-      <c r="H38" s="18" t="n">
+      <c r="H40" s="18" t="n">
         <v>0.6889999999999999</v>
       </c>
-      <c r="I38" s="18" t="n">
+      <c r="I40" s="18" t="n">
         <v>0.463</v>
       </c>
-      <c r="J38" s="18" t="n">
+      <c r="J40" s="18" t="n">
         <v>0.226</v>
       </c>
-      <c r="K38" s="19" t="n">
+      <c r="K40" s="19" t="n">
         <v>5.286</v>
       </c>
-      <c r="L38" s="17" t="n">
+      <c r="L40" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="M38" s="19" t="n">
+      <c r="M40" s="19" t="n">
         <v>1.05</v>
       </c>
-      <c r="N38" s="16" t="n">
+      <c r="N40" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="O38" s="20" t="inlineStr">
+      <c r="O40" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P38" s="21" t="n">
+      <c r="P40" s="21" t="n">
         <v>1.16</v>
-      </c>
-    </row>
-    <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="22" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B39" s="23" t="inlineStr">
-        <is>
-          <t>Will Warren</t>
-        </is>
-      </c>
-      <c r="C39" s="24" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="D39" s="24" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="E39" s="25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F39" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G39" s="24" t="n">
-        <v>110</v>
-      </c>
-      <c r="H39" s="26" t="n">
-        <v>0.573</v>
-      </c>
-      <c r="I39" s="26" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="J39" s="26" t="n">
-        <v>0.0968</v>
-      </c>
-      <c r="K39" s="27" t="n">
-        <v>5.339</v>
-      </c>
-      <c r="L39" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M39" s="27" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="N39" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="O39" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P39" s="29" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="22" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B40" s="23" t="inlineStr">
-        <is>
-          <t>Eury Pérez</t>
-        </is>
-      </c>
-      <c r="C40" s="24" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="D40" s="24" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="E40" s="25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F40" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G40" s="24" t="n">
-        <v>-154</v>
-      </c>
-      <c r="H40" s="26" t="n">
-        <v>0.713</v>
-      </c>
-      <c r="I40" s="26" t="n">
-        <v>0.6063</v>
-      </c>
-      <c r="J40" s="26" t="n">
-        <v>0.1067</v>
-      </c>
-      <c r="K40" s="27" t="n">
-        <v>5.311</v>
-      </c>
-      <c r="L40" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M40" s="27" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="N40" s="24" t="n">
-        <v>8</v>
-      </c>
-      <c r="O40" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P40" s="29" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
@@ -2754,50 +2890,50 @@
       </c>
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>Jeffrey Springs</t>
+          <t>Eury Pérez</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>OAK</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D41" s="24" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E41" s="25" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="F41" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G41" s="24" t="n">
-        <v>102</v>
+        <v>-154</v>
       </c>
       <c r="H41" s="26" t="n">
-        <v>0.599</v>
+        <v>0.713</v>
       </c>
       <c r="I41" s="26" t="n">
-        <v>0.495</v>
+        <v>0.6063</v>
       </c>
       <c r="J41" s="26" t="n">
-        <v>0.104</v>
+        <v>0.1067</v>
       </c>
       <c r="K41" s="27" t="n">
-        <v>4.389</v>
+        <v>5.311</v>
       </c>
       <c r="L41" s="25" t="n">
         <v>1.5</v>
       </c>
       <c r="M41" s="27" t="n">
-        <v>0.51</v>
+        <v>0.68</v>
       </c>
       <c r="N41" s="24" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O41" s="28" t="inlineStr">
         <is>
@@ -2809,86 +2945,86 @@
       </c>
     </row>
     <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="14" t="n">
+      <c r="A42" s="22" t="n">
         <v>46109</v>
       </c>
-      <c r="B42" s="15" t="inlineStr">
-        <is>
-          <t>Michael Wacha</t>
-        </is>
-      </c>
-      <c r="C42" s="16" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="D42" s="16" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="E42" s="17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F42" s="16" t="inlineStr">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Jeffrey Springs</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>OAK</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E42" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F42" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G42" s="16" t="n">
-        <v>140</v>
-      </c>
-      <c r="H42" s="18" t="n">
-        <v>0.476</v>
-      </c>
-      <c r="I42" s="18" t="n">
-        <v>0.4167</v>
-      </c>
-      <c r="J42" s="18" t="n">
-        <v>0.0593</v>
-      </c>
-      <c r="K42" s="19" t="n">
-        <v>4.645</v>
-      </c>
-      <c r="L42" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M42" s="19" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N42" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="O42" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P42" s="21" t="n">
-        <v>1.4</v>
+      <c r="G42" s="24" t="n">
+        <v>102</v>
+      </c>
+      <c r="H42" s="26" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="I42" s="26" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="J42" s="26" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="K42" s="27" t="n">
+        <v>4.389</v>
+      </c>
+      <c r="L42" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M42" s="27" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N42" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O42" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P42" s="29" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="22" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B43" s="23" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Will Warren</t>
         </is>
       </c>
       <c r="C43" s="24" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="D43" s="24" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E43" s="25" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F43" s="24" t="inlineStr">
         <is>
@@ -2896,28 +3032,28 @@
         </is>
       </c>
       <c r="G43" s="24" t="n">
-        <v>-158</v>
+        <v>110</v>
       </c>
       <c r="H43" s="26" t="n">
-        <v>0.677</v>
+        <v>0.573</v>
       </c>
       <c r="I43" s="26" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.4762</v>
       </c>
       <c r="J43" s="26" t="n">
-        <v>0.0646</v>
+        <v>0.0968</v>
       </c>
       <c r="K43" s="27" t="n">
-        <v>4.869</v>
+        <v>5.339</v>
       </c>
       <c r="L43" s="25" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M43" s="27" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="N43" s="24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O43" s="28" t="inlineStr">
         <is>
@@ -2930,422 +3066,422 @@
     </row>
     <row r="44" ht="17" customHeight="1">
       <c r="A44" s="14" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>Robbie Ray</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="C44" s="16" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E44" s="17" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F44" s="16" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G44" s="16" t="n">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>0.532</v>
+        <v>0.476</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>0.463</v>
+        <v>0.4167</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0593</v>
       </c>
       <c r="K44" s="19" t="n">
-        <v>5.578</v>
+        <v>4.645</v>
       </c>
       <c r="L44" s="17" t="n">
         <v>0.5</v>
       </c>
       <c r="M44" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N44" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O44" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P44" s="21" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="22" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t>Kyle Freeland</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E45" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F45" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G45" s="24" t="n">
+        <v>-158</v>
+      </c>
+      <c r="H45" s="26" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="I45" s="26" t="n">
+        <v>0.6124000000000001</v>
+      </c>
+      <c r="J45" s="26" t="n">
+        <v>0.0646</v>
+      </c>
+      <c r="K45" s="27" t="n">
+        <v>4.869</v>
+      </c>
+      <c r="L45" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M45" s="27" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="N45" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O45" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P45" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="14" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>Robbie Ray</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F46" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G46" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="H46" s="18" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="I46" s="18" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J46" s="18" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="K46" s="19" t="n">
+        <v>5.578</v>
+      </c>
+      <c r="L46" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M46" s="19" t="n">
         <v>0.32</v>
       </c>
-      <c r="N44" s="16" t="n">
+      <c r="N46" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="O44" s="20" t="inlineStr">
+      <c r="O46" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P44" s="21" t="n">
+      <c r="P46" s="21" t="n">
         <v>1.16</v>
       </c>
     </row>
-    <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="14" t="n">
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="14" t="n">
         <v>46108</v>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>Cam Schlittler</t>
         </is>
       </c>
-      <c r="C45" s="16" t="inlineStr">
+      <c r="C47" s="16" t="inlineStr">
         <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="D45" s="16" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="E45" s="17" t="n">
+      <c r="E47" s="17" t="n">
         <v>4.5</v>
       </c>
-      <c r="F45" s="16" t="inlineStr">
+      <c r="F47" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G45" s="16" t="n">
+      <c r="G47" s="16" t="n">
         <v>-128</v>
       </c>
-      <c r="H45" s="18" t="n">
+      <c r="H47" s="18" t="n">
         <v>0.659</v>
       </c>
-      <c r="I45" s="18" t="n">
+      <c r="I47" s="18" t="n">
         <v>0.5614</v>
       </c>
-      <c r="J45" s="18" t="n">
+      <c r="J47" s="18" t="n">
         <v>0.09760000000000001</v>
       </c>
-      <c r="K45" s="19" t="n">
+      <c r="K47" s="19" t="n">
         <v>5.818</v>
       </c>
-      <c r="L45" s="17" t="n">
+      <c r="L47" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="M45" s="19" t="n">
+      <c r="M47" s="19" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="N45" s="16" t="n">
+      <c r="N47" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="O45" s="20" t="inlineStr">
+      <c r="O47" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P45" s="21" t="n">
+      <c r="P47" s="21" t="n">
         <v>0.7812</v>
       </c>
     </row>
-    <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="22" t="n">
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="22" t="n">
         <v>46107</v>
       </c>
-      <c r="B46" s="23" t="inlineStr">
+      <c r="B48" s="23" t="inlineStr">
         <is>
           <t>Shane Smith</t>
         </is>
       </c>
-      <c r="C46" s="24" t="inlineStr">
+      <c r="C48" s="24" t="inlineStr">
         <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="D46" s="24" t="inlineStr">
+      <c r="D48" s="24" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E46" s="25" t="n">
+      <c r="E48" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F46" s="24" t="inlineStr">
+      <c r="F48" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G46" s="24" t="n">
+      <c r="G48" s="24" t="n">
         <v>-114</v>
       </c>
-      <c r="H46" s="26" t="n">
+      <c r="H48" s="26" t="n">
         <v>0.607</v>
       </c>
-      <c r="I46" s="26" t="n">
+      <c r="I48" s="26" t="n">
         <v>0.5327</v>
       </c>
-      <c r="J46" s="26" t="n">
+      <c r="J48" s="26" t="n">
         <v>0.0743</v>
       </c>
-      <c r="K46" s="27" t="n">
+      <c r="K48" s="27" t="n">
         <v>5.338</v>
       </c>
-      <c r="L46" s="25" t="n">
+      <c r="L48" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M46" s="27" t="n">
+      <c r="M48" s="27" t="n">
         <v>0.4</v>
       </c>
-      <c r="N46" s="24" t="n">
+      <c r="N48" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="O46" s="28" t="inlineStr">
+      <c r="O48" s="28" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P46" s="29" t="n">
+      <c r="P48" s="29" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="22" t="n">
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="22" t="n">
         <v>46107</v>
       </c>
-      <c r="B47" s="23" t="inlineStr">
+      <c r="B49" s="23" t="inlineStr">
         <is>
           <t>Hunter Brown</t>
         </is>
       </c>
-      <c r="C47" s="24" t="inlineStr">
+      <c r="C49" s="24" t="inlineStr">
         <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="D47" s="24" t="inlineStr">
+      <c r="D49" s="24" t="inlineStr">
         <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="E47" s="25" t="n">
+      <c r="E49" s="25" t="n">
         <v>6.5</v>
       </c>
-      <c r="F47" s="24" t="inlineStr">
+      <c r="F49" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G47" s="24" t="n">
+      <c r="G49" s="24" t="n">
         <v>114</v>
       </c>
-      <c r="H47" s="26" t="n">
+      <c r="H49" s="26" t="n">
         <v>0.587</v>
       </c>
-      <c r="I47" s="26" t="n">
+      <c r="I49" s="26" t="n">
         <v>0.4673</v>
       </c>
-      <c r="J47" s="26" t="n">
+      <c r="J49" s="26" t="n">
         <v>0.1197</v>
       </c>
-      <c r="K47" s="27" t="n">
+      <c r="K49" s="27" t="n">
         <v>6.417</v>
       </c>
-      <c r="L47" s="25" t="n">
+      <c r="L49" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="M47" s="27" t="n">
+      <c r="M49" s="27" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="N47" s="24" t="n">
+      <c r="N49" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="O47" s="28" t="inlineStr">
+      <c r="O49" s="28" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P47" s="29" t="n">
+      <c r="P49" s="29" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="14" t="n">
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="14" t="n">
         <v>46107</v>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>José Soriano</t>
         </is>
       </c>
-      <c r="C48" s="16" t="inlineStr">
+      <c r="C50" s="16" t="inlineStr">
         <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="D48" s="16" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E48" s="17" t="n">
+      <c r="E50" s="17" t="n">
         <v>4.5</v>
       </c>
-      <c r="F48" s="16" t="inlineStr">
+      <c r="F50" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G48" s="16" t="n">
+      <c r="G50" s="16" t="n">
         <v>108</v>
       </c>
-      <c r="H48" s="18" t="n">
+      <c r="H50" s="18" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="I48" s="18" t="n">
+      <c r="I50" s="18" t="n">
         <v>0.4808</v>
       </c>
-      <c r="J48" s="18" t="n">
+      <c r="J50" s="18" t="n">
         <v>0.07920000000000001</v>
       </c>
-      <c r="K48" s="19" t="n">
+      <c r="K50" s="19" t="n">
         <v>5.163</v>
       </c>
-      <c r="L48" s="17" t="n">
+      <c r="L50" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="M48" s="19" t="n">
+      <c r="M50" s="19" t="n">
         <v>0.38</v>
       </c>
-      <c r="N48" s="16" t="n">
+      <c r="N50" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="O48" s="20" t="inlineStr">
+      <c r="O50" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P48" s="21" t="n">
+      <c r="P50" s="21" t="n">
         <v>1.08</v>
-      </c>
-    </row>
-    <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="14" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>Tarik Skubal</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="D49" s="16" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E49" s="17" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F49" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G49" s="16" t="n">
-        <v>-172</v>
-      </c>
-      <c r="H49" s="18" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="I49" s="18" t="n">
-        <v>0.6324</v>
-      </c>
-      <c r="J49" s="18" t="n">
-        <v>0.1346</v>
-      </c>
-      <c r="K49" s="19" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="L49" s="17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M49" s="19" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="N49" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="O49" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P49" s="21" t="n">
-        <v>0.5814</v>
-      </c>
-    </row>
-    <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="22" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B50" s="23" t="inlineStr">
-        <is>
-          <t>Jacob Misiorowski</t>
-        </is>
-      </c>
-      <c r="C50" s="24" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D50" s="24" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="E50" s="25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F50" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G50" s="24" t="n">
-        <v>124</v>
-      </c>
-      <c r="H50" s="26" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I50" s="26" t="n">
-        <v>0.4464</v>
-      </c>
-      <c r="J50" s="26" t="n">
-        <v>0.0736</v>
-      </c>
-      <c r="K50" s="27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L50" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M50" s="27" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="N50" s="24" t="n">
-        <v>11</v>
-      </c>
-      <c r="O50" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P50" s="29" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="51" ht="17" customHeight="1">
@@ -3354,177 +3490,297 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
+          <t>Tarik Skubal</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="D51" s="16" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F51" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G51" s="16" t="n">
+        <v>-172</v>
+      </c>
+      <c r="H51" s="18" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="I51" s="18" t="n">
+        <v>0.6324</v>
+      </c>
+      <c r="J51" s="18" t="n">
+        <v>0.1346</v>
+      </c>
+      <c r="K51" s="19" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="L51" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M51" s="19" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="N51" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O51" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P51" s="21" t="n">
+        <v>0.5814</v>
+      </c>
+    </row>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="22" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D52" s="24" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E52" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F52" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G52" s="24" t="n">
+        <v>124</v>
+      </c>
+      <c r="H52" s="26" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I52" s="26" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="J52" s="26" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="K52" s="27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L52" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M52" s="27" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N52" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="O52" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P52" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="53" ht="17" customHeight="1">
+      <c r="A53" s="14" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
           <t>Nick Pivetta</t>
         </is>
       </c>
-      <c r="C51" s="16" t="inlineStr">
+      <c r="C53" s="16" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="D51" s="16" t="inlineStr">
+      <c r="D53" s="16" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="E51" s="17" t="n">
+      <c r="E53" s="17" t="n">
         <v>5.5</v>
       </c>
-      <c r="F51" s="16" t="inlineStr">
+      <c r="F53" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G51" s="16" t="n">
+      <c r="G53" s="16" t="n">
         <v>110</v>
       </c>
-      <c r="H51" s="18" t="n">
+      <c r="H53" s="18" t="n">
         <v>0.54</v>
       </c>
-      <c r="I51" s="18" t="n">
+      <c r="I53" s="18" t="n">
         <v>0.4762</v>
       </c>
-      <c r="J51" s="18" t="n">
+      <c r="J53" s="18" t="n">
         <v>0.0638</v>
       </c>
-      <c r="K51" s="19" t="n">
+      <c r="K53" s="19" t="n">
         <v>5.548</v>
       </c>
-      <c r="L51" s="17" t="n">
+      <c r="L53" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="M51" s="19" t="n">
+      <c r="M53" s="19" t="n">
         <v>0.3</v>
       </c>
-      <c r="N51" s="16" t="n">
+      <c r="N53" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="O51" s="20" t="inlineStr">
+      <c r="O53" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P51" s="21" t="n">
+      <c r="P53" s="21" t="n">
         <v>1.1</v>
       </c>
     </row>
-    <row r="52" ht="17" customHeight="1">
-      <c r="A52" s="14" t="n">
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="14" t="n">
         <v>46107</v>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B54" s="15" t="inlineStr">
         <is>
           <t>Andrew Abbott</t>
         </is>
       </c>
-      <c r="C52" s="16" t="inlineStr">
+      <c r="C54" s="16" t="inlineStr">
         <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="D52" s="16" t="inlineStr">
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>BOS</t>
         </is>
       </c>
-      <c r="E52" s="17" t="n">
+      <c r="E54" s="17" t="n">
         <v>4.5</v>
       </c>
-      <c r="F52" s="16" t="inlineStr">
+      <c r="F54" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G52" s="16" t="n">
+      <c r="G54" s="16" t="n">
         <v>120</v>
       </c>
-      <c r="H52" s="18" t="n">
+      <c r="H54" s="18" t="n">
         <v>0.509</v>
       </c>
-      <c r="I52" s="18" t="n">
+      <c r="I54" s="18" t="n">
         <v>0.4545</v>
       </c>
-      <c r="J52" s="18" t="n">
+      <c r="J54" s="18" t="n">
         <v>0.0545</v>
       </c>
-      <c r="K52" s="19" t="n">
+      <c r="K54" s="19" t="n">
         <v>4.814</v>
       </c>
-      <c r="L52" s="17" t="n">
+      <c r="L54" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="M52" s="19" t="n">
+      <c r="M54" s="19" t="n">
         <v>0.25</v>
       </c>
-      <c r="N52" s="16" t="n">
+      <c r="N54" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="O52" s="20" t="inlineStr">
+      <c r="O54" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P52" s="21" t="n">
+      <c r="P54" s="21" t="n">
         <v>1.2</v>
       </c>
     </row>
-    <row r="53" ht="17" customHeight="1">
-      <c r="A53" s="22" t="n">
+    <row r="55" ht="17" customHeight="1">
+      <c r="A55" s="22" t="n">
         <v>46107</v>
       </c>
-      <c r="B53" s="23" t="inlineStr">
+      <c r="B55" s="23" t="inlineStr">
         <is>
           <t>Matthew Boyd</t>
         </is>
       </c>
-      <c r="C53" s="24" t="inlineStr">
+      <c r="C55" s="24" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="D53" s="24" t="inlineStr">
+      <c r="D55" s="24" t="inlineStr">
         <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E53" s="25" t="n">
+      <c r="E55" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F53" s="24" t="inlineStr">
+      <c r="F55" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G53" s="24" t="n">
+      <c r="G55" s="24" t="n">
         <v>132</v>
       </c>
-      <c r="H53" s="26" t="n">
+      <c r="H55" s="26" t="n">
         <v>0.59</v>
       </c>
-      <c r="I53" s="26" t="n">
+      <c r="I55" s="26" t="n">
         <v>0.431</v>
       </c>
-      <c r="J53" s="26" t="n">
+      <c r="J55" s="26" t="n">
         <v>0.159</v>
       </c>
-      <c r="K53" s="27" t="n">
+      <c r="K55" s="27" t="n">
         <v>4.258</v>
       </c>
-      <c r="L53" s="25" t="n">
+      <c r="L55" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M53" s="27" t="n">
+      <c r="M55" s="27" t="n">
         <v>0.7</v>
       </c>
-      <c r="N53" s="24" t="n">
+      <c r="N55" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="O53" s="28" t="inlineStr">
+      <c r="O55" s="28" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P53" s="29" t="n">
+      <c r="P55" s="29" t="n">
         <v>-1</v>
       </c>
     </row>

--- a/bet_log.xlsx
+++ b/bet_log.xlsx
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
@@ -828,16 +828,16 @@
         </is>
       </c>
       <c r="G6" s="8" t="n">
-        <v>118</v>
+        <v>-152</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>0.722</v>
+        <v>0.821</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.4587</v>
+        <v>0.6032</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.2633</v>
+        <v>0.2178</v>
       </c>
       <c r="K6" s="11" t="n">
         <v>5.263</v>
@@ -846,7 +846,7 @@
         <v>2</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="N6" s="8" t="inlineStr"/>
       <c r="O6" s="12" t="inlineStr"/>
@@ -880,16 +880,16 @@
         </is>
       </c>
       <c r="G7" s="8" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H7" s="10" t="n">
         <v>0.868</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>0.4587</v>
+        <v>0.463</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.4093</v>
+        <v>0.405</v>
       </c>
       <c r="K7" s="11" t="n">
         <v>7.999</v>

--- a/bet_log.xlsx
+++ b/bet_log.xlsx
@@ -806,47 +806,47 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Cole Ragans</t>
+          <t>Taj Bradley</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
       <c r="E6" s="9" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G6" s="8" t="n">
-        <v>-152</v>
+        <v>118</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>0.821</v>
+        <v>0.573</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.6032</v>
+        <v>0.4587</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.2178</v>
+        <v>0.1143</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>5.263</v>
+        <v>5.159</v>
       </c>
       <c r="L6" s="9" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>1.37</v>
+        <v>0.53</v>
       </c>
       <c r="N6" s="8" t="inlineStr"/>
       <c r="O6" s="12" t="inlineStr"/>
@@ -858,47 +858,47 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Cole Ragans</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
       <c r="E7" s="9" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G7" s="8" t="n">
-        <v>116</v>
+        <v>-152</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.868</v>
+        <v>0.738</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>0.463</v>
+        <v>0.6032</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.405</v>
+        <v>0.1348</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>7.999</v>
+        <v>5.951</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>1.89</v>
+        <v>0.85</v>
       </c>
       <c r="N7" s="8" t="inlineStr"/>
       <c r="O7" s="12" t="inlineStr"/>

--- a/bet_log.xlsx
+++ b/bet_log.xlsx
@@ -867,17 +867,17 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Will Warren</t>
+          <t>Framber Valdez</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E7" s="10" t="n">
@@ -889,25 +889,25 @@
         </is>
       </c>
       <c r="G7" s="9" t="n">
-        <v>-174</v>
+        <v>-112</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.591</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.635</v>
+        <v>0.5283</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>0.055</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>4.541</v>
+        <v>5.166</v>
       </c>
       <c r="L7" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="N7" s="9" t="inlineStr"/>
       <c r="O7" s="13" t="inlineStr"/>
@@ -919,17 +919,17 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Framber Valdez</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E8" s="10" t="n">
@@ -937,29 +937,29 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G8" s="9" t="n">
-        <v>-110</v>
+        <v>-146</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.583</v>
+        <v>0.659</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.5238</v>
+        <v>0.5935</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>0.0592</v>
+        <v>0.0655</v>
       </c>
       <c r="K8" s="12" t="n">
-        <v>5.166</v>
+        <v>6.943</v>
       </c>
       <c r="L8" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>0.31</v>
+        <v>0.4</v>
       </c>
       <c r="N8" s="9" t="inlineStr"/>
       <c r="O8" s="13" t="inlineStr"/>
@@ -971,47 +971,47 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Michael McGreevy</t>
+          <t>Michael King</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E9" s="10" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G9" s="9" t="n">
-        <v>-136</v>
+        <v>102</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.637</v>
+        <v>0.584</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.5763</v>
+        <v>0.495</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>0.0607</v>
+        <v>0.089</v>
       </c>
       <c r="K9" s="12" t="n">
-        <v>4.433</v>
+        <v>5.081</v>
       </c>
       <c r="L9" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>0.36</v>
+        <v>0.44</v>
       </c>
       <c r="N9" s="9" t="inlineStr"/>
       <c r="O9" s="13" t="inlineStr"/>
@@ -1023,47 +1023,47 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Michael King</t>
+          <t>Chad Patrick</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E10" s="10" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G10" s="9" t="n">
-        <v>102</v>
+        <v>-138</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.578</v>
+        <v>0.672</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>0.495</v>
+        <v>0.5798</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>0.083</v>
+        <v>0.0922</v>
       </c>
       <c r="K10" s="12" t="n">
-        <v>5.081</v>
+        <v>4.705</v>
       </c>
       <c r="L10" s="10" t="n">
         <v>1</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="N10" s="9" t="inlineStr"/>
       <c r="O10" s="13" t="inlineStr"/>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Chad Patrick</t>
+          <t>Cade Horton</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E11" s="10" t="n">
@@ -1097,25 +1097,25 @@
         </is>
       </c>
       <c r="G11" s="9" t="n">
-        <v>-138</v>
+        <v>-136</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.68</v>
+        <v>0.676</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.5798</v>
+        <v>0.5763</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>0.1002</v>
+        <v>0.0997</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>4.705</v>
+        <v>4.806</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="N11" s="9" t="inlineStr"/>
       <c r="O11" s="13" t="inlineStr"/>
@@ -1127,47 +1127,47 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>MacKenzie Gore</t>
+          <t>Emmet Sheehan</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E12" s="10" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G12" s="9" t="n">
-        <v>108</v>
+        <v>-128</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.722</v>
+        <v>0.68</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>0.4808</v>
+        <v>0.5614</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>0.2412</v>
+        <v>0.1186</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>5.126</v>
+        <v>6.988</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>1.16</v>
+        <v>0.68</v>
       </c>
       <c r="N12" s="9" t="inlineStr"/>
       <c r="O12" s="13" t="inlineStr"/>

--- a/bet_log.xlsx
+++ b/bet_log.xlsx
@@ -624,7 +624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P67"/>
+  <dimension ref="A1:P69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -696,7 +696,7 @@
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>56</v>
@@ -815,17 +815,17 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Chad Patrick</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E6" s="10" t="n">
@@ -837,25 +837,25 @@
         </is>
       </c>
       <c r="G6" s="9" t="n">
-        <v>-128</v>
+        <v>-154</v>
       </c>
       <c r="H6" s="11" t="n">
         <v>0.678</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>0.5614</v>
+        <v>0.6063</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>0.1166</v>
+        <v>0.0717</v>
       </c>
       <c r="K6" s="12" t="n">
-        <v>4.813</v>
+        <v>4.705</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>0.66</v>
+        <v>0.46</v>
       </c>
       <c r="N6" s="9" t="inlineStr"/>
       <c r="O6" s="13" t="inlineStr"/>
@@ -867,47 +867,47 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Carmen Mlodzinski</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G7" s="9" t="n">
-        <v>-108</v>
+        <v>-130</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.666</v>
+        <v>0.678</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.5192</v>
+        <v>0.5652</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>0.1468</v>
+        <v>0.1128</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>3.828</v>
+        <v>4.813</v>
       </c>
       <c r="L7" s="10" t="n">
         <v>1.5</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>0.76</v>
+        <v>0.65</v>
       </c>
       <c r="N7" s="9" t="inlineStr"/>
       <c r="O7" s="13" t="inlineStr"/>
@@ -919,21 +919,21 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Jack Flaherty</t>
+          <t>Carmen Mlodzinski</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E8" s="10" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
@@ -941,25 +941,25 @@
         </is>
       </c>
       <c r="G8" s="9" t="n">
-        <v>104</v>
+        <v>-108</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.653</v>
+        <v>0.666</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.4902</v>
+        <v>0.5192</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>0.1628</v>
+        <v>0.1468</v>
       </c>
       <c r="K8" s="12" t="n">
-        <v>4.756</v>
+        <v>3.828</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="N8" s="9" t="inlineStr"/>
       <c r="O8" s="13" t="inlineStr"/>
@@ -971,47 +971,47 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Ryan Weathers</t>
+          <t>Bryce Elder</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E9" s="10" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G9" s="9" t="n">
-        <v>-128</v>
+        <v>-132</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.741</v>
+        <v>0.753</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.5614</v>
+        <v>0.569</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>0.1796</v>
+        <v>0.184</v>
       </c>
       <c r="K9" s="12" t="n">
-        <v>4.217</v>
+        <v>5.551</v>
       </c>
       <c r="L9" s="10" t="n">
         <v>2</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="N9" s="9" t="inlineStr"/>
       <c r="O9" s="13" t="inlineStr"/>
@@ -1023,283 +1023,275 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Bryce Elder</t>
+          <t>Ryan Weathers</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G10" s="9" t="n">
-        <v>-132</v>
+        <v>-125</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.753</v>
+        <v>0.741</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>0.569</v>
+        <v>0.5556</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>0.184</v>
+        <v>0.1854</v>
       </c>
       <c r="K10" s="12" t="n">
-        <v>5.551</v>
+        <v>4.217</v>
       </c>
       <c r="L10" s="10" t="n">
         <v>2</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N10" s="9" t="inlineStr"/>
       <c r="O10" s="13" t="inlineStr"/>
       <c r="P10" s="14" t="inlineStr"/>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="15" t="n">
+      <c r="A11" s="7" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Steven Matz</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>116</v>
+      </c>
+      <c r="H11" s="11" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="K11" s="12" t="n">
+        <v>5.743</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" s="12" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N11" s="9" t="inlineStr"/>
+      <c r="O11" s="13" t="inlineStr"/>
+      <c r="P11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Jack Flaherty</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>116</v>
+      </c>
+      <c r="H12" s="11" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J12" s="11" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>4.756</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N12" s="9" t="inlineStr"/>
+      <c r="O12" s="13" t="inlineStr"/>
+      <c r="P12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="15" t="n">
         <v>46115</v>
       </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>Michael King</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="n">
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Mitch Keller</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>122</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>0.4505</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>0.0545</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>4.723</v>
+      </c>
+      <c r="L13" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M13" s="20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N13" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="O13" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P13" s="22" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="15" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Framber Valdez</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="n">
         <v>5.5</v>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G11" s="17" t="n">
-        <v>102</v>
-      </c>
-      <c r="H11" s="19" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="I11" s="19" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="J11" s="19" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="K11" s="20" t="n">
-        <v>5.081</v>
-      </c>
-      <c r="L11" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" s="20" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="N11" s="17" t="n">
+      <c r="G14" s="17" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H14" s="19" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>0.5283</v>
+      </c>
+      <c r="J14" s="19" t="n">
+        <v>0.06270000000000001</v>
+      </c>
+      <c r="K14" s="20" t="n">
+        <v>5.166</v>
+      </c>
+      <c r="L14" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M14" s="20" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N14" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="O11" s="21" t="inlineStr">
+      <c r="O14" s="21" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P11" s="22" t="n">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="23" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>Emmet Sheehan</t>
-        </is>
-      </c>
-      <c r="C12" s="25" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
-      <c r="D12" s="25" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
-      <c r="E12" s="26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F12" s="25" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G12" s="25" t="n">
-        <v>-128</v>
-      </c>
-      <c r="H12" s="27" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="I12" s="27" t="n">
-        <v>0.5614</v>
-      </c>
-      <c r="J12" s="27" t="n">
-        <v>0.1186</v>
-      </c>
-      <c r="K12" s="28" t="n">
-        <v>6.988</v>
-      </c>
-      <c r="L12" s="26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M12" s="28" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="N12" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="O12" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P12" s="30" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="23" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>Cade Horton</t>
-        </is>
-      </c>
-      <c r="C13" s="25" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="D13" s="25" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
-      <c r="E13" s="26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F13" s="25" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G13" s="25" t="n">
-        <v>-136</v>
-      </c>
-      <c r="H13" s="27" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="I13" s="27" t="n">
-        <v>0.5763</v>
-      </c>
-      <c r="J13" s="27" t="n">
-        <v>0.0997</v>
-      </c>
-      <c r="K13" s="28" t="n">
-        <v>4.806</v>
-      </c>
-      <c r="L13" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" s="28" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="N13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P13" s="30" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="7" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Chad Patrick</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>-138</v>
-      </c>
-      <c r="H14" s="11" t="n">
-        <v>0.672</v>
-      </c>
-      <c r="I14" s="11" t="n">
-        <v>0.5798</v>
-      </c>
-      <c r="J14" s="11" t="n">
-        <v>0.0922</v>
-      </c>
-      <c r="K14" s="12" t="n">
-        <v>4.705</v>
-      </c>
-      <c r="L14" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" s="12" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="N14" s="9" t="inlineStr"/>
-      <c r="O14" s="13" t="inlineStr"/>
-      <c r="P14" s="14" t="inlineStr"/>
+      <c r="P14" s="22" t="n">
+        <v>0.8929</v>
+      </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="15" t="n">
@@ -1367,17 +1359,17 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>Framber Valdez</t>
+          <t>Michael King</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E16" s="18" t="n">
@@ -1389,25 +1381,25 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>-112</v>
+        <v>102</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>0.591</v>
+        <v>0.584</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>0.5283</v>
+        <v>0.495</v>
       </c>
       <c r="J16" s="19" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.089</v>
       </c>
       <c r="K16" s="20" t="n">
-        <v>5.166</v>
+        <v>5.081</v>
       </c>
       <c r="L16" s="18" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M16" s="20" t="n">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="N16" s="17" t="n">
         <v>5</v>
@@ -1418,90 +1410,82 @@
         </is>
       </c>
       <c r="P16" s="22" t="n">
-        <v>0.8929</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="7" t="n">
         <v>46115</v>
       </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>Mitch Keller</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="n">
-        <v>122</v>
-      </c>
-      <c r="H17" s="19" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="I17" s="19" t="n">
-        <v>0.4505</v>
-      </c>
-      <c r="J17" s="19" t="n">
-        <v>0.0545</v>
-      </c>
-      <c r="K17" s="20" t="n">
-        <v>4.723</v>
-      </c>
-      <c r="L17" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M17" s="20" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N17" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="O17" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P17" s="22" t="n">
-        <v>1.22</v>
-      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Chad Patrick</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>-138</v>
+      </c>
+      <c r="H17" s="11" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>0.5798</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>0.0922</v>
+      </c>
+      <c r="K17" s="12" t="n">
+        <v>4.705</v>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N17" s="9" t="inlineStr"/>
+      <c r="O17" s="13" t="inlineStr"/>
+      <c r="P17" s="14" t="inlineStr"/>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="23" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Cade Horton</t>
         </is>
       </c>
       <c r="C18" s="25" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="D18" s="25" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
@@ -1509,28 +1493,28 @@
         </is>
       </c>
       <c r="G18" s="25" t="n">
-        <v>118</v>
+        <v>-136</v>
       </c>
       <c r="H18" s="27" t="n">
-        <v>0.573</v>
+        <v>0.676</v>
       </c>
       <c r="I18" s="27" t="n">
-        <v>0.4587</v>
+        <v>0.5763</v>
       </c>
       <c r="J18" s="27" t="n">
-        <v>0.1143</v>
+        <v>0.0997</v>
       </c>
       <c r="K18" s="28" t="n">
-        <v>5.159</v>
+        <v>4.806</v>
       </c>
       <c r="L18" s="26" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M18" s="28" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="N18" s="25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O18" s="29" t="inlineStr">
         <is>
@@ -1543,54 +1527,54 @@
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="23" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>Cole Ragans</t>
+          <t>Emmet Sheehan</t>
         </is>
       </c>
       <c r="C19" s="25" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="D19" s="25" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E19" s="26" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G19" s="25" t="n">
-        <v>-152</v>
+        <v>-128</v>
       </c>
       <c r="H19" s="27" t="n">
-        <v>0.738</v>
+        <v>0.68</v>
       </c>
       <c r="I19" s="27" t="n">
-        <v>0.6032</v>
+        <v>0.5614</v>
       </c>
       <c r="J19" s="27" t="n">
-        <v>0.1348</v>
+        <v>0.1186</v>
       </c>
       <c r="K19" s="28" t="n">
-        <v>5.951</v>
+        <v>6.988</v>
       </c>
       <c r="L19" s="26" t="n">
         <v>1.5</v>
       </c>
       <c r="M19" s="28" t="n">
-        <v>0.85</v>
+        <v>0.68</v>
       </c>
       <c r="N19" s="25" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O19" s="29" t="inlineStr">
         <is>
@@ -1603,25 +1587,25 @@
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="23" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>Mike Burrows</t>
+          <t>Cole Ragans</t>
         </is>
       </c>
       <c r="C20" s="25" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D20" s="25" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
@@ -1629,28 +1613,28 @@
         </is>
       </c>
       <c r="G20" s="25" t="n">
-        <v>-114</v>
+        <v>-152</v>
       </c>
       <c r="H20" s="27" t="n">
-        <v>0.636</v>
+        <v>0.738</v>
       </c>
       <c r="I20" s="27" t="n">
-        <v>0.5327</v>
+        <v>0.6032</v>
       </c>
       <c r="J20" s="27" t="n">
-        <v>0.1033</v>
+        <v>0.1348</v>
       </c>
       <c r="K20" s="28" t="n">
-        <v>4.943</v>
+        <v>5.951</v>
       </c>
       <c r="L20" s="26" t="n">
         <v>1.5</v>
       </c>
       <c r="M20" s="28" t="n">
-        <v>0.55</v>
+        <v>0.85</v>
       </c>
       <c r="N20" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O20" s="29" t="inlineStr">
         <is>
@@ -1662,123 +1646,123 @@
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="15" t="n">
+      <c r="A21" s="23" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>Taj Bradley</t>
+        </is>
+      </c>
+      <c r="C21" s="25" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="D21" s="25" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="E21" s="26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F21" s="25" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G21" s="25" t="n">
+        <v>118</v>
+      </c>
+      <c r="H21" s="27" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="I21" s="27" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="J21" s="27" t="n">
+        <v>0.1143</v>
+      </c>
+      <c r="K21" s="28" t="n">
+        <v>5.159</v>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M21" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="N21" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O21" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P21" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="23" t="n">
         <v>46113</v>
       </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>Andrew Abbott</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="n">
-        <v>-112</v>
-      </c>
-      <c r="H21" s="19" t="n">
-        <v>0.677</v>
-      </c>
-      <c r="I21" s="19" t="n">
-        <v>0.5283</v>
-      </c>
-      <c r="J21" s="19" t="n">
-        <v>0.1487</v>
-      </c>
-      <c r="K21" s="20" t="n">
-        <v>4.469</v>
-      </c>
-      <c r="L21" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M21" s="20" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="N21" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="O21" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P21" s="22" t="n">
-        <v>0.8929</v>
-      </c>
-    </row>
-    <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>Cam Schlittler</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>Cade Cavalli</t>
+        </is>
+      </c>
+      <c r="C22" s="25" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="D22" s="25" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F22" s="25" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G22" s="17" t="n">
-        <v>-144</v>
-      </c>
-      <c r="H22" s="19" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="I22" s="19" t="n">
-        <v>0.5901999999999999</v>
-      </c>
-      <c r="J22" s="19" t="n">
-        <v>0.1448</v>
-      </c>
-      <c r="K22" s="20" t="n">
-        <v>7.561</v>
-      </c>
-      <c r="L22" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M22" s="20" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="N22" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="O22" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P22" s="22" t="n">
-        <v>0.6944</v>
+      <c r="G22" s="25" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H22" s="27" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="I22" s="27" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="J22" s="27" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="K22" s="28" t="n">
+        <v>5.697</v>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" s="28" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="N22" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O22" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P22" s="30" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
@@ -1787,238 +1771,238 @@
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E23" s="18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="n">
+        <v>116</v>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="I23" s="19" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J23" s="19" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="K23" s="20" t="n">
+        <v>6.789</v>
+      </c>
+      <c r="L23" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M23" s="20" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N23" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="O23" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P23" s="22" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="23" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>Yusei Kikuchi</t>
+        </is>
+      </c>
+      <c r="C24" s="25" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D24" s="25" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F24" s="25" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G24" s="25" t="n">
+        <v>102</v>
+      </c>
+      <c r="H24" s="27" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="I24" s="27" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="J24" s="27" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="K24" s="28" t="n">
+        <v>4.364</v>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M24" s="28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N24" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="O24" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P24" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>Kevin Gausman</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="n">
         <v>7.5</v>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="n">
+        <v>116</v>
+      </c>
+      <c r="H25" s="19" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="I25" s="19" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J25" s="19" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="K25" s="20" t="n">
+        <v>7.914</v>
+      </c>
+      <c r="L25" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M25" s="20" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N25" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="O25" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P25" s="22" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>Matthew Liberatore</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G23" s="17" t="n">
-        <v>-132</v>
-      </c>
-      <c r="H23" s="19" t="n">
-        <v>0.696</v>
-      </c>
-      <c r="I23" s="19" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="J23" s="19" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="K23" s="20" t="n">
-        <v>6.191</v>
-      </c>
-      <c r="L23" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M23" s="20" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="N23" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="O23" s="21" t="inlineStr">
+      <c r="G26" s="17" t="n">
+        <v>118</v>
+      </c>
+      <c r="H26" s="19" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="I26" s="19" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="J26" s="19" t="n">
+        <v>0.0663</v>
+      </c>
+      <c r="K26" s="20" t="n">
+        <v>3.583</v>
+      </c>
+      <c r="L26" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M26" s="20" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N26" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O26" s="21" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P23" s="22" t="n">
-        <v>0.7576000000000001</v>
-      </c>
-    </row>
-    <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>Jacob Misiorowski</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="n">
-        <v>100</v>
-      </c>
-      <c r="H24" s="19" t="n">
-        <v>0.624</v>
-      </c>
-      <c r="I24" s="19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J24" s="19" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="K24" s="20" t="n">
-        <v>7.784</v>
-      </c>
-      <c r="L24" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M24" s="20" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="N24" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="O24" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P24" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="23" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B25" s="24" t="inlineStr">
-        <is>
-          <t>Nathan Eovaldi</t>
-        </is>
-      </c>
-      <c r="C25" s="25" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
-      <c r="D25" s="25" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="E25" s="26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F25" s="25" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G25" s="25" t="n">
-        <v>-168</v>
-      </c>
-      <c r="H25" s="27" t="n">
-        <v>0.743</v>
-      </c>
-      <c r="I25" s="27" t="n">
-        <v>0.6269</v>
-      </c>
-      <c r="J25" s="27" t="n">
-        <v>0.1161</v>
-      </c>
-      <c r="K25" s="28" t="n">
-        <v>7.699</v>
-      </c>
-      <c r="L25" s="26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M25" s="28" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="N25" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="O25" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P25" s="30" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="23" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B26" s="24" t="inlineStr">
-        <is>
-          <t>Nick Pivetta</t>
-        </is>
-      </c>
-      <c r="C26" s="25" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="D26" s="25" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="E26" s="26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F26" s="25" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G26" s="25" t="n">
-        <v>128</v>
-      </c>
-      <c r="H26" s="27" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I26" s="27" t="n">
-        <v>0.4386</v>
-      </c>
-      <c r="J26" s="27" t="n">
-        <v>0.1114</v>
-      </c>
-      <c r="K26" s="28" t="n">
-        <v>5.551</v>
-      </c>
-      <c r="L26" s="26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M26" s="28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N26" s="25" t="n">
-        <v>8</v>
-      </c>
-      <c r="O26" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P26" s="30" t="n">
-        <v>-1</v>
+      <c r="P26" s="22" t="n">
+        <v>1.18</v>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
@@ -2027,21 +2011,21 @@
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D27" s="17" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E27" s="18" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
@@ -2049,396 +2033,396 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>0.515</v>
+        <v>0.57</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>0.463</v>
+        <v>0.5</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>0.052</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K27" s="20" t="n">
-        <v>6.789</v>
+        <v>4.038</v>
       </c>
       <c r="L27" s="18" t="n">
         <v>0.5</v>
       </c>
       <c r="M27" s="20" t="n">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="N27" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="O27" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P27" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="23" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>Shane Smith</t>
+        </is>
+      </c>
+      <c r="C28" s="25" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D28" s="25" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F28" s="25" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G28" s="25" t="n">
+        <v>100</v>
+      </c>
+      <c r="H28" s="27" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="I28" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J28" s="27" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="K28" s="28" t="n">
+        <v>5.393</v>
+      </c>
+      <c r="L28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" s="28" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N28" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P28" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>George Kirby</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="n">
+        <v>-178</v>
+      </c>
+      <c r="H29" s="19" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="I29" s="19" t="n">
+        <v>0.6403</v>
+      </c>
+      <c r="J29" s="19" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="K29" s="20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L29" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N29" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="O29" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P29" s="22" t="n">
+        <v>0.5618</v>
+      </c>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="23" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>Mike Burrows</t>
+        </is>
+      </c>
+      <c r="C30" s="25" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="D30" s="25" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F30" s="25" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G30" s="25" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H30" s="27" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="I30" s="27" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="J30" s="27" t="n">
+        <v>0.1033</v>
+      </c>
+      <c r="K30" s="28" t="n">
+        <v>4.943</v>
+      </c>
+      <c r="L30" s="26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M30" s="28" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N30" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="O30" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P30" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="23" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>Nick Pivetta</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D31" s="25" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="E31" s="26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F31" s="25" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G31" s="25" t="n">
+        <v>128</v>
+      </c>
+      <c r="H31" s="27" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I31" s="27" t="n">
+        <v>0.4386</v>
+      </c>
+      <c r="J31" s="27" t="n">
+        <v>0.1114</v>
+      </c>
+      <c r="K31" s="28" t="n">
+        <v>5.551</v>
+      </c>
+      <c r="L31" s="26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M31" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N31" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="O31" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P31" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="23" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>Nathan Eovaldi</t>
+        </is>
+      </c>
+      <c r="C32" s="25" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="D32" s="25" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E32" s="26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F32" s="25" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G32" s="25" t="n">
+        <v>-168</v>
+      </c>
+      <c r="H32" s="27" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="I32" s="27" t="n">
+        <v>0.6269</v>
+      </c>
+      <c r="J32" s="27" t="n">
+        <v>0.1161</v>
+      </c>
+      <c r="K32" s="28" t="n">
+        <v>7.699</v>
+      </c>
+      <c r="L32" s="26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M32" s="28" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="N32" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="O32" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P32" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="H33" s="19" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="I33" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J33" s="19" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="K33" s="20" t="n">
+        <v>7.784</v>
+      </c>
+      <c r="L33" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M33" s="20" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="N33" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="O27" s="21" t="inlineStr">
+      <c r="O33" s="21" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P27" s="22" t="n">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>George Kirby</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="n">
-        <v>-178</v>
-      </c>
-      <c r="H28" s="19" t="n">
-        <v>0.726</v>
-      </c>
-      <c r="I28" s="19" t="n">
-        <v>0.6403</v>
-      </c>
-      <c r="J28" s="19" t="n">
-        <v>0.0857</v>
-      </c>
-      <c r="K28" s="20" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L28" s="18" t="n">
+      <c r="P33" s="22" t="n">
         <v>1</v>
-      </c>
-      <c r="M28" s="20" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N28" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="O28" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P28" s="22" t="n">
-        <v>0.5618</v>
-      </c>
-    </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="23" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B29" s="24" t="inlineStr">
-        <is>
-          <t>Shane Smith</t>
-        </is>
-      </c>
-      <c r="C29" s="25" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="D29" s="25" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="E29" s="26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F29" s="25" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G29" s="25" t="n">
-        <v>100</v>
-      </c>
-      <c r="H29" s="27" t="n">
-        <v>0.576</v>
-      </c>
-      <c r="I29" s="27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J29" s="27" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="K29" s="28" t="n">
-        <v>5.393</v>
-      </c>
-      <c r="L29" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" s="28" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="N29" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O29" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P29" s="30" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>Kyle Freeland</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="n">
-        <v>100</v>
-      </c>
-      <c r="H30" s="19" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="I30" s="19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J30" s="19" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K30" s="20" t="n">
-        <v>4.038</v>
-      </c>
-      <c r="L30" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M30" s="20" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="N30" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="O30" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P30" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>Matthew Liberatore</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>NYM</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G31" s="17" t="n">
-        <v>118</v>
-      </c>
-      <c r="H31" s="19" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="I31" s="19" t="n">
-        <v>0.4587</v>
-      </c>
-      <c r="J31" s="19" t="n">
-        <v>0.0663</v>
-      </c>
-      <c r="K31" s="20" t="n">
-        <v>3.583</v>
-      </c>
-      <c r="L31" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M31" s="20" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="N31" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="O31" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P31" s="22" t="n">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>Kevin Gausman</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G32" s="17" t="n">
-        <v>116</v>
-      </c>
-      <c r="H32" s="19" t="n">
-        <v>0.529</v>
-      </c>
-      <c r="I32" s="19" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J32" s="19" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="K32" s="20" t="n">
-        <v>7.914</v>
-      </c>
-      <c r="L32" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M32" s="20" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="N32" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="O32" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P32" s="22" t="n">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="23" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B33" s="24" t="inlineStr">
-        <is>
-          <t>Yusei Kikuchi</t>
-        </is>
-      </c>
-      <c r="C33" s="25" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="D33" s="25" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="E33" s="26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F33" s="25" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G33" s="25" t="n">
-        <v>102</v>
-      </c>
-      <c r="H33" s="27" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="I33" s="27" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="J33" s="27" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="K33" s="28" t="n">
-        <v>4.364</v>
-      </c>
-      <c r="L33" s="26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M33" s="28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N33" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="O33" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P33" s="30" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
@@ -2447,21 +2431,21 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="D34" s="17" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E34" s="18" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
@@ -2469,28 +2453,28 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>108</v>
+        <v>-132</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>0.644</v>
+        <v>0.696</v>
       </c>
       <c r="I34" s="19" t="n">
-        <v>0.4808</v>
+        <v>0.569</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>0.1632</v>
+        <v>0.127</v>
       </c>
       <c r="K34" s="20" t="n">
-        <v>5.865</v>
+        <v>6.191</v>
       </c>
       <c r="L34" s="18" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M34" s="20" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="N34" s="17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O34" s="21" t="inlineStr">
         <is>
@@ -2498,67 +2482,67 @@
         </is>
       </c>
       <c r="P34" s="22" t="n">
-        <v>1.08</v>
+        <v>0.7576000000000001</v>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="23" t="n">
+      <c r="A35" s="15" t="n">
         <v>46113</v>
       </c>
-      <c r="B35" s="24" t="inlineStr">
-        <is>
-          <t>Cade Cavalli</t>
-        </is>
-      </c>
-      <c r="C35" s="25" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
-      <c r="D35" s="25" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="E35" s="26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F35" s="25" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>Cam Schlittler</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G35" s="25" t="n">
-        <v>-102</v>
-      </c>
-      <c r="H35" s="27" t="n">
-        <v>0.668</v>
-      </c>
-      <c r="I35" s="27" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="J35" s="27" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="K35" s="28" t="n">
-        <v>5.697</v>
-      </c>
-      <c r="L35" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="M35" s="28" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="N35" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="O35" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P35" s="30" t="n">
-        <v>-1</v>
+      <c r="G35" s="17" t="n">
+        <v>-144</v>
+      </c>
+      <c r="H35" s="19" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="I35" s="19" t="n">
+        <v>0.5901999999999999</v>
+      </c>
+      <c r="J35" s="19" t="n">
+        <v>0.1448</v>
+      </c>
+      <c r="K35" s="20" t="n">
+        <v>7.561</v>
+      </c>
+      <c r="L35" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M35" s="20" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N35" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="O35" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P35" s="22" t="n">
+        <v>0.6944</v>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
@@ -2567,50 +2551,50 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>Adrian Houser</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="D36" s="17" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E36" s="18" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>-125</v>
+        <v>-112</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>0.724</v>
+        <v>0.677</v>
       </c>
       <c r="I36" s="19" t="n">
-        <v>0.5556</v>
+        <v>0.5283</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>0.1684</v>
+        <v>0.1487</v>
       </c>
       <c r="K36" s="20" t="n">
-        <v>5.063</v>
+        <v>4.469</v>
       </c>
       <c r="L36" s="18" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M36" s="20" t="n">
-        <v>0.95</v>
+        <v>0.79</v>
       </c>
       <c r="N36" s="17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O36" s="21" t="inlineStr">
         <is>
@@ -2618,7 +2602,7 @@
         </is>
       </c>
       <c r="P36" s="22" t="n">
-        <v>0.8</v>
+        <v>0.8929</v>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
@@ -2627,21 +2611,21 @@
       </c>
       <c r="B37" s="16" t="inlineStr">
         <is>
-          <t>Zac Gallen</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
       <c r="E37" s="18" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="F37" s="17" t="inlineStr">
         <is>
@@ -2649,28 +2633,28 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>0.707</v>
+        <v>0.644</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>0.4717</v>
+        <v>0.4808</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>0.2353</v>
+        <v>0.1632</v>
       </c>
       <c r="K37" s="20" t="n">
-        <v>4.34</v>
+        <v>5.865</v>
       </c>
       <c r="L37" s="18" t="n">
         <v>2</v>
       </c>
       <c r="M37" s="20" t="n">
-        <v>1.11</v>
+        <v>0.79</v>
       </c>
       <c r="N37" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O37" s="21" t="inlineStr">
         <is>
@@ -2678,7 +2662,7 @@
         </is>
       </c>
       <c r="P37" s="22" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="38" ht="17" customHeight="1">
@@ -2742,243 +2726,243 @@
       </c>
     </row>
     <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="23" t="n">
+      <c r="A39" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>Zac Gallen</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F39" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G39" s="17" t="n">
+        <v>112</v>
+      </c>
+      <c r="H39" s="19" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="I39" s="19" t="n">
+        <v>0.4717</v>
+      </c>
+      <c r="J39" s="19" t="n">
+        <v>0.2353</v>
+      </c>
+      <c r="K39" s="20" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="L39" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M39" s="20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N39" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O39" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P39" s="22" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>Adrian Houser</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H40" s="19" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="I40" s="19" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="J40" s="19" t="n">
+        <v>0.1684</v>
+      </c>
+      <c r="K40" s="20" t="n">
+        <v>5.063</v>
+      </c>
+      <c r="L40" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M40" s="20" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N40" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="O40" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P40" s="22" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="23" t="n">
         <v>46112</v>
       </c>
-      <c r="B39" s="24" t="inlineStr">
+      <c r="B41" s="24" t="inlineStr">
         <is>
           <t>Aaron Civale</t>
         </is>
       </c>
-      <c r="C39" s="25" t="inlineStr">
+      <c r="C41" s="25" t="inlineStr">
         <is>
           <t>OAK</t>
         </is>
       </c>
-      <c r="D39" s="25" t="inlineStr">
+      <c r="D41" s="25" t="inlineStr">
         <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E39" s="26" t="n">
+      <c r="E41" s="26" t="n">
         <v>3.5</v>
       </c>
-      <c r="F39" s="25" t="inlineStr">
+      <c r="F41" s="25" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G39" s="25" t="n">
+      <c r="G41" s="25" t="n">
         <v>-146</v>
       </c>
-      <c r="H39" s="27" t="n">
+      <c r="H41" s="27" t="n">
         <v>0.666</v>
       </c>
-      <c r="I39" s="27" t="n">
+      <c r="I41" s="27" t="n">
         <v>0.5935</v>
       </c>
-      <c r="J39" s="27" t="n">
+      <c r="J41" s="27" t="n">
         <v>0.0725</v>
       </c>
-      <c r="K39" s="28" t="n">
+      <c r="K41" s="28" t="n">
         <v>4.714</v>
       </c>
-      <c r="L39" s="26" t="n">
+      <c r="L41" s="26" t="n">
         <v>0.5</v>
       </c>
-      <c r="M39" s="28" t="n">
+      <c r="M41" s="28" t="n">
         <v>0.45</v>
       </c>
-      <c r="N39" s="25" t="n">
+      <c r="N41" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="O39" s="29" t="inlineStr">
+      <c r="O41" s="29" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P39" s="30" t="n">
+      <c r="P41" s="30" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="23" t="n">
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="23" t="n">
         <v>46112</v>
       </c>
-      <c r="B40" s="24" t="inlineStr">
+      <c r="B42" s="24" t="inlineStr">
         <is>
           <t>Andre Pallante</t>
         </is>
       </c>
-      <c r="C40" s="25" t="inlineStr">
+      <c r="C42" s="25" t="inlineStr">
         <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="D40" s="25" t="inlineStr">
+      <c r="D42" s="25" t="inlineStr">
         <is>
           <t>NYM</t>
         </is>
       </c>
-      <c r="E40" s="26" t="n">
+      <c r="E42" s="26" t="n">
         <v>3.5</v>
       </c>
-      <c r="F40" s="25" t="inlineStr">
+      <c r="F42" s="25" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G40" s="25" t="n">
+      <c r="G42" s="25" t="n">
         <v>126</v>
       </c>
-      <c r="H40" s="27" t="n">
+      <c r="H42" s="27" t="n">
         <v>0.523</v>
       </c>
-      <c r="I40" s="27" t="n">
+      <c r="I42" s="27" t="n">
         <v>0.4425</v>
       </c>
-      <c r="J40" s="27" t="n">
+      <c r="J42" s="27" t="n">
         <v>0.0805</v>
       </c>
-      <c r="K40" s="28" t="n">
+      <c r="K42" s="28" t="n">
         <v>3.876</v>
       </c>
-      <c r="L40" s="26" t="n">
+      <c r="L42" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="M40" s="28" t="n">
+      <c r="M42" s="28" t="n">
         <v>0.36</v>
       </c>
-      <c r="N40" s="25" t="n">
+      <c r="N42" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="O40" s="29" t="inlineStr">
+      <c r="O42" s="29" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P40" s="30" t="n">
+      <c r="P42" s="30" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="15" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B41" s="16" t="inlineStr">
-        <is>
-          <t>Max Scherzer</t>
-        </is>
-      </c>
-      <c r="C41" s="17" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="D41" s="17" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="E41" s="18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F41" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G41" s="17" t="n">
-        <v>-130</v>
-      </c>
-      <c r="H41" s="19" t="n">
-        <v>0.652</v>
-      </c>
-      <c r="I41" s="19" t="n">
-        <v>0.5652</v>
-      </c>
-      <c r="J41" s="19" t="n">
-        <v>0.0868</v>
-      </c>
-      <c r="K41" s="20" t="n">
-        <v>4.757</v>
-      </c>
-      <c r="L41" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M41" s="20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N41" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="O41" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P41" s="22" t="n">
-        <v>0.7692</v>
-      </c>
-    </row>
-    <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="15" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B42" s="16" t="inlineStr">
-        <is>
-          <t>Erick Fedde</t>
-        </is>
-      </c>
-      <c r="C42" s="17" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="E42" s="18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F42" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G42" s="17" t="n">
-        <v>134</v>
-      </c>
-      <c r="H42" s="19" t="n">
-        <v>0.527</v>
-      </c>
-      <c r="I42" s="19" t="n">
-        <v>0.4274</v>
-      </c>
-      <c r="J42" s="19" t="n">
-        <v>0.09959999999999999</v>
-      </c>
-      <c r="K42" s="20" t="n">
-        <v>3.852</v>
-      </c>
-      <c r="L42" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M42" s="20" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="N42" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="O42" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P42" s="22" t="n">
-        <v>1.34</v>
       </c>
     </row>
     <row r="43" ht="17" customHeight="1">
@@ -2987,21 +2971,21 @@
       </c>
       <c r="B43" s="16" t="inlineStr">
         <is>
-          <t>Jameson Taillon</t>
+          <t>Max Scherzer</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D43" s="17" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E43" s="18" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F43" s="17" t="inlineStr">
         <is>
@@ -3009,28 +2993,28 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>116</v>
+        <v>-130</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>0.569</v>
+        <v>0.652</v>
       </c>
       <c r="I43" s="19" t="n">
-        <v>0.463</v>
+        <v>0.5652</v>
       </c>
       <c r="J43" s="19" t="n">
-        <v>0.106</v>
+        <v>0.0868</v>
       </c>
       <c r="K43" s="20" t="n">
-        <v>4.313</v>
+        <v>4.757</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M43" s="20" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="N43" s="17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O43" s="21" t="inlineStr">
         <is>
@@ -3038,7 +3022,7 @@
         </is>
       </c>
       <c r="P43" s="22" t="n">
-        <v>1.16</v>
+        <v>0.7692</v>
       </c>
     </row>
     <row r="44" ht="17" customHeight="1">
@@ -3047,17 +3031,17 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Erick Fedde</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="D44" s="17" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E44" s="18" t="n">
@@ -3069,25 +3053,25 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>-108</v>
+        <v>134</v>
       </c>
       <c r="H44" s="19" t="n">
-        <v>0.655</v>
+        <v>0.527</v>
       </c>
       <c r="I44" s="19" t="n">
-        <v>0.5192</v>
+        <v>0.4274</v>
       </c>
       <c r="J44" s="19" t="n">
-        <v>0.1358</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="K44" s="20" t="n">
-        <v>4.719</v>
+        <v>3.852</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M44" s="20" t="n">
-        <v>0.71</v>
+        <v>0.44</v>
       </c>
       <c r="N44" s="17" t="n">
         <v>4</v>
@@ -3098,247 +3082,247 @@
         </is>
       </c>
       <c r="P44" s="22" t="n">
-        <v>0.9258999999999999</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="23" t="n">
+      <c r="A45" s="15" t="n">
         <v>46112</v>
       </c>
-      <c r="B45" s="24" t="inlineStr">
-        <is>
-          <t>José Soriano</t>
-        </is>
-      </c>
-      <c r="C45" s="25" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
+        <is>
+          <t>Jameson Taillon</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="inlineStr">
         <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="D45" s="25" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="E45" s="26" t="n">
+      <c r="E45" s="18" t="n">
         <v>4.5</v>
       </c>
-      <c r="F45" s="25" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G45" s="25" t="n">
-        <v>-110</v>
-      </c>
-      <c r="H45" s="27" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="I45" s="27" t="n">
-        <v>0.5238</v>
-      </c>
-      <c r="J45" s="27" t="n">
-        <v>0.1522</v>
-      </c>
-      <c r="K45" s="28" t="n">
-        <v>5.918</v>
-      </c>
-      <c r="L45" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="M45" s="28" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N45" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="O45" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P45" s="30" t="n">
-        <v>-1</v>
+      <c r="F45" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="n">
+        <v>116</v>
+      </c>
+      <c r="H45" s="19" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="I45" s="19" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J45" s="19" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="K45" s="20" t="n">
+        <v>4.313</v>
+      </c>
+      <c r="L45" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M45" s="20" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="N45" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="O45" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P45" s="22" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="46" ht="17" customHeight="1">
       <c r="A46" s="15" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>Ryan Feltner</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G46" s="17" t="n">
+        <v>-108</v>
+      </c>
+      <c r="H46" s="19" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="I46" s="19" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="J46" s="19" t="n">
+        <v>0.1358</v>
+      </c>
+      <c r="K46" s="20" t="n">
+        <v>4.719</v>
+      </c>
+      <c r="L46" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M46" s="20" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="N46" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="O46" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P46" s="22" t="n">
+        <v>0.9258999999999999</v>
+      </c>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="23" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>José Soriano</t>
+        </is>
+      </c>
+      <c r="C47" s="25" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D47" s="25" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="E47" s="26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F47" s="25" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G47" s="25" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H47" s="27" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="I47" s="27" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="J47" s="27" t="n">
+        <v>0.1522</v>
+      </c>
+      <c r="K47" s="28" t="n">
+        <v>5.918</v>
+      </c>
+      <c r="L47" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M47" s="28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N47" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="O47" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P47" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="15" t="n">
         <v>46111</v>
       </c>
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>Edward Cabrera</t>
         </is>
       </c>
-      <c r="C46" s="17" t="inlineStr">
+      <c r="C48" s="17" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="D46" s="17" t="inlineStr">
+      <c r="D48" s="17" t="inlineStr">
         <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="E46" s="18" t="n">
+      <c r="E48" s="18" t="n">
         <v>6.5</v>
       </c>
-      <c r="F46" s="17" t="inlineStr">
+      <c r="F48" s="17" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G46" s="17" t="n">
+      <c r="G48" s="17" t="n">
         <v>116</v>
       </c>
-      <c r="H46" s="19" t="n">
+      <c r="H48" s="19" t="n">
         <v>0.6889999999999999</v>
       </c>
-      <c r="I46" s="19" t="n">
+      <c r="I48" s="19" t="n">
         <v>0.463</v>
       </c>
-      <c r="J46" s="19" t="n">
+      <c r="J48" s="19" t="n">
         <v>0.226</v>
       </c>
-      <c r="K46" s="20" t="n">
+      <c r="K48" s="20" t="n">
         <v>5.286</v>
       </c>
-      <c r="L46" s="18" t="n">
+      <c r="L48" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="M46" s="20" t="n">
+      <c r="M48" s="20" t="n">
         <v>1.05</v>
       </c>
-      <c r="N46" s="17" t="n">
+      <c r="N48" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="O46" s="21" t="inlineStr">
+      <c r="O48" s="21" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P46" s="22" t="n">
+      <c r="P48" s="22" t="n">
         <v>1.16</v>
-      </c>
-    </row>
-    <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="15" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B47" s="16" t="inlineStr">
-        <is>
-          <t>Jack Leiter</t>
-        </is>
-      </c>
-      <c r="C47" s="17" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
-      <c r="D47" s="17" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="E47" s="18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F47" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G47" s="17" t="n">
-        <v>-144</v>
-      </c>
-      <c r="H47" s="19" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="I47" s="19" t="n">
-        <v>0.5901999999999999</v>
-      </c>
-      <c r="J47" s="19" t="n">
-        <v>0.0888</v>
-      </c>
-      <c r="K47" s="20" t="n">
-        <v>6.017</v>
-      </c>
-      <c r="L47" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M47" s="20" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="N47" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="O47" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P47" s="22" t="n">
-        <v>0.6944</v>
-      </c>
-    </row>
-    <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="23" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B48" s="24" t="inlineStr">
-        <is>
-          <t>Simeon Woods Richardson</t>
-        </is>
-      </c>
-      <c r="C48" s="25" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="D48" s="25" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="E48" s="26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F48" s="25" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G48" s="25" t="n">
-        <v>-112</v>
-      </c>
-      <c r="H48" s="27" t="n">
-        <v>0.783</v>
-      </c>
-      <c r="I48" s="27" t="n">
-        <v>0.5283</v>
-      </c>
-      <c r="J48" s="27" t="n">
-        <v>0.2547</v>
-      </c>
-      <c r="K48" s="28" t="n">
-        <v>5.562</v>
-      </c>
-      <c r="L48" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="M48" s="28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="N48" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="O48" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P48" s="30" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="49" ht="17" customHeight="1">
@@ -3407,17 +3391,17 @@
       </c>
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Simeon Woods Richardson</t>
         </is>
       </c>
       <c r="C50" s="25" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D50" s="25" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E50" s="26" t="n">
@@ -3429,28 +3413,28 @@
         </is>
       </c>
       <c r="G50" s="25" t="n">
-        <v>-174</v>
+        <v>-112</v>
       </c>
       <c r="H50" s="27" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.783</v>
       </c>
       <c r="I50" s="27" t="n">
-        <v>0.635</v>
+        <v>0.5283</v>
       </c>
       <c r="J50" s="27" t="n">
-        <v>0.054</v>
+        <v>0.2547</v>
       </c>
       <c r="K50" s="28" t="n">
-        <v>4.97</v>
+        <v>5.562</v>
       </c>
       <c r="L50" s="26" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="M50" s="28" t="n">
-        <v>0.37</v>
+        <v>1.35</v>
       </c>
       <c r="N50" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O50" s="29" t="inlineStr">
         <is>
@@ -3462,303 +3446,303 @@
       </c>
     </row>
     <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="23" t="n">
+      <c r="A51" s="15" t="n">
         <v>46111</v>
       </c>
-      <c r="B51" s="24" t="inlineStr">
+      <c r="B51" s="16" t="inlineStr">
+        <is>
+          <t>Jack Leiter</t>
+        </is>
+      </c>
+      <c r="C51" s="17" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="D51" s="17" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E51" s="18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F51" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G51" s="17" t="n">
+        <v>-144</v>
+      </c>
+      <c r="H51" s="19" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="I51" s="19" t="n">
+        <v>0.5901999999999999</v>
+      </c>
+      <c r="J51" s="19" t="n">
+        <v>0.0888</v>
+      </c>
+      <c r="K51" s="20" t="n">
+        <v>6.017</v>
+      </c>
+      <c r="L51" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" s="20" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N51" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="O51" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P51" s="22" t="n">
+        <v>0.6944</v>
+      </c>
+    </row>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="23" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="C52" s="25" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="D52" s="25" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E52" s="26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F52" s="25" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G52" s="25" t="n">
+        <v>-174</v>
+      </c>
+      <c r="H52" s="27" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="I52" s="27" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="J52" s="27" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="K52" s="28" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="L52" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M52" s="28" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="N52" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O52" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P52" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="53" ht="17" customHeight="1">
+      <c r="A53" s="23" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B53" s="24" t="inlineStr">
         <is>
           <t>Kyle Harrison</t>
         </is>
       </c>
-      <c r="C51" s="25" t="inlineStr">
+      <c r="C53" s="25" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="D51" s="25" t="inlineStr">
+      <c r="D53" s="25" t="inlineStr">
         <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E51" s="26" t="n">
+      <c r="E53" s="26" t="n">
         <v>4.5</v>
       </c>
-      <c r="F51" s="25" t="inlineStr">
+      <c r="F53" s="25" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G51" s="25" t="n">
+      <c r="G53" s="25" t="n">
         <v>114</v>
       </c>
-      <c r="H51" s="27" t="n">
+      <c r="H53" s="27" t="n">
         <v>0.521</v>
       </c>
-      <c r="I51" s="27" t="n">
+      <c r="I53" s="27" t="n">
         <v>0.4673</v>
       </c>
-      <c r="J51" s="27" t="n">
+      <c r="J53" s="27" t="n">
         <v>0.0537</v>
       </c>
-      <c r="K51" s="28" t="n">
+      <c r="K53" s="28" t="n">
         <v>4.628</v>
       </c>
-      <c r="L51" s="26" t="n">
+      <c r="L53" s="26" t="n">
         <v>0.5</v>
       </c>
-      <c r="M51" s="28" t="n">
+      <c r="M53" s="28" t="n">
         <v>0.25</v>
       </c>
-      <c r="N51" s="25" t="n">
+      <c r="N53" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="O51" s="29" t="inlineStr">
+      <c r="O53" s="29" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P51" s="30" t="n">
+      <c r="P53" s="30" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="52" ht="17" customHeight="1">
-      <c r="A52" s="15" t="n">
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="15" t="n">
         <v>46111</v>
       </c>
-      <c r="B52" s="16" t="inlineStr">
+      <c r="B54" s="16" t="inlineStr">
         <is>
           <t>Davis Martin</t>
         </is>
       </c>
-      <c r="C52" s="17" t="inlineStr">
+      <c r="C54" s="17" t="inlineStr">
         <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="D52" s="17" t="inlineStr">
+      <c r="D54" s="17" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="E52" s="18" t="n">
+      <c r="E54" s="18" t="n">
         <v>3.5</v>
       </c>
-      <c r="F52" s="17" t="inlineStr">
+      <c r="F54" s="17" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G52" s="17" t="n">
+      <c r="G54" s="17" t="n">
         <v>-114</v>
       </c>
-      <c r="H52" s="19" t="n">
+      <c r="H54" s="19" t="n">
         <v>0.584</v>
       </c>
-      <c r="I52" s="19" t="n">
+      <c r="I54" s="19" t="n">
         <v>0.5327</v>
       </c>
-      <c r="J52" s="19" t="n">
+      <c r="J54" s="19" t="n">
         <v>0.0513</v>
       </c>
-      <c r="K52" s="20" t="n">
+      <c r="K54" s="20" t="n">
         <v>4.252</v>
       </c>
-      <c r="L52" s="18" t="n">
+      <c r="L54" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="M52" s="20" t="n">
+      <c r="M54" s="20" t="n">
         <v>0.27</v>
       </c>
-      <c r="N52" s="17" t="n">
+      <c r="N54" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="O52" s="21" t="inlineStr">
+      <c r="O54" s="21" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P52" s="22" t="n">
+      <c r="P54" s="22" t="n">
         <v>0.8772</v>
       </c>
     </row>
-    <row r="53" ht="17" customHeight="1">
-      <c r="A53" s="15" t="n">
+    <row r="55" ht="17" customHeight="1">
+      <c r="A55" s="15" t="n">
         <v>46109</v>
       </c>
-      <c r="B53" s="16" t="inlineStr">
+      <c r="B55" s="16" t="inlineStr">
         <is>
           <t>Michael Wacha</t>
         </is>
       </c>
-      <c r="C53" s="17" t="inlineStr">
+      <c r="C55" s="17" t="inlineStr">
         <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="D53" s="17" t="inlineStr">
+      <c r="D55" s="17" t="inlineStr">
         <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E53" s="18" t="n">
+      <c r="E55" s="18" t="n">
         <v>4.5</v>
       </c>
-      <c r="F53" s="17" t="inlineStr">
+      <c r="F55" s="17" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G53" s="17" t="n">
+      <c r="G55" s="17" t="n">
         <v>140</v>
       </c>
-      <c r="H53" s="19" t="n">
+      <c r="H55" s="19" t="n">
         <v>0.476</v>
       </c>
-      <c r="I53" s="19" t="n">
+      <c r="I55" s="19" t="n">
         <v>0.4167</v>
       </c>
-      <c r="J53" s="19" t="n">
+      <c r="J55" s="19" t="n">
         <v>0.0593</v>
       </c>
-      <c r="K53" s="20" t="n">
+      <c r="K55" s="20" t="n">
         <v>4.645</v>
       </c>
-      <c r="L53" s="18" t="n">
+      <c r="L55" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="M53" s="20" t="n">
+      <c r="M55" s="20" t="n">
         <v>0.25</v>
       </c>
-      <c r="N53" s="17" t="n">
+      <c r="N55" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="O53" s="21" t="inlineStr">
+      <c r="O55" s="21" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P53" s="22" t="n">
+      <c r="P55" s="22" t="n">
         <v>1.4</v>
-      </c>
-    </row>
-    <row r="54" ht="17" customHeight="1">
-      <c r="A54" s="23" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B54" s="24" t="inlineStr">
-        <is>
-          <t>Will Warren</t>
-        </is>
-      </c>
-      <c r="C54" s="25" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="D54" s="25" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="E54" s="26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F54" s="25" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G54" s="25" t="n">
-        <v>110</v>
-      </c>
-      <c r="H54" s="27" t="n">
-        <v>0.573</v>
-      </c>
-      <c r="I54" s="27" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="J54" s="27" t="n">
-        <v>0.0968</v>
-      </c>
-      <c r="K54" s="28" t="n">
-        <v>5.339</v>
-      </c>
-      <c r="L54" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M54" s="28" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="N54" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="O54" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P54" s="30" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="23" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B55" s="24" t="inlineStr">
-        <is>
-          <t>Jeffrey Springs</t>
-        </is>
-      </c>
-      <c r="C55" s="25" t="inlineStr">
-        <is>
-          <t>OAK</t>
-        </is>
-      </c>
-      <c r="D55" s="25" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="E55" s="26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F55" s="25" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G55" s="25" t="n">
-        <v>102</v>
-      </c>
-      <c r="H55" s="27" t="n">
-        <v>0.599</v>
-      </c>
-      <c r="I55" s="27" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="J55" s="27" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="K55" s="28" t="n">
-        <v>4.389</v>
-      </c>
-      <c r="L55" s="26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M55" s="28" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="N55" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="O55" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P55" s="30" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="56" ht="17" customHeight="1">
@@ -3767,50 +3751,50 @@
       </c>
       <c r="B56" s="24" t="inlineStr">
         <is>
-          <t>Eury Pérez</t>
+          <t>Will Warren</t>
         </is>
       </c>
       <c r="C56" s="25" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="D56" s="25" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E56" s="26" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="F56" s="25" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G56" s="25" t="n">
-        <v>-154</v>
+        <v>110</v>
       </c>
       <c r="H56" s="27" t="n">
-        <v>0.713</v>
+        <v>0.573</v>
       </c>
       <c r="I56" s="27" t="n">
-        <v>0.6063</v>
+        <v>0.4762</v>
       </c>
       <c r="J56" s="27" t="n">
-        <v>0.1067</v>
+        <v>0.0968</v>
       </c>
       <c r="K56" s="28" t="n">
-        <v>5.311</v>
+        <v>5.339</v>
       </c>
       <c r="L56" s="26" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M56" s="28" t="n">
-        <v>0.68</v>
+        <v>0.46</v>
       </c>
       <c r="N56" s="25" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O56" s="29" t="inlineStr">
         <is>
@@ -3823,21 +3807,21 @@
     </row>
     <row r="57" ht="17" customHeight="1">
       <c r="A57" s="23" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Jeffrey Springs</t>
         </is>
       </c>
       <c r="C57" s="25" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>OAK</t>
         </is>
       </c>
       <c r="D57" s="25" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E57" s="26" t="n">
@@ -3849,25 +3833,25 @@
         </is>
       </c>
       <c r="G57" s="25" t="n">
-        <v>-158</v>
+        <v>102</v>
       </c>
       <c r="H57" s="27" t="n">
-        <v>0.677</v>
+        <v>0.599</v>
       </c>
       <c r="I57" s="27" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.495</v>
       </c>
       <c r="J57" s="27" t="n">
-        <v>0.0646</v>
+        <v>0.104</v>
       </c>
       <c r="K57" s="28" t="n">
-        <v>4.869</v>
+        <v>4.389</v>
       </c>
       <c r="L57" s="26" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M57" s="28" t="n">
-        <v>0.42</v>
+        <v>0.51</v>
       </c>
       <c r="N57" s="25" t="n">
         <v>2</v>
@@ -3882,423 +3866,423 @@
       </c>
     </row>
     <row r="58" ht="17" customHeight="1">
-      <c r="A58" s="15" t="n">
+      <c r="A58" s="23" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B58" s="24" t="inlineStr">
+        <is>
+          <t>Eury Pérez</t>
+        </is>
+      </c>
+      <c r="C58" s="25" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="D58" s="25" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E58" s="26" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F58" s="25" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G58" s="25" t="n">
+        <v>-154</v>
+      </c>
+      <c r="H58" s="27" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="I58" s="27" t="n">
+        <v>0.6063</v>
+      </c>
+      <c r="J58" s="27" t="n">
+        <v>0.1067</v>
+      </c>
+      <c r="K58" s="28" t="n">
+        <v>5.311</v>
+      </c>
+      <c r="L58" s="26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M58" s="28" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="N58" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="O58" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P58" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="59" ht="17" customHeight="1">
+      <c r="A59" s="23" t="n">
         <v>46108</v>
       </c>
-      <c r="B58" s="16" t="inlineStr">
+      <c r="B59" s="24" t="inlineStr">
+        <is>
+          <t>Kyle Freeland</t>
+        </is>
+      </c>
+      <c r="C59" s="25" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D59" s="25" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E59" s="26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F59" s="25" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G59" s="25" t="n">
+        <v>-158</v>
+      </c>
+      <c r="H59" s="27" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="I59" s="27" t="n">
+        <v>0.6124000000000001</v>
+      </c>
+      <c r="J59" s="27" t="n">
+        <v>0.0646</v>
+      </c>
+      <c r="K59" s="28" t="n">
+        <v>4.869</v>
+      </c>
+      <c r="L59" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M59" s="28" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="N59" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="O59" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P59" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="60" ht="17" customHeight="1">
+      <c r="A60" s="15" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B60" s="16" t="inlineStr">
         <is>
           <t>Robbie Ray</t>
         </is>
       </c>
-      <c r="C58" s="17" t="inlineStr">
+      <c r="C60" s="17" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="D58" s="17" t="inlineStr">
+      <c r="D60" s="17" t="inlineStr">
         <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E58" s="18" t="n">
+      <c r="E60" s="18" t="n">
         <v>5.5</v>
       </c>
-      <c r="F58" s="17" t="inlineStr">
+      <c r="F60" s="17" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G58" s="17" t="n">
+      <c r="G60" s="17" t="n">
         <v>116</v>
       </c>
-      <c r="H58" s="19" t="n">
+      <c r="H60" s="19" t="n">
         <v>0.532</v>
       </c>
-      <c r="I58" s="19" t="n">
+      <c r="I60" s="19" t="n">
         <v>0.463</v>
       </c>
-      <c r="J58" s="19" t="n">
+      <c r="J60" s="19" t="n">
         <v>0.06900000000000001</v>
       </c>
-      <c r="K58" s="20" t="n">
+      <c r="K60" s="20" t="n">
         <v>5.578</v>
       </c>
-      <c r="L58" s="18" t="n">
+      <c r="L60" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="M58" s="20" t="n">
+      <c r="M60" s="20" t="n">
         <v>0.32</v>
       </c>
-      <c r="N58" s="17" t="n">
+      <c r="N60" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="O58" s="21" t="inlineStr">
+      <c r="O60" s="21" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P58" s="22" t="n">
+      <c r="P60" s="22" t="n">
         <v>1.16</v>
       </c>
     </row>
-    <row r="59" ht="17" customHeight="1">
-      <c r="A59" s="15" t="n">
+    <row r="61" ht="17" customHeight="1">
+      <c r="A61" s="15" t="n">
         <v>46108</v>
       </c>
-      <c r="B59" s="16" t="inlineStr">
+      <c r="B61" s="16" t="inlineStr">
         <is>
           <t>Cam Schlittler</t>
         </is>
       </c>
-      <c r="C59" s="17" t="inlineStr">
+      <c r="C61" s="17" t="inlineStr">
         <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="D59" s="17" t="inlineStr">
+      <c r="D61" s="17" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="E59" s="18" t="n">
+      <c r="E61" s="18" t="n">
         <v>4.5</v>
       </c>
-      <c r="F59" s="17" t="inlineStr">
+      <c r="F61" s="17" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G59" s="17" t="n">
+      <c r="G61" s="17" t="n">
         <v>-128</v>
       </c>
-      <c r="H59" s="19" t="n">
+      <c r="H61" s="19" t="n">
         <v>0.659</v>
       </c>
-      <c r="I59" s="19" t="n">
+      <c r="I61" s="19" t="n">
         <v>0.5614</v>
       </c>
-      <c r="J59" s="19" t="n">
+      <c r="J61" s="19" t="n">
         <v>0.09760000000000001</v>
       </c>
-      <c r="K59" s="20" t="n">
+      <c r="K61" s="20" t="n">
         <v>5.818</v>
       </c>
-      <c r="L59" s="18" t="n">
+      <c r="L61" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="M59" s="20" t="n">
+      <c r="M61" s="20" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="N59" s="17" t="n">
+      <c r="N61" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="O59" s="21" t="inlineStr">
+      <c r="O61" s="21" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P59" s="22" t="n">
+      <c r="P61" s="22" t="n">
         <v>0.7812</v>
       </c>
     </row>
-    <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="23" t="n">
+    <row r="62" ht="17" customHeight="1">
+      <c r="A62" s="23" t="n">
         <v>46107</v>
       </c>
-      <c r="B60" s="24" t="inlineStr">
+      <c r="B62" s="24" t="inlineStr">
         <is>
           <t>Shane Smith</t>
         </is>
       </c>
-      <c r="C60" s="25" t="inlineStr">
+      <c r="C62" s="25" t="inlineStr">
         <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="D60" s="25" t="inlineStr">
+      <c r="D62" s="25" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E60" s="26" t="n">
+      <c r="E62" s="26" t="n">
         <v>4.5</v>
       </c>
-      <c r="F60" s="25" t="inlineStr">
+      <c r="F62" s="25" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G60" s="25" t="n">
+      <c r="G62" s="25" t="n">
         <v>-114</v>
       </c>
-      <c r="H60" s="27" t="n">
+      <c r="H62" s="27" t="n">
         <v>0.607</v>
       </c>
-      <c r="I60" s="27" t="n">
+      <c r="I62" s="27" t="n">
         <v>0.5327</v>
       </c>
-      <c r="J60" s="27" t="n">
+      <c r="J62" s="27" t="n">
         <v>0.0743</v>
       </c>
-      <c r="K60" s="28" t="n">
+      <c r="K62" s="28" t="n">
         <v>5.338</v>
       </c>
-      <c r="L60" s="26" t="n">
+      <c r="L62" s="26" t="n">
         <v>0.5</v>
       </c>
-      <c r="M60" s="28" t="n">
+      <c r="M62" s="28" t="n">
         <v>0.4</v>
       </c>
-      <c r="N60" s="25" t="n">
+      <c r="N62" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="O60" s="29" t="inlineStr">
+      <c r="O62" s="29" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P60" s="30" t="n">
+      <c r="P62" s="30" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="61" ht="17" customHeight="1">
-      <c r="A61" s="23" t="n">
+    <row r="63" ht="17" customHeight="1">
+      <c r="A63" s="23" t="n">
         <v>46107</v>
       </c>
-      <c r="B61" s="24" t="inlineStr">
+      <c r="B63" s="24" t="inlineStr">
         <is>
           <t>Hunter Brown</t>
         </is>
       </c>
-      <c r="C61" s="25" t="inlineStr">
+      <c r="C63" s="25" t="inlineStr">
         <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="D61" s="25" t="inlineStr">
+      <c r="D63" s="25" t="inlineStr">
         <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="E61" s="26" t="n">
+      <c r="E63" s="26" t="n">
         <v>6.5</v>
       </c>
-      <c r="F61" s="25" t="inlineStr">
+      <c r="F63" s="25" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G61" s="25" t="n">
+      <c r="G63" s="25" t="n">
         <v>114</v>
       </c>
-      <c r="H61" s="27" t="n">
+      <c r="H63" s="27" t="n">
         <v>0.587</v>
       </c>
-      <c r="I61" s="27" t="n">
+      <c r="I63" s="27" t="n">
         <v>0.4673</v>
       </c>
-      <c r="J61" s="27" t="n">
+      <c r="J63" s="27" t="n">
         <v>0.1197</v>
       </c>
-      <c r="K61" s="28" t="n">
+      <c r="K63" s="28" t="n">
         <v>6.417</v>
       </c>
-      <c r="L61" s="26" t="n">
+      <c r="L63" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="M61" s="28" t="n">
+      <c r="M63" s="28" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="N61" s="25" t="n">
+      <c r="N63" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="O61" s="29" t="inlineStr">
+      <c r="O63" s="29" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P61" s="30" t="n">
+      <c r="P63" s="30" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="62" ht="17" customHeight="1">
-      <c r="A62" s="15" t="n">
+    <row r="64" ht="17" customHeight="1">
+      <c r="A64" s="15" t="n">
         <v>46107</v>
       </c>
-      <c r="B62" s="16" t="inlineStr">
+      <c r="B64" s="16" t="inlineStr">
         <is>
           <t>José Soriano</t>
         </is>
       </c>
-      <c r="C62" s="17" t="inlineStr">
+      <c r="C64" s="17" t="inlineStr">
         <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="D62" s="17" t="inlineStr">
+      <c r="D64" s="17" t="inlineStr">
         <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E62" s="18" t="n">
+      <c r="E64" s="18" t="n">
         <v>4.5</v>
       </c>
-      <c r="F62" s="17" t="inlineStr">
+      <c r="F64" s="17" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G62" s="17" t="n">
+      <c r="G64" s="17" t="n">
         <v>108</v>
       </c>
-      <c r="H62" s="19" t="n">
+      <c r="H64" s="19" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="I62" s="19" t="n">
+      <c r="I64" s="19" t="n">
         <v>0.4808</v>
       </c>
-      <c r="J62" s="19" t="n">
+      <c r="J64" s="19" t="n">
         <v>0.07920000000000001</v>
       </c>
-      <c r="K62" s="20" t="n">
+      <c r="K64" s="20" t="n">
         <v>5.163</v>
       </c>
-      <c r="L62" s="18" t="n">
+      <c r="L64" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="M62" s="20" t="n">
+      <c r="M64" s="20" t="n">
         <v>0.38</v>
       </c>
-      <c r="N62" s="17" t="n">
+      <c r="N64" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="O62" s="21" t="inlineStr">
+      <c r="O64" s="21" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P62" s="22" t="n">
+      <c r="P64" s="22" t="n">
         <v>1.08</v>
-      </c>
-    </row>
-    <row r="63" ht="17" customHeight="1">
-      <c r="A63" s="15" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B63" s="16" t="inlineStr">
-        <is>
-          <t>Tarik Skubal</t>
-        </is>
-      </c>
-      <c r="C63" s="17" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="D63" s="17" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E63" s="18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F63" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G63" s="17" t="n">
-        <v>-172</v>
-      </c>
-      <c r="H63" s="19" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="I63" s="19" t="n">
-        <v>0.6324</v>
-      </c>
-      <c r="J63" s="19" t="n">
-        <v>0.1346</v>
-      </c>
-      <c r="K63" s="20" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="L63" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M63" s="20" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="N63" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="O63" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P63" s="22" t="n">
-        <v>0.5814</v>
-      </c>
-    </row>
-    <row r="64" ht="17" customHeight="1">
-      <c r="A64" s="23" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B64" s="24" t="inlineStr">
-        <is>
-          <t>Jacob Misiorowski</t>
-        </is>
-      </c>
-      <c r="C64" s="25" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D64" s="25" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="E64" s="26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F64" s="25" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G64" s="25" t="n">
-        <v>124</v>
-      </c>
-      <c r="H64" s="27" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I64" s="27" t="n">
-        <v>0.4464</v>
-      </c>
-      <c r="J64" s="27" t="n">
-        <v>0.0736</v>
-      </c>
-      <c r="K64" s="28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L64" s="26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M64" s="28" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="N64" s="25" t="n">
-        <v>11</v>
-      </c>
-      <c r="O64" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P64" s="30" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="65" ht="17" customHeight="1">
@@ -4307,177 +4291,297 @@
       </c>
       <c r="B65" s="16" t="inlineStr">
         <is>
+          <t>Tarik Skubal</t>
+        </is>
+      </c>
+      <c r="C65" s="17" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="D65" s="17" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E65" s="18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F65" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G65" s="17" t="n">
+        <v>-172</v>
+      </c>
+      <c r="H65" s="19" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="I65" s="19" t="n">
+        <v>0.6324</v>
+      </c>
+      <c r="J65" s="19" t="n">
+        <v>0.1346</v>
+      </c>
+      <c r="K65" s="20" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="L65" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M65" s="20" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="N65" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="O65" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P65" s="22" t="n">
+        <v>0.5814</v>
+      </c>
+    </row>
+    <row r="66" ht="17" customHeight="1">
+      <c r="A66" s="23" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B66" s="24" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="C66" s="25" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D66" s="25" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E66" s="26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F66" s="25" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G66" s="25" t="n">
+        <v>124</v>
+      </c>
+      <c r="H66" s="27" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I66" s="27" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="J66" s="27" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="K66" s="28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L66" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M66" s="28" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N66" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="O66" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P66" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="67" ht="17" customHeight="1">
+      <c r="A67" s="15" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B67" s="16" t="inlineStr">
+        <is>
           <t>Nick Pivetta</t>
         </is>
       </c>
-      <c r="C65" s="17" t="inlineStr">
+      <c r="C67" s="17" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="D65" s="17" t="inlineStr">
+      <c r="D67" s="17" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="E65" s="18" t="n">
+      <c r="E67" s="18" t="n">
         <v>5.5</v>
       </c>
-      <c r="F65" s="17" t="inlineStr">
+      <c r="F67" s="17" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G65" s="17" t="n">
+      <c r="G67" s="17" t="n">
         <v>110</v>
       </c>
-      <c r="H65" s="19" t="n">
+      <c r="H67" s="19" t="n">
         <v>0.54</v>
       </c>
-      <c r="I65" s="19" t="n">
+      <c r="I67" s="19" t="n">
         <v>0.4762</v>
       </c>
-      <c r="J65" s="19" t="n">
+      <c r="J67" s="19" t="n">
         <v>0.0638</v>
       </c>
-      <c r="K65" s="20" t="n">
+      <c r="K67" s="20" t="n">
         <v>5.548</v>
       </c>
-      <c r="L65" s="18" t="n">
+      <c r="L67" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="M65" s="20" t="n">
+      <c r="M67" s="20" t="n">
         <v>0.3</v>
       </c>
-      <c r="N65" s="17" t="n">
+      <c r="N67" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="O65" s="21" t="inlineStr">
+      <c r="O67" s="21" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P65" s="22" t="n">
+      <c r="P67" s="22" t="n">
         <v>1.1</v>
       </c>
     </row>
-    <row r="66" ht="17" customHeight="1">
-      <c r="A66" s="15" t="n">
+    <row r="68" ht="17" customHeight="1">
+      <c r="A68" s="15" t="n">
         <v>46107</v>
       </c>
-      <c r="B66" s="16" t="inlineStr">
+      <c r="B68" s="16" t="inlineStr">
         <is>
           <t>Andrew Abbott</t>
         </is>
       </c>
-      <c r="C66" s="17" t="inlineStr">
+      <c r="C68" s="17" t="inlineStr">
         <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="D66" s="17" t="inlineStr">
+      <c r="D68" s="17" t="inlineStr">
         <is>
           <t>BOS</t>
         </is>
       </c>
-      <c r="E66" s="18" t="n">
+      <c r="E68" s="18" t="n">
         <v>4.5</v>
       </c>
-      <c r="F66" s="17" t="inlineStr">
+      <c r="F68" s="17" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G66" s="17" t="n">
+      <c r="G68" s="17" t="n">
         <v>120</v>
       </c>
-      <c r="H66" s="19" t="n">
+      <c r="H68" s="19" t="n">
         <v>0.509</v>
       </c>
-      <c r="I66" s="19" t="n">
+      <c r="I68" s="19" t="n">
         <v>0.4545</v>
       </c>
-      <c r="J66" s="19" t="n">
+      <c r="J68" s="19" t="n">
         <v>0.0545</v>
       </c>
-      <c r="K66" s="20" t="n">
+      <c r="K68" s="20" t="n">
         <v>4.814</v>
       </c>
-      <c r="L66" s="18" t="n">
+      <c r="L68" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="M66" s="20" t="n">
+      <c r="M68" s="20" t="n">
         <v>0.25</v>
       </c>
-      <c r="N66" s="17" t="n">
+      <c r="N68" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="O66" s="21" t="inlineStr">
+      <c r="O68" s="21" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P66" s="22" t="n">
+      <c r="P68" s="22" t="n">
         <v>1.2</v>
       </c>
     </row>
-    <row r="67" ht="17" customHeight="1">
-      <c r="A67" s="23" t="n">
+    <row r="69" ht="17" customHeight="1">
+      <c r="A69" s="23" t="n">
         <v>46107</v>
       </c>
-      <c r="B67" s="24" t="inlineStr">
+      <c r="B69" s="24" t="inlineStr">
         <is>
           <t>Matthew Boyd</t>
         </is>
       </c>
-      <c r="C67" s="25" t="inlineStr">
+      <c r="C69" s="25" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="D67" s="25" t="inlineStr">
+      <c r="D69" s="25" t="inlineStr">
         <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E67" s="26" t="n">
+      <c r="E69" s="26" t="n">
         <v>4.5</v>
       </c>
-      <c r="F67" s="25" t="inlineStr">
+      <c r="F69" s="25" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G67" s="25" t="n">
+      <c r="G69" s="25" t="n">
         <v>132</v>
       </c>
-      <c r="H67" s="27" t="n">
+      <c r="H69" s="27" t="n">
         <v>0.59</v>
       </c>
-      <c r="I67" s="27" t="n">
+      <c r="I69" s="27" t="n">
         <v>0.431</v>
       </c>
-      <c r="J67" s="27" t="n">
+      <c r="J69" s="27" t="n">
         <v>0.159</v>
       </c>
-      <c r="K67" s="28" t="n">
+      <c r="K69" s="28" t="n">
         <v>4.258</v>
       </c>
-      <c r="L67" s="26" t="n">
+      <c r="L69" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="M67" s="28" t="n">
+      <c r="M69" s="28" t="n">
         <v>0.7</v>
       </c>
-      <c r="N67" s="25" t="n">
+      <c r="N69" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="O67" s="29" t="inlineStr">
+      <c r="O69" s="29" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P67" s="30" t="n">
+      <c r="P69" s="30" t="n">
         <v>-1</v>
       </c>
     </row>

--- a/bet_log.xlsx
+++ b/bet_log.xlsx
@@ -624,7 +624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P69"/>
+  <dimension ref="A1:P77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -696,33 +696,33 @@
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>30</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>26</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>+3.454 u</t>
+          <t>+2.171 u</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>-1.898 u</t>
+          <t>-1.962 u</t>
         </is>
       </c>
     </row>
@@ -811,25 +811,25 @@
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="7" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Chad Patrick</t>
+          <t>Simeon Woods Richardson</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E6" s="10" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
@@ -837,25 +837,25 @@
         </is>
       </c>
       <c r="G6" s="9" t="n">
-        <v>-154</v>
+        <v>106</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.678</v>
+        <v>0.547</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>0.6063</v>
+        <v>0.4854</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>0.0717</v>
+        <v>0.0616</v>
       </c>
       <c r="K6" s="12" t="n">
-        <v>4.705</v>
+        <v>5.027</v>
       </c>
       <c r="L6" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>0.46</v>
+        <v>0.3</v>
       </c>
       <c r="N6" s="9" t="inlineStr"/>
       <c r="O6" s="13" t="inlineStr"/>
@@ -863,21 +863,21 @@
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="7" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E7" s="10" t="n">
@@ -889,25 +889,25 @@
         </is>
       </c>
       <c r="G7" s="9" t="n">
-        <v>-130</v>
+        <v>-112</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.678</v>
+        <v>0.591</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.5652</v>
+        <v>0.5283</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>0.1128</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>4.813</v>
+        <v>4.188</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>0.65</v>
+        <v>0.33</v>
       </c>
       <c r="N7" s="9" t="inlineStr"/>
       <c r="O7" s="13" t="inlineStr"/>
@@ -915,25 +915,25 @@
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="7" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Carmen Mlodzinski</t>
+          <t>Jack Leiter</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E8" s="10" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
@@ -941,25 +941,25 @@
         </is>
       </c>
       <c r="G8" s="9" t="n">
-        <v>-108</v>
+        <v>-146</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.666</v>
+        <v>0.659</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.5192</v>
+        <v>0.5935</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>0.1468</v>
+        <v>0.0655</v>
       </c>
       <c r="K8" s="12" t="n">
-        <v>3.828</v>
+        <v>5.601</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>0.76</v>
+        <v>0.4</v>
       </c>
       <c r="N8" s="9" t="inlineStr"/>
       <c r="O8" s="13" t="inlineStr"/>
@@ -967,51 +967,51 @@
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="7" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Bryce Elder</t>
+          <t>Luis Castillo</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E9" s="10" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G9" s="9" t="n">
-        <v>-132</v>
+        <v>126</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.753</v>
+        <v>0.518</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.569</v>
+        <v>0.4425</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>0.184</v>
+        <v>0.0755</v>
       </c>
       <c r="K9" s="12" t="n">
-        <v>5.551</v>
+        <v>5.702</v>
       </c>
       <c r="L9" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>1.07</v>
+        <v>0.34</v>
       </c>
       <c r="N9" s="9" t="inlineStr"/>
       <c r="O9" s="13" t="inlineStr"/>
@@ -1019,51 +1019,51 @@
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="7" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Ryan Weathers</t>
+          <t>Taijuan Walker</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E10" s="10" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G10" s="9" t="n">
-        <v>-125</v>
+        <v>-106</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.741</v>
+        <v>0.6</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>0.5556</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>0.1854</v>
+        <v>0.0854</v>
       </c>
       <c r="K10" s="12" t="n">
-        <v>4.217</v>
+        <v>4.331</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>1.04</v>
+        <v>0.44</v>
       </c>
       <c r="N10" s="9" t="inlineStr"/>
       <c r="O10" s="13" t="inlineStr"/>
@@ -1071,51 +1071,51 @@
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="7" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Steven Matz</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E11" s="10" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G11" s="9" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.651</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.463</v>
+        <v>0.4587</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>0.188</v>
+        <v>0.1003</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>5.743</v>
+        <v>5.372</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.88</v>
+        <v>0.46</v>
       </c>
       <c r="N11" s="9" t="inlineStr"/>
       <c r="O11" s="13" t="inlineStr"/>
@@ -1123,365 +1123,365 @@
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="7" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Jack Flaherty</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E12" s="10" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G12" s="9" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.653</v>
+        <v>0.575</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>0.463</v>
+        <v>0.4587</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>0.19</v>
+        <v>0.1163</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>4.756</v>
+        <v>5.165</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.88</v>
+        <v>0.54</v>
       </c>
       <c r="N12" s="9" t="inlineStr"/>
       <c r="O12" s="13" t="inlineStr"/>
       <c r="P12" s="14" t="inlineStr"/>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="15" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>Mitch Keller</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="n">
+      <c r="A13" s="7" t="n">
+        <v>46117</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Eric Lauer</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="n">
         <v>4.5</v>
       </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="n">
-        <v>122</v>
-      </c>
-      <c r="H13" s="19" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>0.4505</v>
-      </c>
-      <c r="J13" s="19" t="n">
-        <v>0.0545</v>
-      </c>
-      <c r="K13" s="20" t="n">
-        <v>4.723</v>
-      </c>
-      <c r="L13" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M13" s="20" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N13" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="O13" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P13" s="22" t="n">
-        <v>1.22</v>
-      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>120</v>
+      </c>
+      <c r="H13" s="11" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>0.1335</v>
+      </c>
+      <c r="K13" s="12" t="n">
+        <v>5.457</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M13" s="12" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="N13" s="9" t="inlineStr"/>
+      <c r="O13" s="13" t="inlineStr"/>
+      <c r="P13" s="14" t="inlineStr"/>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="15" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>Framber Valdez</t>
+          <t>Bryce Elder</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>-132</v>
+      </c>
+      <c r="H14" s="19" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="J14" s="19" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="K14" s="20" t="n">
+        <v>5.551</v>
+      </c>
+      <c r="L14" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" s="20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N14" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="O14" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P14" s="22" t="n">
+        <v>0.7576000000000001</v>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="23" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>Jack Flaherty</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D15" s="25" t="inlineStr">
         <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E15" s="26" t="n">
         <v>5.5</v>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F15" s="25" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G14" s="17" t="n">
-        <v>-112</v>
-      </c>
-      <c r="H14" s="19" t="n">
-        <v>0.591</v>
-      </c>
-      <c r="I14" s="19" t="n">
-        <v>0.5283</v>
-      </c>
-      <c r="J14" s="19" t="n">
-        <v>0.06270000000000001</v>
-      </c>
-      <c r="K14" s="20" t="n">
-        <v>5.166</v>
-      </c>
-      <c r="L14" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M14" s="20" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="N14" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="O14" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P14" s="22" t="n">
-        <v>0.8929</v>
-      </c>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="15" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>Kyle Bradish</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="n">
-        <v>-146</v>
-      </c>
-      <c r="H15" s="19" t="n">
-        <v>0.659</v>
-      </c>
-      <c r="I15" s="19" t="n">
-        <v>0.5935</v>
-      </c>
-      <c r="J15" s="19" t="n">
-        <v>0.0655</v>
-      </c>
-      <c r="K15" s="20" t="n">
-        <v>6.943</v>
-      </c>
-      <c r="L15" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M15" s="20" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N15" s="17" t="n">
+      <c r="G15" s="25" t="n">
+        <v>116</v>
+      </c>
+      <c r="H15" s="27" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="I15" s="27" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J15" s="27" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K15" s="28" t="n">
+        <v>4.756</v>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" s="28" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N15" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="O15" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P15" s="22" t="n">
-        <v>0.6849</v>
+      <c r="O15" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P15" s="30" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="15" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>Michael King</t>
+          <t>Steven Matz</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E16" s="18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>116</v>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="I16" s="19" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J16" s="19" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="K16" s="20" t="n">
+        <v>5.743</v>
+      </c>
+      <c r="L16" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" s="20" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N16" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="O16" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P16" s="22" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="15" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Ryan Weathers</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E17" s="18" t="n">
         <v>5.5</v>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G16" s="17" t="n">
-        <v>102</v>
-      </c>
-      <c r="H16" s="19" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="I16" s="19" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="J16" s="19" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="K16" s="20" t="n">
-        <v>5.081</v>
-      </c>
-      <c r="L16" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" s="20" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="N16" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="O16" s="21" t="inlineStr">
+      <c r="G17" s="17" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="J17" s="19" t="n">
+        <v>0.1854</v>
+      </c>
+      <c r="K17" s="20" t="n">
+        <v>4.217</v>
+      </c>
+      <c r="L17" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" s="20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N17" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="O17" s="21" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P16" s="22" t="n">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="7" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Chad Patrick</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="n">
-        <v>-138</v>
-      </c>
-      <c r="H17" s="11" t="n">
-        <v>0.672</v>
-      </c>
-      <c r="I17" s="11" t="n">
-        <v>0.5798</v>
-      </c>
-      <c r="J17" s="11" t="n">
-        <v>0.0922</v>
-      </c>
-      <c r="K17" s="12" t="n">
-        <v>4.705</v>
-      </c>
-      <c r="L17" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" s="12" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="N17" s="9" t="inlineStr"/>
-      <c r="O17" s="13" t="inlineStr"/>
-      <c r="P17" s="14" t="inlineStr"/>
+      <c r="P17" s="22" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="23" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>Cade Horton</t>
+          <t>Chad Patrick</t>
         </is>
       </c>
       <c r="C18" s="25" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D18" s="25" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E18" s="26" t="n">
@@ -1493,28 +1493,28 @@
         </is>
       </c>
       <c r="G18" s="25" t="n">
-        <v>-136</v>
+        <v>-154</v>
       </c>
       <c r="H18" s="27" t="n">
-        <v>0.676</v>
+        <v>0.678</v>
       </c>
       <c r="I18" s="27" t="n">
-        <v>0.5763</v>
+        <v>0.6063</v>
       </c>
       <c r="J18" s="27" t="n">
-        <v>0.0997</v>
+        <v>0.0717</v>
       </c>
       <c r="K18" s="28" t="n">
-        <v>4.806</v>
+        <v>4.705</v>
       </c>
       <c r="L18" s="26" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M18" s="28" t="n">
-        <v>0.59</v>
+        <v>0.46</v>
       </c>
       <c r="N18" s="25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O18" s="29" t="inlineStr">
         <is>
@@ -1527,54 +1527,54 @@
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="23" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>Emmet Sheehan</t>
+          <t>Carmen Mlodzinski</t>
         </is>
       </c>
       <c r="C19" s="25" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="D19" s="25" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E19" s="26" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G19" s="25" t="n">
-        <v>-128</v>
+        <v>-108</v>
       </c>
       <c r="H19" s="27" t="n">
-        <v>0.68</v>
+        <v>0.666</v>
       </c>
       <c r="I19" s="27" t="n">
-        <v>0.5614</v>
+        <v>0.5192</v>
       </c>
       <c r="J19" s="27" t="n">
-        <v>0.1186</v>
+        <v>0.1468</v>
       </c>
       <c r="K19" s="28" t="n">
-        <v>6.988</v>
+        <v>3.828</v>
       </c>
       <c r="L19" s="26" t="n">
         <v>1.5</v>
       </c>
       <c r="M19" s="28" t="n">
-        <v>0.68</v>
+        <v>0.76</v>
       </c>
       <c r="N19" s="25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O19" s="29" t="inlineStr">
         <is>
@@ -1587,54 +1587,54 @@
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="23" t="n">
-        <v>46114</v>
+        <v>46116</v>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>Cole Ragans</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="C20" s="25" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="D20" s="25" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G20" s="25" t="n">
-        <v>-152</v>
+        <v>-130</v>
       </c>
       <c r="H20" s="27" t="n">
-        <v>0.738</v>
+        <v>0.678</v>
       </c>
       <c r="I20" s="27" t="n">
-        <v>0.6032</v>
+        <v>0.5652</v>
       </c>
       <c r="J20" s="27" t="n">
-        <v>0.1348</v>
+        <v>0.1128</v>
       </c>
       <c r="K20" s="28" t="n">
-        <v>5.951</v>
+        <v>4.813</v>
       </c>
       <c r="L20" s="26" t="n">
         <v>1.5</v>
       </c>
       <c r="M20" s="28" t="n">
-        <v>0.85</v>
+        <v>0.65</v>
       </c>
       <c r="N20" s="25" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O20" s="29" t="inlineStr">
         <is>
@@ -1646,86 +1646,86 @@
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="23" t="n">
-        <v>46114</v>
-      </c>
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t>Taj Bradley</t>
-        </is>
-      </c>
-      <c r="C21" s="25" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="D21" s="25" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="E21" s="26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F21" s="25" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G21" s="25" t="n">
-        <v>118</v>
-      </c>
-      <c r="H21" s="27" t="n">
-        <v>0.573</v>
-      </c>
-      <c r="I21" s="27" t="n">
-        <v>0.4587</v>
-      </c>
-      <c r="J21" s="27" t="n">
-        <v>0.1143</v>
-      </c>
-      <c r="K21" s="28" t="n">
-        <v>5.159</v>
-      </c>
-      <c r="L21" s="26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M21" s="28" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="N21" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="O21" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P21" s="30" t="n">
-        <v>-1</v>
+      <c r="A21" s="15" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>Michael King</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="n">
+        <v>102</v>
+      </c>
+      <c r="H21" s="19" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="I21" s="19" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="J21" s="19" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="K21" s="20" t="n">
+        <v>5.081</v>
+      </c>
+      <c r="L21" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="20" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="N21" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O21" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P21" s="22" t="n">
+        <v>1.02</v>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="23" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>Cade Cavalli</t>
+          <t>Emmet Sheehan</t>
         </is>
       </c>
       <c r="C22" s="25" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="D22" s="25" t="inlineStr">
+        <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="D22" s="25" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="E22" s="26" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
@@ -1733,28 +1733,28 @@
         </is>
       </c>
       <c r="G22" s="25" t="n">
-        <v>-102</v>
+        <v>-128</v>
       </c>
       <c r="H22" s="27" t="n">
-        <v>0.668</v>
+        <v>0.68</v>
       </c>
       <c r="I22" s="27" t="n">
-        <v>0.505</v>
+        <v>0.5614</v>
       </c>
       <c r="J22" s="27" t="n">
-        <v>0.163</v>
+        <v>0.1186</v>
       </c>
       <c r="K22" s="28" t="n">
-        <v>5.697</v>
+        <v>6.988</v>
       </c>
       <c r="L22" s="26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M22" s="28" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="N22" s="25" t="n">
         <v>2</v>
-      </c>
-      <c r="M22" s="28" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="N22" s="25" t="n">
-        <v>3</v>
       </c>
       <c r="O22" s="29" t="inlineStr">
         <is>
@@ -1766,175 +1766,167 @@
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>Freddy Peralta</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>NYM</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="A23" s="23" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>Cade Horton</t>
+        </is>
+      </c>
+      <c r="C23" s="25" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="D23" s="25" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E23" s="26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F23" s="25" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G23" s="17" t="n">
-        <v>116</v>
-      </c>
-      <c r="H23" s="19" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="I23" s="19" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J23" s="19" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="K23" s="20" t="n">
-        <v>6.789</v>
-      </c>
-      <c r="L23" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M23" s="20" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="N23" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="O23" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P23" s="22" t="n">
-        <v>1.16</v>
+      <c r="G23" s="25" t="n">
+        <v>-136</v>
+      </c>
+      <c r="H23" s="27" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="I23" s="27" t="n">
+        <v>0.5763</v>
+      </c>
+      <c r="J23" s="27" t="n">
+        <v>0.0997</v>
+      </c>
+      <c r="K23" s="28" t="n">
+        <v>4.806</v>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="28" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="N23" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P23" s="30" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="23" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B24" s="24" t="inlineStr">
-        <is>
-          <t>Yusei Kikuchi</t>
-        </is>
-      </c>
-      <c r="C24" s="25" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="D24" s="25" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="E24" s="26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F24" s="25" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G24" s="25" t="n">
-        <v>102</v>
-      </c>
-      <c r="H24" s="27" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="I24" s="27" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="J24" s="27" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="K24" s="28" t="n">
-        <v>4.364</v>
-      </c>
-      <c r="L24" s="26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M24" s="28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N24" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="O24" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P24" s="30" t="n">
-        <v>-1</v>
-      </c>
+      <c r="A24" s="7" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Chad Patrick</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>-138</v>
+      </c>
+      <c r="H24" s="11" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="I24" s="11" t="n">
+        <v>0.5798</v>
+      </c>
+      <c r="J24" s="11" t="n">
+        <v>0.0922</v>
+      </c>
+      <c r="K24" s="12" t="n">
+        <v>4.705</v>
+      </c>
+      <c r="L24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N24" s="9" t="inlineStr"/>
+      <c r="O24" s="13" t="inlineStr"/>
+      <c r="P24" s="14" t="inlineStr"/>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="15" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>Kevin Gausman</t>
+          <t>Framber Valdez</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E25" s="18" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>116</v>
+        <v>-112</v>
       </c>
       <c r="H25" s="19" t="n">
-        <v>0.529</v>
+        <v>0.591</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>0.463</v>
+        <v>0.5283</v>
       </c>
       <c r="J25" s="19" t="n">
-        <v>0.066</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="K25" s="20" t="n">
-        <v>7.914</v>
+        <v>5.166</v>
       </c>
       <c r="L25" s="18" t="n">
         <v>0.5</v>
       </c>
       <c r="M25" s="20" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="N25" s="17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O25" s="21" t="inlineStr">
         <is>
@@ -1942,59 +1934,59 @@
         </is>
       </c>
       <c r="P25" s="22" t="n">
-        <v>1.16</v>
+        <v>0.8929</v>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="15" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>Matthew Liberatore</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E26" s="18" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>118</v>
+        <v>-146</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>0.525</v>
+        <v>0.659</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>0.4587</v>
+        <v>0.5935</v>
       </c>
       <c r="J26" s="19" t="n">
-        <v>0.0663</v>
+        <v>0.0655</v>
       </c>
       <c r="K26" s="20" t="n">
-        <v>3.583</v>
+        <v>6.943</v>
       </c>
       <c r="L26" s="18" t="n">
         <v>0.5</v>
       </c>
       <c r="M26" s="20" t="n">
-        <v>0.31</v>
+        <v>0.4</v>
       </c>
       <c r="N26" s="17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O26" s="21" t="inlineStr">
         <is>
@@ -2002,59 +1994,59 @@
         </is>
       </c>
       <c r="P26" s="22" t="n">
-        <v>1.18</v>
+        <v>0.6849</v>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="15" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="D27" s="17" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E27" s="18" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>0.57</v>
+        <v>0.505</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>0.5</v>
+        <v>0.4505</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0545</v>
       </c>
       <c r="K27" s="20" t="n">
-        <v>4.038</v>
+        <v>4.723</v>
       </c>
       <c r="L27" s="18" t="n">
         <v>0.5</v>
       </c>
       <c r="M27" s="20" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="N27" s="17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O27" s="21" t="inlineStr">
         <is>
@@ -2062,26 +2054,26 @@
         </is>
       </c>
       <c r="P27" s="22" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="23" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>Shane Smith</t>
+          <t>Taj Bradley</t>
         </is>
       </c>
       <c r="C28" s="25" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D28" s="25" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E28" s="26" t="n">
@@ -2093,28 +2085,28 @@
         </is>
       </c>
       <c r="G28" s="25" t="n">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="H28" s="27" t="n">
-        <v>0.576</v>
+        <v>0.573</v>
       </c>
       <c r="I28" s="27" t="n">
-        <v>0.5</v>
+        <v>0.4587</v>
       </c>
       <c r="J28" s="27" t="n">
-        <v>0.076</v>
+        <v>0.1143</v>
       </c>
       <c r="K28" s="28" t="n">
-        <v>5.393</v>
+        <v>5.159</v>
       </c>
       <c r="L28" s="26" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M28" s="28" t="n">
-        <v>0.38</v>
+        <v>0.53</v>
       </c>
       <c r="N28" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O28" s="29" t="inlineStr">
         <is>
@@ -2126,183 +2118,183 @@
       </c>
     </row>
     <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="15" t="n">
+      <c r="A29" s="23" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>Cole Ragans</t>
+        </is>
+      </c>
+      <c r="C29" s="25" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="D29" s="25" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E29" s="26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F29" s="25" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G29" s="25" t="n">
+        <v>-152</v>
+      </c>
+      <c r="H29" s="27" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="I29" s="27" t="n">
+        <v>0.6032</v>
+      </c>
+      <c r="J29" s="27" t="n">
+        <v>0.1348</v>
+      </c>
+      <c r="K29" s="28" t="n">
+        <v>5.951</v>
+      </c>
+      <c r="L29" s="26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M29" s="28" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="N29" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="O29" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P29" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="15" t="n">
         <v>46113</v>
       </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>George Kirby</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="n">
-        <v>-178</v>
-      </c>
-      <c r="H29" s="19" t="n">
-        <v>0.726</v>
-      </c>
-      <c r="I29" s="19" t="n">
-        <v>0.6403</v>
-      </c>
-      <c r="J29" s="19" t="n">
-        <v>0.0857</v>
-      </c>
-      <c r="K29" s="20" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L29" s="18" t="n">
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="H30" s="19" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="I30" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J30" s="19" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="K30" s="20" t="n">
+        <v>7.784</v>
+      </c>
+      <c r="L30" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M30" s="20" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="N30" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="O30" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P30" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="M29" s="20" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N29" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="O29" s="21" t="inlineStr">
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="n">
+        <v>116</v>
+      </c>
+      <c r="H31" s="19" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="I31" s="19" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J31" s="19" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="K31" s="20" t="n">
+        <v>6.789</v>
+      </c>
+      <c r="L31" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M31" s="20" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N31" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="O31" s="21" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P29" s="22" t="n">
-        <v>0.5618</v>
-      </c>
-    </row>
-    <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="23" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B30" s="24" t="inlineStr">
-        <is>
-          <t>Mike Burrows</t>
-        </is>
-      </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="D30" s="25" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="E30" s="26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F30" s="25" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G30" s="25" t="n">
-        <v>-114</v>
-      </c>
-      <c r="H30" s="27" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="I30" s="27" t="n">
-        <v>0.5327</v>
-      </c>
-      <c r="J30" s="27" t="n">
-        <v>0.1033</v>
-      </c>
-      <c r="K30" s="28" t="n">
-        <v>4.943</v>
-      </c>
-      <c r="L30" s="26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M30" s="28" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="N30" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="O30" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P30" s="30" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="23" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B31" s="24" t="inlineStr">
-        <is>
-          <t>Nick Pivetta</t>
-        </is>
-      </c>
-      <c r="C31" s="25" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="D31" s="25" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="E31" s="26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F31" s="25" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G31" s="25" t="n">
-        <v>128</v>
-      </c>
-      <c r="H31" s="27" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I31" s="27" t="n">
-        <v>0.4386</v>
-      </c>
-      <c r="J31" s="27" t="n">
-        <v>0.1114</v>
-      </c>
-      <c r="K31" s="28" t="n">
-        <v>5.551</v>
-      </c>
-      <c r="L31" s="26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M31" s="28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N31" s="25" t="n">
-        <v>8</v>
-      </c>
-      <c r="O31" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P31" s="30" t="n">
-        <v>-1</v>
+      <c r="P31" s="22" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
@@ -2311,47 +2303,47 @@
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>Nathan Eovaldi</t>
+          <t>Yusei Kikuchi</t>
         </is>
       </c>
       <c r="C32" s="25" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="D32" s="25" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E32" s="26" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G32" s="25" t="n">
-        <v>-168</v>
+        <v>102</v>
       </c>
       <c r="H32" s="27" t="n">
-        <v>0.743</v>
+        <v>0.556</v>
       </c>
       <c r="I32" s="27" t="n">
-        <v>0.6269</v>
+        <v>0.495</v>
       </c>
       <c r="J32" s="27" t="n">
-        <v>0.1161</v>
+        <v>0.061</v>
       </c>
       <c r="K32" s="28" t="n">
-        <v>7.699</v>
+        <v>4.364</v>
       </c>
       <c r="L32" s="26" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M32" s="28" t="n">
-        <v>0.78</v>
+        <v>0.3</v>
       </c>
       <c r="N32" s="25" t="n">
         <v>5</v>
@@ -2371,21 +2363,21 @@
       </c>
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Kevin Gausman</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D33" s="17" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E33" s="18" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="F33" s="17" t="inlineStr">
         <is>
@@ -2393,28 +2385,28 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>0.624</v>
+        <v>0.529</v>
       </c>
       <c r="I33" s="19" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J33" s="19" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="K33" s="20" t="n">
+        <v>7.914</v>
+      </c>
+      <c r="L33" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="J33" s="19" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="K33" s="20" t="n">
-        <v>7.784</v>
-      </c>
-      <c r="L33" s="18" t="n">
-        <v>1.5</v>
-      </c>
       <c r="M33" s="20" t="n">
-        <v>0.62</v>
+        <v>0.31</v>
       </c>
       <c r="N33" s="17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O33" s="21" t="inlineStr">
         <is>
@@ -2422,7 +2414,7 @@
         </is>
       </c>
       <c r="P33" s="22" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
@@ -2431,21 +2423,21 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Matthew Liberatore</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D34" s="17" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E34" s="18" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
@@ -2453,28 +2445,28 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>-132</v>
+        <v>118</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>0.696</v>
+        <v>0.525</v>
       </c>
       <c r="I34" s="19" t="n">
-        <v>0.569</v>
+        <v>0.4587</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>0.127</v>
+        <v>0.0663</v>
       </c>
       <c r="K34" s="20" t="n">
-        <v>6.191</v>
+        <v>3.583</v>
       </c>
       <c r="L34" s="18" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M34" s="20" t="n">
-        <v>0.74</v>
+        <v>0.31</v>
       </c>
       <c r="N34" s="17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O34" s="21" t="inlineStr">
         <is>
@@ -2482,7 +2474,7 @@
         </is>
       </c>
       <c r="P34" s="22" t="n">
-        <v>0.7576000000000001</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
@@ -2491,21 +2483,21 @@
       </c>
       <c r="B35" s="16" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D35" s="17" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E35" s="18" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F35" s="17" t="inlineStr">
         <is>
@@ -2513,28 +2505,28 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>-144</v>
+        <v>100</v>
       </c>
       <c r="H35" s="19" t="n">
-        <v>0.735</v>
+        <v>0.57</v>
       </c>
       <c r="I35" s="19" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>0.1448</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K35" s="20" t="n">
-        <v>7.561</v>
+        <v>4.038</v>
       </c>
       <c r="L35" s="18" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M35" s="20" t="n">
-        <v>0.88</v>
+        <v>0.35</v>
       </c>
       <c r="N35" s="17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O35" s="21" t="inlineStr">
         <is>
@@ -2542,67 +2534,67 @@
         </is>
       </c>
       <c r="P35" s="22" t="n">
-        <v>0.6944</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="15" t="n">
+      <c r="A36" s="23" t="n">
         <v>46113</v>
       </c>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>Andrew Abbott</t>
-        </is>
-      </c>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="E36" s="18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F36" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G36" s="17" t="n">
-        <v>-112</v>
-      </c>
-      <c r="H36" s="19" t="n">
-        <v>0.677</v>
-      </c>
-      <c r="I36" s="19" t="n">
-        <v>0.5283</v>
-      </c>
-      <c r="J36" s="19" t="n">
-        <v>0.1487</v>
-      </c>
-      <c r="K36" s="20" t="n">
-        <v>4.469</v>
-      </c>
-      <c r="L36" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M36" s="20" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="N36" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="O36" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P36" s="22" t="n">
-        <v>0.8929</v>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>Shane Smith</t>
+        </is>
+      </c>
+      <c r="C36" s="25" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D36" s="25" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E36" s="26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F36" s="25" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G36" s="25" t="n">
+        <v>100</v>
+      </c>
+      <c r="H36" s="27" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="I36" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J36" s="27" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="K36" s="28" t="n">
+        <v>5.393</v>
+      </c>
+      <c r="L36" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" s="28" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N36" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P36" s="30" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
@@ -2611,21 +2603,21 @@
       </c>
       <c r="B37" s="16" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>George Kirby</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D37" s="17" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E37" s="18" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="F37" s="17" t="inlineStr">
         <is>
@@ -2633,28 +2625,28 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>108</v>
+        <v>-178</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>0.644</v>
+        <v>0.726</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>0.4808</v>
+        <v>0.6403</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>0.1632</v>
+        <v>0.0857</v>
       </c>
       <c r="K37" s="20" t="n">
-        <v>5.865</v>
+        <v>5.8</v>
       </c>
       <c r="L37" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M37" s="20" t="n">
-        <v>0.79</v>
+        <v>0.6</v>
       </c>
       <c r="N37" s="17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O37" s="21" t="inlineStr">
         <is>
@@ -2662,7 +2654,7 @@
         </is>
       </c>
       <c r="P37" s="22" t="n">
-        <v>1.08</v>
+        <v>0.5618</v>
       </c>
     </row>
     <row r="38" ht="17" customHeight="1">
@@ -2671,21 +2663,21 @@
       </c>
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Mike Burrows</t>
         </is>
       </c>
       <c r="C38" s="25" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D38" s="25" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E38" s="26" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
@@ -2693,28 +2685,28 @@
         </is>
       </c>
       <c r="G38" s="25" t="n">
-        <v>-118</v>
+        <v>-114</v>
       </c>
       <c r="H38" s="27" t="n">
-        <v>0.732</v>
+        <v>0.636</v>
       </c>
       <c r="I38" s="27" t="n">
-        <v>0.5413</v>
+        <v>0.5327</v>
       </c>
       <c r="J38" s="27" t="n">
-        <v>0.1907</v>
+        <v>0.1033</v>
       </c>
       <c r="K38" s="28" t="n">
-        <v>3.414</v>
+        <v>4.943</v>
       </c>
       <c r="L38" s="26" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M38" s="28" t="n">
-        <v>1.04</v>
+        <v>0.55</v>
       </c>
       <c r="N38" s="25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O38" s="29" t="inlineStr">
         <is>
@@ -2726,355 +2718,355 @@
       </c>
     </row>
     <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="15" t="n">
+      <c r="A39" s="23" t="n">
         <v>46113</v>
       </c>
-      <c r="B39" s="16" t="inlineStr">
-        <is>
-          <t>Zac Gallen</t>
-        </is>
-      </c>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="E39" s="18" t="n">
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>Nick Pivetta</t>
+        </is>
+      </c>
+      <c r="C39" s="25" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D39" s="25" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="E39" s="26" t="n">
         <v>5.5</v>
       </c>
-      <c r="F39" s="17" t="inlineStr">
+      <c r="F39" s="25" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G39" s="17" t="n">
-        <v>112</v>
-      </c>
-      <c r="H39" s="19" t="n">
-        <v>0.707</v>
-      </c>
-      <c r="I39" s="19" t="n">
-        <v>0.4717</v>
-      </c>
-      <c r="J39" s="19" t="n">
-        <v>0.2353</v>
-      </c>
-      <c r="K39" s="20" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="L39" s="18" t="n">
+      <c r="G39" s="25" t="n">
+        <v>128</v>
+      </c>
+      <c r="H39" s="27" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I39" s="27" t="n">
+        <v>0.4386</v>
+      </c>
+      <c r="J39" s="27" t="n">
+        <v>0.1114</v>
+      </c>
+      <c r="K39" s="28" t="n">
+        <v>5.551</v>
+      </c>
+      <c r="L39" s="26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M39" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N39" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="O39" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P39" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="23" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>Nathan Eovaldi</t>
+        </is>
+      </c>
+      <c r="C40" s="25" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="D40" s="25" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E40" s="26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F40" s="25" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G40" s="25" t="n">
+        <v>-168</v>
+      </c>
+      <c r="H40" s="27" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="I40" s="27" t="n">
+        <v>0.6269</v>
+      </c>
+      <c r="J40" s="27" t="n">
+        <v>0.1161</v>
+      </c>
+      <c r="K40" s="28" t="n">
+        <v>7.699</v>
+      </c>
+      <c r="L40" s="26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M40" s="28" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="N40" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="O40" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P40" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>Paul Skenes</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F41" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G41" s="17" t="n">
+        <v>-132</v>
+      </c>
+      <c r="H41" s="19" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="I41" s="19" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="J41" s="19" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="K41" s="20" t="n">
+        <v>6.191</v>
+      </c>
+      <c r="L41" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M41" s="20" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="N41" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O41" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P41" s="22" t="n">
+        <v>0.7576000000000001</v>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>Andrew Abbott</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H42" s="19" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="I42" s="19" t="n">
+        <v>0.5283</v>
+      </c>
+      <c r="J42" s="19" t="n">
+        <v>0.1487</v>
+      </c>
+      <c r="K42" s="20" t="n">
+        <v>4.469</v>
+      </c>
+      <c r="L42" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M42" s="20" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="N42" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O42" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P42" s="22" t="n">
+        <v>0.8929</v>
+      </c>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="23" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>Cade Cavalli</t>
+        </is>
+      </c>
+      <c r="C43" s="25" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="D43" s="25" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E43" s="26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F43" s="25" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G43" s="25" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H43" s="27" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="I43" s="27" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="J43" s="27" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="K43" s="28" t="n">
+        <v>5.697</v>
+      </c>
+      <c r="L43" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="M39" s="20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N39" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="O39" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P39" s="22" t="n">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B40" s="16" t="inlineStr">
-        <is>
-          <t>Adrian Houser</t>
-        </is>
-      </c>
-      <c r="C40" s="17" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E40" s="18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F40" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G40" s="17" t="n">
-        <v>-125</v>
-      </c>
-      <c r="H40" s="19" t="n">
-        <v>0.724</v>
-      </c>
-      <c r="I40" s="19" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="J40" s="19" t="n">
-        <v>0.1684</v>
-      </c>
-      <c r="K40" s="20" t="n">
-        <v>5.063</v>
-      </c>
-      <c r="L40" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M40" s="20" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="N40" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="O40" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P40" s="22" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="23" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B41" s="24" t="inlineStr">
-        <is>
-          <t>Aaron Civale</t>
-        </is>
-      </c>
-      <c r="C41" s="25" t="inlineStr">
-        <is>
-          <t>OAK</t>
-        </is>
-      </c>
-      <c r="D41" s="25" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="E41" s="26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F41" s="25" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G41" s="25" t="n">
-        <v>-146</v>
-      </c>
-      <c r="H41" s="27" t="n">
-        <v>0.666</v>
-      </c>
-      <c r="I41" s="27" t="n">
-        <v>0.5935</v>
-      </c>
-      <c r="J41" s="27" t="n">
-        <v>0.0725</v>
-      </c>
-      <c r="K41" s="28" t="n">
-        <v>4.714</v>
-      </c>
-      <c r="L41" s="26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M41" s="28" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="N41" s="25" t="n">
+      <c r="M43" s="28" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="N43" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="O41" s="29" t="inlineStr">
+      <c r="O43" s="29" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P41" s="30" t="n">
+      <c r="P43" s="30" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="23" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B42" s="24" t="inlineStr">
-        <is>
-          <t>Andre Pallante</t>
-        </is>
-      </c>
-      <c r="C42" s="25" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="D42" s="25" t="inlineStr">
-        <is>
-          <t>NYM</t>
-        </is>
-      </c>
-      <c r="E42" s="26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F42" s="25" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G42" s="25" t="n">
-        <v>126</v>
-      </c>
-      <c r="H42" s="27" t="n">
-        <v>0.523</v>
-      </c>
-      <c r="I42" s="27" t="n">
-        <v>0.4425</v>
-      </c>
-      <c r="J42" s="27" t="n">
-        <v>0.0805</v>
-      </c>
-      <c r="K42" s="28" t="n">
-        <v>3.876</v>
-      </c>
-      <c r="L42" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M42" s="28" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="N42" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="O42" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P42" s="30" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="15" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B43" s="16" t="inlineStr">
-        <is>
-          <t>Max Scherzer</t>
-        </is>
-      </c>
-      <c r="C43" s="17" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="D43" s="17" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="E43" s="18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F43" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G43" s="17" t="n">
-        <v>-130</v>
-      </c>
-      <c r="H43" s="19" t="n">
-        <v>0.652</v>
-      </c>
-      <c r="I43" s="19" t="n">
-        <v>0.5652</v>
-      </c>
-      <c r="J43" s="19" t="n">
-        <v>0.0868</v>
-      </c>
-      <c r="K43" s="20" t="n">
-        <v>4.757</v>
-      </c>
-      <c r="L43" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M43" s="20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N43" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="O43" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P43" s="22" t="n">
-        <v>0.7692</v>
       </c>
     </row>
     <row r="44" ht="17" customHeight="1">
       <c r="A44" s="15" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>Erick Fedde</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D44" s="17" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E44" s="18" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="H44" s="19" t="n">
-        <v>0.527</v>
+        <v>0.644</v>
       </c>
       <c r="I44" s="19" t="n">
-        <v>0.4274</v>
+        <v>0.4808</v>
       </c>
       <c r="J44" s="19" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.1632</v>
       </c>
       <c r="K44" s="20" t="n">
-        <v>3.852</v>
+        <v>5.865</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M44" s="20" t="n">
-        <v>0.44</v>
+        <v>0.79</v>
       </c>
       <c r="N44" s="17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O44" s="21" t="inlineStr">
         <is>
@@ -3082,239 +3074,239 @@
         </is>
       </c>
       <c r="P44" s="22" t="n">
-        <v>1.34</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="45" ht="17" customHeight="1">
       <c r="A45" s="15" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B45" s="16" t="inlineStr">
         <is>
-          <t>Jameson Taillon</t>
+          <t>Adrian Houser</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D45" s="17" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E45" s="18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F45" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H45" s="19" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="I45" s="19" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="J45" s="19" t="n">
+        <v>0.1684</v>
+      </c>
+      <c r="K45" s="20" t="n">
+        <v>5.063</v>
+      </c>
+      <c r="L45" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M45" s="20" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N45" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="O45" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P45" s="22" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="23" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="C46" s="25" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="D46" s="25" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E46" s="26" t="n">
         <v>4.5</v>
       </c>
-      <c r="F45" s="17" t="inlineStr">
+      <c r="F46" s="25" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G45" s="17" t="n">
-        <v>116</v>
-      </c>
-      <c r="H45" s="19" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="I45" s="19" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J45" s="19" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="K45" s="20" t="n">
-        <v>4.313</v>
-      </c>
-      <c r="L45" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M45" s="20" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="N45" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O45" s="21" t="inlineStr">
+      <c r="G46" s="25" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H46" s="27" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="I46" s="27" t="n">
+        <v>0.5413</v>
+      </c>
+      <c r="J46" s="27" t="n">
+        <v>0.1907</v>
+      </c>
+      <c r="K46" s="28" t="n">
+        <v>3.414</v>
+      </c>
+      <c r="L46" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M46" s="28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N46" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="O46" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P46" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>Zac Gallen</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="D47" s="17" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="E47" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F47" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G47" s="17" t="n">
+        <v>112</v>
+      </c>
+      <c r="H47" s="19" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="I47" s="19" t="n">
+        <v>0.4717</v>
+      </c>
+      <c r="J47" s="19" t="n">
+        <v>0.2353</v>
+      </c>
+      <c r="K47" s="20" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="L47" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M47" s="20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N47" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O47" s="21" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P45" s="22" t="n">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="15" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B46" s="16" t="inlineStr">
-        <is>
-          <t>Ryan Feltner</t>
-        </is>
-      </c>
-      <c r="C46" s="17" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="D46" s="17" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="E46" s="18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F46" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G46" s="17" t="n">
-        <v>-108</v>
-      </c>
-      <c r="H46" s="19" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="I46" s="19" t="n">
-        <v>0.5192</v>
-      </c>
-      <c r="J46" s="19" t="n">
-        <v>0.1358</v>
-      </c>
-      <c r="K46" s="20" t="n">
-        <v>4.719</v>
-      </c>
-      <c r="L46" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M46" s="20" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="N46" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="O46" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P46" s="22" t="n">
-        <v>0.9258999999999999</v>
-      </c>
-    </row>
-    <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="23" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B47" s="24" t="inlineStr">
-        <is>
-          <t>José Soriano</t>
-        </is>
-      </c>
-      <c r="C47" s="25" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="D47" s="25" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="E47" s="26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F47" s="25" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G47" s="25" t="n">
-        <v>-110</v>
-      </c>
-      <c r="H47" s="27" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="I47" s="27" t="n">
-        <v>0.5238</v>
-      </c>
-      <c r="J47" s="27" t="n">
-        <v>0.1522</v>
-      </c>
-      <c r="K47" s="28" t="n">
-        <v>5.918</v>
-      </c>
-      <c r="L47" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="M47" s="28" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N47" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="O47" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P47" s="30" t="n">
-        <v>-1</v>
+      <c r="P47" s="22" t="n">
+        <v>1.12</v>
       </c>
     </row>
     <row r="48" ht="17" customHeight="1">
       <c r="A48" s="15" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>Edward Cabrera</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E48" s="18" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>116</v>
+        <v>-144</v>
       </c>
       <c r="H48" s="19" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.735</v>
       </c>
       <c r="I48" s="19" t="n">
-        <v>0.463</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="J48" s="19" t="n">
-        <v>0.226</v>
+        <v>0.1448</v>
       </c>
       <c r="K48" s="20" t="n">
-        <v>5.286</v>
+        <v>7.561</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M48" s="20" t="n">
-        <v>1.05</v>
+        <v>0.88</v>
       </c>
       <c r="N48" s="17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O48" s="21" t="inlineStr">
         <is>
@@ -3322,30 +3314,30 @@
         </is>
       </c>
       <c r="P48" s="22" t="n">
-        <v>1.16</v>
+        <v>0.6944</v>
       </c>
     </row>
     <row r="49" ht="17" customHeight="1">
       <c r="A49" s="23" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Andre Pallante</t>
         </is>
       </c>
       <c r="C49" s="25" t="inlineStr">
         <is>
-          <t>OAK</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D49" s="25" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E49" s="26" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
@@ -3353,28 +3345,28 @@
         </is>
       </c>
       <c r="G49" s="25" t="n">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="H49" s="27" t="n">
-        <v>0.586</v>
+        <v>0.523</v>
       </c>
       <c r="I49" s="27" t="n">
-        <v>0.5</v>
+        <v>0.4425</v>
       </c>
       <c r="J49" s="27" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0805</v>
       </c>
       <c r="K49" s="28" t="n">
-        <v>6.418</v>
+        <v>3.876</v>
       </c>
       <c r="L49" s="26" t="n">
         <v>1</v>
       </c>
       <c r="M49" s="28" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
       <c r="N49" s="25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O49" s="29" t="inlineStr">
         <is>
@@ -3387,21 +3379,21 @@
     </row>
     <row r="50" ht="17" customHeight="1">
       <c r="A50" s="23" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>Simeon Woods Richardson</t>
+          <t>Aaron Civale</t>
         </is>
       </c>
       <c r="C50" s="25" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OAK</t>
         </is>
       </c>
       <c r="D50" s="25" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E50" s="26" t="n">
@@ -3413,28 +3405,28 @@
         </is>
       </c>
       <c r="G50" s="25" t="n">
-        <v>-112</v>
+        <v>-146</v>
       </c>
       <c r="H50" s="27" t="n">
-        <v>0.783</v>
+        <v>0.666</v>
       </c>
       <c r="I50" s="27" t="n">
-        <v>0.5283</v>
+        <v>0.5935</v>
       </c>
       <c r="J50" s="27" t="n">
-        <v>0.2547</v>
+        <v>0.0725</v>
       </c>
       <c r="K50" s="28" t="n">
-        <v>5.562</v>
+        <v>4.714</v>
       </c>
       <c r="L50" s="26" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="M50" s="28" t="n">
-        <v>1.35</v>
+        <v>0.45</v>
       </c>
       <c r="N50" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O50" s="29" t="inlineStr">
         <is>
@@ -3447,54 +3439,54 @@
     </row>
     <row r="51" ht="17" customHeight="1">
       <c r="A51" s="15" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B51" s="16" t="inlineStr">
         <is>
-          <t>Jack Leiter</t>
+          <t>Max Scherzer</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D51" s="17" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E51" s="18" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F51" s="17" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>-144</v>
+        <v>-130</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>0.679</v>
+        <v>0.652</v>
       </c>
       <c r="I51" s="19" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.5652</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>0.0888</v>
+        <v>0.0868</v>
       </c>
       <c r="K51" s="20" t="n">
-        <v>6.017</v>
+        <v>4.757</v>
       </c>
       <c r="L51" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M51" s="20" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="N51" s="17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O51" s="21" t="inlineStr">
         <is>
@@ -3502,146 +3494,146 @@
         </is>
       </c>
       <c r="P51" s="22" t="n">
-        <v>0.6944</v>
+        <v>0.7692</v>
       </c>
     </row>
     <row r="52" ht="17" customHeight="1">
-      <c r="A52" s="23" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B52" s="24" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="C52" s="25" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="D52" s="25" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="E52" s="26" t="n">
+      <c r="A52" s="15" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B52" s="16" t="inlineStr">
+        <is>
+          <t>Erick Fedde</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E52" s="18" t="n">
         <v>3.5</v>
       </c>
-      <c r="F52" s="25" t="inlineStr">
+      <c r="F52" s="17" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G52" s="25" t="n">
-        <v>-174</v>
-      </c>
-      <c r="H52" s="27" t="n">
-        <v>0.6889999999999999</v>
-      </c>
-      <c r="I52" s="27" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="J52" s="27" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="K52" s="28" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="L52" s="26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M52" s="28" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="N52" s="25" t="n">
+      <c r="G52" s="17" t="n">
+        <v>134</v>
+      </c>
+      <c r="H52" s="19" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="I52" s="19" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="J52" s="19" t="n">
+        <v>0.09959999999999999</v>
+      </c>
+      <c r="K52" s="20" t="n">
+        <v>3.852</v>
+      </c>
+      <c r="L52" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" s="20" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="N52" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="O52" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P52" s="22" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="53" ht="17" customHeight="1">
+      <c r="A53" s="15" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B53" s="16" t="inlineStr">
+        <is>
+          <t>Jameson Taillon</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="D53" s="17" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E53" s="18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F53" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G53" s="17" t="n">
+        <v>116</v>
+      </c>
+      <c r="H53" s="19" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="I53" s="19" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J53" s="19" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="K53" s="20" t="n">
+        <v>4.313</v>
+      </c>
+      <c r="L53" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M53" s="20" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="N53" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="O52" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P52" s="30" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="53" ht="17" customHeight="1">
-      <c r="A53" s="23" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B53" s="24" t="inlineStr">
-        <is>
-          <t>Kyle Harrison</t>
-        </is>
-      </c>
-      <c r="C53" s="25" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D53" s="25" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="E53" s="26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F53" s="25" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G53" s="25" t="n">
-        <v>114</v>
-      </c>
-      <c r="H53" s="27" t="n">
-        <v>0.521</v>
-      </c>
-      <c r="I53" s="27" t="n">
-        <v>0.4673</v>
-      </c>
-      <c r="J53" s="27" t="n">
-        <v>0.0537</v>
-      </c>
-      <c r="K53" s="28" t="n">
-        <v>4.628</v>
-      </c>
-      <c r="L53" s="26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M53" s="28" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N53" s="25" t="n">
-        <v>8</v>
-      </c>
-      <c r="O53" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P53" s="30" t="n">
-        <v>-1</v>
+      <c r="O53" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P53" s="22" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="54" ht="17" customHeight="1">
       <c r="A54" s="15" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E54" s="18" t="n">
@@ -3653,28 +3645,28 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>-114</v>
+        <v>-108</v>
       </c>
       <c r="H54" s="19" t="n">
-        <v>0.584</v>
+        <v>0.655</v>
       </c>
       <c r="I54" s="19" t="n">
-        <v>0.5327</v>
+        <v>0.5192</v>
       </c>
       <c r="J54" s="19" t="n">
-        <v>0.0513</v>
+        <v>0.1358</v>
       </c>
       <c r="K54" s="20" t="n">
-        <v>4.252</v>
+        <v>4.719</v>
       </c>
       <c r="L54" s="18" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M54" s="20" t="n">
-        <v>0.27</v>
+        <v>0.71</v>
       </c>
       <c r="N54" s="17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O54" s="21" t="inlineStr">
         <is>
@@ -3682,136 +3674,136 @@
         </is>
       </c>
       <c r="P54" s="22" t="n">
-        <v>0.8772</v>
+        <v>0.9258999999999999</v>
       </c>
     </row>
     <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="15" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B55" s="16" t="inlineStr">
-        <is>
-          <t>Michael Wacha</t>
-        </is>
-      </c>
-      <c r="C55" s="17" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="D55" s="17" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="E55" s="18" t="n">
+      <c r="A55" s="23" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B55" s="24" t="inlineStr">
+        <is>
+          <t>José Soriano</t>
+        </is>
+      </c>
+      <c r="C55" s="25" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D55" s="25" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="E55" s="26" t="n">
         <v>4.5</v>
       </c>
-      <c r="F55" s="17" t="inlineStr">
+      <c r="F55" s="25" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G55" s="17" t="n">
-        <v>140</v>
-      </c>
-      <c r="H55" s="19" t="n">
-        <v>0.476</v>
-      </c>
-      <c r="I55" s="19" t="n">
-        <v>0.4167</v>
-      </c>
-      <c r="J55" s="19" t="n">
-        <v>0.0593</v>
-      </c>
-      <c r="K55" s="20" t="n">
-        <v>4.645</v>
-      </c>
-      <c r="L55" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M55" s="20" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N55" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="O55" s="21" t="inlineStr">
+      <c r="G55" s="25" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H55" s="27" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="I55" s="27" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="J55" s="27" t="n">
+        <v>0.1522</v>
+      </c>
+      <c r="K55" s="28" t="n">
+        <v>5.918</v>
+      </c>
+      <c r="L55" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M55" s="28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N55" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="O55" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P55" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="56" ht="17" customHeight="1">
+      <c r="A56" s="15" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B56" s="16" t="inlineStr">
+        <is>
+          <t>Edward Cabrera</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E56" s="18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="n">
+        <v>116</v>
+      </c>
+      <c r="H56" s="19" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="I56" s="19" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J56" s="19" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="K56" s="20" t="n">
+        <v>5.286</v>
+      </c>
+      <c r="L56" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M56" s="20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N56" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O56" s="21" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P55" s="22" t="n">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="56" ht="17" customHeight="1">
-      <c r="A56" s="23" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B56" s="24" t="inlineStr">
-        <is>
-          <t>Will Warren</t>
-        </is>
-      </c>
-      <c r="C56" s="25" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="D56" s="25" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="E56" s="26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F56" s="25" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G56" s="25" t="n">
-        <v>110</v>
-      </c>
-      <c r="H56" s="27" t="n">
-        <v>0.573</v>
-      </c>
-      <c r="I56" s="27" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="J56" s="27" t="n">
-        <v>0.0968</v>
-      </c>
-      <c r="K56" s="28" t="n">
-        <v>5.339</v>
-      </c>
-      <c r="L56" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M56" s="28" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="N56" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="O56" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P56" s="30" t="n">
-        <v>-1</v>
+      <c r="P56" s="22" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="57" ht="17" customHeight="1">
       <c r="A57" s="23" t="n">
-        <v>46109</v>
+        <v>46111</v>
       </c>
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>Jeffrey Springs</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="C57" s="25" t="inlineStr">
@@ -3821,11 +3813,11 @@
       </c>
       <c r="D57" s="25" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E57" s="26" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="F57" s="25" t="inlineStr">
         <is>
@@ -3833,28 +3825,28 @@
         </is>
       </c>
       <c r="G57" s="25" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H57" s="27" t="n">
-        <v>0.599</v>
+        <v>0.586</v>
       </c>
       <c r="I57" s="27" t="n">
-        <v>0.495</v>
+        <v>0.5</v>
       </c>
       <c r="J57" s="27" t="n">
-        <v>0.104</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="K57" s="28" t="n">
-        <v>4.389</v>
+        <v>6.418</v>
       </c>
       <c r="L57" s="26" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M57" s="28" t="n">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
       <c r="N57" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O57" s="29" t="inlineStr">
         <is>
@@ -3867,54 +3859,54 @@
     </row>
     <row r="58" ht="17" customHeight="1">
       <c r="A58" s="23" t="n">
-        <v>46109</v>
+        <v>46111</v>
       </c>
       <c r="B58" s="24" t="inlineStr">
         <is>
-          <t>Eury Pérez</t>
+          <t>Simeon Woods Richardson</t>
         </is>
       </c>
       <c r="C58" s="25" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D58" s="25" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E58" s="26" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="F58" s="25" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G58" s="25" t="n">
-        <v>-154</v>
+        <v>-112</v>
       </c>
       <c r="H58" s="27" t="n">
-        <v>0.713</v>
+        <v>0.783</v>
       </c>
       <c r="I58" s="27" t="n">
-        <v>0.6063</v>
+        <v>0.5283</v>
       </c>
       <c r="J58" s="27" t="n">
-        <v>0.1067</v>
+        <v>0.2547</v>
       </c>
       <c r="K58" s="28" t="n">
-        <v>5.311</v>
+        <v>5.562</v>
       </c>
       <c r="L58" s="26" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M58" s="28" t="n">
-        <v>0.68</v>
+        <v>1.35</v>
       </c>
       <c r="N58" s="25" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O58" s="29" t="inlineStr">
         <is>
@@ -3926,115 +3918,115 @@
       </c>
     </row>
     <row r="59" ht="17" customHeight="1">
-      <c r="A59" s="23" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B59" s="24" t="inlineStr">
-        <is>
-          <t>Kyle Freeland</t>
-        </is>
-      </c>
-      <c r="C59" s="25" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="D59" s="25" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="E59" s="26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F59" s="25" t="inlineStr">
+      <c r="A59" s="15" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B59" s="16" t="inlineStr">
+        <is>
+          <t>Jack Leiter</t>
+        </is>
+      </c>
+      <c r="C59" s="17" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="D59" s="17" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E59" s="18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F59" s="17" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G59" s="25" t="n">
-        <v>-158</v>
-      </c>
-      <c r="H59" s="27" t="n">
-        <v>0.677</v>
-      </c>
-      <c r="I59" s="27" t="n">
-        <v>0.6124000000000001</v>
-      </c>
-      <c r="J59" s="27" t="n">
-        <v>0.0646</v>
-      </c>
-      <c r="K59" s="28" t="n">
-        <v>4.869</v>
-      </c>
-      <c r="L59" s="26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M59" s="28" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="N59" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="O59" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P59" s="30" t="n">
-        <v>-1</v>
+      <c r="G59" s="17" t="n">
+        <v>-144</v>
+      </c>
+      <c r="H59" s="19" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="I59" s="19" t="n">
+        <v>0.5901999999999999</v>
+      </c>
+      <c r="J59" s="19" t="n">
+        <v>0.0888</v>
+      </c>
+      <c r="K59" s="20" t="n">
+        <v>6.017</v>
+      </c>
+      <c r="L59" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" s="20" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N59" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="O59" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P59" s="22" t="n">
+        <v>0.6944</v>
       </c>
     </row>
     <row r="60" ht="17" customHeight="1">
       <c r="A60" s="15" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>Robbie Ray</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E60" s="18" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>116</v>
+        <v>-114</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>0.532</v>
+        <v>0.584</v>
       </c>
       <c r="I60" s="19" t="n">
-        <v>0.463</v>
+        <v>0.5327</v>
       </c>
       <c r="J60" s="19" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0513</v>
       </c>
       <c r="K60" s="20" t="n">
-        <v>5.578</v>
+        <v>4.252</v>
       </c>
       <c r="L60" s="18" t="n">
         <v>0.5</v>
       </c>
       <c r="M60" s="20" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="N60" s="17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O60" s="21" t="inlineStr">
         <is>
@@ -4042,86 +4034,86 @@
         </is>
       </c>
       <c r="P60" s="22" t="n">
-        <v>1.16</v>
+        <v>0.8772</v>
       </c>
     </row>
     <row r="61" ht="17" customHeight="1">
-      <c r="A61" s="15" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B61" s="16" t="inlineStr">
-        <is>
-          <t>Cam Schlittler</t>
-        </is>
-      </c>
-      <c r="C61" s="17" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="D61" s="17" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="E61" s="18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F61" s="17" t="inlineStr">
+      <c r="A61" s="23" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B61" s="24" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="C61" s="25" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="D61" s="25" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E61" s="26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F61" s="25" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G61" s="17" t="n">
-        <v>-128</v>
-      </c>
-      <c r="H61" s="19" t="n">
-        <v>0.659</v>
-      </c>
-      <c r="I61" s="19" t="n">
-        <v>0.5614</v>
-      </c>
-      <c r="J61" s="19" t="n">
-        <v>0.09760000000000001</v>
-      </c>
-      <c r="K61" s="20" t="n">
-        <v>5.818</v>
-      </c>
-      <c r="L61" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M61" s="20" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="N61" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="O61" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P61" s="22" t="n">
-        <v>0.7812</v>
+      <c r="G61" s="25" t="n">
+        <v>-174</v>
+      </c>
+      <c r="H61" s="27" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="I61" s="27" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="J61" s="27" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="K61" s="28" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="L61" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M61" s="28" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="N61" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O61" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P61" s="30" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="62" ht="17" customHeight="1">
       <c r="A62" s="23" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>Shane Smith</t>
+          <t>Kyle Harrison</t>
         </is>
       </c>
       <c r="C62" s="25" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D62" s="25" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E62" s="26" t="n">
@@ -4129,32 +4121,32 @@
       </c>
       <c r="F62" s="25" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G62" s="25" t="n">
-        <v>-114</v>
+        <v>114</v>
       </c>
       <c r="H62" s="27" t="n">
-        <v>0.607</v>
+        <v>0.521</v>
       </c>
       <c r="I62" s="27" t="n">
-        <v>0.5327</v>
+        <v>0.4673</v>
       </c>
       <c r="J62" s="27" t="n">
-        <v>0.0743</v>
+        <v>0.0537</v>
       </c>
       <c r="K62" s="28" t="n">
-        <v>5.338</v>
+        <v>4.628</v>
       </c>
       <c r="L62" s="26" t="n">
         <v>0.5</v>
       </c>
       <c r="M62" s="28" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="N62" s="25" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O62" s="29" t="inlineStr">
         <is>
@@ -4166,206 +4158,206 @@
       </c>
     </row>
     <row r="63" ht="17" customHeight="1">
-      <c r="A63" s="23" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B63" s="24" t="inlineStr">
-        <is>
-          <t>Hunter Brown</t>
-        </is>
-      </c>
-      <c r="C63" s="25" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="D63" s="25" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="E63" s="26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F63" s="25" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G63" s="25" t="n">
-        <v>114</v>
-      </c>
-      <c r="H63" s="27" t="n">
-        <v>0.587</v>
-      </c>
-      <c r="I63" s="27" t="n">
-        <v>0.4673</v>
-      </c>
-      <c r="J63" s="27" t="n">
-        <v>0.1197</v>
-      </c>
-      <c r="K63" s="28" t="n">
-        <v>6.417</v>
-      </c>
-      <c r="L63" s="26" t="n">
+      <c r="A63" s="15" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B63" s="16" t="inlineStr">
+        <is>
+          <t>Michael Wacha</t>
+        </is>
+      </c>
+      <c r="C63" s="17" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="D63" s="17" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E63" s="18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F63" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G63" s="17" t="n">
+        <v>140</v>
+      </c>
+      <c r="H63" s="19" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="I63" s="19" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="J63" s="19" t="n">
+        <v>0.0593</v>
+      </c>
+      <c r="K63" s="20" t="n">
+        <v>4.645</v>
+      </c>
+      <c r="L63" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M63" s="20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N63" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="O63" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P63" s="22" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="64" ht="17" customHeight="1">
+      <c r="A64" s="23" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B64" s="24" t="inlineStr">
+        <is>
+          <t>Will Warren</t>
+        </is>
+      </c>
+      <c r="C64" s="25" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="D64" s="25" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="E64" s="26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F64" s="25" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G64" s="25" t="n">
+        <v>110</v>
+      </c>
+      <c r="H64" s="27" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="I64" s="27" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="J64" s="27" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="K64" s="28" t="n">
+        <v>5.339</v>
+      </c>
+      <c r="L64" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M64" s="28" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N64" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O64" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P64" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="65" ht="17" customHeight="1">
+      <c r="A65" s="23" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B65" s="24" t="inlineStr">
+        <is>
+          <t>Jeffrey Springs</t>
+        </is>
+      </c>
+      <c r="C65" s="25" t="inlineStr">
+        <is>
+          <t>OAK</t>
+        </is>
+      </c>
+      <c r="D65" s="25" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E65" s="26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F65" s="25" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G65" s="25" t="n">
+        <v>102</v>
+      </c>
+      <c r="H65" s="27" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="I65" s="27" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="J65" s="27" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="K65" s="28" t="n">
+        <v>4.389</v>
+      </c>
+      <c r="L65" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="M63" s="28" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="N63" s="25" t="n">
-        <v>9</v>
-      </c>
-      <c r="O63" s="29" t="inlineStr">
+      <c r="M65" s="28" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N65" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="O65" s="29" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P63" s="30" t="n">
+      <c r="P65" s="30" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="64" ht="17" customHeight="1">
-      <c r="A64" s="15" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B64" s="16" t="inlineStr">
-        <is>
-          <t>José Soriano</t>
-        </is>
-      </c>
-      <c r="C64" s="17" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="D64" s="17" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="E64" s="18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F64" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G64" s="17" t="n">
-        <v>108</v>
-      </c>
-      <c r="H64" s="19" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I64" s="19" t="n">
-        <v>0.4808</v>
-      </c>
-      <c r="J64" s="19" t="n">
-        <v>0.07920000000000001</v>
-      </c>
-      <c r="K64" s="20" t="n">
-        <v>5.163</v>
-      </c>
-      <c r="L64" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M64" s="20" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="N64" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="O64" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P64" s="22" t="n">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="65" ht="17" customHeight="1">
-      <c r="A65" s="15" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B65" s="16" t="inlineStr">
-        <is>
-          <t>Tarik Skubal</t>
-        </is>
-      </c>
-      <c r="C65" s="17" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="D65" s="17" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E65" s="18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F65" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G65" s="17" t="n">
-        <v>-172</v>
-      </c>
-      <c r="H65" s="19" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="I65" s="19" t="n">
-        <v>0.6324</v>
-      </c>
-      <c r="J65" s="19" t="n">
-        <v>0.1346</v>
-      </c>
-      <c r="K65" s="20" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="L65" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M65" s="20" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="N65" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="O65" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P65" s="22" t="n">
-        <v>0.5814</v>
       </c>
     </row>
     <row r="66" ht="17" customHeight="1">
       <c r="A66" s="23" t="n">
-        <v>46107</v>
+        <v>46109</v>
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Eury Pérez</t>
         </is>
       </c>
       <c r="C66" s="25" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D66" s="25" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E66" s="26" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="F66" s="25" t="inlineStr">
         <is>
@@ -4373,28 +4365,28 @@
         </is>
       </c>
       <c r="G66" s="25" t="n">
-        <v>124</v>
+        <v>-154</v>
       </c>
       <c r="H66" s="27" t="n">
-        <v>0.52</v>
+        <v>0.713</v>
       </c>
       <c r="I66" s="27" t="n">
-        <v>0.4464</v>
+        <v>0.6063</v>
       </c>
       <c r="J66" s="27" t="n">
-        <v>0.0736</v>
+        <v>0.1067</v>
       </c>
       <c r="K66" s="28" t="n">
-        <v>5.5</v>
+        <v>5.311</v>
       </c>
       <c r="L66" s="26" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M66" s="28" t="n">
-        <v>0.33</v>
+        <v>0.68</v>
       </c>
       <c r="N66" s="25" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="O66" s="29" t="inlineStr">
         <is>
@@ -4406,86 +4398,86 @@
       </c>
     </row>
     <row r="67" ht="17" customHeight="1">
-      <c r="A67" s="15" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B67" s="16" t="inlineStr">
-        <is>
-          <t>Nick Pivetta</t>
-        </is>
-      </c>
-      <c r="C67" s="17" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="D67" s="17" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="E67" s="18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F67" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G67" s="17" t="n">
-        <v>110</v>
-      </c>
-      <c r="H67" s="19" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I67" s="19" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="J67" s="19" t="n">
-        <v>0.0638</v>
-      </c>
-      <c r="K67" s="20" t="n">
-        <v>5.548</v>
-      </c>
-      <c r="L67" s="18" t="n">
+      <c r="A67" s="23" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B67" s="24" t="inlineStr">
+        <is>
+          <t>Kyle Freeland</t>
+        </is>
+      </c>
+      <c r="C67" s="25" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D67" s="25" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E67" s="26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F67" s="25" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G67" s="25" t="n">
+        <v>-158</v>
+      </c>
+      <c r="H67" s="27" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="I67" s="27" t="n">
+        <v>0.6124000000000001</v>
+      </c>
+      <c r="J67" s="27" t="n">
+        <v>0.0646</v>
+      </c>
+      <c r="K67" s="28" t="n">
+        <v>4.869</v>
+      </c>
+      <c r="L67" s="26" t="n">
         <v>0.5</v>
       </c>
-      <c r="M67" s="20" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N67" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="O67" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P67" s="22" t="n">
-        <v>1.1</v>
+      <c r="M67" s="28" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="N67" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="O67" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P67" s="30" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="68" ht="17" customHeight="1">
       <c r="A68" s="15" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>Andrew Abbott</t>
+          <t>Robbie Ray</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D68" s="17" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E68" s="18" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F68" s="17" t="inlineStr">
         <is>
@@ -4493,25 +4485,25 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H68" s="19" t="n">
-        <v>0.509</v>
+        <v>0.532</v>
       </c>
       <c r="I68" s="19" t="n">
-        <v>0.4545</v>
+        <v>0.463</v>
       </c>
       <c r="J68" s="19" t="n">
-        <v>0.0545</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K68" s="20" t="n">
-        <v>4.814</v>
+        <v>5.578</v>
       </c>
       <c r="L68" s="18" t="n">
         <v>0.5</v>
       </c>
       <c r="M68" s="20" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="N68" s="17" t="n">
         <v>4</v>
@@ -4522,66 +4514,546 @@
         </is>
       </c>
       <c r="P68" s="22" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="69" ht="17" customHeight="1">
+      <c r="A69" s="15" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B69" s="16" t="inlineStr">
+        <is>
+          <t>Cam Schlittler</t>
+        </is>
+      </c>
+      <c r="C69" s="17" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="D69" s="17" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="E69" s="18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F69" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G69" s="17" t="n">
+        <v>-128</v>
+      </c>
+      <c r="H69" s="19" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="I69" s="19" t="n">
+        <v>0.5614</v>
+      </c>
+      <c r="J69" s="19" t="n">
+        <v>0.09760000000000001</v>
+      </c>
+      <c r="K69" s="20" t="n">
+        <v>5.818</v>
+      </c>
+      <c r="L69" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M69" s="20" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="N69" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="O69" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P69" s="22" t="n">
+        <v>0.7812</v>
+      </c>
+    </row>
+    <row r="70" ht="17" customHeight="1">
+      <c r="A70" s="23" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B70" s="24" t="inlineStr">
+        <is>
+          <t>Shane Smith</t>
+        </is>
+      </c>
+      <c r="C70" s="25" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D70" s="25" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E70" s="26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F70" s="25" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G70" s="25" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H70" s="27" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="I70" s="27" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="J70" s="27" t="n">
+        <v>0.0743</v>
+      </c>
+      <c r="K70" s="28" t="n">
+        <v>5.338</v>
+      </c>
+      <c r="L70" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M70" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N70" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="O70" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P70" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="71" ht="17" customHeight="1">
+      <c r="A71" s="23" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B71" s="24" t="inlineStr">
+        <is>
+          <t>Hunter Brown</t>
+        </is>
+      </c>
+      <c r="C71" s="25" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="D71" s="25" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E71" s="26" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F71" s="25" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G71" s="25" t="n">
+        <v>114</v>
+      </c>
+      <c r="H71" s="27" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="I71" s="27" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="J71" s="27" t="n">
+        <v>0.1197</v>
+      </c>
+      <c r="K71" s="28" t="n">
+        <v>6.417</v>
+      </c>
+      <c r="L71" s="26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M71" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="N71" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="O71" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P71" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="72" ht="17" customHeight="1">
+      <c r="A72" s="15" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B72" s="16" t="inlineStr">
+        <is>
+          <t>José Soriano</t>
+        </is>
+      </c>
+      <c r="C72" s="17" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D72" s="17" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E72" s="18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F72" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G72" s="17" t="n">
+        <v>108</v>
+      </c>
+      <c r="H72" s="19" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I72" s="19" t="n">
+        <v>0.4808</v>
+      </c>
+      <c r="J72" s="19" t="n">
+        <v>0.07920000000000001</v>
+      </c>
+      <c r="K72" s="20" t="n">
+        <v>5.163</v>
+      </c>
+      <c r="L72" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" s="20" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N72" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="O72" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P72" s="22" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="73" ht="17" customHeight="1">
+      <c r="A73" s="15" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B73" s="16" t="inlineStr">
+        <is>
+          <t>Tarik Skubal</t>
+        </is>
+      </c>
+      <c r="C73" s="17" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="D73" s="17" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E73" s="18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F73" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G73" s="17" t="n">
+        <v>-172</v>
+      </c>
+      <c r="H73" s="19" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="I73" s="19" t="n">
+        <v>0.6324</v>
+      </c>
+      <c r="J73" s="19" t="n">
+        <v>0.1346</v>
+      </c>
+      <c r="K73" s="20" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="L73" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M73" s="20" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="N73" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="O73" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P73" s="22" t="n">
+        <v>0.5814</v>
+      </c>
+    </row>
+    <row r="74" ht="17" customHeight="1">
+      <c r="A74" s="23" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B74" s="24" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="C74" s="25" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D74" s="25" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E74" s="26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F74" s="25" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G74" s="25" t="n">
+        <v>124</v>
+      </c>
+      <c r="H74" s="27" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I74" s="27" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="J74" s="27" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="K74" s="28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L74" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M74" s="28" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N74" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="O74" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P74" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="75" ht="17" customHeight="1">
+      <c r="A75" s="15" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B75" s="16" t="inlineStr">
+        <is>
+          <t>Nick Pivetta</t>
+        </is>
+      </c>
+      <c r="C75" s="17" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D75" s="17" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="E75" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F75" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G75" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="H75" s="19" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I75" s="19" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="J75" s="19" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="K75" s="20" t="n">
+        <v>5.548</v>
+      </c>
+      <c r="L75" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M75" s="20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N75" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="O75" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P75" s="22" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="76" ht="17" customHeight="1">
+      <c r="A76" s="15" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B76" s="16" t="inlineStr">
+        <is>
+          <t>Andrew Abbott</t>
+        </is>
+      </c>
+      <c r="C76" s="17" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="D76" s="17" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="E76" s="18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F76" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G76" s="17" t="n">
+        <v>120</v>
+      </c>
+      <c r="H76" s="19" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="I76" s="19" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="J76" s="19" t="n">
+        <v>0.0545</v>
+      </c>
+      <c r="K76" s="20" t="n">
+        <v>4.814</v>
+      </c>
+      <c r="L76" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M76" s="20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N76" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="O76" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P76" s="22" t="n">
         <v>1.2</v>
       </c>
     </row>
-    <row r="69" ht="17" customHeight="1">
-      <c r="A69" s="23" t="n">
+    <row r="77" ht="17" customHeight="1">
+      <c r="A77" s="23" t="n">
         <v>46107</v>
       </c>
-      <c r="B69" s="24" t="inlineStr">
+      <c r="B77" s="24" t="inlineStr">
         <is>
           <t>Matthew Boyd</t>
         </is>
       </c>
-      <c r="C69" s="25" t="inlineStr">
+      <c r="C77" s="25" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="D69" s="25" t="inlineStr">
+      <c r="D77" s="25" t="inlineStr">
         <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E69" s="26" t="n">
+      <c r="E77" s="26" t="n">
         <v>4.5</v>
       </c>
-      <c r="F69" s="25" t="inlineStr">
+      <c r="F77" s="25" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G69" s="25" t="n">
+      <c r="G77" s="25" t="n">
         <v>132</v>
       </c>
-      <c r="H69" s="27" t="n">
+      <c r="H77" s="27" t="n">
         <v>0.59</v>
       </c>
-      <c r="I69" s="27" t="n">
+      <c r="I77" s="27" t="n">
         <v>0.431</v>
       </c>
-      <c r="J69" s="27" t="n">
+      <c r="J77" s="27" t="n">
         <v>0.159</v>
       </c>
-      <c r="K69" s="28" t="n">
+      <c r="K77" s="28" t="n">
         <v>4.258</v>
       </c>
-      <c r="L69" s="26" t="n">
+      <c r="L77" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="M69" s="28" t="n">
+      <c r="M77" s="28" t="n">
         <v>0.7</v>
       </c>
-      <c r="N69" s="25" t="n">
+      <c r="N77" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="O69" s="29" t="inlineStr">
+      <c r="O77" s="29" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P69" s="30" t="n">
+      <c r="P77" s="30" t="n">
         <v>-1</v>
       </c>
     </row>

--- a/bet_log.xlsx
+++ b/bet_log.xlsx
@@ -624,7 +624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P77"/>
+  <dimension ref="A1:P76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -696,7 +696,7 @@
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>63</v>
@@ -867,17 +867,17 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Keider Montero</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E7" s="10" t="n">
@@ -889,25 +889,25 @@
         </is>
       </c>
       <c r="G7" s="9" t="n">
-        <v>-112</v>
+        <v>108</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.591</v>
+        <v>0.546</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.5283</v>
+        <v>0.4808</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>4.188</v>
+        <v>3.968</v>
       </c>
       <c r="L7" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="N7" s="9" t="inlineStr"/>
       <c r="O7" s="13" t="inlineStr"/>
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="G9" s="9" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H9" s="11" t="n">
         <v>0.518</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.4425</v>
+        <v>0.4386</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>0.0755</v>
+        <v>0.0794</v>
       </c>
       <c r="K9" s="12" t="n">
         <v>5.702</v>
@@ -1011,7 +1011,7 @@
         <v>1</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="N9" s="9" t="inlineStr"/>
       <c r="O9" s="13" t="inlineStr"/>
@@ -1075,47 +1075,47 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Logan Webb</t>
+          <t>Eric Lauer</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E11" s="10" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G11" s="9" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.588</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.4587</v>
+        <v>0.5</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>0.1003</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>5.372</v>
+        <v>5.457</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="N11" s="9" t="inlineStr"/>
       <c r="O11" s="13" t="inlineStr"/>
@@ -1149,16 +1149,16 @@
         </is>
       </c>
       <c r="G12" s="9" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H12" s="11" t="n">
         <v>0.575</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>0.4587</v>
+        <v>0.4545</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>0.1163</v>
+        <v>0.1205</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>5.165</v>
@@ -1167,182 +1167,190 @@
         <v>1.5</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="N12" s="9" t="inlineStr"/>
       <c r="O12" s="13" t="inlineStr"/>
       <c r="P12" s="14" t="inlineStr"/>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="7" t="n">
-        <v>46117</v>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Eric Lauer</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="n">
+      <c r="A13" s="15" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Bryce Elder</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>-132</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>5.551</v>
+      </c>
+      <c r="L13" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" s="20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N13" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="O13" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P13" s="22" t="n">
+        <v>0.7576000000000001</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="23" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>Jack Flaherty</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F14" s="25" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>116</v>
+      </c>
+      <c r="H14" s="27" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="I14" s="27" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J14" s="27" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K14" s="28" t="n">
+        <v>4.756</v>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" s="28" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N14" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="O14" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P14" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="15" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Steven Matz</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="n">
         <v>4.5</v>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G13" s="9" t="n">
-        <v>120</v>
-      </c>
-      <c r="H13" s="11" t="n">
-        <v>0.588</v>
-      </c>
-      <c r="I13" s="11" t="n">
-        <v>0.4545</v>
-      </c>
-      <c r="J13" s="11" t="n">
-        <v>0.1335</v>
-      </c>
-      <c r="K13" s="12" t="n">
-        <v>5.457</v>
-      </c>
-      <c r="L13" s="10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M13" s="12" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="N13" s="9" t="inlineStr"/>
-      <c r="O13" s="13" t="inlineStr"/>
-      <c r="P13" s="14" t="inlineStr"/>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="15" t="n">
-        <v>46116</v>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>Bryce Elder</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="n">
-        <v>-132</v>
-      </c>
-      <c r="H14" s="19" t="n">
-        <v>0.753</v>
-      </c>
-      <c r="I14" s="19" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="J14" s="19" t="n">
-        <v>0.184</v>
-      </c>
-      <c r="K14" s="20" t="n">
-        <v>5.551</v>
-      </c>
-      <c r="L14" s="18" t="n">
+      <c r="G15" s="17" t="n">
+        <v>116</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J15" s="19" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="K15" s="20" t="n">
+        <v>5.743</v>
+      </c>
+      <c r="L15" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="M14" s="20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N14" s="17" t="n">
+      <c r="M15" s="20" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N15" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="O14" s="21" t="inlineStr">
+      <c r="O15" s="21" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P14" s="22" t="n">
-        <v>0.7576000000000001</v>
-      </c>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="23" t="n">
-        <v>46116</v>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>Jack Flaherty</t>
-        </is>
-      </c>
-      <c r="C15" s="25" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="D15" s="25" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="E15" s="26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F15" s="25" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G15" s="25" t="n">
-        <v>116</v>
-      </c>
-      <c r="H15" s="27" t="n">
-        <v>0.653</v>
-      </c>
-      <c r="I15" s="27" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J15" s="27" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="K15" s="28" t="n">
-        <v>4.756</v>
-      </c>
-      <c r="L15" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" s="28" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="N15" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="O15" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P15" s="30" t="n">
-        <v>-1</v>
+      <c r="P15" s="22" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1351,50 +1359,50 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>Steven Matz</t>
+          <t>Ryan Weathers</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E16" s="18" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>116</v>
+        <v>-125</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>0.651</v>
+        <v>0.741</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>0.463</v>
+        <v>0.5556</v>
       </c>
       <c r="J16" s="19" t="n">
-        <v>0.188</v>
+        <v>0.1854</v>
       </c>
       <c r="K16" s="20" t="n">
-        <v>5.743</v>
+        <v>4.217</v>
       </c>
       <c r="L16" s="18" t="n">
         <v>2</v>
       </c>
       <c r="M16" s="20" t="n">
-        <v>0.88</v>
+        <v>1.04</v>
       </c>
       <c r="N16" s="17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O16" s="21" t="inlineStr">
         <is>
@@ -1402,67 +1410,67 @@
         </is>
       </c>
       <c r="P16" s="22" t="n">
-        <v>1.16</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="23" t="n">
         <v>46116</v>
       </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>Ryan Weathers</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="n">
-        <v>-125</v>
-      </c>
-      <c r="H17" s="19" t="n">
-        <v>0.741</v>
-      </c>
-      <c r="I17" s="19" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="J17" s="19" t="n">
-        <v>0.1854</v>
-      </c>
-      <c r="K17" s="20" t="n">
-        <v>4.217</v>
-      </c>
-      <c r="L17" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" s="20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N17" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="O17" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P17" s="22" t="n">
-        <v>0.8</v>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>Randy Vásquez</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F17" s="25" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G17" s="25" t="n">
+        <v>-130</v>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="I17" s="27" t="n">
+        <v>0.5652</v>
+      </c>
+      <c r="J17" s="27" t="n">
+        <v>0.1128</v>
+      </c>
+      <c r="K17" s="28" t="n">
+        <v>4.813</v>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M17" s="28" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="N17" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O17" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P17" s="30" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
@@ -1471,50 +1479,50 @@
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>Chad Patrick</t>
+          <t>Carmen Mlodzinski</t>
         </is>
       </c>
       <c r="C18" s="25" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="D18" s="25" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G18" s="25" t="n">
-        <v>-154</v>
+        <v>-108</v>
       </c>
       <c r="H18" s="27" t="n">
-        <v>0.678</v>
+        <v>0.666</v>
       </c>
       <c r="I18" s="27" t="n">
-        <v>0.6063</v>
+        <v>0.5192</v>
       </c>
       <c r="J18" s="27" t="n">
-        <v>0.0717</v>
+        <v>0.1468</v>
       </c>
       <c r="K18" s="28" t="n">
-        <v>4.705</v>
+        <v>3.828</v>
       </c>
       <c r="L18" s="26" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M18" s="28" t="n">
-        <v>0.46</v>
+        <v>0.76</v>
       </c>
       <c r="N18" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O18" s="29" t="inlineStr">
         <is>
@@ -1531,50 +1539,50 @@
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>Carmen Mlodzinski</t>
+          <t>Chad Patrick</t>
         </is>
       </c>
       <c r="C19" s="25" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D19" s="25" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E19" s="26" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G19" s="25" t="n">
-        <v>-108</v>
+        <v>-154</v>
       </c>
       <c r="H19" s="27" t="n">
-        <v>0.666</v>
+        <v>0.678</v>
       </c>
       <c r="I19" s="27" t="n">
-        <v>0.5192</v>
+        <v>0.6063</v>
       </c>
       <c r="J19" s="27" t="n">
-        <v>0.1468</v>
+        <v>0.0717</v>
       </c>
       <c r="K19" s="28" t="n">
-        <v>3.828</v>
+        <v>4.705</v>
       </c>
       <c r="L19" s="26" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M19" s="28" t="n">
-        <v>0.76</v>
+        <v>0.46</v>
       </c>
       <c r="N19" s="25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O19" s="29" t="inlineStr">
         <is>
@@ -1586,123 +1594,123 @@
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="23" t="n">
-        <v>46116</v>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>Randy Vásquez</t>
-        </is>
-      </c>
-      <c r="C20" s="25" t="inlineStr">
+      <c r="A20" s="15" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>Michael King</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>BOS</t>
         </is>
       </c>
-      <c r="E20" s="26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F20" s="25" t="inlineStr">
+      <c r="E20" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="n">
+        <v>102</v>
+      </c>
+      <c r="H20" s="19" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="J20" s="19" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="K20" s="20" t="n">
+        <v>5.081</v>
+      </c>
+      <c r="L20" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="20" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="N20" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O20" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P20" s="22" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="23" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>Emmet Sheehan</t>
+        </is>
+      </c>
+      <c r="C21" s="25" t="inlineStr">
+        <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="D21" s="25" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="E21" s="26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F21" s="25" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G20" s="25" t="n">
-        <v>-130</v>
-      </c>
-      <c r="H20" s="27" t="n">
-        <v>0.678</v>
-      </c>
-      <c r="I20" s="27" t="n">
-        <v>0.5652</v>
-      </c>
-      <c r="J20" s="27" t="n">
-        <v>0.1128</v>
-      </c>
-      <c r="K20" s="28" t="n">
-        <v>4.813</v>
-      </c>
-      <c r="L20" s="26" t="n">
+      <c r="G21" s="25" t="n">
+        <v>-128</v>
+      </c>
+      <c r="H21" s="27" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I21" s="27" t="n">
+        <v>0.5614</v>
+      </c>
+      <c r="J21" s="27" t="n">
+        <v>0.1186</v>
+      </c>
+      <c r="K21" s="28" t="n">
+        <v>6.988</v>
+      </c>
+      <c r="L21" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="M20" s="28" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="N20" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="O20" s="29" t="inlineStr">
+      <c r="M21" s="28" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="N21" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="O21" s="29" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P20" s="30" t="n">
+      <c r="P21" s="30" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="15" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>Michael King</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="n">
-        <v>102</v>
-      </c>
-      <c r="H21" s="19" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="I21" s="19" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="J21" s="19" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="K21" s="20" t="n">
-        <v>5.081</v>
-      </c>
-      <c r="L21" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" s="20" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="N21" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="O21" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P21" s="22" t="n">
-        <v>1.02</v>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
@@ -1711,21 +1719,21 @@
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>Emmet Sheehan</t>
+          <t>Cade Horton</t>
         </is>
       </c>
       <c r="C22" s="25" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="D22" s="25" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
@@ -1733,28 +1741,28 @@
         </is>
       </c>
       <c r="G22" s="25" t="n">
-        <v>-128</v>
+        <v>-136</v>
       </c>
       <c r="H22" s="27" t="n">
-        <v>0.68</v>
+        <v>0.676</v>
       </c>
       <c r="I22" s="27" t="n">
-        <v>0.5614</v>
+        <v>0.5763</v>
       </c>
       <c r="J22" s="27" t="n">
-        <v>0.1186</v>
+        <v>0.0997</v>
       </c>
       <c r="K22" s="28" t="n">
-        <v>6.988</v>
+        <v>4.806</v>
       </c>
       <c r="L22" s="26" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M22" s="28" t="n">
-        <v>0.68</v>
+        <v>0.59</v>
       </c>
       <c r="N22" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O22" s="29" t="inlineStr">
         <is>
@@ -1766,116 +1774,116 @@
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="23" t="n">
+      <c r="A23" s="7" t="n">
         <v>46115</v>
       </c>
-      <c r="B23" s="24" t="inlineStr">
-        <is>
-          <t>Cade Horton</t>
-        </is>
-      </c>
-      <c r="C23" s="25" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="D23" s="25" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
-      <c r="E23" s="26" t="n">
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Chad Patrick</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="n">
         <v>3.5</v>
       </c>
-      <c r="F23" s="25" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G23" s="25" t="n">
-        <v>-136</v>
-      </c>
-      <c r="H23" s="27" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="I23" s="27" t="n">
-        <v>0.5763</v>
-      </c>
-      <c r="J23" s="27" t="n">
-        <v>0.0997</v>
-      </c>
-      <c r="K23" s="28" t="n">
-        <v>4.806</v>
-      </c>
-      <c r="L23" s="26" t="n">
+      <c r="G23" s="9" t="n">
+        <v>-138</v>
+      </c>
+      <c r="H23" s="11" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>0.5798</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>0.0922</v>
+      </c>
+      <c r="K23" s="12" t="n">
+        <v>4.705</v>
+      </c>
+      <c r="L23" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M23" s="28" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="N23" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P23" s="30" t="n">
-        <v>-1</v>
-      </c>
+      <c r="M23" s="12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N23" s="9" t="inlineStr"/>
+      <c r="O23" s="13" t="inlineStr"/>
+      <c r="P23" s="14" t="inlineStr"/>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="15" t="n">
         <v>46115</v>
       </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Chad Patrick</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>Kyle Bradish</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G24" s="9" t="n">
-        <v>-138</v>
-      </c>
-      <c r="H24" s="11" t="n">
-        <v>0.672</v>
-      </c>
-      <c r="I24" s="11" t="n">
-        <v>0.5798</v>
-      </c>
-      <c r="J24" s="11" t="n">
-        <v>0.0922</v>
-      </c>
-      <c r="K24" s="12" t="n">
-        <v>4.705</v>
-      </c>
-      <c r="L24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" s="12" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="N24" s="9" t="inlineStr"/>
-      <c r="O24" s="13" t="inlineStr"/>
-      <c r="P24" s="14" t="inlineStr"/>
+      <c r="G24" s="17" t="n">
+        <v>-146</v>
+      </c>
+      <c r="H24" s="19" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <v>0.5935</v>
+      </c>
+      <c r="J24" s="19" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="K24" s="20" t="n">
+        <v>6.943</v>
+      </c>
+      <c r="L24" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M24" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N24" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="O24" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P24" s="22" t="n">
+        <v>0.6849</v>
+      </c>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="15" t="n">
@@ -1943,50 +1951,50 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
           <t>BAL</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
       <c r="E26" s="18" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>-146</v>
+        <v>122</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>0.659</v>
+        <v>0.505</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>0.5935</v>
+        <v>0.4505</v>
       </c>
       <c r="J26" s="19" t="n">
-        <v>0.0655</v>
+        <v>0.0545</v>
       </c>
       <c r="K26" s="20" t="n">
-        <v>6.943</v>
+        <v>4.723</v>
       </c>
       <c r="L26" s="18" t="n">
         <v>0.5</v>
       </c>
       <c r="M26" s="20" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="N26" s="17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O26" s="21" t="inlineStr">
         <is>
@@ -1994,67 +2002,67 @@
         </is>
       </c>
       <c r="P26" s="22" t="n">
-        <v>0.6849</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="15" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>Mitch Keller</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="n">
+      <c r="A27" s="23" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>Taj Bradley</t>
+        </is>
+      </c>
+      <c r="C27" s="25" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="D27" s="25" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="E27" s="26" t="n">
         <v>4.5</v>
       </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="n">
-        <v>122</v>
-      </c>
-      <c r="H27" s="19" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="I27" s="19" t="n">
-        <v>0.4505</v>
-      </c>
-      <c r="J27" s="19" t="n">
-        <v>0.0545</v>
-      </c>
-      <c r="K27" s="20" t="n">
-        <v>4.723</v>
-      </c>
-      <c r="L27" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M27" s="20" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N27" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="O27" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P27" s="22" t="n">
-        <v>1.22</v>
+      <c r="F27" s="25" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G27" s="25" t="n">
+        <v>118</v>
+      </c>
+      <c r="H27" s="27" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="I27" s="27" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="J27" s="27" t="n">
+        <v>0.1143</v>
+      </c>
+      <c r="K27" s="28" t="n">
+        <v>5.159</v>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M27" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="N27" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O27" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P27" s="30" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
@@ -2063,50 +2071,50 @@
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Cole Ragans</t>
         </is>
       </c>
       <c r="C28" s="25" t="inlineStr">
         <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="D28" s="25" t="inlineStr">
+        <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="D28" s="25" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
       <c r="E28" s="26" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G28" s="25" t="n">
-        <v>118</v>
+        <v>-152</v>
       </c>
       <c r="H28" s="27" t="n">
-        <v>0.573</v>
+        <v>0.738</v>
       </c>
       <c r="I28" s="27" t="n">
-        <v>0.4587</v>
+        <v>0.6032</v>
       </c>
       <c r="J28" s="27" t="n">
-        <v>0.1143</v>
+        <v>0.1348</v>
       </c>
       <c r="K28" s="28" t="n">
-        <v>5.159</v>
+        <v>5.951</v>
       </c>
       <c r="L28" s="26" t="n">
         <v>1.5</v>
       </c>
       <c r="M28" s="28" t="n">
-        <v>0.53</v>
+        <v>0.85</v>
       </c>
       <c r="N28" s="25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O28" s="29" t="inlineStr">
         <is>
@@ -2118,63 +2126,63 @@
       </c>
     </row>
     <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="23" t="n">
-        <v>46114</v>
-      </c>
-      <c r="B29" s="24" t="inlineStr">
-        <is>
-          <t>Cole Ragans</t>
-        </is>
-      </c>
-      <c r="C29" s="25" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="D29" s="25" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="E29" s="26" t="n">
+      <c r="A29" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>Paul Skenes</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="E29" s="18" t="n">
         <v>7.5</v>
       </c>
-      <c r="F29" s="25" t="inlineStr">
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G29" s="25" t="n">
-        <v>-152</v>
-      </c>
-      <c r="H29" s="27" t="n">
-        <v>0.738</v>
-      </c>
-      <c r="I29" s="27" t="n">
-        <v>0.6032</v>
-      </c>
-      <c r="J29" s="27" t="n">
-        <v>0.1348</v>
-      </c>
-      <c r="K29" s="28" t="n">
-        <v>5.951</v>
-      </c>
-      <c r="L29" s="26" t="n">
+      <c r="G29" s="17" t="n">
+        <v>-132</v>
+      </c>
+      <c r="H29" s="19" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="I29" s="19" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="J29" s="19" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="K29" s="20" t="n">
+        <v>6.191</v>
+      </c>
+      <c r="L29" s="18" t="n">
         <v>1.5</v>
       </c>
-      <c r="M29" s="28" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="N29" s="25" t="n">
-        <v>8</v>
-      </c>
-      <c r="O29" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P29" s="30" t="n">
-        <v>-1</v>
+      <c r="M29" s="20" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="N29" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O29" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P29" s="22" t="n">
+        <v>0.7576000000000001</v>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1">
@@ -2183,17 +2191,17 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="D30" s="17" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E30" s="18" t="n">
@@ -2205,25 +2213,25 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>0.624</v>
+        <v>0.515</v>
       </c>
       <c r="I30" s="19" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J30" s="19" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="K30" s="20" t="n">
+        <v>6.789</v>
+      </c>
+      <c r="L30" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="J30" s="19" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="K30" s="20" t="n">
-        <v>7.784</v>
-      </c>
-      <c r="L30" s="18" t="n">
-        <v>1.5</v>
-      </c>
       <c r="M30" s="20" t="n">
-        <v>0.62</v>
+        <v>0.24</v>
       </c>
       <c r="N30" s="17" t="n">
         <v>7</v>
@@ -2234,127 +2242,127 @@
         </is>
       </c>
       <c r="P30" s="22" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="15" t="n">
+      <c r="A31" s="23" t="n">
         <v>46113</v>
       </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>Freddy Peralta</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>NYM</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>Yusei Kikuchi</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D31" s="25" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="E31" s="26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F31" s="25" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G31" s="25" t="n">
+        <v>102</v>
+      </c>
+      <c r="H31" s="27" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="I31" s="27" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="J31" s="27" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="K31" s="28" t="n">
+        <v>4.364</v>
+      </c>
+      <c r="L31" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M31" s="28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N31" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="O31" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P31" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>Kevin Gausman</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G31" s="17" t="n">
+      <c r="G32" s="17" t="n">
         <v>116</v>
       </c>
-      <c r="H31" s="19" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="I31" s="19" t="n">
+      <c r="H32" s="19" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="I32" s="19" t="n">
         <v>0.463</v>
       </c>
-      <c r="J31" s="19" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="K31" s="20" t="n">
-        <v>6.789</v>
-      </c>
-      <c r="L31" s="18" t="n">
+      <c r="J32" s="19" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="K32" s="20" t="n">
+        <v>7.914</v>
+      </c>
+      <c r="L32" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="M31" s="20" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="N31" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="O31" s="21" t="inlineStr">
+      <c r="M32" s="20" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N32" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="O32" s="21" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P31" s="22" t="n">
+      <c r="P32" s="22" t="n">
         <v>1.16</v>
-      </c>
-    </row>
-    <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="23" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B32" s="24" t="inlineStr">
-        <is>
-          <t>Yusei Kikuchi</t>
-        </is>
-      </c>
-      <c r="C32" s="25" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="D32" s="25" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="E32" s="26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F32" s="25" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G32" s="25" t="n">
-        <v>102</v>
-      </c>
-      <c r="H32" s="27" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="I32" s="27" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="J32" s="27" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="K32" s="28" t="n">
-        <v>4.364</v>
-      </c>
-      <c r="L32" s="26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M32" s="28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N32" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="O32" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P32" s="30" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
@@ -2363,41 +2371,41 @@
       </c>
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>Kevin Gausman</t>
+          <t>Matthew Liberatore</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D33" s="17" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E33" s="18" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="F33" s="17" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>0.529</v>
+        <v>0.525</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>0.463</v>
+        <v>0.4587</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>0.066</v>
+        <v>0.0663</v>
       </c>
       <c r="K33" s="20" t="n">
-        <v>7.914</v>
+        <v>3.583</v>
       </c>
       <c r="L33" s="18" t="n">
         <v>0.5</v>
@@ -2406,7 +2414,7 @@
         <v>0.31</v>
       </c>
       <c r="N33" s="17" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O33" s="21" t="inlineStr">
         <is>
@@ -2414,7 +2422,7 @@
         </is>
       </c>
       <c r="P33" s="22" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
@@ -2423,17 +2431,17 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>Matthew Liberatore</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D34" s="17" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E34" s="18" t="n">
@@ -2441,32 +2449,32 @@
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>0.525</v>
+        <v>0.57</v>
       </c>
       <c r="I34" s="19" t="n">
-        <v>0.4587</v>
+        <v>0.5</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>0.0663</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K34" s="20" t="n">
-        <v>3.583</v>
+        <v>4.038</v>
       </c>
       <c r="L34" s="18" t="n">
         <v>0.5</v>
       </c>
       <c r="M34" s="20" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="N34" s="17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O34" s="21" t="inlineStr">
         <is>
@@ -2474,187 +2482,187 @@
         </is>
       </c>
       <c r="P34" s="22" t="n">
-        <v>1.18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="15" t="n">
+      <c r="A35" s="23" t="n">
         <v>46113</v>
       </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>Kyle Freeland</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="E35" s="18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>Shane Smith</t>
+        </is>
+      </c>
+      <c r="C35" s="25" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D35" s="25" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E35" s="26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F35" s="25" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G35" s="17" t="n">
+      <c r="G35" s="25" t="n">
         <v>100</v>
       </c>
-      <c r="H35" s="19" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="I35" s="19" t="n">
+      <c r="H35" s="27" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="I35" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="J35" s="19" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K35" s="20" t="n">
-        <v>4.038</v>
-      </c>
-      <c r="L35" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M35" s="20" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="N35" s="17" t="n">
+      <c r="J35" s="27" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="K35" s="28" t="n">
+        <v>5.393</v>
+      </c>
+      <c r="L35" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="28" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N35" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P35" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>George Kirby</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="n">
+        <v>-178</v>
+      </c>
+      <c r="H36" s="19" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="I36" s="19" t="n">
+        <v>0.6403</v>
+      </c>
+      <c r="J36" s="19" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="K36" s="20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L36" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N36" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="O35" s="21" t="inlineStr">
+      <c r="O36" s="21" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P35" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="23" t="n">
+      <c r="P36" s="22" t="n">
+        <v>0.5618</v>
+      </c>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="23" t="n">
         <v>46113</v>
       </c>
-      <c r="B36" s="24" t="inlineStr">
-        <is>
-          <t>Shane Smith</t>
-        </is>
-      </c>
-      <c r="C36" s="25" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="D36" s="25" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="E36" s="26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F36" s="25" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G36" s="25" t="n">
-        <v>100</v>
-      </c>
-      <c r="H36" s="27" t="n">
-        <v>0.576</v>
-      </c>
-      <c r="I36" s="27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J36" s="27" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="K36" s="28" t="n">
-        <v>5.393</v>
-      </c>
-      <c r="L36" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" s="28" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="N36" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" s="29" t="inlineStr">
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>Mike Burrows</t>
+        </is>
+      </c>
+      <c r="C37" s="25" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="D37" s="25" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="E37" s="26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F37" s="25" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G37" s="25" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H37" s="27" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="I37" s="27" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="J37" s="27" t="n">
+        <v>0.1033</v>
+      </c>
+      <c r="K37" s="28" t="n">
+        <v>4.943</v>
+      </c>
+      <c r="L37" s="26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M37" s="28" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N37" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="O37" s="29" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P36" s="30" t="n">
+      <c r="P37" s="30" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B37" s="16" t="inlineStr">
-        <is>
-          <t>George Kirby</t>
-        </is>
-      </c>
-      <c r="C37" s="17" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="E37" s="18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G37" s="17" t="n">
-        <v>-178</v>
-      </c>
-      <c r="H37" s="19" t="n">
-        <v>0.726</v>
-      </c>
-      <c r="I37" s="19" t="n">
-        <v>0.6403</v>
-      </c>
-      <c r="J37" s="19" t="n">
-        <v>0.0857</v>
-      </c>
-      <c r="K37" s="20" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L37" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M37" s="20" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N37" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="O37" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P37" s="22" t="n">
-        <v>0.5618</v>
       </c>
     </row>
     <row r="38" ht="17" customHeight="1">
@@ -2663,17 +2671,17 @@
       </c>
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>Mike Burrows</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="C38" s="25" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="D38" s="25" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E38" s="26" t="n">
@@ -2685,28 +2693,28 @@
         </is>
       </c>
       <c r="G38" s="25" t="n">
-        <v>-114</v>
+        <v>128</v>
       </c>
       <c r="H38" s="27" t="n">
-        <v>0.636</v>
+        <v>0.55</v>
       </c>
       <c r="I38" s="27" t="n">
-        <v>0.5327</v>
+        <v>0.4386</v>
       </c>
       <c r="J38" s="27" t="n">
-        <v>0.1033</v>
+        <v>0.1114</v>
       </c>
       <c r="K38" s="28" t="n">
-        <v>4.943</v>
+        <v>5.551</v>
       </c>
       <c r="L38" s="26" t="n">
         <v>1.5</v>
       </c>
       <c r="M38" s="28" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="N38" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O38" s="29" t="inlineStr">
         <is>
@@ -2723,17 +2731,17 @@
       </c>
       <c r="B39" s="24" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Nathan Eovaldi</t>
         </is>
       </c>
       <c r="C39" s="25" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="D39" s="25" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E39" s="26" t="n">
@@ -2741,32 +2749,32 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G39" s="25" t="n">
-        <v>128</v>
+        <v>-168</v>
       </c>
       <c r="H39" s="27" t="n">
-        <v>0.55</v>
+        <v>0.743</v>
       </c>
       <c r="I39" s="27" t="n">
-        <v>0.4386</v>
+        <v>0.6269</v>
       </c>
       <c r="J39" s="27" t="n">
-        <v>0.1114</v>
+        <v>0.1161</v>
       </c>
       <c r="K39" s="28" t="n">
-        <v>5.551</v>
+        <v>7.699</v>
       </c>
       <c r="L39" s="26" t="n">
         <v>1.5</v>
       </c>
       <c r="M39" s="28" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="N39" s="25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O39" s="29" t="inlineStr">
         <is>
@@ -2778,63 +2786,63 @@
       </c>
     </row>
     <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="23" t="n">
+      <c r="A40" s="15" t="n">
         <v>46113</v>
       </c>
-      <c r="B40" s="24" t="inlineStr">
-        <is>
-          <t>Nathan Eovaldi</t>
-        </is>
-      </c>
-      <c r="C40" s="25" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
-      <c r="D40" s="25" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="E40" s="26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F40" s="25" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F40" s="17" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G40" s="25" t="n">
-        <v>-168</v>
-      </c>
-      <c r="H40" s="27" t="n">
-        <v>0.743</v>
-      </c>
-      <c r="I40" s="27" t="n">
-        <v>0.6269</v>
-      </c>
-      <c r="J40" s="27" t="n">
-        <v>0.1161</v>
-      </c>
-      <c r="K40" s="28" t="n">
-        <v>7.699</v>
-      </c>
-      <c r="L40" s="26" t="n">
+      <c r="G40" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="H40" s="19" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="I40" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J40" s="19" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="K40" s="20" t="n">
+        <v>7.784</v>
+      </c>
+      <c r="L40" s="18" t="n">
         <v>1.5</v>
       </c>
-      <c r="M40" s="28" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="N40" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="O40" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P40" s="30" t="n">
-        <v>-1</v>
+      <c r="M40" s="20" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="N40" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="O40" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P40" s="22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
@@ -2843,50 +2851,50 @@
       </c>
       <c r="B41" s="16" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="D41" s="17" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E41" s="18" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="F41" s="17" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>-132</v>
+        <v>-144</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>0.696</v>
+        <v>0.735</v>
       </c>
       <c r="I41" s="19" t="n">
-        <v>0.569</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>0.127</v>
+        <v>0.1448</v>
       </c>
       <c r="K41" s="20" t="n">
-        <v>6.191</v>
+        <v>7.561</v>
       </c>
       <c r="L41" s="18" t="n">
         <v>1.5</v>
       </c>
       <c r="M41" s="20" t="n">
-        <v>0.74</v>
+        <v>0.88</v>
       </c>
       <c r="N41" s="17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O41" s="21" t="inlineStr">
         <is>
@@ -2894,127 +2902,127 @@
         </is>
       </c>
       <c r="P41" s="22" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.6944</v>
       </c>
     </row>
     <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="15" t="n">
+      <c r="A42" s="23" t="n">
         <v>46113</v>
       </c>
-      <c r="B42" s="16" t="inlineStr">
-        <is>
-          <t>Andrew Abbott</t>
-        </is>
-      </c>
-      <c r="C42" s="17" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="E42" s="18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F42" s="17" t="inlineStr">
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>Cade Cavalli</t>
+        </is>
+      </c>
+      <c r="C42" s="25" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="D42" s="25" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E42" s="26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F42" s="25" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G42" s="25" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H42" s="27" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="I42" s="27" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="J42" s="27" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="K42" s="28" t="n">
+        <v>5.697</v>
+      </c>
+      <c r="L42" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M42" s="28" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="N42" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O42" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P42" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>Tarik Skubal</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="E43" s="18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F43" s="17" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G42" s="17" t="n">
-        <v>-112</v>
-      </c>
-      <c r="H42" s="19" t="n">
-        <v>0.677</v>
-      </c>
-      <c r="I42" s="19" t="n">
-        <v>0.5283</v>
-      </c>
-      <c r="J42" s="19" t="n">
-        <v>0.1487</v>
-      </c>
-      <c r="K42" s="20" t="n">
-        <v>4.469</v>
-      </c>
-      <c r="L42" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M42" s="20" t="n">
+      <c r="G43" s="17" t="n">
+        <v>108</v>
+      </c>
+      <c r="H43" s="19" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="I43" s="19" t="n">
+        <v>0.4808</v>
+      </c>
+      <c r="J43" s="19" t="n">
+        <v>0.1632</v>
+      </c>
+      <c r="K43" s="20" t="n">
+        <v>5.865</v>
+      </c>
+      <c r="L43" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M43" s="20" t="n">
         <v>0.79</v>
       </c>
-      <c r="N42" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="O42" s="21" t="inlineStr">
+      <c r="N43" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="O43" s="21" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P42" s="22" t="n">
-        <v>0.8929</v>
-      </c>
-    </row>
-    <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="23" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B43" s="24" t="inlineStr">
-        <is>
-          <t>Cade Cavalli</t>
-        </is>
-      </c>
-      <c r="C43" s="25" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
-      <c r="D43" s="25" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="E43" s="26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F43" s="25" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G43" s="25" t="n">
-        <v>-102</v>
-      </c>
-      <c r="H43" s="27" t="n">
-        <v>0.668</v>
-      </c>
-      <c r="I43" s="27" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="J43" s="27" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="K43" s="28" t="n">
-        <v>5.697</v>
-      </c>
-      <c r="L43" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="M43" s="28" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="N43" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="O43" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P43" s="30" t="n">
-        <v>-1</v>
+      <c r="P43" s="22" t="n">
+        <v>1.08</v>
       </c>
     </row>
     <row r="44" ht="17" customHeight="1">
@@ -3023,50 +3031,50 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Adrian Houser</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D44" s="17" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E44" s="18" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>108</v>
+        <v>-125</v>
       </c>
       <c r="H44" s="19" t="n">
-        <v>0.644</v>
+        <v>0.724</v>
       </c>
       <c r="I44" s="19" t="n">
-        <v>0.4808</v>
+        <v>0.5556</v>
       </c>
       <c r="J44" s="19" t="n">
-        <v>0.1632</v>
+        <v>0.1684</v>
       </c>
       <c r="K44" s="20" t="n">
-        <v>5.865</v>
+        <v>5.063</v>
       </c>
       <c r="L44" s="18" t="n">
         <v>2</v>
       </c>
       <c r="M44" s="20" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="N44" s="17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O44" s="21" t="inlineStr">
         <is>
@@ -3074,127 +3082,127 @@
         </is>
       </c>
       <c r="P44" s="22" t="n">
-        <v>1.08</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="15" t="n">
+      <c r="A45" s="23" t="n">
         <v>46113</v>
       </c>
-      <c r="B45" s="16" t="inlineStr">
-        <is>
-          <t>Adrian Houser</t>
-        </is>
-      </c>
-      <c r="C45" s="17" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="D45" s="17" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E45" s="18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F45" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G45" s="17" t="n">
-        <v>-125</v>
-      </c>
-      <c r="H45" s="19" t="n">
-        <v>0.724</v>
-      </c>
-      <c r="I45" s="19" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="J45" s="19" t="n">
-        <v>0.1684</v>
-      </c>
-      <c r="K45" s="20" t="n">
-        <v>5.063</v>
-      </c>
-      <c r="L45" s="18" t="n">
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="C45" s="25" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="D45" s="25" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E45" s="26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F45" s="25" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G45" s="25" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H45" s="27" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="I45" s="27" t="n">
+        <v>0.5413</v>
+      </c>
+      <c r="J45" s="27" t="n">
+        <v>0.1907</v>
+      </c>
+      <c r="K45" s="28" t="n">
+        <v>3.414</v>
+      </c>
+      <c r="L45" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="M45" s="20" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="N45" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="O45" s="21" t="inlineStr">
+      <c r="M45" s="28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N45" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="O45" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P45" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>Zac Gallen</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G46" s="17" t="n">
+        <v>112</v>
+      </c>
+      <c r="H46" s="19" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="I46" s="19" t="n">
+        <v>0.4717</v>
+      </c>
+      <c r="J46" s="19" t="n">
+        <v>0.2353</v>
+      </c>
+      <c r="K46" s="20" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="L46" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M46" s="20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N46" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O46" s="21" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P45" s="22" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="23" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B46" s="24" t="inlineStr">
-        <is>
-          <t>Drew Rasmussen</t>
-        </is>
-      </c>
-      <c r="C46" s="25" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="D46" s="25" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="E46" s="26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F46" s="25" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G46" s="25" t="n">
-        <v>-118</v>
-      </c>
-      <c r="H46" s="27" t="n">
-        <v>0.732</v>
-      </c>
-      <c r="I46" s="27" t="n">
-        <v>0.5413</v>
-      </c>
-      <c r="J46" s="27" t="n">
-        <v>0.1907</v>
-      </c>
-      <c r="K46" s="28" t="n">
-        <v>3.414</v>
-      </c>
-      <c r="L46" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="M46" s="28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N46" s="25" t="n">
-        <v>8</v>
-      </c>
-      <c r="O46" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P46" s="30" t="n">
-        <v>-1</v>
+      <c r="P46" s="22" t="n">
+        <v>1.12</v>
       </c>
     </row>
     <row r="47" ht="17" customHeight="1">
@@ -3203,17 +3211,17 @@
       </c>
       <c r="B47" s="16" t="inlineStr">
         <is>
-          <t>Zac Gallen</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="D47" s="17" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E47" s="18" t="n">
@@ -3225,28 +3233,28 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>112</v>
+        <v>-112</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>0.707</v>
+        <v>0.677</v>
       </c>
       <c r="I47" s="19" t="n">
-        <v>0.4717</v>
+        <v>0.5283</v>
       </c>
       <c r="J47" s="19" t="n">
-        <v>0.2353</v>
+        <v>0.1487</v>
       </c>
       <c r="K47" s="20" t="n">
-        <v>4.34</v>
+        <v>4.469</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M47" s="20" t="n">
-        <v>1.11</v>
+        <v>0.79</v>
       </c>
       <c r="N47" s="17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O47" s="21" t="inlineStr">
         <is>
@@ -3254,67 +3262,67 @@
         </is>
       </c>
       <c r="P47" s="22" t="n">
-        <v>1.12</v>
+        <v>0.8929</v>
       </c>
     </row>
     <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B48" s="16" t="inlineStr">
-        <is>
-          <t>Cam Schlittler</t>
-        </is>
-      </c>
-      <c r="C48" s="17" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="D48" s="17" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="E48" s="18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F48" s="17" t="inlineStr">
+      <c r="A48" s="23" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t>Andre Pallante</t>
+        </is>
+      </c>
+      <c r="C48" s="25" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D48" s="25" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="E48" s="26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F48" s="25" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G48" s="17" t="n">
-        <v>-144</v>
-      </c>
-      <c r="H48" s="19" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="I48" s="19" t="n">
-        <v>0.5901999999999999</v>
-      </c>
-      <c r="J48" s="19" t="n">
-        <v>0.1448</v>
-      </c>
-      <c r="K48" s="20" t="n">
-        <v>7.561</v>
-      </c>
-      <c r="L48" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M48" s="20" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="N48" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="O48" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P48" s="22" t="n">
-        <v>0.6944</v>
+      <c r="G48" s="25" t="n">
+        <v>126</v>
+      </c>
+      <c r="H48" s="27" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="I48" s="27" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="J48" s="27" t="n">
+        <v>0.0805</v>
+      </c>
+      <c r="K48" s="28" t="n">
+        <v>3.876</v>
+      </c>
+      <c r="L48" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" s="28" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="N48" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O48" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P48" s="30" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="49" ht="17" customHeight="1">
@@ -3323,17 +3331,17 @@
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>Andre Pallante</t>
+          <t>Aaron Civale</t>
         </is>
       </c>
       <c r="C49" s="25" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>OAK</t>
         </is>
       </c>
       <c r="D49" s="25" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E49" s="26" t="n">
@@ -3345,25 +3353,25 @@
         </is>
       </c>
       <c r="G49" s="25" t="n">
-        <v>126</v>
+        <v>-146</v>
       </c>
       <c r="H49" s="27" t="n">
-        <v>0.523</v>
+        <v>0.666</v>
       </c>
       <c r="I49" s="27" t="n">
-        <v>0.4425</v>
+        <v>0.5935</v>
       </c>
       <c r="J49" s="27" t="n">
-        <v>0.0805</v>
+        <v>0.0725</v>
       </c>
       <c r="K49" s="28" t="n">
-        <v>3.876</v>
+        <v>4.714</v>
       </c>
       <c r="L49" s="26" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M49" s="28" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
       <c r="N49" s="25" t="n">
         <v>3</v>
@@ -3378,63 +3386,63 @@
       </c>
     </row>
     <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="23" t="n">
+      <c r="A50" s="15" t="n">
         <v>46112</v>
       </c>
-      <c r="B50" s="24" t="inlineStr">
-        <is>
-          <t>Aaron Civale</t>
-        </is>
-      </c>
-      <c r="C50" s="25" t="inlineStr">
-        <is>
-          <t>OAK</t>
-        </is>
-      </c>
-      <c r="D50" s="25" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="E50" s="26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F50" s="25" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G50" s="25" t="n">
-        <v>-146</v>
-      </c>
-      <c r="H50" s="27" t="n">
-        <v>0.666</v>
-      </c>
-      <c r="I50" s="27" t="n">
-        <v>0.5935</v>
-      </c>
-      <c r="J50" s="27" t="n">
-        <v>0.0725</v>
-      </c>
-      <c r="K50" s="28" t="n">
-        <v>4.714</v>
-      </c>
-      <c r="L50" s="26" t="n">
+      <c r="B50" s="16" t="inlineStr">
+        <is>
+          <t>Max Scherzer</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E50" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F50" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="n">
+        <v>-130</v>
+      </c>
+      <c r="H50" s="19" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="I50" s="19" t="n">
+        <v>0.5652</v>
+      </c>
+      <c r="J50" s="19" t="n">
+        <v>0.0868</v>
+      </c>
+      <c r="K50" s="20" t="n">
+        <v>4.757</v>
+      </c>
+      <c r="L50" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="M50" s="28" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="N50" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="O50" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P50" s="30" t="n">
-        <v>-1</v>
+      <c r="N50" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="O50" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P50" s="22" t="n">
+        <v>0.7692</v>
       </c>
     </row>
     <row r="51" ht="17" customHeight="1">
@@ -3443,47 +3451,47 @@
       </c>
       <c r="B51" s="16" t="inlineStr">
         <is>
-          <t>Max Scherzer</t>
+          <t>Erick Fedde</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="D51" s="17" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E51" s="18" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F51" s="17" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>-130</v>
+        <v>134</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>0.652</v>
+        <v>0.527</v>
       </c>
       <c r="I51" s="19" t="n">
-        <v>0.5652</v>
+        <v>0.4274</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>0.0868</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="K51" s="20" t="n">
-        <v>4.757</v>
+        <v>3.852</v>
       </c>
       <c r="L51" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M51" s="20" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="N51" s="17" t="n">
         <v>4</v>
@@ -3494,7 +3502,7 @@
         </is>
       </c>
       <c r="P51" s="22" t="n">
-        <v>0.7692</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="52" ht="17" customHeight="1">
@@ -3503,50 +3511,50 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>Erick Fedde</t>
+          <t>Jameson Taillon</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E52" s="18" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="H52" s="19" t="n">
-        <v>0.527</v>
+        <v>0.569</v>
       </c>
       <c r="I52" s="19" t="n">
-        <v>0.4274</v>
+        <v>0.463</v>
       </c>
       <c r="J52" s="19" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.106</v>
       </c>
       <c r="K52" s="20" t="n">
-        <v>3.852</v>
+        <v>4.313</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M52" s="20" t="n">
-        <v>0.44</v>
+        <v>0.49</v>
       </c>
       <c r="N52" s="17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O52" s="21" t="inlineStr">
         <is>
@@ -3554,7 +3562,7 @@
         </is>
       </c>
       <c r="P52" s="22" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="53" ht="17" customHeight="1">
@@ -3563,50 +3571,50 @@
       </c>
       <c r="B53" s="16" t="inlineStr">
         <is>
-          <t>Jameson Taillon</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D53" s="17" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E53" s="18" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F53" s="17" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>116</v>
+        <v>-108</v>
       </c>
       <c r="H53" s="19" t="n">
-        <v>0.569</v>
+        <v>0.655</v>
       </c>
       <c r="I53" s="19" t="n">
-        <v>0.463</v>
+        <v>0.5192</v>
       </c>
       <c r="J53" s="19" t="n">
-        <v>0.106</v>
+        <v>0.1358</v>
       </c>
       <c r="K53" s="20" t="n">
-        <v>4.313</v>
+        <v>4.719</v>
       </c>
       <c r="L53" s="18" t="n">
         <v>1.5</v>
       </c>
       <c r="M53" s="20" t="n">
-        <v>0.49</v>
+        <v>0.71</v>
       </c>
       <c r="N53" s="17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O53" s="21" t="inlineStr">
         <is>
@@ -3614,187 +3622,187 @@
         </is>
       </c>
       <c r="P53" s="22" t="n">
+        <v>0.9258999999999999</v>
+      </c>
+    </row>
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="23" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B54" s="24" t="inlineStr">
+        <is>
+          <t>José Soriano</t>
+        </is>
+      </c>
+      <c r="C54" s="25" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D54" s="25" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="E54" s="26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F54" s="25" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G54" s="25" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H54" s="27" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="I54" s="27" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="J54" s="27" t="n">
+        <v>0.1522</v>
+      </c>
+      <c r="K54" s="28" t="n">
+        <v>5.918</v>
+      </c>
+      <c r="L54" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M54" s="28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N54" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="O54" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P54" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="55" ht="17" customHeight="1">
+      <c r="A55" s="15" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B55" s="16" t="inlineStr">
+        <is>
+          <t>Edward Cabrera</t>
+        </is>
+      </c>
+      <c r="C55" s="17" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="D55" s="17" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E55" s="18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F55" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G55" s="17" t="n">
+        <v>116</v>
+      </c>
+      <c r="H55" s="19" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="I55" s="19" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J55" s="19" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="K55" s="20" t="n">
+        <v>5.286</v>
+      </c>
+      <c r="L55" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M55" s="20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N55" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O55" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P55" s="22" t="n">
         <v>1.16</v>
       </c>
     </row>
-    <row r="54" ht="17" customHeight="1">
-      <c r="A54" s="15" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B54" s="16" t="inlineStr">
-        <is>
-          <t>Ryan Feltner</t>
-        </is>
-      </c>
-      <c r="C54" s="17" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="D54" s="17" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="E54" s="18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F54" s="17" t="inlineStr">
+    <row r="56" ht="17" customHeight="1">
+      <c r="A56" s="23" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B56" s="24" t="inlineStr">
+        <is>
+          <t>Jacob Lopez</t>
+        </is>
+      </c>
+      <c r="C56" s="25" t="inlineStr">
+        <is>
+          <t>OAK</t>
+        </is>
+      </c>
+      <c r="D56" s="25" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E56" s="26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F56" s="25" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G54" s="17" t="n">
-        <v>-108</v>
-      </c>
-      <c r="H54" s="19" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="I54" s="19" t="n">
-        <v>0.5192</v>
-      </c>
-      <c r="J54" s="19" t="n">
-        <v>0.1358</v>
-      </c>
-      <c r="K54" s="20" t="n">
-        <v>4.719</v>
-      </c>
-      <c r="L54" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M54" s="20" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="N54" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="O54" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P54" s="22" t="n">
-        <v>0.9258999999999999</v>
-      </c>
-    </row>
-    <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="23" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B55" s="24" t="inlineStr">
-        <is>
-          <t>José Soriano</t>
-        </is>
-      </c>
-      <c r="C55" s="25" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="D55" s="25" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="E55" s="26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F55" s="25" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G55" s="25" t="n">
-        <v>-110</v>
-      </c>
-      <c r="H55" s="27" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="I55" s="27" t="n">
-        <v>0.5238</v>
-      </c>
-      <c r="J55" s="27" t="n">
-        <v>0.1522</v>
-      </c>
-      <c r="K55" s="28" t="n">
-        <v>5.918</v>
-      </c>
-      <c r="L55" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="M55" s="28" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N55" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="O55" s="29" t="inlineStr">
+      <c r="G56" s="25" t="n">
+        <v>100</v>
+      </c>
+      <c r="H56" s="27" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="I56" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J56" s="27" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="K56" s="28" t="n">
+        <v>6.418</v>
+      </c>
+      <c r="L56" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" s="28" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N56" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="29" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P55" s="30" t="n">
+      <c r="P56" s="30" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="56" ht="17" customHeight="1">
-      <c r="A56" s="15" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B56" s="16" t="inlineStr">
-        <is>
-          <t>Edward Cabrera</t>
-        </is>
-      </c>
-      <c r="C56" s="17" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="D56" s="17" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="E56" s="18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F56" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G56" s="17" t="n">
-        <v>116</v>
-      </c>
-      <c r="H56" s="19" t="n">
-        <v>0.6889999999999999</v>
-      </c>
-      <c r="I56" s="19" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J56" s="19" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="K56" s="20" t="n">
-        <v>5.286</v>
-      </c>
-      <c r="L56" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M56" s="20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N56" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="O56" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P56" s="22" t="n">
-        <v>1.16</v>
       </c>
     </row>
     <row r="57" ht="17" customHeight="1">
@@ -3803,21 +3811,21 @@
       </c>
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Simeon Woods Richardson</t>
         </is>
       </c>
       <c r="C57" s="25" t="inlineStr">
         <is>
-          <t>OAK</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D57" s="25" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E57" s="26" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F57" s="25" t="inlineStr">
         <is>
@@ -3825,28 +3833,28 @@
         </is>
       </c>
       <c r="G57" s="25" t="n">
-        <v>100</v>
+        <v>-112</v>
       </c>
       <c r="H57" s="27" t="n">
-        <v>0.586</v>
+        <v>0.783</v>
       </c>
       <c r="I57" s="27" t="n">
-        <v>0.5</v>
+        <v>0.5283</v>
       </c>
       <c r="J57" s="27" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.2547</v>
       </c>
       <c r="K57" s="28" t="n">
-        <v>6.418</v>
+        <v>5.562</v>
       </c>
       <c r="L57" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M57" s="28" t="n">
-        <v>0.43</v>
+        <v>1.35</v>
       </c>
       <c r="N57" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O57" s="29" t="inlineStr">
         <is>
@@ -3858,363 +3866,363 @@
       </c>
     </row>
     <row r="58" ht="17" customHeight="1">
-      <c r="A58" s="23" t="n">
+      <c r="A58" s="15" t="n">
         <v>46111</v>
       </c>
-      <c r="B58" s="24" t="inlineStr">
-        <is>
-          <t>Simeon Woods Richardson</t>
-        </is>
-      </c>
-      <c r="C58" s="25" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="D58" s="25" t="inlineStr">
+      <c r="B58" s="16" t="inlineStr">
+        <is>
+          <t>Jack Leiter</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="D58" s="17" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E58" s="18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F58" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G58" s="17" t="n">
+        <v>-144</v>
+      </c>
+      <c r="H58" s="19" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="I58" s="19" t="n">
+        <v>0.5901999999999999</v>
+      </c>
+      <c r="J58" s="19" t="n">
+        <v>0.0888</v>
+      </c>
+      <c r="K58" s="20" t="n">
+        <v>6.017</v>
+      </c>
+      <c r="L58" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" s="20" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N58" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="O58" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P58" s="22" t="n">
+        <v>0.6944</v>
+      </c>
+    </row>
+    <row r="59" ht="17" customHeight="1">
+      <c r="A59" s="23" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B59" s="24" t="inlineStr">
+        <is>
+          <t>Kyle Harrison</t>
+        </is>
+      </c>
+      <c r="C59" s="25" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D59" s="25" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E59" s="26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F59" s="25" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G59" s="25" t="n">
+        <v>114</v>
+      </c>
+      <c r="H59" s="27" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="I59" s="27" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="J59" s="27" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="K59" s="28" t="n">
+        <v>4.628</v>
+      </c>
+      <c r="L59" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M59" s="28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N59" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="O59" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P59" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="60" ht="17" customHeight="1">
+      <c r="A60" s="23" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B60" s="24" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="C60" s="25" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="D60" s="25" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E60" s="26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F60" s="25" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G60" s="25" t="n">
+        <v>-174</v>
+      </c>
+      <c r="H60" s="27" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="I60" s="27" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="J60" s="27" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="K60" s="28" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="L60" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M60" s="28" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="N60" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O60" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P60" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="61" ht="17" customHeight="1">
+      <c r="A61" s="15" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B61" s="16" t="inlineStr">
+        <is>
+          <t>Davis Martin</t>
+        </is>
+      </c>
+      <c r="C61" s="17" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D61" s="17" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E61" s="18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F61" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G61" s="17" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H61" s="19" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="I61" s="19" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="J61" s="19" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="K61" s="20" t="n">
+        <v>4.252</v>
+      </c>
+      <c r="L61" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M61" s="20" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="N61" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="O61" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P61" s="22" t="n">
+        <v>0.8772</v>
+      </c>
+    </row>
+    <row r="62" ht="17" customHeight="1">
+      <c r="A62" s="15" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B62" s="16" t="inlineStr">
+        <is>
+          <t>Michael Wacha</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
         <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="E58" s="26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F58" s="25" t="inlineStr">
+      <c r="D62" s="17" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E62" s="18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F62" s="17" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G58" s="25" t="n">
-        <v>-112</v>
-      </c>
-      <c r="H58" s="27" t="n">
-        <v>0.783</v>
-      </c>
-      <c r="I58" s="27" t="n">
-        <v>0.5283</v>
-      </c>
-      <c r="J58" s="27" t="n">
-        <v>0.2547</v>
-      </c>
-      <c r="K58" s="28" t="n">
-        <v>5.562</v>
-      </c>
-      <c r="L58" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="M58" s="28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="N58" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="O58" s="29" t="inlineStr">
+      <c r="G62" s="17" t="n">
+        <v>140</v>
+      </c>
+      <c r="H62" s="19" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="I62" s="19" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="J62" s="19" t="n">
+        <v>0.0593</v>
+      </c>
+      <c r="K62" s="20" t="n">
+        <v>4.645</v>
+      </c>
+      <c r="L62" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M62" s="20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N62" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="O62" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P62" s="22" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="63" ht="17" customHeight="1">
+      <c r="A63" s="23" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B63" s="24" t="inlineStr">
+        <is>
+          <t>Will Warren</t>
+        </is>
+      </c>
+      <c r="C63" s="25" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="D63" s="25" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="E63" s="26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F63" s="25" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G63" s="25" t="n">
+        <v>110</v>
+      </c>
+      <c r="H63" s="27" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="I63" s="27" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="J63" s="27" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="K63" s="28" t="n">
+        <v>5.339</v>
+      </c>
+      <c r="L63" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M63" s="28" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N63" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O63" s="29" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P58" s="30" t="n">
+      <c r="P63" s="30" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="59" ht="17" customHeight="1">
-      <c r="A59" s="15" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B59" s="16" t="inlineStr">
-        <is>
-          <t>Jack Leiter</t>
-        </is>
-      </c>
-      <c r="C59" s="17" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
-      <c r="D59" s="17" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="E59" s="18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F59" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G59" s="17" t="n">
-        <v>-144</v>
-      </c>
-      <c r="H59" s="19" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="I59" s="19" t="n">
-        <v>0.5901999999999999</v>
-      </c>
-      <c r="J59" s="19" t="n">
-        <v>0.0888</v>
-      </c>
-      <c r="K59" s="20" t="n">
-        <v>6.017</v>
-      </c>
-      <c r="L59" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M59" s="20" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="N59" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="O59" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P59" s="22" t="n">
-        <v>0.6944</v>
-      </c>
-    </row>
-    <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="15" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B60" s="16" t="inlineStr">
-        <is>
-          <t>Davis Martin</t>
-        </is>
-      </c>
-      <c r="C60" s="17" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="D60" s="17" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="E60" s="18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F60" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G60" s="17" t="n">
-        <v>-114</v>
-      </c>
-      <c r="H60" s="19" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="I60" s="19" t="n">
-        <v>0.5327</v>
-      </c>
-      <c r="J60" s="19" t="n">
-        <v>0.0513</v>
-      </c>
-      <c r="K60" s="20" t="n">
-        <v>4.252</v>
-      </c>
-      <c r="L60" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M60" s="20" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="N60" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="O60" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P60" s="22" t="n">
-        <v>0.8772</v>
-      </c>
-    </row>
-    <row r="61" ht="17" customHeight="1">
-      <c r="A61" s="23" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B61" s="24" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="C61" s="25" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="D61" s="25" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="E61" s="26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F61" s="25" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G61" s="25" t="n">
-        <v>-174</v>
-      </c>
-      <c r="H61" s="27" t="n">
-        <v>0.6889999999999999</v>
-      </c>
-      <c r="I61" s="27" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="J61" s="27" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="K61" s="28" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="L61" s="26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M61" s="28" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="N61" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="O61" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P61" s="30" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="62" ht="17" customHeight="1">
-      <c r="A62" s="23" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B62" s="24" t="inlineStr">
-        <is>
-          <t>Kyle Harrison</t>
-        </is>
-      </c>
-      <c r="C62" s="25" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D62" s="25" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="E62" s="26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F62" s="25" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G62" s="25" t="n">
-        <v>114</v>
-      </c>
-      <c r="H62" s="27" t="n">
-        <v>0.521</v>
-      </c>
-      <c r="I62" s="27" t="n">
-        <v>0.4673</v>
-      </c>
-      <c r="J62" s="27" t="n">
-        <v>0.0537</v>
-      </c>
-      <c r="K62" s="28" t="n">
-        <v>4.628</v>
-      </c>
-      <c r="L62" s="26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M62" s="28" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N62" s="25" t="n">
-        <v>8</v>
-      </c>
-      <c r="O62" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P62" s="30" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="63" ht="17" customHeight="1">
-      <c r="A63" s="15" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B63" s="16" t="inlineStr">
-        <is>
-          <t>Michael Wacha</t>
-        </is>
-      </c>
-      <c r="C63" s="17" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="D63" s="17" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="E63" s="18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F63" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G63" s="17" t="n">
-        <v>140</v>
-      </c>
-      <c r="H63" s="19" t="n">
-        <v>0.476</v>
-      </c>
-      <c r="I63" s="19" t="n">
-        <v>0.4167</v>
-      </c>
-      <c r="J63" s="19" t="n">
-        <v>0.0593</v>
-      </c>
-      <c r="K63" s="20" t="n">
-        <v>4.645</v>
-      </c>
-      <c r="L63" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M63" s="20" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N63" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="O63" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P63" s="22" t="n">
-        <v>1.4</v>
       </c>
     </row>
     <row r="64" ht="17" customHeight="1">
@@ -4223,21 +4231,21 @@
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>Will Warren</t>
+          <t>Jeffrey Springs</t>
         </is>
       </c>
       <c r="C64" s="25" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>OAK</t>
         </is>
       </c>
       <c r="D64" s="25" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E64" s="26" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F64" s="25" t="inlineStr">
         <is>
@@ -4245,28 +4253,28 @@
         </is>
       </c>
       <c r="G64" s="25" t="n">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H64" s="27" t="n">
-        <v>0.573</v>
+        <v>0.599</v>
       </c>
       <c r="I64" s="27" t="n">
-        <v>0.4762</v>
+        <v>0.495</v>
       </c>
       <c r="J64" s="27" t="n">
-        <v>0.0968</v>
+        <v>0.104</v>
       </c>
       <c r="K64" s="28" t="n">
-        <v>5.339</v>
+        <v>4.389</v>
       </c>
       <c r="L64" s="26" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M64" s="28" t="n">
-        <v>0.46</v>
+        <v>0.51</v>
       </c>
       <c r="N64" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O64" s="29" t="inlineStr">
         <is>
@@ -4283,50 +4291,50 @@
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>Jeffrey Springs</t>
+          <t>Eury Pérez</t>
         </is>
       </c>
       <c r="C65" s="25" t="inlineStr">
         <is>
-          <t>OAK</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D65" s="25" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E65" s="26" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="F65" s="25" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G65" s="25" t="n">
-        <v>102</v>
+        <v>-154</v>
       </c>
       <c r="H65" s="27" t="n">
-        <v>0.599</v>
+        <v>0.713</v>
       </c>
       <c r="I65" s="27" t="n">
-        <v>0.495</v>
+        <v>0.6063</v>
       </c>
       <c r="J65" s="27" t="n">
-        <v>0.104</v>
+        <v>0.1067</v>
       </c>
       <c r="K65" s="28" t="n">
-        <v>4.389</v>
+        <v>5.311</v>
       </c>
       <c r="L65" s="26" t="n">
         <v>1.5</v>
       </c>
       <c r="M65" s="28" t="n">
-        <v>0.51</v>
+        <v>0.68</v>
       </c>
       <c r="N65" s="25" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O65" s="29" t="inlineStr">
         <is>
@@ -4339,54 +4347,54 @@
     </row>
     <row r="66" ht="17" customHeight="1">
       <c r="A66" s="23" t="n">
-        <v>46109</v>
+        <v>46108</v>
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>Eury Pérez</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="C66" s="25" t="inlineStr">
         <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D66" s="25" t="inlineStr">
+        <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="D66" s="25" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
       <c r="E66" s="26" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="F66" s="25" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G66" s="25" t="n">
-        <v>-154</v>
+        <v>-158</v>
       </c>
       <c r="H66" s="27" t="n">
-        <v>0.713</v>
+        <v>0.677</v>
       </c>
       <c r="I66" s="27" t="n">
-        <v>0.6063</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J66" s="27" t="n">
-        <v>0.1067</v>
+        <v>0.0646</v>
       </c>
       <c r="K66" s="28" t="n">
-        <v>5.311</v>
+        <v>4.869</v>
       </c>
       <c r="L66" s="26" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M66" s="28" t="n">
-        <v>0.68</v>
+        <v>0.42</v>
       </c>
       <c r="N66" s="25" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O66" s="29" t="inlineStr">
         <is>
@@ -4398,63 +4406,63 @@
       </c>
     </row>
     <row r="67" ht="17" customHeight="1">
-      <c r="A67" s="23" t="n">
+      <c r="A67" s="15" t="n">
         <v>46108</v>
       </c>
-      <c r="B67" s="24" t="inlineStr">
-        <is>
-          <t>Kyle Freeland</t>
-        </is>
-      </c>
-      <c r="C67" s="25" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="D67" s="25" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="E67" s="26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F67" s="25" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G67" s="25" t="n">
-        <v>-158</v>
-      </c>
-      <c r="H67" s="27" t="n">
-        <v>0.677</v>
-      </c>
-      <c r="I67" s="27" t="n">
-        <v>0.6124000000000001</v>
-      </c>
-      <c r="J67" s="27" t="n">
-        <v>0.0646</v>
-      </c>
-      <c r="K67" s="28" t="n">
-        <v>4.869</v>
-      </c>
-      <c r="L67" s="26" t="n">
+      <c r="B67" s="16" t="inlineStr">
+        <is>
+          <t>Robbie Ray</t>
+        </is>
+      </c>
+      <c r="C67" s="17" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="D67" s="17" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E67" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F67" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G67" s="17" t="n">
+        <v>116</v>
+      </c>
+      <c r="H67" s="19" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="I67" s="19" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J67" s="19" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="K67" s="20" t="n">
+        <v>5.578</v>
+      </c>
+      <c r="L67" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="M67" s="28" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="N67" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="O67" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P67" s="30" t="n">
-        <v>-1</v>
+      <c r="M67" s="20" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N67" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="O67" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P67" s="22" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="68" ht="17" customHeight="1">
@@ -4463,118 +4471,118 @@
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>Robbie Ray</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="D68" s="17" t="inlineStr">
+        <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="D68" s="17" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="E68" s="18" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F68" s="17" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>116</v>
+        <v>-128</v>
       </c>
       <c r="H68" s="19" t="n">
-        <v>0.532</v>
+        <v>0.659</v>
       </c>
       <c r="I68" s="19" t="n">
-        <v>0.463</v>
+        <v>0.5614</v>
       </c>
       <c r="J68" s="19" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="K68" s="20" t="n">
-        <v>5.578</v>
+        <v>5.818</v>
       </c>
       <c r="L68" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M68" s="20" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="N68" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="O68" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P68" s="22" t="n">
+        <v>0.7812</v>
+      </c>
+    </row>
+    <row r="69" ht="17" customHeight="1">
+      <c r="A69" s="23" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B69" s="24" t="inlineStr">
+        <is>
+          <t>Shane Smith</t>
+        </is>
+      </c>
+      <c r="C69" s="25" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D69" s="25" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E69" s="26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F69" s="25" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G69" s="25" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H69" s="27" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="I69" s="27" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="J69" s="27" t="n">
+        <v>0.0743</v>
+      </c>
+      <c r="K69" s="28" t="n">
+        <v>5.338</v>
+      </c>
+      <c r="L69" s="26" t="n">
         <v>0.5</v>
       </c>
-      <c r="M68" s="20" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="N68" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="O68" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P68" s="22" t="n">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="69" ht="17" customHeight="1">
-      <c r="A69" s="15" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B69" s="16" t="inlineStr">
-        <is>
-          <t>Cam Schlittler</t>
-        </is>
-      </c>
-      <c r="C69" s="17" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="D69" s="17" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="E69" s="18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F69" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G69" s="17" t="n">
-        <v>-128</v>
-      </c>
-      <c r="H69" s="19" t="n">
-        <v>0.659</v>
-      </c>
-      <c r="I69" s="19" t="n">
-        <v>0.5614</v>
-      </c>
-      <c r="J69" s="19" t="n">
-        <v>0.09760000000000001</v>
-      </c>
-      <c r="K69" s="20" t="n">
-        <v>5.818</v>
-      </c>
-      <c r="L69" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M69" s="20" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="N69" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="O69" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P69" s="22" t="n">
-        <v>0.7812</v>
+      <c r="M69" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N69" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="O69" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P69" s="30" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="70" ht="17" customHeight="1">
@@ -4583,50 +4591,50 @@
       </c>
       <c r="B70" s="24" t="inlineStr">
         <is>
-          <t>Shane Smith</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="C70" s="25" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D70" s="25" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E70" s="26" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="F70" s="25" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G70" s="25" t="n">
-        <v>-114</v>
+        <v>114</v>
       </c>
       <c r="H70" s="27" t="n">
-        <v>0.607</v>
+        <v>0.587</v>
       </c>
       <c r="I70" s="27" t="n">
-        <v>0.5327</v>
+        <v>0.4673</v>
       </c>
       <c r="J70" s="27" t="n">
-        <v>0.0743</v>
+        <v>0.1197</v>
       </c>
       <c r="K70" s="28" t="n">
-        <v>5.338</v>
+        <v>6.417</v>
       </c>
       <c r="L70" s="26" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M70" s="28" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N70" s="25" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O70" s="29" t="inlineStr">
         <is>
@@ -4638,63 +4646,63 @@
       </c>
     </row>
     <row r="71" ht="17" customHeight="1">
-      <c r="A71" s="23" t="n">
+      <c r="A71" s="15" t="n">
         <v>46107</v>
       </c>
-      <c r="B71" s="24" t="inlineStr">
-        <is>
-          <t>Hunter Brown</t>
-        </is>
-      </c>
-      <c r="C71" s="25" t="inlineStr">
+      <c r="B71" s="16" t="inlineStr">
+        <is>
+          <t>José Soriano</t>
+        </is>
+      </c>
+      <c r="C71" s="17" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D71" s="17" t="inlineStr">
         <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="D71" s="25" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="E71" s="26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F71" s="25" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G71" s="25" t="n">
-        <v>114</v>
-      </c>
-      <c r="H71" s="27" t="n">
-        <v>0.587</v>
-      </c>
-      <c r="I71" s="27" t="n">
-        <v>0.4673</v>
-      </c>
-      <c r="J71" s="27" t="n">
-        <v>0.1197</v>
-      </c>
-      <c r="K71" s="28" t="n">
-        <v>6.417</v>
-      </c>
-      <c r="L71" s="26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M71" s="28" t="n">
+      <c r="E71" s="18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F71" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G71" s="17" t="n">
+        <v>108</v>
+      </c>
+      <c r="H71" s="19" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="N71" s="25" t="n">
-        <v>9</v>
-      </c>
-      <c r="O71" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P71" s="30" t="n">
-        <v>-1</v>
+      <c r="I71" s="19" t="n">
+        <v>0.4808</v>
+      </c>
+      <c r="J71" s="19" t="n">
+        <v>0.07920000000000001</v>
+      </c>
+      <c r="K71" s="20" t="n">
+        <v>5.163</v>
+      </c>
+      <c r="L71" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M71" s="20" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N71" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="O71" s="21" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P71" s="22" t="n">
+        <v>1.08</v>
       </c>
     </row>
     <row r="72" ht="17" customHeight="1">
@@ -4703,50 +4711,50 @@
       </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>José Soriano</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D72" s="17" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E72" s="18" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="F72" s="17" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>108</v>
+        <v>-172</v>
       </c>
       <c r="H72" s="19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.767</v>
       </c>
       <c r="I72" s="19" t="n">
-        <v>0.4808</v>
+        <v>0.6324</v>
       </c>
       <c r="J72" s="19" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.1346</v>
       </c>
       <c r="K72" s="20" t="n">
-        <v>5.163</v>
+        <v>5.68</v>
       </c>
       <c r="L72" s="18" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M72" s="20" t="n">
-        <v>0.38</v>
+        <v>0.92</v>
       </c>
       <c r="N72" s="17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O72" s="21" t="inlineStr">
         <is>
@@ -4754,127 +4762,127 @@
         </is>
       </c>
       <c r="P72" s="22" t="n">
-        <v>1.08</v>
+        <v>0.5814</v>
       </c>
     </row>
     <row r="73" ht="17" customHeight="1">
-      <c r="A73" s="15" t="n">
+      <c r="A73" s="23" t="n">
         <v>46107</v>
       </c>
-      <c r="B73" s="16" t="inlineStr">
-        <is>
-          <t>Tarik Skubal</t>
-        </is>
-      </c>
-      <c r="C73" s="17" t="inlineStr">
+      <c r="B73" s="24" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="C73" s="25" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D73" s="25" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E73" s="26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F73" s="25" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G73" s="25" t="n">
+        <v>124</v>
+      </c>
+      <c r="H73" s="27" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I73" s="27" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="J73" s="27" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="K73" s="28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L73" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M73" s="28" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N73" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="O73" s="29" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P73" s="30" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="74" ht="17" customHeight="1">
+      <c r="A74" s="15" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B74" s="16" t="inlineStr">
+        <is>
+          <t>Nick Pivetta</t>
+        </is>
+      </c>
+      <c r="C74" s="17" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D74" s="17" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="D73" s="17" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E73" s="18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F73" s="17" t="inlineStr">
+      <c r="E74" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F74" s="17" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G73" s="17" t="n">
-        <v>-172</v>
-      </c>
-      <c r="H73" s="19" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="I73" s="19" t="n">
-        <v>0.6324</v>
-      </c>
-      <c r="J73" s="19" t="n">
-        <v>0.1346</v>
-      </c>
-      <c r="K73" s="20" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="L73" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M73" s="20" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="N73" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="O73" s="21" t="inlineStr">
+      <c r="G74" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="H74" s="19" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I74" s="19" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="J74" s="19" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="K74" s="20" t="n">
+        <v>5.548</v>
+      </c>
+      <c r="L74" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M74" s="20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N74" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="O74" s="21" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P73" s="22" t="n">
-        <v>0.5814</v>
-      </c>
-    </row>
-    <row r="74" ht="17" customHeight="1">
-      <c r="A74" s="23" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B74" s="24" t="inlineStr">
-        <is>
-          <t>Jacob Misiorowski</t>
-        </is>
-      </c>
-      <c r="C74" s="25" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D74" s="25" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="E74" s="26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F74" s="25" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G74" s="25" t="n">
-        <v>124</v>
-      </c>
-      <c r="H74" s="27" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I74" s="27" t="n">
-        <v>0.4464</v>
-      </c>
-      <c r="J74" s="27" t="n">
-        <v>0.0736</v>
-      </c>
-      <c r="K74" s="28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L74" s="26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M74" s="28" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="N74" s="25" t="n">
-        <v>11</v>
-      </c>
-      <c r="O74" s="29" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P74" s="30" t="n">
-        <v>-1</v>
+      <c r="P74" s="22" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="75" ht="17" customHeight="1">
@@ -4883,21 +4891,21 @@
       </c>
       <c r="B75" s="16" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="C75" s="17" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="D75" s="17" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E75" s="18" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F75" s="17" t="inlineStr">
         <is>
@@ -4905,25 +4913,25 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H75" s="19" t="n">
-        <v>0.54</v>
+        <v>0.509</v>
       </c>
       <c r="I75" s="19" t="n">
-        <v>0.4762</v>
+        <v>0.4545</v>
       </c>
       <c r="J75" s="19" t="n">
-        <v>0.0638</v>
+        <v>0.0545</v>
       </c>
       <c r="K75" s="20" t="n">
-        <v>5.548</v>
+        <v>4.814</v>
       </c>
       <c r="L75" s="18" t="n">
         <v>0.5</v>
       </c>
       <c r="M75" s="20" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="N75" s="17" t="n">
         <v>4</v>
@@ -4934,126 +4942,66 @@
         </is>
       </c>
       <c r="P75" s="22" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="76" ht="17" customHeight="1">
-      <c r="A76" s="15" t="n">
+      <c r="A76" s="23" t="n">
         <v>46107</v>
       </c>
-      <c r="B76" s="16" t="inlineStr">
-        <is>
-          <t>Andrew Abbott</t>
-        </is>
-      </c>
-      <c r="C76" s="17" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="D76" s="17" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="E76" s="18" t="n">
+      <c r="B76" s="24" t="inlineStr">
+        <is>
+          <t>Matthew Boyd</t>
+        </is>
+      </c>
+      <c r="C76" s="25" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="D76" s="25" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="E76" s="26" t="n">
         <v>4.5</v>
       </c>
-      <c r="F76" s="17" t="inlineStr">
+      <c r="F76" s="25" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G76" s="17" t="n">
-        <v>120</v>
-      </c>
-      <c r="H76" s="19" t="n">
-        <v>0.509</v>
-      </c>
-      <c r="I76" s="19" t="n">
-        <v>0.4545</v>
-      </c>
-      <c r="J76" s="19" t="n">
-        <v>0.0545</v>
-      </c>
-      <c r="K76" s="20" t="n">
-        <v>4.814</v>
-      </c>
-      <c r="L76" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M76" s="20" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N76" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="O76" s="21" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P76" s="22" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="77" ht="17" customHeight="1">
-      <c r="A77" s="23" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B77" s="24" t="inlineStr">
-        <is>
-          <t>Matthew Boyd</t>
-        </is>
-      </c>
-      <c r="C77" s="25" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="D77" s="25" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
-      <c r="E77" s="26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F77" s="25" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G77" s="25" t="n">
+      <c r="G76" s="25" t="n">
         <v>132</v>
       </c>
-      <c r="H77" s="27" t="n">
+      <c r="H76" s="27" t="n">
         <v>0.59</v>
       </c>
-      <c r="I77" s="27" t="n">
+      <c r="I76" s="27" t="n">
         <v>0.431</v>
       </c>
-      <c r="J77" s="27" t="n">
+      <c r="J76" s="27" t="n">
         <v>0.159</v>
       </c>
-      <c r="K77" s="28" t="n">
+      <c r="K76" s="28" t="n">
         <v>4.258</v>
       </c>
-      <c r="L77" s="26" t="n">
+      <c r="L76" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="M77" s="28" t="n">
+      <c r="M76" s="28" t="n">
         <v>0.7</v>
       </c>
-      <c r="N77" s="25" t="n">
+      <c r="N76" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="O77" s="29" t="inlineStr">
+      <c r="O76" s="29" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P77" s="30" t="n">
+      <c r="P76" s="30" t="n">
         <v>-1</v>
       </c>
     </row>

--- a/bet_log.xlsx
+++ b/bet_log.xlsx
@@ -880,16 +880,16 @@
         </is>
       </c>
       <c r="G7" s="8" t="n">
-        <v>-160</v>
+        <v>-162</v>
       </c>
       <c r="H7" s="10" t="n">
         <v>0.708</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.6183</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.0926</v>
+        <v>0.0897</v>
       </c>
       <c r="K7" s="11" t="n">
         <v>6.298</v>
@@ -898,7 +898,7 @@
         <v>1</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="N7" s="8" t="inlineStr"/>
       <c r="O7" s="12" t="inlineStr"/>

--- a/bet_log.xlsx
+++ b/bet_log.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P95"/>
+  <dimension ref="A1:P98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -687,7 +687,7 @@
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>81</v>
@@ -806,47 +806,47 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Eury Pérez</t>
+          <t>Michael McGreevy</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G6" s="8" t="n">
-        <v>-132</v>
+        <v>-114</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>0.635</v>
+        <v>0.586</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.569</v>
+        <v>0.5327</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.066</v>
+        <v>0.0533</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>5.853</v>
+        <v>4.248</v>
       </c>
       <c r="L6" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>0.38</v>
+        <v>0.29</v>
       </c>
       <c r="N6" s="8" t="inlineStr"/>
       <c r="O6" s="12" t="inlineStr"/>
@@ -858,47 +858,47 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Joey Cantillo</t>
+          <t>Michael Lorenzen</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G7" s="8" t="n">
-        <v>-154</v>
+        <v>-130</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.679</v>
+        <v>0.63</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>0.6063</v>
+        <v>0.5652</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.0727</v>
+        <v>0.0648</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>4.665</v>
+        <v>4.329</v>
       </c>
       <c r="L7" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.46</v>
+        <v>0.37</v>
       </c>
       <c r="N7" s="8" t="inlineStr"/>
       <c r="O7" s="12" t="inlineStr"/>
@@ -910,21 +910,21 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Eury Pérez</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
@@ -932,25 +932,25 @@
         </is>
       </c>
       <c r="G8" s="8" t="n">
-        <v>-125</v>
+        <v>-132</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>0.634</v>
+        <v>0.635</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>0.5556</v>
+        <v>0.569</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.0784</v>
+        <v>0.066</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>4.033</v>
+        <v>5.853</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="N8" s="8" t="inlineStr"/>
       <c r="O8" s="12" t="inlineStr"/>
@@ -984,25 +984,25 @@
         </is>
       </c>
       <c r="G9" s="8" t="n">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="H9" s="10" t="n">
         <v>0.546</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>0.4386</v>
+        <v>0.4762</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.1074</v>
+        <v>0.0698</v>
       </c>
       <c r="K9" s="11" t="n">
         <v>6.326</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.48</v>
+        <v>0.33</v>
       </c>
       <c r="N9" s="8" t="inlineStr"/>
       <c r="O9" s="12" t="inlineStr"/>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Michael King</t>
+          <t>Joey Cantillo</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
@@ -1036,25 +1036,25 @@
         </is>
       </c>
       <c r="G10" s="8" t="n">
-        <v>-102</v>
+        <v>-154</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>0.63</v>
+        <v>0.679</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>0.505</v>
+        <v>0.6063</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.125</v>
+        <v>0.0727</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>4.885</v>
+        <v>4.665</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
       <c r="N10" s="8" t="inlineStr"/>
       <c r="O10" s="12" t="inlineStr"/>
@@ -1066,47 +1066,47 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Grant Holmes</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G11" s="8" t="n">
-        <v>-138</v>
+        <v>124</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.712</v>
+        <v>0.521</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>0.5798</v>
+        <v>0.4464</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.1322</v>
+        <v>0.0746</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>5.341</v>
+        <v>4.922</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.79</v>
+        <v>0.34</v>
       </c>
       <c r="N11" s="8" t="inlineStr"/>
       <c r="O11" s="12" t="inlineStr"/>
@@ -1118,21 +1118,21 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="G12" s="8" t="n">
-        <v>110</v>
+        <v>-125</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>0.649</v>
+        <v>0.634</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>0.4762</v>
+        <v>0.5556</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.1728</v>
+        <v>0.0784</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>4.876</v>
+        <v>4.033</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.82</v>
+        <v>0.44</v>
       </c>
       <c r="N12" s="8" t="inlineStr"/>
       <c r="O12" s="12" t="inlineStr"/>
@@ -1166,25 +1166,25 @@
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Michael King</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
@@ -1192,328 +1192,304 @@
         </is>
       </c>
       <c r="G13" s="8" t="n">
-        <v>-104</v>
+        <v>-102</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.599</v>
+        <v>0.63</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>0.5098</v>
+        <v>0.505</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.0892</v>
+        <v>0.125</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>4.186</v>
+        <v>4.885</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.45</v>
+        <v>0.63</v>
       </c>
       <c r="N13" s="8" t="inlineStr"/>
       <c r="O13" s="12" t="inlineStr"/>
       <c r="P13" s="13" t="inlineStr"/>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="14" t="n">
+      <c r="A14" s="6" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Sean Burke</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>0.1728</v>
+      </c>
+      <c r="K14" s="11" t="n">
+        <v>4.876</v>
+      </c>
+      <c r="L14" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" s="11" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="N14" s="8" t="inlineStr"/>
+      <c r="O14" s="12" t="inlineStr"/>
+      <c r="P14" s="13" t="inlineStr"/>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="6" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Colin Rea</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>114</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>0.2067</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>4.888</v>
+      </c>
+      <c r="L15" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" s="11" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="N15" s="8" t="inlineStr"/>
+      <c r="O15" s="12" t="inlineStr"/>
+      <c r="P15" s="13" t="inlineStr"/>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="6" t="n">
         <v>46119</v>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>-104</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>0.5098</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>0.0892</v>
+      </c>
+      <c r="K16" s="11" t="n">
+        <v>4.186</v>
+      </c>
+      <c r="L16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="11" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N16" s="8" t="inlineStr"/>
+      <c r="O16" s="12" t="inlineStr"/>
+      <c r="P16" s="13" t="inlineStr"/>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="14" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>Paul Skenes</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E17" s="17" t="n">
         <v>6.5</v>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G14" s="16" t="n">
+      <c r="G17" s="16" t="n">
         <v>-110</v>
       </c>
-      <c r="H14" s="18" t="n">
+      <c r="H17" s="18" t="n">
         <v>0.701</v>
       </c>
-      <c r="I14" s="18" t="n">
+      <c r="I17" s="18" t="n">
         <v>0.5238</v>
       </c>
-      <c r="J14" s="18" t="n">
+      <c r="J17" s="18" t="n">
         <v>0.1772</v>
       </c>
-      <c r="K14" s="19" t="n">
+      <c r="K17" s="19" t="n">
         <v>5.249</v>
       </c>
-      <c r="L14" s="17" t="n">
+      <c r="L17" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="M14" s="19" t="n">
+      <c r="M17" s="19" t="n">
         <v>0.93</v>
       </c>
-      <c r="N14" s="16" t="n">
+      <c r="N17" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="O14" s="20" t="inlineStr">
+      <c r="O17" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P14" s="21" t="n">
+      <c r="P17" s="21" t="n">
         <v>0.9091</v>
       </c>
     </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="14" t="n">
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="14" t="n">
         <v>46119</v>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>Noah Cameron</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E15" s="17" t="n">
+      <c r="E18" s="17" t="n">
         <v>4.5</v>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G15" s="16" t="n">
+      <c r="G18" s="16" t="n">
         <v>-114</v>
       </c>
-      <c r="H15" s="18" t="n">
+      <c r="H18" s="18" t="n">
         <v>0.644</v>
       </c>
-      <c r="I15" s="18" t="n">
+      <c r="I18" s="18" t="n">
         <v>0.5327</v>
       </c>
-      <c r="J15" s="18" t="n">
+      <c r="J18" s="18" t="n">
         <v>0.1113</v>
       </c>
-      <c r="K15" s="19" t="n">
+      <c r="K18" s="19" t="n">
         <v>5.746</v>
       </c>
-      <c r="L15" s="17" t="n">
+      <c r="L18" s="17" t="n">
         <v>1.5</v>
       </c>
-      <c r="M15" s="19" t="n">
+      <c r="M18" s="19" t="n">
         <v>0.6</v>
       </c>
-      <c r="N15" s="16" t="n">
+      <c r="N18" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="O15" s="20" t="inlineStr">
+      <c r="O18" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P15" s="21" t="n">
+      <c r="P18" s="21" t="n">
         <v>0.8772</v>
-      </c>
-    </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="14" t="n">
-        <v>46119</v>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>Kevin Gausman</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="n">
-        <v>154</v>
-      </c>
-      <c r="H16" s="18" t="n">
-        <v>0.501</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>0.3937</v>
-      </c>
-      <c r="J16" s="18" t="n">
-        <v>0.1073</v>
-      </c>
-      <c r="K16" s="19" t="n">
-        <v>5.736</v>
-      </c>
-      <c r="L16" s="17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M16" s="19" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="N16" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="O16" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P16" s="21" t="n">
-        <v>1.54</v>
-      </c>
-    </row>
-    <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="22" t="n">
-        <v>46119</v>
-      </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>Nick Pivetta</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F17" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G17" s="24" t="n">
-        <v>-125</v>
-      </c>
-      <c r="H17" s="26" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="I17" s="26" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="J17" s="26" t="n">
-        <v>0.0914</v>
-      </c>
-      <c r="K17" s="27" t="n">
-        <v>5.709</v>
-      </c>
-      <c r="L17" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" s="27" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="N17" s="24" t="n">
-        <v>8</v>
-      </c>
-      <c r="O17" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P17" s="29" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="22" t="n">
-        <v>46119</v>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>Jacob Misiorowski</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F18" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G18" s="24" t="n">
-        <v>116</v>
-      </c>
-      <c r="H18" s="26" t="n">
-        <v>0.539</v>
-      </c>
-      <c r="I18" s="26" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J18" s="26" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="K18" s="27" t="n">
-        <v>6.457</v>
-      </c>
-      <c r="L18" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" s="27" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="N18" s="24" t="n">
-        <v>10</v>
-      </c>
-      <c r="O18" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P18" s="29" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1">
@@ -1522,21 +1498,21 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>Cade Cavalli</t>
+          <t>Kevin Gausman</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E19" s="17" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -1544,28 +1520,28 @@
         </is>
       </c>
       <c r="G19" s="16" t="n">
-        <v>-112</v>
+        <v>154</v>
       </c>
       <c r="H19" s="18" t="n">
-        <v>0.602</v>
+        <v>0.501</v>
       </c>
       <c r="I19" s="18" t="n">
-        <v>0.5283</v>
+        <v>0.3937</v>
       </c>
       <c r="J19" s="18" t="n">
-        <v>0.0737</v>
+        <v>0.1073</v>
       </c>
       <c r="K19" s="19" t="n">
-        <v>4.074</v>
+        <v>5.736</v>
       </c>
       <c r="L19" s="17" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="N19" s="16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O19" s="20" t="inlineStr">
         <is>
@@ -1573,7 +1549,7 @@
         </is>
       </c>
       <c r="P19" s="21" t="n">
-        <v>0.8929</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
@@ -1582,50 +1558,50 @@
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>Javier Assad</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E20" s="25" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G20" s="24" t="n">
-        <v>-108</v>
+        <v>-125</v>
       </c>
       <c r="H20" s="26" t="n">
-        <v>0.582</v>
+        <v>0.647</v>
       </c>
       <c r="I20" s="26" t="n">
-        <v>0.5192</v>
+        <v>0.5556</v>
       </c>
       <c r="J20" s="26" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.0914</v>
       </c>
       <c r="K20" s="27" t="n">
-        <v>4.073</v>
+        <v>5.709</v>
       </c>
       <c r="L20" s="25" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>0.33</v>
+        <v>0.51</v>
       </c>
       <c r="N20" s="24" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O20" s="28" t="inlineStr">
         <is>
@@ -1642,21 +1618,21 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Garrett Crochet</t>
+          <t>Cade Cavalli</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -1664,28 +1640,28 @@
         </is>
       </c>
       <c r="G21" s="16" t="n">
-        <v>-118</v>
+        <v>-112</v>
       </c>
       <c r="H21" s="18" t="n">
-        <v>0.594</v>
+        <v>0.602</v>
       </c>
       <c r="I21" s="18" t="n">
-        <v>0.5413</v>
+        <v>0.5283</v>
       </c>
       <c r="J21" s="18" t="n">
-        <v>0.0527</v>
+        <v>0.0737</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>7.154</v>
+        <v>4.074</v>
       </c>
       <c r="L21" s="17" t="n">
         <v>0.5</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>0.29</v>
+        <v>0.39</v>
       </c>
       <c r="N21" s="16" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O21" s="20" t="inlineStr">
         <is>
@@ -1693,59 +1669,59 @@
         </is>
       </c>
       <c r="P21" s="21" t="n">
-        <v>0.8475</v>
+        <v>0.8929</v>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="22" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>Andre Pallante</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D22" s="24" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E22" s="25" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="F22" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G22" s="24" t="n">
-        <v>-112</v>
+        <v>116</v>
       </c>
       <c r="H22" s="26" t="n">
-        <v>0.614</v>
+        <v>0.539</v>
       </c>
       <c r="I22" s="26" t="n">
-        <v>0.5283</v>
+        <v>0.463</v>
       </c>
       <c r="J22" s="26" t="n">
-        <v>0.0857</v>
+        <v>0.076</v>
       </c>
       <c r="K22" s="27" t="n">
-        <v>4.355</v>
+        <v>6.457</v>
       </c>
       <c r="L22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="M22" s="27" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="N22" s="24" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O22" s="28" t="inlineStr">
         <is>
@@ -1758,25 +1734,25 @@
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="22" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>Casey Mize</t>
+          <t>Javier Assad</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E23" s="25" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
@@ -1784,28 +1760,28 @@
         </is>
       </c>
       <c r="G23" s="24" t="n">
-        <v>-162</v>
+        <v>-108</v>
       </c>
       <c r="H23" s="26" t="n">
-        <v>0.708</v>
+        <v>0.582</v>
       </c>
       <c r="I23" s="26" t="n">
-        <v>0.6183</v>
+        <v>0.5192</v>
       </c>
       <c r="J23" s="26" t="n">
-        <v>0.0897</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="K23" s="27" t="n">
-        <v>6.298</v>
+        <v>4.073</v>
       </c>
       <c r="L23" s="25" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M23" s="27" t="n">
-        <v>0.59</v>
+        <v>0.33</v>
       </c>
       <c r="N23" s="24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O23" s="28" t="inlineStr">
         <is>
@@ -1817,137 +1793,137 @@
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="22" t="n">
+      <c r="A24" s="14" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Garrett Crochet</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G24" s="16" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H24" s="18" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="I24" s="18" t="n">
+        <v>0.5413</v>
+      </c>
+      <c r="J24" s="18" t="n">
+        <v>0.0527</v>
+      </c>
+      <c r="K24" s="19" t="n">
+        <v>7.154</v>
+      </c>
+      <c r="L24" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M24" s="19" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N24" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O24" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P24" s="21" t="n">
+        <v>0.8475</v>
+      </c>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="22" t="n">
         <v>46118</v>
       </c>
-      <c r="B24" s="23" t="inlineStr">
-        <is>
-          <t>Joe Ryan</t>
-        </is>
-      </c>
-      <c r="C24" s="24" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="D24" s="24" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="E24" s="25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F24" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G24" s="24" t="n">
-        <v>-132</v>
-      </c>
-      <c r="H24" s="26" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="I24" s="26" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="J24" s="26" t="n">
-        <v>0.151</v>
-      </c>
-      <c r="K24" s="27" t="n">
-        <v>5.221</v>
-      </c>
-      <c r="L24" s="25" t="n">
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>Andre Pallante</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="E25" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H25" s="26" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="I25" s="26" t="n">
+        <v>0.5283</v>
+      </c>
+      <c r="J25" s="26" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="K25" s="27" t="n">
+        <v>4.355</v>
+      </c>
+      <c r="L25" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N25" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="M24" s="27" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="N24" s="24" t="n">
-        <v>7</v>
-      </c>
-      <c r="O24" s="28" t="inlineStr">
+      <c r="O25" s="28" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P24" s="29" t="n">
+      <c r="P25" s="29" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="14" t="n">
-        <v>46117</v>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>Luis Castillo</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="n">
-        <v>128</v>
-      </c>
-      <c r="H25" s="18" t="n">
-        <v>0.518</v>
-      </c>
-      <c r="I25" s="18" t="n">
-        <v>0.4386</v>
-      </c>
-      <c r="J25" s="18" t="n">
-        <v>0.0794</v>
-      </c>
-      <c r="K25" s="19" t="n">
-        <v>5.702</v>
-      </c>
-      <c r="L25" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" s="19" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="N25" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="O25" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P25" s="21" t="n">
-        <v>1.28</v>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="22" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Casey Mize</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
@@ -1964,25 +1940,25 @@
         </is>
       </c>
       <c r="G26" s="24" t="n">
-        <v>120</v>
+        <v>-162</v>
       </c>
       <c r="H26" s="26" t="n">
-        <v>0.575</v>
+        <v>0.708</v>
       </c>
       <c r="I26" s="26" t="n">
-        <v>0.4545</v>
+        <v>0.6183</v>
       </c>
       <c r="J26" s="26" t="n">
-        <v>0.1205</v>
+        <v>0.0897</v>
       </c>
       <c r="K26" s="27" t="n">
-        <v>5.165</v>
+        <v>6.298</v>
       </c>
       <c r="L26" s="25" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>0.55</v>
+        <v>0.59</v>
       </c>
       <c r="N26" s="24" t="n">
         <v>4</v>
@@ -1998,54 +1974,54 @@
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="22" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>Eric Lauer</t>
+          <t>Joe Ryan</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E27" s="25" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G27" s="24" t="n">
-        <v>100</v>
+        <v>-132</v>
       </c>
       <c r="H27" s="26" t="n">
-        <v>0.588</v>
+        <v>0.72</v>
       </c>
       <c r="I27" s="26" t="n">
-        <v>0.5</v>
+        <v>0.569</v>
       </c>
       <c r="J27" s="26" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.151</v>
       </c>
       <c r="K27" s="27" t="n">
-        <v>5.457</v>
+        <v>5.221</v>
       </c>
       <c r="L27" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M27" s="27" t="n">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="N27" s="24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O27" s="28" t="inlineStr">
         <is>
@@ -2062,47 +2038,47 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Taijuan Walker</t>
+          <t>Luis Castillo</t>
         </is>
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E28" s="17" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="F28" s="16" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G28" s="16" t="n">
-        <v>-106</v>
+        <v>128</v>
       </c>
       <c r="H28" s="18" t="n">
-        <v>0.6</v>
+        <v>0.518</v>
       </c>
       <c r="I28" s="18" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.4386</v>
       </c>
       <c r="J28" s="18" t="n">
-        <v>0.0854</v>
+        <v>0.0794</v>
       </c>
       <c r="K28" s="19" t="n">
-        <v>4.331</v>
+        <v>5.702</v>
       </c>
       <c r="L28" s="17" t="n">
         <v>1</v>
       </c>
       <c r="M28" s="19" t="n">
-        <v>0.44</v>
+        <v>0.35</v>
       </c>
       <c r="N28" s="16" t="n">
         <v>4</v>
@@ -2113,7 +2089,7 @@
         </is>
       </c>
       <c r="P28" s="21" t="n">
-        <v>0.9434</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="29" ht="17" customHeight="1">
@@ -2122,50 +2098,50 @@
       </c>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>Jack Leiter</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="D29" s="24" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E29" s="25" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="F29" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G29" s="24" t="n">
-        <v>-146</v>
+        <v>120</v>
       </c>
       <c r="H29" s="26" t="n">
-        <v>0.659</v>
+        <v>0.575</v>
       </c>
       <c r="I29" s="26" t="n">
-        <v>0.5935</v>
+        <v>0.4545</v>
       </c>
       <c r="J29" s="26" t="n">
-        <v>0.0655</v>
+        <v>0.1205</v>
       </c>
       <c r="K29" s="27" t="n">
-        <v>5.601</v>
+        <v>5.165</v>
       </c>
       <c r="L29" s="25" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M29" s="27" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="N29" s="24" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O29" s="28" t="inlineStr">
         <is>
@@ -2182,17 +2158,17 @@
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>Simeon Woods Richardson</t>
+          <t>Eric Lauer</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D30" s="24" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E30" s="25" t="n">
@@ -2204,28 +2180,28 @@
         </is>
       </c>
       <c r="G30" s="24" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="H30" s="26" t="n">
-        <v>0.547</v>
+        <v>0.588</v>
       </c>
       <c r="I30" s="26" t="n">
-        <v>0.4854</v>
+        <v>0.5</v>
       </c>
       <c r="J30" s="26" t="n">
-        <v>0.0616</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="K30" s="27" t="n">
-        <v>5.027</v>
+        <v>5.457</v>
       </c>
       <c r="L30" s="25" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M30" s="27" t="n">
-        <v>0.3</v>
+        <v>0.44</v>
       </c>
       <c r="N30" s="24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O30" s="28" t="inlineStr">
         <is>
@@ -2237,115 +2213,115 @@
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="22" t="n">
+      <c r="A31" s="14" t="n">
         <v>46117</v>
       </c>
-      <c r="B31" s="23" t="inlineStr">
-        <is>
-          <t>Keider Montero</t>
-        </is>
-      </c>
-      <c r="C31" s="24" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="D31" s="24" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="E31" s="25" t="n">
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>Taijuan Walker</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="n">
         <v>3.5</v>
       </c>
-      <c r="F31" s="24" t="inlineStr">
+      <c r="F31" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G31" s="24" t="n">
-        <v>108</v>
-      </c>
-      <c r="H31" s="26" t="n">
-        <v>0.546</v>
-      </c>
-      <c r="I31" s="26" t="n">
-        <v>0.4808</v>
-      </c>
-      <c r="J31" s="26" t="n">
-        <v>0.06519999999999999</v>
-      </c>
-      <c r="K31" s="27" t="n">
-        <v>3.968</v>
-      </c>
-      <c r="L31" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M31" s="27" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="N31" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="O31" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P31" s="29" t="n">
-        <v>-1</v>
+      <c r="G31" s="16" t="n">
+        <v>-106</v>
+      </c>
+      <c r="H31" s="18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I31" s="18" t="n">
+        <v>0.5145999999999999</v>
+      </c>
+      <c r="J31" s="18" t="n">
+        <v>0.0854</v>
+      </c>
+      <c r="K31" s="19" t="n">
+        <v>4.331</v>
+      </c>
+      <c r="L31" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="19" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="N31" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O31" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P31" s="21" t="n">
+        <v>0.9434</v>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="22" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>Jack Flaherty</t>
+          <t>Simeon Woods Richardson</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E32" s="25" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F32" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G32" s="24" t="n">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="H32" s="26" t="n">
-        <v>0.653</v>
+        <v>0.547</v>
       </c>
       <c r="I32" s="26" t="n">
-        <v>0.463</v>
+        <v>0.4854</v>
       </c>
       <c r="J32" s="26" t="n">
-        <v>0.19</v>
+        <v>0.0616</v>
       </c>
       <c r="K32" s="27" t="n">
-        <v>4.756</v>
+        <v>5.027</v>
       </c>
       <c r="L32" s="25" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="M32" s="27" t="n">
-        <v>0.88</v>
+        <v>0.3</v>
       </c>
       <c r="N32" s="24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O32" s="28" t="inlineStr">
         <is>
@@ -2358,54 +2334,54 @@
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="22" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="B33" s="23" t="inlineStr">
         <is>
-          <t>Chad Patrick</t>
+          <t>Jack Leiter</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="D33" s="24" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E33" s="25" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="F33" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G33" s="24" t="n">
-        <v>-154</v>
+        <v>-146</v>
       </c>
       <c r="H33" s="26" t="n">
-        <v>0.678</v>
+        <v>0.659</v>
       </c>
       <c r="I33" s="26" t="n">
-        <v>0.6063</v>
+        <v>0.5935</v>
       </c>
       <c r="J33" s="26" t="n">
-        <v>0.0717</v>
+        <v>0.0655</v>
       </c>
       <c r="K33" s="27" t="n">
-        <v>4.705</v>
+        <v>5.601</v>
       </c>
       <c r="L33" s="25" t="n">
         <v>0.5</v>
       </c>
       <c r="M33" s="27" t="n">
-        <v>0.46</v>
+        <v>0.4</v>
       </c>
       <c r="N33" s="24" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O33" s="28" t="inlineStr">
         <is>
@@ -2418,21 +2394,21 @@
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="22" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="B34" s="23" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Keider Montero</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E34" s="25" t="n">
@@ -2444,25 +2420,25 @@
         </is>
       </c>
       <c r="G34" s="24" t="n">
-        <v>-130</v>
+        <v>108</v>
       </c>
       <c r="H34" s="26" t="n">
-        <v>0.678</v>
+        <v>0.546</v>
       </c>
       <c r="I34" s="26" t="n">
-        <v>0.5652</v>
+        <v>0.4808</v>
       </c>
       <c r="J34" s="26" t="n">
-        <v>0.1128</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="K34" s="27" t="n">
-        <v>4.813</v>
+        <v>3.968</v>
       </c>
       <c r="L34" s="25" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M34" s="27" t="n">
-        <v>0.65</v>
+        <v>0.31</v>
       </c>
       <c r="N34" s="24" t="n">
         <v>3</v>
@@ -2477,63 +2453,63 @@
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="22" t="n">
+      <c r="A35" s="14" t="n">
         <v>46116</v>
       </c>
-      <c r="B35" s="23" t="inlineStr">
-        <is>
-          <t>Carmen Mlodzinski</t>
-        </is>
-      </c>
-      <c r="C35" s="24" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="D35" s="24" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="E35" s="25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F35" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G35" s="24" t="n">
-        <v>-108</v>
-      </c>
-      <c r="H35" s="26" t="n">
-        <v>0.666</v>
-      </c>
-      <c r="I35" s="26" t="n">
-        <v>0.5192</v>
-      </c>
-      <c r="J35" s="26" t="n">
-        <v>0.1468</v>
-      </c>
-      <c r="K35" s="27" t="n">
-        <v>3.828</v>
-      </c>
-      <c r="L35" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M35" s="27" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="N35" s="24" t="n">
-        <v>5</v>
-      </c>
-      <c r="O35" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P35" s="29" t="n">
-        <v>-1</v>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>Bryce Elder</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G35" s="16" t="n">
+        <v>-132</v>
+      </c>
+      <c r="H35" s="18" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="I35" s="18" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="J35" s="18" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="K35" s="19" t="n">
+        <v>5.551</v>
+      </c>
+      <c r="L35" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M35" s="19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N35" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="O35" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P35" s="21" t="n">
+        <v>0.7576000000000001</v>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
@@ -2542,21 +2518,21 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>Bryce Elder</t>
+          <t>Steven Matz</t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E36" s="17" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F36" s="16" t="inlineStr">
         <is>
@@ -2564,25 +2540,25 @@
         </is>
       </c>
       <c r="G36" s="16" t="n">
-        <v>-132</v>
+        <v>116</v>
       </c>
       <c r="H36" s="18" t="n">
-        <v>0.753</v>
+        <v>0.651</v>
       </c>
       <c r="I36" s="18" t="n">
-        <v>0.569</v>
+        <v>0.463</v>
       </c>
       <c r="J36" s="18" t="n">
-        <v>0.184</v>
+        <v>0.188</v>
       </c>
       <c r="K36" s="19" t="n">
-        <v>5.551</v>
+        <v>5.743</v>
       </c>
       <c r="L36" s="17" t="n">
         <v>2</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>1.07</v>
+        <v>0.88</v>
       </c>
       <c r="N36" s="16" t="n">
         <v>8</v>
@@ -2593,7 +2569,7 @@
         </is>
       </c>
       <c r="P36" s="21" t="n">
-        <v>0.7576000000000001</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
@@ -2657,146 +2633,146 @@
       </c>
     </row>
     <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="14" t="n">
+      <c r="A38" s="22" t="n">
         <v>46116</v>
       </c>
-      <c r="B38" s="15" t="inlineStr">
-        <is>
-          <t>Steven Matz</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="D38" s="16" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="E38" s="17" t="n">
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>Jack Flaherty</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="E38" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="n">
+        <v>116</v>
+      </c>
+      <c r="H38" s="26" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="I38" s="26" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J38" s="26" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K38" s="27" t="n">
+        <v>4.756</v>
+      </c>
+      <c r="L38" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M38" s="27" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N38" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="O38" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P38" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="22" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>Carmen Mlodzinski</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E39" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F38" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G38" s="16" t="n">
-        <v>116</v>
-      </c>
-      <c r="H38" s="18" t="n">
-        <v>0.651</v>
-      </c>
-      <c r="I38" s="18" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J38" s="18" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="K38" s="19" t="n">
-        <v>5.743</v>
-      </c>
-      <c r="L38" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M38" s="19" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="N38" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="O38" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P38" s="21" t="n">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="14" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B39" s="15" t="inlineStr">
-        <is>
-          <t>Michael King</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="D39" s="16" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="E39" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F39" s="16" t="inlineStr">
+      <c r="F39" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G39" s="16" t="n">
-        <v>102</v>
-      </c>
-      <c r="H39" s="18" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="I39" s="18" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="J39" s="18" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="K39" s="19" t="n">
-        <v>5.081</v>
-      </c>
-      <c r="L39" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M39" s="19" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="N39" s="16" t="n">
+      <c r="G39" s="24" t="n">
+        <v>-108</v>
+      </c>
+      <c r="H39" s="26" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="I39" s="26" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="J39" s="26" t="n">
+        <v>0.1468</v>
+      </c>
+      <c r="K39" s="27" t="n">
+        <v>3.828</v>
+      </c>
+      <c r="L39" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M39" s="27" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="N39" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="O39" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P39" s="21" t="n">
-        <v>1.02</v>
+      <c r="O39" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P39" s="29" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="22" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="B40" s="23" t="inlineStr">
         <is>
-          <t>Emmet Sheehan</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="D40" s="24" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E40" s="25" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F40" s="24" t="inlineStr">
         <is>
@@ -2804,28 +2780,28 @@
         </is>
       </c>
       <c r="G40" s="24" t="n">
-        <v>-128</v>
+        <v>-130</v>
       </c>
       <c r="H40" s="26" t="n">
-        <v>0.68</v>
+        <v>0.678</v>
       </c>
       <c r="I40" s="26" t="n">
-        <v>0.5614</v>
+        <v>0.5652</v>
       </c>
       <c r="J40" s="26" t="n">
-        <v>0.1186</v>
+        <v>0.1128</v>
       </c>
       <c r="K40" s="27" t="n">
-        <v>6.988</v>
+        <v>4.813</v>
       </c>
       <c r="L40" s="25" t="n">
         <v>1.5</v>
       </c>
       <c r="M40" s="27" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="N40" s="24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O40" s="28" t="inlineStr">
         <is>
@@ -2838,21 +2814,21 @@
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="22" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>Cade Horton</t>
+          <t>Chad Patrick</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D41" s="24" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E41" s="25" t="n">
@@ -2864,28 +2840,28 @@
         </is>
       </c>
       <c r="G41" s="24" t="n">
-        <v>-136</v>
+        <v>-154</v>
       </c>
       <c r="H41" s="26" t="n">
-        <v>0.676</v>
+        <v>0.678</v>
       </c>
       <c r="I41" s="26" t="n">
-        <v>0.5763</v>
+        <v>0.6063</v>
       </c>
       <c r="J41" s="26" t="n">
-        <v>0.0997</v>
+        <v>0.0717</v>
       </c>
       <c r="K41" s="27" t="n">
-        <v>4.806</v>
+        <v>4.705</v>
       </c>
       <c r="L41" s="25" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M41" s="27" t="n">
-        <v>0.59</v>
+        <v>0.46</v>
       </c>
       <c r="N41" s="24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O41" s="28" t="inlineStr">
         <is>
@@ -2897,56 +2873,64 @@
       </c>
     </row>
     <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="6" t="n">
+      <c r="A42" s="14" t="n">
         <v>46115</v>
       </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Chad Patrick</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="n">
-        <v>-138</v>
-      </c>
-      <c r="H42" s="10" t="n">
-        <v>0.672</v>
-      </c>
-      <c r="I42" s="10" t="n">
-        <v>0.5798</v>
-      </c>
-      <c r="J42" s="10" t="n">
-        <v>0.0922</v>
-      </c>
-      <c r="K42" s="11" t="n">
-        <v>4.705</v>
-      </c>
-      <c r="L42" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M42" s="11" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="N42" s="8" t="inlineStr"/>
-      <c r="O42" s="12" t="inlineStr"/>
-      <c r="P42" s="13" t="inlineStr"/>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>Mitch Keller</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G42" s="16" t="n">
+        <v>122</v>
+      </c>
+      <c r="H42" s="18" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="I42" s="18" t="n">
+        <v>0.4505</v>
+      </c>
+      <c r="J42" s="18" t="n">
+        <v>0.0545</v>
+      </c>
+      <c r="K42" s="19" t="n">
+        <v>4.723</v>
+      </c>
+      <c r="L42" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M42" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N42" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O42" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P42" s="21" t="n">
+        <v>1.22</v>
+      </c>
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="14" t="n">
@@ -2954,21 +2938,21 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>Framber Valdez</t>
         </is>
       </c>
       <c r="C43" s="16" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
@@ -2976,28 +2960,28 @@
         </is>
       </c>
       <c r="G43" s="16" t="n">
-        <v>122</v>
+        <v>-112</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>0.505</v>
+        <v>0.591</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>0.4505</v>
+        <v>0.5283</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>0.0545</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="K43" s="19" t="n">
-        <v>4.723</v>
+        <v>5.166</v>
       </c>
       <c r="L43" s="17" t="n">
         <v>0.5</v>
       </c>
       <c r="M43" s="19" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="N43" s="16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O43" s="20" t="inlineStr">
         <is>
@@ -3005,7 +2989,7 @@
         </is>
       </c>
       <c r="P43" s="21" t="n">
-        <v>1.22</v>
+        <v>0.8929</v>
       </c>
     </row>
     <row r="44" ht="17" customHeight="1">
@@ -3074,17 +3058,17 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>Framber Valdez</t>
+          <t>Michael King</t>
         </is>
       </c>
       <c r="C45" s="16" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E45" s="17" t="n">
@@ -3096,25 +3080,25 @@
         </is>
       </c>
       <c r="G45" s="16" t="n">
-        <v>-112</v>
+        <v>102</v>
       </c>
       <c r="H45" s="18" t="n">
-        <v>0.591</v>
+        <v>0.584</v>
       </c>
       <c r="I45" s="18" t="n">
-        <v>0.5283</v>
+        <v>0.495</v>
       </c>
       <c r="J45" s="18" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.089</v>
       </c>
       <c r="K45" s="19" t="n">
-        <v>5.166</v>
+        <v>5.081</v>
       </c>
       <c r="L45" s="17" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M45" s="19" t="n">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="N45" s="16" t="n">
         <v>5</v>
@@ -3125,90 +3109,82 @@
         </is>
       </c>
       <c r="P45" s="21" t="n">
-        <v>0.8929</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="22" t="n">
-        <v>46114</v>
-      </c>
-      <c r="B46" s="23" t="inlineStr">
-        <is>
-          <t>Cole Ragans</t>
-        </is>
-      </c>
-      <c r="C46" s="24" t="inlineStr">
+      <c r="A46" s="6" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Chad Patrick</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="D46" s="24" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="E46" s="25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F46" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G46" s="24" t="n">
-        <v>-152</v>
-      </c>
-      <c r="H46" s="26" t="n">
-        <v>0.738</v>
-      </c>
-      <c r="I46" s="26" t="n">
-        <v>0.6032</v>
-      </c>
-      <c r="J46" s="26" t="n">
-        <v>0.1348</v>
-      </c>
-      <c r="K46" s="27" t="n">
-        <v>5.951</v>
-      </c>
-      <c r="L46" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M46" s="27" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="N46" s="24" t="n">
-        <v>8</v>
-      </c>
-      <c r="O46" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P46" s="29" t="n">
-        <v>-1</v>
-      </c>
+      <c r="E46" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>-138</v>
+      </c>
+      <c r="H46" s="10" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="I46" s="10" t="n">
+        <v>0.5798</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>0.0922</v>
+      </c>
+      <c r="K46" s="11" t="n">
+        <v>4.705</v>
+      </c>
+      <c r="L46" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" s="11" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N46" s="8" t="inlineStr"/>
+      <c r="O46" s="12" t="inlineStr"/>
+      <c r="P46" s="13" t="inlineStr"/>
     </row>
     <row r="47" ht="17" customHeight="1">
       <c r="A47" s="22" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B47" s="23" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Cade Horton</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="D47" s="24" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E47" s="25" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F47" s="24" t="inlineStr">
         <is>
@@ -3216,28 +3192,28 @@
         </is>
       </c>
       <c r="G47" s="24" t="n">
-        <v>118</v>
+        <v>-136</v>
       </c>
       <c r="H47" s="26" t="n">
-        <v>0.573</v>
+        <v>0.676</v>
       </c>
       <c r="I47" s="26" t="n">
-        <v>0.4587</v>
+        <v>0.5763</v>
       </c>
       <c r="J47" s="26" t="n">
-        <v>0.1143</v>
+        <v>0.0997</v>
       </c>
       <c r="K47" s="27" t="n">
-        <v>5.159</v>
+        <v>4.806</v>
       </c>
       <c r="L47" s="25" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M47" s="27" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="N47" s="24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O47" s="28" t="inlineStr">
         <is>
@@ -3250,54 +3226,54 @@
     </row>
     <row r="48" ht="17" customHeight="1">
       <c r="A48" s="22" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="B48" s="23" t="inlineStr">
         <is>
-          <t>Yusei Kikuchi</t>
+          <t>Emmet Sheehan</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="D48" s="24" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E48" s="25" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F48" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G48" s="24" t="n">
-        <v>102</v>
+        <v>-128</v>
       </c>
       <c r="H48" s="26" t="n">
-        <v>0.556</v>
+        <v>0.68</v>
       </c>
       <c r="I48" s="26" t="n">
-        <v>0.495</v>
+        <v>0.5614</v>
       </c>
       <c r="J48" s="26" t="n">
-        <v>0.061</v>
+        <v>0.1186</v>
       </c>
       <c r="K48" s="27" t="n">
-        <v>4.364</v>
+        <v>6.988</v>
       </c>
       <c r="L48" s="25" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M48" s="27" t="n">
-        <v>0.3</v>
+        <v>0.68</v>
       </c>
       <c r="N48" s="24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O48" s="28" t="inlineStr">
         <is>
@@ -3309,123 +3285,123 @@
       </c>
     </row>
     <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="14" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>Freddy Peralta</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="inlineStr">
-        <is>
-          <t>NYM</t>
-        </is>
-      </c>
-      <c r="D49" s="16" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="E49" s="17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F49" s="16" t="inlineStr">
+      <c r="A49" s="22" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t>Taj Bradley</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="E49" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F49" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G49" s="16" t="n">
-        <v>116</v>
-      </c>
-      <c r="H49" s="18" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="I49" s="18" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J49" s="18" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="K49" s="19" t="n">
-        <v>6.789</v>
-      </c>
-      <c r="L49" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M49" s="19" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="N49" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="O49" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P49" s="21" t="n">
-        <v>1.16</v>
+      <c r="G49" s="24" t="n">
+        <v>118</v>
+      </c>
+      <c r="H49" s="26" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="I49" s="26" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="J49" s="26" t="n">
+        <v>0.1143</v>
+      </c>
+      <c r="K49" s="27" t="n">
+        <v>5.159</v>
+      </c>
+      <c r="L49" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M49" s="27" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="N49" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O49" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P49" s="29" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="14" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t>Kevin Gausman</t>
-        </is>
-      </c>
-      <c r="C50" s="16" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="D50" s="16" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="E50" s="17" t="n">
+      <c r="A50" s="22" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t>Cole Ragans</t>
+        </is>
+      </c>
+      <c r="C50" s="24" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="D50" s="24" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E50" s="25" t="n">
         <v>7.5</v>
       </c>
-      <c r="F50" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G50" s="16" t="n">
-        <v>116</v>
-      </c>
-      <c r="H50" s="18" t="n">
-        <v>0.529</v>
-      </c>
-      <c r="I50" s="18" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J50" s="18" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="K50" s="19" t="n">
-        <v>7.914</v>
-      </c>
-      <c r="L50" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M50" s="19" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="N50" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="O50" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P50" s="21" t="n">
-        <v>1.16</v>
+      <c r="F50" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G50" s="24" t="n">
+        <v>-152</v>
+      </c>
+      <c r="H50" s="26" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="I50" s="26" t="n">
+        <v>0.6032</v>
+      </c>
+      <c r="J50" s="26" t="n">
+        <v>0.1348</v>
+      </c>
+      <c r="K50" s="27" t="n">
+        <v>5.951</v>
+      </c>
+      <c r="L50" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M50" s="27" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="N50" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="O50" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P50" s="29" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="51" ht="17" customHeight="1">
@@ -3434,118 +3410,118 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="C51" s="16" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E51" s="17" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="F51" s="16" t="inlineStr">
         <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G51" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="H51" s="18" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="I51" s="18" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J51" s="18" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="K51" s="19" t="n">
+        <v>6.789</v>
+      </c>
+      <c r="L51" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M51" s="19" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N51" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O51" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P51" s="21" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="22" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t>Yusei Kikuchi</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D52" s="24" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="E52" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F52" s="24" t="inlineStr">
+        <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G51" s="16" t="n">
-        <v>-132</v>
-      </c>
-      <c r="H51" s="18" t="n">
-        <v>0.696</v>
-      </c>
-      <c r="I51" s="18" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="J51" s="18" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="K51" s="19" t="n">
-        <v>6.191</v>
-      </c>
-      <c r="L51" s="17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M51" s="19" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="N51" s="16" t="n">
+      <c r="G52" s="24" t="n">
+        <v>102</v>
+      </c>
+      <c r="H52" s="26" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="I52" s="26" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="J52" s="26" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="K52" s="27" t="n">
+        <v>4.364</v>
+      </c>
+      <c r="L52" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M52" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N52" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="O51" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P51" s="21" t="n">
-        <v>0.7576000000000001</v>
-      </c>
-    </row>
-    <row r="52" ht="17" customHeight="1">
-      <c r="A52" s="14" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B52" s="15" t="inlineStr">
-        <is>
-          <t>Cam Schlittler</t>
-        </is>
-      </c>
-      <c r="C52" s="16" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="D52" s="16" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="E52" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F52" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G52" s="16" t="n">
-        <v>-144</v>
-      </c>
-      <c r="H52" s="18" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="I52" s="18" t="n">
-        <v>0.5901999999999999</v>
-      </c>
-      <c r="J52" s="18" t="n">
-        <v>0.1448</v>
-      </c>
-      <c r="K52" s="19" t="n">
-        <v>7.561</v>
-      </c>
-      <c r="L52" s="17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M52" s="19" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="N52" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="O52" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P52" s="21" t="n">
-        <v>0.6944</v>
+      <c r="O52" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P52" s="29" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="53" ht="17" customHeight="1">
@@ -3554,21 +3530,21 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>Zac Gallen</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="C53" s="16" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E53" s="17" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="F53" s="16" t="inlineStr">
         <is>
@@ -3576,156 +3552,156 @@
         </is>
       </c>
       <c r="G53" s="16" t="n">
-        <v>112</v>
+        <v>-132</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>0.707</v>
+        <v>0.696</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>0.4717</v>
+        <v>0.569</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>0.2353</v>
+        <v>0.127</v>
       </c>
       <c r="K53" s="19" t="n">
-        <v>4.34</v>
+        <v>6.191</v>
       </c>
       <c r="L53" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M53" s="19" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="N53" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="O53" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P53" s="21" t="n">
+        <v>0.7576000000000001</v>
+      </c>
+    </row>
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="14" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>Kevin Gausman</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D54" s="16" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F54" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G54" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="H54" s="18" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="I54" s="18" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J54" s="18" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="K54" s="19" t="n">
+        <v>7.914</v>
+      </c>
+      <c r="L54" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M54" s="19" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N54" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="O54" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P54" s="21" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="55" ht="17" customHeight="1">
+      <c r="A55" s="22" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B55" s="23" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="C55" s="24" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="D55" s="24" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E55" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F55" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G55" s="24" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H55" s="26" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="I55" s="26" t="n">
+        <v>0.5413</v>
+      </c>
+      <c r="J55" s="26" t="n">
+        <v>0.1907</v>
+      </c>
+      <c r="K55" s="27" t="n">
+        <v>3.414</v>
+      </c>
+      <c r="L55" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M53" s="19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N53" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="O53" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P53" s="21" t="n">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="54" ht="17" customHeight="1">
-      <c r="A54" s="22" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B54" s="23" t="inlineStr">
-        <is>
-          <t>Drew Rasmussen</t>
-        </is>
-      </c>
-      <c r="C54" s="24" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="D54" s="24" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="E54" s="25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F54" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G54" s="24" t="n">
-        <v>-118</v>
-      </c>
-      <c r="H54" s="26" t="n">
-        <v>0.732</v>
-      </c>
-      <c r="I54" s="26" t="n">
-        <v>0.5413</v>
-      </c>
-      <c r="J54" s="26" t="n">
-        <v>0.1907</v>
-      </c>
-      <c r="K54" s="27" t="n">
-        <v>3.414</v>
-      </c>
-      <c r="L54" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M54" s="27" t="n">
+      <c r="M55" s="27" t="n">
         <v>1.04</v>
       </c>
-      <c r="N54" s="24" t="n">
+      <c r="N55" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="O54" s="28" t="inlineStr">
+      <c r="O55" s="28" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P54" s="29" t="n">
+      <c r="P55" s="29" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="14" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B55" s="15" t="inlineStr">
-        <is>
-          <t>Adrian Houser</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="D55" s="16" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E55" s="17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F55" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G55" s="16" t="n">
-        <v>-125</v>
-      </c>
-      <c r="H55" s="18" t="n">
-        <v>0.724</v>
-      </c>
-      <c r="I55" s="18" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="J55" s="18" t="n">
-        <v>0.1684</v>
-      </c>
-      <c r="K55" s="19" t="n">
-        <v>5.063</v>
-      </c>
-      <c r="L55" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M55" s="19" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="N55" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="O55" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P55" s="21" t="n">
-        <v>0.8</v>
       </c>
     </row>
     <row r="56" ht="17" customHeight="1">
@@ -3734,178 +3710,178 @@
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Adrian Houser</t>
         </is>
       </c>
       <c r="C56" s="16" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E56" s="17" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="F56" s="16" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G56" s="16" t="n">
-        <v>108</v>
+        <v>-125</v>
       </c>
       <c r="H56" s="18" t="n">
-        <v>0.644</v>
+        <v>0.724</v>
       </c>
       <c r="I56" s="18" t="n">
-        <v>0.4808</v>
+        <v>0.5556</v>
       </c>
       <c r="J56" s="18" t="n">
-        <v>0.1632</v>
+        <v>0.1684</v>
       </c>
       <c r="K56" s="19" t="n">
-        <v>5.865</v>
+        <v>5.063</v>
       </c>
       <c r="L56" s="17" t="n">
         <v>2</v>
       </c>
       <c r="M56" s="19" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N56" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O56" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P56" s="21" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="57" ht="17" customHeight="1">
+      <c r="A57" s="14" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>Tarik Skubal</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="D57" s="16" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F57" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G57" s="16" t="n">
+        <v>108</v>
+      </c>
+      <c r="H57" s="18" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="I57" s="18" t="n">
+        <v>0.4808</v>
+      </c>
+      <c r="J57" s="18" t="n">
+        <v>0.1632</v>
+      </c>
+      <c r="K57" s="19" t="n">
+        <v>5.865</v>
+      </c>
+      <c r="L57" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M57" s="19" t="n">
         <v>0.79</v>
       </c>
-      <c r="N56" s="16" t="n">
+      <c r="N57" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="O56" s="20" t="inlineStr">
+      <c r="O57" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P56" s="21" t="n">
+      <c r="P57" s="21" t="n">
         <v>1.08</v>
       </c>
     </row>
-    <row r="57" ht="17" customHeight="1">
-      <c r="A57" s="22" t="n">
+    <row r="58" ht="17" customHeight="1">
+      <c r="A58" s="22" t="n">
         <v>46113</v>
       </c>
-      <c r="B57" s="23" t="inlineStr">
+      <c r="B58" s="23" t="inlineStr">
         <is>
           <t>Cade Cavalli</t>
         </is>
       </c>
-      <c r="C57" s="24" t="inlineStr">
+      <c r="C58" s="24" t="inlineStr">
         <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="D57" s="24" t="inlineStr">
+      <c r="D58" s="24" t="inlineStr">
         <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E57" s="25" t="n">
+      <c r="E58" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F57" s="24" t="inlineStr">
+      <c r="F58" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G57" s="24" t="n">
+      <c r="G58" s="24" t="n">
         <v>-102</v>
       </c>
-      <c r="H57" s="26" t="n">
+      <c r="H58" s="26" t="n">
         <v>0.668</v>
       </c>
-      <c r="I57" s="26" t="n">
+      <c r="I58" s="26" t="n">
         <v>0.505</v>
       </c>
-      <c r="J57" s="26" t="n">
+      <c r="J58" s="26" t="n">
         <v>0.163</v>
       </c>
-      <c r="K57" s="27" t="n">
+      <c r="K58" s="27" t="n">
         <v>5.697</v>
       </c>
-      <c r="L57" s="25" t="n">
+      <c r="L58" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M57" s="27" t="n">
+      <c r="M58" s="27" t="n">
         <v>0.82</v>
       </c>
-      <c r="N57" s="24" t="n">
+      <c r="N58" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="O57" s="28" t="inlineStr">
+      <c r="O58" s="28" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P57" s="29" t="n">
+      <c r="P58" s="29" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="58" ht="17" customHeight="1">
-      <c r="A58" s="14" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B58" s="15" t="inlineStr">
-        <is>
-          <t>Andrew Abbott</t>
-        </is>
-      </c>
-      <c r="C58" s="16" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="D58" s="16" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="E58" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F58" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G58" s="16" t="n">
-        <v>-112</v>
-      </c>
-      <c r="H58" s="18" t="n">
-        <v>0.677</v>
-      </c>
-      <c r="I58" s="18" t="n">
-        <v>0.5283</v>
-      </c>
-      <c r="J58" s="18" t="n">
-        <v>0.1487</v>
-      </c>
-      <c r="K58" s="19" t="n">
-        <v>4.469</v>
-      </c>
-      <c r="L58" s="17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M58" s="19" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="N58" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="O58" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P58" s="21" t="n">
-        <v>0.8929</v>
       </c>
     </row>
     <row r="59" ht="17" customHeight="1">
@@ -3914,21 +3890,21 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>Matthew Liberatore</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="C59" s="16" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E59" s="17" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="F59" s="16" t="inlineStr">
         <is>
@@ -3936,28 +3912,28 @@
         </is>
       </c>
       <c r="G59" s="16" t="n">
-        <v>118</v>
+        <v>-112</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>0.525</v>
+        <v>0.677</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>0.4587</v>
+        <v>0.5283</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>0.0663</v>
+        <v>0.1487</v>
       </c>
       <c r="K59" s="19" t="n">
-        <v>3.583</v>
+        <v>4.469</v>
       </c>
       <c r="L59" s="17" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M59" s="19" t="n">
-        <v>0.31</v>
+        <v>0.79</v>
       </c>
       <c r="N59" s="16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O59" s="20" t="inlineStr">
         <is>
@@ -3965,7 +3941,7 @@
         </is>
       </c>
       <c r="P59" s="21" t="n">
-        <v>1.18</v>
+        <v>0.8929</v>
       </c>
     </row>
     <row r="60" ht="17" customHeight="1">
@@ -3974,21 +3950,21 @@
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="C60" s="16" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E60" s="17" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="F60" s="16" t="inlineStr">
         <is>
@@ -3996,25 +3972,25 @@
         </is>
       </c>
       <c r="G60" s="16" t="n">
-        <v>100</v>
+        <v>-144</v>
       </c>
       <c r="H60" s="18" t="n">
-        <v>0.624</v>
+        <v>0.735</v>
       </c>
       <c r="I60" s="18" t="n">
-        <v>0.5</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="J60" s="18" t="n">
-        <v>0.124</v>
+        <v>0.1448</v>
       </c>
       <c r="K60" s="19" t="n">
-        <v>7.784</v>
+        <v>7.561</v>
       </c>
       <c r="L60" s="17" t="n">
         <v>1.5</v>
       </c>
       <c r="M60" s="19" t="n">
-        <v>0.62</v>
+        <v>0.88</v>
       </c>
       <c r="N60" s="16" t="n">
         <v>7</v>
@@ -4025,67 +4001,67 @@
         </is>
       </c>
       <c r="P60" s="21" t="n">
+        <v>0.6944</v>
+      </c>
+    </row>
+    <row r="61" ht="17" customHeight="1">
+      <c r="A61" s="14" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D61" s="16" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F61" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G61" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="H61" s="18" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="I61" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J61" s="18" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="K61" s="19" t="n">
+        <v>7.784</v>
+      </c>
+      <c r="L61" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M61" s="19" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="N61" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O61" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P61" s="21" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="61" ht="17" customHeight="1">
-      <c r="A61" s="22" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B61" s="23" t="inlineStr">
-        <is>
-          <t>Nathan Eovaldi</t>
-        </is>
-      </c>
-      <c r="C61" s="24" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
-      <c r="D61" s="24" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="E61" s="25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F61" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G61" s="24" t="n">
-        <v>-168</v>
-      </c>
-      <c r="H61" s="26" t="n">
-        <v>0.743</v>
-      </c>
-      <c r="I61" s="26" t="n">
-        <v>0.6269</v>
-      </c>
-      <c r="J61" s="26" t="n">
-        <v>0.1161</v>
-      </c>
-      <c r="K61" s="27" t="n">
-        <v>7.699</v>
-      </c>
-      <c r="L61" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M61" s="27" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="N61" s="24" t="n">
-        <v>5</v>
-      </c>
-      <c r="O61" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P61" s="29" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="62" ht="17" customHeight="1">
@@ -4094,17 +4070,17 @@
       </c>
       <c r="B62" s="23" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Nathan Eovaldi</t>
         </is>
       </c>
       <c r="C62" s="24" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="D62" s="24" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E62" s="25" t="n">
@@ -4112,32 +4088,32 @@
       </c>
       <c r="F62" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G62" s="24" t="n">
-        <v>128</v>
+        <v>-168</v>
       </c>
       <c r="H62" s="26" t="n">
-        <v>0.55</v>
+        <v>0.743</v>
       </c>
       <c r="I62" s="26" t="n">
-        <v>0.4386</v>
+        <v>0.6269</v>
       </c>
       <c r="J62" s="26" t="n">
-        <v>0.1114</v>
+        <v>0.1161</v>
       </c>
       <c r="K62" s="27" t="n">
-        <v>5.551</v>
+        <v>7.699</v>
       </c>
       <c r="L62" s="25" t="n">
         <v>1.5</v>
       </c>
       <c r="M62" s="27" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="N62" s="24" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O62" s="28" t="inlineStr">
         <is>
@@ -4154,17 +4130,17 @@
       </c>
       <c r="B63" s="23" t="inlineStr">
         <is>
-          <t>Mike Burrows</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="C63" s="24" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="D63" s="24" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E63" s="25" t="n">
@@ -4176,28 +4152,28 @@
         </is>
       </c>
       <c r="G63" s="24" t="n">
-        <v>-114</v>
+        <v>128</v>
       </c>
       <c r="H63" s="26" t="n">
-        <v>0.636</v>
+        <v>0.55</v>
       </c>
       <c r="I63" s="26" t="n">
-        <v>0.5327</v>
+        <v>0.4386</v>
       </c>
       <c r="J63" s="26" t="n">
-        <v>0.1033</v>
+        <v>0.1114</v>
       </c>
       <c r="K63" s="27" t="n">
-        <v>4.943</v>
+        <v>5.551</v>
       </c>
       <c r="L63" s="25" t="n">
         <v>1.5</v>
       </c>
       <c r="M63" s="27" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="N63" s="24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O63" s="28" t="inlineStr">
         <is>
@@ -4209,543 +4185,543 @@
       </c>
     </row>
     <row r="64" ht="17" customHeight="1">
-      <c r="A64" s="14" t="n">
+      <c r="A64" s="22" t="n">
         <v>46113</v>
       </c>
-      <c r="B64" s="15" t="inlineStr">
+      <c r="B64" s="23" t="inlineStr">
+        <is>
+          <t>Mike Burrows</t>
+        </is>
+      </c>
+      <c r="C64" s="24" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="D64" s="24" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="E64" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F64" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G64" s="24" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H64" s="26" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="I64" s="26" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="J64" s="26" t="n">
+        <v>0.1033</v>
+      </c>
+      <c r="K64" s="27" t="n">
+        <v>4.943</v>
+      </c>
+      <c r="L64" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M64" s="27" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N64" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="O64" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P64" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="65" ht="17" customHeight="1">
+      <c r="A65" s="14" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B65" s="15" t="inlineStr">
         <is>
           <t>George Kirby</t>
         </is>
       </c>
-      <c r="C64" s="16" t="inlineStr">
+      <c r="C65" s="16" t="inlineStr">
         <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="D64" s="16" t="inlineStr">
+      <c r="D65" s="16" t="inlineStr">
         <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E64" s="17" t="n">
+      <c r="E65" s="17" t="n">
         <v>7.5</v>
       </c>
-      <c r="F64" s="16" t="inlineStr">
+      <c r="F65" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G64" s="16" t="n">
+      <c r="G65" s="16" t="n">
         <v>-178</v>
       </c>
-      <c r="H64" s="18" t="n">
+      <c r="H65" s="18" t="n">
         <v>0.726</v>
       </c>
-      <c r="I64" s="18" t="n">
+      <c r="I65" s="18" t="n">
         <v>0.6403</v>
       </c>
-      <c r="J64" s="18" t="n">
+      <c r="J65" s="18" t="n">
         <v>0.0857</v>
       </c>
-      <c r="K64" s="19" t="n">
+      <c r="K65" s="19" t="n">
         <v>5.8</v>
       </c>
-      <c r="L64" s="17" t="n">
+      <c r="L65" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="M64" s="19" t="n">
+      <c r="M65" s="19" t="n">
         <v>0.6</v>
       </c>
-      <c r="N64" s="16" t="n">
+      <c r="N65" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="O64" s="20" t="inlineStr">
+      <c r="O65" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P64" s="21" t="n">
+      <c r="P65" s="21" t="n">
         <v>0.5618</v>
       </c>
     </row>
-    <row r="65" ht="17" customHeight="1">
-      <c r="A65" s="22" t="n">
+    <row r="66" ht="17" customHeight="1">
+      <c r="A66" s="22" t="n">
         <v>46113</v>
       </c>
-      <c r="B65" s="23" t="inlineStr">
+      <c r="B66" s="23" t="inlineStr">
         <is>
           <t>Shane Smith</t>
         </is>
       </c>
-      <c r="C65" s="24" t="inlineStr">
+      <c r="C66" s="24" t="inlineStr">
         <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="D65" s="24" t="inlineStr">
+      <c r="D66" s="24" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="E65" s="25" t="n">
+      <c r="E66" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F65" s="24" t="inlineStr">
+      <c r="F66" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G65" s="24" t="n">
+      <c r="G66" s="24" t="n">
         <v>100</v>
       </c>
-      <c r="H65" s="26" t="n">
+      <c r="H66" s="26" t="n">
         <v>0.576</v>
       </c>
-      <c r="I65" s="26" t="n">
+      <c r="I66" s="26" t="n">
         <v>0.5</v>
       </c>
-      <c r="J65" s="26" t="n">
+      <c r="J66" s="26" t="n">
         <v>0.076</v>
       </c>
-      <c r="K65" s="27" t="n">
+      <c r="K66" s="27" t="n">
         <v>5.393</v>
       </c>
-      <c r="L65" s="25" t="n">
+      <c r="L66" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="M65" s="27" t="n">
+      <c r="M66" s="27" t="n">
         <v>0.38</v>
       </c>
-      <c r="N65" s="24" t="n">
+      <c r="N66" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="O65" s="28" t="inlineStr">
+      <c r="O66" s="28" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P65" s="29" t="n">
+      <c r="P66" s="29" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="66" ht="17" customHeight="1">
-      <c r="A66" s="14" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B66" s="15" t="inlineStr">
-        <is>
-          <t>Kyle Freeland</t>
-        </is>
-      </c>
-      <c r="C66" s="16" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="D66" s="16" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="E66" s="17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F66" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G66" s="16" t="n">
-        <v>100</v>
-      </c>
-      <c r="H66" s="18" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="I66" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J66" s="18" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K66" s="19" t="n">
-        <v>4.038</v>
-      </c>
-      <c r="L66" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M66" s="19" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="N66" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="O66" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P66" s="21" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="67" ht="17" customHeight="1">
       <c r="A67" s="14" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>Jameson Taillon</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="C67" s="16" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E67" s="17" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F67" s="16" t="inlineStr">
         <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G67" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="H67" s="18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I67" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J67" s="18" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K67" s="19" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="L67" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M67" s="19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N67" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O67" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P67" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" ht="17" customHeight="1">
+      <c r="A68" s="14" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>Matthew Liberatore</t>
+        </is>
+      </c>
+      <c r="C68" s="16" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D68" s="16" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="E68" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F68" s="16" t="inlineStr">
+        <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G67" s="16" t="n">
-        <v>116</v>
-      </c>
-      <c r="H67" s="18" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="I67" s="18" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J67" s="18" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="K67" s="19" t="n">
-        <v>4.313</v>
-      </c>
-      <c r="L67" s="17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M67" s="19" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="N67" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="O67" s="20" t="inlineStr">
+      <c r="G68" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="H68" s="18" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="I68" s="18" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="J68" s="18" t="n">
+        <v>0.0663</v>
+      </c>
+      <c r="K68" s="19" t="n">
+        <v>3.583</v>
+      </c>
+      <c r="L68" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M68" s="19" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N68" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O68" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P67" s="21" t="n">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="68" ht="17" customHeight="1">
-      <c r="A68" s="22" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B68" s="23" t="inlineStr">
-        <is>
-          <t>José Soriano</t>
-        </is>
-      </c>
-      <c r="C68" s="24" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="D68" s="24" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="E68" s="25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F68" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G68" s="24" t="n">
-        <v>-110</v>
-      </c>
-      <c r="H68" s="26" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="I68" s="26" t="n">
-        <v>0.5238</v>
-      </c>
-      <c r="J68" s="26" t="n">
-        <v>0.1522</v>
-      </c>
-      <c r="K68" s="27" t="n">
-        <v>5.918</v>
-      </c>
-      <c r="L68" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M68" s="27" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N68" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="O68" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P68" s="29" t="n">
-        <v>-1</v>
+      <c r="P68" s="21" t="n">
+        <v>1.18</v>
       </c>
     </row>
     <row r="69" ht="17" customHeight="1">
       <c r="A69" s="14" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>Zac Gallen</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="D69" s="16" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="E69" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F69" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G69" s="16" t="n">
+        <v>112</v>
+      </c>
+      <c r="H69" s="18" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="I69" s="18" t="n">
+        <v>0.4717</v>
+      </c>
+      <c r="J69" s="18" t="n">
+        <v>0.2353</v>
+      </c>
+      <c r="K69" s="19" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="L69" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M69" s="19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N69" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O69" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P69" s="21" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="70" ht="17" customHeight="1">
+      <c r="A70" s="22" t="n">
         <v>46112</v>
       </c>
-      <c r="B69" s="15" t="inlineStr">
+      <c r="B70" s="23" t="inlineStr">
+        <is>
+          <t>José Soriano</t>
+        </is>
+      </c>
+      <c r="C70" s="24" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D70" s="24" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="E70" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F70" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G70" s="24" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H70" s="26" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="I70" s="26" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="J70" s="26" t="n">
+        <v>0.1522</v>
+      </c>
+      <c r="K70" s="27" t="n">
+        <v>5.918</v>
+      </c>
+      <c r="L70" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M70" s="27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N70" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="O70" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P70" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="71" ht="17" customHeight="1">
+      <c r="A71" s="14" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B71" s="15" t="inlineStr">
         <is>
           <t>Ryan Feltner</t>
         </is>
       </c>
-      <c r="C69" s="16" t="inlineStr">
+      <c r="C71" s="16" t="inlineStr">
         <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="D69" s="16" t="inlineStr">
+      <c r="D71" s="16" t="inlineStr">
         <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="E69" s="17" t="n">
+      <c r="E71" s="17" t="n">
         <v>3.5</v>
       </c>
-      <c r="F69" s="16" t="inlineStr">
+      <c r="F71" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G69" s="16" t="n">
+      <c r="G71" s="16" t="n">
         <v>-108</v>
       </c>
-      <c r="H69" s="18" t="n">
+      <c r="H71" s="18" t="n">
         <v>0.655</v>
       </c>
-      <c r="I69" s="18" t="n">
+      <c r="I71" s="18" t="n">
         <v>0.5192</v>
       </c>
-      <c r="J69" s="18" t="n">
+      <c r="J71" s="18" t="n">
         <v>0.1358</v>
       </c>
-      <c r="K69" s="19" t="n">
+      <c r="K71" s="19" t="n">
         <v>4.719</v>
       </c>
-      <c r="L69" s="17" t="n">
+      <c r="L71" s="17" t="n">
         <v>1.5</v>
       </c>
-      <c r="M69" s="19" t="n">
+      <c r="M71" s="19" t="n">
         <v>0.71</v>
       </c>
-      <c r="N69" s="16" t="n">
+      <c r="N71" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="O69" s="20" t="inlineStr">
+      <c r="O71" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P69" s="21" t="n">
+      <c r="P71" s="21" t="n">
         <v>0.9258999999999999</v>
       </c>
     </row>
-    <row r="70" ht="17" customHeight="1">
-      <c r="A70" s="14" t="n">
+    <row r="72" ht="17" customHeight="1">
+      <c r="A72" s="14" t="n">
         <v>46112</v>
       </c>
-      <c r="B70" s="15" t="inlineStr">
+      <c r="B72" s="15" t="inlineStr">
         <is>
           <t>Erick Fedde</t>
         </is>
       </c>
-      <c r="C70" s="16" t="inlineStr">
+      <c r="C72" s="16" t="inlineStr">
         <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="D70" s="16" t="inlineStr">
+      <c r="D72" s="16" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="E70" s="17" t="n">
+      <c r="E72" s="17" t="n">
         <v>3.5</v>
       </c>
-      <c r="F70" s="16" t="inlineStr">
+      <c r="F72" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G70" s="16" t="n">
+      <c r="G72" s="16" t="n">
         <v>134</v>
       </c>
-      <c r="H70" s="18" t="n">
+      <c r="H72" s="18" t="n">
         <v>0.527</v>
       </c>
-      <c r="I70" s="18" t="n">
+      <c r="I72" s="18" t="n">
         <v>0.4274</v>
       </c>
-      <c r="J70" s="18" t="n">
+      <c r="J72" s="18" t="n">
         <v>0.09959999999999999</v>
       </c>
-      <c r="K70" s="19" t="n">
+      <c r="K72" s="19" t="n">
         <v>3.852</v>
       </c>
-      <c r="L70" s="17" t="n">
+      <c r="L72" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="M70" s="19" t="n">
+      <c r="M72" s="19" t="n">
         <v>0.44</v>
       </c>
-      <c r="N70" s="16" t="n">
+      <c r="N72" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="O70" s="20" t="inlineStr">
+      <c r="O72" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P70" s="21" t="n">
+      <c r="P72" s="21" t="n">
         <v>1.34</v>
-      </c>
-    </row>
-    <row r="71" ht="17" customHeight="1">
-      <c r="A71" s="22" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B71" s="23" t="inlineStr">
-        <is>
-          <t>Andre Pallante</t>
-        </is>
-      </c>
-      <c r="C71" s="24" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="D71" s="24" t="inlineStr">
-        <is>
-          <t>NYM</t>
-        </is>
-      </c>
-      <c r="E71" s="25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F71" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G71" s="24" t="n">
-        <v>126</v>
-      </c>
-      <c r="H71" s="26" t="n">
-        <v>0.523</v>
-      </c>
-      <c r="I71" s="26" t="n">
-        <v>0.4425</v>
-      </c>
-      <c r="J71" s="26" t="n">
-        <v>0.0805</v>
-      </c>
-      <c r="K71" s="27" t="n">
-        <v>3.876</v>
-      </c>
-      <c r="L71" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M71" s="27" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="N71" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="O71" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P71" s="29" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="72" ht="17" customHeight="1">
-      <c r="A72" s="22" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B72" s="23" t="inlineStr">
-        <is>
-          <t>Aaron Civale</t>
-        </is>
-      </c>
-      <c r="C72" s="24" t="inlineStr">
-        <is>
-          <t>OAK</t>
-        </is>
-      </c>
-      <c r="D72" s="24" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="E72" s="25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F72" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G72" s="24" t="n">
-        <v>-146</v>
-      </c>
-      <c r="H72" s="26" t="n">
-        <v>0.666</v>
-      </c>
-      <c r="I72" s="26" t="n">
-        <v>0.5935</v>
-      </c>
-      <c r="J72" s="26" t="n">
-        <v>0.0725</v>
-      </c>
-      <c r="K72" s="27" t="n">
-        <v>4.714</v>
-      </c>
-      <c r="L72" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M72" s="27" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="N72" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="O72" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P72" s="29" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="73" ht="17" customHeight="1">
@@ -4754,127 +4730,127 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
+          <t>Jameson Taillon</t>
+        </is>
+      </c>
+      <c r="C73" s="16" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="D73" s="16" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F73" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G73" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="H73" s="18" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="I73" s="18" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J73" s="18" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="K73" s="19" t="n">
+        <v>4.313</v>
+      </c>
+      <c r="L73" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M73" s="19" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="N73" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O73" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P73" s="21" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="74" ht="17" customHeight="1">
+      <c r="A74" s="14" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B74" s="15" t="inlineStr">
+        <is>
           <t>Max Scherzer</t>
         </is>
       </c>
-      <c r="C73" s="16" t="inlineStr">
+      <c r="C74" s="16" t="inlineStr">
         <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="D73" s="16" t="inlineStr">
+      <c r="D74" s="16" t="inlineStr">
         <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="E73" s="17" t="n">
+      <c r="E74" s="17" t="n">
         <v>5.5</v>
       </c>
-      <c r="F73" s="16" t="inlineStr">
+      <c r="F74" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G73" s="16" t="n">
+      <c r="G74" s="16" t="n">
         <v>-130</v>
       </c>
-      <c r="H73" s="18" t="n">
+      <c r="H74" s="18" t="n">
         <v>0.652</v>
       </c>
-      <c r="I73" s="18" t="n">
+      <c r="I74" s="18" t="n">
         <v>0.5652</v>
       </c>
-      <c r="J73" s="18" t="n">
+      <c r="J74" s="18" t="n">
         <v>0.0868</v>
       </c>
-      <c r="K73" s="19" t="n">
+      <c r="K74" s="19" t="n">
         <v>4.757</v>
       </c>
-      <c r="L73" s="17" t="n">
+      <c r="L74" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="M73" s="19" t="n">
+      <c r="M74" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="N73" s="16" t="n">
+      <c r="N74" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="O73" s="20" t="inlineStr">
+      <c r="O74" s="20" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P73" s="21" t="n">
+      <c r="P74" s="21" t="n">
         <v>0.7692</v>
-      </c>
-    </row>
-    <row r="74" ht="17" customHeight="1">
-      <c r="A74" s="22" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B74" s="23" t="inlineStr">
-        <is>
-          <t>Simeon Woods Richardson</t>
-        </is>
-      </c>
-      <c r="C74" s="24" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="D74" s="24" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="E74" s="25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F74" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G74" s="24" t="n">
-        <v>-112</v>
-      </c>
-      <c r="H74" s="26" t="n">
-        <v>0.783</v>
-      </c>
-      <c r="I74" s="26" t="n">
-        <v>0.5283</v>
-      </c>
-      <c r="J74" s="26" t="n">
-        <v>0.2547</v>
-      </c>
-      <c r="K74" s="27" t="n">
-        <v>5.562</v>
-      </c>
-      <c r="L74" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M74" s="27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="N74" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="O74" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P74" s="29" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="75" ht="17" customHeight="1">
       <c r="A75" s="22" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B75" s="23" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Aaron Civale</t>
         </is>
       </c>
       <c r="C75" s="24" t="inlineStr">
@@ -4888,7 +4864,7 @@
         </is>
       </c>
       <c r="E75" s="25" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F75" s="24" t="inlineStr">
         <is>
@@ -4896,28 +4872,28 @@
         </is>
       </c>
       <c r="G75" s="24" t="n">
-        <v>100</v>
+        <v>-146</v>
       </c>
       <c r="H75" s="26" t="n">
-        <v>0.586</v>
+        <v>0.666</v>
       </c>
       <c r="I75" s="26" t="n">
+        <v>0.5935</v>
+      </c>
+      <c r="J75" s="26" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="K75" s="27" t="n">
+        <v>4.714</v>
+      </c>
+      <c r="L75" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="J75" s="26" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="K75" s="27" t="n">
-        <v>6.418</v>
-      </c>
-      <c r="L75" s="25" t="n">
-        <v>1</v>
-      </c>
       <c r="M75" s="27" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="N75" s="24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O75" s="28" t="inlineStr">
         <is>
@@ -4929,123 +4905,123 @@
       </c>
     </row>
     <row r="76" ht="17" customHeight="1">
-      <c r="A76" s="14" t="n">
+      <c r="A76" s="22" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B76" s="23" t="inlineStr">
+        <is>
+          <t>Andre Pallante</t>
+        </is>
+      </c>
+      <c r="C76" s="24" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D76" s="24" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="E76" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F76" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G76" s="24" t="n">
+        <v>126</v>
+      </c>
+      <c r="H76" s="26" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="I76" s="26" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="J76" s="26" t="n">
+        <v>0.0805</v>
+      </c>
+      <c r="K76" s="27" t="n">
+        <v>3.876</v>
+      </c>
+      <c r="L76" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" s="27" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="N76" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O76" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P76" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="77" ht="17" customHeight="1">
+      <c r="A77" s="22" t="n">
         <v>46111</v>
       </c>
-      <c r="B76" s="15" t="inlineStr">
-        <is>
-          <t>Jack Leiter</t>
-        </is>
-      </c>
-      <c r="C76" s="16" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
-      <c r="D76" s="16" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="E76" s="17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F76" s="16" t="inlineStr">
+      <c r="B77" s="23" t="inlineStr">
+        <is>
+          <t>Simeon Woods Richardson</t>
+        </is>
+      </c>
+      <c r="C77" s="24" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="D77" s="24" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="E77" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F77" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G76" s="16" t="n">
-        <v>-144</v>
-      </c>
-      <c r="H76" s="18" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="I76" s="18" t="n">
-        <v>0.5901999999999999</v>
-      </c>
-      <c r="J76" s="18" t="n">
-        <v>0.0888</v>
-      </c>
-      <c r="K76" s="19" t="n">
-        <v>6.017</v>
-      </c>
-      <c r="L76" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M76" s="19" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="N76" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="O76" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P76" s="21" t="n">
-        <v>0.6944</v>
-      </c>
-    </row>
-    <row r="77" ht="17" customHeight="1">
-      <c r="A77" s="14" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B77" s="15" t="inlineStr">
-        <is>
-          <t>Edward Cabrera</t>
-        </is>
-      </c>
-      <c r="C77" s="16" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="D77" s="16" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="E77" s="17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F77" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G77" s="16" t="n">
-        <v>116</v>
-      </c>
-      <c r="H77" s="18" t="n">
-        <v>0.6889999999999999</v>
-      </c>
-      <c r="I77" s="18" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J77" s="18" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="K77" s="19" t="n">
-        <v>5.286</v>
-      </c>
-      <c r="L77" s="17" t="n">
+      <c r="G77" s="24" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H77" s="26" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="I77" s="26" t="n">
+        <v>0.5283</v>
+      </c>
+      <c r="J77" s="26" t="n">
+        <v>0.2547</v>
+      </c>
+      <c r="K77" s="27" t="n">
+        <v>5.562</v>
+      </c>
+      <c r="L77" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M77" s="19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N77" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="O77" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P77" s="21" t="n">
-        <v>1.16</v>
+      <c r="M77" s="27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="N77" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O77" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P77" s="29" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="78" ht="17" customHeight="1">
@@ -5054,21 +5030,21 @@
       </c>
       <c r="B78" s="23" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="C78" s="24" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>OAK</t>
         </is>
       </c>
       <c r="D78" s="24" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E78" s="25" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="F78" s="24" t="inlineStr">
         <is>
@@ -5076,28 +5052,28 @@
         </is>
       </c>
       <c r="G78" s="24" t="n">
-        <v>-174</v>
+        <v>100</v>
       </c>
       <c r="H78" s="26" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.586</v>
       </c>
       <c r="I78" s="26" t="n">
-        <v>0.635</v>
+        <v>0.5</v>
       </c>
       <c r="J78" s="26" t="n">
-        <v>0.054</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="K78" s="27" t="n">
-        <v>4.97</v>
+        <v>6.418</v>
       </c>
       <c r="L78" s="25" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M78" s="27" t="n">
-        <v>0.37</v>
+        <v>0.43</v>
       </c>
       <c r="N78" s="24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O78" s="28" t="inlineStr">
         <is>
@@ -5109,63 +5085,63 @@
       </c>
     </row>
     <row r="79" ht="17" customHeight="1">
-      <c r="A79" s="22" t="n">
+      <c r="A79" s="14" t="n">
         <v>46111</v>
       </c>
-      <c r="B79" s="23" t="inlineStr">
-        <is>
-          <t>Kyle Harrison</t>
-        </is>
-      </c>
-      <c r="C79" s="24" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D79" s="24" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="E79" s="25" t="n">
+      <c r="B79" s="15" t="inlineStr">
+        <is>
+          <t>Jack Leiter</t>
+        </is>
+      </c>
+      <c r="C79" s="16" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="D79" s="16" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E79" s="17" t="n">
         <v>4.5</v>
       </c>
-      <c r="F79" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G79" s="24" t="n">
-        <v>114</v>
-      </c>
-      <c r="H79" s="26" t="n">
-        <v>0.521</v>
-      </c>
-      <c r="I79" s="26" t="n">
-        <v>0.4673</v>
-      </c>
-      <c r="J79" s="26" t="n">
-        <v>0.0537</v>
-      </c>
-      <c r="K79" s="27" t="n">
-        <v>4.628</v>
-      </c>
-      <c r="L79" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M79" s="27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N79" s="24" t="n">
+      <c r="F79" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G79" s="16" t="n">
+        <v>-144</v>
+      </c>
+      <c r="H79" s="18" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="I79" s="18" t="n">
+        <v>0.5901999999999999</v>
+      </c>
+      <c r="J79" s="18" t="n">
+        <v>0.0888</v>
+      </c>
+      <c r="K79" s="19" t="n">
+        <v>6.017</v>
+      </c>
+      <c r="L79" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" s="19" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N79" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="O79" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P79" s="29" t="n">
-        <v>-1</v>
+      <c r="O79" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P79" s="21" t="n">
+        <v>0.6944</v>
       </c>
     </row>
     <row r="80" ht="17" customHeight="1">
@@ -5174,137 +5150,137 @@
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Edward Cabrera</t>
         </is>
       </c>
       <c r="C80" s="16" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E80" s="17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F80" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G80" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="H80" s="18" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="I80" s="18" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J80" s="18" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="K80" s="19" t="n">
+        <v>5.286</v>
+      </c>
+      <c r="L80" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M80" s="19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N80" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="O80" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P80" s="21" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="81" ht="17" customHeight="1">
+      <c r="A81" s="22" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B81" s="23" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="C81" s="24" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="D81" s="24" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E81" s="25" t="n">
         <v>3.5</v>
       </c>
-      <c r="F80" s="16" t="inlineStr">
+      <c r="F81" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G80" s="16" t="n">
-        <v>-114</v>
-      </c>
-      <c r="H80" s="18" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="I80" s="18" t="n">
-        <v>0.5327</v>
-      </c>
-      <c r="J80" s="18" t="n">
-        <v>0.0513</v>
-      </c>
-      <c r="K80" s="19" t="n">
-        <v>4.252</v>
-      </c>
-      <c r="L80" s="17" t="n">
+      <c r="G81" s="24" t="n">
+        <v>-174</v>
+      </c>
+      <c r="H81" s="26" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="I81" s="26" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="J81" s="26" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="K81" s="27" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="L81" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M80" s="19" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="N80" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="O80" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P80" s="21" t="n">
-        <v>0.8772</v>
-      </c>
-    </row>
-    <row r="81" ht="17" customHeight="1">
-      <c r="A81" s="14" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B81" s="15" t="inlineStr">
-        <is>
-          <t>Michael Wacha</t>
-        </is>
-      </c>
-      <c r="C81" s="16" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="D81" s="16" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="E81" s="17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F81" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G81" s="16" t="n">
-        <v>140</v>
-      </c>
-      <c r="H81" s="18" t="n">
-        <v>0.476</v>
-      </c>
-      <c r="I81" s="18" t="n">
-        <v>0.4167</v>
-      </c>
-      <c r="J81" s="18" t="n">
-        <v>0.0593</v>
-      </c>
-      <c r="K81" s="19" t="n">
-        <v>4.645</v>
-      </c>
-      <c r="L81" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M81" s="19" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N81" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="O81" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P81" s="21" t="n">
-        <v>1.4</v>
+      <c r="M81" s="27" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="N81" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O81" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P81" s="29" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="82" ht="17" customHeight="1">
       <c r="A82" s="22" t="n">
-        <v>46109</v>
+        <v>46111</v>
       </c>
       <c r="B82" s="23" t="inlineStr">
         <is>
-          <t>Will Warren</t>
+          <t>Kyle Harrison</t>
         </is>
       </c>
       <c r="C82" s="24" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D82" s="24" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E82" s="25" t="n">
@@ -5312,32 +5288,32 @@
       </c>
       <c r="F82" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G82" s="24" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H82" s="26" t="n">
-        <v>0.573</v>
+        <v>0.521</v>
       </c>
       <c r="I82" s="26" t="n">
-        <v>0.4762</v>
+        <v>0.4673</v>
       </c>
       <c r="J82" s="26" t="n">
-        <v>0.0968</v>
+        <v>0.0537</v>
       </c>
       <c r="K82" s="27" t="n">
-        <v>5.339</v>
+        <v>4.628</v>
       </c>
       <c r="L82" s="25" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M82" s="27" t="n">
-        <v>0.46</v>
+        <v>0.25</v>
       </c>
       <c r="N82" s="24" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O82" s="28" t="inlineStr">
         <is>
@@ -5349,146 +5325,146 @@
       </c>
     </row>
     <row r="83" ht="17" customHeight="1">
-      <c r="A83" s="22" t="n">
+      <c r="A83" s="14" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>Davis Martin</t>
+        </is>
+      </c>
+      <c r="C83" s="16" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D83" s="16" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E83" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F83" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G83" s="16" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H83" s="18" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="I83" s="18" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="J83" s="18" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="K83" s="19" t="n">
+        <v>4.252</v>
+      </c>
+      <c r="L83" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M83" s="19" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="N83" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O83" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P83" s="21" t="n">
+        <v>0.8772</v>
+      </c>
+    </row>
+    <row r="84" ht="17" customHeight="1">
+      <c r="A84" s="14" t="n">
         <v>46109</v>
       </c>
-      <c r="B83" s="23" t="inlineStr">
-        <is>
-          <t>Jeffrey Springs</t>
-        </is>
-      </c>
-      <c r="C83" s="24" t="inlineStr">
-        <is>
-          <t>OAK</t>
-        </is>
-      </c>
-      <c r="D83" s="24" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="E83" s="25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F83" s="24" t="inlineStr">
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>Michael Wacha</t>
+        </is>
+      </c>
+      <c r="C84" s="16" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="D84" s="16" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E84" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F84" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G83" s="24" t="n">
-        <v>102</v>
-      </c>
-      <c r="H83" s="26" t="n">
-        <v>0.599</v>
-      </c>
-      <c r="I83" s="26" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="J83" s="26" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="K83" s="27" t="n">
-        <v>4.389</v>
-      </c>
-      <c r="L83" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M83" s="27" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="N83" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="O83" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P83" s="29" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="84" ht="17" customHeight="1">
-      <c r="A84" s="22" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B84" s="23" t="inlineStr">
-        <is>
-          <t>Eury Pérez</t>
-        </is>
-      </c>
-      <c r="C84" s="24" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="D84" s="24" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="E84" s="25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F84" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G84" s="24" t="n">
-        <v>-154</v>
-      </c>
-      <c r="H84" s="26" t="n">
-        <v>0.713</v>
-      </c>
-      <c r="I84" s="26" t="n">
-        <v>0.6063</v>
-      </c>
-      <c r="J84" s="26" t="n">
-        <v>0.1067</v>
-      </c>
-      <c r="K84" s="27" t="n">
-        <v>5.311</v>
-      </c>
-      <c r="L84" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M84" s="27" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="N84" s="24" t="n">
-        <v>8</v>
-      </c>
-      <c r="O84" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P84" s="29" t="n">
-        <v>-1</v>
+      <c r="G84" s="16" t="n">
+        <v>140</v>
+      </c>
+      <c r="H84" s="18" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="I84" s="18" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="J84" s="18" t="n">
+        <v>0.0593</v>
+      </c>
+      <c r="K84" s="19" t="n">
+        <v>4.645</v>
+      </c>
+      <c r="L84" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M84" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N84" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O84" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P84" s="21" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="85" ht="17" customHeight="1">
       <c r="A85" s="22" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B85" s="23" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Will Warren</t>
         </is>
       </c>
       <c r="C85" s="24" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="D85" s="24" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E85" s="25" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F85" s="24" t="inlineStr">
         <is>
@@ -5496,28 +5472,28 @@
         </is>
       </c>
       <c r="G85" s="24" t="n">
-        <v>-158</v>
+        <v>110</v>
       </c>
       <c r="H85" s="26" t="n">
-        <v>0.677</v>
+        <v>0.573</v>
       </c>
       <c r="I85" s="26" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.4762</v>
       </c>
       <c r="J85" s="26" t="n">
-        <v>0.0646</v>
+        <v>0.0968</v>
       </c>
       <c r="K85" s="27" t="n">
-        <v>4.869</v>
+        <v>5.339</v>
       </c>
       <c r="L85" s="25" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M85" s="27" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="N85" s="24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O85" s="28" t="inlineStr">
         <is>
@@ -5529,175 +5505,175 @@
       </c>
     </row>
     <row r="86" ht="17" customHeight="1">
-      <c r="A86" s="14" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B86" s="15" t="inlineStr">
-        <is>
-          <t>Robbie Ray</t>
-        </is>
-      </c>
-      <c r="C86" s="16" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="D86" s="16" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="E86" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F86" s="16" t="inlineStr">
+      <c r="A86" s="22" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B86" s="23" t="inlineStr">
+        <is>
+          <t>Jeffrey Springs</t>
+        </is>
+      </c>
+      <c r="C86" s="24" t="inlineStr">
+        <is>
+          <t>OAK</t>
+        </is>
+      </c>
+      <c r="D86" s="24" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E86" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F86" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G86" s="24" t="n">
+        <v>102</v>
+      </c>
+      <c r="H86" s="26" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="I86" s="26" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="J86" s="26" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="K86" s="27" t="n">
+        <v>4.389</v>
+      </c>
+      <c r="L86" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M86" s="27" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N86" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O86" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P86" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="87" ht="17" customHeight="1">
+      <c r="A87" s="22" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B87" s="23" t="inlineStr">
+        <is>
+          <t>Eury Pérez</t>
+        </is>
+      </c>
+      <c r="C87" s="24" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="D87" s="24" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E87" s="25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F87" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G86" s="16" t="n">
-        <v>116</v>
-      </c>
-      <c r="H86" s="18" t="n">
-        <v>0.532</v>
-      </c>
-      <c r="I86" s="18" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J86" s="18" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="K86" s="19" t="n">
-        <v>5.578</v>
-      </c>
-      <c r="L86" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M86" s="19" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="N86" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="O86" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P86" s="21" t="n">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="87" ht="17" customHeight="1">
-      <c r="A87" s="14" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B87" s="15" t="inlineStr">
-        <is>
-          <t>Cam Schlittler</t>
-        </is>
-      </c>
-      <c r="C87" s="16" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="D87" s="16" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="E87" s="17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F87" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G87" s="16" t="n">
-        <v>-128</v>
-      </c>
-      <c r="H87" s="18" t="n">
-        <v>0.659</v>
-      </c>
-      <c r="I87" s="18" t="n">
-        <v>0.5614</v>
-      </c>
-      <c r="J87" s="18" t="n">
-        <v>0.09760000000000001</v>
-      </c>
-      <c r="K87" s="19" t="n">
-        <v>5.818</v>
-      </c>
-      <c r="L87" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M87" s="19" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="N87" s="16" t="n">
+      <c r="G87" s="24" t="n">
+        <v>-154</v>
+      </c>
+      <c r="H87" s="26" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="I87" s="26" t="n">
+        <v>0.6063</v>
+      </c>
+      <c r="J87" s="26" t="n">
+        <v>0.1067</v>
+      </c>
+      <c r="K87" s="27" t="n">
+        <v>5.311</v>
+      </c>
+      <c r="L87" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M87" s="27" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="N87" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="O87" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P87" s="21" t="n">
-        <v>0.7812</v>
+      <c r="O87" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P87" s="29" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="88" ht="17" customHeight="1">
       <c r="A88" s="22" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B88" s="23" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="C88" s="24" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D88" s="24" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E88" s="25" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="F88" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G88" s="24" t="n">
-        <v>114</v>
+        <v>-158</v>
       </c>
       <c r="H88" s="26" t="n">
-        <v>0.587</v>
+        <v>0.677</v>
       </c>
       <c r="I88" s="26" t="n">
-        <v>0.4673</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J88" s="26" t="n">
-        <v>0.1197</v>
+        <v>0.0646</v>
       </c>
       <c r="K88" s="27" t="n">
-        <v>6.417</v>
+        <v>4.869</v>
       </c>
       <c r="L88" s="25" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M88" s="27" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="N88" s="24" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O88" s="28" t="inlineStr">
         <is>
@@ -5709,82 +5685,82 @@
       </c>
     </row>
     <row r="89" ht="17" customHeight="1">
-      <c r="A89" s="22" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B89" s="23" t="inlineStr">
-        <is>
-          <t>Shane Smith</t>
-        </is>
-      </c>
-      <c r="C89" s="24" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="D89" s="24" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="E89" s="25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F89" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G89" s="24" t="n">
-        <v>-114</v>
-      </c>
-      <c r="H89" s="26" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="I89" s="26" t="n">
-        <v>0.5327</v>
-      </c>
-      <c r="J89" s="26" t="n">
-        <v>0.0743</v>
-      </c>
-      <c r="K89" s="27" t="n">
-        <v>5.338</v>
-      </c>
-      <c r="L89" s="25" t="n">
+      <c r="A89" s="14" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>Robbie Ray</t>
+        </is>
+      </c>
+      <c r="C89" s="16" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="D89" s="16" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E89" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F89" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G89" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="H89" s="18" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="I89" s="18" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J89" s="18" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="K89" s="19" t="n">
+        <v>5.578</v>
+      </c>
+      <c r="L89" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="M89" s="27" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N89" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="O89" s="28" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P89" s="29" t="n">
-        <v>-1</v>
+      <c r="M89" s="19" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N89" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O89" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P89" s="21" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="90" ht="17" customHeight="1">
       <c r="A90" s="14" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>José Soriano</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="C90" s="16" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E90" s="17" t="n">
@@ -5796,28 +5772,28 @@
         </is>
       </c>
       <c r="G90" s="16" t="n">
-        <v>108</v>
+        <v>-128</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.659</v>
       </c>
       <c r="I90" s="18" t="n">
-        <v>0.4808</v>
+        <v>0.5614</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="K90" s="19" t="n">
-        <v>5.163</v>
+        <v>5.818</v>
       </c>
       <c r="L90" s="17" t="n">
         <v>1</v>
       </c>
       <c r="M90" s="19" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N90" s="16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O90" s="20" t="inlineStr">
         <is>
@@ -5825,67 +5801,67 @@
         </is>
       </c>
       <c r="P90" s="21" t="n">
-        <v>1.08</v>
+        <v>0.7812</v>
       </c>
     </row>
     <row r="91" ht="17" customHeight="1">
-      <c r="A91" s="14" t="n">
+      <c r="A91" s="22" t="n">
         <v>46107</v>
       </c>
-      <c r="B91" s="15" t="inlineStr">
-        <is>
-          <t>Tarik Skubal</t>
-        </is>
-      </c>
-      <c r="C91" s="16" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="D91" s="16" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E91" s="17" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F91" s="16" t="inlineStr">
+      <c r="B91" s="23" t="inlineStr">
+        <is>
+          <t>Hunter Brown</t>
+        </is>
+      </c>
+      <c r="C91" s="24" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="D91" s="24" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E91" s="25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F91" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G91" s="16" t="n">
-        <v>-172</v>
-      </c>
-      <c r="H91" s="18" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="I91" s="18" t="n">
-        <v>0.6324</v>
-      </c>
-      <c r="J91" s="18" t="n">
-        <v>0.1346</v>
-      </c>
-      <c r="K91" s="19" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="L91" s="17" t="n">
+      <c r="G91" s="24" t="n">
+        <v>114</v>
+      </c>
+      <c r="H91" s="26" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="I91" s="26" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="J91" s="26" t="n">
+        <v>0.1197</v>
+      </c>
+      <c r="K91" s="27" t="n">
+        <v>6.417</v>
+      </c>
+      <c r="L91" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="M91" s="19" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="N91" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="O91" s="20" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P91" s="21" t="n">
-        <v>0.5814</v>
+      <c r="M91" s="27" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="N91" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="O91" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P91" s="29" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="92" ht="17" customHeight="1">
@@ -5894,50 +5870,50 @@
       </c>
       <c r="B92" s="23" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Shane Smith</t>
         </is>
       </c>
       <c r="C92" s="24" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D92" s="24" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="D92" s="24" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="E92" s="25" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F92" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G92" s="24" t="n">
-        <v>124</v>
+        <v>-114</v>
       </c>
       <c r="H92" s="26" t="n">
-        <v>0.52</v>
+        <v>0.607</v>
       </c>
       <c r="I92" s="26" t="n">
-        <v>0.4464</v>
+        <v>0.5327</v>
       </c>
       <c r="J92" s="26" t="n">
-        <v>0.0736</v>
+        <v>0.0743</v>
       </c>
       <c r="K92" s="27" t="n">
-        <v>5.5</v>
+        <v>5.338</v>
       </c>
       <c r="L92" s="25" t="n">
         <v>0.5</v>
       </c>
       <c r="M92" s="27" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="N92" s="24" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O92" s="28" t="inlineStr">
         <is>
@@ -5954,50 +5930,50 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>José Soriano</t>
         </is>
       </c>
       <c r="C93" s="16" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="D93" s="16" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E93" s="17" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F93" s="16" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G93" s="16" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H93" s="18" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I93" s="18" t="n">
-        <v>0.4762</v>
+        <v>0.4808</v>
       </c>
       <c r="J93" s="18" t="n">
-        <v>0.0638</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="K93" s="19" t="n">
-        <v>5.548</v>
+        <v>5.163</v>
       </c>
       <c r="L93" s="17" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M93" s="19" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="N93" s="16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O93" s="20" t="inlineStr">
         <is>
@@ -6005,7 +5981,7 @@
         </is>
       </c>
       <c r="P93" s="21" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="94" ht="17" customHeight="1">
@@ -6014,21 +5990,21 @@
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>Andrew Abbott</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="C94" s="16" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D94" s="16" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E94" s="17" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="F94" s="16" t="inlineStr">
         <is>
@@ -6036,28 +6012,28 @@
         </is>
       </c>
       <c r="G94" s="16" t="n">
-        <v>120</v>
+        <v>-172</v>
       </c>
       <c r="H94" s="18" t="n">
-        <v>0.509</v>
+        <v>0.767</v>
       </c>
       <c r="I94" s="18" t="n">
-        <v>0.4545</v>
+        <v>0.6324</v>
       </c>
       <c r="J94" s="18" t="n">
-        <v>0.0545</v>
+        <v>0.1346</v>
       </c>
       <c r="K94" s="19" t="n">
-        <v>4.814</v>
+        <v>5.68</v>
       </c>
       <c r="L94" s="17" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M94" s="19" t="n">
-        <v>0.25</v>
+        <v>0.92</v>
       </c>
       <c r="N94" s="16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O94" s="20" t="inlineStr">
         <is>
@@ -6065,7 +6041,7 @@
         </is>
       </c>
       <c r="P94" s="21" t="n">
-        <v>1.2</v>
+        <v>0.5814</v>
       </c>
     </row>
     <row r="95" ht="17" customHeight="1">
@@ -6074,57 +6050,237 @@
       </c>
       <c r="B95" s="23" t="inlineStr">
         <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="C95" s="24" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D95" s="24" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E95" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F95" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G95" s="24" t="n">
+        <v>124</v>
+      </c>
+      <c r="H95" s="26" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I95" s="26" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="J95" s="26" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="K95" s="27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L95" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M95" s="27" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N95" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="O95" s="28" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P95" s="29" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="96" ht="17" customHeight="1">
+      <c r="A96" s="14" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B96" s="15" t="inlineStr">
+        <is>
+          <t>Nick Pivetta</t>
+        </is>
+      </c>
+      <c r="C96" s="16" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D96" s="16" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="E96" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F96" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G96" s="16" t="n">
+        <v>110</v>
+      </c>
+      <c r="H96" s="18" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I96" s="18" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="J96" s="18" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="K96" s="19" t="n">
+        <v>5.548</v>
+      </c>
+      <c r="L96" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M96" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N96" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O96" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P96" s="21" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="97" ht="17" customHeight="1">
+      <c r="A97" s="14" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B97" s="15" t="inlineStr">
+        <is>
+          <t>Andrew Abbott</t>
+        </is>
+      </c>
+      <c r="C97" s="16" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="D97" s="16" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="E97" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F97" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G97" s="16" t="n">
+        <v>120</v>
+      </c>
+      <c r="H97" s="18" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="I97" s="18" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="J97" s="18" t="n">
+        <v>0.0545</v>
+      </c>
+      <c r="K97" s="19" t="n">
+        <v>4.814</v>
+      </c>
+      <c r="L97" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M97" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N97" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O97" s="20" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P97" s="21" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="98" ht="17" customHeight="1">
+      <c r="A98" s="22" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B98" s="23" t="inlineStr">
+        <is>
           <t>Matthew Boyd</t>
         </is>
       </c>
-      <c r="C95" s="24" t="inlineStr">
+      <c r="C98" s="24" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="D95" s="24" t="inlineStr">
+      <c r="D98" s="24" t="inlineStr">
         <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E95" s="25" t="n">
+      <c r="E98" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F95" s="24" t="inlineStr">
+      <c r="F98" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G95" s="24" t="n">
+      <c r="G98" s="24" t="n">
         <v>132</v>
       </c>
-      <c r="H95" s="26" t="n">
+      <c r="H98" s="26" t="n">
         <v>0.59</v>
       </c>
-      <c r="I95" s="26" t="n">
+      <c r="I98" s="26" t="n">
         <v>0.431</v>
       </c>
-      <c r="J95" s="26" t="n">
+      <c r="J98" s="26" t="n">
         <v>0.159</v>
       </c>
-      <c r="K95" s="27" t="n">
+      <c r="K98" s="27" t="n">
         <v>4.258</v>
       </c>
-      <c r="L95" s="25" t="n">
+      <c r="L98" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M95" s="27" t="n">
+      <c r="M98" s="27" t="n">
         <v>0.7</v>
       </c>
-      <c r="N95" s="24" t="n">
+      <c r="N98" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="O95" s="28" t="inlineStr">
+      <c r="O98" s="28" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P95" s="29" t="n">
+      <c r="P98" s="29" t="n">
         <v>-1</v>
       </c>
     </row>

--- a/bet_log.xlsx
+++ b/bet_log.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P101"/>
+  <dimension ref="A1:P100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -687,7 +687,7 @@
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>91</v>
@@ -828,16 +828,16 @@
         </is>
       </c>
       <c r="G6" s="8" t="n">
-        <v>-125</v>
+        <v>-122</v>
       </c>
       <c r="H6" s="10" t="n">
         <v>0.615</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.5556</v>
+        <v>0.5495</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.0594</v>
+        <v>0.0655</v>
       </c>
       <c r="K6" s="11" t="n">
         <v>6.497</v>
@@ -846,7 +846,7 @@
         <v>0.5</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="N6" s="8" t="inlineStr"/>
       <c r="O6" s="12" t="inlineStr"/>
@@ -905,56 +905,64 @@
       <c r="P7" s="13" t="inlineStr"/>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>46121</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Max Meyer</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="n">
+      <c r="A8" s="14" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Joey Cantillo</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="n">
         <v>5.5</v>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G8" s="8" t="n">
-        <v>-102</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>0.653</v>
-      </c>
-      <c r="I8" s="10" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="J8" s="10" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="K8" s="11" t="n">
-        <v>4.816</v>
-      </c>
-      <c r="L8" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M8" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N8" s="8" t="inlineStr"/>
-      <c r="O8" s="12" t="inlineStr"/>
-      <c r="P8" s="13" t="inlineStr"/>
+      <c r="G8" s="16" t="n">
+        <v>-154</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>0.6063</v>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>0.0727</v>
+      </c>
+      <c r="K8" s="19" t="n">
+        <v>4.665</v>
+      </c>
+      <c r="L8" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M8" s="19" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N8" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="O8" s="20" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P8" s="21" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="14" t="n">
@@ -962,50 +970,50 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Joey Cantillo</t>
+          <t>Colin Rea</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E9" s="17" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G9" s="16" t="n">
-        <v>-154</v>
+        <v>114</v>
       </c>
       <c r="H9" s="18" t="n">
-        <v>0.679</v>
+        <v>0.674</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>0.6063</v>
+        <v>0.4673</v>
       </c>
       <c r="J9" s="18" t="n">
-        <v>0.0727</v>
+        <v>0.2067</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>4.665</v>
+        <v>4.888</v>
       </c>
       <c r="L9" s="17" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>0.46</v>
+        <v>0.97</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O9" s="20" t="inlineStr">
         <is>
@@ -1017,123 +1025,123 @@
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="14" t="n">
+      <c r="A10" s="22" t="n">
         <v>46120</v>
       </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>Colin Rea</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="n">
-        <v>114</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>0.674</v>
-      </c>
-      <c r="I10" s="18" t="n">
-        <v>0.4673</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>0.2067</v>
-      </c>
-      <c r="K10" s="19" t="n">
-        <v>4.888</v>
-      </c>
-      <c r="L10" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" s="19" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="N10" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" s="20" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>Michael King</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H10" s="26" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="I10" s="26" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="J10" s="26" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="K10" s="27" t="n">
+        <v>4.885</v>
+      </c>
+      <c r="L10" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N10" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P10" s="29" t="n">
+        <v>0.9804</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="14" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Tyler Mahle</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>0.0784</v>
+      </c>
+      <c r="K11" s="19" t="n">
+        <v>4.033</v>
+      </c>
+      <c r="L11" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="19" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="N11" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O11" s="20" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P10" s="21" t="n">
+      <c r="P11" s="21" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="22" t="n">
-        <v>46120</v>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>Michael King</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="D11" s="24" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="E11" s="25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F11" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G11" s="24" t="n">
-        <v>-102</v>
-      </c>
-      <c r="H11" s="26" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="I11" s="26" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="J11" s="26" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="K11" s="27" t="n">
-        <v>4.885</v>
-      </c>
-      <c r="L11" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M11" s="27" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="N11" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="O11" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P11" s="29" t="n">
-        <v>0.9804</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
@@ -1142,17 +1150,17 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E12" s="17" t="n">
@@ -1160,32 +1168,32 @@
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G12" s="16" t="n">
-        <v>-125</v>
+        <v>124</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>0.634</v>
+        <v>0.521</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>0.5556</v>
+        <v>0.4464</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>0.0784</v>
+        <v>0.0746</v>
       </c>
       <c r="K12" s="19" t="n">
-        <v>4.033</v>
+        <v>4.922</v>
       </c>
       <c r="L12" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M12" s="19" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N12" s="16" t="n">
         <v>1</v>
-      </c>
-      <c r="M12" s="19" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="N12" s="16" t="n">
-        <v>6</v>
       </c>
       <c r="O12" s="20" t="inlineStr">
         <is>
@@ -1197,183 +1205,183 @@
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="14" t="n">
+      <c r="A13" s="22" t="n">
         <v>46120</v>
       </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>Cristian Javier</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="n">
-        <v>124</v>
-      </c>
-      <c r="H13" s="18" t="n">
-        <v>0.521</v>
-      </c>
-      <c r="I13" s="18" t="n">
-        <v>0.4464</v>
-      </c>
-      <c r="J13" s="18" t="n">
-        <v>0.0746</v>
-      </c>
-      <c r="K13" s="19" t="n">
-        <v>4.922</v>
-      </c>
-      <c r="L13" s="17" t="n">
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>Sean Burke</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="n">
+        <v>110</v>
+      </c>
+      <c r="H13" s="26" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="I13" s="26" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="J13" s="26" t="n">
+        <v>0.1728</v>
+      </c>
+      <c r="K13" s="27" t="n">
+        <v>4.876</v>
+      </c>
+      <c r="L13" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="N13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P13" s="29" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="14" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Dylan Cease</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="n">
+        <v>110</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>0.0698</v>
+      </c>
+      <c r="K14" s="19" t="n">
+        <v>6.326</v>
+      </c>
+      <c r="L14" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="M13" s="19" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="N13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" s="20" t="inlineStr">
+      <c r="M14" s="19" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N14" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="O14" s="20" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P13" s="21" t="n">
+      <c r="P14" s="21" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="22" t="n">
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="22" t="n">
         <v>46120</v>
       </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>Sean Burke</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="E14" s="25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F14" s="24" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>Eury Pérez</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G14" s="24" t="n">
-        <v>110</v>
-      </c>
-      <c r="H14" s="26" t="n">
-        <v>0.649</v>
-      </c>
-      <c r="I14" s="26" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="J14" s="26" t="n">
-        <v>0.1728</v>
-      </c>
-      <c r="K14" s="27" t="n">
-        <v>4.876</v>
-      </c>
-      <c r="L14" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" s="27" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="N14" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="O14" s="28" t="inlineStr">
+      <c r="G15" s="24" t="n">
+        <v>-132</v>
+      </c>
+      <c r="H15" s="26" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="I15" s="26" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="J15" s="26" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="K15" s="27" t="n">
+        <v>5.853</v>
+      </c>
+      <c r="L15" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N15" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="O15" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P14" s="29" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="14" t="n">
-        <v>46120</v>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>Dylan Cease</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="n">
-        <v>110</v>
-      </c>
-      <c r="H15" s="18" t="n">
-        <v>0.546</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <v>0.0698</v>
-      </c>
-      <c r="K15" s="19" t="n">
-        <v>6.326</v>
-      </c>
-      <c r="L15" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M15" s="19" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="N15" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="O15" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P15" s="21" t="n">
-        <v>-1</v>
+      <c r="P15" s="29" t="n">
+        <v>0.7576000000000001</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1382,50 +1390,50 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Eury Pérez</t>
+          <t>Michael Lorenzen</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E16" s="25" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="F16" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G16" s="24" t="n">
-        <v>-132</v>
+        <v>-130</v>
       </c>
       <c r="H16" s="26" t="n">
-        <v>0.635</v>
+        <v>0.63</v>
       </c>
       <c r="I16" s="26" t="n">
-        <v>0.569</v>
+        <v>0.5652</v>
       </c>
       <c r="J16" s="26" t="n">
-        <v>0.066</v>
+        <v>0.0648</v>
       </c>
       <c r="K16" s="27" t="n">
-        <v>5.853</v>
+        <v>4.329</v>
       </c>
       <c r="L16" s="25" t="n">
         <v>0.5</v>
       </c>
       <c r="M16" s="27" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="N16" s="24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O16" s="28" t="inlineStr">
         <is>
@@ -1433,479 +1441,479 @@
         </is>
       </c>
       <c r="P16" s="29" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.7692</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="22" t="n">
+      <c r="A17" s="14" t="n">
         <v>46120</v>
       </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>Michael Lorenzen</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="n">
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Michael McGreevy</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="n">
         <v>3.5</v>
       </c>
-      <c r="F17" s="24" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G17" s="24" t="n">
-        <v>-130</v>
-      </c>
-      <c r="H17" s="26" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="I17" s="26" t="n">
-        <v>0.5652</v>
-      </c>
-      <c r="J17" s="26" t="n">
-        <v>0.0648</v>
-      </c>
-      <c r="K17" s="27" t="n">
-        <v>4.329</v>
-      </c>
-      <c r="L17" s="25" t="n">
+      <c r="G17" s="16" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H17" s="18" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="J17" s="18" t="n">
+        <v>0.0533</v>
+      </c>
+      <c r="K17" s="19" t="n">
+        <v>4.248</v>
+      </c>
+      <c r="L17" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="M17" s="27" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="N17" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="O17" s="28" t="inlineStr">
+      <c r="M17" s="19" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N17" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="20" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P17" s="21" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="22" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>Garrett Crochet</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H18" s="26" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="I18" s="26" t="n">
+        <v>0.5413</v>
+      </c>
+      <c r="J18" s="26" t="n">
+        <v>0.0527</v>
+      </c>
+      <c r="K18" s="27" t="n">
+        <v>7.154</v>
+      </c>
+      <c r="L18" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N18" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="O18" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P17" s="29" t="n">
-        <v>0.7692</v>
-      </c>
-    </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="14" t="n">
-        <v>46120</v>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>Michael McGreevy</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="P18" s="29" t="n">
+        <v>0.8475</v>
+      </c>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="14" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Javier Assad</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="n">
+        <v>-108</v>
+      </c>
+      <c r="H19" s="18" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="I19" s="18" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="J19" s="18" t="n">
+        <v>0.06279999999999999</v>
+      </c>
+      <c r="K19" s="19" t="n">
+        <v>4.073</v>
+      </c>
+      <c r="L19" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M19" s="19" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N19" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O19" s="20" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P19" s="21" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="22" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>Cade Cavalli</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
         <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="n">
-        <v>-114</v>
-      </c>
-      <c r="H18" s="18" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="I18" s="18" t="n">
-        <v>0.5327</v>
-      </c>
-      <c r="J18" s="18" t="n">
-        <v>0.0533</v>
-      </c>
-      <c r="K18" s="19" t="n">
-        <v>4.248</v>
-      </c>
-      <c r="L18" s="17" t="n">
+      <c r="E20" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H20" s="26" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="I20" s="26" t="n">
+        <v>0.5283</v>
+      </c>
+      <c r="J20" s="26" t="n">
+        <v>0.0737</v>
+      </c>
+      <c r="K20" s="27" t="n">
+        <v>4.074</v>
+      </c>
+      <c r="L20" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M18" s="19" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="N18" s="16" t="n">
+      <c r="M20" s="27" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="N20" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O20" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P20" s="29" t="n">
+        <v>0.8929</v>
+      </c>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="14" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G21" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="H21" s="18" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="I21" s="18" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J21" s="18" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="K21" s="19" t="n">
+        <v>6.457</v>
+      </c>
+      <c r="L21" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="O18" s="20" t="inlineStr">
+      <c r="M21" s="19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N21" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="O21" s="20" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P18" s="21" t="n">
+      <c r="P21" s="21" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="22" t="n">
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="6" t="n">
         <v>46119</v>
       </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>Garrett Crochet</t>
-        </is>
-      </c>
-      <c r="C19" s="24" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="E19" s="25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F19" s="24" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G19" s="24" t="n">
-        <v>-118</v>
-      </c>
-      <c r="H19" s="26" t="n">
-        <v>0.594</v>
-      </c>
-      <c r="I19" s="26" t="n">
-        <v>0.5413</v>
-      </c>
-      <c r="J19" s="26" t="n">
-        <v>0.0527</v>
-      </c>
-      <c r="K19" s="27" t="n">
-        <v>7.154</v>
-      </c>
-      <c r="L19" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M19" s="27" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="N19" s="24" t="n">
-        <v>7</v>
-      </c>
-      <c r="O19" s="28" t="inlineStr">
+      <c r="G22" s="8" t="n">
+        <v>-104</v>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="I22" s="10" t="n">
+        <v>0.5098</v>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>0.0892</v>
+      </c>
+      <c r="K22" s="11" t="n">
+        <v>4.186</v>
+      </c>
+      <c r="L22" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="11" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N22" s="8" t="inlineStr"/>
+      <c r="O22" s="12" t="inlineStr"/>
+      <c r="P22" s="13" t="inlineStr"/>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="14" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>Nick Pivetta</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G23" s="16" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H23" s="18" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="I23" s="18" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="J23" s="18" t="n">
+        <v>0.0914</v>
+      </c>
+      <c r="K23" s="19" t="n">
+        <v>5.709</v>
+      </c>
+      <c r="L23" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="19" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N23" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="O23" s="20" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P23" s="21" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="22" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>Kevin Gausman</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E24" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="n">
+        <v>154</v>
+      </c>
+      <c r="H24" s="26" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="I24" s="26" t="n">
+        <v>0.3937</v>
+      </c>
+      <c r="J24" s="26" t="n">
+        <v>0.1073</v>
+      </c>
+      <c r="K24" s="27" t="n">
+        <v>5.736</v>
+      </c>
+      <c r="L24" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M24" s="27" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="N24" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="O24" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P19" s="29" t="n">
-        <v>0.8475</v>
-      </c>
-    </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="14" t="n">
-        <v>46119</v>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>Javier Assad</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="n">
-        <v>-108</v>
-      </c>
-      <c r="H20" s="18" t="n">
-        <v>0.582</v>
-      </c>
-      <c r="I20" s="18" t="n">
-        <v>0.5192</v>
-      </c>
-      <c r="J20" s="18" t="n">
-        <v>0.06279999999999999</v>
-      </c>
-      <c r="K20" s="19" t="n">
-        <v>4.073</v>
-      </c>
-      <c r="L20" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M20" s="19" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="N20" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="O20" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P20" s="21" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="22" t="n">
-        <v>46119</v>
-      </c>
-      <c r="B21" s="23" t="inlineStr">
-        <is>
-          <t>Cade Cavalli</t>
-        </is>
-      </c>
-      <c r="C21" s="24" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="E21" s="25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F21" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G21" s="24" t="n">
-        <v>-112</v>
-      </c>
-      <c r="H21" s="26" t="n">
-        <v>0.602</v>
-      </c>
-      <c r="I21" s="26" t="n">
-        <v>0.5283</v>
-      </c>
-      <c r="J21" s="26" t="n">
-        <v>0.0737</v>
-      </c>
-      <c r="K21" s="27" t="n">
-        <v>4.074</v>
-      </c>
-      <c r="L21" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M21" s="27" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="N21" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="O21" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P21" s="29" t="n">
-        <v>0.8929</v>
-      </c>
-    </row>
-    <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="14" t="n">
-        <v>46119</v>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>Jacob Misiorowski</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="n">
-        <v>116</v>
-      </c>
-      <c r="H22" s="18" t="n">
-        <v>0.539</v>
-      </c>
-      <c r="I22" s="18" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J22" s="18" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="K22" s="19" t="n">
-        <v>6.457</v>
-      </c>
-      <c r="L22" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" s="19" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="N22" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="O22" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P22" s="21" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="6" t="n">
-        <v>46119</v>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Drew Rasmussen</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="n">
-        <v>-104</v>
-      </c>
-      <c r="H23" s="10" t="n">
-        <v>0.599</v>
-      </c>
-      <c r="I23" s="10" t="n">
-        <v>0.5098</v>
-      </c>
-      <c r="J23" s="10" t="n">
-        <v>0.0892</v>
-      </c>
-      <c r="K23" s="11" t="n">
-        <v>4.186</v>
-      </c>
-      <c r="L23" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" s="11" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="N23" s="8" t="inlineStr"/>
-      <c r="O23" s="12" t="inlineStr"/>
-      <c r="P23" s="13" t="inlineStr"/>
-    </row>
-    <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="14" t="n">
-        <v>46119</v>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>Nick Pivetta</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="n">
-        <v>-125</v>
-      </c>
-      <c r="H24" s="18" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="I24" s="18" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="J24" s="18" t="n">
-        <v>0.0914</v>
-      </c>
-      <c r="K24" s="19" t="n">
-        <v>5.709</v>
-      </c>
-      <c r="L24" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" s="19" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="N24" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="O24" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P24" s="21" t="n">
-        <v>-1</v>
+      <c r="P24" s="29" t="n">
+        <v>1.54</v>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
@@ -1914,47 +1922,47 @@
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>Kevin Gausman</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E25" s="25" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G25" s="24" t="n">
-        <v>154</v>
+        <v>-114</v>
       </c>
       <c r="H25" s="26" t="n">
-        <v>0.501</v>
+        <v>0.644</v>
       </c>
       <c r="I25" s="26" t="n">
-        <v>0.3937</v>
+        <v>0.5327</v>
       </c>
       <c r="J25" s="26" t="n">
-        <v>0.1073</v>
+        <v>0.1113</v>
       </c>
       <c r="K25" s="27" t="n">
-        <v>5.736</v>
+        <v>5.746</v>
       </c>
       <c r="L25" s="25" t="n">
         <v>1.5</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="N25" s="24" t="n">
         <v>5</v>
@@ -1965,7 +1973,7 @@
         </is>
       </c>
       <c r="P25" s="29" t="n">
-        <v>1.54</v>
+        <v>0.8772</v>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
@@ -1974,50 +1982,50 @@
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E26" s="25" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G26" s="24" t="n">
-        <v>-114</v>
+        <v>-110</v>
       </c>
       <c r="H26" s="26" t="n">
-        <v>0.644</v>
+        <v>0.701</v>
       </c>
       <c r="I26" s="26" t="n">
-        <v>0.5327</v>
+        <v>0.5238</v>
       </c>
       <c r="J26" s="26" t="n">
-        <v>0.1113</v>
+        <v>0.1772</v>
       </c>
       <c r="K26" s="27" t="n">
-        <v>5.746</v>
+        <v>5.249</v>
       </c>
       <c r="L26" s="25" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>0.6</v>
+        <v>0.93</v>
       </c>
       <c r="N26" s="24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O26" s="28" t="inlineStr">
         <is>
@@ -2025,67 +2033,67 @@
         </is>
       </c>
       <c r="P26" s="29" t="n">
-        <v>0.8772</v>
+        <v>0.9091</v>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="22" t="n">
-        <v>46119</v>
-      </c>
-      <c r="B27" s="23" t="inlineStr">
-        <is>
-          <t>Paul Skenes</t>
-        </is>
-      </c>
-      <c r="C27" s="24" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="D27" s="24" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E27" s="25" t="n">
+      <c r="A27" s="14" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Joe Ryan</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="n">
         <v>6.5</v>
       </c>
-      <c r="F27" s="24" t="inlineStr">
+      <c r="F27" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G27" s="24" t="n">
-        <v>-110</v>
-      </c>
-      <c r="H27" s="26" t="n">
-        <v>0.701</v>
-      </c>
-      <c r="I27" s="26" t="n">
-        <v>0.5238</v>
-      </c>
-      <c r="J27" s="26" t="n">
-        <v>0.1772</v>
-      </c>
-      <c r="K27" s="27" t="n">
-        <v>5.249</v>
-      </c>
-      <c r="L27" s="25" t="n">
+      <c r="G27" s="16" t="n">
+        <v>-132</v>
+      </c>
+      <c r="H27" s="18" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="I27" s="18" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="J27" s="18" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="K27" s="19" t="n">
+        <v>5.221</v>
+      </c>
+      <c r="L27" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="M27" s="27" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="N27" s="24" t="n">
-        <v>6</v>
-      </c>
-      <c r="O27" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P27" s="29" t="n">
-        <v>0.9091</v>
+      <c r="M27" s="19" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N27" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O27" s="20" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P27" s="21" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
@@ -2154,50 +2162,50 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Joe Ryan</t>
+          <t>Andre Pallante</t>
         </is>
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E29" s="17" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G29" s="16" t="n">
-        <v>-132</v>
+        <v>-112</v>
       </c>
       <c r="H29" s="18" t="n">
-        <v>0.72</v>
+        <v>0.614</v>
       </c>
       <c r="I29" s="18" t="n">
-        <v>0.569</v>
+        <v>0.5283</v>
       </c>
       <c r="J29" s="18" t="n">
-        <v>0.151</v>
+        <v>0.0857</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>5.221</v>
+        <v>4.355</v>
       </c>
       <c r="L29" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" s="19" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N29" s="16" t="n">
         <v>2</v>
-      </c>
-      <c r="M29" s="19" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="N29" s="16" t="n">
-        <v>7</v>
       </c>
       <c r="O29" s="20" t="inlineStr">
         <is>
@@ -2210,25 +2218,25 @@
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="14" t="n">
-        <v>46118</v>
+        <v>46117</v>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Andre Pallante</t>
+          <t>Simeon Woods Richardson</t>
         </is>
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E30" s="17" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F30" s="16" t="inlineStr">
         <is>
@@ -2236,28 +2244,28 @@
         </is>
       </c>
       <c r="G30" s="16" t="n">
-        <v>-112</v>
+        <v>106</v>
       </c>
       <c r="H30" s="18" t="n">
-        <v>0.614</v>
+        <v>0.547</v>
       </c>
       <c r="I30" s="18" t="n">
-        <v>0.5283</v>
+        <v>0.4854</v>
       </c>
       <c r="J30" s="18" t="n">
-        <v>0.0857</v>
+        <v>0.0616</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>4.355</v>
+        <v>5.027</v>
       </c>
       <c r="L30" s="17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="N30" s="16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O30" s="20" t="inlineStr">
         <is>
@@ -2274,21 +2282,21 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Simeon Woods Richardson</t>
+          <t>Keider Montero</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
@@ -2296,28 +2304,28 @@
         </is>
       </c>
       <c r="G31" s="16" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H31" s="18" t="n">
-        <v>0.547</v>
+        <v>0.546</v>
       </c>
       <c r="I31" s="18" t="n">
-        <v>0.4854</v>
+        <v>0.4808</v>
       </c>
       <c r="J31" s="18" t="n">
-        <v>0.0616</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>5.027</v>
+        <v>3.968</v>
       </c>
       <c r="L31" s="17" t="n">
         <v>0.5</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="N31" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O31" s="20" t="inlineStr">
         <is>
@@ -2334,50 +2342,50 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Keider Montero</t>
+          <t>Jack Leiter</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E32" s="17" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="F32" s="16" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G32" s="16" t="n">
-        <v>108</v>
+        <v>-146</v>
       </c>
       <c r="H32" s="18" t="n">
-        <v>0.546</v>
+        <v>0.659</v>
       </c>
       <c r="I32" s="18" t="n">
-        <v>0.4808</v>
+        <v>0.5935</v>
       </c>
       <c r="J32" s="18" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0655</v>
       </c>
       <c r="K32" s="19" t="n">
-        <v>3.968</v>
+        <v>5.601</v>
       </c>
       <c r="L32" s="17" t="n">
         <v>0.5</v>
       </c>
       <c r="M32" s="19" t="n">
-        <v>0.31</v>
+        <v>0.4</v>
       </c>
       <c r="N32" s="16" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O32" s="20" t="inlineStr">
         <is>
@@ -2389,63 +2397,63 @@
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="22" t="n">
         <v>46117</v>
       </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>Jack Leiter</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>Luis Castillo</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G33" s="16" t="n">
-        <v>-146</v>
-      </c>
-      <c r="H33" s="18" t="n">
-        <v>0.659</v>
-      </c>
-      <c r="I33" s="18" t="n">
-        <v>0.5935</v>
-      </c>
-      <c r="J33" s="18" t="n">
-        <v>0.0655</v>
-      </c>
-      <c r="K33" s="19" t="n">
-        <v>5.601</v>
-      </c>
-      <c r="L33" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M33" s="19" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N33" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="O33" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P33" s="21" t="n">
-        <v>-1</v>
+      <c r="G33" s="24" t="n">
+        <v>128</v>
+      </c>
+      <c r="H33" s="26" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="I33" s="26" t="n">
+        <v>0.4386</v>
+      </c>
+      <c r="J33" s="26" t="n">
+        <v>0.0794</v>
+      </c>
+      <c r="K33" s="27" t="n">
+        <v>5.702</v>
+      </c>
+      <c r="L33" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="27" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N33" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="O33" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P33" s="29" t="n">
+        <v>1.28</v>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
@@ -2454,47 +2462,47 @@
       </c>
       <c r="B34" s="23" t="inlineStr">
         <is>
-          <t>Luis Castillo</t>
+          <t>Taijuan Walker</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E34" s="25" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F34" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G34" s="24" t="n">
-        <v>128</v>
+        <v>-106</v>
       </c>
       <c r="H34" s="26" t="n">
-        <v>0.518</v>
+        <v>0.6</v>
       </c>
       <c r="I34" s="26" t="n">
-        <v>0.4386</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="J34" s="26" t="n">
-        <v>0.0794</v>
+        <v>0.0854</v>
       </c>
       <c r="K34" s="27" t="n">
-        <v>5.702</v>
+        <v>4.331</v>
       </c>
       <c r="L34" s="25" t="n">
         <v>1</v>
       </c>
       <c r="M34" s="27" t="n">
-        <v>0.35</v>
+        <v>0.44</v>
       </c>
       <c r="N34" s="24" t="n">
         <v>4</v>
@@ -2505,67 +2513,67 @@
         </is>
       </c>
       <c r="P34" s="29" t="n">
-        <v>1.28</v>
+        <v>0.9434</v>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="22" t="n">
+      <c r="A35" s="14" t="n">
         <v>46117</v>
       </c>
-      <c r="B35" s="23" t="inlineStr">
-        <is>
-          <t>Taijuan Walker</t>
-        </is>
-      </c>
-      <c r="C35" s="24" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="D35" s="24" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="E35" s="25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F35" s="24" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>Eric Lauer</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G35" s="24" t="n">
-        <v>-106</v>
-      </c>
-      <c r="H35" s="26" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I35" s="26" t="n">
-        <v>0.5145999999999999</v>
-      </c>
-      <c r="J35" s="26" t="n">
-        <v>0.0854</v>
-      </c>
-      <c r="K35" s="27" t="n">
-        <v>4.331</v>
-      </c>
-      <c r="L35" s="25" t="n">
+      <c r="G35" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="H35" s="18" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="I35" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J35" s="18" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="K35" s="19" t="n">
+        <v>5.457</v>
+      </c>
+      <c r="L35" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="M35" s="27" t="n">
+      <c r="M35" s="19" t="n">
         <v>0.44</v>
       </c>
-      <c r="N35" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="O35" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P35" s="29" t="n">
-        <v>0.9434</v>
+      <c r="N35" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="20" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P35" s="21" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
@@ -2574,17 +2582,17 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>Eric Lauer</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E36" s="17" t="n">
@@ -2596,28 +2604,28 @@
         </is>
       </c>
       <c r="G36" s="16" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H36" s="18" t="n">
-        <v>0.588</v>
+        <v>0.575</v>
       </c>
       <c r="I36" s="18" t="n">
-        <v>0.5</v>
+        <v>0.4545</v>
       </c>
       <c r="J36" s="18" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.1205</v>
       </c>
       <c r="K36" s="19" t="n">
-        <v>5.457</v>
+        <v>5.165</v>
       </c>
       <c r="L36" s="17" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>0.44</v>
+        <v>0.55</v>
       </c>
       <c r="N36" s="16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O36" s="20" t="inlineStr">
         <is>
@@ -2629,183 +2637,183 @@
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="14" t="n">
-        <v>46117</v>
-      </c>
-      <c r="B37" s="15" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
+      <c r="A37" s="22" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>Bryce Elder</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="E37" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G37" s="24" t="n">
+        <v>-132</v>
+      </c>
+      <c r="H37" s="26" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="I37" s="26" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="J37" s="26" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="K37" s="27" t="n">
+        <v>5.551</v>
+      </c>
+      <c r="L37" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M37" s="27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N37" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="O37" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P37" s="29" t="n">
+        <v>0.7576000000000001</v>
+      </c>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="14" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>Jack Flaherty</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G38" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="H38" s="18" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="I38" s="18" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J38" s="18" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K38" s="19" t="n">
+        <v>4.756</v>
+      </c>
+      <c r="L38" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M38" s="19" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N38" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O38" s="20" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P38" s="21" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="22" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>Steven Matz</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
         <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D39" s="24" t="inlineStr">
         <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="E37" s="17" t="n">
+      <c r="E39" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="F39" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G37" s="16" t="n">
-        <v>120</v>
-      </c>
-      <c r="H37" s="18" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="I37" s="18" t="n">
-        <v>0.4545</v>
-      </c>
-      <c r="J37" s="18" t="n">
-        <v>0.1205</v>
-      </c>
-      <c r="K37" s="19" t="n">
-        <v>5.165</v>
-      </c>
-      <c r="L37" s="17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M37" s="19" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="N37" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="O37" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P37" s="21" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="22" t="n">
-        <v>46116</v>
-      </c>
-      <c r="B38" s="23" t="inlineStr">
-        <is>
-          <t>Bryce Elder</t>
-        </is>
-      </c>
-      <c r="C38" s="24" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="D38" s="24" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="E38" s="25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F38" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G38" s="24" t="n">
-        <v>-132</v>
-      </c>
-      <c r="H38" s="26" t="n">
-        <v>0.753</v>
-      </c>
-      <c r="I38" s="26" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="J38" s="26" t="n">
-        <v>0.184</v>
-      </c>
-      <c r="K38" s="27" t="n">
-        <v>5.551</v>
-      </c>
-      <c r="L38" s="25" t="n">
+      <c r="G39" s="24" t="n">
+        <v>116</v>
+      </c>
+      <c r="H39" s="26" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="I39" s="26" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J39" s="26" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="K39" s="27" t="n">
+        <v>5.743</v>
+      </c>
+      <c r="L39" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M38" s="27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N38" s="24" t="n">
+      <c r="M39" s="27" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N39" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="O38" s="28" t="inlineStr">
+      <c r="O39" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P38" s="29" t="n">
-        <v>0.7576000000000001</v>
-      </c>
-    </row>
-    <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="14" t="n">
-        <v>46116</v>
-      </c>
-      <c r="B39" s="15" t="inlineStr">
-        <is>
-          <t>Jack Flaherty</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="D39" s="16" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="E39" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F39" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G39" s="16" t="n">
-        <v>116</v>
-      </c>
-      <c r="H39" s="18" t="n">
-        <v>0.653</v>
-      </c>
-      <c r="I39" s="18" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J39" s="18" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="K39" s="19" t="n">
-        <v>4.756</v>
-      </c>
-      <c r="L39" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M39" s="19" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="N39" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="O39" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P39" s="21" t="n">
-        <v>-1</v>
+      <c r="P39" s="29" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="40" ht="17" customHeight="1">
@@ -2814,50 +2822,50 @@
       </c>
       <c r="B40" s="23" t="inlineStr">
         <is>
-          <t>Steven Matz</t>
+          <t>Ryan Weathers</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="D40" s="24" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E40" s="25" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F40" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G40" s="24" t="n">
-        <v>116</v>
+        <v>-125</v>
       </c>
       <c r="H40" s="26" t="n">
-        <v>0.651</v>
+        <v>0.741</v>
       </c>
       <c r="I40" s="26" t="n">
-        <v>0.463</v>
+        <v>0.5556</v>
       </c>
       <c r="J40" s="26" t="n">
-        <v>0.188</v>
+        <v>0.1854</v>
       </c>
       <c r="K40" s="27" t="n">
-        <v>5.743</v>
+        <v>4.217</v>
       </c>
       <c r="L40" s="25" t="n">
         <v>2</v>
       </c>
       <c r="M40" s="27" t="n">
-        <v>0.88</v>
+        <v>1.04</v>
       </c>
       <c r="N40" s="24" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O40" s="28" t="inlineStr">
         <is>
@@ -2865,67 +2873,67 @@
         </is>
       </c>
       <c r="P40" s="29" t="n">
-        <v>1.16</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="22" t="n">
+      <c r="A41" s="14" t="n">
         <v>46116</v>
       </c>
-      <c r="B41" s="23" t="inlineStr">
-        <is>
-          <t>Ryan Weathers</t>
-        </is>
-      </c>
-      <c r="C41" s="24" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="D41" s="24" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="E41" s="25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F41" s="24" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>Carmen Mlodzinski</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G41" s="24" t="n">
-        <v>-125</v>
-      </c>
-      <c r="H41" s="26" t="n">
-        <v>0.741</v>
-      </c>
-      <c r="I41" s="26" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="J41" s="26" t="n">
-        <v>0.1854</v>
-      </c>
-      <c r="K41" s="27" t="n">
-        <v>4.217</v>
-      </c>
-      <c r="L41" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M41" s="27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N41" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="O41" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P41" s="29" t="n">
-        <v>0.8</v>
+      <c r="G41" s="16" t="n">
+        <v>-108</v>
+      </c>
+      <c r="H41" s="18" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="I41" s="18" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="J41" s="18" t="n">
+        <v>0.1468</v>
+      </c>
+      <c r="K41" s="19" t="n">
+        <v>3.828</v>
+      </c>
+      <c r="L41" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M41" s="19" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="N41" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="O41" s="20" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P41" s="21" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="42" ht="17" customHeight="1">
@@ -2934,17 +2942,17 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>Chad Patrick</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="C42" s="16" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E42" s="17" t="n">
@@ -2956,25 +2964,25 @@
         </is>
       </c>
       <c r="G42" s="16" t="n">
-        <v>-154</v>
+        <v>-130</v>
       </c>
       <c r="H42" s="18" t="n">
         <v>0.678</v>
       </c>
       <c r="I42" s="18" t="n">
-        <v>0.6063</v>
+        <v>0.5652</v>
       </c>
       <c r="J42" s="18" t="n">
-        <v>0.0717</v>
+        <v>0.1128</v>
       </c>
       <c r="K42" s="19" t="n">
-        <v>4.705</v>
+        <v>4.813</v>
       </c>
       <c r="L42" s="17" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M42" s="19" t="n">
-        <v>0.46</v>
+        <v>0.65</v>
       </c>
       <c r="N42" s="16" t="n">
         <v>3</v>
@@ -2994,50 +3002,50 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>Carmen Mlodzinski</t>
+          <t>Chad Patrick</t>
         </is>
       </c>
       <c r="C43" s="16" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G43" s="16" t="n">
-        <v>-108</v>
+        <v>-154</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>0.666</v>
+        <v>0.678</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>0.5192</v>
+        <v>0.6063</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>0.1468</v>
+        <v>0.0717</v>
       </c>
       <c r="K43" s="19" t="n">
-        <v>3.828</v>
+        <v>4.705</v>
       </c>
       <c r="L43" s="17" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M43" s="19" t="n">
-        <v>0.76</v>
+        <v>0.46</v>
       </c>
       <c r="N43" s="16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O43" s="20" t="inlineStr">
         <is>
@@ -3050,25 +3058,25 @@
     </row>
     <row r="44" ht="17" customHeight="1">
       <c r="A44" s="14" t="n">
-        <v>46116</v>
+        <v>46115</v>
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Emmet Sheehan</t>
         </is>
       </c>
       <c r="C44" s="16" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E44" s="17" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="F44" s="16" t="inlineStr">
         <is>
@@ -3076,28 +3084,28 @@
         </is>
       </c>
       <c r="G44" s="16" t="n">
-        <v>-130</v>
+        <v>-128</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>0.678</v>
+        <v>0.68</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>0.5652</v>
+        <v>0.5614</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>0.1128</v>
+        <v>0.1186</v>
       </c>
       <c r="K44" s="19" t="n">
-        <v>4.813</v>
+        <v>6.988</v>
       </c>
       <c r="L44" s="17" t="n">
         <v>1.5</v>
       </c>
       <c r="M44" s="19" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="N44" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O44" s="20" t="inlineStr">
         <is>
@@ -3114,410 +3122,410 @@
       </c>
       <c r="B45" s="23" t="inlineStr">
         <is>
+          <t>Mitch Keller</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E45" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F45" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G45" s="24" t="n">
+        <v>122</v>
+      </c>
+      <c r="H45" s="26" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="I45" s="26" t="n">
+        <v>0.4505</v>
+      </c>
+      <c r="J45" s="26" t="n">
+        <v>0.0545</v>
+      </c>
+      <c r="K45" s="27" t="n">
+        <v>4.723</v>
+      </c>
+      <c r="L45" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M45" s="27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N45" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="O45" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P45" s="29" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="22" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>Framber Valdez</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="E46" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F46" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G46" s="24" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H46" s="26" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="I46" s="26" t="n">
+        <v>0.5283</v>
+      </c>
+      <c r="J46" s="26" t="n">
+        <v>0.06270000000000001</v>
+      </c>
+      <c r="K46" s="27" t="n">
+        <v>5.166</v>
+      </c>
+      <c r="L46" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M46" s="27" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N46" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="O46" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P46" s="29" t="n">
+        <v>0.8929</v>
+      </c>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="22" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t>Kyle Bradish</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="E47" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F47" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G47" s="24" t="n">
+        <v>-146</v>
+      </c>
+      <c r="H47" s="26" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="I47" s="26" t="n">
+        <v>0.5935</v>
+      </c>
+      <c r="J47" s="26" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="K47" s="27" t="n">
+        <v>6.943</v>
+      </c>
+      <c r="L47" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M47" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N47" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="O47" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P47" s="29" t="n">
+        <v>0.6849</v>
+      </c>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="22" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B48" s="23" t="inlineStr">
+        <is>
           <t>Michael King</t>
         </is>
       </c>
-      <c r="C45" s="24" t="inlineStr">
+      <c r="C48" s="24" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="D45" s="24" t="inlineStr">
+      <c r="D48" s="24" t="inlineStr">
         <is>
           <t>BOS</t>
         </is>
       </c>
-      <c r="E45" s="25" t="n">
+      <c r="E48" s="25" t="n">
         <v>5.5</v>
       </c>
-      <c r="F45" s="24" t="inlineStr">
+      <c r="F48" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G45" s="24" t="n">
+      <c r="G48" s="24" t="n">
         <v>102</v>
       </c>
-      <c r="H45" s="26" t="n">
+      <c r="H48" s="26" t="n">
         <v>0.584</v>
       </c>
-      <c r="I45" s="26" t="n">
+      <c r="I48" s="26" t="n">
         <v>0.495</v>
       </c>
-      <c r="J45" s="26" t="n">
+      <c r="J48" s="26" t="n">
         <v>0.089</v>
       </c>
-      <c r="K45" s="27" t="n">
+      <c r="K48" s="27" t="n">
         <v>5.081</v>
       </c>
-      <c r="L45" s="25" t="n">
+      <c r="L48" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="M45" s="27" t="n">
+      <c r="M48" s="27" t="n">
         <v>0.44</v>
       </c>
-      <c r="N45" s="24" t="n">
+      <c r="N48" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="O45" s="28" t="inlineStr">
+      <c r="O48" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P45" s="29" t="n">
+      <c r="P48" s="29" t="n">
         <v>1.02</v>
       </c>
     </row>
-    <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="14" t="n">
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="6" t="n">
         <v>46115</v>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Chad Patrick</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="n">
+        <v>-138</v>
+      </c>
+      <c r="H49" s="10" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="I49" s="10" t="n">
+        <v>0.5798</v>
+      </c>
+      <c r="J49" s="10" t="n">
+        <v>0.0922</v>
+      </c>
+      <c r="K49" s="11" t="n">
+        <v>4.705</v>
+      </c>
+      <c r="L49" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" s="11" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N49" s="8" t="inlineStr"/>
+      <c r="O49" s="12" t="inlineStr"/>
+      <c r="P49" s="13" t="inlineStr"/>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="14" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>Cade Horton</t>
         </is>
       </c>
-      <c r="C46" s="16" t="inlineStr">
+      <c r="C50" s="16" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="D46" s="16" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E46" s="17" t="n">
+      <c r="E50" s="17" t="n">
         <v>3.5</v>
       </c>
-      <c r="F46" s="16" t="inlineStr">
+      <c r="F50" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G46" s="16" t="n">
+      <c r="G50" s="16" t="n">
         <v>-136</v>
       </c>
-      <c r="H46" s="18" t="n">
+      <c r="H50" s="18" t="n">
         <v>0.676</v>
       </c>
-      <c r="I46" s="18" t="n">
+      <c r="I50" s="18" t="n">
         <v>0.5763</v>
       </c>
-      <c r="J46" s="18" t="n">
+      <c r="J50" s="18" t="n">
         <v>0.0997</v>
       </c>
-      <c r="K46" s="19" t="n">
+      <c r="K50" s="19" t="n">
         <v>4.806</v>
       </c>
-      <c r="L46" s="17" t="n">
+      <c r="L50" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="M46" s="19" t="n">
+      <c r="M50" s="19" t="n">
         <v>0.59</v>
       </c>
-      <c r="N46" s="16" t="n">
+      <c r="N50" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="O46" s="20" t="inlineStr">
+      <c r="O50" s="20" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P46" s="21" t="n">
+      <c r="P50" s="21" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="6" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Chad Patrick</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="inlineStr">
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="14" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>Cole Ragans</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
         <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="E47" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G47" s="8" t="n">
-        <v>-138</v>
-      </c>
-      <c r="H47" s="10" t="n">
-        <v>0.672</v>
-      </c>
-      <c r="I47" s="10" t="n">
-        <v>0.5798</v>
-      </c>
-      <c r="J47" s="10" t="n">
-        <v>0.0922</v>
-      </c>
-      <c r="K47" s="11" t="n">
-        <v>4.705</v>
-      </c>
-      <c r="L47" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M47" s="11" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="N47" s="8" t="inlineStr"/>
-      <c r="O47" s="12" t="inlineStr"/>
-      <c r="P47" s="13" t="inlineStr"/>
-    </row>
-    <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="14" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>Emmet Sheehan</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
-      <c r="D48" s="16" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
-      <c r="E48" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F48" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G48" s="16" t="n">
-        <v>-128</v>
-      </c>
-      <c r="H48" s="18" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="I48" s="18" t="n">
-        <v>0.5614</v>
-      </c>
-      <c r="J48" s="18" t="n">
-        <v>0.1186</v>
-      </c>
-      <c r="K48" s="19" t="n">
-        <v>6.988</v>
-      </c>
-      <c r="L48" s="17" t="n">
+      <c r="D51" s="16" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F51" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G51" s="16" t="n">
+        <v>-152</v>
+      </c>
+      <c r="H51" s="18" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="I51" s="18" t="n">
+        <v>0.6032</v>
+      </c>
+      <c r="J51" s="18" t="n">
+        <v>0.1348</v>
+      </c>
+      <c r="K51" s="19" t="n">
+        <v>5.951</v>
+      </c>
+      <c r="L51" s="17" t="n">
         <v>1.5</v>
       </c>
-      <c r="M48" s="19" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="N48" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="O48" s="20" t="inlineStr">
+      <c r="M51" s="19" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="N51" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="O51" s="20" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P48" s="21" t="n">
+      <c r="P51" s="21" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="22" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B49" s="23" t="inlineStr">
-        <is>
-          <t>Kyle Bradish</t>
-        </is>
-      </c>
-      <c r="C49" s="24" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="D49" s="24" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="E49" s="25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F49" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G49" s="24" t="n">
-        <v>-146</v>
-      </c>
-      <c r="H49" s="26" t="n">
-        <v>0.659</v>
-      </c>
-      <c r="I49" s="26" t="n">
-        <v>0.5935</v>
-      </c>
-      <c r="J49" s="26" t="n">
-        <v>0.0655</v>
-      </c>
-      <c r="K49" s="27" t="n">
-        <v>6.943</v>
-      </c>
-      <c r="L49" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M49" s="27" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N49" s="24" t="n">
-        <v>6</v>
-      </c>
-      <c r="O49" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P49" s="29" t="n">
-        <v>0.6849</v>
-      </c>
-    </row>
-    <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="22" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B50" s="23" t="inlineStr">
-        <is>
-          <t>Framber Valdez</t>
-        </is>
-      </c>
-      <c r="C50" s="24" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="D50" s="24" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="E50" s="25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F50" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G50" s="24" t="n">
-        <v>-112</v>
-      </c>
-      <c r="H50" s="26" t="n">
-        <v>0.591</v>
-      </c>
-      <c r="I50" s="26" t="n">
-        <v>0.5283</v>
-      </c>
-      <c r="J50" s="26" t="n">
-        <v>0.06270000000000001</v>
-      </c>
-      <c r="K50" s="27" t="n">
-        <v>5.166</v>
-      </c>
-      <c r="L50" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M50" s="27" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="N50" s="24" t="n">
-        <v>5</v>
-      </c>
-      <c r="O50" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P50" s="29" t="n">
-        <v>0.8929</v>
-      </c>
-    </row>
-    <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="22" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B51" s="23" t="inlineStr">
-        <is>
-          <t>Mitch Keller</t>
-        </is>
-      </c>
-      <c r="C51" s="24" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="D51" s="24" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="E51" s="25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F51" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G51" s="24" t="n">
-        <v>122</v>
-      </c>
-      <c r="H51" s="26" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="I51" s="26" t="n">
-        <v>0.4505</v>
-      </c>
-      <c r="J51" s="26" t="n">
-        <v>0.0545</v>
-      </c>
-      <c r="K51" s="27" t="n">
-        <v>4.723</v>
-      </c>
-      <c r="L51" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M51" s="27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N51" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="O51" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P51" s="29" t="n">
-        <v>1.22</v>
       </c>
     </row>
     <row r="52" ht="17" customHeight="1">
@@ -3581,63 +3589,63 @@
       </c>
     </row>
     <row r="53" ht="17" customHeight="1">
-      <c r="A53" s="14" t="n">
-        <v>46114</v>
-      </c>
-      <c r="B53" s="15" t="inlineStr">
-        <is>
-          <t>Cole Ragans</t>
-        </is>
-      </c>
-      <c r="C53" s="16" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="D53" s="16" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="E53" s="17" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F53" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G53" s="16" t="n">
-        <v>-152</v>
-      </c>
-      <c r="H53" s="18" t="n">
-        <v>0.738</v>
-      </c>
-      <c r="I53" s="18" t="n">
-        <v>0.6032</v>
-      </c>
-      <c r="J53" s="18" t="n">
-        <v>0.1348</v>
-      </c>
-      <c r="K53" s="19" t="n">
-        <v>5.951</v>
-      </c>
-      <c r="L53" s="17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M53" s="19" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="N53" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="O53" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P53" s="21" t="n">
-        <v>-1</v>
+      <c r="A53" s="22" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B53" s="23" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="C53" s="24" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="D53" s="24" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="E53" s="25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F53" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G53" s="24" t="n">
+        <v>116</v>
+      </c>
+      <c r="H53" s="26" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="I53" s="26" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J53" s="26" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="K53" s="27" t="n">
+        <v>6.789</v>
+      </c>
+      <c r="L53" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M53" s="27" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N53" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="O53" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P53" s="29" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="54" ht="17" customHeight="1">
@@ -3646,118 +3654,118 @@
       </c>
       <c r="B54" s="23" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="C54" s="24" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="D54" s="24" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E54" s="25" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="F54" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G54" s="24" t="n">
-        <v>100</v>
+        <v>-132</v>
       </c>
       <c r="H54" s="26" t="n">
-        <v>0.624</v>
+        <v>0.696</v>
       </c>
       <c r="I54" s="26" t="n">
-        <v>0.5</v>
+        <v>0.569</v>
       </c>
       <c r="J54" s="26" t="n">
-        <v>0.124</v>
+        <v>0.127</v>
       </c>
       <c r="K54" s="27" t="n">
-        <v>7.784</v>
+        <v>6.191</v>
       </c>
       <c r="L54" s="25" t="n">
         <v>1.5</v>
       </c>
       <c r="M54" s="27" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="N54" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="O54" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P54" s="29" t="n">
+        <v>0.7576000000000001</v>
+      </c>
+    </row>
+    <row r="55" ht="17" customHeight="1">
+      <c r="A55" s="22" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B55" s="23" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="C55" s="24" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D55" s="24" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E55" s="25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F55" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G55" s="24" t="n">
+        <v>100</v>
+      </c>
+      <c r="H55" s="26" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="I55" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J55" s="26" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="K55" s="27" t="n">
+        <v>7.784</v>
+      </c>
+      <c r="L55" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M55" s="27" t="n">
         <v>0.62</v>
       </c>
-      <c r="N54" s="24" t="n">
+      <c r="N55" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="O54" s="28" t="inlineStr">
+      <c r="O55" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P54" s="29" t="n">
+      <c r="P55" s="29" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="14" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B55" s="15" t="inlineStr">
-        <is>
-          <t>Nathan Eovaldi</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
-      <c r="D55" s="16" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="E55" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F55" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G55" s="16" t="n">
-        <v>-168</v>
-      </c>
-      <c r="H55" s="18" t="n">
-        <v>0.743</v>
-      </c>
-      <c r="I55" s="18" t="n">
-        <v>0.6269</v>
-      </c>
-      <c r="J55" s="18" t="n">
-        <v>0.1161</v>
-      </c>
-      <c r="K55" s="19" t="n">
-        <v>7.699</v>
-      </c>
-      <c r="L55" s="17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M55" s="19" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="N55" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="O55" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P55" s="21" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="56" ht="17" customHeight="1">
@@ -4181,123 +4189,123 @@
       </c>
     </row>
     <row r="63" ht="17" customHeight="1">
-      <c r="A63" s="22" t="n">
+      <c r="A63" s="14" t="n">
         <v>46113</v>
       </c>
-      <c r="B63" s="23" t="inlineStr">
-        <is>
-          <t>Paul Skenes</t>
-        </is>
-      </c>
-      <c r="C63" s="24" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="D63" s="24" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="E63" s="25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F63" s="24" t="inlineStr">
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>Yusei Kikuchi</t>
+        </is>
+      </c>
+      <c r="C63" s="16" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D63" s="16" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="E63" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F63" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G63" s="24" t="n">
-        <v>-132</v>
-      </c>
-      <c r="H63" s="26" t="n">
-        <v>0.696</v>
-      </c>
-      <c r="I63" s="26" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="J63" s="26" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="K63" s="27" t="n">
-        <v>6.191</v>
-      </c>
-      <c r="L63" s="25" t="n">
+      <c r="G63" s="16" t="n">
+        <v>102</v>
+      </c>
+      <c r="H63" s="18" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="I63" s="18" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="J63" s="18" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="K63" s="19" t="n">
+        <v>4.364</v>
+      </c>
+      <c r="L63" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M63" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N63" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="O63" s="20" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P63" s="21" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="64" ht="17" customHeight="1">
+      <c r="A64" s="14" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>Nathan Eovaldi</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="D64" s="16" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F64" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G64" s="16" t="n">
+        <v>-168</v>
+      </c>
+      <c r="H64" s="18" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="I64" s="18" t="n">
+        <v>0.6269</v>
+      </c>
+      <c r="J64" s="18" t="n">
+        <v>0.1161</v>
+      </c>
+      <c r="K64" s="19" t="n">
+        <v>7.699</v>
+      </c>
+      <c r="L64" s="17" t="n">
         <v>1.5</v>
       </c>
-      <c r="M63" s="27" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="N63" s="24" t="n">
+      <c r="M64" s="19" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="N64" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="O63" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P63" s="29" t="n">
-        <v>0.7576000000000001</v>
-      </c>
-    </row>
-    <row r="64" ht="17" customHeight="1">
-      <c r="A64" s="22" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B64" s="23" t="inlineStr">
-        <is>
-          <t>Freddy Peralta</t>
-        </is>
-      </c>
-      <c r="C64" s="24" t="inlineStr">
-        <is>
-          <t>NYM</t>
-        </is>
-      </c>
-      <c r="D64" s="24" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="E64" s="25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F64" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G64" s="24" t="n">
-        <v>116</v>
-      </c>
-      <c r="H64" s="26" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="I64" s="26" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J64" s="26" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="K64" s="27" t="n">
-        <v>6.789</v>
-      </c>
-      <c r="L64" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M64" s="27" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="N64" s="24" t="n">
-        <v>7</v>
-      </c>
-      <c r="O64" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P64" s="29" t="n">
-        <v>1.16</v>
+      <c r="O64" s="20" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P64" s="21" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="65" ht="17" customHeight="1">
@@ -4721,183 +4729,183 @@
       </c>
     </row>
     <row r="72" ht="17" customHeight="1">
-      <c r="A72" s="14" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B72" s="15" t="inlineStr">
-        <is>
-          <t>Yusei Kikuchi</t>
-        </is>
-      </c>
-      <c r="C72" s="16" t="inlineStr">
+      <c r="A72" s="22" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B72" s="23" t="inlineStr">
+        <is>
+          <t>Erick Fedde</t>
+        </is>
+      </c>
+      <c r="C72" s="24" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D72" s="24" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E72" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F72" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G72" s="24" t="n">
+        <v>134</v>
+      </c>
+      <c r="H72" s="26" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="I72" s="26" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="J72" s="26" t="n">
+        <v>0.09959999999999999</v>
+      </c>
+      <c r="K72" s="27" t="n">
+        <v>3.852</v>
+      </c>
+      <c r="L72" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" s="27" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="N72" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="O72" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P72" s="29" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="73" ht="17" customHeight="1">
+      <c r="A73" s="14" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B73" s="15" t="inlineStr">
+        <is>
+          <t>José Soriano</t>
+        </is>
+      </c>
+      <c r="C73" s="16" t="inlineStr">
         <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="D72" s="16" t="inlineStr">
+      <c r="D73" s="16" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="E72" s="17" t="n">
+      <c r="E73" s="17" t="n">
         <v>4.5</v>
       </c>
-      <c r="F72" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G72" s="16" t="n">
-        <v>102</v>
-      </c>
-      <c r="H72" s="18" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="I72" s="18" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="J72" s="18" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="K72" s="19" t="n">
-        <v>4.364</v>
-      </c>
-      <c r="L72" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M72" s="19" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N72" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="O72" s="20" t="inlineStr">
+      <c r="F73" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G73" s="16" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H73" s="18" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="I73" s="18" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="J73" s="18" t="n">
+        <v>0.1522</v>
+      </c>
+      <c r="K73" s="19" t="n">
+        <v>5.918</v>
+      </c>
+      <c r="L73" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M73" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N73" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O73" s="20" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P72" s="21" t="n">
+      <c r="P73" s="21" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="73" ht="17" customHeight="1">
-      <c r="A73" s="22" t="n">
+    <row r="74" ht="17" customHeight="1">
+      <c r="A74" s="22" t="n">
         <v>46112</v>
       </c>
-      <c r="B73" s="23" t="inlineStr">
-        <is>
-          <t>Erick Fedde</t>
-        </is>
-      </c>
-      <c r="C73" s="24" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="D73" s="24" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="E73" s="25" t="n">
+      <c r="B74" s="23" t="inlineStr">
+        <is>
+          <t>Ryan Feltner</t>
+        </is>
+      </c>
+      <c r="C74" s="24" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D74" s="24" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E74" s="25" t="n">
         <v>3.5</v>
       </c>
-      <c r="F73" s="24" t="inlineStr">
+      <c r="F74" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G73" s="24" t="n">
-        <v>134</v>
-      </c>
-      <c r="H73" s="26" t="n">
-        <v>0.527</v>
-      </c>
-      <c r="I73" s="26" t="n">
-        <v>0.4274</v>
-      </c>
-      <c r="J73" s="26" t="n">
-        <v>0.09959999999999999</v>
-      </c>
-      <c r="K73" s="27" t="n">
-        <v>3.852</v>
-      </c>
-      <c r="L73" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M73" s="27" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="N73" s="24" t="n">
+      <c r="G74" s="24" t="n">
+        <v>-108</v>
+      </c>
+      <c r="H74" s="26" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="I74" s="26" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="J74" s="26" t="n">
+        <v>0.1358</v>
+      </c>
+      <c r="K74" s="27" t="n">
+        <v>4.719</v>
+      </c>
+      <c r="L74" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M74" s="27" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="N74" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="O73" s="28" t="inlineStr">
+      <c r="O74" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P73" s="29" t="n">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="74" ht="17" customHeight="1">
-      <c r="A74" s="14" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B74" s="15" t="inlineStr">
-        <is>
-          <t>José Soriano</t>
-        </is>
-      </c>
-      <c r="C74" s="16" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="D74" s="16" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="E74" s="17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F74" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G74" s="16" t="n">
-        <v>-110</v>
-      </c>
-      <c r="H74" s="18" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="I74" s="18" t="n">
-        <v>0.5238</v>
-      </c>
-      <c r="J74" s="18" t="n">
-        <v>0.1522</v>
-      </c>
-      <c r="K74" s="19" t="n">
-        <v>5.918</v>
-      </c>
-      <c r="L74" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M74" s="19" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N74" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="O74" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P74" s="21" t="n">
-        <v>-1</v>
+      <c r="P74" s="29" t="n">
+        <v>0.9258999999999999</v>
       </c>
     </row>
     <row r="75" ht="17" customHeight="1">
@@ -4906,50 +4914,50 @@
       </c>
       <c r="B75" s="23" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Jameson Taillon</t>
         </is>
       </c>
       <c r="C75" s="24" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="D75" s="24" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E75" s="25" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F75" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G75" s="24" t="n">
-        <v>-108</v>
+        <v>116</v>
       </c>
       <c r="H75" s="26" t="n">
-        <v>0.655</v>
+        <v>0.569</v>
       </c>
       <c r="I75" s="26" t="n">
-        <v>0.5192</v>
+        <v>0.463</v>
       </c>
       <c r="J75" s="26" t="n">
-        <v>0.1358</v>
+        <v>0.106</v>
       </c>
       <c r="K75" s="27" t="n">
-        <v>4.719</v>
+        <v>4.313</v>
       </c>
       <c r="L75" s="25" t="n">
         <v>1.5</v>
       </c>
       <c r="M75" s="27" t="n">
-        <v>0.71</v>
+        <v>0.49</v>
       </c>
       <c r="N75" s="24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O75" s="28" t="inlineStr">
         <is>
@@ -4957,7 +4965,7 @@
         </is>
       </c>
       <c r="P75" s="29" t="n">
-        <v>0.9258999999999999</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="76" ht="17" customHeight="1">
@@ -4966,21 +4974,21 @@
       </c>
       <c r="B76" s="23" t="inlineStr">
         <is>
-          <t>Jameson Taillon</t>
+          <t>Max Scherzer</t>
         </is>
       </c>
       <c r="C76" s="24" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D76" s="24" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E76" s="25" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F76" s="24" t="inlineStr">
         <is>
@@ -4988,28 +4996,28 @@
         </is>
       </c>
       <c r="G76" s="24" t="n">
-        <v>116</v>
+        <v>-130</v>
       </c>
       <c r="H76" s="26" t="n">
-        <v>0.569</v>
+        <v>0.652</v>
       </c>
       <c r="I76" s="26" t="n">
-        <v>0.463</v>
+        <v>0.5652</v>
       </c>
       <c r="J76" s="26" t="n">
-        <v>0.106</v>
+        <v>0.0868</v>
       </c>
       <c r="K76" s="27" t="n">
-        <v>4.313</v>
+        <v>4.757</v>
       </c>
       <c r="L76" s="25" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M76" s="27" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="N76" s="24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O76" s="28" t="inlineStr">
         <is>
@@ -5017,7 +5025,7 @@
         </is>
       </c>
       <c r="P76" s="29" t="n">
-        <v>1.16</v>
+        <v>0.7692</v>
       </c>
     </row>
     <row r="77" ht="17" customHeight="1">
@@ -5026,17 +5034,17 @@
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>Andre Pallante</t>
+          <t>Aaron Civale</t>
         </is>
       </c>
       <c r="C77" s="16" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>OAK</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E77" s="17" t="n">
@@ -5048,25 +5056,25 @@
         </is>
       </c>
       <c r="G77" s="16" t="n">
-        <v>126</v>
+        <v>-146</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>0.523</v>
+        <v>0.666</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>0.4425</v>
+        <v>0.5935</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>0.0805</v>
+        <v>0.0725</v>
       </c>
       <c r="K77" s="19" t="n">
-        <v>3.876</v>
+        <v>4.714</v>
       </c>
       <c r="L77" s="17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M77" s="19" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
       <c r="N77" s="16" t="n">
         <v>3</v>
@@ -5081,82 +5089,82 @@
       </c>
     </row>
     <row r="78" ht="17" customHeight="1">
-      <c r="A78" s="22" t="n">
+      <c r="A78" s="14" t="n">
         <v>46112</v>
       </c>
-      <c r="B78" s="23" t="inlineStr">
-        <is>
-          <t>Max Scherzer</t>
-        </is>
-      </c>
-      <c r="C78" s="24" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="D78" s="24" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="E78" s="25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F78" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G78" s="24" t="n">
-        <v>-130</v>
-      </c>
-      <c r="H78" s="26" t="n">
-        <v>0.652</v>
-      </c>
-      <c r="I78" s="26" t="n">
-        <v>0.5652</v>
-      </c>
-      <c r="J78" s="26" t="n">
-        <v>0.0868</v>
-      </c>
-      <c r="K78" s="27" t="n">
-        <v>4.757</v>
-      </c>
-      <c r="L78" s="25" t="n">
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>Andre Pallante</t>
+        </is>
+      </c>
+      <c r="C78" s="16" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D78" s="16" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="E78" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F78" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G78" s="16" t="n">
+        <v>126</v>
+      </c>
+      <c r="H78" s="18" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="I78" s="18" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="J78" s="18" t="n">
+        <v>0.0805</v>
+      </c>
+      <c r="K78" s="19" t="n">
+        <v>3.876</v>
+      </c>
+      <c r="L78" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="M78" s="27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N78" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="O78" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P78" s="29" t="n">
-        <v>0.7692</v>
+      <c r="M78" s="19" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="N78" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O78" s="20" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P78" s="21" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="79" ht="17" customHeight="1">
       <c r="A79" s="14" t="n">
-        <v>46112</v>
+        <v>46111</v>
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>Aaron Civale</t>
+          <t>Simeon Woods Richardson</t>
         </is>
       </c>
       <c r="C79" s="16" t="inlineStr">
         <is>
-          <t>OAK</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D79" s="16" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E79" s="17" t="n">
@@ -5168,28 +5176,28 @@
         </is>
       </c>
       <c r="G79" s="16" t="n">
-        <v>-146</v>
+        <v>-112</v>
       </c>
       <c r="H79" s="18" t="n">
-        <v>0.666</v>
+        <v>0.783</v>
       </c>
       <c r="I79" s="18" t="n">
-        <v>0.5935</v>
+        <v>0.5283</v>
       </c>
       <c r="J79" s="18" t="n">
-        <v>0.0725</v>
+        <v>0.2547</v>
       </c>
       <c r="K79" s="19" t="n">
-        <v>4.714</v>
+        <v>5.562</v>
       </c>
       <c r="L79" s="17" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="M79" s="19" t="n">
-        <v>0.45</v>
+        <v>1.35</v>
       </c>
       <c r="N79" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O79" s="20" t="inlineStr">
         <is>
@@ -5266,50 +5274,50 @@
       </c>
       <c r="B81" s="23" t="inlineStr">
         <is>
-          <t>Edward Cabrera</t>
+          <t>Jack Leiter</t>
         </is>
       </c>
       <c r="C81" s="24" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="D81" s="24" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E81" s="25" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="F81" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G81" s="24" t="n">
-        <v>116</v>
+        <v>-144</v>
       </c>
       <c r="H81" s="26" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.679</v>
       </c>
       <c r="I81" s="26" t="n">
-        <v>0.463</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="J81" s="26" t="n">
-        <v>0.226</v>
+        <v>0.0888</v>
       </c>
       <c r="K81" s="27" t="n">
-        <v>5.286</v>
+        <v>6.017</v>
       </c>
       <c r="L81" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M81" s="27" t="n">
-        <v>1.05</v>
+        <v>0.54</v>
       </c>
       <c r="N81" s="24" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O81" s="28" t="inlineStr">
         <is>
@@ -5317,7 +5325,7 @@
         </is>
       </c>
       <c r="P81" s="29" t="n">
-        <v>1.16</v>
+        <v>0.6944</v>
       </c>
     </row>
     <row r="82" ht="17" customHeight="1">
@@ -5326,50 +5334,50 @@
       </c>
       <c r="B82" s="23" t="inlineStr">
         <is>
-          <t>Jack Leiter</t>
+          <t>Edward Cabrera</t>
         </is>
       </c>
       <c r="C82" s="24" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="D82" s="24" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E82" s="25" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="F82" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G82" s="24" t="n">
-        <v>-144</v>
+        <v>116</v>
       </c>
       <c r="H82" s="26" t="n">
-        <v>0.679</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="I82" s="26" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.463</v>
       </c>
       <c r="J82" s="26" t="n">
-        <v>0.0888</v>
+        <v>0.226</v>
       </c>
       <c r="K82" s="27" t="n">
-        <v>6.017</v>
+        <v>5.286</v>
       </c>
       <c r="L82" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M82" s="27" t="n">
-        <v>0.54</v>
+        <v>1.05</v>
       </c>
       <c r="N82" s="24" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O82" s="28" t="inlineStr">
         <is>
@@ -5377,7 +5385,7 @@
         </is>
       </c>
       <c r="P82" s="29" t="n">
-        <v>0.6944</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="83" ht="17" customHeight="1">
@@ -5386,17 +5394,17 @@
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>Simeon Woods Richardson</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="C83" s="16" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="D83" s="16" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E83" s="17" t="n">
@@ -5408,28 +5416,28 @@
         </is>
       </c>
       <c r="G83" s="16" t="n">
-        <v>-112</v>
+        <v>-174</v>
       </c>
       <c r="H83" s="18" t="n">
-        <v>0.783</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="I83" s="18" t="n">
-        <v>0.5283</v>
+        <v>0.635</v>
       </c>
       <c r="J83" s="18" t="n">
-        <v>0.2547</v>
+        <v>0.054</v>
       </c>
       <c r="K83" s="19" t="n">
-        <v>5.562</v>
+        <v>4.97</v>
       </c>
       <c r="L83" s="17" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="M83" s="19" t="n">
-        <v>1.35</v>
+        <v>0.37</v>
       </c>
       <c r="N83" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O83" s="20" t="inlineStr">
         <is>
@@ -5446,50 +5454,50 @@
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Kyle Harrison</t>
         </is>
       </c>
       <c r="C84" s="16" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D84" s="16" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="D84" s="16" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="E84" s="17" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F84" s="16" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G84" s="16" t="n">
-        <v>-174</v>
+        <v>114</v>
       </c>
       <c r="H84" s="18" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.521</v>
       </c>
       <c r="I84" s="18" t="n">
-        <v>0.635</v>
+        <v>0.4673</v>
       </c>
       <c r="J84" s="18" t="n">
-        <v>0.054</v>
+        <v>0.0537</v>
       </c>
       <c r="K84" s="19" t="n">
-        <v>4.97</v>
+        <v>4.628</v>
       </c>
       <c r="L84" s="17" t="n">
         <v>0.5</v>
       </c>
       <c r="M84" s="19" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="N84" s="16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O84" s="20" t="inlineStr">
         <is>
@@ -5501,86 +5509,86 @@
       </c>
     </row>
     <row r="85" ht="17" customHeight="1">
-      <c r="A85" s="14" t="n">
+      <c r="A85" s="22" t="n">
         <v>46111</v>
       </c>
-      <c r="B85" s="15" t="inlineStr">
-        <is>
-          <t>Kyle Harrison</t>
-        </is>
-      </c>
-      <c r="C85" s="16" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D85" s="16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="E85" s="17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F85" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G85" s="16" t="n">
-        <v>114</v>
-      </c>
-      <c r="H85" s="18" t="n">
-        <v>0.521</v>
-      </c>
-      <c r="I85" s="18" t="n">
-        <v>0.4673</v>
-      </c>
-      <c r="J85" s="18" t="n">
-        <v>0.0537</v>
-      </c>
-      <c r="K85" s="19" t="n">
-        <v>4.628</v>
-      </c>
-      <c r="L85" s="17" t="n">
+      <c r="B85" s="23" t="inlineStr">
+        <is>
+          <t>Davis Martin</t>
+        </is>
+      </c>
+      <c r="C85" s="24" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D85" s="24" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E85" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F85" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G85" s="24" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H85" s="26" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="I85" s="26" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="J85" s="26" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="K85" s="27" t="n">
+        <v>4.252</v>
+      </c>
+      <c r="L85" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M85" s="19" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N85" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="O85" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P85" s="21" t="n">
-        <v>-1</v>
+      <c r="M85" s="27" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="N85" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="O85" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P85" s="29" t="n">
+        <v>0.8772</v>
       </c>
     </row>
     <row r="86" ht="17" customHeight="1">
       <c r="A86" s="22" t="n">
-        <v>46111</v>
+        <v>46109</v>
       </c>
       <c r="B86" s="23" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="C86" s="24" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D86" s="24" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E86" s="25" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F86" s="24" t="inlineStr">
         <is>
@@ -5588,28 +5596,28 @@
         </is>
       </c>
       <c r="G86" s="24" t="n">
-        <v>-114</v>
+        <v>140</v>
       </c>
       <c r="H86" s="26" t="n">
-        <v>0.584</v>
+        <v>0.476</v>
       </c>
       <c r="I86" s="26" t="n">
-        <v>0.5327</v>
+        <v>0.4167</v>
       </c>
       <c r="J86" s="26" t="n">
-        <v>0.0513</v>
+        <v>0.0593</v>
       </c>
       <c r="K86" s="27" t="n">
-        <v>4.252</v>
+        <v>4.645</v>
       </c>
       <c r="L86" s="25" t="n">
         <v>0.5</v>
       </c>
       <c r="M86" s="27" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="N86" s="24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O86" s="28" t="inlineStr">
         <is>
@@ -5617,67 +5625,67 @@
         </is>
       </c>
       <c r="P86" s="29" t="n">
-        <v>0.8772</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="87" ht="17" customHeight="1">
-      <c r="A87" s="22" t="n">
+      <c r="A87" s="14" t="n">
         <v>46109</v>
       </c>
-      <c r="B87" s="23" t="inlineStr">
-        <is>
-          <t>Michael Wacha</t>
-        </is>
-      </c>
-      <c r="C87" s="24" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="D87" s="24" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="E87" s="25" t="n">
+      <c r="B87" s="15" t="inlineStr">
+        <is>
+          <t>Will Warren</t>
+        </is>
+      </c>
+      <c r="C87" s="16" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="D87" s="16" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="E87" s="17" t="n">
         <v>4.5</v>
       </c>
-      <c r="F87" s="24" t="inlineStr">
+      <c r="F87" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G87" s="24" t="n">
-        <v>140</v>
-      </c>
-      <c r="H87" s="26" t="n">
-        <v>0.476</v>
-      </c>
-      <c r="I87" s="26" t="n">
-        <v>0.4167</v>
-      </c>
-      <c r="J87" s="26" t="n">
-        <v>0.0593</v>
-      </c>
-      <c r="K87" s="27" t="n">
-        <v>4.645</v>
-      </c>
-      <c r="L87" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M87" s="27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N87" s="24" t="n">
-        <v>7</v>
-      </c>
-      <c r="O87" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P87" s="29" t="n">
-        <v>1.4</v>
+      <c r="G87" s="16" t="n">
+        <v>110</v>
+      </c>
+      <c r="H87" s="18" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="I87" s="18" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="J87" s="18" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="K87" s="19" t="n">
+        <v>5.339</v>
+      </c>
+      <c r="L87" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M87" s="19" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N87" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O87" s="20" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P87" s="21" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="88" ht="17" customHeight="1">
@@ -5686,21 +5694,21 @@
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>Will Warren</t>
+          <t>Jeffrey Springs</t>
         </is>
       </c>
       <c r="C88" s="16" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>OAK</t>
         </is>
       </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E88" s="17" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F88" s="16" t="inlineStr">
         <is>
@@ -5708,28 +5716,28 @@
         </is>
       </c>
       <c r="G88" s="16" t="n">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H88" s="18" t="n">
-        <v>0.573</v>
+        <v>0.599</v>
       </c>
       <c r="I88" s="18" t="n">
-        <v>0.4762</v>
+        <v>0.495</v>
       </c>
       <c r="J88" s="18" t="n">
-        <v>0.0968</v>
+        <v>0.104</v>
       </c>
       <c r="K88" s="19" t="n">
-        <v>5.339</v>
+        <v>4.389</v>
       </c>
       <c r="L88" s="17" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M88" s="19" t="n">
-        <v>0.46</v>
+        <v>0.51</v>
       </c>
       <c r="N88" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O88" s="20" t="inlineStr">
         <is>
@@ -5746,50 +5754,50 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>Jeffrey Springs</t>
+          <t>Eury Pérez</t>
         </is>
       </c>
       <c r="C89" s="16" t="inlineStr">
         <is>
-          <t>OAK</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D89" s="16" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E89" s="17" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="F89" s="16" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G89" s="16" t="n">
-        <v>102</v>
+        <v>-154</v>
       </c>
       <c r="H89" s="18" t="n">
-        <v>0.599</v>
+        <v>0.713</v>
       </c>
       <c r="I89" s="18" t="n">
-        <v>0.495</v>
+        <v>0.6063</v>
       </c>
       <c r="J89" s="18" t="n">
-        <v>0.104</v>
+        <v>0.1067</v>
       </c>
       <c r="K89" s="19" t="n">
-        <v>4.389</v>
+        <v>5.311</v>
       </c>
       <c r="L89" s="17" t="n">
         <v>1.5</v>
       </c>
       <c r="M89" s="19" t="n">
-        <v>0.51</v>
+        <v>0.68</v>
       </c>
       <c r="N89" s="16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O89" s="20" t="inlineStr">
         <is>
@@ -5802,54 +5810,54 @@
     </row>
     <row r="90" ht="17" customHeight="1">
       <c r="A90" s="14" t="n">
-        <v>46109</v>
+        <v>46108</v>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>Eury Pérez</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="C90" s="16" t="inlineStr">
         <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D90" s="16" t="inlineStr">
+        <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="D90" s="16" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
       <c r="E90" s="17" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="F90" s="16" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G90" s="16" t="n">
-        <v>-154</v>
+        <v>-158</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>0.713</v>
+        <v>0.677</v>
       </c>
       <c r="I90" s="18" t="n">
-        <v>0.6063</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>0.1067</v>
+        <v>0.0646</v>
       </c>
       <c r="K90" s="19" t="n">
-        <v>5.311</v>
+        <v>4.869</v>
       </c>
       <c r="L90" s="17" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M90" s="19" t="n">
-        <v>0.68</v>
+        <v>0.42</v>
       </c>
       <c r="N90" s="16" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O90" s="20" t="inlineStr">
         <is>
@@ -5861,63 +5869,63 @@
       </c>
     </row>
     <row r="91" ht="17" customHeight="1">
-      <c r="A91" s="14" t="n">
+      <c r="A91" s="22" t="n">
         <v>46108</v>
       </c>
-      <c r="B91" s="15" t="inlineStr">
-        <is>
-          <t>Kyle Freeland</t>
-        </is>
-      </c>
-      <c r="C91" s="16" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="D91" s="16" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="E91" s="17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F91" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G91" s="16" t="n">
-        <v>-158</v>
-      </c>
-      <c r="H91" s="18" t="n">
-        <v>0.677</v>
-      </c>
-      <c r="I91" s="18" t="n">
-        <v>0.6124000000000001</v>
-      </c>
-      <c r="J91" s="18" t="n">
-        <v>0.0646</v>
-      </c>
-      <c r="K91" s="19" t="n">
-        <v>4.869</v>
-      </c>
-      <c r="L91" s="17" t="n">
+      <c r="B91" s="23" t="inlineStr">
+        <is>
+          <t>Robbie Ray</t>
+        </is>
+      </c>
+      <c r="C91" s="24" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="D91" s="24" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E91" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F91" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G91" s="24" t="n">
+        <v>116</v>
+      </c>
+      <c r="H91" s="26" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="I91" s="26" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J91" s="26" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="K91" s="27" t="n">
+        <v>5.578</v>
+      </c>
+      <c r="L91" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M91" s="19" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="N91" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="O91" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P91" s="21" t="n">
-        <v>-1</v>
+      <c r="M91" s="27" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N91" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="O91" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P91" s="29" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="92" ht="17" customHeight="1">
@@ -5926,118 +5934,118 @@
       </c>
       <c r="B92" s="23" t="inlineStr">
         <is>
-          <t>Robbie Ray</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="C92" s="24" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="D92" s="24" t="inlineStr">
+        <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="D92" s="24" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="E92" s="25" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F92" s="24" t="inlineStr">
         <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G92" s="24" t="n">
+        <v>-128</v>
+      </c>
+      <c r="H92" s="26" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="I92" s="26" t="n">
+        <v>0.5614</v>
+      </c>
+      <c r="J92" s="26" t="n">
+        <v>0.09760000000000001</v>
+      </c>
+      <c r="K92" s="27" t="n">
+        <v>5.818</v>
+      </c>
+      <c r="L92" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M92" s="27" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="N92" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="O92" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P92" s="29" t="n">
+        <v>0.7812</v>
+      </c>
+    </row>
+    <row r="93" ht="17" customHeight="1">
+      <c r="A93" s="14" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B93" s="15" t="inlineStr">
+        <is>
+          <t>Hunter Brown</t>
+        </is>
+      </c>
+      <c r="C93" s="16" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="D93" s="16" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E93" s="17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F93" s="16" t="inlineStr">
+        <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G92" s="24" t="n">
-        <v>116</v>
-      </c>
-      <c r="H92" s="26" t="n">
-        <v>0.532</v>
-      </c>
-      <c r="I92" s="26" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="J92" s="26" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="K92" s="27" t="n">
-        <v>5.578</v>
-      </c>
-      <c r="L92" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M92" s="27" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="N92" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="O92" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P92" s="29" t="n">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="93" ht="17" customHeight="1">
-      <c r="A93" s="22" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B93" s="23" t="inlineStr">
-        <is>
-          <t>Cam Schlittler</t>
-        </is>
-      </c>
-      <c r="C93" s="24" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="D93" s="24" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="E93" s="25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F93" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="G93" s="24" t="n">
-        <v>-128</v>
-      </c>
-      <c r="H93" s="26" t="n">
-        <v>0.659</v>
-      </c>
-      <c r="I93" s="26" t="n">
-        <v>0.5614</v>
-      </c>
-      <c r="J93" s="26" t="n">
-        <v>0.09760000000000001</v>
-      </c>
-      <c r="K93" s="27" t="n">
-        <v>5.818</v>
-      </c>
-      <c r="L93" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M93" s="27" t="n">
+      <c r="G93" s="16" t="n">
+        <v>114</v>
+      </c>
+      <c r="H93" s="18" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="I93" s="18" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="J93" s="18" t="n">
+        <v>0.1197</v>
+      </c>
+      <c r="K93" s="19" t="n">
+        <v>6.417</v>
+      </c>
+      <c r="L93" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M93" s="19" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="N93" s="24" t="n">
-        <v>8</v>
-      </c>
-      <c r="O93" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P93" s="29" t="n">
-        <v>0.7812</v>
+      <c r="N93" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="O93" s="20" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P93" s="21" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="94" ht="17" customHeight="1">
@@ -6101,63 +6109,63 @@
       </c>
     </row>
     <row r="95" ht="17" customHeight="1">
-      <c r="A95" s="14" t="n">
+      <c r="A95" s="22" t="n">
         <v>46107</v>
       </c>
-      <c r="B95" s="15" t="inlineStr">
-        <is>
-          <t>Hunter Brown</t>
-        </is>
-      </c>
-      <c r="C95" s="16" t="inlineStr">
+      <c r="B95" s="23" t="inlineStr">
+        <is>
+          <t>José Soriano</t>
+        </is>
+      </c>
+      <c r="C95" s="24" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D95" s="24" t="inlineStr">
         <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="D95" s="16" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="E95" s="17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F95" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G95" s="16" t="n">
-        <v>114</v>
-      </c>
-      <c r="H95" s="18" t="n">
-        <v>0.587</v>
-      </c>
-      <c r="I95" s="18" t="n">
-        <v>0.4673</v>
-      </c>
-      <c r="J95" s="18" t="n">
-        <v>0.1197</v>
-      </c>
-      <c r="K95" s="19" t="n">
-        <v>6.417</v>
-      </c>
-      <c r="L95" s="17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M95" s="19" t="n">
+      <c r="E95" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F95" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G95" s="24" t="n">
+        <v>108</v>
+      </c>
+      <c r="H95" s="26" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="N95" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="O95" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P95" s="21" t="n">
-        <v>-1</v>
+      <c r="I95" s="26" t="n">
+        <v>0.4808</v>
+      </c>
+      <c r="J95" s="26" t="n">
+        <v>0.07920000000000001</v>
+      </c>
+      <c r="K95" s="27" t="n">
+        <v>5.163</v>
+      </c>
+      <c r="L95" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M95" s="27" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N95" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="O95" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P95" s="29" t="n">
+        <v>1.08</v>
       </c>
     </row>
     <row r="96" ht="17" customHeight="1">
@@ -6166,50 +6174,50 @@
       </c>
       <c r="B96" s="23" t="inlineStr">
         <is>
-          <t>José Soriano</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="C96" s="24" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D96" s="24" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E96" s="25" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="F96" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G96" s="24" t="n">
-        <v>108</v>
+        <v>-172</v>
       </c>
       <c r="H96" s="26" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.767</v>
       </c>
       <c r="I96" s="26" t="n">
-        <v>0.4808</v>
+        <v>0.6324</v>
       </c>
       <c r="J96" s="26" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.1346</v>
       </c>
       <c r="K96" s="27" t="n">
-        <v>5.163</v>
+        <v>5.68</v>
       </c>
       <c r="L96" s="25" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M96" s="27" t="n">
-        <v>0.38</v>
+        <v>0.92</v>
       </c>
       <c r="N96" s="24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O96" s="28" t="inlineStr">
         <is>
@@ -6217,127 +6225,127 @@
         </is>
       </c>
       <c r="P96" s="29" t="n">
-        <v>1.08</v>
+        <v>0.5814</v>
       </c>
     </row>
     <row r="97" ht="17" customHeight="1">
-      <c r="A97" s="22" t="n">
+      <c r="A97" s="14" t="n">
         <v>46107</v>
       </c>
-      <c r="B97" s="23" t="inlineStr">
-        <is>
-          <t>Tarik Skubal</t>
-        </is>
-      </c>
-      <c r="C97" s="24" t="inlineStr">
+      <c r="B97" s="15" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="C97" s="16" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D97" s="16" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E97" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F97" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="G97" s="16" t="n">
+        <v>124</v>
+      </c>
+      <c r="H97" s="18" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I97" s="18" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="J97" s="18" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="K97" s="19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L97" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M97" s="19" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N97" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="O97" s="20" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P97" s="21" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="98" ht="17" customHeight="1">
+      <c r="A98" s="22" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B98" s="23" t="inlineStr">
+        <is>
+          <t>Nick Pivetta</t>
+        </is>
+      </c>
+      <c r="C98" s="24" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D98" s="24" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="D97" s="24" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E97" s="25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F97" s="24" t="inlineStr">
+      <c r="E98" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F98" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G97" s="24" t="n">
-        <v>-172</v>
-      </c>
-      <c r="H97" s="26" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="I97" s="26" t="n">
-        <v>0.6324</v>
-      </c>
-      <c r="J97" s="26" t="n">
-        <v>0.1346</v>
-      </c>
-      <c r="K97" s="27" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="L97" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M97" s="27" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="N97" s="24" t="n">
-        <v>6</v>
-      </c>
-      <c r="O97" s="28" t="inlineStr">
+      <c r="G98" s="24" t="n">
+        <v>110</v>
+      </c>
+      <c r="H98" s="26" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I98" s="26" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="J98" s="26" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="K98" s="27" t="n">
+        <v>5.548</v>
+      </c>
+      <c r="L98" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M98" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N98" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="O98" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P97" s="29" t="n">
-        <v>0.5814</v>
-      </c>
-    </row>
-    <row r="98" ht="17" customHeight="1">
-      <c r="A98" s="14" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B98" s="15" t="inlineStr">
-        <is>
-          <t>Jacob Misiorowski</t>
-        </is>
-      </c>
-      <c r="C98" s="16" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D98" s="16" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="E98" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F98" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G98" s="16" t="n">
-        <v>124</v>
-      </c>
-      <c r="H98" s="18" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I98" s="18" t="n">
-        <v>0.4464</v>
-      </c>
-      <c r="J98" s="18" t="n">
-        <v>0.0736</v>
-      </c>
-      <c r="K98" s="19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L98" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M98" s="19" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="N98" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="O98" s="20" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P98" s="21" t="n">
-        <v>-1</v>
+      <c r="P98" s="29" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="99" ht="17" customHeight="1">
@@ -6346,21 +6354,21 @@
       </c>
       <c r="B99" s="23" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="C99" s="24" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="D99" s="24" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E99" s="25" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F99" s="24" t="inlineStr">
         <is>
@@ -6368,25 +6376,25 @@
         </is>
       </c>
       <c r="G99" s="24" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H99" s="26" t="n">
-        <v>0.54</v>
+        <v>0.509</v>
       </c>
       <c r="I99" s="26" t="n">
-        <v>0.4762</v>
+        <v>0.4545</v>
       </c>
       <c r="J99" s="26" t="n">
-        <v>0.0638</v>
+        <v>0.0545</v>
       </c>
       <c r="K99" s="27" t="n">
-        <v>5.548</v>
+        <v>4.814</v>
       </c>
       <c r="L99" s="25" t="n">
         <v>0.5</v>
       </c>
       <c r="M99" s="27" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="N99" s="24" t="n">
         <v>4</v>
@@ -6397,126 +6405,66 @@
         </is>
       </c>
       <c r="P99" s="29" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="100" ht="17" customHeight="1">
-      <c r="A100" s="22" t="n">
+      <c r="A100" s="14" t="n">
         <v>46107</v>
       </c>
-      <c r="B100" s="23" t="inlineStr">
-        <is>
-          <t>Andrew Abbott</t>
-        </is>
-      </c>
-      <c r="C100" s="24" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="D100" s="24" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="E100" s="25" t="n">
+      <c r="B100" s="15" t="inlineStr">
+        <is>
+          <t>Matthew Boyd</t>
+        </is>
+      </c>
+      <c r="C100" s="16" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="D100" s="16" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="E100" s="17" t="n">
         <v>4.5</v>
       </c>
-      <c r="F100" s="24" t="inlineStr">
+      <c r="F100" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G100" s="24" t="n">
-        <v>120</v>
-      </c>
-      <c r="H100" s="26" t="n">
-        <v>0.509</v>
-      </c>
-      <c r="I100" s="26" t="n">
-        <v>0.4545</v>
-      </c>
-      <c r="J100" s="26" t="n">
-        <v>0.0545</v>
-      </c>
-      <c r="K100" s="27" t="n">
-        <v>4.814</v>
-      </c>
-      <c r="L100" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M100" s="27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N100" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="O100" s="28" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="P100" s="29" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="101" ht="17" customHeight="1">
-      <c r="A101" s="14" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B101" s="15" t="inlineStr">
-        <is>
-          <t>Matthew Boyd</t>
-        </is>
-      </c>
-      <c r="C101" s="16" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="D101" s="16" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
-      <c r="E101" s="17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F101" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="G101" s="16" t="n">
+      <c r="G100" s="16" t="n">
         <v>132</v>
       </c>
-      <c r="H101" s="18" t="n">
+      <c r="H100" s="18" t="n">
         <v>0.59</v>
       </c>
-      <c r="I101" s="18" t="n">
+      <c r="I100" s="18" t="n">
         <v>0.431</v>
       </c>
-      <c r="J101" s="18" t="n">
+      <c r="J100" s="18" t="n">
         <v>0.159</v>
       </c>
-      <c r="K101" s="19" t="n">
+      <c r="K100" s="19" t="n">
         <v>4.258</v>
       </c>
-      <c r="L101" s="17" t="n">
+      <c r="L100" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="M101" s="19" t="n">
+      <c r="M100" s="19" t="n">
         <v>0.7</v>
       </c>
-      <c r="N101" s="16" t="n">
+      <c r="N100" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="O101" s="20" t="inlineStr">
+      <c r="O100" s="20" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P101" s="21" t="n">
+      <c r="P100" s="21" t="n">
         <v>-1</v>
       </c>
     </row>

--- a/bet_log.xlsx
+++ b/bet_log.xlsx
@@ -828,16 +828,16 @@
         </is>
       </c>
       <c r="G6" s="8" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H6" s="10" t="n">
         <v>0.532</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.4762</v>
+        <v>0.4808</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.0558</v>
+        <v>0.0512</v>
       </c>
       <c r="K6" s="11" t="n">
         <v>4.44</v>
@@ -846,7 +846,7 @@
         <v>0.5</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="N6" s="8" t="inlineStr"/>
       <c r="O6" s="12" t="inlineStr"/>
@@ -858,47 +858,47 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Kris Bubic</t>
+          <t>Jake Irvin</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G7" s="8" t="n">
-        <v>-114</v>
+        <v>124</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.589</v>
+        <v>0.522</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>0.5327</v>
+        <v>0.4464</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.0563</v>
+        <v>0.0756</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>5.274</v>
+        <v>4.956</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="N7" s="8" t="inlineStr"/>
       <c r="O7" s="12" t="inlineStr"/>
@@ -910,47 +910,47 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Jake Irvin</t>
+          <t>Kris Bubic</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G8" s="8" t="n">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>0.522</v>
+        <v>0.589</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>0.4464</v>
+        <v>0.495</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.0756</v>
+        <v>0.094</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>4.956</v>
+        <v>5.274</v>
       </c>
       <c r="L8" s="9" t="n">
         <v>1</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.34</v>
+        <v>0.47</v>
       </c>
       <c r="N8" s="8" t="inlineStr"/>
       <c r="O8" s="12" t="inlineStr"/>
@@ -1192,16 +1192,16 @@
         </is>
       </c>
       <c r="G13" s="8" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="H13" s="10" t="n">
         <v>0.652</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>0.4902</v>
+        <v>0.4762</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.1618</v>
+        <v>0.1758</v>
       </c>
       <c r="K13" s="11" t="n">
         <v>4.815</v>
@@ -1210,7 +1210,7 @@
         <v>2</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
       <c r="N13" s="8" t="inlineStr"/>
       <c r="O13" s="12" t="inlineStr"/>

--- a/bet_log.xlsx
+++ b/bet_log.xlsx
@@ -69,6 +69,18 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00A4262C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C0392B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
@@ -82,18 +94,6 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="001A7431"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00A4262C"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00C0392B"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -121,17 +121,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FAD7D7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF8E7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D6EFD8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FAD7D7"/>
       </patternFill>
     </fill>
   </fills>
@@ -199,7 +199,7 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -220,10 +220,10 @@
     <xf numFmtId="2" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -690,30 +690,30 @@
         <v>120</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>-1.535 u</t>
+          <t>-3.431 u</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>-2.616 u</t>
+          <t>-1.142 u</t>
         </is>
       </c>
     </row>
@@ -848,61 +848,69 @@
       <c r="M6" s="11" t="n">
         <v>0.24</v>
       </c>
-      <c r="N6" s="8" t="inlineStr"/>
-      <c r="O6" s="12" t="inlineStr"/>
-      <c r="P6" s="13" t="inlineStr"/>
+      <c r="N6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P6" s="13" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="14" t="n">
         <v>46124</v>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Kyle Freeland</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="17" t="n">
         <v>3.5</v>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="G7" s="16" t="n">
         <v>-138</v>
       </c>
-      <c r="H7" s="10" t="n">
+      <c r="H7" s="18" t="n">
         <v>0.635</v>
       </c>
-      <c r="I7" s="10" t="n">
+      <c r="I7" s="18" t="n">
         <v>0.5798</v>
       </c>
-      <c r="J7" s="10" t="n">
+      <c r="J7" s="18" t="n">
         <v>0.0552</v>
       </c>
-      <c r="K7" s="11" t="n">
+      <c r="K7" s="19" t="n">
         <v>4.527</v>
       </c>
-      <c r="L7" s="9" t="n">
+      <c r="L7" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="M7" s="11" t="n">
+      <c r="M7" s="19" t="n">
         <v>0.33</v>
       </c>
-      <c r="N7" s="8" t="inlineStr"/>
-      <c r="O7" s="12" t="inlineStr"/>
-      <c r="P7" s="13" t="inlineStr"/>
+      <c r="N7" s="16" t="inlineStr"/>
+      <c r="O7" s="20" t="inlineStr"/>
+      <c r="P7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="6" t="n">
@@ -952,9 +960,17 @@
       <c r="M8" s="11" t="n">
         <v>0.28</v>
       </c>
-      <c r="N8" s="8" t="inlineStr"/>
-      <c r="O8" s="12" t="inlineStr"/>
-      <c r="P8" s="13" t="inlineStr"/>
+      <c r="N8" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P8" s="13" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="6" t="n">
@@ -1004,9 +1020,17 @@
       <c r="M9" s="11" t="n">
         <v>0.38</v>
       </c>
-      <c r="N9" s="8" t="inlineStr"/>
-      <c r="O9" s="12" t="inlineStr"/>
-      <c r="P9" s="13" t="inlineStr"/>
+      <c r="N9" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P9" s="13" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="6" t="n">
@@ -1056,9 +1080,17 @@
       <c r="M10" s="11" t="n">
         <v>0.4</v>
       </c>
-      <c r="N10" s="8" t="inlineStr"/>
-      <c r="O10" s="12" t="inlineStr"/>
-      <c r="P10" s="13" t="inlineStr"/>
+      <c r="N10" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P10" s="13" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="6" t="n">
@@ -1108,61 +1140,77 @@
       <c r="M11" s="11" t="n">
         <v>0.58</v>
       </c>
-      <c r="N11" s="8" t="inlineStr"/>
-      <c r="O11" s="12" t="inlineStr"/>
-      <c r="P11" s="13" t="inlineStr"/>
+      <c r="N11" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P11" s="13" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="6" t="n">
+      <c r="A12" s="22" t="n">
         <v>46124</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Cade Povich</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>BAL</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="24" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="25" t="n">
         <v>5.5</v>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G12" s="8" t="n">
+      <c r="G12" s="24" t="n">
         <v>-144</v>
       </c>
-      <c r="H12" s="10" t="n">
+      <c r="H12" s="26" t="n">
         <v>0.6870000000000001</v>
       </c>
-      <c r="I12" s="10" t="n">
+      <c r="I12" s="26" t="n">
         <v>0.5901999999999999</v>
       </c>
-      <c r="J12" s="10" t="n">
+      <c r="J12" s="26" t="n">
         <v>0.0968</v>
       </c>
-      <c r="K12" s="11" t="n">
+      <c r="K12" s="27" t="n">
         <v>4.556</v>
       </c>
-      <c r="L12" s="9" t="n">
+      <c r="L12" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="M12" s="11" t="n">
+      <c r="M12" s="27" t="n">
         <v>0.59</v>
       </c>
-      <c r="N12" s="8" t="inlineStr"/>
-      <c r="O12" s="12" t="inlineStr"/>
-      <c r="P12" s="13" t="inlineStr"/>
+      <c r="N12" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="O12" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P12" s="29" t="n">
+        <v>0.6944</v>
+      </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="6" t="n">
@@ -1212,6679 +1260,6719 @@
       <c r="M13" s="11" t="n">
         <v>0.52</v>
       </c>
-      <c r="N13" s="8" t="inlineStr"/>
-      <c r="O13" s="12" t="inlineStr"/>
-      <c r="P13" s="13" t="inlineStr"/>
+      <c r="N13" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P13" s="13" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="6" t="n">
+      <c r="A14" s="22" t="n">
         <v>46124</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Chris Sale</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="25" t="n">
         <v>6.5</v>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F14" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G14" s="8" t="n">
+      <c r="G14" s="24" t="n">
         <v>108</v>
       </c>
-      <c r="H14" s="10" t="n">
+      <c r="H14" s="26" t="n">
         <v>0.624</v>
       </c>
-      <c r="I14" s="10" t="n">
+      <c r="I14" s="26" t="n">
         <v>0.4808</v>
       </c>
-      <c r="J14" s="10" t="n">
+      <c r="J14" s="26" t="n">
         <v>0.1432</v>
       </c>
-      <c r="K14" s="11" t="n">
+      <c r="K14" s="27" t="n">
         <v>6.026</v>
       </c>
-      <c r="L14" s="9" t="n">
+      <c r="L14" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="M14" s="11" t="n">
+      <c r="M14" s="27" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="N14" s="8" t="inlineStr"/>
-      <c r="O14" s="12" t="inlineStr"/>
-      <c r="P14" s="13" t="inlineStr"/>
+      <c r="N14" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="O14" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P14" s="29" t="n">
+        <v>1.08</v>
+      </c>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="22" t="n">
         <v>46124</v>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>Andrew Abbott</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="24" t="inlineStr">
         <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="25" t="n">
         <v>6.5</v>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F15" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G15" s="8" t="n">
+      <c r="G15" s="24" t="n">
         <v>-168</v>
       </c>
-      <c r="H15" s="10" t="n">
+      <c r="H15" s="26" t="n">
         <v>0.821</v>
       </c>
-      <c r="I15" s="10" t="n">
+      <c r="I15" s="26" t="n">
         <v>0.6269</v>
       </c>
-      <c r="J15" s="10" t="n">
+      <c r="J15" s="26" t="n">
         <v>0.1941</v>
       </c>
-      <c r="K15" s="11" t="n">
+      <c r="K15" s="27" t="n">
         <v>4.439</v>
       </c>
-      <c r="L15" s="9" t="n">
+      <c r="L15" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M15" s="11" t="n">
+      <c r="M15" s="27" t="n">
         <v>1.3</v>
       </c>
-      <c r="N15" s="8" t="inlineStr"/>
-      <c r="O15" s="12" t="inlineStr"/>
-      <c r="P15" s="13" t="inlineStr"/>
+      <c r="N15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P15" s="29" t="n">
+        <v>0.5952</v>
+      </c>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="6" t="n">
+      <c r="A16" s="22" t="n">
         <v>46124</v>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>Nick Pivetta</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="25" t="n">
         <v>7.5</v>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G16" s="8" t="n">
+      <c r="G16" s="24" t="n">
         <v>-140</v>
       </c>
-      <c r="H16" s="10" t="n">
+      <c r="H16" s="26" t="n">
         <v>0.805</v>
       </c>
-      <c r="I16" s="10" t="n">
+      <c r="I16" s="26" t="n">
         <v>0.5833</v>
       </c>
-      <c r="J16" s="10" t="n">
+      <c r="J16" s="26" t="n">
         <v>0.2217</v>
       </c>
-      <c r="K16" s="11" t="n">
+      <c r="K16" s="27" t="n">
         <v>5.508</v>
       </c>
-      <c r="L16" s="9" t="n">
+      <c r="L16" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M16" s="11" t="n">
+      <c r="M16" s="27" t="n">
         <v>1.33</v>
       </c>
-      <c r="N16" s="8" t="inlineStr"/>
-      <c r="O16" s="12" t="inlineStr"/>
-      <c r="P16" s="13" t="inlineStr"/>
+      <c r="N16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="O16" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P16" s="29" t="n">
+        <v>0.7143</v>
+      </c>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="6" t="n">
+      <c r="A17" s="22" t="n">
         <v>46124</v>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>Tarik Skubal</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="25" t="n">
         <v>7.5</v>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G17" s="8" t="n">
+      <c r="G17" s="24" t="n">
         <v>102</v>
       </c>
-      <c r="H17" s="10" t="n">
+      <c r="H17" s="26" t="n">
         <v>0.721</v>
       </c>
-      <c r="I17" s="10" t="n">
+      <c r="I17" s="26" t="n">
         <v>0.495</v>
       </c>
-      <c r="J17" s="10" t="n">
+      <c r="J17" s="26" t="n">
         <v>0.226</v>
       </c>
-      <c r="K17" s="11" t="n">
+      <c r="K17" s="27" t="n">
         <v>5.716</v>
       </c>
-      <c r="L17" s="9" t="n">
+      <c r="L17" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M17" s="11" t="n">
+      <c r="M17" s="27" t="n">
         <v>1.12</v>
       </c>
-      <c r="N17" s="8" t="inlineStr"/>
-      <c r="O17" s="12" t="inlineStr"/>
-      <c r="P17" s="13" t="inlineStr"/>
+      <c r="N17" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="O17" s="28" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="P17" s="29" t="n">
+        <v>1.02</v>
+      </c>
     </row>
     <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="22" t="n">
         <v>46123</v>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Casey Mize</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="E18" s="17" t="n">
+      <c r="E18" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F18" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G18" s="16" t="n">
+      <c r="G18" s="24" t="n">
         <v>114</v>
       </c>
-      <c r="H18" s="18" t="n">
+      <c r="H18" s="26" t="n">
         <v>0.5620000000000001</v>
       </c>
-      <c r="I18" s="18" t="n">
+      <c r="I18" s="26" t="n">
         <v>0.4673</v>
       </c>
-      <c r="J18" s="18" t="n">
+      <c r="J18" s="26" t="n">
         <v>0.09470000000000001</v>
       </c>
-      <c r="K18" s="19" t="n">
+      <c r="K18" s="27" t="n">
         <v>4.99</v>
       </c>
-      <c r="L18" s="17" t="n">
+      <c r="L18" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="M18" s="19" t="n">
+      <c r="M18" s="27" t="n">
         <v>0.44</v>
       </c>
-      <c r="N18" s="16" t="n">
+      <c r="N18" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="O18" s="20" t="inlineStr">
+      <c r="O18" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P18" s="21" t="n">
+      <c r="P18" s="29" t="n">
         <v>1.14</v>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="22" t="n">
         <v>46123</v>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Kyle Harrison</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E19" s="17" t="n">
+      <c r="E19" s="25" t="n">
         <v>5.5</v>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F19" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G19" s="16" t="n">
+      <c r="G19" s="24" t="n">
         <v>102</v>
       </c>
-      <c r="H19" s="18" t="n">
+      <c r="H19" s="26" t="n">
         <v>0.615</v>
       </c>
-      <c r="I19" s="18" t="n">
+      <c r="I19" s="26" t="n">
         <v>0.495</v>
       </c>
-      <c r="J19" s="18" t="n">
+      <c r="J19" s="26" t="n">
         <v>0.12</v>
       </c>
-      <c r="K19" s="19" t="n">
+      <c r="K19" s="27" t="n">
         <v>5.176</v>
       </c>
-      <c r="L19" s="17" t="n">
+      <c r="L19" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="M19" s="19" t="n">
+      <c r="M19" s="27" t="n">
         <v>0.59</v>
       </c>
-      <c r="N19" s="16" t="n">
+      <c r="N19" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="O19" s="20" t="inlineStr">
+      <c r="O19" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P19" s="21" t="n">
+      <c r="P19" s="29" t="n">
         <v>1.02</v>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="22" t="n">
         <v>46123</v>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Edward Cabrera</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr">
         <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="E20" s="17" t="n">
+      <c r="E20" s="25" t="n">
         <v>6.5</v>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F20" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G20" s="16" t="n">
+      <c r="G20" s="24" t="n">
         <v>-154</v>
       </c>
-      <c r="H20" s="18" t="n">
+      <c r="H20" s="26" t="n">
         <v>0.736</v>
       </c>
-      <c r="I20" s="18" t="n">
+      <c r="I20" s="26" t="n">
         <v>0.6063</v>
       </c>
-      <c r="J20" s="18" t="n">
+      <c r="J20" s="26" t="n">
         <v>0.1297</v>
       </c>
-      <c r="K20" s="19" t="n">
+      <c r="K20" s="27" t="n">
         <v>5.09</v>
       </c>
-      <c r="L20" s="17" t="n">
+      <c r="L20" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="M20" s="19" t="n">
+      <c r="M20" s="27" t="n">
         <v>0.82</v>
       </c>
-      <c r="N20" s="16" t="n">
+      <c r="N20" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="O20" s="20" t="inlineStr">
+      <c r="O20" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P20" s="21" t="n">
+      <c r="P20" s="29" t="n">
         <v>0.6494</v>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="22" t="n">
         <v>46123</v>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>Jacob Lopez</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="24" t="inlineStr">
         <is>
           <t>OAK</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="24" t="inlineStr">
         <is>
           <t>NYM</t>
         </is>
       </c>
-      <c r="E21" s="17" t="n">
+      <c r="E21" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F21" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G21" s="16" t="n">
+      <c r="G21" s="24" t="n">
         <v>-154</v>
       </c>
-      <c r="H21" s="18" t="n">
+      <c r="H21" s="26" t="n">
         <v>0.674</v>
       </c>
-      <c r="I21" s="18" t="n">
+      <c r="I21" s="26" t="n">
         <v>0.6063</v>
       </c>
-      <c r="J21" s="18" t="n">
+      <c r="J21" s="26" t="n">
         <v>0.0677</v>
       </c>
-      <c r="K21" s="19" t="n">
+      <c r="K21" s="27" t="n">
         <v>5.882</v>
       </c>
-      <c r="L21" s="17" t="n">
+      <c r="L21" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M21" s="19" t="n">
+      <c r="M21" s="27" t="n">
         <v>0.43</v>
       </c>
-      <c r="N21" s="16" t="n">
+      <c r="N21" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="O21" s="20" t="inlineStr">
+      <c r="O21" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P21" s="21" t="n">
+      <c r="P21" s="29" t="n">
         <v>0.6494</v>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="22" t="n">
         <v>46122</v>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>Shane Baz</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>BAL</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="24" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="E22" s="17" t="n">
+      <c r="E22" s="25" t="n">
         <v>5.5</v>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F22" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G22" s="16" t="n">
+      <c r="G22" s="24" t="n">
         <v>-132</v>
       </c>
-      <c r="H22" s="18" t="n">
+      <c r="H22" s="26" t="n">
         <v>0.67</v>
       </c>
-      <c r="I22" s="18" t="n">
+      <c r="I22" s="26" t="n">
         <v>0.569</v>
       </c>
-      <c r="J22" s="18" t="n">
+      <c r="J22" s="26" t="n">
         <v>0.101</v>
       </c>
-      <c r="K22" s="19" t="n">
+      <c r="K22" s="27" t="n">
         <v>4.584</v>
       </c>
-      <c r="L22" s="17" t="n">
+      <c r="L22" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="M22" s="19" t="n">
+      <c r="M22" s="27" t="n">
         <v>0.59</v>
       </c>
-      <c r="N22" s="16" t="n">
+      <c r="N22" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="O22" s="20" t="inlineStr">
+      <c r="O22" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P22" s="21" t="n">
+      <c r="P22" s="29" t="n">
         <v>0.7576000000000001</v>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="22" t="n">
         <v>46122</v>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>Steven Matz</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C23" s="24" t="inlineStr">
         <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="24" t="inlineStr">
         <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E23" s="17" t="n">
+      <c r="E23" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F23" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G23" s="16" t="n">
+      <c r="G23" s="24" t="n">
         <v>104</v>
       </c>
-      <c r="H23" s="18" t="n">
+      <c r="H23" s="26" t="n">
         <v>0.671</v>
       </c>
-      <c r="I23" s="18" t="n">
+      <c r="I23" s="26" t="n">
         <v>0.4902</v>
       </c>
-      <c r="J23" s="18" t="n">
+      <c r="J23" s="26" t="n">
         <v>0.1808</v>
       </c>
-      <c r="K23" s="19" t="n">
+      <c r="K23" s="27" t="n">
         <v>5.795</v>
       </c>
-      <c r="L23" s="17" t="n">
+      <c r="L23" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M23" s="19" t="n">
+      <c r="M23" s="27" t="n">
         <v>0.89</v>
       </c>
-      <c r="N23" s="16" t="n">
+      <c r="N23" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="O23" s="20" t="inlineStr">
+      <c r="O23" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P23" s="21" t="n">
+      <c r="P23" s="29" t="n">
         <v>1.04</v>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="22" t="n">
+      <c r="A24" s="6" t="n">
         <v>46122</v>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Shota Imanaga</t>
         </is>
       </c>
-      <c r="C24" s="24" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="D24" s="24" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="E24" s="25" t="n">
+      <c r="E24" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="F24" s="24" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G24" s="24" t="n">
+      <c r="G24" s="8" t="n">
         <v>110</v>
       </c>
-      <c r="H24" s="26" t="n">
+      <c r="H24" s="10" t="n">
         <v>0.652</v>
       </c>
-      <c r="I24" s="26" t="n">
+      <c r="I24" s="10" t="n">
         <v>0.4762</v>
       </c>
-      <c r="J24" s="26" t="n">
+      <c r="J24" s="10" t="n">
         <v>0.1758</v>
       </c>
-      <c r="K24" s="27" t="n">
+      <c r="K24" s="11" t="n">
         <v>4.815</v>
       </c>
-      <c r="L24" s="25" t="n">
+      <c r="L24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="M24" s="27" t="n">
+      <c r="M24" s="11" t="n">
         <v>0.84</v>
       </c>
-      <c r="N24" s="24" t="n">
+      <c r="N24" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="O24" s="28" t="inlineStr">
+      <c r="O24" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P24" s="29" t="n">
+      <c r="P24" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="22" t="n">
+      <c r="A25" s="6" t="n">
         <v>46122</v>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Simeon Woods Richardson</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="D25" s="24" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="E25" s="25" t="n">
+      <c r="E25" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="F25" s="24" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G25" s="24" t="n">
+      <c r="G25" s="8" t="n">
         <v>-154</v>
       </c>
-      <c r="H25" s="26" t="n">
+      <c r="H25" s="10" t="n">
         <v>0.724</v>
       </c>
-      <c r="I25" s="26" t="n">
+      <c r="I25" s="10" t="n">
         <v>0.6063</v>
       </c>
-      <c r="J25" s="26" t="n">
+      <c r="J25" s="10" t="n">
         <v>0.1177</v>
       </c>
-      <c r="K25" s="27" t="n">
+      <c r="K25" s="11" t="n">
         <v>5.206</v>
       </c>
-      <c r="L25" s="25" t="n">
+      <c r="L25" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="M25" s="27" t="n">
+      <c r="M25" s="11" t="n">
         <v>0.75</v>
       </c>
-      <c r="N25" s="24" t="n">
+      <c r="N25" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="O25" s="28" t="inlineStr">
+      <c r="O25" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P25" s="29" t="n">
+      <c r="P25" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="22" t="n">
+      <c r="A26" s="6" t="n">
         <v>46122</v>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Bryce Elder</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="D26" s="24" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E26" s="25" t="n">
+      <c r="E26" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F26" s="24" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G26" s="24" t="n">
+      <c r="G26" s="8" t="n">
         <v>110</v>
       </c>
-      <c r="H26" s="26" t="n">
+      <c r="H26" s="10" t="n">
         <v>0.598</v>
       </c>
-      <c r="I26" s="26" t="n">
+      <c r="I26" s="10" t="n">
         <v>0.4762</v>
       </c>
-      <c r="J26" s="26" t="n">
+      <c r="J26" s="10" t="n">
         <v>0.1218</v>
       </c>
-      <c r="K26" s="27" t="n">
+      <c r="K26" s="11" t="n">
         <v>5.484</v>
       </c>
-      <c r="L26" s="25" t="n">
+      <c r="L26" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="M26" s="27" t="n">
+      <c r="M26" s="11" t="n">
         <v>0.58</v>
       </c>
-      <c r="N26" s="24" t="n">
+      <c r="N26" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="O26" s="28" t="inlineStr">
+      <c r="O26" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P26" s="29" t="n">
+      <c r="P26" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="22" t="n">
+      <c r="A27" s="6" t="n">
         <v>46122</v>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>Davis Martin</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="D27" s="24" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="E27" s="25" t="n">
+      <c r="E27" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="F27" s="24" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G27" s="24" t="n">
+      <c r="G27" s="8" t="n">
         <v>-118</v>
       </c>
-      <c r="H27" s="26" t="n">
+      <c r="H27" s="10" t="n">
         <v>0.641</v>
       </c>
-      <c r="I27" s="26" t="n">
+      <c r="I27" s="10" t="n">
         <v>0.5413</v>
       </c>
-      <c r="J27" s="26" t="n">
+      <c r="J27" s="10" t="n">
         <v>0.0997</v>
       </c>
-      <c r="K27" s="27" t="n">
+      <c r="K27" s="11" t="n">
         <v>4.654</v>
       </c>
-      <c r="L27" s="25" t="n">
+      <c r="L27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M27" s="27" t="n">
+      <c r="M27" s="11" t="n">
         <v>0.54</v>
       </c>
-      <c r="N27" s="24" t="n">
+      <c r="N27" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="O27" s="28" t="inlineStr">
+      <c r="O27" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P27" s="29" t="n">
+      <c r="P27" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="22" t="n">
+      <c r="A28" s="6" t="n">
         <v>46122</v>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Kris Bubic</t>
         </is>
       </c>
-      <c r="C28" s="24" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="D28" s="24" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E28" s="25" t="n">
+      <c r="E28" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="F28" s="24" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G28" s="24" t="n">
+      <c r="G28" s="8" t="n">
         <v>102</v>
       </c>
-      <c r="H28" s="26" t="n">
+      <c r="H28" s="10" t="n">
         <v>0.589</v>
       </c>
-      <c r="I28" s="26" t="n">
+      <c r="I28" s="10" t="n">
         <v>0.495</v>
       </c>
-      <c r="J28" s="26" t="n">
+      <c r="J28" s="10" t="n">
         <v>0.094</v>
       </c>
-      <c r="K28" s="27" t="n">
+      <c r="K28" s="11" t="n">
         <v>5.274</v>
       </c>
-      <c r="L28" s="25" t="n">
+      <c r="L28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M28" s="27" t="n">
+      <c r="M28" s="11" t="n">
         <v>0.47</v>
       </c>
-      <c r="N28" s="24" t="n">
+      <c r="N28" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="O28" s="28" t="inlineStr">
+      <c r="O28" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P28" s="29" t="n">
+      <c r="P28" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="22" t="n">
         <v>46122</v>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>Jake Irvin</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D29" s="24" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E29" s="17" t="n">
+      <c r="E29" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F29" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G29" s="16" t="n">
+      <c r="G29" s="24" t="n">
         <v>124</v>
       </c>
-      <c r="H29" s="18" t="n">
+      <c r="H29" s="26" t="n">
         <v>0.522</v>
       </c>
-      <c r="I29" s="18" t="n">
+      <c r="I29" s="26" t="n">
         <v>0.4464</v>
       </c>
-      <c r="J29" s="18" t="n">
+      <c r="J29" s="26" t="n">
         <v>0.0756</v>
       </c>
-      <c r="K29" s="19" t="n">
+      <c r="K29" s="27" t="n">
         <v>4.956</v>
       </c>
-      <c r="L29" s="17" t="n">
+      <c r="L29" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="M29" s="19" t="n">
+      <c r="M29" s="27" t="n">
         <v>0.34</v>
       </c>
-      <c r="N29" s="16" t="n">
+      <c r="N29" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="O29" s="20" t="inlineStr">
+      <c r="O29" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P29" s="21" t="n">
+      <c r="P29" s="29" t="n">
         <v>1.24</v>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="22" t="n">
         <v>46122</v>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>Chad Patrick</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C30" s="24" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D30" s="24" t="inlineStr">
         <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E30" s="17" t="n">
+      <c r="E30" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F30" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G30" s="16" t="n">
+      <c r="G30" s="24" t="n">
         <v>108</v>
       </c>
-      <c r="H30" s="18" t="n">
+      <c r="H30" s="26" t="n">
         <v>0.532</v>
       </c>
-      <c r="I30" s="18" t="n">
+      <c r="I30" s="26" t="n">
         <v>0.4808</v>
       </c>
-      <c r="J30" s="18" t="n">
+      <c r="J30" s="26" t="n">
         <v>0.0512</v>
       </c>
-      <c r="K30" s="19" t="n">
+      <c r="K30" s="27" t="n">
         <v>4.44</v>
       </c>
-      <c r="L30" s="17" t="n">
+      <c r="L30" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M30" s="19" t="n">
+      <c r="M30" s="27" t="n">
         <v>0.25</v>
       </c>
-      <c r="N30" s="16" t="n">
+      <c r="N30" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="O30" s="20" t="inlineStr">
+      <c r="O30" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P30" s="21" t="n">
+      <c r="P30" s="29" t="n">
         <v>1.08</v>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="22" t="n">
         <v>46121</v>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>Nolan McLean</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C31" s="24" t="inlineStr">
         <is>
           <t>NYM</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D31" s="24" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="E31" s="17" t="n">
+      <c r="E31" s="25" t="n">
         <v>5.5</v>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F31" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G31" s="16" t="n">
+      <c r="G31" s="24" t="n">
         <v>-122</v>
       </c>
-      <c r="H31" s="18" t="n">
+      <c r="H31" s="26" t="n">
         <v>0.615</v>
       </c>
-      <c r="I31" s="18" t="n">
+      <c r="I31" s="26" t="n">
         <v>0.5495</v>
       </c>
-      <c r="J31" s="18" t="n">
+      <c r="J31" s="26" t="n">
         <v>0.0655</v>
       </c>
-      <c r="K31" s="19" t="n">
+      <c r="K31" s="27" t="n">
         <v>6.497</v>
       </c>
-      <c r="L31" s="17" t="n">
+      <c r="L31" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M31" s="19" t="n">
+      <c r="M31" s="27" t="n">
         <v>0.36</v>
       </c>
-      <c r="N31" s="16" t="n">
+      <c r="N31" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="O31" s="20" t="inlineStr">
+      <c r="O31" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P31" s="21" t="n">
+      <c r="P31" s="29" t="n">
         <v>0.8197</v>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="22" t="n">
+      <c r="A32" s="6" t="n">
         <v>46121</v>
       </c>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Jack Flaherty</t>
         </is>
       </c>
-      <c r="C32" s="24" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="D32" s="24" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="E32" s="25" t="n">
+      <c r="E32" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="F32" s="24" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G32" s="24" t="n">
+      <c r="G32" s="8" t="n">
         <v>112</v>
       </c>
-      <c r="H32" s="26" t="n">
+      <c r="H32" s="10" t="n">
         <v>0.542</v>
       </c>
-      <c r="I32" s="26" t="n">
+      <c r="I32" s="10" t="n">
         <v>0.4717</v>
       </c>
-      <c r="J32" s="26" t="n">
+      <c r="J32" s="10" t="n">
         <v>0.0703</v>
       </c>
-      <c r="K32" s="27" t="n">
+      <c r="K32" s="11" t="n">
         <v>5.418</v>
       </c>
-      <c r="L32" s="25" t="n">
+      <c r="L32" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="M32" s="27" t="n">
+      <c r="M32" s="11" t="n">
         <v>0.33</v>
       </c>
-      <c r="N32" s="24" t="n">
+      <c r="N32" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="O32" s="28" t="inlineStr">
+      <c r="O32" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P32" s="29" t="n">
+      <c r="P32" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="22" t="n">
+      <c r="A33" s="6" t="n">
         <v>46120</v>
       </c>
-      <c r="B33" s="23" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>Cristian Javier</t>
         </is>
       </c>
-      <c r="C33" s="24" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="D33" s="24" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="E33" s="25" t="n">
+      <c r="E33" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F33" s="24" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G33" s="24" t="n">
+      <c r="G33" s="8" t="n">
         <v>124</v>
       </c>
-      <c r="H33" s="26" t="n">
+      <c r="H33" s="10" t="n">
         <v>0.521</v>
       </c>
-      <c r="I33" s="26" t="n">
+      <c r="I33" s="10" t="n">
         <v>0.4464</v>
       </c>
-      <c r="J33" s="26" t="n">
+      <c r="J33" s="10" t="n">
         <v>0.0746</v>
       </c>
-      <c r="K33" s="27" t="n">
+      <c r="K33" s="11" t="n">
         <v>4.922</v>
       </c>
-      <c r="L33" s="25" t="n">
+      <c r="L33" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="M33" s="27" t="n">
+      <c r="M33" s="11" t="n">
         <v>0.34</v>
       </c>
-      <c r="N33" s="24" t="n">
+      <c r="N33" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="O33" s="28" t="inlineStr">
+      <c r="O33" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P33" s="29" t="n">
+      <c r="P33" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="22" t="n">
+      <c r="A34" s="6" t="n">
         <v>46120</v>
       </c>
-      <c r="B34" s="23" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>Colin Rea</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="D34" s="24" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E34" s="25" t="n">
+      <c r="E34" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="F34" s="24" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G34" s="24" t="n">
+      <c r="G34" s="8" t="n">
         <v>114</v>
       </c>
-      <c r="H34" s="26" t="n">
+      <c r="H34" s="10" t="n">
         <v>0.674</v>
       </c>
-      <c r="I34" s="26" t="n">
+      <c r="I34" s="10" t="n">
         <v>0.4673</v>
       </c>
-      <c r="J34" s="26" t="n">
+      <c r="J34" s="10" t="n">
         <v>0.2067</v>
       </c>
-      <c r="K34" s="27" t="n">
+      <c r="K34" s="11" t="n">
         <v>4.888</v>
       </c>
-      <c r="L34" s="25" t="n">
+      <c r="L34" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="M34" s="27" t="n">
+      <c r="M34" s="11" t="n">
         <v>0.97</v>
       </c>
-      <c r="N34" s="24" t="n">
+      <c r="N34" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="O34" s="28" t="inlineStr">
+      <c r="O34" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P34" s="29" t="n">
+      <c r="P34" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="14" t="n">
+      <c r="A35" s="22" t="n">
         <v>46120</v>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>Sean Burke</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C35" s="24" t="inlineStr">
         <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D35" s="24" t="inlineStr">
         <is>
           <t>BAL</t>
         </is>
       </c>
-      <c r="E35" s="17" t="n">
+      <c r="E35" s="25" t="n">
         <v>5.5</v>
       </c>
-      <c r="F35" s="16" t="inlineStr">
+      <c r="F35" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G35" s="16" t="n">
+      <c r="G35" s="24" t="n">
         <v>110</v>
       </c>
-      <c r="H35" s="18" t="n">
+      <c r="H35" s="26" t="n">
         <v>0.649</v>
       </c>
-      <c r="I35" s="18" t="n">
+      <c r="I35" s="26" t="n">
         <v>0.4762</v>
       </c>
-      <c r="J35" s="18" t="n">
+      <c r="J35" s="26" t="n">
         <v>0.1728</v>
       </c>
-      <c r="K35" s="19" t="n">
+      <c r="K35" s="27" t="n">
         <v>4.876</v>
       </c>
-      <c r="L35" s="17" t="n">
+      <c r="L35" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M35" s="19" t="n">
+      <c r="M35" s="27" t="n">
         <v>0.82</v>
       </c>
-      <c r="N35" s="16" t="n">
+      <c r="N35" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="O35" s="20" t="inlineStr">
+      <c r="O35" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P35" s="21" t="n">
+      <c r="P35" s="29" t="n">
         <v>1.1</v>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="14" t="n">
+      <c r="A36" s="22" t="n">
         <v>46120</v>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B36" s="23" t="inlineStr">
         <is>
           <t>Michael King</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="C36" s="24" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D36" s="24" t="inlineStr">
         <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="E36" s="17" t="n">
+      <c r="E36" s="25" t="n">
         <v>5.5</v>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="F36" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G36" s="16" t="n">
+      <c r="G36" s="24" t="n">
         <v>-102</v>
       </c>
-      <c r="H36" s="18" t="n">
+      <c r="H36" s="26" t="n">
         <v>0.63</v>
       </c>
-      <c r="I36" s="18" t="n">
+      <c r="I36" s="26" t="n">
         <v>0.505</v>
       </c>
-      <c r="J36" s="18" t="n">
+      <c r="J36" s="26" t="n">
         <v>0.125</v>
       </c>
-      <c r="K36" s="19" t="n">
+      <c r="K36" s="27" t="n">
         <v>4.885</v>
       </c>
-      <c r="L36" s="17" t="n">
+      <c r="L36" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="M36" s="19" t="n">
+      <c r="M36" s="27" t="n">
         <v>0.63</v>
       </c>
-      <c r="N36" s="16" t="n">
+      <c r="N36" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="O36" s="20" t="inlineStr">
+      <c r="O36" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P36" s="21" t="n">
+      <c r="P36" s="29" t="n">
         <v>0.9804</v>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="22" t="n">
+      <c r="A37" s="6" t="n">
         <v>46120</v>
       </c>
-      <c r="B37" s="23" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>Tyler Mahle</t>
         </is>
       </c>
-      <c r="C37" s="24" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="D37" s="24" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E37" s="25" t="n">
+      <c r="E37" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F37" s="24" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G37" s="24" t="n">
+      <c r="G37" s="8" t="n">
         <v>-125</v>
       </c>
-      <c r="H37" s="26" t="n">
+      <c r="H37" s="10" t="n">
         <v>0.634</v>
       </c>
-      <c r="I37" s="26" t="n">
+      <c r="I37" s="10" t="n">
         <v>0.5556</v>
       </c>
-      <c r="J37" s="26" t="n">
+      <c r="J37" s="10" t="n">
         <v>0.0784</v>
       </c>
-      <c r="K37" s="27" t="n">
+      <c r="K37" s="11" t="n">
         <v>4.033</v>
       </c>
-      <c r="L37" s="25" t="n">
+      <c r="L37" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M37" s="27" t="n">
+      <c r="M37" s="11" t="n">
         <v>0.44</v>
       </c>
-      <c r="N37" s="24" t="n">
+      <c r="N37" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="O37" s="28" t="inlineStr">
+      <c r="O37" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P37" s="29" t="n">
+      <c r="P37" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="14" t="n">
+      <c r="A38" s="22" t="n">
         <v>46120</v>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B38" s="23" t="inlineStr">
         <is>
           <t>Michael Lorenzen</t>
         </is>
       </c>
-      <c r="C38" s="16" t="inlineStr">
+      <c r="C38" s="24" t="inlineStr">
         <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="D38" s="24" t="inlineStr">
         <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E38" s="17" t="n">
+      <c r="E38" s="25" t="n">
         <v>3.5</v>
       </c>
-      <c r="F38" s="16" t="inlineStr">
+      <c r="F38" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G38" s="16" t="n">
+      <c r="G38" s="24" t="n">
         <v>-130</v>
       </c>
-      <c r="H38" s="18" t="n">
+      <c r="H38" s="26" t="n">
         <v>0.63</v>
       </c>
-      <c r="I38" s="18" t="n">
+      <c r="I38" s="26" t="n">
         <v>0.5652</v>
       </c>
-      <c r="J38" s="18" t="n">
+      <c r="J38" s="26" t="n">
         <v>0.0648</v>
       </c>
-      <c r="K38" s="19" t="n">
+      <c r="K38" s="27" t="n">
         <v>4.329</v>
       </c>
-      <c r="L38" s="17" t="n">
+      <c r="L38" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M38" s="19" t="n">
+      <c r="M38" s="27" t="n">
         <v>0.37</v>
       </c>
-      <c r="N38" s="16" t="n">
+      <c r="N38" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="O38" s="20" t="inlineStr">
+      <c r="O38" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P38" s="21" t="n">
+      <c r="P38" s="29" t="n">
         <v>0.7692</v>
       </c>
     </row>
     <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="22" t="n">
+      <c r="A39" s="6" t="n">
         <v>46120</v>
       </c>
-      <c r="B39" s="23" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>Joey Cantillo</t>
         </is>
       </c>
-      <c r="C39" s="24" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="D39" s="24" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="E39" s="25" t="n">
+      <c r="E39" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="F39" s="24" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G39" s="24" t="n">
+      <c r="G39" s="8" t="n">
         <v>-154</v>
       </c>
-      <c r="H39" s="26" t="n">
+      <c r="H39" s="10" t="n">
         <v>0.679</v>
       </c>
-      <c r="I39" s="26" t="n">
+      <c r="I39" s="10" t="n">
         <v>0.6063</v>
       </c>
-      <c r="J39" s="26" t="n">
+      <c r="J39" s="10" t="n">
         <v>0.0727</v>
       </c>
-      <c r="K39" s="27" t="n">
+      <c r="K39" s="11" t="n">
         <v>4.665</v>
       </c>
-      <c r="L39" s="25" t="n">
+      <c r="L39" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="M39" s="27" t="n">
+      <c r="M39" s="11" t="n">
         <v>0.46</v>
       </c>
-      <c r="N39" s="24" t="n">
+      <c r="N39" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="O39" s="28" t="inlineStr">
+      <c r="O39" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P39" s="29" t="n">
+      <c r="P39" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="14" t="n">
+      <c r="A40" s="22" t="n">
         <v>46120</v>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B40" s="23" t="inlineStr">
         <is>
           <t>Eury Pérez</t>
         </is>
       </c>
-      <c r="C40" s="16" t="inlineStr">
+      <c r="C40" s="24" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D40" s="24" t="inlineStr">
         <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="E40" s="17" t="n">
+      <c r="E40" s="25" t="n">
         <v>6.5</v>
       </c>
-      <c r="F40" s="16" t="inlineStr">
+      <c r="F40" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G40" s="16" t="n">
+      <c r="G40" s="24" t="n">
         <v>-132</v>
       </c>
-      <c r="H40" s="18" t="n">
+      <c r="H40" s="26" t="n">
         <v>0.635</v>
       </c>
-      <c r="I40" s="18" t="n">
+      <c r="I40" s="26" t="n">
         <v>0.569</v>
       </c>
-      <c r="J40" s="18" t="n">
+      <c r="J40" s="26" t="n">
         <v>0.066</v>
       </c>
-      <c r="K40" s="19" t="n">
+      <c r="K40" s="27" t="n">
         <v>5.853</v>
       </c>
-      <c r="L40" s="17" t="n">
+      <c r="L40" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M40" s="19" t="n">
+      <c r="M40" s="27" t="n">
         <v>0.38</v>
       </c>
-      <c r="N40" s="16" t="n">
+      <c r="N40" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="O40" s="20" t="inlineStr">
+      <c r="O40" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P40" s="21" t="n">
+      <c r="P40" s="29" t="n">
         <v>0.7576000000000001</v>
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="22" t="n">
+      <c r="A41" s="6" t="n">
         <v>46120</v>
       </c>
-      <c r="B41" s="23" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Dylan Cease</t>
         </is>
       </c>
-      <c r="C41" s="24" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="D41" s="24" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E41" s="25" t="n">
+      <c r="E41" s="9" t="n">
         <v>6.5</v>
       </c>
-      <c r="F41" s="24" t="inlineStr">
+      <c r="F41" s="8" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G41" s="24" t="n">
+      <c r="G41" s="8" t="n">
         <v>110</v>
       </c>
-      <c r="H41" s="26" t="n">
+      <c r="H41" s="10" t="n">
         <v>0.546</v>
       </c>
-      <c r="I41" s="26" t="n">
+      <c r="I41" s="10" t="n">
         <v>0.4762</v>
       </c>
-      <c r="J41" s="26" t="n">
+      <c r="J41" s="10" t="n">
         <v>0.0698</v>
       </c>
-      <c r="K41" s="27" t="n">
+      <c r="K41" s="11" t="n">
         <v>6.326</v>
       </c>
-      <c r="L41" s="25" t="n">
+      <c r="L41" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="M41" s="27" t="n">
+      <c r="M41" s="11" t="n">
         <v>0.33</v>
       </c>
-      <c r="N41" s="24" t="n">
+      <c r="N41" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="O41" s="28" t="inlineStr">
+      <c r="O41" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P41" s="29" t="n">
+      <c r="P41" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="22" t="n">
+      <c r="A42" s="6" t="n">
         <v>46120</v>
       </c>
-      <c r="B42" s="23" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>Michael McGreevy</t>
         </is>
       </c>
-      <c r="C42" s="24" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="D42" s="24" t="inlineStr">
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E42" s="25" t="n">
+      <c r="E42" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="F42" s="24" t="inlineStr">
+      <c r="F42" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G42" s="24" t="n">
+      <c r="G42" s="8" t="n">
         <v>-114</v>
       </c>
-      <c r="H42" s="26" t="n">
+      <c r="H42" s="10" t="n">
         <v>0.586</v>
       </c>
-      <c r="I42" s="26" t="n">
+      <c r="I42" s="10" t="n">
         <v>0.5327</v>
       </c>
-      <c r="J42" s="26" t="n">
+      <c r="J42" s="10" t="n">
         <v>0.0533</v>
       </c>
-      <c r="K42" s="27" t="n">
+      <c r="K42" s="11" t="n">
         <v>4.248</v>
       </c>
-      <c r="L42" s="25" t="n">
+      <c r="L42" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="M42" s="27" t="n">
+      <c r="M42" s="11" t="n">
         <v>0.29</v>
       </c>
-      <c r="N42" s="24" t="n">
+      <c r="N42" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="O42" s="28" t="inlineStr">
+      <c r="O42" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P42" s="29" t="n">
+      <c r="P42" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="6" t="n">
+      <c r="A43" s="14" t="n">
         <v>46119</v>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>Drew Rasmussen</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C43" s="16" t="inlineStr">
         <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="E43" s="9" t="n">
+      <c r="E43" s="17" t="n">
         <v>4.5</v>
       </c>
-      <c r="F43" s="8" t="inlineStr">
+      <c r="F43" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G43" s="8" t="n">
+      <c r="G43" s="16" t="n">
         <v>-104</v>
       </c>
-      <c r="H43" s="10" t="n">
+      <c r="H43" s="18" t="n">
         <v>0.599</v>
       </c>
-      <c r="I43" s="10" t="n">
+      <c r="I43" s="18" t="n">
         <v>0.5098</v>
       </c>
-      <c r="J43" s="10" t="n">
+      <c r="J43" s="18" t="n">
         <v>0.0892</v>
       </c>
-      <c r="K43" s="11" t="n">
+      <c r="K43" s="19" t="n">
         <v>4.186</v>
       </c>
-      <c r="L43" s="9" t="n">
+      <c r="L43" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="M43" s="11" t="n">
+      <c r="M43" s="19" t="n">
         <v>0.45</v>
       </c>
-      <c r="N43" s="8" t="inlineStr"/>
-      <c r="O43" s="12" t="inlineStr"/>
-      <c r="P43" s="13" t="inlineStr"/>
+      <c r="N43" s="16" t="inlineStr"/>
+      <c r="O43" s="20" t="inlineStr"/>
+      <c r="P43" s="21" t="inlineStr"/>
     </row>
     <row r="44" ht="17" customHeight="1">
-      <c r="A44" s="14" t="n">
+      <c r="A44" s="22" t="n">
         <v>46119</v>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B44" s="23" t="inlineStr">
         <is>
           <t>Noah Cameron</t>
         </is>
       </c>
-      <c r="C44" s="16" t="inlineStr">
+      <c r="C44" s="24" t="inlineStr">
         <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="D44" s="16" t="inlineStr">
+      <c r="D44" s="24" t="inlineStr">
         <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E44" s="17" t="n">
+      <c r="E44" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F44" s="16" t="inlineStr">
+      <c r="F44" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G44" s="16" t="n">
+      <c r="G44" s="24" t="n">
         <v>-114</v>
       </c>
-      <c r="H44" s="18" t="n">
+      <c r="H44" s="26" t="n">
         <v>0.644</v>
       </c>
-      <c r="I44" s="18" t="n">
+      <c r="I44" s="26" t="n">
         <v>0.5327</v>
       </c>
-      <c r="J44" s="18" t="n">
+      <c r="J44" s="26" t="n">
         <v>0.1113</v>
       </c>
-      <c r="K44" s="19" t="n">
+      <c r="K44" s="27" t="n">
         <v>5.746</v>
       </c>
-      <c r="L44" s="17" t="n">
+      <c r="L44" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="M44" s="19" t="n">
+      <c r="M44" s="27" t="n">
         <v>0.6</v>
       </c>
-      <c r="N44" s="16" t="n">
+      <c r="N44" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="O44" s="20" t="inlineStr">
+      <c r="O44" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P44" s="21" t="n">
+      <c r="P44" s="29" t="n">
         <v>0.8772</v>
       </c>
     </row>
     <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="14" t="n">
+      <c r="A45" s="22" t="n">
         <v>46119</v>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B45" s="23" t="inlineStr">
         <is>
           <t>Kevin Gausman</t>
         </is>
       </c>
-      <c r="C45" s="16" t="inlineStr">
+      <c r="C45" s="24" t="inlineStr">
         <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="D45" s="16" t="inlineStr">
+      <c r="D45" s="24" t="inlineStr">
         <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E45" s="17" t="n">
+      <c r="E45" s="25" t="n">
         <v>5.5</v>
       </c>
-      <c r="F45" s="16" t="inlineStr">
+      <c r="F45" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G45" s="16" t="n">
+      <c r="G45" s="24" t="n">
         <v>154</v>
       </c>
-      <c r="H45" s="18" t="n">
+      <c r="H45" s="26" t="n">
         <v>0.501</v>
       </c>
-      <c r="I45" s="18" t="n">
+      <c r="I45" s="26" t="n">
         <v>0.3937</v>
       </c>
-      <c r="J45" s="18" t="n">
+      <c r="J45" s="26" t="n">
         <v>0.1073</v>
       </c>
-      <c r="K45" s="19" t="n">
+      <c r="K45" s="27" t="n">
         <v>5.736</v>
       </c>
-      <c r="L45" s="17" t="n">
+      <c r="L45" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="M45" s="19" t="n">
+      <c r="M45" s="27" t="n">
         <v>0.44</v>
       </c>
-      <c r="N45" s="16" t="n">
+      <c r="N45" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="O45" s="20" t="inlineStr">
+      <c r="O45" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P45" s="21" t="n">
+      <c r="P45" s="29" t="n">
         <v>1.54</v>
       </c>
     </row>
     <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="22" t="n">
+      <c r="A46" s="6" t="n">
         <v>46119</v>
       </c>
-      <c r="B46" s="23" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Nick Pivetta</t>
         </is>
       </c>
-      <c r="C46" s="24" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="D46" s="24" t="inlineStr">
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="E46" s="25" t="n">
+      <c r="E46" s="9" t="n">
         <v>6.5</v>
       </c>
-      <c r="F46" s="24" t="inlineStr">
+      <c r="F46" s="8" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G46" s="24" t="n">
+      <c r="G46" s="8" t="n">
         <v>-125</v>
       </c>
-      <c r="H46" s="26" t="n">
+      <c r="H46" s="10" t="n">
         <v>0.647</v>
       </c>
-      <c r="I46" s="26" t="n">
+      <c r="I46" s="10" t="n">
         <v>0.5556</v>
       </c>
-      <c r="J46" s="26" t="n">
+      <c r="J46" s="10" t="n">
         <v>0.0914</v>
       </c>
-      <c r="K46" s="27" t="n">
+      <c r="K46" s="11" t="n">
         <v>5.709</v>
       </c>
-      <c r="L46" s="25" t="n">
+      <c r="L46" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M46" s="27" t="n">
+      <c r="M46" s="11" t="n">
         <v>0.51</v>
       </c>
-      <c r="N46" s="24" t="n">
+      <c r="N46" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="O46" s="28" t="inlineStr">
+      <c r="O46" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P46" s="29" t="n">
+      <c r="P46" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="14" t="n">
+      <c r="A47" s="22" t="n">
         <v>46119</v>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B47" s="23" t="inlineStr">
         <is>
           <t>Paul Skenes</t>
         </is>
       </c>
-      <c r="C47" s="16" t="inlineStr">
+      <c r="C47" s="24" t="inlineStr">
         <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="D47" s="16" t="inlineStr">
+      <c r="D47" s="24" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E47" s="17" t="n">
+      <c r="E47" s="25" t="n">
         <v>6.5</v>
       </c>
-      <c r="F47" s="16" t="inlineStr">
+      <c r="F47" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G47" s="16" t="n">
+      <c r="G47" s="24" t="n">
         <v>-110</v>
       </c>
-      <c r="H47" s="18" t="n">
+      <c r="H47" s="26" t="n">
         <v>0.701</v>
       </c>
-      <c r="I47" s="18" t="n">
+      <c r="I47" s="26" t="n">
         <v>0.5238</v>
       </c>
-      <c r="J47" s="18" t="n">
+      <c r="J47" s="26" t="n">
         <v>0.1772</v>
       </c>
-      <c r="K47" s="19" t="n">
+      <c r="K47" s="27" t="n">
         <v>5.249</v>
       </c>
-      <c r="L47" s="17" t="n">
+      <c r="L47" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M47" s="19" t="n">
+      <c r="M47" s="27" t="n">
         <v>0.93</v>
       </c>
-      <c r="N47" s="16" t="n">
+      <c r="N47" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="O47" s="20" t="inlineStr">
+      <c r="O47" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P47" s="21" t="n">
+      <c r="P47" s="29" t="n">
         <v>0.9091</v>
       </c>
     </row>
     <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="22" t="n">
+      <c r="A48" s="6" t="n">
         <v>46119</v>
       </c>
-      <c r="B48" s="23" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>Jacob Misiorowski</t>
         </is>
       </c>
-      <c r="C48" s="24" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="D48" s="24" t="inlineStr">
+      <c r="D48" s="8" t="inlineStr">
         <is>
           <t>BOS</t>
         </is>
       </c>
-      <c r="E48" s="25" t="n">
+      <c r="E48" s="9" t="n">
         <v>6.5</v>
       </c>
-      <c r="F48" s="24" t="inlineStr">
+      <c r="F48" s="8" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G48" s="24" t="n">
+      <c r="G48" s="8" t="n">
         <v>116</v>
       </c>
-      <c r="H48" s="26" t="n">
+      <c r="H48" s="10" t="n">
         <v>0.539</v>
       </c>
-      <c r="I48" s="26" t="n">
+      <c r="I48" s="10" t="n">
         <v>0.463</v>
       </c>
-      <c r="J48" s="26" t="n">
+      <c r="J48" s="10" t="n">
         <v>0.076</v>
       </c>
-      <c r="K48" s="27" t="n">
+      <c r="K48" s="11" t="n">
         <v>6.457</v>
       </c>
-      <c r="L48" s="25" t="n">
+      <c r="L48" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M48" s="27" t="n">
+      <c r="M48" s="11" t="n">
         <v>0.35</v>
       </c>
-      <c r="N48" s="24" t="n">
+      <c r="N48" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="O48" s="28" t="inlineStr">
+      <c r="O48" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P48" s="29" t="n">
+      <c r="P48" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="22" t="n">
+      <c r="A49" s="6" t="n">
         <v>46119</v>
       </c>
-      <c r="B49" s="23" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>Javier Assad</t>
         </is>
       </c>
-      <c r="C49" s="24" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="D49" s="24" t="inlineStr">
+      <c r="D49" s="8" t="inlineStr">
         <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E49" s="25" t="n">
+      <c r="E49" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="F49" s="24" t="inlineStr">
+      <c r="F49" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G49" s="24" t="n">
+      <c r="G49" s="8" t="n">
         <v>-108</v>
       </c>
-      <c r="H49" s="26" t="n">
+      <c r="H49" s="10" t="n">
         <v>0.582</v>
       </c>
-      <c r="I49" s="26" t="n">
+      <c r="I49" s="10" t="n">
         <v>0.5192</v>
       </c>
-      <c r="J49" s="26" t="n">
+      <c r="J49" s="10" t="n">
         <v>0.06279999999999999</v>
       </c>
-      <c r="K49" s="27" t="n">
+      <c r="K49" s="11" t="n">
         <v>4.073</v>
       </c>
-      <c r="L49" s="25" t="n">
+      <c r="L49" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="M49" s="27" t="n">
+      <c r="M49" s="11" t="n">
         <v>0.33</v>
       </c>
-      <c r="N49" s="24" t="n">
+      <c r="N49" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="O49" s="28" t="inlineStr">
+      <c r="O49" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P49" s="29" t="n">
+      <c r="P49" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="14" t="n">
+      <c r="A50" s="22" t="n">
         <v>46119</v>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B50" s="23" t="inlineStr">
         <is>
           <t>Garrett Crochet</t>
         </is>
       </c>
-      <c r="C50" s="16" t="inlineStr">
+      <c r="C50" s="24" t="inlineStr">
         <is>
           <t>BOS</t>
         </is>
       </c>
-      <c r="D50" s="16" t="inlineStr">
+      <c r="D50" s="24" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E50" s="17" t="n">
+      <c r="E50" s="25" t="n">
         <v>7.5</v>
       </c>
-      <c r="F50" s="16" t="inlineStr">
+      <c r="F50" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G50" s="16" t="n">
+      <c r="G50" s="24" t="n">
         <v>-118</v>
       </c>
-      <c r="H50" s="18" t="n">
+      <c r="H50" s="26" t="n">
         <v>0.594</v>
       </c>
-      <c r="I50" s="18" t="n">
+      <c r="I50" s="26" t="n">
         <v>0.5413</v>
       </c>
-      <c r="J50" s="18" t="n">
+      <c r="J50" s="26" t="n">
         <v>0.0527</v>
       </c>
-      <c r="K50" s="19" t="n">
+      <c r="K50" s="27" t="n">
         <v>7.154</v>
       </c>
-      <c r="L50" s="17" t="n">
+      <c r="L50" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M50" s="19" t="n">
+      <c r="M50" s="27" t="n">
         <v>0.29</v>
       </c>
-      <c r="N50" s="16" t="n">
+      <c r="N50" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="O50" s="20" t="inlineStr">
+      <c r="O50" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P50" s="21" t="n">
+      <c r="P50" s="29" t="n">
         <v>0.8475</v>
       </c>
     </row>
     <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="14" t="n">
+      <c r="A51" s="22" t="n">
         <v>46119</v>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B51" s="23" t="inlineStr">
         <is>
           <t>Cade Cavalli</t>
         </is>
       </c>
-      <c r="C51" s="16" t="inlineStr">
+      <c r="C51" s="24" t="inlineStr">
         <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="D51" s="16" t="inlineStr">
+      <c r="D51" s="24" t="inlineStr">
         <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="E51" s="17" t="n">
+      <c r="E51" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F51" s="16" t="inlineStr">
+      <c r="F51" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G51" s="16" t="n">
+      <c r="G51" s="24" t="n">
         <v>-112</v>
       </c>
-      <c r="H51" s="18" t="n">
+      <c r="H51" s="26" t="n">
         <v>0.602</v>
       </c>
-      <c r="I51" s="18" t="n">
+      <c r="I51" s="26" t="n">
         <v>0.5283</v>
       </c>
-      <c r="J51" s="18" t="n">
+      <c r="J51" s="26" t="n">
         <v>0.0737</v>
       </c>
-      <c r="K51" s="19" t="n">
+      <c r="K51" s="27" t="n">
         <v>4.074</v>
       </c>
-      <c r="L51" s="17" t="n">
+      <c r="L51" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M51" s="19" t="n">
+      <c r="M51" s="27" t="n">
         <v>0.39</v>
       </c>
-      <c r="N51" s="16" t="n">
+      <c r="N51" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="O51" s="20" t="inlineStr">
+      <c r="O51" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P51" s="21" t="n">
+      <c r="P51" s="29" t="n">
         <v>0.8929</v>
       </c>
     </row>
     <row r="52" ht="17" customHeight="1">
-      <c r="A52" s="22" t="n">
+      <c r="A52" s="6" t="n">
         <v>46118</v>
       </c>
-      <c r="B52" s="23" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>Andre Pallante</t>
         </is>
       </c>
-      <c r="C52" s="24" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="D52" s="24" t="inlineStr">
+      <c r="D52" s="8" t="inlineStr">
         <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E52" s="25" t="n">
+      <c r="E52" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="F52" s="24" t="inlineStr">
+      <c r="F52" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G52" s="24" t="n">
+      <c r="G52" s="8" t="n">
         <v>-112</v>
       </c>
-      <c r="H52" s="26" t="n">
+      <c r="H52" s="10" t="n">
         <v>0.614</v>
       </c>
-      <c r="I52" s="26" t="n">
+      <c r="I52" s="10" t="n">
         <v>0.5283</v>
       </c>
-      <c r="J52" s="26" t="n">
+      <c r="J52" s="10" t="n">
         <v>0.0857</v>
       </c>
-      <c r="K52" s="27" t="n">
+      <c r="K52" s="11" t="n">
         <v>4.355</v>
       </c>
-      <c r="L52" s="25" t="n">
+      <c r="L52" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M52" s="27" t="n">
+      <c r="M52" s="11" t="n">
         <v>0.45</v>
       </c>
-      <c r="N52" s="24" t="n">
+      <c r="N52" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="O52" s="28" t="inlineStr">
+      <c r="O52" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P52" s="29" t="n">
+      <c r="P52" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="53" ht="17" customHeight="1">
-      <c r="A53" s="22" t="n">
+      <c r="A53" s="6" t="n">
         <v>46118</v>
       </c>
-      <c r="B53" s="23" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>Casey Mize</t>
         </is>
       </c>
-      <c r="C53" s="24" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="D53" s="24" t="inlineStr">
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="E53" s="25" t="n">
+      <c r="E53" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F53" s="24" t="inlineStr">
+      <c r="F53" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G53" s="24" t="n">
+      <c r="G53" s="8" t="n">
         <v>-162</v>
       </c>
-      <c r="H53" s="26" t="n">
+      <c r="H53" s="10" t="n">
         <v>0.708</v>
       </c>
-      <c r="I53" s="26" t="n">
+      <c r="I53" s="10" t="n">
         <v>0.6183</v>
       </c>
-      <c r="J53" s="26" t="n">
+      <c r="J53" s="10" t="n">
         <v>0.0897</v>
       </c>
-      <c r="K53" s="27" t="n">
+      <c r="K53" s="11" t="n">
         <v>6.298</v>
       </c>
-      <c r="L53" s="25" t="n">
+      <c r="L53" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M53" s="27" t="n">
+      <c r="M53" s="11" t="n">
         <v>0.59</v>
       </c>
-      <c r="N53" s="24" t="n">
+      <c r="N53" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="O53" s="28" t="inlineStr">
+      <c r="O53" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P53" s="29" t="n">
+      <c r="P53" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="54" ht="17" customHeight="1">
-      <c r="A54" s="22" t="n">
+      <c r="A54" s="6" t="n">
         <v>46118</v>
       </c>
-      <c r="B54" s="23" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>Joe Ryan</t>
         </is>
       </c>
-      <c r="C54" s="24" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="D54" s="24" t="inlineStr">
+      <c r="D54" s="8" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="E54" s="25" t="n">
+      <c r="E54" s="9" t="n">
         <v>6.5</v>
       </c>
-      <c r="F54" s="24" t="inlineStr">
+      <c r="F54" s="8" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G54" s="24" t="n">
+      <c r="G54" s="8" t="n">
         <v>-132</v>
       </c>
-      <c r="H54" s="26" t="n">
+      <c r="H54" s="10" t="n">
         <v>0.72</v>
       </c>
-      <c r="I54" s="26" t="n">
+      <c r="I54" s="10" t="n">
         <v>0.569</v>
       </c>
-      <c r="J54" s="26" t="n">
+      <c r="J54" s="10" t="n">
         <v>0.151</v>
       </c>
-      <c r="K54" s="27" t="n">
+      <c r="K54" s="11" t="n">
         <v>5.221</v>
       </c>
-      <c r="L54" s="25" t="n">
+      <c r="L54" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="M54" s="27" t="n">
+      <c r="M54" s="11" t="n">
         <v>0.88</v>
       </c>
-      <c r="N54" s="24" t="n">
+      <c r="N54" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="O54" s="28" t="inlineStr">
+      <c r="O54" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P54" s="29" t="n">
+      <c r="P54" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="14" t="n">
+      <c r="A55" s="22" t="n">
         <v>46117</v>
       </c>
-      <c r="B55" s="15" t="inlineStr">
+      <c r="B55" s="23" t="inlineStr">
         <is>
           <t>Luis Castillo</t>
         </is>
       </c>
-      <c r="C55" s="16" t="inlineStr">
+      <c r="C55" s="24" t="inlineStr">
         <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="D55" s="16" t="inlineStr">
+      <c r="D55" s="24" t="inlineStr">
         <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="E55" s="17" t="n">
+      <c r="E55" s="25" t="n">
         <v>5.5</v>
       </c>
-      <c r="F55" s="16" t="inlineStr">
+      <c r="F55" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G55" s="16" t="n">
+      <c r="G55" s="24" t="n">
         <v>128</v>
       </c>
-      <c r="H55" s="18" t="n">
+      <c r="H55" s="26" t="n">
         <v>0.518</v>
       </c>
-      <c r="I55" s="18" t="n">
+      <c r="I55" s="26" t="n">
         <v>0.4386</v>
       </c>
-      <c r="J55" s="18" t="n">
+      <c r="J55" s="26" t="n">
         <v>0.0794</v>
       </c>
-      <c r="K55" s="19" t="n">
+      <c r="K55" s="27" t="n">
         <v>5.702</v>
       </c>
-      <c r="L55" s="17" t="n">
+      <c r="L55" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="M55" s="19" t="n">
+      <c r="M55" s="27" t="n">
         <v>0.35</v>
       </c>
-      <c r="N55" s="16" t="n">
+      <c r="N55" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="O55" s="20" t="inlineStr">
+      <c r="O55" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P55" s="21" t="n">
+      <c r="P55" s="29" t="n">
         <v>1.28</v>
       </c>
     </row>
     <row r="56" ht="17" customHeight="1">
-      <c r="A56" s="22" t="n">
+      <c r="A56" s="6" t="n">
         <v>46117</v>
       </c>
-      <c r="B56" s="23" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>Nick Martinez</t>
         </is>
       </c>
-      <c r="C56" s="24" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="D56" s="24" t="inlineStr">
+      <c r="D56" s="8" t="inlineStr">
         <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="E56" s="25" t="n">
+      <c r="E56" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F56" s="24" t="inlineStr">
+      <c r="F56" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G56" s="24" t="n">
+      <c r="G56" s="8" t="n">
         <v>120</v>
       </c>
-      <c r="H56" s="26" t="n">
+      <c r="H56" s="10" t="n">
         <v>0.575</v>
       </c>
-      <c r="I56" s="26" t="n">
+      <c r="I56" s="10" t="n">
         <v>0.4545</v>
       </c>
-      <c r="J56" s="26" t="n">
+      <c r="J56" s="10" t="n">
         <v>0.1205</v>
       </c>
-      <c r="K56" s="27" t="n">
+      <c r="K56" s="11" t="n">
         <v>5.165</v>
       </c>
-      <c r="L56" s="25" t="n">
+      <c r="L56" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="M56" s="27" t="n">
+      <c r="M56" s="11" t="n">
         <v>0.55</v>
       </c>
-      <c r="N56" s="24" t="n">
+      <c r="N56" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="O56" s="28" t="inlineStr">
+      <c r="O56" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P56" s="29" t="n">
+      <c r="P56" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="57" ht="17" customHeight="1">
-      <c r="A57" s="22" t="n">
+      <c r="A57" s="6" t="n">
         <v>46117</v>
       </c>
-      <c r="B57" s="23" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>Eric Lauer</t>
         </is>
       </c>
-      <c r="C57" s="24" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="D57" s="24" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E57" s="25" t="n">
+      <c r="E57" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F57" s="24" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G57" s="24" t="n">
+      <c r="G57" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="H57" s="26" t="n">
+      <c r="H57" s="10" t="n">
         <v>0.588</v>
       </c>
-      <c r="I57" s="26" t="n">
+      <c r="I57" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="J57" s="26" t="n">
+      <c r="J57" s="10" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="K57" s="27" t="n">
+      <c r="K57" s="11" t="n">
         <v>5.457</v>
       </c>
-      <c r="L57" s="25" t="n">
+      <c r="L57" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M57" s="27" t="n">
+      <c r="M57" s="11" t="n">
         <v>0.44</v>
       </c>
-      <c r="N57" s="24" t="n">
+      <c r="N57" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="O57" s="28" t="inlineStr">
+      <c r="O57" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P57" s="29" t="n">
+      <c r="P57" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="58" ht="17" customHeight="1">
-      <c r="A58" s="14" t="n">
+      <c r="A58" s="22" t="n">
         <v>46117</v>
       </c>
-      <c r="B58" s="15" t="inlineStr">
+      <c r="B58" s="23" t="inlineStr">
         <is>
           <t>Taijuan Walker</t>
         </is>
       </c>
-      <c r="C58" s="16" t="inlineStr">
+      <c r="C58" s="24" t="inlineStr">
         <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="D58" s="16" t="inlineStr">
+      <c r="D58" s="24" t="inlineStr">
         <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="E58" s="17" t="n">
+      <c r="E58" s="25" t="n">
         <v>3.5</v>
       </c>
-      <c r="F58" s="16" t="inlineStr">
+      <c r="F58" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G58" s="16" t="n">
+      <c r="G58" s="24" t="n">
         <v>-106</v>
       </c>
-      <c r="H58" s="18" t="n">
+      <c r="H58" s="26" t="n">
         <v>0.6</v>
       </c>
-      <c r="I58" s="18" t="n">
+      <c r="I58" s="26" t="n">
         <v>0.5145999999999999</v>
       </c>
-      <c r="J58" s="18" t="n">
+      <c r="J58" s="26" t="n">
         <v>0.0854</v>
       </c>
-      <c r="K58" s="19" t="n">
+      <c r="K58" s="27" t="n">
         <v>4.331</v>
       </c>
-      <c r="L58" s="17" t="n">
+      <c r="L58" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="M58" s="19" t="n">
+      <c r="M58" s="27" t="n">
         <v>0.44</v>
       </c>
-      <c r="N58" s="16" t="n">
+      <c r="N58" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="O58" s="20" t="inlineStr">
+      <c r="O58" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P58" s="21" t="n">
+      <c r="P58" s="29" t="n">
         <v>0.9434</v>
       </c>
     </row>
     <row r="59" ht="17" customHeight="1">
-      <c r="A59" s="22" t="n">
+      <c r="A59" s="6" t="n">
         <v>46117</v>
       </c>
-      <c r="B59" s="23" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>Simeon Woods Richardson</t>
         </is>
       </c>
-      <c r="C59" s="24" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="D59" s="24" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E59" s="25" t="n">
+      <c r="E59" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F59" s="24" t="inlineStr">
+      <c r="F59" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G59" s="24" t="n">
+      <c r="G59" s="8" t="n">
         <v>106</v>
       </c>
-      <c r="H59" s="26" t="n">
+      <c r="H59" s="10" t="n">
         <v>0.547</v>
       </c>
-      <c r="I59" s="26" t="n">
+      <c r="I59" s="10" t="n">
         <v>0.4854</v>
       </c>
-      <c r="J59" s="26" t="n">
+      <c r="J59" s="10" t="n">
         <v>0.0616</v>
       </c>
-      <c r="K59" s="27" t="n">
+      <c r="K59" s="11" t="n">
         <v>5.027</v>
       </c>
-      <c r="L59" s="25" t="n">
+      <c r="L59" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="M59" s="27" t="n">
+      <c r="M59" s="11" t="n">
         <v>0.3</v>
       </c>
-      <c r="N59" s="24" t="n">
+      <c r="N59" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="O59" s="28" t="inlineStr">
+      <c r="O59" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P59" s="29" t="n">
+      <c r="P59" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="22" t="n">
+      <c r="A60" s="6" t="n">
         <v>46117</v>
       </c>
-      <c r="B60" s="23" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>Jack Leiter</t>
         </is>
       </c>
-      <c r="C60" s="24" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>TEX</t>
         </is>
       </c>
-      <c r="D60" s="24" t="inlineStr">
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="E60" s="25" t="n">
+      <c r="E60" s="9" t="n">
         <v>6.5</v>
       </c>
-      <c r="F60" s="24" t="inlineStr">
+      <c r="F60" s="8" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G60" s="24" t="n">
+      <c r="G60" s="8" t="n">
         <v>-146</v>
       </c>
-      <c r="H60" s="26" t="n">
+      <c r="H60" s="10" t="n">
         <v>0.659</v>
       </c>
-      <c r="I60" s="26" t="n">
+      <c r="I60" s="10" t="n">
         <v>0.5935</v>
       </c>
-      <c r="J60" s="26" t="n">
+      <c r="J60" s="10" t="n">
         <v>0.0655</v>
       </c>
-      <c r="K60" s="27" t="n">
+      <c r="K60" s="11" t="n">
         <v>5.601</v>
       </c>
-      <c r="L60" s="25" t="n">
+      <c r="L60" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="M60" s="27" t="n">
+      <c r="M60" s="11" t="n">
         <v>0.4</v>
       </c>
-      <c r="N60" s="24" t="n">
+      <c r="N60" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="O60" s="28" t="inlineStr">
+      <c r="O60" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P60" s="29" t="n">
+      <c r="P60" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="61" ht="17" customHeight="1">
-      <c r="A61" s="22" t="n">
+      <c r="A61" s="6" t="n">
         <v>46117</v>
       </c>
-      <c r="B61" s="23" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>Keider Montero</t>
         </is>
       </c>
-      <c r="C61" s="24" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="D61" s="24" t="inlineStr">
+      <c r="D61" s="8" t="inlineStr">
         <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="E61" s="25" t="n">
+      <c r="E61" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="F61" s="24" t="inlineStr">
+      <c r="F61" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G61" s="24" t="n">
+      <c r="G61" s="8" t="n">
         <v>108</v>
       </c>
-      <c r="H61" s="26" t="n">
+      <c r="H61" s="10" t="n">
         <v>0.546</v>
       </c>
-      <c r="I61" s="26" t="n">
+      <c r="I61" s="10" t="n">
         <v>0.4808</v>
       </c>
-      <c r="J61" s="26" t="n">
+      <c r="J61" s="10" t="n">
         <v>0.06519999999999999</v>
       </c>
-      <c r="K61" s="27" t="n">
+      <c r="K61" s="11" t="n">
         <v>3.968</v>
       </c>
-      <c r="L61" s="25" t="n">
+      <c r="L61" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="M61" s="27" t="n">
+      <c r="M61" s="11" t="n">
         <v>0.31</v>
       </c>
-      <c r="N61" s="24" t="n">
+      <c r="N61" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="O61" s="28" t="inlineStr">
+      <c r="O61" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P61" s="29" t="n">
+      <c r="P61" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="62" ht="17" customHeight="1">
-      <c r="A62" s="22" t="n">
+      <c r="A62" s="6" t="n">
         <v>46116</v>
       </c>
-      <c r="B62" s="23" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>Carmen Mlodzinski</t>
         </is>
       </c>
-      <c r="C62" s="24" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="D62" s="24" t="inlineStr">
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>BAL</t>
         </is>
       </c>
-      <c r="E62" s="25" t="n">
+      <c r="E62" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F62" s="24" t="inlineStr">
+      <c r="F62" s="8" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G62" s="24" t="n">
+      <c r="G62" s="8" t="n">
         <v>-108</v>
       </c>
-      <c r="H62" s="26" t="n">
+      <c r="H62" s="10" t="n">
         <v>0.666</v>
       </c>
-      <c r="I62" s="26" t="n">
+      <c r="I62" s="10" t="n">
         <v>0.5192</v>
       </c>
-      <c r="J62" s="26" t="n">
+      <c r="J62" s="10" t="n">
         <v>0.1468</v>
       </c>
-      <c r="K62" s="27" t="n">
+      <c r="K62" s="11" t="n">
         <v>3.828</v>
       </c>
-      <c r="L62" s="25" t="n">
+      <c r="L62" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="M62" s="27" t="n">
+      <c r="M62" s="11" t="n">
         <v>0.76</v>
       </c>
-      <c r="N62" s="24" t="n">
+      <c r="N62" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O62" s="28" t="inlineStr">
+      <c r="O62" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P62" s="29" t="n">
+      <c r="P62" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="63" ht="17" customHeight="1">
-      <c r="A63" s="22" t="n">
+      <c r="A63" s="6" t="n">
         <v>46116</v>
       </c>
-      <c r="B63" s="23" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>Chad Patrick</t>
         </is>
       </c>
-      <c r="C63" s="24" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="D63" s="24" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="E63" s="25" t="n">
+      <c r="E63" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="F63" s="24" t="inlineStr">
+      <c r="F63" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G63" s="24" t="n">
+      <c r="G63" s="8" t="n">
         <v>-154</v>
       </c>
-      <c r="H63" s="26" t="n">
+      <c r="H63" s="10" t="n">
         <v>0.678</v>
       </c>
-      <c r="I63" s="26" t="n">
+      <c r="I63" s="10" t="n">
         <v>0.6063</v>
       </c>
-      <c r="J63" s="26" t="n">
+      <c r="J63" s="10" t="n">
         <v>0.0717</v>
       </c>
-      <c r="K63" s="27" t="n">
+      <c r="K63" s="11" t="n">
         <v>4.705</v>
       </c>
-      <c r="L63" s="25" t="n">
+      <c r="L63" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="M63" s="27" t="n">
+      <c r="M63" s="11" t="n">
         <v>0.46</v>
       </c>
-      <c r="N63" s="24" t="n">
+      <c r="N63" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="O63" s="28" t="inlineStr">
+      <c r="O63" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P63" s="29" t="n">
+      <c r="P63" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="64" ht="17" customHeight="1">
-      <c r="A64" s="22" t="n">
+      <c r="A64" s="6" t="n">
         <v>46116</v>
       </c>
-      <c r="B64" s="23" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>Randy Vásquez</t>
         </is>
       </c>
-      <c r="C64" s="24" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="D64" s="24" t="inlineStr">
+      <c r="D64" s="8" t="inlineStr">
         <is>
           <t>BOS</t>
         </is>
       </c>
-      <c r="E64" s="25" t="n">
+      <c r="E64" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="F64" s="24" t="inlineStr">
+      <c r="F64" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G64" s="24" t="n">
+      <c r="G64" s="8" t="n">
         <v>-130</v>
       </c>
-      <c r="H64" s="26" t="n">
+      <c r="H64" s="10" t="n">
         <v>0.678</v>
       </c>
-      <c r="I64" s="26" t="n">
+      <c r="I64" s="10" t="n">
         <v>0.5652</v>
       </c>
-      <c r="J64" s="26" t="n">
+      <c r="J64" s="10" t="n">
         <v>0.1128</v>
       </c>
-      <c r="K64" s="27" t="n">
+      <c r="K64" s="11" t="n">
         <v>4.813</v>
       </c>
-      <c r="L64" s="25" t="n">
+      <c r="L64" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="M64" s="27" t="n">
+      <c r="M64" s="11" t="n">
         <v>0.65</v>
       </c>
-      <c r="N64" s="24" t="n">
+      <c r="N64" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="O64" s="28" t="inlineStr">
+      <c r="O64" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P64" s="29" t="n">
+      <c r="P64" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="65" ht="17" customHeight="1">
-      <c r="A65" s="14" t="n">
+      <c r="A65" s="22" t="n">
         <v>46116</v>
       </c>
-      <c r="B65" s="15" t="inlineStr">
+      <c r="B65" s="23" t="inlineStr">
         <is>
           <t>Bryce Elder</t>
         </is>
       </c>
-      <c r="C65" s="16" t="inlineStr">
+      <c r="C65" s="24" t="inlineStr">
         <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="D65" s="16" t="inlineStr">
+      <c r="D65" s="24" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="E65" s="17" t="n">
+      <c r="E65" s="25" t="n">
         <v>3.5</v>
       </c>
-      <c r="F65" s="16" t="inlineStr">
+      <c r="F65" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G65" s="16" t="n">
+      <c r="G65" s="24" t="n">
         <v>-132</v>
       </c>
-      <c r="H65" s="18" t="n">
+      <c r="H65" s="26" t="n">
         <v>0.753</v>
       </c>
-      <c r="I65" s="18" t="n">
+      <c r="I65" s="26" t="n">
         <v>0.569</v>
       </c>
-      <c r="J65" s="18" t="n">
+      <c r="J65" s="26" t="n">
         <v>0.184</v>
       </c>
-      <c r="K65" s="19" t="n">
+      <c r="K65" s="27" t="n">
         <v>5.551</v>
       </c>
-      <c r="L65" s="17" t="n">
+      <c r="L65" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M65" s="19" t="n">
+      <c r="M65" s="27" t="n">
         <v>1.07</v>
       </c>
-      <c r="N65" s="16" t="n">
+      <c r="N65" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="O65" s="20" t="inlineStr">
+      <c r="O65" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P65" s="21" t="n">
+      <c r="P65" s="29" t="n">
         <v>0.7576000000000001</v>
       </c>
     </row>
     <row r="66" ht="17" customHeight="1">
-      <c r="A66" s="14" t="n">
+      <c r="A66" s="22" t="n">
         <v>46116</v>
       </c>
-      <c r="B66" s="15" t="inlineStr">
+      <c r="B66" s="23" t="inlineStr">
         <is>
           <t>Steven Matz</t>
         </is>
       </c>
-      <c r="C66" s="16" t="inlineStr">
+      <c r="C66" s="24" t="inlineStr">
         <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="D66" s="16" t="inlineStr">
+      <c r="D66" s="24" t="inlineStr">
         <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="E66" s="17" t="n">
+      <c r="E66" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F66" s="16" t="inlineStr">
+      <c r="F66" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G66" s="16" t="n">
+      <c r="G66" s="24" t="n">
         <v>116</v>
       </c>
-      <c r="H66" s="18" t="n">
+      <c r="H66" s="26" t="n">
         <v>0.651</v>
       </c>
-      <c r="I66" s="18" t="n">
+      <c r="I66" s="26" t="n">
         <v>0.463</v>
       </c>
-      <c r="J66" s="18" t="n">
+      <c r="J66" s="26" t="n">
         <v>0.188</v>
       </c>
-      <c r="K66" s="19" t="n">
+      <c r="K66" s="27" t="n">
         <v>5.743</v>
       </c>
-      <c r="L66" s="17" t="n">
+      <c r="L66" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M66" s="19" t="n">
+      <c r="M66" s="27" t="n">
         <v>0.88</v>
       </c>
-      <c r="N66" s="16" t="n">
+      <c r="N66" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="O66" s="20" t="inlineStr">
+      <c r="O66" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P66" s="21" t="n">
+      <c r="P66" s="29" t="n">
         <v>1.16</v>
       </c>
     </row>
     <row r="67" ht="17" customHeight="1">
-      <c r="A67" s="22" t="n">
+      <c r="A67" s="6" t="n">
         <v>46116</v>
       </c>
-      <c r="B67" s="23" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>Jack Flaherty</t>
         </is>
       </c>
-      <c r="C67" s="24" t="inlineStr">
+      <c r="C67" s="8" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="D67" s="24" t="inlineStr">
+      <c r="D67" s="8" t="inlineStr">
         <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="E67" s="25" t="n">
+      <c r="E67" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="F67" s="24" t="inlineStr">
+      <c r="F67" s="8" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G67" s="24" t="n">
+      <c r="G67" s="8" t="n">
         <v>116</v>
       </c>
-      <c r="H67" s="26" t="n">
+      <c r="H67" s="10" t="n">
         <v>0.653</v>
       </c>
-      <c r="I67" s="26" t="n">
+      <c r="I67" s="10" t="n">
         <v>0.463</v>
       </c>
-      <c r="J67" s="26" t="n">
+      <c r="J67" s="10" t="n">
         <v>0.19</v>
       </c>
-      <c r="K67" s="27" t="n">
+      <c r="K67" s="11" t="n">
         <v>4.756</v>
       </c>
-      <c r="L67" s="25" t="n">
+      <c r="L67" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="M67" s="27" t="n">
+      <c r="M67" s="11" t="n">
         <v>0.88</v>
       </c>
-      <c r="N67" s="24" t="n">
+      <c r="N67" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="O67" s="28" t="inlineStr">
+      <c r="O67" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P67" s="29" t="n">
+      <c r="P67" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="68" ht="17" customHeight="1">
-      <c r="A68" s="14" t="n">
+      <c r="A68" s="22" t="n">
         <v>46116</v>
       </c>
-      <c r="B68" s="15" t="inlineStr">
+      <c r="B68" s="23" t="inlineStr">
         <is>
           <t>Ryan Weathers</t>
         </is>
       </c>
-      <c r="C68" s="16" t="inlineStr">
+      <c r="C68" s="24" t="inlineStr">
         <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="D68" s="16" t="inlineStr">
+      <c r="D68" s="24" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="E68" s="17" t="n">
+      <c r="E68" s="25" t="n">
         <v>5.5</v>
       </c>
-      <c r="F68" s="16" t="inlineStr">
+      <c r="F68" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G68" s="16" t="n">
+      <c r="G68" s="24" t="n">
         <v>-125</v>
       </c>
-      <c r="H68" s="18" t="n">
+      <c r="H68" s="26" t="n">
         <v>0.741</v>
       </c>
-      <c r="I68" s="18" t="n">
+      <c r="I68" s="26" t="n">
         <v>0.5556</v>
       </c>
-      <c r="J68" s="18" t="n">
+      <c r="J68" s="26" t="n">
         <v>0.1854</v>
       </c>
-      <c r="K68" s="19" t="n">
+      <c r="K68" s="27" t="n">
         <v>4.217</v>
       </c>
-      <c r="L68" s="17" t="n">
+      <c r="L68" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M68" s="19" t="n">
+      <c r="M68" s="27" t="n">
         <v>1.04</v>
       </c>
-      <c r="N68" s="16" t="n">
+      <c r="N68" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="O68" s="20" t="inlineStr">
+      <c r="O68" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P68" s="21" t="n">
+      <c r="P68" s="29" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="69" ht="17" customHeight="1">
-      <c r="A69" s="22" t="n">
+      <c r="A69" s="6" t="n">
         <v>46115</v>
       </c>
-      <c r="B69" s="23" t="inlineStr">
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>Emmet Sheehan</t>
         </is>
       </c>
-      <c r="C69" s="24" t="inlineStr">
+      <c r="C69" s="8" t="inlineStr">
         <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="D69" s="24" t="inlineStr">
+      <c r="D69" s="8" t="inlineStr">
         <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E69" s="25" t="n">
+      <c r="E69" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="F69" s="24" t="inlineStr">
+      <c r="F69" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G69" s="24" t="n">
+      <c r="G69" s="8" t="n">
         <v>-128</v>
       </c>
-      <c r="H69" s="26" t="n">
+      <c r="H69" s="10" t="n">
         <v>0.68</v>
       </c>
-      <c r="I69" s="26" t="n">
+      <c r="I69" s="10" t="n">
         <v>0.5614</v>
       </c>
-      <c r="J69" s="26" t="n">
+      <c r="J69" s="10" t="n">
         <v>0.1186</v>
       </c>
-      <c r="K69" s="27" t="n">
+      <c r="K69" s="11" t="n">
         <v>6.988</v>
       </c>
-      <c r="L69" s="25" t="n">
+      <c r="L69" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="M69" s="27" t="n">
+      <c r="M69" s="11" t="n">
         <v>0.68</v>
       </c>
-      <c r="N69" s="24" t="n">
+      <c r="N69" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="O69" s="28" t="inlineStr">
+      <c r="O69" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P69" s="29" t="n">
+      <c r="P69" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="70" ht="17" customHeight="1">
-      <c r="A70" s="14" t="n">
+      <c r="A70" s="22" t="n">
         <v>46115</v>
       </c>
-      <c r="B70" s="15" t="inlineStr">
+      <c r="B70" s="23" t="inlineStr">
         <is>
           <t>Mitch Keller</t>
         </is>
       </c>
-      <c r="C70" s="16" t="inlineStr">
+      <c r="C70" s="24" t="inlineStr">
         <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="D70" s="16" t="inlineStr">
+      <c r="D70" s="24" t="inlineStr">
         <is>
           <t>BAL</t>
         </is>
       </c>
-      <c r="E70" s="17" t="n">
+      <c r="E70" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F70" s="16" t="inlineStr">
+      <c r="F70" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G70" s="16" t="n">
+      <c r="G70" s="24" t="n">
         <v>122</v>
       </c>
-      <c r="H70" s="18" t="n">
+      <c r="H70" s="26" t="n">
         <v>0.505</v>
       </c>
-      <c r="I70" s="18" t="n">
+      <c r="I70" s="26" t="n">
         <v>0.4505</v>
       </c>
-      <c r="J70" s="18" t="n">
+      <c r="J70" s="26" t="n">
         <v>0.0545</v>
       </c>
-      <c r="K70" s="19" t="n">
+      <c r="K70" s="27" t="n">
         <v>4.723</v>
       </c>
-      <c r="L70" s="17" t="n">
+      <c r="L70" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M70" s="19" t="n">
+      <c r="M70" s="27" t="n">
         <v>0.25</v>
       </c>
-      <c r="N70" s="16" t="n">
+      <c r="N70" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="O70" s="20" t="inlineStr">
+      <c r="O70" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P70" s="21" t="n">
+      <c r="P70" s="29" t="n">
         <v>1.22</v>
       </c>
     </row>
     <row r="71" ht="17" customHeight="1">
-      <c r="A71" s="14" t="n">
+      <c r="A71" s="22" t="n">
         <v>46115</v>
       </c>
-      <c r="B71" s="15" t="inlineStr">
+      <c r="B71" s="23" t="inlineStr">
         <is>
           <t>Framber Valdez</t>
         </is>
       </c>
-      <c r="C71" s="16" t="inlineStr">
+      <c r="C71" s="24" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="D71" s="16" t="inlineStr">
+      <c r="D71" s="24" t="inlineStr">
         <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="E71" s="17" t="n">
+      <c r="E71" s="25" t="n">
         <v>5.5</v>
       </c>
-      <c r="F71" s="16" t="inlineStr">
+      <c r="F71" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G71" s="16" t="n">
+      <c r="G71" s="24" t="n">
         <v>-112</v>
       </c>
-      <c r="H71" s="18" t="n">
+      <c r="H71" s="26" t="n">
         <v>0.591</v>
       </c>
-      <c r="I71" s="18" t="n">
+      <c r="I71" s="26" t="n">
         <v>0.5283</v>
       </c>
-      <c r="J71" s="18" t="n">
+      <c r="J71" s="26" t="n">
         <v>0.06270000000000001</v>
       </c>
-      <c r="K71" s="19" t="n">
+      <c r="K71" s="27" t="n">
         <v>5.166</v>
       </c>
-      <c r="L71" s="17" t="n">
+      <c r="L71" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M71" s="19" t="n">
+      <c r="M71" s="27" t="n">
         <v>0.33</v>
       </c>
-      <c r="N71" s="16" t="n">
+      <c r="N71" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="O71" s="20" t="inlineStr">
+      <c r="O71" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P71" s="21" t="n">
+      <c r="P71" s="29" t="n">
         <v>0.8929</v>
       </c>
     </row>
     <row r="72" ht="17" customHeight="1">
-      <c r="A72" s="14" t="n">
+      <c r="A72" s="22" t="n">
         <v>46115</v>
       </c>
-      <c r="B72" s="15" t="inlineStr">
+      <c r="B72" s="23" t="inlineStr">
         <is>
           <t>Kyle Bradish</t>
         </is>
       </c>
-      <c r="C72" s="16" t="inlineStr">
+      <c r="C72" s="24" t="inlineStr">
         <is>
           <t>BAL</t>
         </is>
       </c>
-      <c r="D72" s="16" t="inlineStr">
+      <c r="D72" s="24" t="inlineStr">
         <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="E72" s="17" t="n">
+      <c r="E72" s="25" t="n">
         <v>5.5</v>
       </c>
-      <c r="F72" s="16" t="inlineStr">
+      <c r="F72" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G72" s="16" t="n">
+      <c r="G72" s="24" t="n">
         <v>-146</v>
       </c>
-      <c r="H72" s="18" t="n">
+      <c r="H72" s="26" t="n">
         <v>0.659</v>
       </c>
-      <c r="I72" s="18" t="n">
+      <c r="I72" s="26" t="n">
         <v>0.5935</v>
       </c>
-      <c r="J72" s="18" t="n">
+      <c r="J72" s="26" t="n">
         <v>0.0655</v>
       </c>
-      <c r="K72" s="19" t="n">
+      <c r="K72" s="27" t="n">
         <v>6.943</v>
       </c>
-      <c r="L72" s="17" t="n">
+      <c r="L72" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M72" s="19" t="n">
+      <c r="M72" s="27" t="n">
         <v>0.4</v>
       </c>
-      <c r="N72" s="16" t="n">
+      <c r="N72" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="O72" s="20" t="inlineStr">
+      <c r="O72" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P72" s="21" t="n">
+      <c r="P72" s="29" t="n">
         <v>0.6849</v>
       </c>
     </row>
     <row r="73" ht="17" customHeight="1">
-      <c r="A73" s="14" t="n">
+      <c r="A73" s="22" t="n">
         <v>46115</v>
       </c>
-      <c r="B73" s="15" t="inlineStr">
+      <c r="B73" s="23" t="inlineStr">
         <is>
           <t>Michael King</t>
         </is>
       </c>
-      <c r="C73" s="16" t="inlineStr">
+      <c r="C73" s="24" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="D73" s="16" t="inlineStr">
+      <c r="D73" s="24" t="inlineStr">
         <is>
           <t>BOS</t>
         </is>
       </c>
-      <c r="E73" s="17" t="n">
+      <c r="E73" s="25" t="n">
         <v>5.5</v>
       </c>
-      <c r="F73" s="16" t="inlineStr">
+      <c r="F73" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G73" s="16" t="n">
+      <c r="G73" s="24" t="n">
         <v>102</v>
       </c>
-      <c r="H73" s="18" t="n">
+      <c r="H73" s="26" t="n">
         <v>0.584</v>
       </c>
-      <c r="I73" s="18" t="n">
+      <c r="I73" s="26" t="n">
         <v>0.495</v>
       </c>
-      <c r="J73" s="18" t="n">
+      <c r="J73" s="26" t="n">
         <v>0.089</v>
       </c>
-      <c r="K73" s="19" t="n">
+      <c r="K73" s="27" t="n">
         <v>5.081</v>
       </c>
-      <c r="L73" s="17" t="n">
+      <c r="L73" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="M73" s="19" t="n">
+      <c r="M73" s="27" t="n">
         <v>0.44</v>
       </c>
-      <c r="N73" s="16" t="n">
+      <c r="N73" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="O73" s="20" t="inlineStr">
+      <c r="O73" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P73" s="21" t="n">
+      <c r="P73" s="29" t="n">
         <v>1.02</v>
       </c>
     </row>
     <row r="74" ht="17" customHeight="1">
-      <c r="A74" s="6" t="n">
+      <c r="A74" s="14" t="n">
         <v>46115</v>
       </c>
-      <c r="B74" s="7" t="inlineStr">
+      <c r="B74" s="15" t="inlineStr">
         <is>
           <t>Chad Patrick</t>
         </is>
       </c>
-      <c r="C74" s="8" t="inlineStr">
+      <c r="C74" s="16" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="D74" s="8" t="inlineStr">
+      <c r="D74" s="16" t="inlineStr">
         <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="E74" s="9" t="n">
+      <c r="E74" s="17" t="n">
         <v>3.5</v>
       </c>
-      <c r="F74" s="8" t="inlineStr">
+      <c r="F74" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G74" s="8" t="n">
+      <c r="G74" s="16" t="n">
         <v>-138</v>
       </c>
-      <c r="H74" s="10" t="n">
+      <c r="H74" s="18" t="n">
         <v>0.672</v>
       </c>
-      <c r="I74" s="10" t="n">
+      <c r="I74" s="18" t="n">
         <v>0.5798</v>
       </c>
-      <c r="J74" s="10" t="n">
+      <c r="J74" s="18" t="n">
         <v>0.0922</v>
       </c>
-      <c r="K74" s="11" t="n">
+      <c r="K74" s="19" t="n">
         <v>4.705</v>
       </c>
-      <c r="L74" s="9" t="n">
+      <c r="L74" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="M74" s="11" t="n">
+      <c r="M74" s="19" t="n">
         <v>0.55</v>
       </c>
-      <c r="N74" s="8" t="inlineStr"/>
-      <c r="O74" s="12" t="inlineStr"/>
-      <c r="P74" s="13" t="inlineStr"/>
+      <c r="N74" s="16" t="inlineStr"/>
+      <c r="O74" s="20" t="inlineStr"/>
+      <c r="P74" s="21" t="inlineStr"/>
     </row>
     <row r="75" ht="17" customHeight="1">
-      <c r="A75" s="22" t="n">
+      <c r="A75" s="6" t="n">
         <v>46115</v>
       </c>
-      <c r="B75" s="23" t="inlineStr">
+      <c r="B75" s="7" t="inlineStr">
         <is>
           <t>Cade Horton</t>
         </is>
       </c>
-      <c r="C75" s="24" t="inlineStr">
+      <c r="C75" s="8" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="D75" s="24" t="inlineStr">
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E75" s="25" t="n">
+      <c r="E75" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="F75" s="24" t="inlineStr">
+      <c r="F75" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G75" s="24" t="n">
+      <c r="G75" s="8" t="n">
         <v>-136</v>
       </c>
-      <c r="H75" s="26" t="n">
+      <c r="H75" s="10" t="n">
         <v>0.676</v>
       </c>
-      <c r="I75" s="26" t="n">
+      <c r="I75" s="10" t="n">
         <v>0.5763</v>
       </c>
-      <c r="J75" s="26" t="n">
+      <c r="J75" s="10" t="n">
         <v>0.0997</v>
       </c>
-      <c r="K75" s="27" t="n">
+      <c r="K75" s="11" t="n">
         <v>4.806</v>
       </c>
-      <c r="L75" s="25" t="n">
+      <c r="L75" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M75" s="27" t="n">
+      <c r="M75" s="11" t="n">
         <v>0.59</v>
       </c>
-      <c r="N75" s="24" t="n">
+      <c r="N75" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="O75" s="28" t="inlineStr">
+      <c r="O75" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P75" s="29" t="n">
+      <c r="P75" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="76" ht="17" customHeight="1">
-      <c r="A76" s="22" t="n">
+      <c r="A76" s="6" t="n">
         <v>46114</v>
       </c>
-      <c r="B76" s="23" t="inlineStr">
+      <c r="B76" s="7" t="inlineStr">
         <is>
           <t>Taj Bradley</t>
         </is>
       </c>
-      <c r="C76" s="24" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
         <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="D76" s="24" t="inlineStr">
+      <c r="D76" s="8" t="inlineStr">
         <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="E76" s="25" t="n">
+      <c r="E76" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F76" s="24" t="inlineStr">
+      <c r="F76" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G76" s="24" t="n">
+      <c r="G76" s="8" t="n">
         <v>118</v>
       </c>
-      <c r="H76" s="26" t="n">
+      <c r="H76" s="10" t="n">
         <v>0.573</v>
       </c>
-      <c r="I76" s="26" t="n">
+      <c r="I76" s="10" t="n">
         <v>0.4587</v>
       </c>
-      <c r="J76" s="26" t="n">
+      <c r="J76" s="10" t="n">
         <v>0.1143</v>
       </c>
-      <c r="K76" s="27" t="n">
+      <c r="K76" s="11" t="n">
         <v>5.159</v>
       </c>
-      <c r="L76" s="25" t="n">
+      <c r="L76" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="M76" s="27" t="n">
+      <c r="M76" s="11" t="n">
         <v>0.53</v>
       </c>
-      <c r="N76" s="24" t="n">
+      <c r="N76" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="O76" s="28" t="inlineStr">
+      <c r="O76" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P76" s="29" t="n">
+      <c r="P76" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="77" ht="17" customHeight="1">
-      <c r="A77" s="22" t="n">
+      <c r="A77" s="6" t="n">
         <v>46114</v>
       </c>
-      <c r="B77" s="23" t="inlineStr">
+      <c r="B77" s="7" t="inlineStr">
         <is>
           <t>Cole Ragans</t>
         </is>
       </c>
-      <c r="C77" s="24" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="D77" s="24" t="inlineStr">
+      <c r="D77" s="8" t="inlineStr">
         <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="E77" s="25" t="n">
+      <c r="E77" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="F77" s="24" t="inlineStr">
+      <c r="F77" s="8" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G77" s="24" t="n">
+      <c r="G77" s="8" t="n">
         <v>-152</v>
       </c>
-      <c r="H77" s="26" t="n">
+      <c r="H77" s="10" t="n">
         <v>0.738</v>
       </c>
-      <c r="I77" s="26" t="n">
+      <c r="I77" s="10" t="n">
         <v>0.6032</v>
       </c>
-      <c r="J77" s="26" t="n">
+      <c r="J77" s="10" t="n">
         <v>0.1348</v>
       </c>
-      <c r="K77" s="27" t="n">
+      <c r="K77" s="11" t="n">
         <v>5.951</v>
       </c>
-      <c r="L77" s="25" t="n">
+      <c r="L77" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="M77" s="27" t="n">
+      <c r="M77" s="11" t="n">
         <v>0.85</v>
       </c>
-      <c r="N77" s="24" t="n">
+      <c r="N77" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="O77" s="28" t="inlineStr">
+      <c r="O77" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P77" s="29" t="n">
+      <c r="P77" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="78" ht="17" customHeight="1">
-      <c r="A78" s="14" t="n">
+      <c r="A78" s="22" t="n">
         <v>46113</v>
       </c>
-      <c r="B78" s="15" t="inlineStr">
+      <c r="B78" s="23" t="inlineStr">
         <is>
           <t>Tarik Skubal</t>
         </is>
       </c>
-      <c r="C78" s="16" t="inlineStr">
+      <c r="C78" s="24" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="D78" s="16" t="inlineStr">
+      <c r="D78" s="24" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="E78" s="17" t="n">
+      <c r="E78" s="25" t="n">
         <v>6.5</v>
       </c>
-      <c r="F78" s="16" t="inlineStr">
+      <c r="F78" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G78" s="16" t="n">
+      <c r="G78" s="24" t="n">
         <v>108</v>
       </c>
-      <c r="H78" s="18" t="n">
+      <c r="H78" s="26" t="n">
         <v>0.644</v>
       </c>
-      <c r="I78" s="18" t="n">
+      <c r="I78" s="26" t="n">
         <v>0.4808</v>
       </c>
-      <c r="J78" s="18" t="n">
+      <c r="J78" s="26" t="n">
         <v>0.1632</v>
       </c>
-      <c r="K78" s="19" t="n">
+      <c r="K78" s="27" t="n">
         <v>5.865</v>
       </c>
-      <c r="L78" s="17" t="n">
+      <c r="L78" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M78" s="19" t="n">
+      <c r="M78" s="27" t="n">
         <v>0.79</v>
       </c>
-      <c r="N78" s="16" t="n">
+      <c r="N78" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="O78" s="20" t="inlineStr">
+      <c r="O78" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P78" s="21" t="n">
+      <c r="P78" s="29" t="n">
         <v>1.08</v>
       </c>
     </row>
     <row r="79" ht="17" customHeight="1">
-      <c r="A79" s="14" t="n">
+      <c r="A79" s="22" t="n">
         <v>46113</v>
       </c>
-      <c r="B79" s="15" t="inlineStr">
+      <c r="B79" s="23" t="inlineStr">
         <is>
           <t>Paul Skenes</t>
         </is>
       </c>
-      <c r="C79" s="16" t="inlineStr">
+      <c r="C79" s="24" t="inlineStr">
         <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="D79" s="16" t="inlineStr">
+      <c r="D79" s="24" t="inlineStr">
         <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="E79" s="17" t="n">
+      <c r="E79" s="25" t="n">
         <v>7.5</v>
       </c>
-      <c r="F79" s="16" t="inlineStr">
+      <c r="F79" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G79" s="16" t="n">
+      <c r="G79" s="24" t="n">
         <v>-132</v>
       </c>
-      <c r="H79" s="18" t="n">
+      <c r="H79" s="26" t="n">
         <v>0.696</v>
       </c>
-      <c r="I79" s="18" t="n">
+      <c r="I79" s="26" t="n">
         <v>0.569</v>
       </c>
-      <c r="J79" s="18" t="n">
+      <c r="J79" s="26" t="n">
         <v>0.127</v>
       </c>
-      <c r="K79" s="19" t="n">
+      <c r="K79" s="27" t="n">
         <v>6.191</v>
       </c>
-      <c r="L79" s="17" t="n">
+      <c r="L79" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="M79" s="19" t="n">
+      <c r="M79" s="27" t="n">
         <v>0.74</v>
       </c>
-      <c r="N79" s="16" t="n">
+      <c r="N79" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="O79" s="20" t="inlineStr">
+      <c r="O79" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P79" s="21" t="n">
+      <c r="P79" s="29" t="n">
         <v>0.7576000000000001</v>
       </c>
     </row>
     <row r="80" ht="17" customHeight="1">
-      <c r="A80" s="14" t="n">
+      <c r="A80" s="22" t="n">
         <v>46113</v>
       </c>
-      <c r="B80" s="15" t="inlineStr">
+      <c r="B80" s="23" t="inlineStr">
         <is>
           <t>Cam Schlittler</t>
         </is>
       </c>
-      <c r="C80" s="16" t="inlineStr">
+      <c r="C80" s="24" t="inlineStr">
         <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="D80" s="16" t="inlineStr">
+      <c r="D80" s="24" t="inlineStr">
         <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E80" s="17" t="n">
+      <c r="E80" s="25" t="n">
         <v>5.5</v>
       </c>
-      <c r="F80" s="16" t="inlineStr">
+      <c r="F80" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G80" s="16" t="n">
+      <c r="G80" s="24" t="n">
         <v>-144</v>
       </c>
-      <c r="H80" s="18" t="n">
+      <c r="H80" s="26" t="n">
         <v>0.735</v>
       </c>
-      <c r="I80" s="18" t="n">
+      <c r="I80" s="26" t="n">
         <v>0.5901999999999999</v>
       </c>
-      <c r="J80" s="18" t="n">
+      <c r="J80" s="26" t="n">
         <v>0.1448</v>
       </c>
-      <c r="K80" s="19" t="n">
+      <c r="K80" s="27" t="n">
         <v>7.561</v>
       </c>
-      <c r="L80" s="17" t="n">
+      <c r="L80" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="M80" s="19" t="n">
+      <c r="M80" s="27" t="n">
         <v>0.88</v>
       </c>
-      <c r="N80" s="16" t="n">
+      <c r="N80" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="O80" s="20" t="inlineStr">
+      <c r="O80" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P80" s="21" t="n">
+      <c r="P80" s="29" t="n">
         <v>0.6944</v>
       </c>
     </row>
     <row r="81" ht="17" customHeight="1">
-      <c r="A81" s="14" t="n">
+      <c r="A81" s="22" t="n">
         <v>46113</v>
       </c>
-      <c r="B81" s="15" t="inlineStr">
+      <c r="B81" s="23" t="inlineStr">
         <is>
           <t>Andrew Abbott</t>
         </is>
       </c>
-      <c r="C81" s="16" t="inlineStr">
+      <c r="C81" s="24" t="inlineStr">
         <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="D81" s="16" t="inlineStr">
+      <c r="D81" s="24" t="inlineStr">
         <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="E81" s="17" t="n">
+      <c r="E81" s="25" t="n">
         <v>5.5</v>
       </c>
-      <c r="F81" s="16" t="inlineStr">
+      <c r="F81" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G81" s="16" t="n">
+      <c r="G81" s="24" t="n">
         <v>-112</v>
       </c>
-      <c r="H81" s="18" t="n">
+      <c r="H81" s="26" t="n">
         <v>0.677</v>
       </c>
-      <c r="I81" s="18" t="n">
+      <c r="I81" s="26" t="n">
         <v>0.5283</v>
       </c>
-      <c r="J81" s="18" t="n">
+      <c r="J81" s="26" t="n">
         <v>0.1487</v>
       </c>
-      <c r="K81" s="19" t="n">
+      <c r="K81" s="27" t="n">
         <v>4.469</v>
       </c>
-      <c r="L81" s="17" t="n">
+      <c r="L81" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="M81" s="19" t="n">
+      <c r="M81" s="27" t="n">
         <v>0.79</v>
       </c>
-      <c r="N81" s="16" t="n">
+      <c r="N81" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="O81" s="20" t="inlineStr">
+      <c r="O81" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P81" s="21" t="n">
+      <c r="P81" s="29" t="n">
         <v>0.8929</v>
       </c>
     </row>
     <row r="82" ht="17" customHeight="1">
-      <c r="A82" s="22" t="n">
+      <c r="A82" s="6" t="n">
         <v>46113</v>
       </c>
-      <c r="B82" s="23" t="inlineStr">
+      <c r="B82" s="7" t="inlineStr">
         <is>
           <t>Drew Rasmussen</t>
         </is>
       </c>
-      <c r="C82" s="24" t="inlineStr">
+      <c r="C82" s="8" t="inlineStr">
         <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="D82" s="24" t="inlineStr">
+      <c r="D82" s="8" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E82" s="25" t="n">
+      <c r="E82" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F82" s="24" t="inlineStr">
+      <c r="F82" s="8" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G82" s="24" t="n">
+      <c r="G82" s="8" t="n">
         <v>-118</v>
       </c>
-      <c r="H82" s="26" t="n">
+      <c r="H82" s="10" t="n">
         <v>0.732</v>
       </c>
-      <c r="I82" s="26" t="n">
+      <c r="I82" s="10" t="n">
         <v>0.5413</v>
       </c>
-      <c r="J82" s="26" t="n">
+      <c r="J82" s="10" t="n">
         <v>0.1907</v>
       </c>
-      <c r="K82" s="27" t="n">
+      <c r="K82" s="11" t="n">
         <v>3.414</v>
       </c>
-      <c r="L82" s="25" t="n">
+      <c r="L82" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="M82" s="27" t="n">
+      <c r="M82" s="11" t="n">
         <v>1.04</v>
       </c>
-      <c r="N82" s="24" t="n">
+      <c r="N82" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="O82" s="28" t="inlineStr">
+      <c r="O82" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P82" s="29" t="n">
+      <c r="P82" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="83" ht="17" customHeight="1">
-      <c r="A83" s="14" t="n">
+      <c r="A83" s="22" t="n">
         <v>46113</v>
       </c>
-      <c r="B83" s="15" t="inlineStr">
+      <c r="B83" s="23" t="inlineStr">
         <is>
           <t>Adrian Houser</t>
         </is>
       </c>
-      <c r="C83" s="16" t="inlineStr">
+      <c r="C83" s="24" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="D83" s="16" t="inlineStr">
+      <c r="D83" s="24" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E83" s="17" t="n">
+      <c r="E83" s="25" t="n">
         <v>3.5</v>
       </c>
-      <c r="F83" s="16" t="inlineStr">
+      <c r="F83" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G83" s="16" t="n">
+      <c r="G83" s="24" t="n">
         <v>-125</v>
       </c>
-      <c r="H83" s="18" t="n">
+      <c r="H83" s="26" t="n">
         <v>0.724</v>
       </c>
-      <c r="I83" s="18" t="n">
+      <c r="I83" s="26" t="n">
         <v>0.5556</v>
       </c>
-      <c r="J83" s="18" t="n">
+      <c r="J83" s="26" t="n">
         <v>0.1684</v>
       </c>
-      <c r="K83" s="19" t="n">
+      <c r="K83" s="27" t="n">
         <v>5.063</v>
       </c>
-      <c r="L83" s="17" t="n">
+      <c r="L83" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M83" s="19" t="n">
+      <c r="M83" s="27" t="n">
         <v>0.95</v>
       </c>
-      <c r="N83" s="16" t="n">
+      <c r="N83" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="O83" s="20" t="inlineStr">
+      <c r="O83" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P83" s="21" t="n">
+      <c r="P83" s="29" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="84" ht="17" customHeight="1">
-      <c r="A84" s="14" t="n">
+      <c r="A84" s="22" t="n">
         <v>46113</v>
       </c>
-      <c r="B84" s="15" t="inlineStr">
+      <c r="B84" s="23" t="inlineStr">
         <is>
           <t>Zac Gallen</t>
         </is>
       </c>
-      <c r="C84" s="16" t="inlineStr">
+      <c r="C84" s="24" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="D84" s="16" t="inlineStr">
+      <c r="D84" s="24" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="E84" s="17" t="n">
+      <c r="E84" s="25" t="n">
         <v>5.5</v>
       </c>
-      <c r="F84" s="16" t="inlineStr">
+      <c r="F84" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G84" s="16" t="n">
+      <c r="G84" s="24" t="n">
         <v>112</v>
       </c>
-      <c r="H84" s="18" t="n">
+      <c r="H84" s="26" t="n">
         <v>0.707</v>
       </c>
-      <c r="I84" s="18" t="n">
+      <c r="I84" s="26" t="n">
         <v>0.4717</v>
       </c>
-      <c r="J84" s="18" t="n">
+      <c r="J84" s="26" t="n">
         <v>0.2353</v>
       </c>
-      <c r="K84" s="19" t="n">
+      <c r="K84" s="27" t="n">
         <v>4.34</v>
       </c>
-      <c r="L84" s="17" t="n">
+      <c r="L84" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M84" s="19" t="n">
+      <c r="M84" s="27" t="n">
         <v>1.11</v>
       </c>
-      <c r="N84" s="16" t="n">
+      <c r="N84" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="O84" s="20" t="inlineStr">
+      <c r="O84" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P84" s="21" t="n">
+      <c r="P84" s="29" t="n">
         <v>1.12</v>
       </c>
     </row>
     <row r="85" ht="17" customHeight="1">
-      <c r="A85" s="22" t="n">
+      <c r="A85" s="6" t="n">
         <v>46113</v>
       </c>
-      <c r="B85" s="23" t="inlineStr">
+      <c r="B85" s="7" t="inlineStr">
         <is>
           <t>Nathan Eovaldi</t>
         </is>
       </c>
-      <c r="C85" s="24" t="inlineStr">
+      <c r="C85" s="8" t="inlineStr">
         <is>
           <t>TEX</t>
         </is>
       </c>
-      <c r="D85" s="24" t="inlineStr">
+      <c r="D85" s="8" t="inlineStr">
         <is>
           <t>BAL</t>
         </is>
       </c>
-      <c r="E85" s="25" t="n">
+      <c r="E85" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="F85" s="24" t="inlineStr">
+      <c r="F85" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G85" s="24" t="n">
+      <c r="G85" s="8" t="n">
         <v>-168</v>
       </c>
-      <c r="H85" s="26" t="n">
+      <c r="H85" s="10" t="n">
         <v>0.743</v>
       </c>
-      <c r="I85" s="26" t="n">
+      <c r="I85" s="10" t="n">
         <v>0.6269</v>
       </c>
-      <c r="J85" s="26" t="n">
+      <c r="J85" s="10" t="n">
         <v>0.1161</v>
       </c>
-      <c r="K85" s="27" t="n">
+      <c r="K85" s="11" t="n">
         <v>7.699</v>
       </c>
-      <c r="L85" s="25" t="n">
+      <c r="L85" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="M85" s="27" t="n">
+      <c r="M85" s="11" t="n">
         <v>0.78</v>
       </c>
-      <c r="N85" s="24" t="n">
+      <c r="N85" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O85" s="28" t="inlineStr">
+      <c r="O85" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P85" s="29" t="n">
+      <c r="P85" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="86" ht="17" customHeight="1">
-      <c r="A86" s="14" t="n">
+      <c r="A86" s="22" t="n">
         <v>46113</v>
       </c>
-      <c r="B86" s="15" t="inlineStr">
+      <c r="B86" s="23" t="inlineStr">
         <is>
           <t>Jacob Misiorowski</t>
         </is>
       </c>
-      <c r="C86" s="16" t="inlineStr">
+      <c r="C86" s="24" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="D86" s="16" t="inlineStr">
+      <c r="D86" s="24" t="inlineStr">
         <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E86" s="17" t="n">
+      <c r="E86" s="25" t="n">
         <v>6.5</v>
       </c>
-      <c r="F86" s="16" t="inlineStr">
+      <c r="F86" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G86" s="16" t="n">
+      <c r="G86" s="24" t="n">
         <v>100</v>
       </c>
-      <c r="H86" s="18" t="n">
+      <c r="H86" s="26" t="n">
         <v>0.624</v>
       </c>
-      <c r="I86" s="18" t="n">
+      <c r="I86" s="26" t="n">
         <v>0.5</v>
       </c>
-      <c r="J86" s="18" t="n">
+      <c r="J86" s="26" t="n">
         <v>0.124</v>
       </c>
-      <c r="K86" s="19" t="n">
+      <c r="K86" s="27" t="n">
         <v>7.784</v>
       </c>
-      <c r="L86" s="17" t="n">
+      <c r="L86" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="M86" s="19" t="n">
+      <c r="M86" s="27" t="n">
         <v>0.62</v>
       </c>
-      <c r="N86" s="16" t="n">
+      <c r="N86" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="O86" s="20" t="inlineStr">
+      <c r="O86" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P86" s="21" t="n">
+      <c r="P86" s="29" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="87" ht="17" customHeight="1">
-      <c r="A87" s="22" t="n">
+      <c r="A87" s="6" t="n">
         <v>46113</v>
       </c>
-      <c r="B87" s="23" t="inlineStr">
+      <c r="B87" s="7" t="inlineStr">
         <is>
           <t>Cade Cavalli</t>
         </is>
       </c>
-      <c r="C87" s="24" t="inlineStr">
+      <c r="C87" s="8" t="inlineStr">
         <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="D87" s="24" t="inlineStr">
+      <c r="D87" s="8" t="inlineStr">
         <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E87" s="25" t="n">
+      <c r="E87" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F87" s="24" t="inlineStr">
+      <c r="F87" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G87" s="24" t="n">
+      <c r="G87" s="8" t="n">
         <v>-102</v>
       </c>
-      <c r="H87" s="26" t="n">
+      <c r="H87" s="10" t="n">
         <v>0.668</v>
       </c>
-      <c r="I87" s="26" t="n">
+      <c r="I87" s="10" t="n">
         <v>0.505</v>
       </c>
-      <c r="J87" s="26" t="n">
+      <c r="J87" s="10" t="n">
         <v>0.163</v>
       </c>
-      <c r="K87" s="27" t="n">
+      <c r="K87" s="11" t="n">
         <v>5.697</v>
       </c>
-      <c r="L87" s="25" t="n">
+      <c r="L87" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="M87" s="27" t="n">
+      <c r="M87" s="11" t="n">
         <v>0.82</v>
       </c>
-      <c r="N87" s="24" t="n">
+      <c r="N87" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="O87" s="28" t="inlineStr">
+      <c r="O87" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P87" s="29" t="n">
+      <c r="P87" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="88" ht="17" customHeight="1">
-      <c r="A88" s="22" t="n">
+      <c r="A88" s="6" t="n">
         <v>46113</v>
       </c>
-      <c r="B88" s="23" t="inlineStr">
+      <c r="B88" s="7" t="inlineStr">
         <is>
           <t>Nick Pivetta</t>
         </is>
       </c>
-      <c r="C88" s="24" t="inlineStr">
+      <c r="C88" s="8" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="D88" s="24" t="inlineStr">
+      <c r="D88" s="8" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="E88" s="25" t="n">
+      <c r="E88" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="F88" s="24" t="inlineStr">
+      <c r="F88" s="8" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G88" s="24" t="n">
+      <c r="G88" s="8" t="n">
         <v>128</v>
       </c>
-      <c r="H88" s="26" t="n">
+      <c r="H88" s="10" t="n">
         <v>0.55</v>
       </c>
-      <c r="I88" s="26" t="n">
+      <c r="I88" s="10" t="n">
         <v>0.4386</v>
       </c>
-      <c r="J88" s="26" t="n">
+      <c r="J88" s="10" t="n">
         <v>0.1114</v>
       </c>
-      <c r="K88" s="27" t="n">
+      <c r="K88" s="11" t="n">
         <v>5.551</v>
       </c>
-      <c r="L88" s="25" t="n">
+      <c r="L88" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="M88" s="27" t="n">
+      <c r="M88" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="N88" s="24" t="n">
+      <c r="N88" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="O88" s="28" t="inlineStr">
+      <c r="O88" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P88" s="29" t="n">
+      <c r="P88" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="89" ht="17" customHeight="1">
-      <c r="A89" s="14" t="n">
+      <c r="A89" s="22" t="n">
         <v>46113</v>
       </c>
-      <c r="B89" s="15" t="inlineStr">
+      <c r="B89" s="23" t="inlineStr">
         <is>
           <t>George Kirby</t>
         </is>
       </c>
-      <c r="C89" s="16" t="inlineStr">
+      <c r="C89" s="24" t="inlineStr">
         <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="D89" s="16" t="inlineStr">
+      <c r="D89" s="24" t="inlineStr">
         <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E89" s="17" t="n">
+      <c r="E89" s="25" t="n">
         <v>7.5</v>
       </c>
-      <c r="F89" s="16" t="inlineStr">
+      <c r="F89" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G89" s="16" t="n">
+      <c r="G89" s="24" t="n">
         <v>-178</v>
       </c>
-      <c r="H89" s="18" t="n">
+      <c r="H89" s="26" t="n">
         <v>0.726</v>
       </c>
-      <c r="I89" s="18" t="n">
+      <c r="I89" s="26" t="n">
         <v>0.6403</v>
       </c>
-      <c r="J89" s="18" t="n">
+      <c r="J89" s="26" t="n">
         <v>0.0857</v>
       </c>
-      <c r="K89" s="19" t="n">
+      <c r="K89" s="27" t="n">
         <v>5.8</v>
       </c>
-      <c r="L89" s="17" t="n">
+      <c r="L89" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="M89" s="19" t="n">
+      <c r="M89" s="27" t="n">
         <v>0.6</v>
       </c>
-      <c r="N89" s="16" t="n">
+      <c r="N89" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="O89" s="20" t="inlineStr">
+      <c r="O89" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P89" s="21" t="n">
+      <c r="P89" s="29" t="n">
         <v>0.5618</v>
       </c>
     </row>
     <row r="90" ht="17" customHeight="1">
-      <c r="A90" s="22" t="n">
+      <c r="A90" s="6" t="n">
         <v>46113</v>
       </c>
-      <c r="B90" s="23" t="inlineStr">
+      <c r="B90" s="7" t="inlineStr">
         <is>
           <t>Shane Smith</t>
         </is>
       </c>
-      <c r="C90" s="24" t="inlineStr">
+      <c r="C90" s="8" t="inlineStr">
         <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="D90" s="24" t="inlineStr">
+      <c r="D90" s="8" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="E90" s="25" t="n">
+      <c r="E90" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F90" s="24" t="inlineStr">
+      <c r="F90" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G90" s="24" t="n">
+      <c r="G90" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="H90" s="26" t="n">
+      <c r="H90" s="10" t="n">
         <v>0.576</v>
       </c>
-      <c r="I90" s="26" t="n">
+      <c r="I90" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="J90" s="26" t="n">
+      <c r="J90" s="10" t="n">
         <v>0.076</v>
       </c>
-      <c r="K90" s="27" t="n">
+      <c r="K90" s="11" t="n">
         <v>5.393</v>
       </c>
-      <c r="L90" s="25" t="n">
+      <c r="L90" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M90" s="27" t="n">
+      <c r="M90" s="11" t="n">
         <v>0.38</v>
       </c>
-      <c r="N90" s="24" t="n">
+      <c r="N90" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="O90" s="28" t="inlineStr">
+      <c r="O90" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P90" s="29" t="n">
+      <c r="P90" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="91" ht="17" customHeight="1">
-      <c r="A91" s="14" t="n">
+      <c r="A91" s="22" t="n">
         <v>46113</v>
       </c>
-      <c r="B91" s="15" t="inlineStr">
+      <c r="B91" s="23" t="inlineStr">
         <is>
           <t>Kyle Freeland</t>
         </is>
       </c>
-      <c r="C91" s="16" t="inlineStr">
+      <c r="C91" s="24" t="inlineStr">
         <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="D91" s="16" t="inlineStr">
+      <c r="D91" s="24" t="inlineStr">
         <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="E91" s="17" t="n">
+      <c r="E91" s="25" t="n">
         <v>3.5</v>
       </c>
-      <c r="F91" s="16" t="inlineStr">
+      <c r="F91" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G91" s="16" t="n">
+      <c r="G91" s="24" t="n">
         <v>100</v>
       </c>
-      <c r="H91" s="18" t="n">
+      <c r="H91" s="26" t="n">
         <v>0.57</v>
       </c>
-      <c r="I91" s="18" t="n">
+      <c r="I91" s="26" t="n">
         <v>0.5</v>
       </c>
-      <c r="J91" s="18" t="n">
+      <c r="J91" s="26" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="K91" s="19" t="n">
+      <c r="K91" s="27" t="n">
         <v>4.038</v>
       </c>
-      <c r="L91" s="17" t="n">
+      <c r="L91" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M91" s="19" t="n">
+      <c r="M91" s="27" t="n">
         <v>0.35</v>
       </c>
-      <c r="N91" s="16" t="n">
+      <c r="N91" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="O91" s="20" t="inlineStr">
+      <c r="O91" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P91" s="21" t="n">
+      <c r="P91" s="29" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="92" ht="17" customHeight="1">
-      <c r="A92" s="22" t="n">
+      <c r="A92" s="6" t="n">
         <v>46113</v>
       </c>
-      <c r="B92" s="23" t="inlineStr">
+      <c r="B92" s="7" t="inlineStr">
         <is>
           <t>Mike Burrows</t>
         </is>
       </c>
-      <c r="C92" s="24" t="inlineStr">
+      <c r="C92" s="8" t="inlineStr">
         <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="D92" s="24" t="inlineStr">
+      <c r="D92" s="8" t="inlineStr">
         <is>
           <t>BOS</t>
         </is>
       </c>
-      <c r="E92" s="25" t="n">
+      <c r="E92" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="F92" s="24" t="inlineStr">
+      <c r="F92" s="8" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G92" s="24" t="n">
+      <c r="G92" s="8" t="n">
         <v>-114</v>
       </c>
-      <c r="H92" s="26" t="n">
+      <c r="H92" s="10" t="n">
         <v>0.636</v>
       </c>
-      <c r="I92" s="26" t="n">
+      <c r="I92" s="10" t="n">
         <v>0.5327</v>
       </c>
-      <c r="J92" s="26" t="n">
+      <c r="J92" s="10" t="n">
         <v>0.1033</v>
       </c>
-      <c r="K92" s="27" t="n">
+      <c r="K92" s="11" t="n">
         <v>4.943</v>
       </c>
-      <c r="L92" s="25" t="n">
+      <c r="L92" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="M92" s="27" t="n">
+      <c r="M92" s="11" t="n">
         <v>0.55</v>
       </c>
-      <c r="N92" s="24" t="n">
+      <c r="N92" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="O92" s="28" t="inlineStr">
+      <c r="O92" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P92" s="29" t="n">
+      <c r="P92" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="93" ht="17" customHeight="1">
-      <c r="A93" s="14" t="n">
+      <c r="A93" s="22" t="n">
         <v>46113</v>
       </c>
-      <c r="B93" s="15" t="inlineStr">
+      <c r="B93" s="23" t="inlineStr">
         <is>
           <t>Matthew Liberatore</t>
         </is>
       </c>
-      <c r="C93" s="16" t="inlineStr">
+      <c r="C93" s="24" t="inlineStr">
         <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="D93" s="16" t="inlineStr">
+      <c r="D93" s="24" t="inlineStr">
         <is>
           <t>NYM</t>
         </is>
       </c>
-      <c r="E93" s="17" t="n">
+      <c r="E93" s="25" t="n">
         <v>3.5</v>
       </c>
-      <c r="F93" s="16" t="inlineStr">
+      <c r="F93" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G93" s="16" t="n">
+      <c r="G93" s="24" t="n">
         <v>118</v>
       </c>
-      <c r="H93" s="18" t="n">
+      <c r="H93" s="26" t="n">
         <v>0.525</v>
       </c>
-      <c r="I93" s="18" t="n">
+      <c r="I93" s="26" t="n">
         <v>0.4587</v>
       </c>
-      <c r="J93" s="18" t="n">
+      <c r="J93" s="26" t="n">
         <v>0.0663</v>
       </c>
-      <c r="K93" s="19" t="n">
+      <c r="K93" s="27" t="n">
         <v>3.583</v>
       </c>
-      <c r="L93" s="17" t="n">
+      <c r="L93" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M93" s="19" t="n">
+      <c r="M93" s="27" t="n">
         <v>0.31</v>
       </c>
-      <c r="N93" s="16" t="n">
+      <c r="N93" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="O93" s="20" t="inlineStr">
+      <c r="O93" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P93" s="21" t="n">
+      <c r="P93" s="29" t="n">
         <v>1.18</v>
       </c>
     </row>
     <row r="94" ht="17" customHeight="1">
-      <c r="A94" s="14" t="n">
+      <c r="A94" s="22" t="n">
         <v>46113</v>
       </c>
-      <c r="B94" s="15" t="inlineStr">
+      <c r="B94" s="23" t="inlineStr">
         <is>
           <t>Kevin Gausman</t>
         </is>
       </c>
-      <c r="C94" s="16" t="inlineStr">
+      <c r="C94" s="24" t="inlineStr">
         <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="D94" s="16" t="inlineStr">
+      <c r="D94" s="24" t="inlineStr">
         <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="E94" s="17" t="n">
+      <c r="E94" s="25" t="n">
         <v>7.5</v>
       </c>
-      <c r="F94" s="16" t="inlineStr">
+      <c r="F94" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G94" s="16" t="n">
+      <c r="G94" s="24" t="n">
         <v>116</v>
       </c>
-      <c r="H94" s="18" t="n">
+      <c r="H94" s="26" t="n">
         <v>0.529</v>
       </c>
-      <c r="I94" s="18" t="n">
+      <c r="I94" s="26" t="n">
         <v>0.463</v>
       </c>
-      <c r="J94" s="18" t="n">
+      <c r="J94" s="26" t="n">
         <v>0.066</v>
       </c>
-      <c r="K94" s="19" t="n">
+      <c r="K94" s="27" t="n">
         <v>7.914</v>
       </c>
-      <c r="L94" s="17" t="n">
+      <c r="L94" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M94" s="19" t="n">
+      <c r="M94" s="27" t="n">
         <v>0.31</v>
       </c>
-      <c r="N94" s="16" t="n">
+      <c r="N94" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="O94" s="20" t="inlineStr">
+      <c r="O94" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P94" s="21" t="n">
+      <c r="P94" s="29" t="n">
         <v>1.16</v>
       </c>
     </row>
     <row r="95" ht="17" customHeight="1">
-      <c r="A95" s="22" t="n">
+      <c r="A95" s="6" t="n">
         <v>46113</v>
       </c>
-      <c r="B95" s="23" t="inlineStr">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>Yusei Kikuchi</t>
         </is>
       </c>
-      <c r="C95" s="24" t="inlineStr">
+      <c r="C95" s="8" t="inlineStr">
         <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="D95" s="24" t="inlineStr">
+      <c r="D95" s="8" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="E95" s="25" t="n">
+      <c r="E95" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F95" s="24" t="inlineStr">
+      <c r="F95" s="8" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G95" s="24" t="n">
+      <c r="G95" s="8" t="n">
         <v>102</v>
       </c>
-      <c r="H95" s="26" t="n">
+      <c r="H95" s="10" t="n">
         <v>0.556</v>
       </c>
-      <c r="I95" s="26" t="n">
+      <c r="I95" s="10" t="n">
         <v>0.495</v>
       </c>
-      <c r="J95" s="26" t="n">
+      <c r="J95" s="10" t="n">
         <v>0.061</v>
       </c>
-      <c r="K95" s="27" t="n">
+      <c r="K95" s="11" t="n">
         <v>4.364</v>
       </c>
-      <c r="L95" s="25" t="n">
+      <c r="L95" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="M95" s="27" t="n">
+      <c r="M95" s="11" t="n">
         <v>0.3</v>
       </c>
-      <c r="N95" s="24" t="n">
+      <c r="N95" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O95" s="28" t="inlineStr">
+      <c r="O95" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P95" s="29" t="n">
+      <c r="P95" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="96" ht="17" customHeight="1">
-      <c r="A96" s="14" t="n">
+      <c r="A96" s="22" t="n">
         <v>46113</v>
       </c>
-      <c r="B96" s="15" t="inlineStr">
+      <c r="B96" s="23" t="inlineStr">
         <is>
           <t>Freddy Peralta</t>
         </is>
       </c>
-      <c r="C96" s="16" t="inlineStr">
+      <c r="C96" s="24" t="inlineStr">
         <is>
           <t>NYM</t>
         </is>
       </c>
-      <c r="D96" s="16" t="inlineStr">
+      <c r="D96" s="24" t="inlineStr">
         <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="E96" s="17" t="n">
+      <c r="E96" s="25" t="n">
         <v>6.5</v>
       </c>
-      <c r="F96" s="16" t="inlineStr">
+      <c r="F96" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G96" s="16" t="n">
+      <c r="G96" s="24" t="n">
         <v>116</v>
       </c>
-      <c r="H96" s="18" t="n">
+      <c r="H96" s="26" t="n">
         <v>0.515</v>
       </c>
-      <c r="I96" s="18" t="n">
+      <c r="I96" s="26" t="n">
         <v>0.463</v>
       </c>
-      <c r="J96" s="18" t="n">
+      <c r="J96" s="26" t="n">
         <v>0.052</v>
       </c>
-      <c r="K96" s="19" t="n">
+      <c r="K96" s="27" t="n">
         <v>6.789</v>
       </c>
-      <c r="L96" s="17" t="n">
+      <c r="L96" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M96" s="19" t="n">
+      <c r="M96" s="27" t="n">
         <v>0.24</v>
       </c>
-      <c r="N96" s="16" t="n">
+      <c r="N96" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="O96" s="20" t="inlineStr">
+      <c r="O96" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P96" s="21" t="n">
+      <c r="P96" s="29" t="n">
         <v>1.16</v>
       </c>
     </row>
     <row r="97" ht="17" customHeight="1">
-      <c r="A97" s="14" t="n">
+      <c r="A97" s="22" t="n">
         <v>46112</v>
       </c>
-      <c r="B97" s="15" t="inlineStr">
+      <c r="B97" s="23" t="inlineStr">
         <is>
           <t>Erick Fedde</t>
         </is>
       </c>
-      <c r="C97" s="16" t="inlineStr">
+      <c r="C97" s="24" t="inlineStr">
         <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="D97" s="16" t="inlineStr">
+      <c r="D97" s="24" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="E97" s="17" t="n">
+      <c r="E97" s="25" t="n">
         <v>3.5</v>
       </c>
-      <c r="F97" s="16" t="inlineStr">
+      <c r="F97" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G97" s="16" t="n">
+      <c r="G97" s="24" t="n">
         <v>134</v>
       </c>
-      <c r="H97" s="18" t="n">
+      <c r="H97" s="26" t="n">
         <v>0.527</v>
       </c>
-      <c r="I97" s="18" t="n">
+      <c r="I97" s="26" t="n">
         <v>0.4274</v>
       </c>
-      <c r="J97" s="18" t="n">
+      <c r="J97" s="26" t="n">
         <v>0.09959999999999999</v>
       </c>
-      <c r="K97" s="19" t="n">
+      <c r="K97" s="27" t="n">
         <v>3.852</v>
       </c>
-      <c r="L97" s="17" t="n">
+      <c r="L97" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="M97" s="19" t="n">
+      <c r="M97" s="27" t="n">
         <v>0.44</v>
       </c>
-      <c r="N97" s="16" t="n">
+      <c r="N97" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="O97" s="20" t="inlineStr">
+      <c r="O97" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P97" s="21" t="n">
+      <c r="P97" s="29" t="n">
         <v>1.34</v>
       </c>
     </row>
     <row r="98" ht="17" customHeight="1">
-      <c r="A98" s="14" t="n">
+      <c r="A98" s="22" t="n">
         <v>46112</v>
       </c>
-      <c r="B98" s="15" t="inlineStr">
+      <c r="B98" s="23" t="inlineStr">
         <is>
           <t>Ryan Feltner</t>
         </is>
       </c>
-      <c r="C98" s="16" t="inlineStr">
+      <c r="C98" s="24" t="inlineStr">
         <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="D98" s="16" t="inlineStr">
+      <c r="D98" s="24" t="inlineStr">
         <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="E98" s="17" t="n">
+      <c r="E98" s="25" t="n">
         <v>3.5</v>
       </c>
-      <c r="F98" s="16" t="inlineStr">
+      <c r="F98" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G98" s="16" t="n">
+      <c r="G98" s="24" t="n">
         <v>-108</v>
       </c>
-      <c r="H98" s="18" t="n">
+      <c r="H98" s="26" t="n">
         <v>0.655</v>
       </c>
-      <c r="I98" s="18" t="n">
+      <c r="I98" s="26" t="n">
         <v>0.5192</v>
       </c>
-      <c r="J98" s="18" t="n">
+      <c r="J98" s="26" t="n">
         <v>0.1358</v>
       </c>
-      <c r="K98" s="19" t="n">
+      <c r="K98" s="27" t="n">
         <v>4.719</v>
       </c>
-      <c r="L98" s="17" t="n">
+      <c r="L98" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="M98" s="19" t="n">
+      <c r="M98" s="27" t="n">
         <v>0.71</v>
       </c>
-      <c r="N98" s="16" t="n">
+      <c r="N98" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="O98" s="20" t="inlineStr">
+      <c r="O98" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P98" s="21" t="n">
+      <c r="P98" s="29" t="n">
         <v>0.9258999999999999</v>
       </c>
     </row>
     <row r="99" ht="17" customHeight="1">
-      <c r="A99" s="14" t="n">
+      <c r="A99" s="22" t="n">
         <v>46112</v>
       </c>
-      <c r="B99" s="15" t="inlineStr">
+      <c r="B99" s="23" t="inlineStr">
         <is>
           <t>Jameson Taillon</t>
         </is>
       </c>
-      <c r="C99" s="16" t="inlineStr">
+      <c r="C99" s="24" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="D99" s="16" t="inlineStr">
+      <c r="D99" s="24" t="inlineStr">
         <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="E99" s="17" t="n">
+      <c r="E99" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F99" s="16" t="inlineStr">
+      <c r="F99" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G99" s="16" t="n">
+      <c r="G99" s="24" t="n">
         <v>116</v>
       </c>
-      <c r="H99" s="18" t="n">
+      <c r="H99" s="26" t="n">
         <v>0.569</v>
       </c>
-      <c r="I99" s="18" t="n">
+      <c r="I99" s="26" t="n">
         <v>0.463</v>
       </c>
-      <c r="J99" s="18" t="n">
+      <c r="J99" s="26" t="n">
         <v>0.106</v>
       </c>
-      <c r="K99" s="19" t="n">
+      <c r="K99" s="27" t="n">
         <v>4.313</v>
       </c>
-      <c r="L99" s="17" t="n">
+      <c r="L99" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="M99" s="19" t="n">
+      <c r="M99" s="27" t="n">
         <v>0.49</v>
       </c>
-      <c r="N99" s="16" t="n">
+      <c r="N99" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="O99" s="20" t="inlineStr">
+      <c r="O99" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P99" s="21" t="n">
+      <c r="P99" s="29" t="n">
         <v>1.16</v>
       </c>
     </row>
     <row r="100" ht="17" customHeight="1">
-      <c r="A100" s="22" t="n">
+      <c r="A100" s="6" t="n">
         <v>46112</v>
       </c>
-      <c r="B100" s="23" t="inlineStr">
+      <c r="B100" s="7" t="inlineStr">
         <is>
           <t>José Soriano</t>
         </is>
       </c>
-      <c r="C100" s="24" t="inlineStr">
+      <c r="C100" s="8" t="inlineStr">
         <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="D100" s="24" t="inlineStr">
+      <c r="D100" s="8" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="E100" s="25" t="n">
+      <c r="E100" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F100" s="24" t="inlineStr">
+      <c r="F100" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G100" s="24" t="n">
+      <c r="G100" s="8" t="n">
         <v>-110</v>
       </c>
-      <c r="H100" s="26" t="n">
+      <c r="H100" s="10" t="n">
         <v>0.676</v>
       </c>
-      <c r="I100" s="26" t="n">
+      <c r="I100" s="10" t="n">
         <v>0.5238</v>
       </c>
-      <c r="J100" s="26" t="n">
+      <c r="J100" s="10" t="n">
         <v>0.1522</v>
       </c>
-      <c r="K100" s="27" t="n">
+      <c r="K100" s="11" t="n">
         <v>5.918</v>
       </c>
-      <c r="L100" s="25" t="n">
+      <c r="L100" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="M100" s="27" t="n">
+      <c r="M100" s="11" t="n">
         <v>0.8</v>
       </c>
-      <c r="N100" s="24" t="n">
+      <c r="N100" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="O100" s="28" t="inlineStr">
+      <c r="O100" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P100" s="29" t="n">
+      <c r="P100" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="101" ht="17" customHeight="1">
-      <c r="A101" s="14" t="n">
+      <c r="A101" s="22" t="n">
         <v>46112</v>
       </c>
-      <c r="B101" s="15" t="inlineStr">
+      <c r="B101" s="23" t="inlineStr">
         <is>
           <t>Max Scherzer</t>
         </is>
       </c>
-      <c r="C101" s="16" t="inlineStr">
+      <c r="C101" s="24" t="inlineStr">
         <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="D101" s="16" t="inlineStr">
+      <c r="D101" s="24" t="inlineStr">
         <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="E101" s="17" t="n">
+      <c r="E101" s="25" t="n">
         <v>5.5</v>
       </c>
-      <c r="F101" s="16" t="inlineStr">
+      <c r="F101" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G101" s="16" t="n">
+      <c r="G101" s="24" t="n">
         <v>-130</v>
       </c>
-      <c r="H101" s="18" t="n">
+      <c r="H101" s="26" t="n">
         <v>0.652</v>
       </c>
-      <c r="I101" s="18" t="n">
+      <c r="I101" s="26" t="n">
         <v>0.5652</v>
       </c>
-      <c r="J101" s="18" t="n">
+      <c r="J101" s="26" t="n">
         <v>0.0868</v>
       </c>
-      <c r="K101" s="19" t="n">
+      <c r="K101" s="27" t="n">
         <v>4.757</v>
       </c>
-      <c r="L101" s="17" t="n">
+      <c r="L101" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="M101" s="19" t="n">
+      <c r="M101" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="N101" s="16" t="n">
+      <c r="N101" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="O101" s="20" t="inlineStr">
+      <c r="O101" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P101" s="21" t="n">
+      <c r="P101" s="29" t="n">
         <v>0.7692</v>
       </c>
     </row>
     <row r="102" ht="17" customHeight="1">
-      <c r="A102" s="22" t="n">
+      <c r="A102" s="6" t="n">
         <v>46112</v>
       </c>
-      <c r="B102" s="23" t="inlineStr">
+      <c r="B102" s="7" t="inlineStr">
         <is>
           <t>Aaron Civale</t>
         </is>
       </c>
-      <c r="C102" s="24" t="inlineStr">
+      <c r="C102" s="8" t="inlineStr">
         <is>
           <t>OAK</t>
         </is>
       </c>
-      <c r="D102" s="24" t="inlineStr">
+      <c r="D102" s="8" t="inlineStr">
         <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E102" s="25" t="n">
+      <c r="E102" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="F102" s="24" t="inlineStr">
+      <c r="F102" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G102" s="24" t="n">
+      <c r="G102" s="8" t="n">
         <v>-146</v>
       </c>
-      <c r="H102" s="26" t="n">
+      <c r="H102" s="10" t="n">
         <v>0.666</v>
       </c>
-      <c r="I102" s="26" t="n">
+      <c r="I102" s="10" t="n">
         <v>0.5935</v>
       </c>
-      <c r="J102" s="26" t="n">
+      <c r="J102" s="10" t="n">
         <v>0.0725</v>
       </c>
-      <c r="K102" s="27" t="n">
+      <c r="K102" s="11" t="n">
         <v>4.714</v>
       </c>
-      <c r="L102" s="25" t="n">
+      <c r="L102" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="M102" s="27" t="n">
+      <c r="M102" s="11" t="n">
         <v>0.45</v>
       </c>
-      <c r="N102" s="24" t="n">
+      <c r="N102" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="O102" s="28" t="inlineStr">
+      <c r="O102" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P102" s="29" t="n">
+      <c r="P102" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="103" ht="17" customHeight="1">
-      <c r="A103" s="22" t="n">
+      <c r="A103" s="6" t="n">
         <v>46112</v>
       </c>
-      <c r="B103" s="23" t="inlineStr">
+      <c r="B103" s="7" t="inlineStr">
         <is>
           <t>Andre Pallante</t>
         </is>
       </c>
-      <c r="C103" s="24" t="inlineStr">
+      <c r="C103" s="8" t="inlineStr">
         <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="D103" s="24" t="inlineStr">
+      <c r="D103" s="8" t="inlineStr">
         <is>
           <t>NYM</t>
         </is>
       </c>
-      <c r="E103" s="25" t="n">
+      <c r="E103" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="F103" s="24" t="inlineStr">
+      <c r="F103" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G103" s="24" t="n">
+      <c r="G103" s="8" t="n">
         <v>126</v>
       </c>
-      <c r="H103" s="26" t="n">
+      <c r="H103" s="10" t="n">
         <v>0.523</v>
       </c>
-      <c r="I103" s="26" t="n">
+      <c r="I103" s="10" t="n">
         <v>0.4425</v>
       </c>
-      <c r="J103" s="26" t="n">
+      <c r="J103" s="10" t="n">
         <v>0.0805</v>
       </c>
-      <c r="K103" s="27" t="n">
+      <c r="K103" s="11" t="n">
         <v>3.876</v>
       </c>
-      <c r="L103" s="25" t="n">
+      <c r="L103" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M103" s="27" t="n">
+      <c r="M103" s="11" t="n">
         <v>0.36</v>
       </c>
-      <c r="N103" s="24" t="n">
+      <c r="N103" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="O103" s="28" t="inlineStr">
+      <c r="O103" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P103" s="29" t="n">
+      <c r="P103" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="104" ht="17" customHeight="1">
-      <c r="A104" s="22" t="n">
+      <c r="A104" s="6" t="n">
         <v>46111</v>
       </c>
-      <c r="B104" s="23" t="inlineStr">
+      <c r="B104" s="7" t="inlineStr">
         <is>
           <t>Jacob Lopez</t>
         </is>
       </c>
-      <c r="C104" s="24" t="inlineStr">
+      <c r="C104" s="8" t="inlineStr">
         <is>
           <t>OAK</t>
         </is>
       </c>
-      <c r="D104" s="24" t="inlineStr">
+      <c r="D104" s="8" t="inlineStr">
         <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E104" s="25" t="n">
+      <c r="E104" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="F104" s="24" t="inlineStr">
+      <c r="F104" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G104" s="24" t="n">
+      <c r="G104" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="H104" s="26" t="n">
+      <c r="H104" s="10" t="n">
         <v>0.586</v>
       </c>
-      <c r="I104" s="26" t="n">
+      <c r="I104" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="J104" s="26" t="n">
+      <c r="J104" s="10" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="K104" s="27" t="n">
+      <c r="K104" s="11" t="n">
         <v>6.418</v>
       </c>
-      <c r="L104" s="25" t="n">
+      <c r="L104" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M104" s="27" t="n">
+      <c r="M104" s="11" t="n">
         <v>0.43</v>
       </c>
-      <c r="N104" s="24" t="n">
+      <c r="N104" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="O104" s="28" t="inlineStr">
+      <c r="O104" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P104" s="29" t="n">
+      <c r="P104" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="105" ht="17" customHeight="1">
-      <c r="A105" s="14" t="n">
+      <c r="A105" s="22" t="n">
         <v>46111</v>
       </c>
-      <c r="B105" s="15" t="inlineStr">
+      <c r="B105" s="23" t="inlineStr">
         <is>
           <t>Edward Cabrera</t>
         </is>
       </c>
-      <c r="C105" s="16" t="inlineStr">
+      <c r="C105" s="24" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="D105" s="16" t="inlineStr">
+      <c r="D105" s="24" t="inlineStr">
         <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="E105" s="17" t="n">
+      <c r="E105" s="25" t="n">
         <v>6.5</v>
       </c>
-      <c r="F105" s="16" t="inlineStr">
+      <c r="F105" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G105" s="16" t="n">
+      <c r="G105" s="24" t="n">
         <v>116</v>
       </c>
-      <c r="H105" s="18" t="n">
+      <c r="H105" s="26" t="n">
         <v>0.6889999999999999</v>
       </c>
-      <c r="I105" s="18" t="n">
+      <c r="I105" s="26" t="n">
         <v>0.463</v>
       </c>
-      <c r="J105" s="18" t="n">
+      <c r="J105" s="26" t="n">
         <v>0.226</v>
       </c>
-      <c r="K105" s="19" t="n">
+      <c r="K105" s="27" t="n">
         <v>5.286</v>
       </c>
-      <c r="L105" s="17" t="n">
+      <c r="L105" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="M105" s="19" t="n">
+      <c r="M105" s="27" t="n">
         <v>1.05</v>
       </c>
-      <c r="N105" s="16" t="n">
+      <c r="N105" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="O105" s="20" t="inlineStr">
+      <c r="O105" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P105" s="21" t="n">
+      <c r="P105" s="29" t="n">
         <v>1.16</v>
       </c>
     </row>
     <row r="106" ht="17" customHeight="1">
-      <c r="A106" s="14" t="n">
+      <c r="A106" s="22" t="n">
         <v>46111</v>
       </c>
-      <c r="B106" s="15" t="inlineStr">
+      <c r="B106" s="23" t="inlineStr">
         <is>
           <t>Jack Leiter</t>
         </is>
       </c>
-      <c r="C106" s="16" t="inlineStr">
+      <c r="C106" s="24" t="inlineStr">
         <is>
           <t>TEX</t>
         </is>
       </c>
-      <c r="D106" s="16" t="inlineStr">
+      <c r="D106" s="24" t="inlineStr">
         <is>
           <t>BAL</t>
         </is>
       </c>
-      <c r="E106" s="17" t="n">
+      <c r="E106" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F106" s="16" t="inlineStr">
+      <c r="F106" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G106" s="16" t="n">
+      <c r="G106" s="24" t="n">
         <v>-144</v>
       </c>
-      <c r="H106" s="18" t="n">
+      <c r="H106" s="26" t="n">
         <v>0.679</v>
       </c>
-      <c r="I106" s="18" t="n">
+      <c r="I106" s="26" t="n">
         <v>0.5901999999999999</v>
       </c>
-      <c r="J106" s="18" t="n">
+      <c r="J106" s="26" t="n">
         <v>0.0888</v>
       </c>
-      <c r="K106" s="19" t="n">
+      <c r="K106" s="27" t="n">
         <v>6.017</v>
       </c>
-      <c r="L106" s="17" t="n">
+      <c r="L106" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="M106" s="19" t="n">
+      <c r="M106" s="27" t="n">
         <v>0.54</v>
       </c>
-      <c r="N106" s="16" t="n">
+      <c r="N106" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="O106" s="20" t="inlineStr">
+      <c r="O106" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P106" s="21" t="n">
+      <c r="P106" s="29" t="n">
         <v>0.6944</v>
       </c>
     </row>
     <row r="107" ht="17" customHeight="1">
-      <c r="A107" s="22" t="n">
+      <c r="A107" s="6" t="n">
         <v>46111</v>
       </c>
-      <c r="B107" s="23" t="inlineStr">
+      <c r="B107" s="7" t="inlineStr">
         <is>
           <t>Simeon Woods Richardson</t>
         </is>
       </c>
-      <c r="C107" s="24" t="inlineStr">
+      <c r="C107" s="8" t="inlineStr">
         <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="D107" s="24" t="inlineStr">
+      <c r="D107" s="8" t="inlineStr">
         <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="E107" s="25" t="n">
+      <c r="E107" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="F107" s="24" t="inlineStr">
+      <c r="F107" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G107" s="24" t="n">
+      <c r="G107" s="8" t="n">
         <v>-112</v>
       </c>
-      <c r="H107" s="26" t="n">
+      <c r="H107" s="10" t="n">
         <v>0.783</v>
       </c>
-      <c r="I107" s="26" t="n">
+      <c r="I107" s="10" t="n">
         <v>0.5283</v>
       </c>
-      <c r="J107" s="26" t="n">
+      <c r="J107" s="10" t="n">
         <v>0.2547</v>
       </c>
-      <c r="K107" s="27" t="n">
+      <c r="K107" s="11" t="n">
         <v>5.562</v>
       </c>
-      <c r="L107" s="25" t="n">
+      <c r="L107" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="M107" s="27" t="n">
+      <c r="M107" s="11" t="n">
         <v>1.35</v>
       </c>
-      <c r="N107" s="24" t="n">
+      <c r="N107" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="O107" s="28" t="inlineStr">
+      <c r="O107" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P107" s="29" t="n">
+      <c r="P107" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="108" ht="17" customHeight="1">
-      <c r="A108" s="22" t="n">
+      <c r="A108" s="6" t="n">
         <v>46111</v>
       </c>
-      <c r="B108" s="23" t="inlineStr">
+      <c r="B108" s="7" t="inlineStr">
         <is>
           <t>Nick Martinez</t>
         </is>
       </c>
-      <c r="C108" s="24" t="inlineStr">
+      <c r="C108" s="8" t="inlineStr">
         <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="D108" s="24" t="inlineStr">
+      <c r="D108" s="8" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E108" s="25" t="n">
+      <c r="E108" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="F108" s="24" t="inlineStr">
+      <c r="F108" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G108" s="24" t="n">
+      <c r="G108" s="8" t="n">
         <v>-174</v>
       </c>
-      <c r="H108" s="26" t="n">
+      <c r="H108" s="10" t="n">
         <v>0.6889999999999999</v>
       </c>
-      <c r="I108" s="26" t="n">
+      <c r="I108" s="10" t="n">
         <v>0.635</v>
       </c>
-      <c r="J108" s="26" t="n">
+      <c r="J108" s="10" t="n">
         <v>0.054</v>
       </c>
-      <c r="K108" s="27" t="n">
+      <c r="K108" s="11" t="n">
         <v>4.97</v>
       </c>
-      <c r="L108" s="25" t="n">
+      <c r="L108" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="M108" s="27" t="n">
+      <c r="M108" s="11" t="n">
         <v>0.37</v>
       </c>
-      <c r="N108" s="24" t="n">
+      <c r="N108" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="O108" s="28" t="inlineStr">
+      <c r="O108" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P108" s="29" t="n">
+      <c r="P108" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="109" ht="17" customHeight="1">
-      <c r="A109" s="22" t="n">
+      <c r="A109" s="6" t="n">
         <v>46111</v>
       </c>
-      <c r="B109" s="23" t="inlineStr">
+      <c r="B109" s="7" t="inlineStr">
         <is>
           <t>Kyle Harrison</t>
         </is>
       </c>
-      <c r="C109" s="24" t="inlineStr">
+      <c r="C109" s="8" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="D109" s="24" t="inlineStr">
+      <c r="D109" s="8" t="inlineStr">
         <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E109" s="25" t="n">
+      <c r="E109" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F109" s="24" t="inlineStr">
+      <c r="F109" s="8" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G109" s="24" t="n">
+      <c r="G109" s="8" t="n">
         <v>114</v>
       </c>
-      <c r="H109" s="26" t="n">
+      <c r="H109" s="10" t="n">
         <v>0.521</v>
       </c>
-      <c r="I109" s="26" t="n">
+      <c r="I109" s="10" t="n">
         <v>0.4673</v>
       </c>
-      <c r="J109" s="26" t="n">
+      <c r="J109" s="10" t="n">
         <v>0.0537</v>
       </c>
-      <c r="K109" s="27" t="n">
+      <c r="K109" s="11" t="n">
         <v>4.628</v>
       </c>
-      <c r="L109" s="25" t="n">
+      <c r="L109" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="M109" s="27" t="n">
+      <c r="M109" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="N109" s="24" t="n">
+      <c r="N109" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="O109" s="28" t="inlineStr">
+      <c r="O109" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P109" s="29" t="n">
+      <c r="P109" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="110" ht="17" customHeight="1">
-      <c r="A110" s="14" t="n">
+      <c r="A110" s="22" t="n">
         <v>46111</v>
       </c>
-      <c r="B110" s="15" t="inlineStr">
+      <c r="B110" s="23" t="inlineStr">
         <is>
           <t>Davis Martin</t>
         </is>
       </c>
-      <c r="C110" s="16" t="inlineStr">
+      <c r="C110" s="24" t="inlineStr">
         <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="D110" s="16" t="inlineStr">
+      <c r="D110" s="24" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="E110" s="17" t="n">
+      <c r="E110" s="25" t="n">
         <v>3.5</v>
       </c>
-      <c r="F110" s="16" t="inlineStr">
+      <c r="F110" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G110" s="16" t="n">
+      <c r="G110" s="24" t="n">
         <v>-114</v>
       </c>
-      <c r="H110" s="18" t="n">
+      <c r="H110" s="26" t="n">
         <v>0.584</v>
       </c>
-      <c r="I110" s="18" t="n">
+      <c r="I110" s="26" t="n">
         <v>0.5327</v>
       </c>
-      <c r="J110" s="18" t="n">
+      <c r="J110" s="26" t="n">
         <v>0.0513</v>
       </c>
-      <c r="K110" s="19" t="n">
+      <c r="K110" s="27" t="n">
         <v>4.252</v>
       </c>
-      <c r="L110" s="17" t="n">
+      <c r="L110" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M110" s="19" t="n">
+      <c r="M110" s="27" t="n">
         <v>0.27</v>
       </c>
-      <c r="N110" s="16" t="n">
+      <c r="N110" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="O110" s="20" t="inlineStr">
+      <c r="O110" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P110" s="21" t="n">
+      <c r="P110" s="29" t="n">
         <v>0.8772</v>
       </c>
     </row>
     <row r="111" ht="17" customHeight="1">
-      <c r="A111" s="14" t="n">
+      <c r="A111" s="22" t="n">
         <v>46109</v>
       </c>
-      <c r="B111" s="15" t="inlineStr">
+      <c r="B111" s="23" t="inlineStr">
         <is>
           <t>Michael Wacha</t>
         </is>
       </c>
-      <c r="C111" s="16" t="inlineStr">
+      <c r="C111" s="24" t="inlineStr">
         <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="D111" s="16" t="inlineStr">
+      <c r="D111" s="24" t="inlineStr">
         <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E111" s="17" t="n">
+      <c r="E111" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F111" s="16" t="inlineStr">
+      <c r="F111" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G111" s="16" t="n">
+      <c r="G111" s="24" t="n">
         <v>140</v>
       </c>
-      <c r="H111" s="18" t="n">
+      <c r="H111" s="26" t="n">
         <v>0.476</v>
       </c>
-      <c r="I111" s="18" t="n">
+      <c r="I111" s="26" t="n">
         <v>0.4167</v>
       </c>
-      <c r="J111" s="18" t="n">
+      <c r="J111" s="26" t="n">
         <v>0.0593</v>
       </c>
-      <c r="K111" s="19" t="n">
+      <c r="K111" s="27" t="n">
         <v>4.645</v>
       </c>
-      <c r="L111" s="17" t="n">
+      <c r="L111" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M111" s="19" t="n">
+      <c r="M111" s="27" t="n">
         <v>0.25</v>
       </c>
-      <c r="N111" s="16" t="n">
+      <c r="N111" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="O111" s="20" t="inlineStr">
+      <c r="O111" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P111" s="21" t="n">
+      <c r="P111" s="29" t="n">
         <v>1.4</v>
       </c>
     </row>
     <row r="112" ht="17" customHeight="1">
-      <c r="A112" s="22" t="n">
+      <c r="A112" s="6" t="n">
         <v>46109</v>
       </c>
-      <c r="B112" s="23" t="inlineStr">
+      <c r="B112" s="7" t="inlineStr">
         <is>
           <t>Will Warren</t>
         </is>
       </c>
-      <c r="C112" s="24" t="inlineStr">
+      <c r="C112" s="8" t="inlineStr">
         <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="D112" s="24" t="inlineStr">
+      <c r="D112" s="8" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="E112" s="25" t="n">
+      <c r="E112" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F112" s="24" t="inlineStr">
+      <c r="F112" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G112" s="24" t="n">
+      <c r="G112" s="8" t="n">
         <v>110</v>
       </c>
-      <c r="H112" s="26" t="n">
+      <c r="H112" s="10" t="n">
         <v>0.573</v>
       </c>
-      <c r="I112" s="26" t="n">
+      <c r="I112" s="10" t="n">
         <v>0.4762</v>
       </c>
-      <c r="J112" s="26" t="n">
+      <c r="J112" s="10" t="n">
         <v>0.0968</v>
       </c>
-      <c r="K112" s="27" t="n">
+      <c r="K112" s="11" t="n">
         <v>5.339</v>
       </c>
-      <c r="L112" s="25" t="n">
+      <c r="L112" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M112" s="27" t="n">
+      <c r="M112" s="11" t="n">
         <v>0.46</v>
       </c>
-      <c r="N112" s="24" t="n">
+      <c r="N112" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="O112" s="28" t="inlineStr">
+      <c r="O112" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P112" s="29" t="n">
+      <c r="P112" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="113" ht="17" customHeight="1">
-      <c r="A113" s="22" t="n">
+      <c r="A113" s="6" t="n">
         <v>46109</v>
       </c>
-      <c r="B113" s="23" t="inlineStr">
+      <c r="B113" s="7" t="inlineStr">
         <is>
           <t>Jeffrey Springs</t>
         </is>
       </c>
-      <c r="C113" s="24" t="inlineStr">
+      <c r="C113" s="8" t="inlineStr">
         <is>
           <t>OAK</t>
         </is>
       </c>
-      <c r="D113" s="24" t="inlineStr">
+      <c r="D113" s="8" t="inlineStr">
         <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="E113" s="25" t="n">
+      <c r="E113" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="F113" s="24" t="inlineStr">
+      <c r="F113" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G113" s="24" t="n">
+      <c r="G113" s="8" t="n">
         <v>102</v>
       </c>
-      <c r="H113" s="26" t="n">
+      <c r="H113" s="10" t="n">
         <v>0.599</v>
       </c>
-      <c r="I113" s="26" t="n">
+      <c r="I113" s="10" t="n">
         <v>0.495</v>
       </c>
-      <c r="J113" s="26" t="n">
+      <c r="J113" s="10" t="n">
         <v>0.104</v>
       </c>
-      <c r="K113" s="27" t="n">
+      <c r="K113" s="11" t="n">
         <v>4.389</v>
       </c>
-      <c r="L113" s="25" t="n">
+      <c r="L113" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="M113" s="27" t="n">
+      <c r="M113" s="11" t="n">
         <v>0.51</v>
       </c>
-      <c r="N113" s="24" t="n">
+      <c r="N113" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="O113" s="28" t="inlineStr">
+      <c r="O113" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P113" s="29" t="n">
+      <c r="P113" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="114" ht="17" customHeight="1">
-      <c r="A114" s="22" t="n">
+      <c r="A114" s="6" t="n">
         <v>46109</v>
       </c>
-      <c r="B114" s="23" t="inlineStr">
+      <c r="B114" s="7" t="inlineStr">
         <is>
           <t>Eury Pérez</t>
         </is>
       </c>
-      <c r="C114" s="24" t="inlineStr">
+      <c r="C114" s="8" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="D114" s="24" t="inlineStr">
+      <c r="D114" s="8" t="inlineStr">
         <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="E114" s="25" t="n">
+      <c r="E114" s="9" t="n">
         <v>6.5</v>
       </c>
-      <c r="F114" s="24" t="inlineStr">
+      <c r="F114" s="8" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G114" s="24" t="n">
+      <c r="G114" s="8" t="n">
         <v>-154</v>
       </c>
-      <c r="H114" s="26" t="n">
+      <c r="H114" s="10" t="n">
         <v>0.713</v>
       </c>
-      <c r="I114" s="26" t="n">
+      <c r="I114" s="10" t="n">
         <v>0.6063</v>
       </c>
-      <c r="J114" s="26" t="n">
+      <c r="J114" s="10" t="n">
         <v>0.1067</v>
       </c>
-      <c r="K114" s="27" t="n">
+      <c r="K114" s="11" t="n">
         <v>5.311</v>
       </c>
-      <c r="L114" s="25" t="n">
+      <c r="L114" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="M114" s="27" t="n">
+      <c r="M114" s="11" t="n">
         <v>0.68</v>
       </c>
-      <c r="N114" s="24" t="n">
+      <c r="N114" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="O114" s="28" t="inlineStr">
+      <c r="O114" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P114" s="29" t="n">
+      <c r="P114" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="115" ht="17" customHeight="1">
-      <c r="A115" s="22" t="n">
+      <c r="A115" s="6" t="n">
         <v>46108</v>
       </c>
-      <c r="B115" s="23" t="inlineStr">
+      <c r="B115" s="7" t="inlineStr">
         <is>
           <t>Kyle Freeland</t>
         </is>
       </c>
-      <c r="C115" s="24" t="inlineStr">
+      <c r="C115" s="8" t="inlineStr">
         <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="D115" s="24" t="inlineStr">
+      <c r="D115" s="8" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="E115" s="25" t="n">
+      <c r="E115" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="F115" s="24" t="inlineStr">
+      <c r="F115" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G115" s="24" t="n">
+      <c r="G115" s="8" t="n">
         <v>-158</v>
       </c>
-      <c r="H115" s="26" t="n">
+      <c r="H115" s="10" t="n">
         <v>0.677</v>
       </c>
-      <c r="I115" s="26" t="n">
+      <c r="I115" s="10" t="n">
         <v>0.6124000000000001</v>
       </c>
-      <c r="J115" s="26" t="n">
+      <c r="J115" s="10" t="n">
         <v>0.0646</v>
       </c>
-      <c r="K115" s="27" t="n">
+      <c r="K115" s="11" t="n">
         <v>4.869</v>
       </c>
-      <c r="L115" s="25" t="n">
+      <c r="L115" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="M115" s="27" t="n">
+      <c r="M115" s="11" t="n">
         <v>0.42</v>
       </c>
-      <c r="N115" s="24" t="n">
+      <c r="N115" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="O115" s="28" t="inlineStr">
+      <c r="O115" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P115" s="29" t="n">
+      <c r="P115" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="116" ht="17" customHeight="1">
-      <c r="A116" s="14" t="n">
+      <c r="A116" s="22" t="n">
         <v>46108</v>
       </c>
-      <c r="B116" s="15" t="inlineStr">
+      <c r="B116" s="23" t="inlineStr">
         <is>
           <t>Robbie Ray</t>
         </is>
       </c>
-      <c r="C116" s="16" t="inlineStr">
+      <c r="C116" s="24" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="D116" s="16" t="inlineStr">
+      <c r="D116" s="24" t="inlineStr">
         <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E116" s="17" t="n">
+      <c r="E116" s="25" t="n">
         <v>5.5</v>
       </c>
-      <c r="F116" s="16" t="inlineStr">
+      <c r="F116" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G116" s="16" t="n">
+      <c r="G116" s="24" t="n">
         <v>116</v>
       </c>
-      <c r="H116" s="18" t="n">
+      <c r="H116" s="26" t="n">
         <v>0.532</v>
       </c>
-      <c r="I116" s="18" t="n">
+      <c r="I116" s="26" t="n">
         <v>0.463</v>
       </c>
-      <c r="J116" s="18" t="n">
+      <c r="J116" s="26" t="n">
         <v>0.06900000000000001</v>
       </c>
-      <c r="K116" s="19" t="n">
+      <c r="K116" s="27" t="n">
         <v>5.578</v>
       </c>
-      <c r="L116" s="17" t="n">
+      <c r="L116" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M116" s="19" t="n">
+      <c r="M116" s="27" t="n">
         <v>0.32</v>
       </c>
-      <c r="N116" s="16" t="n">
+      <c r="N116" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="O116" s="20" t="inlineStr">
+      <c r="O116" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P116" s="21" t="n">
+      <c r="P116" s="29" t="n">
         <v>1.16</v>
       </c>
     </row>
     <row r="117" ht="17" customHeight="1">
-      <c r="A117" s="14" t="n">
+      <c r="A117" s="22" t="n">
         <v>46108</v>
       </c>
-      <c r="B117" s="15" t="inlineStr">
+      <c r="B117" s="23" t="inlineStr">
         <is>
           <t>Cam Schlittler</t>
         </is>
       </c>
-      <c r="C117" s="16" t="inlineStr">
+      <c r="C117" s="24" t="inlineStr">
         <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="D117" s="16" t="inlineStr">
+      <c r="D117" s="24" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="E117" s="17" t="n">
+      <c r="E117" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F117" s="16" t="inlineStr">
+      <c r="F117" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G117" s="16" t="n">
+      <c r="G117" s="24" t="n">
         <v>-128</v>
       </c>
-      <c r="H117" s="18" t="n">
+      <c r="H117" s="26" t="n">
         <v>0.659</v>
       </c>
-      <c r="I117" s="18" t="n">
+      <c r="I117" s="26" t="n">
         <v>0.5614</v>
       </c>
-      <c r="J117" s="18" t="n">
+      <c r="J117" s="26" t="n">
         <v>0.09760000000000001</v>
       </c>
-      <c r="K117" s="19" t="n">
+      <c r="K117" s="27" t="n">
         <v>5.818</v>
       </c>
-      <c r="L117" s="17" t="n">
+      <c r="L117" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="M117" s="19" t="n">
+      <c r="M117" s="27" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="N117" s="16" t="n">
+      <c r="N117" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="O117" s="20" t="inlineStr">
+      <c r="O117" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P117" s="21" t="n">
+      <c r="P117" s="29" t="n">
         <v>0.7812</v>
       </c>
     </row>
     <row r="118" ht="17" customHeight="1">
-      <c r="A118" s="22" t="n">
+      <c r="A118" s="6" t="n">
         <v>46107</v>
       </c>
-      <c r="B118" s="23" t="inlineStr">
+      <c r="B118" s="7" t="inlineStr">
         <is>
           <t>Shane Smith</t>
         </is>
       </c>
-      <c r="C118" s="24" t="inlineStr">
+      <c r="C118" s="8" t="inlineStr">
         <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="D118" s="24" t="inlineStr">
+      <c r="D118" s="8" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E118" s="25" t="n">
+      <c r="E118" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F118" s="24" t="inlineStr">
+      <c r="F118" s="8" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G118" s="24" t="n">
+      <c r="G118" s="8" t="n">
         <v>-114</v>
       </c>
-      <c r="H118" s="26" t="n">
+      <c r="H118" s="10" t="n">
         <v>0.607</v>
       </c>
-      <c r="I118" s="26" t="n">
+      <c r="I118" s="10" t="n">
         <v>0.5327</v>
       </c>
-      <c r="J118" s="26" t="n">
+      <c r="J118" s="10" t="n">
         <v>0.0743</v>
       </c>
-      <c r="K118" s="27" t="n">
+      <c r="K118" s="11" t="n">
         <v>5.338</v>
       </c>
-      <c r="L118" s="25" t="n">
+      <c r="L118" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="M118" s="27" t="n">
+      <c r="M118" s="11" t="n">
         <v>0.4</v>
       </c>
-      <c r="N118" s="24" t="n">
+      <c r="N118" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="O118" s="28" t="inlineStr">
+      <c r="O118" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P118" s="29" t="n">
+      <c r="P118" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="119" ht="17" customHeight="1">
-      <c r="A119" s="22" t="n">
+      <c r="A119" s="6" t="n">
         <v>46107</v>
       </c>
-      <c r="B119" s="23" t="inlineStr">
+      <c r="B119" s="7" t="inlineStr">
         <is>
           <t>Hunter Brown</t>
         </is>
       </c>
-      <c r="C119" s="24" t="inlineStr">
+      <c r="C119" s="8" t="inlineStr">
         <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="D119" s="24" t="inlineStr">
+      <c r="D119" s="8" t="inlineStr">
         <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="E119" s="25" t="n">
+      <c r="E119" s="9" t="n">
         <v>6.5</v>
       </c>
-      <c r="F119" s="24" t="inlineStr">
+      <c r="F119" s="8" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G119" s="24" t="n">
+      <c r="G119" s="8" t="n">
         <v>114</v>
       </c>
-      <c r="H119" s="26" t="n">
+      <c r="H119" s="10" t="n">
         <v>0.587</v>
       </c>
-      <c r="I119" s="26" t="n">
+      <c r="I119" s="10" t="n">
         <v>0.4673</v>
       </c>
-      <c r="J119" s="26" t="n">
+      <c r="J119" s="10" t="n">
         <v>0.1197</v>
       </c>
-      <c r="K119" s="27" t="n">
+      <c r="K119" s="11" t="n">
         <v>6.417</v>
       </c>
-      <c r="L119" s="25" t="n">
+      <c r="L119" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="M119" s="27" t="n">
+      <c r="M119" s="11" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="N119" s="24" t="n">
+      <c r="N119" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="O119" s="28" t="inlineStr">
+      <c r="O119" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P119" s="29" t="n">
+      <c r="P119" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="120" ht="17" customHeight="1">
-      <c r="A120" s="14" t="n">
+      <c r="A120" s="22" t="n">
         <v>46107</v>
       </c>
-      <c r="B120" s="15" t="inlineStr">
+      <c r="B120" s="23" t="inlineStr">
         <is>
           <t>José Soriano</t>
         </is>
       </c>
-      <c r="C120" s="16" t="inlineStr">
+      <c r="C120" s="24" t="inlineStr">
         <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="D120" s="16" t="inlineStr">
+      <c r="D120" s="24" t="inlineStr">
         <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E120" s="17" t="n">
+      <c r="E120" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F120" s="16" t="inlineStr">
+      <c r="F120" s="24" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G120" s="16" t="n">
+      <c r="G120" s="24" t="n">
         <v>108</v>
       </c>
-      <c r="H120" s="18" t="n">
+      <c r="H120" s="26" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="I120" s="18" t="n">
+      <c r="I120" s="26" t="n">
         <v>0.4808</v>
       </c>
-      <c r="J120" s="18" t="n">
+      <c r="J120" s="26" t="n">
         <v>0.07920000000000001</v>
       </c>
-      <c r="K120" s="19" t="n">
+      <c r="K120" s="27" t="n">
         <v>5.163</v>
       </c>
-      <c r="L120" s="17" t="n">
+      <c r="L120" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="M120" s="19" t="n">
+      <c r="M120" s="27" t="n">
         <v>0.38</v>
       </c>
-      <c r="N120" s="16" t="n">
+      <c r="N120" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="O120" s="20" t="inlineStr">
+      <c r="O120" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P120" s="21" t="n">
+      <c r="P120" s="29" t="n">
         <v>1.08</v>
       </c>
     </row>
     <row r="121" ht="17" customHeight="1">
-      <c r="A121" s="14" t="n">
+      <c r="A121" s="22" t="n">
         <v>46107</v>
       </c>
-      <c r="B121" s="15" t="inlineStr">
+      <c r="B121" s="23" t="inlineStr">
         <is>
           <t>Tarik Skubal</t>
         </is>
       </c>
-      <c r="C121" s="16" t="inlineStr">
+      <c r="C121" s="24" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="D121" s="16" t="inlineStr">
+      <c r="D121" s="24" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E121" s="17" t="n">
+      <c r="E121" s="25" t="n">
         <v>7.5</v>
       </c>
-      <c r="F121" s="16" t="inlineStr">
+      <c r="F121" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G121" s="16" t="n">
+      <c r="G121" s="24" t="n">
         <v>-172</v>
       </c>
-      <c r="H121" s="18" t="n">
+      <c r="H121" s="26" t="n">
         <v>0.767</v>
       </c>
-      <c r="I121" s="18" t="n">
+      <c r="I121" s="26" t="n">
         <v>0.6324</v>
       </c>
-      <c r="J121" s="18" t="n">
+      <c r="J121" s="26" t="n">
         <v>0.1346</v>
       </c>
-      <c r="K121" s="19" t="n">
+      <c r="K121" s="27" t="n">
         <v>5.68</v>
       </c>
-      <c r="L121" s="17" t="n">
+      <c r="L121" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="M121" s="19" t="n">
+      <c r="M121" s="27" t="n">
         <v>0.92</v>
       </c>
-      <c r="N121" s="16" t="n">
+      <c r="N121" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="O121" s="20" t="inlineStr">
+      <c r="O121" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P121" s="21" t="n">
+      <c r="P121" s="29" t="n">
         <v>0.5814</v>
       </c>
     </row>
     <row r="122" ht="17" customHeight="1">
-      <c r="A122" s="22" t="n">
+      <c r="A122" s="6" t="n">
         <v>46107</v>
       </c>
-      <c r="B122" s="23" t="inlineStr">
+      <c r="B122" s="7" t="inlineStr">
         <is>
           <t>Jacob Misiorowski</t>
         </is>
       </c>
-      <c r="C122" s="24" t="inlineStr">
+      <c r="C122" s="8" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="D122" s="24" t="inlineStr">
+      <c r="D122" s="8" t="inlineStr">
         <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E122" s="25" t="n">
+      <c r="E122" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="F122" s="24" t="inlineStr">
+      <c r="F122" s="8" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G122" s="24" t="n">
+      <c r="G122" s="8" t="n">
         <v>124</v>
       </c>
-      <c r="H122" s="26" t="n">
+      <c r="H122" s="10" t="n">
         <v>0.52</v>
       </c>
-      <c r="I122" s="26" t="n">
+      <c r="I122" s="10" t="n">
         <v>0.4464</v>
       </c>
-      <c r="J122" s="26" t="n">
+      <c r="J122" s="10" t="n">
         <v>0.0736</v>
       </c>
-      <c r="K122" s="27" t="n">
+      <c r="K122" s="11" t="n">
         <v>5.5</v>
       </c>
-      <c r="L122" s="25" t="n">
+      <c r="L122" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="M122" s="27" t="n">
+      <c r="M122" s="11" t="n">
         <v>0.33</v>
       </c>
-      <c r="N122" s="24" t="n">
+      <c r="N122" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="O122" s="28" t="inlineStr">
+      <c r="O122" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P122" s="29" t="n">
+      <c r="P122" s="13" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="123" ht="17" customHeight="1">
-      <c r="A123" s="14" t="n">
+      <c r="A123" s="22" t="n">
         <v>46107</v>
       </c>
-      <c r="B123" s="15" t="inlineStr">
+      <c r="B123" s="23" t="inlineStr">
         <is>
           <t>Nick Pivetta</t>
         </is>
       </c>
-      <c r="C123" s="16" t="inlineStr">
+      <c r="C123" s="24" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="D123" s="16" t="inlineStr">
+      <c r="D123" s="24" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="E123" s="17" t="n">
+      <c r="E123" s="25" t="n">
         <v>5.5</v>
       </c>
-      <c r="F123" s="16" t="inlineStr">
+      <c r="F123" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G123" s="16" t="n">
+      <c r="G123" s="24" t="n">
         <v>110</v>
       </c>
-      <c r="H123" s="18" t="n">
+      <c r="H123" s="26" t="n">
         <v>0.54</v>
       </c>
-      <c r="I123" s="18" t="n">
+      <c r="I123" s="26" t="n">
         <v>0.4762</v>
       </c>
-      <c r="J123" s="18" t="n">
+      <c r="J123" s="26" t="n">
         <v>0.0638</v>
       </c>
-      <c r="K123" s="19" t="n">
+      <c r="K123" s="27" t="n">
         <v>5.548</v>
       </c>
-      <c r="L123" s="17" t="n">
+      <c r="L123" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M123" s="19" t="n">
+      <c r="M123" s="27" t="n">
         <v>0.3</v>
       </c>
-      <c r="N123" s="16" t="n">
+      <c r="N123" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="O123" s="20" t="inlineStr">
+      <c r="O123" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P123" s="21" t="n">
+      <c r="P123" s="29" t="n">
         <v>1.1</v>
       </c>
     </row>
     <row r="124" ht="17" customHeight="1">
-      <c r="A124" s="14" t="n">
+      <c r="A124" s="22" t="n">
         <v>46107</v>
       </c>
-      <c r="B124" s="15" t="inlineStr">
+      <c r="B124" s="23" t="inlineStr">
         <is>
           <t>Andrew Abbott</t>
         </is>
       </c>
-      <c r="C124" s="16" t="inlineStr">
+      <c r="C124" s="24" t="inlineStr">
         <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="D124" s="16" t="inlineStr">
+      <c r="D124" s="24" t="inlineStr">
         <is>
           <t>BOS</t>
         </is>
       </c>
-      <c r="E124" s="17" t="n">
+      <c r="E124" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="F124" s="16" t="inlineStr">
+      <c r="F124" s="24" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G124" s="16" t="n">
+      <c r="G124" s="24" t="n">
         <v>120</v>
       </c>
-      <c r="H124" s="18" t="n">
+      <c r="H124" s="26" t="n">
         <v>0.509</v>
       </c>
-      <c r="I124" s="18" t="n">
+      <c r="I124" s="26" t="n">
         <v>0.4545</v>
       </c>
-      <c r="J124" s="18" t="n">
+      <c r="J124" s="26" t="n">
         <v>0.0545</v>
       </c>
-      <c r="K124" s="19" t="n">
+      <c r="K124" s="27" t="n">
         <v>4.814</v>
       </c>
-      <c r="L124" s="17" t="n">
+      <c r="L124" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="M124" s="19" t="n">
+      <c r="M124" s="27" t="n">
         <v>0.25</v>
       </c>
-      <c r="N124" s="16" t="n">
+      <c r="N124" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="O124" s="20" t="inlineStr">
+      <c r="O124" s="28" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="P124" s="21" t="n">
+      <c r="P124" s="29" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="125" ht="17" customHeight="1">
-      <c r="A125" s="22" t="n">
+      <c r="A125" s="6" t="n">
         <v>46107</v>
       </c>
-      <c r="B125" s="23" t="inlineStr">
+      <c r="B125" s="7" t="inlineStr">
         <is>
           <t>Matthew Boyd</t>
         </is>
       </c>
-      <c r="C125" s="24" t="inlineStr">
+      <c r="C125" s="8" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="D125" s="24" t="inlineStr">
+      <c r="D125" s="8" t="inlineStr">
         <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E125" s="25" t="n">
+      <c r="E125" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F125" s="24" t="inlineStr">
+      <c r="F125" s="8" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G125" s="24" t="n">
+      <c r="G125" s="8" t="n">
         <v>132</v>
       </c>
-      <c r="H125" s="26" t="n">
+      <c r="H125" s="10" t="n">
         <v>0.59</v>
       </c>
-      <c r="I125" s="26" t="n">
+      <c r="I125" s="10" t="n">
         <v>0.431</v>
       </c>
-      <c r="J125" s="26" t="n">
+      <c r="J125" s="10" t="n">
         <v>0.159</v>
       </c>
-      <c r="K125" s="27" t="n">
+      <c r="K125" s="11" t="n">
         <v>4.258</v>
       </c>
-      <c r="L125" s="25" t="n">
+      <c r="L125" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="M125" s="27" t="n">
+      <c r="M125" s="11" t="n">
         <v>0.7</v>
       </c>
-      <c r="N125" s="24" t="n">
+      <c r="N125" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="O125" s="28" t="inlineStr">
+      <c r="O125" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P125" s="29" t="n">
+      <c r="P125" s="13" t="n">
         <v>-1</v>
       </c>
     </row>

--- a/bet_log.xlsx
+++ b/bet_log.xlsx
@@ -806,17 +806,17 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Lance McCullers Jr.</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
@@ -824,29 +824,29 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G6" s="8" t="n">
-        <v>118</v>
+        <v>-132</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>0.511</v>
+        <v>0.62</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.4587</v>
+        <v>0.569</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.0523</v>
+        <v>0.051</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>4.775</v>
+        <v>5.461</v>
       </c>
       <c r="L6" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="N6" s="8" t="inlineStr"/>
       <c r="O6" s="12" t="inlineStr"/>
@@ -858,21 +858,21 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Brayan Bello</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
@@ -880,25 +880,25 @@
         </is>
       </c>
       <c r="G7" s="8" t="n">
-        <v>-154</v>
+        <v>-130</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.661</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>0.6063</v>
+        <v>0.5652</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.0837</v>
+        <v>0.0958</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>5.481</v>
+        <v>3.92</v>
       </c>
       <c r="L7" s="9" t="n">
         <v>1</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="N7" s="8" t="inlineStr"/>
       <c r="O7" s="12" t="inlineStr"/>
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="G8" s="8" t="n">
-        <v>-118</v>
+        <v>-112</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>0.729</v>
+        <v>0.73</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>0.5413</v>
+        <v>0.5283</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.1877</v>
+        <v>0.2017</v>
       </c>
       <c r="K8" s="11" t="n">
         <v>6.095</v>
@@ -950,7 +950,7 @@
         <v>2</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="N8" s="8" t="inlineStr"/>
       <c r="O8" s="12" t="inlineStr"/>
@@ -987,22 +987,22 @@
         <v>102</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.63</v>
+        <v>0.648</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>0.495</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.135</v>
+        <v>0.153</v>
       </c>
       <c r="K9" s="11" t="n">
         <v>4.555</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.67</v>
+        <v>0.76</v>
       </c>
       <c r="N9" s="8" t="inlineStr"/>
       <c r="O9" s="12" t="inlineStr"/>
@@ -1014,47 +1014,47 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Max Scherzer</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G10" s="8" t="n">
-        <v>-136</v>
+        <v>-140</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>0.709</v>
+        <v>0.736</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>0.5763</v>
+        <v>0.5833</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.1327</v>
+        <v>0.1527</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>5.079</v>
+        <v>5.235</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="N10" s="8" t="inlineStr"/>
       <c r="O10" s="12" t="inlineStr"/>
@@ -1066,47 +1066,47 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Max Scherzer</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G11" s="8" t="n">
-        <v>124</v>
+        <v>-138</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.578</v>
+        <v>0.726</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>0.4464</v>
+        <v>0.5798</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.1316</v>
+        <v>0.1462</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>5.235</v>
+        <v>5.079</v>
       </c>
       <c r="L11" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.59</v>
+        <v>0.87</v>
       </c>
       <c r="N11" s="8" t="inlineStr"/>
       <c r="O11" s="12" t="inlineStr"/>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Brayan Bello</t>
+          <t>Brandon Woodruff</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="G12" s="8" t="n">
-        <v>-130</v>
+        <v>132</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>0.662</v>
+        <v>0.528</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>0.5652</v>
+        <v>0.431</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.0968</v>
+        <v>0.097</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>3.92</v>
+        <v>6.004</v>
       </c>
       <c r="L12" s="9" t="n">
         <v>1</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="N12" s="8" t="inlineStr"/>
       <c r="O12" s="12" t="inlineStr"/>
@@ -1192,16 +1192,16 @@
         </is>
       </c>
       <c r="G13" s="8" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="H13" s="10" t="n">
         <v>0.639</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>0.5192</v>
+        <v>0.5238</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.1198</v>
+        <v>0.1152</v>
       </c>
       <c r="K13" s="11" t="n">
         <v>6.563</v>
@@ -1210,7 +1210,7 @@
         <v>1.5</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="N13" s="8" t="inlineStr"/>
       <c r="O13" s="12" t="inlineStr"/>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
@@ -1244,25 +1244,25 @@
         </is>
       </c>
       <c r="G14" s="8" t="n">
-        <v>110</v>
+        <v>-154</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>0.4762</v>
+        <v>0.6063</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.0828</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>6.246</v>
+        <v>5.481</v>
       </c>
       <c r="L14" s="9" t="n">
         <v>1</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.4</v>
+        <v>0.52</v>
       </c>
       <c r="N14" s="8" t="inlineStr"/>
       <c r="O14" s="12" t="inlineStr"/>
@@ -1274,47 +1274,47 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Germán Márquez</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G15" s="8" t="n">
-        <v>-104</v>
+        <v>108</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.588</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>0.5098</v>
+        <v>0.4808</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>4.209</v>
+        <v>6.246</v>
       </c>
       <c r="L15" s="9" t="n">
         <v>1</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="N15" s="8" t="inlineStr"/>
       <c r="O15" s="12" t="inlineStr"/>
@@ -1326,21 +1326,21 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Brandon Woodruff</t>
+          <t>Andre Pallante</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
@@ -1348,25 +1348,25 @@
         </is>
       </c>
       <c r="G16" s="8" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>0.528</v>
+        <v>0.518</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>0.4545</v>
+        <v>0.4386</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.0735</v>
+        <v>0.0794</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>6.004</v>
+        <v>3.825</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="N16" s="8" t="inlineStr"/>
       <c r="O16" s="12" t="inlineStr"/>
@@ -1378,17 +1378,17 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Andre Pallante</t>
+          <t>Germán Márquez</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
@@ -1400,25 +1400,25 @@
         </is>
       </c>
       <c r="G17" s="8" t="n">
-        <v>118</v>
+        <v>-104</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>0.519</v>
+        <v>0.588</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>0.4587</v>
+        <v>0.5098</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.0603</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>3.825</v>
+        <v>4.209</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="N17" s="8" t="inlineStr"/>
       <c r="O17" s="12" t="inlineStr"/>
@@ -1455,13 +1455,13 @@
         <v>110</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>0.533</v>
+        <v>0.531</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>0.4762</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.0568</v>
+        <v>0.0548</v>
       </c>
       <c r="K18" s="11" t="n">
         <v>4.509</v>
@@ -1470,7 +1470,7 @@
         <v>0.5</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="N18" s="8" t="inlineStr"/>
       <c r="O18" s="12" t="inlineStr"/>
@@ -1482,17 +1482,17 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Lance McCullers Jr.</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
@@ -1500,29 +1500,29 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="G19" s="8" t="n">
-        <v>-130</v>
+        <v>118</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>0.62</v>
+        <v>0.51</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>0.5652</v>
+        <v>0.4587</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.0548</v>
+        <v>0.0513</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>5.461</v>
+        <v>4.775</v>
       </c>
       <c r="L19" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>0.31</v>
+        <v>0.24</v>
       </c>
       <c r="N19" s="8" t="inlineStr"/>
       <c r="O19" s="12" t="inlineStr"/>
